--- a/artifacts/Rental Specimen.xlsx
+++ b/artifacts/Rental Specimen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z0050s8t\Documents\rental-automation\artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F25104F-C71D-4633-AD76-9B24C06CDD41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3456925D-0E1E-4700-BBF5-B0EA0C94CFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="735" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="16" state="hidden" r:id="rId1"/>
@@ -5009,7 +5009,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="788">
+  <cellXfs count="782">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -6299,436 +6299,26 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="25" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="26" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="4" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="54" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="6" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="55" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="50" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="33" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="29" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="192" fontId="54" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="76" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="77" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="78" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="79" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6738,55 +6328,457 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="10" fillId="14" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="102" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="33" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="29" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="25" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="26" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="4" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="54" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="6" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="55" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="50" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="192" fontId="54" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="76" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="77" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="78" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="79" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1012">
     <cellStyle name="??" xfId="303" xr:uid="{91225FB4-C7AB-4245-B40E-51FA489A4ADF}"/>
@@ -9699,7 +9691,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="636" t="s">
+      <c r="A1" s="645" t="s">
         <v>299</v>
       </c>
       <c r="B1" s="400" t="s">
@@ -9719,7 +9711,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="636"/>
+      <c r="A2" s="645"/>
       <c r="B2" s="403" t="s">
         <v>238</v>
       </c>
@@ -10184,22 +10176,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="16" thickBot="1">
-      <c r="A1" s="736" t="s">
+      <c r="A1" s="769" t="s">
         <v>262</v>
       </c>
-      <c r="B1" s="737"/>
-      <c r="C1" s="737"/>
-      <c r="D1" s="737"/>
-      <c r="E1" s="737"/>
-      <c r="F1" s="737"/>
-      <c r="G1" s="737"/>
-      <c r="H1" s="737"/>
-      <c r="I1" s="737"/>
-      <c r="J1" s="737"/>
-      <c r="K1" s="737"/>
-      <c r="L1" s="737"/>
-      <c r="M1" s="737"/>
-      <c r="N1" s="738"/>
+      <c r="B1" s="770"/>
+      <c r="C1" s="770"/>
+      <c r="D1" s="770"/>
+      <c r="E1" s="770"/>
+      <c r="F1" s="770"/>
+      <c r="G1" s="770"/>
+      <c r="H1" s="770"/>
+      <c r="I1" s="770"/>
+      <c r="J1" s="770"/>
+      <c r="K1" s="770"/>
+      <c r="L1" s="770"/>
+      <c r="M1" s="770"/>
+      <c r="N1" s="771"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="178" t="s">
@@ -11225,21 +11217,21 @@
       <c r="I34" s="358"/>
     </row>
     <row r="35" spans="1:15" ht="16" outlineLevel="1" thickBot="1">
-      <c r="A35" s="736"/>
-      <c r="B35" s="737"/>
-      <c r="C35" s="737"/>
-      <c r="D35" s="737"/>
-      <c r="E35" s="737"/>
-      <c r="F35" s="737"/>
-      <c r="G35" s="737"/>
-      <c r="H35" s="737"/>
-      <c r="I35" s="737"/>
-      <c r="J35" s="737"/>
-      <c r="K35" s="737"/>
-      <c r="L35" s="737"/>
-      <c r="M35" s="737"/>
-      <c r="N35" s="737"/>
-      <c r="O35" s="738"/>
+      <c r="A35" s="769"/>
+      <c r="B35" s="770"/>
+      <c r="C35" s="770"/>
+      <c r="D35" s="770"/>
+      <c r="E35" s="770"/>
+      <c r="F35" s="770"/>
+      <c r="G35" s="770"/>
+      <c r="H35" s="770"/>
+      <c r="I35" s="770"/>
+      <c r="J35" s="770"/>
+      <c r="K35" s="770"/>
+      <c r="L35" s="770"/>
+      <c r="M35" s="770"/>
+      <c r="N35" s="770"/>
+      <c r="O35" s="771"/>
     </row>
     <row r="36" spans="1:15" outlineLevel="1">
       <c r="A36" s="306" t="s">
@@ -13029,21 +13021,21 @@
       <c r="I91" s="186"/>
     </row>
     <row r="92" spans="1:15" ht="16" thickBot="1">
-      <c r="A92" s="739"/>
-      <c r="B92" s="740"/>
-      <c r="C92" s="740"/>
-      <c r="D92" s="740"/>
-      <c r="E92" s="740"/>
-      <c r="F92" s="740"/>
-      <c r="G92" s="740"/>
-      <c r="H92" s="740"/>
-      <c r="I92" s="740"/>
-      <c r="J92" s="740"/>
-      <c r="K92" s="740"/>
-      <c r="L92" s="740"/>
-      <c r="M92" s="740"/>
-      <c r="N92" s="740"/>
-      <c r="O92" s="741"/>
+      <c r="A92" s="772"/>
+      <c r="B92" s="773"/>
+      <c r="C92" s="773"/>
+      <c r="D92" s="773"/>
+      <c r="E92" s="773"/>
+      <c r="F92" s="773"/>
+      <c r="G92" s="773"/>
+      <c r="H92" s="773"/>
+      <c r="I92" s="773"/>
+      <c r="J92" s="773"/>
+      <c r="K92" s="773"/>
+      <c r="L92" s="773"/>
+      <c r="M92" s="773"/>
+      <c r="N92" s="773"/>
+      <c r="O92" s="774"/>
     </row>
     <row r="93" spans="1:15">
       <c r="A93" s="178"/>
@@ -13513,93 +13505,93 @@
     </row>
     <row r="3" spans="1:31">
       <c r="A3" s="258"/>
-      <c r="B3" s="742" t="s">
+      <c r="B3" s="775" t="s">
         <v>473</v>
       </c>
-      <c r="C3" s="743"/>
-      <c r="D3" s="743"/>
-      <c r="E3" s="743"/>
-      <c r="F3" s="744"/>
-      <c r="G3" s="742" t="s">
+      <c r="C3" s="776"/>
+      <c r="D3" s="776"/>
+      <c r="E3" s="776"/>
+      <c r="F3" s="777"/>
+      <c r="G3" s="775" t="s">
         <v>473</v>
       </c>
-      <c r="H3" s="743"/>
-      <c r="I3" s="743"/>
-      <c r="J3" s="743"/>
-      <c r="K3" s="744"/>
-      <c r="L3" s="742" t="s">
+      <c r="H3" s="776"/>
+      <c r="I3" s="776"/>
+      <c r="J3" s="776"/>
+      <c r="K3" s="777"/>
+      <c r="L3" s="775" t="s">
         <v>473</v>
       </c>
-      <c r="M3" s="743"/>
-      <c r="N3" s="743"/>
-      <c r="O3" s="743"/>
-      <c r="P3" s="744"/>
-      <c r="Q3" s="742" t="s">
+      <c r="M3" s="776"/>
+      <c r="N3" s="776"/>
+      <c r="O3" s="776"/>
+      <c r="P3" s="777"/>
+      <c r="Q3" s="775" t="s">
         <v>473</v>
       </c>
-      <c r="R3" s="743"/>
-      <c r="S3" s="743"/>
-      <c r="T3" s="743"/>
-      <c r="U3" s="744"/>
-      <c r="V3" s="742" t="s">
+      <c r="R3" s="776"/>
+      <c r="S3" s="776"/>
+      <c r="T3" s="776"/>
+      <c r="U3" s="777"/>
+      <c r="V3" s="775" t="s">
         <v>473</v>
       </c>
-      <c r="W3" s="743"/>
-      <c r="X3" s="743"/>
-      <c r="Y3" s="743"/>
-      <c r="Z3" s="744"/>
-      <c r="AA3" s="742" t="s">
+      <c r="W3" s="776"/>
+      <c r="X3" s="776"/>
+      <c r="Y3" s="776"/>
+      <c r="Z3" s="777"/>
+      <c r="AA3" s="775" t="s">
         <v>473</v>
       </c>
-      <c r="AB3" s="743"/>
-      <c r="AC3" s="743"/>
-      <c r="AD3" s="743"/>
-      <c r="AE3" s="744"/>
+      <c r="AB3" s="776"/>
+      <c r="AC3" s="776"/>
+      <c r="AD3" s="776"/>
+      <c r="AE3" s="777"/>
     </row>
     <row r="4" spans="1:31" ht="13.25" customHeight="1">
       <c r="A4" s="258"/>
-      <c r="B4" s="745" t="s">
+      <c r="B4" s="778" t="s">
         <v>474</v>
       </c>
-      <c r="C4" s="746"/>
-      <c r="D4" s="746"/>
-      <c r="E4" s="746"/>
-      <c r="F4" s="747"/>
-      <c r="G4" s="745" t="s">
+      <c r="C4" s="779"/>
+      <c r="D4" s="779"/>
+      <c r="E4" s="779"/>
+      <c r="F4" s="780"/>
+      <c r="G4" s="778" t="s">
         <v>474</v>
       </c>
-      <c r="H4" s="746"/>
-      <c r="I4" s="746"/>
-      <c r="J4" s="746"/>
-      <c r="K4" s="747"/>
-      <c r="L4" s="745" t="s">
+      <c r="H4" s="779"/>
+      <c r="I4" s="779"/>
+      <c r="J4" s="779"/>
+      <c r="K4" s="780"/>
+      <c r="L4" s="778" t="s">
         <v>474</v>
       </c>
-      <c r="M4" s="746"/>
-      <c r="N4" s="746"/>
-      <c r="O4" s="746"/>
-      <c r="P4" s="747"/>
-      <c r="Q4" s="745" t="s">
+      <c r="M4" s="779"/>
+      <c r="N4" s="779"/>
+      <c r="O4" s="779"/>
+      <c r="P4" s="780"/>
+      <c r="Q4" s="778" t="s">
         <v>474</v>
       </c>
-      <c r="R4" s="746"/>
-      <c r="S4" s="746"/>
-      <c r="T4" s="746"/>
-      <c r="U4" s="747"/>
-      <c r="V4" s="745" t="s">
+      <c r="R4" s="779"/>
+      <c r="S4" s="779"/>
+      <c r="T4" s="779"/>
+      <c r="U4" s="780"/>
+      <c r="V4" s="778" t="s">
         <v>474</v>
       </c>
-      <c r="W4" s="746"/>
-      <c r="X4" s="746"/>
-      <c r="Y4" s="746"/>
-      <c r="Z4" s="747"/>
-      <c r="AA4" s="745" t="s">
+      <c r="W4" s="779"/>
+      <c r="X4" s="779"/>
+      <c r="Y4" s="779"/>
+      <c r="Z4" s="780"/>
+      <c r="AA4" s="778" t="s">
         <v>474</v>
       </c>
-      <c r="AB4" s="746"/>
-      <c r="AC4" s="746"/>
-      <c r="AD4" s="746"/>
-      <c r="AE4" s="748"/>
+      <c r="AB4" s="779"/>
+      <c r="AC4" s="779"/>
+      <c r="AD4" s="779"/>
+      <c r="AE4" s="781"/>
     </row>
     <row r="5" spans="1:31" ht="13">
       <c r="A5" s="450" t="s">
@@ -15284,18 +15276,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G3:K3"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="L3:P3"/>
+    <mergeCell ref="L4:P4"/>
     <mergeCell ref="V3:Z3"/>
     <mergeCell ref="V4:Z4"/>
     <mergeCell ref="AA3:AE3"/>
     <mergeCell ref="AA4:AE4"/>
     <mergeCell ref="Q3:U3"/>
     <mergeCell ref="Q4:U4"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G3:K3"/>
-    <mergeCell ref="G4:K4"/>
-    <mergeCell ref="L3:P3"/>
-    <mergeCell ref="L4:P4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <customProperties>
@@ -15498,62 +15490,62 @@
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1">
       <c r="A1" s="51"/>
-      <c r="B1" s="686"/>
-      <c r="C1" s="687"/>
-      <c r="D1" s="687"/>
-      <c r="E1" s="687"/>
-      <c r="F1" s="687"/>
-      <c r="G1" s="687"/>
-      <c r="H1" s="687"/>
-      <c r="I1" s="687"/>
-      <c r="J1" s="688"/>
+      <c r="B1" s="685"/>
+      <c r="C1" s="686"/>
+      <c r="D1" s="686"/>
+      <c r="E1" s="686"/>
+      <c r="F1" s="686"/>
+      <c r="G1" s="686"/>
+      <c r="H1" s="686"/>
+      <c r="I1" s="686"/>
+      <c r="J1" s="687"/>
     </row>
     <row r="2" spans="1:10" ht="14.25" customHeight="1">
       <c r="A2" s="51"/>
-      <c r="B2" s="689"/>
-      <c r="C2" s="690"/>
-      <c r="D2" s="690"/>
-      <c r="E2" s="690"/>
-      <c r="F2" s="690"/>
-      <c r="G2" s="690"/>
-      <c r="H2" s="690"/>
-      <c r="I2" s="690"/>
-      <c r="J2" s="691"/>
+      <c r="B2" s="688"/>
+      <c r="C2" s="689"/>
+      <c r="D2" s="689"/>
+      <c r="E2" s="689"/>
+      <c r="F2" s="689"/>
+      <c r="G2" s="689"/>
+      <c r="H2" s="689"/>
+      <c r="I2" s="689"/>
+      <c r="J2" s="690"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A3" s="51"/>
-      <c r="B3" s="692"/>
-      <c r="C3" s="693"/>
-      <c r="D3" s="693"/>
-      <c r="E3" s="693"/>
-      <c r="F3" s="693"/>
-      <c r="G3" s="693"/>
-      <c r="H3" s="693"/>
-      <c r="I3" s="690"/>
-      <c r="J3" s="691"/>
+      <c r="B3" s="691"/>
+      <c r="C3" s="692"/>
+      <c r="D3" s="692"/>
+      <c r="E3" s="692"/>
+      <c r="F3" s="692"/>
+      <c r="G3" s="692"/>
+      <c r="H3" s="692"/>
+      <c r="I3" s="689"/>
+      <c r="J3" s="690"/>
     </row>
     <row r="4" spans="1:10" ht="13">
       <c r="A4" s="51"/>
-      <c r="B4" s="616"/>
-      <c r="C4" s="617"/>
-      <c r="D4" s="617"/>
-      <c r="E4" s="617"/>
-      <c r="F4" s="617"/>
-      <c r="G4" s="617"/>
+      <c r="B4" s="710"/>
+      <c r="C4" s="711"/>
+      <c r="D4" s="711"/>
+      <c r="E4" s="711"/>
+      <c r="F4" s="711"/>
+      <c r="G4" s="711"/>
       <c r="H4" s="415"/>
       <c r="I4" s="416"/>
       <c r="J4" s="417"/>
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="51"/>
-      <c r="B5" s="713" t="s">
+      <c r="B5" s="712" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="714"/>
-      <c r="D5" s="714"/>
-      <c r="E5" s="714"/>
-      <c r="F5" s="714"/>
-      <c r="G5" s="715"/>
+      <c r="C5" s="713"/>
+      <c r="D5" s="713"/>
+      <c r="E5" s="713"/>
+      <c r="F5" s="713"/>
+      <c r="G5" s="714"/>
       <c r="H5" s="418"/>
       <c r="I5" s="546" t="s">
         <v>16</v>
@@ -15564,14 +15556,14 @@
     </row>
     <row r="6" spans="1:10" ht="13.5" thickBot="1">
       <c r="A6" s="51"/>
-      <c r="B6" s="716"/>
-      <c r="C6" s="717"/>
-      <c r="D6" s="718"/>
+      <c r="B6" s="715"/>
+      <c r="C6" s="716"/>
+      <c r="D6" s="717"/>
       <c r="E6" s="52"/>
-      <c r="F6" s="711">
+      <c r="F6" s="708">
         <v>10.763999999999999</v>
       </c>
-      <c r="G6" s="712"/>
+      <c r="G6" s="709"/>
       <c r="H6" s="419"/>
       <c r="I6" s="699">
         <v>10.763999999999999</v>
@@ -15583,10 +15575,10 @@
       <c r="B7" s="547" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="719" t="s">
+      <c r="C7" s="718" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="720"/>
+      <c r="D7" s="719"/>
       <c r="E7" s="548"/>
       <c r="F7" s="548" t="s">
         <v>477</v>
@@ -15614,23 +15606,23 @@
       <c r="C8" s="551"/>
       <c r="D8" s="552"/>
       <c r="E8" s="553"/>
-      <c r="F8" s="645" t="s">
+      <c r="F8" s="646" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="679"/>
+      <c r="G8" s="647"/>
       <c r="H8" s="418"/>
-      <c r="I8" s="680" t="s">
+      <c r="I8" s="648" t="s">
         <v>67</v>
       </c>
-      <c r="J8" s="681"/>
+      <c r="J8" s="649"/>
     </row>
     <row r="9" spans="1:10" ht="13">
       <c r="A9" s="51"/>
-      <c r="B9" s="680" t="s">
+      <c r="B9" s="648" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="679"/>
-      <c r="D9" s="646"/>
+      <c r="C9" s="647"/>
+      <c r="D9" s="663"/>
       <c r="E9" s="554"/>
       <c r="F9" s="376" t="s">
         <v>75</v>
@@ -15651,10 +15643,10 @@
       <c r="B10" s="555">
         <v>1</v>
       </c>
-      <c r="C10" s="694" t="s">
+      <c r="C10" s="693" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="653"/>
+      <c r="D10" s="694"/>
       <c r="E10" s="556"/>
       <c r="F10" s="705" t="s">
         <v>470</v>
@@ -15693,19 +15685,19 @@
         <f>1+B11</f>
         <v>3</v>
       </c>
-      <c r="C12" s="639" t="s">
+      <c r="C12" s="656" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="638"/>
+      <c r="D12" s="657"/>
       <c r="E12" s="557"/>
-      <c r="F12" s="707"/>
-      <c r="G12" s="708"/>
+      <c r="F12" s="684"/>
+      <c r="G12" s="679"/>
       <c r="H12" s="418"/>
-      <c r="I12" s="721">
+      <c r="I12" s="680">
         <f>+F12</f>
         <v>0</v>
       </c>
-      <c r="J12" s="722"/>
+      <c r="J12" s="681"/>
     </row>
     <row r="13" spans="1:10" ht="15.9" customHeight="1">
       <c r="A13" s="51"/>
@@ -15713,16 +15705,16 @@
         <f t="shared" ref="B13:B31" si="0">1+B12</f>
         <v>4</v>
       </c>
-      <c r="C13" s="639" t="s">
+      <c r="C13" s="656" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="638"/>
+      <c r="D13" s="657"/>
       <c r="E13" s="50"/>
-      <c r="F13" s="710"/>
-      <c r="G13" s="708"/>
+      <c r="F13" s="678"/>
+      <c r="G13" s="679"/>
       <c r="H13" s="418"/>
-      <c r="I13" s="721"/>
-      <c r="J13" s="722"/>
+      <c r="I13" s="680"/>
+      <c r="J13" s="681"/>
     </row>
     <row r="14" spans="1:10" ht="48" customHeight="1">
       <c r="A14" s="51"/>
@@ -15735,16 +15727,16 @@
       </c>
       <c r="D14" s="698"/>
       <c r="E14" s="539"/>
-      <c r="F14" s="707" t="s">
+      <c r="F14" s="684" t="s">
         <v>471</v>
       </c>
-      <c r="G14" s="709"/>
+      <c r="G14" s="707"/>
       <c r="H14" s="418"/>
-      <c r="I14" s="721" t="str">
+      <c r="I14" s="680" t="str">
         <f>+F14</f>
         <v>6th floor</v>
       </c>
-      <c r="J14" s="722"/>
+      <c r="J14" s="681"/>
     </row>
     <row r="15" spans="1:10" ht="51.75" customHeight="1">
       <c r="A15" s="51"/>
@@ -15752,19 +15744,19 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="639" t="s">
+      <c r="C15" s="656" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="638"/>
+      <c r="D15" s="657"/>
       <c r="E15" s="58"/>
-      <c r="F15" s="645"/>
-      <c r="G15" s="679"/>
+      <c r="F15" s="646"/>
+      <c r="G15" s="647"/>
       <c r="H15" s="418"/>
-      <c r="I15" s="680">
+      <c r="I15" s="648">
         <f>+F15</f>
         <v>0</v>
       </c>
-      <c r="J15" s="681"/>
+      <c r="J15" s="649"/>
     </row>
     <row r="16" spans="1:10" ht="15.9" customHeight="1">
       <c r="A16" s="51"/>
@@ -15772,16 +15764,16 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="639" t="s">
+      <c r="C16" s="656" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="638"/>
+      <c r="D16" s="657"/>
       <c r="E16" s="58"/>
-      <c r="F16" s="710"/>
-      <c r="G16" s="708"/>
+      <c r="F16" s="678"/>
+      <c r="G16" s="679"/>
       <c r="H16" s="418"/>
-      <c r="I16" s="721"/>
-      <c r="J16" s="722"/>
+      <c r="I16" s="680"/>
+      <c r="J16" s="681"/>
     </row>
     <row r="17" spans="1:10" ht="15.9" customHeight="1">
       <c r="A17" s="51"/>
@@ -15789,21 +15781,21 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="639" t="s">
+      <c r="C17" s="656" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="638"/>
+      <c r="D17" s="657"/>
       <c r="E17" s="58"/>
-      <c r="F17" s="707" t="s">
+      <c r="F17" s="684" t="s">
         <v>85</v>
       </c>
-      <c r="G17" s="708"/>
+      <c r="G17" s="679"/>
       <c r="H17" s="418"/>
-      <c r="I17" s="721" t="str">
+      <c r="I17" s="680" t="str">
         <f>+F17</f>
         <v>Warm Shell</v>
       </c>
-      <c r="J17" s="722"/>
+      <c r="J17" s="681"/>
     </row>
     <row r="18" spans="1:10" ht="48" customHeight="1">
       <c r="A18" s="51"/>
@@ -15811,22 +15803,22 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="639" t="s">
+      <c r="C18" s="656" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="638"/>
+      <c r="D18" s="657"/>
       <c r="E18" s="163"/>
-      <c r="F18" s="645">
+      <c r="F18" s="646">
         <f>F15</f>
         <v>0</v>
       </c>
-      <c r="G18" s="679"/>
+      <c r="G18" s="647"/>
       <c r="H18" s="418"/>
-      <c r="I18" s="680">
+      <c r="I18" s="648">
         <f>+F18</f>
         <v>0</v>
       </c>
-      <c r="J18" s="681"/>
+      <c r="J18" s="649"/>
     </row>
     <row r="19" spans="1:10" ht="15.9" customHeight="1">
       <c r="A19" s="51"/>
@@ -15834,16 +15826,16 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="639" t="s">
+      <c r="C19" s="656" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="638"/>
+      <c r="D19" s="657"/>
       <c r="E19" s="163"/>
-      <c r="F19" s="710"/>
-      <c r="G19" s="708"/>
+      <c r="F19" s="678"/>
+      <c r="G19" s="679"/>
       <c r="H19" s="418"/>
-      <c r="I19" s="721"/>
-      <c r="J19" s="722"/>
+      <c r="I19" s="680"/>
+      <c r="J19" s="681"/>
     </row>
     <row r="20" spans="1:10" ht="15.9" customHeight="1">
       <c r="A20" s="51"/>
@@ -15851,10 +15843,10 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="637" t="s">
+      <c r="C20" s="650" t="s">
         <v>88</v>
       </c>
-      <c r="D20" s="638"/>
+      <c r="D20" s="657"/>
       <c r="E20" s="559"/>
       <c r="F20" s="56"/>
       <c r="G20" s="388"/>
@@ -15874,10 +15866,10 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="639" t="s">
+      <c r="C21" s="656" t="s">
         <v>89</v>
       </c>
-      <c r="D21" s="638"/>
+      <c r="D21" s="657"/>
       <c r="E21" s="559"/>
       <c r="F21" s="56">
         <v>9515</v>
@@ -15902,10 +15894,10 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="637" t="s">
+      <c r="C22" s="650" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="638"/>
+      <c r="D22" s="657"/>
       <c r="E22" s="559"/>
       <c r="F22" s="56">
         <v>0</v>
@@ -15929,10 +15921,10 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="639" t="s">
+      <c r="C23" s="656" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="638"/>
+      <c r="D23" s="657"/>
       <c r="E23" s="559"/>
       <c r="F23" s="56">
         <f>+F21+F22</f>
@@ -15958,10 +15950,10 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="639" t="s">
+      <c r="C24" s="656" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="638"/>
+      <c r="D24" s="657"/>
       <c r="E24" s="59"/>
       <c r="F24" s="56"/>
       <c r="G24" s="388">
@@ -15984,10 +15976,10 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="639" t="s">
+      <c r="C25" s="656" t="s">
         <v>93</v>
       </c>
-      <c r="D25" s="638"/>
+      <c r="D25" s="657"/>
       <c r="E25" s="59"/>
       <c r="F25" s="56">
         <v>0</v>
@@ -16012,10 +16004,10 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="639" t="s">
+      <c r="C26" s="656" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="638"/>
+      <c r="D26" s="657"/>
       <c r="E26" s="60"/>
       <c r="F26" s="61">
         <f>F25/F23</f>
@@ -16041,10 +16033,10 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="637" t="s">
+      <c r="C27" s="650" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="638"/>
+      <c r="D27" s="657"/>
       <c r="E27" s="58"/>
       <c r="F27" s="293">
         <v>72</v>
@@ -16069,10 +16061,10 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="637" t="s">
+      <c r="C28" s="650" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="638"/>
+      <c r="D28" s="657"/>
       <c r="E28" s="58"/>
       <c r="F28" s="293">
         <f>'CAPEX and PM'!E3</f>
@@ -16098,10 +16090,10 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="637" t="s">
+      <c r="C29" s="650" t="s">
         <v>97</v>
       </c>
-      <c r="D29" s="638"/>
+      <c r="D29" s="657"/>
       <c r="E29" s="64"/>
       <c r="F29" s="64">
         <v>0.105</v>
@@ -16126,10 +16118,10 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="637" t="s">
+      <c r="C30" s="650" t="s">
         <v>98</v>
       </c>
-      <c r="D30" s="638"/>
+      <c r="D30" s="657"/>
       <c r="E30" s="64"/>
       <c r="F30" s="60">
         <v>7.1099999999999997E-2</v>
@@ -16154,10 +16146,10 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="639" t="s">
+      <c r="C31" s="656" t="s">
         <v>99</v>
       </c>
-      <c r="D31" s="638"/>
+      <c r="D31" s="657"/>
       <c r="E31" s="58"/>
       <c r="F31" s="56">
         <v>0</v>
@@ -16178,11 +16170,11 @@
     </row>
     <row r="32" spans="1:10" ht="15.9" customHeight="1">
       <c r="A32" s="51"/>
-      <c r="B32" s="723" t="s">
+      <c r="B32" s="675" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="724"/>
-      <c r="D32" s="725"/>
+      <c r="C32" s="676"/>
+      <c r="D32" s="677"/>
       <c r="E32" s="562"/>
       <c r="F32" s="376" t="s">
         <v>75</v>
@@ -16203,10 +16195,10 @@
       <c r="B33" s="162">
         <v>1</v>
       </c>
-      <c r="C33" s="637" t="s">
+      <c r="C33" s="650" t="s">
         <v>101</v>
       </c>
-      <c r="D33" s="638"/>
+      <c r="D33" s="657"/>
       <c r="E33" s="59"/>
       <c r="F33" s="56">
         <v>10</v>
@@ -16231,10 +16223,10 @@
         <f>1+B33</f>
         <v>2</v>
       </c>
-      <c r="C34" s="637" t="s">
+      <c r="C34" s="650" t="s">
         <v>102</v>
       </c>
-      <c r="D34" s="638"/>
+      <c r="D34" s="657"/>
       <c r="E34" s="59"/>
       <c r="F34" s="56">
         <v>0</v>
@@ -16258,10 +16250,10 @@
         <f t="shared" ref="B35:B48" si="1">1+B34</f>
         <v>3</v>
       </c>
-      <c r="C35" s="637" t="s">
+      <c r="C35" s="650" t="s">
         <v>103</v>
       </c>
-      <c r="D35" s="638"/>
+      <c r="D35" s="657"/>
       <c r="E35" s="59"/>
       <c r="F35" s="56">
         <v>0</v>
@@ -16286,10 +16278,10 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="C36" s="639" t="s">
+      <c r="C36" s="656" t="s">
         <v>104</v>
       </c>
-      <c r="D36" s="638"/>
+      <c r="D36" s="657"/>
       <c r="E36" s="563"/>
       <c r="F36" s="68">
         <v>0</v>
@@ -16311,10 +16303,10 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="C37" s="637" t="s">
+      <c r="C37" s="650" t="s">
         <v>105</v>
       </c>
-      <c r="D37" s="638"/>
+      <c r="D37" s="657"/>
       <c r="E37" s="563"/>
       <c r="F37" s="70">
         <f>'Lease Rent'!H37</f>
@@ -16340,10 +16332,10 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="C38" s="637" t="s">
+      <c r="C38" s="650" t="s">
         <v>106</v>
       </c>
-      <c r="D38" s="638"/>
+      <c r="D38" s="657"/>
       <c r="E38" s="563"/>
       <c r="F38" s="70"/>
       <c r="G38" s="204">
@@ -16360,10 +16352,10 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="C39" s="637" t="s">
+      <c r="C39" s="650" t="s">
         <v>107</v>
       </c>
-      <c r="D39" s="638"/>
+      <c r="D39" s="657"/>
       <c r="E39" s="71"/>
       <c r="F39" s="70">
         <f>'Lease Rent'!J31</f>
@@ -16389,10 +16381,10 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="C40" s="637" t="s">
+      <c r="C40" s="650" t="s">
         <v>108</v>
       </c>
-      <c r="D40" s="638"/>
+      <c r="D40" s="657"/>
       <c r="E40" s="563"/>
       <c r="F40" s="70">
         <f>F37</f>
@@ -16418,10 +16410,10 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="C41" s="637" t="s">
+      <c r="C41" s="650" t="s">
         <v>109</v>
       </c>
-      <c r="D41" s="638"/>
+      <c r="D41" s="657"/>
       <c r="E41" s="563"/>
       <c r="F41" s="70">
         <v>0</v>
@@ -16446,10 +16438,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="C42" s="637" t="s">
+      <c r="C42" s="650" t="s">
         <v>110</v>
       </c>
-      <c r="D42" s="638"/>
+      <c r="D42" s="657"/>
       <c r="E42" s="58"/>
       <c r="F42" s="114">
         <f>F39</f>
@@ -16475,10 +16467,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="C43" s="639" t="s">
+      <c r="C43" s="656" t="s">
         <v>111</v>
       </c>
-      <c r="D43" s="638"/>
+      <c r="D43" s="657"/>
       <c r="E43" s="59"/>
       <c r="F43" s="109">
         <v>0</v>
@@ -16503,10 +16495,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="C44" s="639" t="s">
+      <c r="C44" s="656" t="s">
         <v>112</v>
       </c>
-      <c r="D44" s="638"/>
+      <c r="D44" s="657"/>
       <c r="E44" s="73"/>
       <c r="F44" s="68">
         <v>0</v>
@@ -16531,10 +16523,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="C45" s="639" t="s">
+      <c r="C45" s="656" t="s">
         <v>113</v>
       </c>
-      <c r="D45" s="638"/>
+      <c r="D45" s="657"/>
       <c r="E45" s="59"/>
       <c r="F45" s="56">
         <f>'Lease Rent'!C22</f>
@@ -16560,10 +16552,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="C46" s="637" t="s">
+      <c r="C46" s="650" t="s">
         <v>114</v>
       </c>
-      <c r="D46" s="638"/>
+      <c r="D46" s="657"/>
       <c r="E46" s="59"/>
       <c r="F46" s="109">
         <v>0</v>
@@ -16585,10 +16577,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="C47" s="639" t="s">
+      <c r="C47" s="656" t="s">
         <v>112</v>
       </c>
-      <c r="D47" s="638"/>
+      <c r="D47" s="657"/>
       <c r="E47" s="59"/>
       <c r="F47" s="56">
         <f>'Lease Rent'!D23</f>
@@ -16605,10 +16597,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="C48" s="639" t="s">
+      <c r="C48" s="656" t="s">
         <v>113</v>
       </c>
-      <c r="D48" s="638"/>
+      <c r="D48" s="657"/>
       <c r="E48" s="59"/>
       <c r="F48" s="56">
         <f>'Lease Rent'!C23</f>
@@ -16621,44 +16613,44 @@
     </row>
     <row r="49" spans="1:18" ht="28.5" customHeight="1">
       <c r="A49" s="51"/>
-      <c r="B49" s="684">
+      <c r="B49" s="722">
         <f>1+B48</f>
         <v>17</v>
       </c>
-      <c r="C49" s="637" t="s">
+      <c r="C49" s="650" t="s">
         <v>115</v>
       </c>
-      <c r="D49" s="638"/>
+      <c r="D49" s="657"/>
       <c r="E49" s="73"/>
-      <c r="F49" s="728" t="s">
+      <c r="F49" s="666" t="s">
         <v>341</v>
       </c>
-      <c r="G49" s="729"/>
+      <c r="G49" s="667"/>
       <c r="H49" s="418"/>
-      <c r="I49" s="721" t="str">
+      <c r="I49" s="680" t="str">
         <f>+F49</f>
         <v>15% after every 3 years</v>
       </c>
-      <c r="J49" s="722"/>
+      <c r="J49" s="681"/>
     </row>
     <row r="50" spans="1:18" ht="15.9" customHeight="1">
       <c r="A50" s="51"/>
-      <c r="B50" s="685"/>
-      <c r="C50" s="637" t="s">
+      <c r="B50" s="723"/>
+      <c r="C50" s="650" t="s">
         <v>116</v>
       </c>
-      <c r="D50" s="638"/>
+      <c r="D50" s="657"/>
       <c r="E50" s="73"/>
-      <c r="F50" s="728" t="s">
+      <c r="F50" s="666" t="s">
         <v>331</v>
       </c>
-      <c r="G50" s="729"/>
+      <c r="G50" s="667"/>
       <c r="H50" s="418"/>
-      <c r="I50" s="726" t="str">
+      <c r="I50" s="682" t="str">
         <f t="shared" ref="I50:I57" si="2">F50</f>
         <v>5% every year</v>
       </c>
-      <c r="J50" s="727"/>
+      <c r="J50" s="683"/>
     </row>
     <row r="51" spans="1:18" ht="15.9" customHeight="1">
       <c r="A51" s="51"/>
@@ -16666,22 +16658,22 @@
         <f>1+B49</f>
         <v>18</v>
       </c>
-      <c r="C51" s="639" t="s">
+      <c r="C51" s="656" t="s">
         <v>117</v>
       </c>
-      <c r="D51" s="638"/>
+      <c r="D51" s="657"/>
       <c r="E51" s="73"/>
-      <c r="F51" s="675">
+      <c r="F51" s="664">
         <f>'Lease Rent'!B31</f>
         <v>46023</v>
       </c>
-      <c r="G51" s="676"/>
+      <c r="G51" s="665"/>
       <c r="H51" s="418"/>
-      <c r="I51" s="677">
+      <c r="I51" s="673">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J51" s="678"/>
+      <c r="J51" s="674"/>
     </row>
     <row r="52" spans="1:18" ht="15.9" customHeight="1">
       <c r="A52" s="51"/>
@@ -16689,22 +16681,22 @@
         <f t="shared" ref="B52:B58" si="3">1+B51</f>
         <v>19</v>
       </c>
-      <c r="C52" s="637" t="s">
+      <c r="C52" s="650" t="s">
         <v>118</v>
       </c>
-      <c r="D52" s="638"/>
+      <c r="D52" s="657"/>
       <c r="E52" s="73"/>
-      <c r="F52" s="675">
+      <c r="F52" s="664">
         <f>'Lease Rent'!C102</f>
         <v>48213</v>
       </c>
-      <c r="G52" s="676"/>
+      <c r="G52" s="665"/>
       <c r="H52" s="418"/>
-      <c r="I52" s="677">
+      <c r="I52" s="673">
         <f>F52</f>
         <v>48213</v>
       </c>
-      <c r="J52" s="678"/>
+      <c r="J52" s="674"/>
     </row>
     <row r="53" spans="1:18" ht="15.9" customHeight="1">
       <c r="A53" s="51"/>
@@ -16712,22 +16704,22 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="C53" s="637" t="s">
+      <c r="C53" s="650" t="s">
         <v>119</v>
       </c>
-      <c r="D53" s="647"/>
+      <c r="D53" s="651"/>
       <c r="E53" s="73"/>
-      <c r="F53" s="675">
+      <c r="F53" s="664">
         <f>F51</f>
         <v>46023</v>
       </c>
-      <c r="G53" s="676"/>
+      <c r="G53" s="665"/>
       <c r="H53" s="418"/>
-      <c r="I53" s="677">
+      <c r="I53" s="673">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J53" s="678"/>
+      <c r="J53" s="674"/>
     </row>
     <row r="54" spans="1:18" ht="15.9" customHeight="1">
       <c r="A54" s="51"/>
@@ -16735,21 +16727,21 @@
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="C54" s="637" t="s">
+      <c r="C54" s="650" t="s">
         <v>120</v>
       </c>
-      <c r="D54" s="647"/>
+      <c r="D54" s="651"/>
       <c r="E54" s="73"/>
-      <c r="F54" s="645">
-        <v>0</v>
-      </c>
-      <c r="G54" s="679"/>
+      <c r="F54" s="646">
+        <v>0</v>
+      </c>
+      <c r="G54" s="647"/>
       <c r="H54" s="418"/>
-      <c r="I54" s="680">
+      <c r="I54" s="648">
         <f>+F54</f>
         <v>0</v>
       </c>
-      <c r="J54" s="681"/>
+      <c r="J54" s="649"/>
     </row>
     <row r="55" spans="1:18" ht="15.9" customHeight="1">
       <c r="A55" s="51"/>
@@ -16757,10 +16749,10 @@
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="C55" s="639" t="s">
+      <c r="C55" s="656" t="s">
         <v>121</v>
       </c>
-      <c r="D55" s="638"/>
+      <c r="D55" s="657"/>
       <c r="E55" s="58"/>
       <c r="F55" s="56">
         <f>(F52-F51)/365*12</f>
@@ -16787,10 +16779,10 @@
         <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="C56" s="639" t="s">
+      <c r="C56" s="656" t="s">
         <v>122</v>
       </c>
-      <c r="D56" s="638"/>
+      <c r="D56" s="657"/>
       <c r="E56" s="71"/>
       <c r="F56" s="56">
         <v>0</v>
@@ -16816,10 +16808,10 @@
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="C57" s="639" t="s">
+      <c r="C57" s="656" t="s">
         <v>123</v>
       </c>
-      <c r="D57" s="638"/>
+      <c r="D57" s="657"/>
       <c r="E57" s="71"/>
       <c r="F57" s="302" t="s">
         <v>68</v>
@@ -16845,10 +16837,10 @@
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="C58" s="639" t="s">
+      <c r="C58" s="656" t="s">
         <v>124</v>
       </c>
-      <c r="D58" s="638"/>
+      <c r="D58" s="657"/>
       <c r="E58" s="71"/>
       <c r="F58" s="56"/>
       <c r="G58" s="388"/>
@@ -16863,23 +16855,23 @@
       <c r="C59" s="74"/>
       <c r="D59" s="74"/>
       <c r="E59" s="58"/>
-      <c r="F59" s="645" t="s">
+      <c r="F59" s="646" t="s">
         <v>73</v>
       </c>
-      <c r="G59" s="679"/>
+      <c r="G59" s="647"/>
       <c r="H59" s="418"/>
-      <c r="I59" s="680" t="s">
+      <c r="I59" s="648" t="s">
         <v>67</v>
       </c>
-      <c r="J59" s="681"/>
+      <c r="J59" s="649"/>
     </row>
     <row r="60" spans="1:18" ht="15.9" customHeight="1">
       <c r="A60" s="51"/>
-      <c r="B60" s="682" t="s">
+      <c r="B60" s="720" t="s">
         <v>125</v>
       </c>
-      <c r="C60" s="683"/>
-      <c r="D60" s="683"/>
+      <c r="C60" s="721"/>
+      <c r="D60" s="721"/>
       <c r="E60" s="562"/>
       <c r="F60" s="376" t="s">
         <v>75</v>
@@ -16900,10 +16892,10 @@
       <c r="B61" s="162">
         <v>1</v>
       </c>
-      <c r="C61" s="637" t="s">
+      <c r="C61" s="650" t="s">
         <v>126</v>
       </c>
-      <c r="D61" s="638"/>
+      <c r="D61" s="657"/>
       <c r="E61" s="564"/>
       <c r="F61" s="70">
         <f>C221/F21/F27</f>
@@ -16929,10 +16921,10 @@
         <f>1+B61</f>
         <v>2</v>
       </c>
-      <c r="C62" s="637" t="s">
+      <c r="C62" s="650" t="s">
         <v>127</v>
       </c>
-      <c r="D62" s="638"/>
+      <c r="D62" s="657"/>
       <c r="E62" s="564"/>
       <c r="F62" s="70">
         <v>0</v>
@@ -16956,10 +16948,10 @@
         <f t="shared" ref="B63:B84" si="4">1+B62</f>
         <v>3</v>
       </c>
-      <c r="C63" s="640" t="s">
+      <c r="C63" s="652" t="s">
         <v>128</v>
       </c>
-      <c r="D63" s="641"/>
+      <c r="D63" s="653"/>
       <c r="E63" s="75"/>
       <c r="F63" s="76">
         <f>F61+F62</f>
@@ -16985,10 +16977,10 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="C64" s="637" t="s">
+      <c r="C64" s="650" t="s">
         <v>495</v>
       </c>
-      <c r="D64" s="638"/>
+      <c r="D64" s="657"/>
       <c r="E64" s="56"/>
       <c r="F64" s="54">
         <f>F63*F21</f>
@@ -17014,10 +17006,10 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="C65" s="637" t="s">
+      <c r="C65" s="650" t="s">
         <v>129</v>
       </c>
-      <c r="D65" s="638"/>
+      <c r="D65" s="657"/>
       <c r="E65" s="56"/>
       <c r="F65" s="70">
         <f>(I221/F21/F27)*(1+L1)</f>
@@ -17043,10 +17035,10 @@
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="C66" s="639" t="s">
+      <c r="C66" s="656" t="s">
         <v>496</v>
       </c>
-      <c r="D66" s="638"/>
+      <c r="D66" s="657"/>
       <c r="E66" s="71"/>
       <c r="F66" s="54">
         <f>+F65*F21*(1+L1)</f>
@@ -17072,10 +17064,10 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="C67" s="639" t="s">
+      <c r="C67" s="656" t="s">
         <v>497</v>
       </c>
-      <c r="D67" s="638"/>
+      <c r="D67" s="657"/>
       <c r="E67" s="59"/>
       <c r="F67" s="56">
         <f>(+G221/F27)*(1+L1)</f>
@@ -17101,10 +17093,10 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="C68" s="639" t="s">
+      <c r="C68" s="656" t="s">
         <v>130</v>
       </c>
-      <c r="D68" s="638"/>
+      <c r="D68" s="657"/>
       <c r="E68" s="56"/>
       <c r="F68" s="56">
         <v>11418000</v>
@@ -17129,10 +17121,10 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="C69" s="639" t="s">
+      <c r="C69" s="656" t="s">
         <v>131</v>
       </c>
-      <c r="D69" s="638"/>
+      <c r="D69" s="657"/>
       <c r="E69" s="56"/>
       <c r="F69" s="56">
         <v>0</v>
@@ -17157,10 +17149,10 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="C70" s="637" t="s">
+      <c r="C70" s="650" t="s">
         <v>132</v>
       </c>
-      <c r="D70" s="638"/>
+      <c r="D70" s="657"/>
       <c r="E70" s="56"/>
       <c r="F70" s="56">
         <v>500000</v>
@@ -17185,10 +17177,10 @@
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="C71" s="639" t="s">
+      <c r="C71" s="656" t="s">
         <v>133</v>
       </c>
-      <c r="D71" s="638"/>
+      <c r="D71" s="657"/>
       <c r="E71" s="56"/>
       <c r="F71" s="54">
         <v>0</v>
@@ -17210,10 +17202,10 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="C72" s="639" t="s">
+      <c r="C72" s="656" t="s">
         <v>134</v>
       </c>
-      <c r="D72" s="638"/>
+      <c r="D72" s="657"/>
       <c r="E72" s="56"/>
       <c r="F72" s="54">
         <f>F39*F23*F34</f>
@@ -17239,10 +17231,10 @@
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="C73" s="639" t="s">
+      <c r="C73" s="656" t="s">
         <v>135</v>
       </c>
-      <c r="D73" s="638"/>
+      <c r="D73" s="657"/>
       <c r="E73" s="56"/>
       <c r="F73" s="56">
         <v>0</v>
@@ -17267,10 +17259,10 @@
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="C74" s="637" t="s">
+      <c r="C74" s="650" t="s">
         <v>136</v>
       </c>
-      <c r="D74" s="638"/>
+      <c r="D74" s="657"/>
       <c r="E74" s="563"/>
       <c r="F74" s="68">
         <f>+F36*F64</f>
@@ -17324,10 +17316,10 @@
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="C76" s="637" t="s">
+      <c r="C76" s="650" t="s">
         <v>138</v>
       </c>
-      <c r="D76" s="638"/>
+      <c r="D76" s="657"/>
       <c r="E76" s="59"/>
       <c r="F76" s="56">
         <f>+F78/F23</f>
@@ -17353,10 +17345,10 @@
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="C77" s="637" t="s">
+      <c r="C77" s="650" t="s">
         <v>139</v>
       </c>
-      <c r="D77" s="638"/>
+      <c r="D77" s="657"/>
       <c r="E77" s="71"/>
       <c r="F77" s="51"/>
       <c r="G77" s="558"/>
@@ -17376,10 +17368,10 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="C78" s="637" t="s">
+      <c r="C78" s="650" t="s">
         <v>140</v>
       </c>
-      <c r="D78" s="638"/>
+      <c r="D78" s="657"/>
       <c r="E78" s="71"/>
       <c r="F78" s="56">
         <f>'CAPEX and PM'!B6</f>
@@ -17405,10 +17397,10 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="C79" s="637" t="s">
+      <c r="C79" s="650" t="s">
         <v>141</v>
       </c>
-      <c r="D79" s="638"/>
+      <c r="D79" s="657"/>
       <c r="E79" s="71"/>
       <c r="F79" s="56">
         <f>'CAPEX and PM'!B37</f>
@@ -17434,10 +17426,10 @@
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="C80" s="637" t="s">
+      <c r="C80" s="650" t="s">
         <v>142</v>
       </c>
-      <c r="D80" s="638"/>
+      <c r="D80" s="657"/>
       <c r="E80" s="71"/>
       <c r="F80" s="56">
         <f>+'CAPEX and PM'!B95</f>
@@ -17463,10 +17455,10 @@
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="C81" s="637" t="s">
+      <c r="C81" s="650" t="s">
         <v>143</v>
       </c>
-      <c r="D81" s="638"/>
+      <c r="D81" s="657"/>
       <c r="E81" s="71"/>
       <c r="F81" s="56"/>
       <c r="G81" s="388"/>
@@ -17486,10 +17478,10 @@
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="C82" s="637" t="s">
+      <c r="C82" s="650" t="s">
         <v>144</v>
       </c>
-      <c r="D82" s="647"/>
+      <c r="D82" s="651"/>
       <c r="E82" s="71"/>
       <c r="F82" s="56"/>
       <c r="G82" s="388"/>
@@ -17509,10 +17501,10 @@
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="C83" s="637" t="s">
+      <c r="C83" s="650" t="s">
         <v>145</v>
       </c>
-      <c r="D83" s="638"/>
+      <c r="D83" s="657"/>
       <c r="E83" s="59"/>
       <c r="F83" s="56">
         <f>+G208</f>
@@ -17538,10 +17530,10 @@
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="C84" s="637" t="s">
+      <c r="C84" s="650" t="s">
         <v>498</v>
       </c>
-      <c r="D84" s="638"/>
+      <c r="D84" s="657"/>
       <c r="E84" s="563"/>
       <c r="F84" s="56">
         <f>+F31</f>
@@ -17574,11 +17566,11 @@
     </row>
     <row r="86" spans="1:24" ht="15.9" customHeight="1">
       <c r="A86" s="51"/>
-      <c r="B86" s="659" t="s">
+      <c r="B86" s="658" t="s">
         <v>146</v>
       </c>
-      <c r="C86" s="660"/>
-      <c r="D86" s="661"/>
+      <c r="C86" s="659"/>
+      <c r="D86" s="660"/>
       <c r="E86" s="389"/>
       <c r="F86" s="161" t="s">
         <v>75</v>
@@ -17599,10 +17591,10 @@
       <c r="B87" s="162">
         <v>1</v>
       </c>
-      <c r="C87" s="637" t="s">
+      <c r="C87" s="650" t="s">
         <v>147</v>
       </c>
-      <c r="D87" s="638"/>
+      <c r="D87" s="657"/>
       <c r="E87" s="71"/>
       <c r="F87" s="70">
         <f>+F63</f>
@@ -17631,10 +17623,10 @@
         <f>1+B87</f>
         <v>2</v>
       </c>
-      <c r="C88" s="639" t="s">
+      <c r="C88" s="656" t="s">
         <v>148</v>
       </c>
-      <c r="D88" s="638"/>
+      <c r="D88" s="657"/>
       <c r="E88" s="73"/>
       <c r="F88" s="56">
         <v>0</v>
@@ -17657,10 +17649,10 @@
         <f t="shared" ref="B89:B95" si="7">+B88+1</f>
         <v>3</v>
       </c>
-      <c r="C89" s="639" t="s">
+      <c r="C89" s="656" t="s">
         <v>149</v>
       </c>
-      <c r="D89" s="638"/>
+      <c r="D89" s="657"/>
       <c r="E89" s="73"/>
       <c r="F89" s="70">
         <f>(F67/F23)</f>
@@ -17688,10 +17680,10 @@
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="C90" s="639" t="s">
+      <c r="C90" s="656" t="s">
         <v>150</v>
       </c>
-      <c r="D90" s="638"/>
+      <c r="D90" s="657"/>
       <c r="E90" s="73"/>
       <c r="F90" s="66">
         <f>'Security Deposit'!C17</f>
@@ -17719,10 +17711,10 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="C91" s="639" t="s">
+      <c r="C91" s="656" t="s">
         <v>324</v>
       </c>
-      <c r="D91" s="638"/>
+      <c r="D91" s="657"/>
       <c r="E91" s="73"/>
       <c r="F91" s="202">
         <f>+F65</f>
@@ -17750,10 +17742,10 @@
         <f>+B90+1</f>
         <v>5</v>
       </c>
-      <c r="C92" s="639" t="s">
+      <c r="C92" s="656" t="s">
         <v>151</v>
       </c>
-      <c r="D92" s="638"/>
+      <c r="D92" s="657"/>
       <c r="E92" s="73"/>
       <c r="F92" s="66">
         <f>(+F84/F21/F27)</f>
@@ -17780,10 +17772,10 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="C93" s="639" t="s">
+      <c r="C93" s="656" t="s">
         <v>152</v>
       </c>
-      <c r="D93" s="638"/>
+      <c r="D93" s="657"/>
       <c r="E93" s="73"/>
       <c r="F93" s="66">
         <f>F83/F21/F27</f>
@@ -17811,10 +17803,10 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="C94" s="637" t="s">
+      <c r="C94" s="650" t="s">
         <v>153</v>
       </c>
-      <c r="D94" s="638"/>
+      <c r="D94" s="657"/>
       <c r="E94" s="71"/>
       <c r="F94" s="66">
         <f>+G94/F6</f>
@@ -17842,10 +17834,10 @@
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="C95" s="640" t="s">
+      <c r="C95" s="652" t="s">
         <v>69</v>
       </c>
-      <c r="D95" s="641"/>
+      <c r="D95" s="653"/>
       <c r="E95" s="78"/>
       <c r="F95" s="213">
         <f>SUM(F87:F94)</f>
@@ -17870,8 +17862,8 @@
     <row r="96" spans="1:24" ht="15.9" customHeight="1">
       <c r="A96" s="51"/>
       <c r="B96" s="381"/>
-      <c r="C96" s="679"/>
-      <c r="D96" s="679"/>
+      <c r="C96" s="647"/>
+      <c r="D96" s="647"/>
       <c r="E96" s="84"/>
       <c r="F96" s="85"/>
       <c r="G96" s="85"/>
@@ -17881,11 +17873,11 @@
     </row>
     <row r="97" spans="1:26" ht="15.9" customHeight="1">
       <c r="A97" s="51"/>
-      <c r="B97" s="642" t="s">
+      <c r="B97" s="654" t="s">
         <v>154</v>
       </c>
-      <c r="C97" s="643"/>
-      <c r="D97" s="643"/>
+      <c r="C97" s="655"/>
+      <c r="D97" s="655"/>
       <c r="E97" s="87"/>
       <c r="F97" s="161" t="s">
         <v>75</v>
@@ -17907,11 +17899,11 @@
       <c r="B98" s="162">
         <v>1</v>
       </c>
-      <c r="C98" s="639" t="str">
+      <c r="C98" s="656" t="str">
         <f>+C77</f>
         <v>Siemens Standard Fitout (Existing)</v>
       </c>
-      <c r="D98" s="638"/>
+      <c r="D98" s="657"/>
       <c r="E98" s="88"/>
       <c r="F98" s="66">
         <v>0</v>
@@ -17936,11 +17928,11 @@
         <f t="shared" ref="B99:B104" si="8">+B98+1</f>
         <v>2</v>
       </c>
-      <c r="C99" s="639" t="str">
+      <c r="C99" s="656" t="str">
         <f>+C78</f>
         <v>Siemens Standard Fitout (New)</v>
       </c>
-      <c r="D99" s="638"/>
+      <c r="D99" s="657"/>
       <c r="E99" s="71"/>
       <c r="F99" s="66">
         <f>'CAPEX and PM'!B29</f>
@@ -17968,11 +17960,11 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="C100" s="639" t="str">
+      <c r="C100" s="656" t="str">
         <f>+C79</f>
         <v>Capex over the period of lease period</v>
       </c>
-      <c r="D100" s="638"/>
+      <c r="D100" s="657"/>
       <c r="E100" s="71"/>
       <c r="F100" s="66">
         <f>'CAPEX and PM'!B89</f>
@@ -18000,11 +17992,11 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="C101" s="639" t="str">
+      <c r="C101" s="656" t="str">
         <f>+C80</f>
         <v>PM cost over the period of lease period</v>
       </c>
-      <c r="D101" s="638"/>
+      <c r="D101" s="657"/>
       <c r="E101" s="71"/>
       <c r="F101" s="66">
         <f>+'CAPEX and PM'!B96</f>
@@ -18032,11 +18024,11 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="C102" s="639" t="str">
+      <c r="C102" s="656" t="str">
         <f>+C81</f>
         <v>Asset Retirement Obligation ( Removal &amp; Restoration Obligation)</v>
       </c>
-      <c r="D102" s="638"/>
+      <c r="D102" s="657"/>
       <c r="E102" s="71"/>
       <c r="F102" s="66">
         <f>'Security Deposit'!D25</f>
@@ -18067,10 +18059,10 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="C103" s="637" t="s">
+      <c r="C103" s="650" t="s">
         <v>155</v>
       </c>
-      <c r="D103" s="638"/>
+      <c r="D103" s="657"/>
       <c r="E103" s="73"/>
       <c r="F103" s="66">
         <f>+F82/F21/F28</f>
@@ -18098,10 +18090,10 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="C104" s="640" t="s">
+      <c r="C104" s="652" t="s">
         <v>156</v>
       </c>
-      <c r="D104" s="641"/>
+      <c r="D104" s="653"/>
       <c r="E104" s="78"/>
       <c r="F104" s="54">
         <f>SUM(F98:F103)</f>
@@ -18138,11 +18130,11 @@
     </row>
     <row r="106" spans="1:26" ht="15.9" customHeight="1">
       <c r="A106" s="51"/>
-      <c r="B106" s="731" t="s">
+      <c r="B106" s="661" t="s">
         <v>157</v>
       </c>
-      <c r="C106" s="654"/>
-      <c r="D106" s="654"/>
+      <c r="C106" s="662"/>
+      <c r="D106" s="662"/>
       <c r="E106" s="87"/>
       <c r="F106" s="161" t="s">
         <v>75</v>
@@ -18163,10 +18155,10 @@
       <c r="B107" s="162">
         <v>1</v>
       </c>
-      <c r="C107" s="637" t="s">
+      <c r="C107" s="650" t="s">
         <v>69</v>
       </c>
-      <c r="D107" s="638"/>
+      <c r="D107" s="657"/>
       <c r="E107" s="71"/>
       <c r="F107" s="56">
         <f>+F95</f>
@@ -18194,10 +18186,10 @@
         <f>+B107+1</f>
         <v>2</v>
       </c>
-      <c r="C108" s="637" t="s">
+      <c r="C108" s="650" t="s">
         <v>156</v>
       </c>
-      <c r="D108" s="647"/>
+      <c r="D108" s="651"/>
       <c r="E108" s="71"/>
       <c r="F108" s="56">
         <f>+F104</f>
@@ -18225,10 +18217,10 @@
         <f>+B108+1</f>
         <v>3</v>
       </c>
-      <c r="C109" s="640" t="s">
+      <c r="C109" s="652" t="s">
         <v>158</v>
       </c>
-      <c r="D109" s="641"/>
+      <c r="D109" s="653"/>
       <c r="E109" s="78"/>
       <c r="F109" s="54">
         <f>SUM(F107:F108)</f>
@@ -18257,11 +18249,11 @@
     </row>
     <row r="110" spans="1:26" ht="15.9" customHeight="1">
       <c r="A110" s="51"/>
-      <c r="B110" s="642" t="s">
+      <c r="B110" s="654" t="s">
         <v>159</v>
       </c>
-      <c r="C110" s="643"/>
-      <c r="D110" s="643"/>
+      <c r="C110" s="655"/>
+      <c r="D110" s="655"/>
       <c r="E110" s="89"/>
       <c r="F110" s="161" t="s">
         <v>75</v>
@@ -18283,10 +18275,10 @@
       <c r="B111" s="249">
         <v>1</v>
       </c>
-      <c r="C111" s="637" t="s">
+      <c r="C111" s="650" t="s">
         <v>160</v>
       </c>
-      <c r="D111" s="647"/>
+      <c r="D111" s="651"/>
       <c r="E111" s="83"/>
       <c r="F111" s="376"/>
       <c r="G111" s="376"/>
@@ -18300,10 +18292,10 @@
         <f t="shared" ref="B112:B120" si="9">1+B111</f>
         <v>2</v>
       </c>
-      <c r="C112" s="637" t="s">
+      <c r="C112" s="650" t="s">
         <v>161</v>
       </c>
-      <c r="D112" s="647"/>
+      <c r="D112" s="651"/>
       <c r="E112" s="83"/>
       <c r="F112" s="376"/>
       <c r="G112" s="376"/>
@@ -18319,10 +18311,10 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="C113" s="637" t="s">
+      <c r="C113" s="650" t="s">
         <v>162</v>
       </c>
-      <c r="D113" s="647"/>
+      <c r="D113" s="651"/>
       <c r="E113" s="83"/>
       <c r="F113" s="388">
         <f>+F65*0</f>
@@ -18350,10 +18342,10 @@
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="C114" s="637" t="s">
+      <c r="C114" s="650" t="s">
         <v>163</v>
       </c>
-      <c r="D114" s="647"/>
+      <c r="D114" s="651"/>
       <c r="E114" s="83"/>
       <c r="F114" s="376"/>
       <c r="G114" s="376"/>
@@ -18367,10 +18359,10 @@
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="C115" s="637" t="s">
+      <c r="C115" s="650" t="s">
         <v>164</v>
       </c>
-      <c r="D115" s="647"/>
+      <c r="D115" s="651"/>
       <c r="E115" s="83"/>
       <c r="F115" s="376"/>
       <c r="G115" s="376"/>
@@ -18384,10 +18376,10 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="C116" s="637" t="s">
+      <c r="C116" s="650" t="s">
         <v>165</v>
       </c>
-      <c r="D116" s="647"/>
+      <c r="D116" s="651"/>
       <c r="E116" s="83"/>
       <c r="F116" s="376"/>
       <c r="G116" s="376"/>
@@ -18401,10 +18393,10 @@
         <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="C117" s="637" t="s">
+      <c r="C117" s="650" t="s">
         <v>166</v>
       </c>
-      <c r="D117" s="647"/>
+      <c r="D117" s="651"/>
       <c r="E117" s="83"/>
       <c r="F117" s="376"/>
       <c r="G117" s="376"/>
@@ -18418,10 +18410,10 @@
         <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="C118" s="637" t="s">
+      <c r="C118" s="650" t="s">
         <v>167</v>
       </c>
-      <c r="D118" s="638"/>
+      <c r="D118" s="657"/>
       <c r="E118" s="252"/>
       <c r="F118" s="360"/>
       <c r="G118" s="207">
@@ -18444,10 +18436,10 @@
         <f t="shared" si="9"/>
         <v>9</v>
       </c>
-      <c r="C119" s="637" t="s">
+      <c r="C119" s="650" t="s">
         <v>168</v>
       </c>
-      <c r="D119" s="647"/>
+      <c r="D119" s="651"/>
       <c r="E119" s="252"/>
       <c r="F119" s="90"/>
       <c r="G119" s="90">
@@ -18470,10 +18462,10 @@
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="C120" s="640" t="s">
+      <c r="C120" s="652" t="s">
         <v>169</v>
       </c>
-      <c r="D120" s="641"/>
+      <c r="D120" s="653"/>
       <c r="E120" s="253"/>
       <c r="F120" s="54">
         <f>SUM(F111:F119)</f>
@@ -18499,8 +18491,8 @@
     <row r="121" spans="1:26" ht="15.9" customHeight="1">
       <c r="A121" s="77"/>
       <c r="B121" s="162"/>
-      <c r="C121" s="645"/>
-      <c r="D121" s="646"/>
+      <c r="C121" s="646"/>
+      <c r="D121" s="663"/>
       <c r="E121" s="78"/>
       <c r="F121" s="54"/>
       <c r="G121" s="385"/>
@@ -18514,11 +18506,11 @@
     </row>
     <row r="122" spans="1:26" ht="15.9" customHeight="1">
       <c r="A122" s="77"/>
-      <c r="B122" s="642" t="s">
+      <c r="B122" s="654" t="s">
         <v>170</v>
       </c>
-      <c r="C122" s="643"/>
-      <c r="D122" s="643"/>
+      <c r="C122" s="655"/>
+      <c r="D122" s="655"/>
       <c r="E122" s="89"/>
       <c r="F122" s="161" t="s">
         <v>75</v>
@@ -18541,10 +18533,10 @@
       <c r="B123" s="251">
         <v>1</v>
       </c>
-      <c r="C123" s="637" t="s">
+      <c r="C123" s="650" t="s">
         <v>171</v>
       </c>
-      <c r="D123" s="647"/>
+      <c r="D123" s="651"/>
       <c r="E123" s="78"/>
       <c r="F123" s="54"/>
       <c r="G123" s="385"/>
@@ -18557,10 +18549,10 @@
       <c r="B124" s="162">
         <v>2</v>
       </c>
-      <c r="C124" s="640" t="s">
+      <c r="C124" s="652" t="s">
         <v>172</v>
       </c>
-      <c r="D124" s="641"/>
+      <c r="D124" s="653"/>
       <c r="E124" s="78"/>
       <c r="F124" s="54">
         <f>SUM(F123)</f>
@@ -18583,8 +18575,8 @@
     <row r="125" spans="1:26" ht="15.9" customHeight="1">
       <c r="A125" s="77"/>
       <c r="B125" s="162"/>
-      <c r="C125" s="645"/>
-      <c r="D125" s="646"/>
+      <c r="C125" s="646"/>
+      <c r="D125" s="663"/>
       <c r="E125" s="63"/>
       <c r="F125" s="54"/>
       <c r="G125" s="385"/>
@@ -18594,11 +18586,11 @@
     </row>
     <row r="126" spans="1:26" ht="15.9" customHeight="1">
       <c r="A126" s="77"/>
-      <c r="B126" s="642" t="s">
+      <c r="B126" s="654" t="s">
         <v>173</v>
       </c>
-      <c r="C126" s="643"/>
-      <c r="D126" s="643"/>
+      <c r="C126" s="655"/>
+      <c r="D126" s="655"/>
       <c r="E126" s="89"/>
       <c r="F126" s="161" t="s">
         <v>75</v>
@@ -18619,10 +18611,10 @@
       <c r="B127" s="249">
         <v>1</v>
       </c>
-      <c r="C127" s="637" t="s">
+      <c r="C127" s="650" t="s">
         <v>174</v>
       </c>
-      <c r="D127" s="647"/>
+      <c r="D127" s="651"/>
       <c r="E127" s="250"/>
       <c r="F127" s="385"/>
       <c r="G127" s="385"/>
@@ -18636,10 +18628,10 @@
         <f>1+B127</f>
         <v>2</v>
       </c>
-      <c r="C128" s="637" t="s">
+      <c r="C128" s="650" t="s">
         <v>175</v>
       </c>
-      <c r="D128" s="647"/>
+      <c r="D128" s="651"/>
       <c r="E128" s="250"/>
       <c r="F128" s="385"/>
       <c r="G128" s="385"/>
@@ -18653,10 +18645,10 @@
         <f>1+B128</f>
         <v>3</v>
       </c>
-      <c r="C129" s="637" t="s">
+      <c r="C129" s="650" t="s">
         <v>176</v>
       </c>
-      <c r="D129" s="647"/>
+      <c r="D129" s="651"/>
       <c r="E129" s="250"/>
       <c r="F129" s="385"/>
       <c r="G129" s="385"/>
@@ -18670,10 +18662,10 @@
         <f>1+B129</f>
         <v>4</v>
       </c>
-      <c r="C130" s="637" t="s">
+      <c r="C130" s="650" t="s">
         <v>177</v>
       </c>
-      <c r="D130" s="647"/>
+      <c r="D130" s="651"/>
       <c r="E130" s="250"/>
       <c r="F130" s="385"/>
       <c r="G130" s="385"/>
@@ -18687,10 +18679,10 @@
         <f>1+B130</f>
         <v>5</v>
       </c>
-      <c r="C131" s="637" t="s">
+      <c r="C131" s="650" t="s">
         <v>178</v>
       </c>
-      <c r="D131" s="647"/>
+      <c r="D131" s="651"/>
       <c r="E131" s="250"/>
       <c r="F131" s="385"/>
       <c r="G131" s="385"/>
@@ -18704,10 +18696,10 @@
         <f>1+B131</f>
         <v>6</v>
       </c>
-      <c r="C132" s="637" t="s">
+      <c r="C132" s="650" t="s">
         <v>179</v>
       </c>
-      <c r="D132" s="647"/>
+      <c r="D132" s="651"/>
       <c r="E132" s="250"/>
       <c r="F132" s="385"/>
       <c r="G132" s="385"/>
@@ -18720,10 +18712,10 @@
       <c r="B133" s="381">
         <v>7</v>
       </c>
-      <c r="C133" s="640" t="s">
+      <c r="C133" s="652" t="s">
         <v>180</v>
       </c>
-      <c r="D133" s="641"/>
+      <c r="D133" s="653"/>
       <c r="E133" s="250"/>
       <c r="F133" s="385">
         <f>SUM(F127:F132)</f>
@@ -18746,8 +18738,8 @@
     <row r="134" spans="1:20" ht="15.9" customHeight="1">
       <c r="A134" s="77"/>
       <c r="B134" s="162"/>
-      <c r="C134" s="679"/>
-      <c r="D134" s="646"/>
+      <c r="C134" s="647"/>
+      <c r="D134" s="663"/>
       <c r="E134" s="250"/>
       <c r="F134" s="385"/>
       <c r="G134" s="385"/>
@@ -18757,11 +18749,11 @@
     </row>
     <row r="135" spans="1:20" ht="15.9" customHeight="1">
       <c r="A135" s="51"/>
-      <c r="B135" s="642" t="s">
+      <c r="B135" s="654" t="s">
         <v>181</v>
       </c>
-      <c r="C135" s="643"/>
-      <c r="D135" s="643"/>
+      <c r="C135" s="655"/>
+      <c r="D135" s="655"/>
       <c r="E135" s="89"/>
       <c r="F135" s="161" t="s">
         <v>75</v>
@@ -18782,10 +18774,10 @@
       <c r="B136" s="162">
         <v>1</v>
       </c>
-      <c r="C136" s="640" t="s">
+      <c r="C136" s="652" t="s">
         <v>182</v>
       </c>
-      <c r="D136" s="641"/>
+      <c r="D136" s="653"/>
       <c r="E136" s="78"/>
       <c r="F136" s="54">
         <f>F120+F109+F124+F133</f>
@@ -18810,8 +18802,8 @@
     <row r="137" spans="1:20" ht="15.9" customHeight="1">
       <c r="A137" s="77"/>
       <c r="B137" s="162"/>
-      <c r="C137" s="645"/>
-      <c r="D137" s="646"/>
+      <c r="C137" s="646"/>
+      <c r="D137" s="663"/>
       <c r="E137" s="78"/>
       <c r="F137" s="54"/>
       <c r="G137" s="385"/>
@@ -18825,23 +18817,23 @@
       <c r="C138" s="380"/>
       <c r="D138" s="377"/>
       <c r="E138" s="167"/>
-      <c r="F138" s="645" t="s">
+      <c r="F138" s="646" t="s">
         <v>73</v>
       </c>
-      <c r="G138" s="679"/>
+      <c r="G138" s="647"/>
       <c r="H138" s="418"/>
-      <c r="I138" s="680" t="s">
+      <c r="I138" s="648" t="s">
         <v>67</v>
       </c>
-      <c r="J138" s="681"/>
+      <c r="J138" s="649"/>
     </row>
     <row r="139" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A139" s="51"/>
-      <c r="B139" s="642" t="s">
+      <c r="B139" s="654" t="s">
         <v>183</v>
       </c>
-      <c r="C139" s="643"/>
-      <c r="D139" s="644"/>
+      <c r="C139" s="655"/>
+      <c r="D139" s="670"/>
       <c r="E139" s="161"/>
       <c r="F139" s="161" t="s">
         <v>75</v>
@@ -18860,8 +18852,8 @@
     <row r="140" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A140" s="51"/>
       <c r="B140" s="91"/>
-      <c r="C140" s="648"/>
-      <c r="D140" s="649"/>
+      <c r="C140" s="671"/>
+      <c r="D140" s="672"/>
       <c r="E140" s="163"/>
       <c r="F140" s="54"/>
       <c r="G140" s="385"/>
@@ -18872,10 +18864,10 @@
     <row r="141" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A141" s="51"/>
       <c r="B141" s="91"/>
-      <c r="C141" s="637" t="s">
+      <c r="C141" s="650" t="s">
         <v>184</v>
       </c>
-      <c r="D141" s="638"/>
+      <c r="D141" s="657"/>
       <c r="E141" s="58"/>
       <c r="F141" s="243">
         <f>F21</f>
@@ -18898,10 +18890,10 @@
     <row r="142" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A142" s="51"/>
       <c r="B142" s="91"/>
-      <c r="C142" s="639" t="s">
+      <c r="C142" s="656" t="s">
         <v>185</v>
       </c>
-      <c r="D142" s="638"/>
+      <c r="D142" s="657"/>
       <c r="E142" s="59"/>
       <c r="F142" s="56">
         <f>F24</f>
@@ -18924,10 +18916,10 @@
     <row r="143" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A143" s="51"/>
       <c r="B143" s="91"/>
-      <c r="C143" s="639" t="s">
+      <c r="C143" s="656" t="s">
         <v>186</v>
       </c>
-      <c r="D143" s="638"/>
+      <c r="D143" s="657"/>
       <c r="E143" s="73"/>
       <c r="F143" s="56" t="e">
         <f>+#REF!</f>
@@ -18950,10 +18942,10 @@
     <row r="144" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A144" s="51"/>
       <c r="B144" s="91"/>
-      <c r="C144" s="637" t="s">
+      <c r="C144" s="650" t="s">
         <v>187</v>
       </c>
-      <c r="D144" s="638"/>
+      <c r="D144" s="657"/>
       <c r="E144" s="73"/>
       <c r="F144" s="56">
         <f>F109</f>
@@ -18976,10 +18968,10 @@
     <row r="145" spans="1:10" ht="15.9" hidden="1" customHeight="1">
       <c r="A145" s="51"/>
       <c r="B145" s="91"/>
-      <c r="C145" s="667" t="s">
+      <c r="C145" s="741" t="s">
         <v>188</v>
       </c>
-      <c r="D145" s="668"/>
+      <c r="D145" s="742"/>
       <c r="E145" s="92"/>
       <c r="F145" s="93">
         <f>F120</f>
@@ -19002,10 +18994,10 @@
     <row r="146" spans="1:10" ht="15.9" hidden="1" customHeight="1">
       <c r="A146" s="77"/>
       <c r="B146" s="162"/>
-      <c r="C146" s="640" t="s">
+      <c r="C146" s="652" t="s">
         <v>189</v>
       </c>
-      <c r="D146" s="641"/>
+      <c r="D146" s="653"/>
       <c r="E146" s="78"/>
       <c r="F146" s="245" t="e">
         <f>F136*#REF!</f>
@@ -19039,11 +19031,11 @@
     </row>
     <row r="148" spans="1:10" ht="15.9" customHeight="1">
       <c r="A148" s="77"/>
-      <c r="B148" s="642" t="s">
+      <c r="B148" s="654" t="s">
         <v>190</v>
       </c>
-      <c r="C148" s="643"/>
-      <c r="D148" s="644"/>
+      <c r="C148" s="655"/>
+      <c r="D148" s="670"/>
       <c r="E148" s="379"/>
       <c r="F148" s="379" t="s">
         <v>191</v>
@@ -19062,8 +19054,8 @@
     <row r="149" spans="1:10" ht="15.9" customHeight="1">
       <c r="A149" s="51"/>
       <c r="B149" s="99"/>
-      <c r="C149" s="648"/>
-      <c r="D149" s="649"/>
+      <c r="C149" s="671"/>
+      <c r="D149" s="672"/>
       <c r="E149" s="100"/>
       <c r="F149" s="101"/>
       <c r="G149" s="209"/>
@@ -19074,10 +19066,10 @@
     <row r="150" spans="1:10" ht="15.9" customHeight="1">
       <c r="A150" s="51"/>
       <c r="B150" s="99"/>
-      <c r="C150" s="639" t="s">
+      <c r="C150" s="656" t="s">
         <v>192</v>
       </c>
-      <c r="D150" s="638"/>
+      <c r="D150" s="657"/>
       <c r="E150" s="100"/>
       <c r="F150" s="101">
         <f>(+F64/(1+L1))*115%</f>
@@ -19100,10 +19092,10 @@
     <row r="151" spans="1:10" ht="15.9" customHeight="1">
       <c r="A151" s="51"/>
       <c r="B151" s="99"/>
-      <c r="C151" s="639" t="s">
+      <c r="C151" s="656" t="s">
         <v>193</v>
       </c>
-      <c r="D151" s="638"/>
+      <c r="D151" s="657"/>
       <c r="E151" s="100"/>
       <c r="F151" s="101">
         <v>0</v>
@@ -19122,10 +19114,10 @@
     <row r="152" spans="1:10" ht="15.9" customHeight="1">
       <c r="A152" s="51"/>
       <c r="B152" s="99"/>
-      <c r="C152" s="639" t="s">
+      <c r="C152" s="656" t="s">
         <v>194</v>
       </c>
-      <c r="D152" s="638"/>
+      <c r="D152" s="657"/>
       <c r="E152" s="100"/>
       <c r="F152" s="101">
         <f>(+F66/(1+L1))*115%</f>
@@ -19148,10 +19140,10 @@
     <row r="153" spans="1:10" ht="15.9" customHeight="1">
       <c r="A153" s="51"/>
       <c r="B153" s="99"/>
-      <c r="C153" s="639" t="s">
+      <c r="C153" s="656" t="s">
         <v>195</v>
       </c>
-      <c r="D153" s="638"/>
+      <c r="D153" s="657"/>
       <c r="E153" s="100"/>
       <c r="F153" s="101">
         <f>(+F67/(1+L1))*115%</f>
@@ -19174,10 +19166,10 @@
     <row r="154" spans="1:10" ht="15.9" customHeight="1">
       <c r="A154" s="51"/>
       <c r="B154" s="99"/>
-      <c r="C154" s="637" t="s">
+      <c r="C154" s="650" t="s">
         <v>196</v>
       </c>
-      <c r="D154" s="638"/>
+      <c r="D154" s="657"/>
       <c r="E154" s="103"/>
       <c r="F154" s="104">
         <f>SUM(F150:F153)</f>
@@ -19200,10 +19192,10 @@
     <row r="155" spans="1:10" ht="15.9" customHeight="1">
       <c r="A155" s="51"/>
       <c r="B155" s="99"/>
-      <c r="C155" s="637" t="s">
+      <c r="C155" s="650" t="s">
         <v>197</v>
       </c>
-      <c r="D155" s="638"/>
+      <c r="D155" s="657"/>
       <c r="E155" s="105"/>
       <c r="F155" s="101">
         <f>+F154*12</f>
@@ -19226,8 +19218,8 @@
     <row r="156" spans="1:10" ht="15.9" customHeight="1">
       <c r="A156" s="51"/>
       <c r="B156" s="99"/>
-      <c r="C156" s="648"/>
-      <c r="D156" s="649"/>
+      <c r="C156" s="671"/>
+      <c r="D156" s="672"/>
       <c r="E156" s="105"/>
       <c r="F156" s="101"/>
       <c r="G156" s="209"/>
@@ -19237,11 +19229,11 @@
     </row>
     <row r="157" spans="1:10" ht="15.9" customHeight="1">
       <c r="A157" s="51"/>
-      <c r="B157" s="642" t="s">
+      <c r="B157" s="654" t="s">
         <v>198</v>
       </c>
-      <c r="C157" s="643"/>
-      <c r="D157" s="644"/>
+      <c r="C157" s="655"/>
+      <c r="D157" s="670"/>
       <c r="E157" s="375"/>
       <c r="F157" s="379" t="s">
         <v>191</v>
@@ -19260,8 +19252,8 @@
     <row r="158" spans="1:10" ht="15.9" customHeight="1">
       <c r="A158" s="51"/>
       <c r="B158" s="99"/>
-      <c r="C158" s="648"/>
-      <c r="D158" s="649"/>
+      <c r="C158" s="671"/>
+      <c r="D158" s="672"/>
       <c r="E158" s="105"/>
       <c r="F158" s="101"/>
       <c r="G158" s="209"/>
@@ -19272,10 +19264,10 @@
     <row r="159" spans="1:10" ht="15.9" customHeight="1">
       <c r="A159" s="51"/>
       <c r="B159" s="99"/>
-      <c r="C159" s="665" t="s">
+      <c r="C159" s="739" t="s">
         <v>199</v>
       </c>
-      <c r="D159" s="666"/>
+      <c r="D159" s="740"/>
       <c r="E159" s="105"/>
       <c r="F159" s="101">
         <f t="shared" ref="F159:G161" si="10">+F78</f>
@@ -19298,10 +19290,10 @@
     <row r="160" spans="1:10" ht="15.9" customHeight="1">
       <c r="A160" s="51"/>
       <c r="B160" s="99"/>
-      <c r="C160" s="637" t="s">
+      <c r="C160" s="650" t="s">
         <v>200</v>
       </c>
-      <c r="D160" s="647"/>
+      <c r="D160" s="651"/>
       <c r="E160" s="105"/>
       <c r="F160" s="101">
         <f t="shared" si="10"/>
@@ -19324,10 +19316,10 @@
     <row r="161" spans="1:22" ht="15.9" customHeight="1">
       <c r="A161" s="51"/>
       <c r="B161" s="99"/>
-      <c r="C161" s="637" t="s">
+      <c r="C161" s="650" t="s">
         <v>201</v>
       </c>
-      <c r="D161" s="647"/>
+      <c r="D161" s="651"/>
       <c r="E161" s="105"/>
       <c r="F161" s="101">
         <f t="shared" si="10"/>
@@ -19350,10 +19342,10 @@
     <row r="162" spans="1:22" ht="15.9" customHeight="1">
       <c r="A162" s="51"/>
       <c r="B162" s="99"/>
-      <c r="C162" s="640" t="s">
+      <c r="C162" s="652" t="s">
         <v>29</v>
       </c>
-      <c r="D162" s="641"/>
+      <c r="D162" s="653"/>
       <c r="E162" s="105"/>
       <c r="F162" s="237">
         <f>SUM(F159:F161)</f>
@@ -19376,8 +19368,8 @@
     <row r="163" spans="1:22" ht="15.9" customHeight="1">
       <c r="A163" s="51"/>
       <c r="B163" s="99"/>
-      <c r="C163" s="648"/>
-      <c r="D163" s="649"/>
+      <c r="C163" s="671"/>
+      <c r="D163" s="672"/>
       <c r="E163" s="105"/>
       <c r="F163" s="101"/>
       <c r="G163" s="209"/>
@@ -19387,12 +19379,12 @@
     </row>
     <row r="164" spans="1:22" ht="15.9" customHeight="1">
       <c r="A164" s="106"/>
-      <c r="B164" s="659" t="s">
+      <c r="B164" s="658" t="s">
         <v>202</v>
       </c>
-      <c r="C164" s="660"/>
-      <c r="D164" s="661"/>
-      <c r="E164" s="730"/>
+      <c r="C164" s="659"/>
+      <c r="D164" s="660"/>
+      <c r="E164" s="668"/>
       <c r="F164" s="161" t="s">
         <v>75</v>
       </c>
@@ -19409,10 +19401,10 @@
     </row>
     <row r="165" spans="1:22" ht="15.9" customHeight="1">
       <c r="A165" s="106"/>
-      <c r="B165" s="662"/>
-      <c r="C165" s="663"/>
-      <c r="D165" s="664"/>
-      <c r="E165" s="652"/>
+      <c r="B165" s="736"/>
+      <c r="C165" s="737"/>
+      <c r="D165" s="738"/>
+      <c r="E165" s="669"/>
       <c r="F165" s="161" t="s">
         <v>73</v>
       </c>
@@ -19430,8 +19422,8 @@
     <row r="166" spans="1:22" ht="15.9" customHeight="1">
       <c r="A166" s="107"/>
       <c r="B166" s="99"/>
-      <c r="C166" s="648"/>
-      <c r="D166" s="649"/>
+      <c r="C166" s="671"/>
+      <c r="D166" s="672"/>
       <c r="E166" s="59"/>
       <c r="F166" s="56"/>
       <c r="G166" s="388"/>
@@ -19442,11 +19434,11 @@
     <row r="167" spans="1:22" ht="15.9" customHeight="1">
       <c r="A167" s="107"/>
       <c r="B167" s="99"/>
-      <c r="C167" s="650" t="str">
+      <c r="C167" s="734" t="str">
         <f>+C107</f>
         <v>Net Rent I</v>
       </c>
-      <c r="D167" s="651"/>
+      <c r="D167" s="735"/>
       <c r="E167" s="59"/>
       <c r="F167" s="56">
         <f>+F107</f>
@@ -19470,11 +19462,11 @@
     <row r="168" spans="1:22" ht="15.9" customHeight="1">
       <c r="A168" s="107"/>
       <c r="B168" s="99"/>
-      <c r="C168" s="650" t="str">
+      <c r="C168" s="734" t="str">
         <f>+C108</f>
         <v>Net Rent II</v>
       </c>
-      <c r="D168" s="651"/>
+      <c r="D168" s="735"/>
       <c r="E168" s="59"/>
       <c r="F168" s="56">
         <f>+F108</f>
@@ -19498,10 +19490,10 @@
     <row r="169" spans="1:22" ht="15.9" customHeight="1">
       <c r="A169" s="107"/>
       <c r="B169" s="147"/>
-      <c r="C169" s="655" t="s">
+      <c r="C169" s="730" t="s">
         <v>203</v>
       </c>
-      <c r="D169" s="656"/>
+      <c r="D169" s="731"/>
       <c r="E169" s="148"/>
       <c r="F169" s="149">
         <f>SUM(F167:F168)</f>
@@ -19526,8 +19518,8 @@
     <row r="170" spans="1:22" ht="15.9" customHeight="1">
       <c r="A170" s="107"/>
       <c r="B170" s="162"/>
-      <c r="C170" s="657"/>
-      <c r="D170" s="658"/>
+      <c r="C170" s="732"/>
+      <c r="D170" s="733"/>
       <c r="E170" s="75"/>
       <c r="F170" s="54"/>
       <c r="G170" s="385"/>
@@ -19540,11 +19532,11 @@
     <row r="171" spans="1:22" ht="15.9" customHeight="1">
       <c r="A171" s="107"/>
       <c r="B171" s="99"/>
-      <c r="C171" s="650" t="str">
+      <c r="C171" s="734" t="str">
         <f>+C120</f>
         <v xml:space="preserve">OpEx I </v>
       </c>
-      <c r="D171" s="651"/>
+      <c r="D171" s="735"/>
       <c r="E171" s="59"/>
       <c r="F171" s="56">
         <f>+F120</f>
@@ -19568,11 +19560,11 @@
     <row r="172" spans="1:22" ht="15.9" customHeight="1">
       <c r="A172" s="107"/>
       <c r="B172" s="99"/>
-      <c r="C172" s="650" t="str">
+      <c r="C172" s="734" t="str">
         <f>+C124</f>
         <v xml:space="preserve">OpEx II </v>
       </c>
-      <c r="D172" s="651"/>
+      <c r="D172" s="735"/>
       <c r="E172" s="59"/>
       <c r="F172" s="56">
         <f>+F124</f>
@@ -19595,10 +19587,10 @@
     <row r="173" spans="1:22" ht="15.9" customHeight="1">
       <c r="A173" s="107"/>
       <c r="B173" s="150"/>
-      <c r="C173" s="655" t="s">
+      <c r="C173" s="730" t="s">
         <v>204</v>
       </c>
-      <c r="D173" s="656"/>
+      <c r="D173" s="731"/>
       <c r="E173" s="151"/>
       <c r="F173" s="152">
         <f>SUM(F171:F172)</f>
@@ -19633,11 +19625,11 @@
     <row r="175" spans="1:22" ht="15.9" customHeight="1">
       <c r="A175" s="107"/>
       <c r="B175" s="99"/>
-      <c r="C175" s="650" t="str">
+      <c r="C175" s="734" t="str">
         <f>+C133</f>
         <v xml:space="preserve">Services </v>
       </c>
-      <c r="D175" s="651"/>
+      <c r="D175" s="735"/>
       <c r="E175" s="59"/>
       <c r="F175" s="56">
         <f>+F133</f>
@@ -19660,10 +19652,10 @@
     <row r="176" spans="1:22" ht="15.9" customHeight="1">
       <c r="A176" s="107"/>
       <c r="B176" s="150"/>
-      <c r="C176" s="655" t="s">
+      <c r="C176" s="730" t="s">
         <v>205</v>
       </c>
-      <c r="D176" s="656"/>
+      <c r="D176" s="731"/>
       <c r="E176" s="151"/>
       <c r="F176" s="152">
         <f>SUM(F175)</f>
@@ -19686,8 +19678,8 @@
     <row r="177" spans="1:19" ht="15.9" customHeight="1">
       <c r="A177" s="107"/>
       <c r="B177" s="99"/>
-      <c r="C177" s="648"/>
-      <c r="D177" s="649"/>
+      <c r="C177" s="671"/>
+      <c r="D177" s="672"/>
       <c r="E177" s="59"/>
       <c r="F177" s="56"/>
       <c r="G177" s="388"/>
@@ -19698,10 +19690,10 @@
     <row r="178" spans="1:19" ht="15.9" customHeight="1">
       <c r="A178" s="107"/>
       <c r="B178" s="150"/>
-      <c r="C178" s="655" t="s">
+      <c r="C178" s="730" t="s">
         <v>206</v>
       </c>
-      <c r="D178" s="656"/>
+      <c r="D178" s="731"/>
       <c r="E178" s="154"/>
       <c r="F178" s="149">
         <f>+F169+F173+F176</f>
@@ -19736,11 +19728,11 @@
     </row>
     <row r="180" spans="1:19" ht="15.9" customHeight="1">
       <c r="A180" s="107"/>
-      <c r="B180" s="642" t="s">
+      <c r="B180" s="654" t="s">
         <v>207</v>
       </c>
-      <c r="C180" s="643"/>
-      <c r="D180" s="644"/>
+      <c r="C180" s="655"/>
+      <c r="D180" s="670"/>
       <c r="E180" s="379"/>
       <c r="F180" s="379" t="s">
         <v>191</v>
@@ -19759,8 +19751,8 @@
     <row r="181" spans="1:19" ht="15.9" customHeight="1">
       <c r="A181" s="107"/>
       <c r="B181" s="99"/>
-      <c r="C181" s="648"/>
-      <c r="D181" s="649"/>
+      <c r="C181" s="671"/>
+      <c r="D181" s="672"/>
       <c r="E181" s="59"/>
       <c r="F181" s="56"/>
       <c r="G181" s="388"/>
@@ -19771,10 +19763,10 @@
     <row r="182" spans="1:19" ht="15.9" customHeight="1">
       <c r="A182" s="107"/>
       <c r="B182" s="99"/>
-      <c r="C182" s="639" t="s">
+      <c r="C182" s="656" t="s">
         <v>208</v>
       </c>
-      <c r="D182" s="638"/>
+      <c r="D182" s="657"/>
       <c r="E182" s="100"/>
       <c r="F182" s="101"/>
       <c r="G182" s="209">
@@ -19791,10 +19783,10 @@
     <row r="183" spans="1:19" ht="15.9" customHeight="1">
       <c r="A183" s="107"/>
       <c r="B183" s="99"/>
-      <c r="C183" s="637" t="s">
+      <c r="C183" s="650" t="s">
         <v>209</v>
       </c>
-      <c r="D183" s="638"/>
+      <c r="D183" s="657"/>
       <c r="E183" s="100"/>
       <c r="F183" s="101"/>
       <c r="G183" s="209">
@@ -19811,10 +19803,10 @@
     <row r="184" spans="1:19" ht="15.9" customHeight="1">
       <c r="A184" s="107"/>
       <c r="B184" s="99"/>
-      <c r="C184" s="637" t="s">
+      <c r="C184" s="650" t="s">
         <v>210</v>
       </c>
-      <c r="D184" s="647"/>
+      <c r="D184" s="651"/>
       <c r="E184" s="100"/>
       <c r="F184" s="101"/>
       <c r="G184" s="209">
@@ -19828,10 +19820,10 @@
     <row r="185" spans="1:19" ht="15.9" customHeight="1">
       <c r="A185" s="107"/>
       <c r="B185" s="99"/>
-      <c r="C185" s="637" t="s">
+      <c r="C185" s="650" t="s">
         <v>211</v>
       </c>
-      <c r="D185" s="638"/>
+      <c r="D185" s="657"/>
       <c r="E185" s="100"/>
       <c r="F185" s="101"/>
       <c r="G185" s="209">
@@ -19848,10 +19840,10 @@
     <row r="186" spans="1:19" ht="15.9" customHeight="1">
       <c r="A186" s="107"/>
       <c r="B186" s="99"/>
-      <c r="C186" s="637" t="s">
+      <c r="C186" s="650" t="s">
         <v>212</v>
       </c>
-      <c r="D186" s="638"/>
+      <c r="D186" s="657"/>
       <c r="E186" s="100"/>
       <c r="F186" s="101"/>
       <c r="G186" s="209">
@@ -19879,25 +19871,25 @@
     </row>
     <row r="188" spans="1:19" ht="15.9" customHeight="1" thickBot="1">
       <c r="A188" s="107"/>
-      <c r="B188" s="672" t="s">
+      <c r="B188" s="727" t="s">
         <v>213</v>
       </c>
-      <c r="C188" s="673"/>
-      <c r="D188" s="673"/>
-      <c r="E188" s="673"/>
-      <c r="F188" s="673"/>
-      <c r="G188" s="673"/>
-      <c r="H188" s="673"/>
-      <c r="I188" s="673"/>
-      <c r="J188" s="674"/>
+      <c r="C188" s="728"/>
+      <c r="D188" s="728"/>
+      <c r="E188" s="728"/>
+      <c r="F188" s="728"/>
+      <c r="G188" s="728"/>
+      <c r="H188" s="728"/>
+      <c r="I188" s="728"/>
+      <c r="J188" s="729"/>
     </row>
     <row r="189" spans="1:19" ht="15.9" customHeight="1">
       <c r="A189" s="51"/>
       <c r="B189" s="164"/>
-      <c r="C189" s="652" t="s">
+      <c r="C189" s="669" t="s">
         <v>214</v>
       </c>
-      <c r="D189" s="652"/>
+      <c r="D189" s="669"/>
       <c r="E189" s="378"/>
       <c r="F189" s="378" t="s">
         <v>191</v>
@@ -19905,7 +19897,7 @@
       <c r="G189" s="168" t="s">
         <v>191</v>
       </c>
-      <c r="H189" s="669"/>
+      <c r="H189" s="724"/>
       <c r="I189" s="229" t="s">
         <v>67</v>
       </c>
@@ -19916,17 +19908,17 @@
     <row r="190" spans="1:19" ht="15.9" customHeight="1">
       <c r="A190" s="51"/>
       <c r="B190" s="162"/>
-      <c r="C190" s="639" t="s">
+      <c r="C190" s="656" t="s">
         <v>215</v>
       </c>
-      <c r="D190" s="638"/>
+      <c r="D190" s="657"/>
       <c r="E190" s="163"/>
       <c r="F190" s="163"/>
       <c r="G190" s="102">
         <f>+G20</f>
         <v>0</v>
       </c>
-      <c r="H190" s="670"/>
+      <c r="H190" s="725"/>
       <c r="I190" s="162"/>
       <c r="J190" s="102">
         <f>+G190/J5</f>
@@ -19936,17 +19928,17 @@
     <row r="191" spans="1:19" ht="15.9" customHeight="1">
       <c r="A191" s="51"/>
       <c r="B191" s="162"/>
-      <c r="C191" s="639" t="s">
+      <c r="C191" s="656" t="s">
         <v>216</v>
       </c>
-      <c r="D191" s="638"/>
+      <c r="D191" s="657"/>
       <c r="E191" s="163"/>
       <c r="F191" s="163"/>
       <c r="G191" s="102">
         <f>+G190*G23</f>
         <v>0</v>
       </c>
-      <c r="H191" s="670"/>
+      <c r="H191" s="725"/>
       <c r="I191" s="162"/>
       <c r="J191" s="102">
         <f>+J190*J23</f>
@@ -19956,17 +19948,17 @@
     <row r="192" spans="1:19" ht="15.9" customHeight="1">
       <c r="A192" s="51"/>
       <c r="B192" s="162"/>
-      <c r="C192" s="653" t="s">
+      <c r="C192" s="694" t="s">
         <v>217</v>
       </c>
-      <c r="D192" s="653"/>
+      <c r="D192" s="694"/>
       <c r="E192" s="163"/>
       <c r="F192" s="163"/>
       <c r="G192" s="102">
         <f>+G191*25%</f>
         <v>0</v>
       </c>
-      <c r="H192" s="670"/>
+      <c r="H192" s="725"/>
       <c r="I192" s="162"/>
       <c r="J192" s="102">
         <f>+J191*25%</f>
@@ -19976,17 +19968,17 @@
     <row r="193" spans="1:20" ht="15.9" customHeight="1">
       <c r="A193" s="51"/>
       <c r="B193" s="162"/>
-      <c r="C193" s="637" t="s">
+      <c r="C193" s="650" t="s">
         <v>218</v>
       </c>
-      <c r="D193" s="638"/>
+      <c r="D193" s="657"/>
       <c r="E193" s="163"/>
       <c r="F193" s="163"/>
       <c r="G193" s="102">
         <f>+G192*1%</f>
         <v>0</v>
       </c>
-      <c r="H193" s="670"/>
+      <c r="H193" s="725"/>
       <c r="I193" s="162"/>
       <c r="J193" s="102">
         <f>G193/J5</f>
@@ -19996,17 +19988,17 @@
     <row r="194" spans="1:20" ht="15.9" customHeight="1">
       <c r="A194" s="51"/>
       <c r="B194" s="162"/>
-      <c r="C194" s="637" t="s">
+      <c r="C194" s="650" t="s">
         <v>219</v>
       </c>
-      <c r="D194" s="638"/>
+      <c r="D194" s="657"/>
       <c r="E194" s="163"/>
       <c r="F194" s="163"/>
       <c r="G194" s="102">
         <f>G193*0.5</f>
         <v>0</v>
       </c>
-      <c r="H194" s="670"/>
+      <c r="H194" s="725"/>
       <c r="I194" s="162"/>
       <c r="J194" s="102">
         <f>G194/J5</f>
@@ -20016,17 +20008,17 @@
     <row r="195" spans="1:20" ht="15.9" customHeight="1" thickBot="1">
       <c r="A195" s="51"/>
       <c r="B195" s="162"/>
-      <c r="C195" s="653" t="s">
+      <c r="C195" s="694" t="s">
         <v>220</v>
       </c>
-      <c r="D195" s="653"/>
+      <c r="D195" s="694"/>
       <c r="E195" s="163"/>
       <c r="F195" s="163"/>
       <c r="G195" s="110">
         <f>G83</f>
         <v>511749.08384775487</v>
       </c>
-      <c r="H195" s="670"/>
+      <c r="H195" s="725"/>
       <c r="I195" s="162"/>
       <c r="J195" s="110">
         <f>+J193+J194</f>
@@ -20036,8 +20028,8 @@
     <row r="196" spans="1:20" ht="15.9" customHeight="1">
       <c r="A196" s="166"/>
       <c r="B196" s="382"/>
-      <c r="C196" s="654"/>
-      <c r="D196" s="654"/>
+      <c r="C196" s="662"/>
+      <c r="D196" s="662"/>
       <c r="E196" s="379"/>
       <c r="F196" s="379" t="s">
         <v>191</v>
@@ -20045,7 +20037,7 @@
       <c r="G196" s="53" t="s">
         <v>191</v>
       </c>
-      <c r="H196" s="670"/>
+      <c r="H196" s="725"/>
       <c r="I196" s="229" t="s">
         <v>67</v>
       </c>
@@ -20056,17 +20048,17 @@
     <row r="197" spans="1:20" ht="15.9" customHeight="1">
       <c r="A197" s="74"/>
       <c r="B197" s="99"/>
-      <c r="C197" s="639" t="s">
+      <c r="C197" s="656" t="s">
         <v>221</v>
       </c>
-      <c r="D197" s="638"/>
+      <c r="D197" s="657"/>
       <c r="E197" s="58"/>
       <c r="F197" s="50"/>
       <c r="G197" s="102">
         <f>+G55</f>
         <v>72</v>
       </c>
-      <c r="H197" s="670"/>
+      <c r="H197" s="725"/>
       <c r="I197" s="91"/>
       <c r="J197" s="102">
         <f>+J55</f>
@@ -20076,17 +20068,17 @@
     <row r="198" spans="1:20" ht="15.9" customHeight="1">
       <c r="A198" s="74"/>
       <c r="B198" s="99"/>
-      <c r="C198" s="639" t="s">
+      <c r="C198" s="656" t="s">
         <v>222</v>
       </c>
-      <c r="D198" s="638"/>
+      <c r="D198" s="657"/>
       <c r="E198" s="58"/>
       <c r="F198" s="50"/>
       <c r="G198" s="102">
         <f>F141</f>
         <v>9515</v>
       </c>
-      <c r="H198" s="670"/>
+      <c r="H198" s="725"/>
       <c r="I198" s="91"/>
       <c r="J198" s="102">
         <f>I141</f>
@@ -20096,17 +20088,17 @@
     <row r="199" spans="1:20" ht="15.9" customHeight="1">
       <c r="A199" s="120"/>
       <c r="B199" s="99"/>
-      <c r="C199" s="639" t="s">
+      <c r="C199" s="656" t="s">
         <v>223</v>
       </c>
-      <c r="D199" s="638"/>
+      <c r="D199" s="657"/>
       <c r="E199" s="58"/>
       <c r="F199" s="50"/>
       <c r="G199" s="111">
         <f>+F61</f>
         <v>129</v>
       </c>
-      <c r="H199" s="670"/>
+      <c r="H199" s="725"/>
       <c r="I199" s="91"/>
       <c r="J199" s="111">
         <f>+I61</f>
@@ -20116,17 +20108,17 @@
     <row r="200" spans="1:20" ht="15.9" customHeight="1">
       <c r="A200" s="74"/>
       <c r="B200" s="99"/>
-      <c r="C200" s="639" t="s">
+      <c r="C200" s="656" t="s">
         <v>223</v>
       </c>
-      <c r="D200" s="638"/>
+      <c r="D200" s="657"/>
       <c r="E200" s="58"/>
       <c r="F200" s="50"/>
       <c r="G200" s="102">
         <f>(G198*G199*G197)</f>
         <v>88375320</v>
       </c>
-      <c r="H200" s="670"/>
+      <c r="H200" s="725"/>
       <c r="I200" s="91"/>
       <c r="J200" s="102">
         <f>+G200/$J$5</f>
@@ -20136,17 +20128,17 @@
     <row r="201" spans="1:20" ht="15.9" customHeight="1">
       <c r="A201" s="74"/>
       <c r="B201" s="99"/>
-      <c r="C201" s="639" t="s">
+      <c r="C201" s="656" t="s">
         <v>224</v>
       </c>
-      <c r="D201" s="638"/>
+      <c r="D201" s="657"/>
       <c r="E201" s="58"/>
       <c r="F201" s="50"/>
       <c r="G201" s="102">
         <f>G200/G197*12</f>
         <v>14729220</v>
       </c>
-      <c r="H201" s="670"/>
+      <c r="H201" s="725"/>
       <c r="I201" s="91"/>
       <c r="J201" s="102">
         <f>+G201/$J$5</f>
@@ -20156,17 +20148,17 @@
     <row r="202" spans="1:20" ht="15.9" customHeight="1">
       <c r="A202" s="74"/>
       <c r="B202" s="99"/>
-      <c r="C202" s="639" t="s">
+      <c r="C202" s="656" t="s">
         <v>225</v>
       </c>
-      <c r="D202" s="638"/>
+      <c r="D202" s="657"/>
       <c r="E202" s="58"/>
       <c r="F202" s="50"/>
       <c r="G202" s="102">
         <f>(+G221*115%)/5</f>
         <v>0</v>
       </c>
-      <c r="H202" s="670"/>
+      <c r="H202" s="725"/>
       <c r="I202" s="91"/>
       <c r="J202" s="102">
         <f>+G202/$J$5</f>
@@ -20176,17 +20168,17 @@
     <row r="203" spans="1:20" ht="15.9" customHeight="1">
       <c r="A203" s="74"/>
       <c r="B203" s="99"/>
-      <c r="C203" s="639" t="s">
+      <c r="C203" s="656" t="s">
         <v>226</v>
       </c>
-      <c r="D203" s="638"/>
+      <c r="D203" s="657"/>
       <c r="E203" s="58"/>
       <c r="F203" s="50"/>
       <c r="G203" s="102">
         <f>(+I221*115%)/5</f>
         <v>2765157.6185172233</v>
       </c>
-      <c r="H203" s="670"/>
+      <c r="H203" s="725"/>
       <c r="I203" s="91"/>
       <c r="J203" s="102">
         <f>+G203/$J$5</f>
@@ -20196,17 +20188,17 @@
     <row r="204" spans="1:20" ht="15.9" customHeight="1">
       <c r="A204" s="74"/>
       <c r="B204" s="99"/>
-      <c r="C204" s="639" t="s">
+      <c r="C204" s="656" t="s">
         <v>36</v>
       </c>
-      <c r="D204" s="638"/>
+      <c r="D204" s="657"/>
       <c r="E204" s="58"/>
       <c r="F204" s="50"/>
       <c r="G204" s="102">
         <f>+G68</f>
         <v>11418000</v>
       </c>
-      <c r="H204" s="670"/>
+      <c r="H204" s="725"/>
       <c r="I204" s="91"/>
       <c r="J204" s="102">
         <f>+G204/$J$5</f>
@@ -20216,17 +20208,17 @@
     <row r="205" spans="1:20" ht="15.9" customHeight="1">
       <c r="A205" s="74"/>
       <c r="B205" s="99"/>
-      <c r="C205" s="637" t="s">
+      <c r="C205" s="650" t="s">
         <v>227</v>
       </c>
-      <c r="D205" s="638"/>
+      <c r="D205" s="657"/>
       <c r="E205" s="58"/>
       <c r="F205" s="50"/>
       <c r="G205" s="102">
         <f>(G201+G202+G203+G204)*1.18</f>
         <v>34116605.589850321</v>
       </c>
-      <c r="H205" s="670"/>
+      <c r="H205" s="725"/>
       <c r="I205" s="91"/>
       <c r="J205" s="102">
         <f>+J201+J202+J203+J204</f>
@@ -20236,17 +20228,17 @@
     <row r="206" spans="1:20" ht="15.9" customHeight="1">
       <c r="A206" s="74"/>
       <c r="B206" s="99"/>
-      <c r="C206" s="637" t="s">
+      <c r="C206" s="650" t="s">
         <v>228</v>
       </c>
-      <c r="D206" s="638"/>
+      <c r="D206" s="657"/>
       <c r="E206" s="58"/>
       <c r="F206" s="50"/>
       <c r="G206" s="102">
         <f>G205*1%</f>
         <v>341166.05589850323</v>
       </c>
-      <c r="H206" s="670"/>
+      <c r="H206" s="725"/>
       <c r="I206" s="91"/>
       <c r="J206" s="102">
         <f>J205*1%</f>
@@ -20256,17 +20248,17 @@
     <row r="207" spans="1:20" ht="15.9" customHeight="1">
       <c r="A207" s="74"/>
       <c r="B207" s="99"/>
-      <c r="C207" s="639" t="s">
+      <c r="C207" s="656" t="s">
         <v>229</v>
       </c>
-      <c r="D207" s="638"/>
+      <c r="D207" s="657"/>
       <c r="E207" s="58"/>
       <c r="F207" s="50"/>
       <c r="G207" s="102">
         <f>G205*0.5%</f>
         <v>170583.02794925161</v>
       </c>
-      <c r="H207" s="670"/>
+      <c r="H207" s="725"/>
       <c r="I207" s="91"/>
       <c r="J207" s="102">
         <f>J205*0.5%</f>
@@ -20276,17 +20268,17 @@
     <row r="208" spans="1:20" ht="15.9" customHeight="1">
       <c r="A208" s="74"/>
       <c r="B208" s="99"/>
-      <c r="C208" s="640" t="s">
+      <c r="C208" s="652" t="s">
         <v>220</v>
       </c>
-      <c r="D208" s="641"/>
+      <c r="D208" s="653"/>
       <c r="E208" s="58"/>
       <c r="F208" s="50"/>
       <c r="G208" s="102">
         <f>G206+G207</f>
         <v>511749.08384775487</v>
       </c>
-      <c r="H208" s="670"/>
+      <c r="H208" s="725"/>
       <c r="I208" s="91"/>
       <c r="J208" s="102">
         <v>0</v>
@@ -20301,7 +20293,7 @@
       <c r="E209" s="80"/>
       <c r="F209" s="51"/>
       <c r="G209" s="337"/>
-      <c r="H209" s="670"/>
+      <c r="H209" s="725"/>
       <c r="I209" s="94"/>
       <c r="J209" s="81"/>
     </row>
@@ -20323,7 +20315,7 @@
       <c r="G210" s="161" t="s">
         <v>234</v>
       </c>
-      <c r="H210" s="670"/>
+      <c r="H210" s="725"/>
       <c r="I210" s="379" t="s">
         <v>235</v>
       </c>
@@ -20348,7 +20340,7 @@
       <c r="G211" s="101">
         <v>0</v>
       </c>
-      <c r="H211" s="670"/>
+      <c r="H211" s="725"/>
       <c r="I211" s="101">
         <f>'Lease Rent'!O39</f>
         <v>1178337.5999999999</v>
@@ -20377,7 +20369,7 @@
       <c r="G212" s="101">
         <v>0</v>
       </c>
-      <c r="H212" s="670"/>
+      <c r="H212" s="725"/>
       <c r="I212" s="101">
         <f>'Lease Rent'!O51</f>
         <v>1826423.2800000005</v>
@@ -20405,7 +20397,7 @@
       <c r="G213" s="101">
         <v>0</v>
       </c>
-      <c r="H213" s="670"/>
+      <c r="H213" s="725"/>
       <c r="I213" s="101">
         <f>'Lease Rent'!O63</f>
         <v>1917744.4440000001</v>
@@ -20433,7 +20425,7 @@
       <c r="G214" s="101">
         <v>0</v>
       </c>
-      <c r="H214" s="670"/>
+      <c r="H214" s="725"/>
       <c r="I214" s="101">
         <f>'Lease Rent'!O75</f>
         <v>2013631.6662000006</v>
@@ -20461,7 +20453,7 @@
       <c r="G215" s="101">
         <v>0</v>
       </c>
-      <c r="H215" s="670"/>
+      <c r="H215" s="725"/>
       <c r="I215" s="101">
         <f>'Lease Rent'!O87</f>
         <v>2114313.2495100005</v>
@@ -20487,7 +20479,7 @@
         <v>0</v>
       </c>
       <c r="G216" s="113"/>
-      <c r="H216" s="670"/>
+      <c r="H216" s="725"/>
       <c r="I216" s="101">
         <f>'Lease Rent'!O99</f>
         <v>2220028.9119855007</v>
@@ -20515,7 +20507,7 @@
         <f>'Lease Rent'!R9</f>
         <v>0</v>
       </c>
-      <c r="H217" s="670"/>
+      <c r="H217" s="725"/>
       <c r="I217" s="101">
         <f>'Lease Rent'!O103</f>
         <v>751945.27664025011</v>
@@ -20538,7 +20530,7 @@
         <f>'Lease Rent'!R10</f>
         <v>0</v>
       </c>
-      <c r="H218" s="670"/>
+      <c r="H218" s="725"/>
       <c r="I218" s="301"/>
       <c r="J218" s="111"/>
     </row>
@@ -20555,7 +20547,7 @@
         <v>0</v>
       </c>
       <c r="G219" s="118"/>
-      <c r="H219" s="670"/>
+      <c r="H219" s="725"/>
       <c r="I219" s="101"/>
       <c r="J219" s="111"/>
     </row>
@@ -20569,7 +20561,7 @@
       <c r="E220" s="117"/>
       <c r="F220" s="232"/>
       <c r="G220" s="118"/>
-      <c r="H220" s="670"/>
+      <c r="H220" s="725"/>
       <c r="I220" s="101"/>
       <c r="J220" s="111"/>
     </row>
@@ -20592,7 +20584,7 @@
         <f>SUM(G211:G220)</f>
         <v>0</v>
       </c>
-      <c r="H221" s="671"/>
+      <c r="H221" s="726"/>
       <c r="I221" s="283">
         <f>SUM(I211:I220)</f>
         <v>12022424.428335754</v>
@@ -20662,35 +20654,191 @@
     </row>
   </sheetData>
   <mergeCells count="238">
-    <mergeCell ref="F138:G138"/>
-    <mergeCell ref="I138:J138"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="B110:D110"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="B135:D135"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C120:D120"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="C125:D125"/>
-    <mergeCell ref="C118:D118"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C205:D205"/>
+    <mergeCell ref="C204:D204"/>
+    <mergeCell ref="C162:D162"/>
+    <mergeCell ref="B139:D139"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="C193:D193"/>
+    <mergeCell ref="C194:D194"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="C190:D190"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C161:D161"/>
+    <mergeCell ref="C191:D191"/>
+    <mergeCell ref="B180:D180"/>
+    <mergeCell ref="C163:D163"/>
+    <mergeCell ref="C166:D166"/>
+    <mergeCell ref="C206:D206"/>
+    <mergeCell ref="C207:D207"/>
+    <mergeCell ref="C208:D208"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C175:D175"/>
+    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="C143:D143"/>
+    <mergeCell ref="C200:D200"/>
+    <mergeCell ref="C201:D201"/>
+    <mergeCell ref="C202:D202"/>
+    <mergeCell ref="C203:D203"/>
+    <mergeCell ref="C189:D189"/>
+    <mergeCell ref="C192:D192"/>
+    <mergeCell ref="C195:D195"/>
+    <mergeCell ref="C196:D196"/>
+    <mergeCell ref="C197:D197"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C182:D182"/>
+    <mergeCell ref="C186:D186"/>
+    <mergeCell ref="C169:D169"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="C170:D170"/>
+    <mergeCell ref="C184:D184"/>
+    <mergeCell ref="C171:D171"/>
+    <mergeCell ref="C141:D141"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="C123:D123"/>
+    <mergeCell ref="C172:D172"/>
+    <mergeCell ref="C168:D168"/>
+    <mergeCell ref="B148:D148"/>
+    <mergeCell ref="B164:D165"/>
+    <mergeCell ref="B126:D126"/>
+    <mergeCell ref="C159:D159"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="C156:D156"/>
+    <mergeCell ref="C145:D145"/>
+    <mergeCell ref="C140:D140"/>
+    <mergeCell ref="C167:D167"/>
+    <mergeCell ref="C183:D183"/>
+    <mergeCell ref="H189:H221"/>
+    <mergeCell ref="C160:D160"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B188:J188"/>
+    <mergeCell ref="C173:D173"/>
+    <mergeCell ref="C177:D177"/>
+    <mergeCell ref="C178:D178"/>
+    <mergeCell ref="C181:D181"/>
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="C199:D199"/>
+    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="C150:D150"/>
+    <mergeCell ref="C151:D151"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="C144:D144"/>
+    <mergeCell ref="C185:D185"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B1:J3"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C49:D49"/>
     <mergeCell ref="F53:G53"/>
     <mergeCell ref="F49:G49"/>
     <mergeCell ref="F50:G50"/>
@@ -20715,191 +20863,35 @@
     <mergeCell ref="C136:D136"/>
     <mergeCell ref="C137:D137"/>
     <mergeCell ref="C134:D134"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B1:J3"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="H189:H221"/>
-    <mergeCell ref="C160:D160"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B188:J188"/>
-    <mergeCell ref="C173:D173"/>
-    <mergeCell ref="C177:D177"/>
-    <mergeCell ref="C178:D178"/>
-    <mergeCell ref="C181:D181"/>
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="C199:D199"/>
-    <mergeCell ref="C176:D176"/>
-    <mergeCell ref="C150:D150"/>
-    <mergeCell ref="C151:D151"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="I59:J59"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="C144:D144"/>
-    <mergeCell ref="C185:D185"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C182:D182"/>
-    <mergeCell ref="C186:D186"/>
-    <mergeCell ref="C169:D169"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="C170:D170"/>
-    <mergeCell ref="C184:D184"/>
-    <mergeCell ref="C171:D171"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="C123:D123"/>
-    <mergeCell ref="C172:D172"/>
-    <mergeCell ref="C168:D168"/>
-    <mergeCell ref="B148:D148"/>
-    <mergeCell ref="B164:D165"/>
-    <mergeCell ref="B126:D126"/>
-    <mergeCell ref="C159:D159"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="C156:D156"/>
-    <mergeCell ref="C145:D145"/>
-    <mergeCell ref="C140:D140"/>
-    <mergeCell ref="C167:D167"/>
-    <mergeCell ref="C183:D183"/>
-    <mergeCell ref="C206:D206"/>
-    <mergeCell ref="C207:D207"/>
-    <mergeCell ref="C208:D208"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C175:D175"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="C143:D143"/>
-    <mergeCell ref="C200:D200"/>
-    <mergeCell ref="C201:D201"/>
-    <mergeCell ref="C202:D202"/>
-    <mergeCell ref="C203:D203"/>
-    <mergeCell ref="C189:D189"/>
-    <mergeCell ref="C192:D192"/>
-    <mergeCell ref="C195:D195"/>
-    <mergeCell ref="C196:D196"/>
-    <mergeCell ref="C197:D197"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C205:D205"/>
-    <mergeCell ref="C204:D204"/>
-    <mergeCell ref="C162:D162"/>
-    <mergeCell ref="B139:D139"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="C121:D121"/>
-    <mergeCell ref="C193:D193"/>
-    <mergeCell ref="C194:D194"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="C190:D190"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="C161:D161"/>
-    <mergeCell ref="C191:D191"/>
-    <mergeCell ref="B180:D180"/>
-    <mergeCell ref="C163:D163"/>
-    <mergeCell ref="C166:D166"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="B135:D135"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C120:D120"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="C125:D125"/>
+    <mergeCell ref="C118:D118"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="F138:G138"/>
+    <mergeCell ref="I138:J138"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="B110:D110"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C108:D108"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.25" top="0.75" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="58" orientation="portrait" r:id="rId1"/>
@@ -20973,215 +20965,215 @@
       <c r="S1" s="1"/>
     </row>
     <row r="2" spans="1:27" ht="11.25" customHeight="1">
-      <c r="A2" s="616"/>
-      <c r="B2" s="617"/>
-      <c r="C2" s="617"/>
-      <c r="D2" s="617"/>
-      <c r="E2" s="617"/>
-      <c r="F2" s="617"/>
-      <c r="G2" s="617"/>
-      <c r="H2" s="617"/>
-      <c r="I2" s="617"/>
-      <c r="J2" s="617"/>
-      <c r="K2" s="617"/>
-      <c r="L2" s="617"/>
-      <c r="M2" s="617"/>
-      <c r="N2" s="617"/>
-      <c r="O2" s="617"/>
-      <c r="P2" s="617"/>
-      <c r="Q2" s="617"/>
-      <c r="R2" s="617"/>
-      <c r="S2" s="617"/>
-      <c r="T2" s="617"/>
-      <c r="U2" s="617"/>
-      <c r="V2" s="617"/>
-      <c r="W2" s="617"/>
-      <c r="X2" s="617"/>
-      <c r="Y2" s="617"/>
-      <c r="Z2" s="617"/>
-      <c r="AA2" s="618"/>
+      <c r="A2" s="710"/>
+      <c r="B2" s="711"/>
+      <c r="C2" s="711"/>
+      <c r="D2" s="711"/>
+      <c r="E2" s="711"/>
+      <c r="F2" s="711"/>
+      <c r="G2" s="711"/>
+      <c r="H2" s="711"/>
+      <c r="I2" s="711"/>
+      <c r="J2" s="711"/>
+      <c r="K2" s="711"/>
+      <c r="L2" s="711"/>
+      <c r="M2" s="711"/>
+      <c r="N2" s="711"/>
+      <c r="O2" s="711"/>
+      <c r="P2" s="711"/>
+      <c r="Q2" s="711"/>
+      <c r="R2" s="711"/>
+      <c r="S2" s="711"/>
+      <c r="T2" s="711"/>
+      <c r="U2" s="711"/>
+      <c r="V2" s="711"/>
+      <c r="W2" s="711"/>
+      <c r="X2" s="711"/>
+      <c r="Y2" s="711"/>
+      <c r="Z2" s="711"/>
+      <c r="AA2" s="747"/>
     </row>
     <row r="3" spans="1:27" ht="11.25" customHeight="1">
-      <c r="A3" s="619"/>
-      <c r="B3" s="620"/>
-      <c r="C3" s="620"/>
-      <c r="D3" s="620"/>
-      <c r="E3" s="620"/>
-      <c r="F3" s="620"/>
-      <c r="G3" s="620"/>
-      <c r="H3" s="620"/>
-      <c r="I3" s="620"/>
-      <c r="J3" s="620"/>
-      <c r="K3" s="620"/>
-      <c r="L3" s="620"/>
-      <c r="M3" s="620"/>
-      <c r="N3" s="620"/>
-      <c r="O3" s="620"/>
-      <c r="P3" s="620"/>
-      <c r="Q3" s="620"/>
-      <c r="R3" s="620"/>
-      <c r="S3" s="620"/>
-      <c r="T3" s="620"/>
-      <c r="U3" s="620"/>
-      <c r="V3" s="620"/>
-      <c r="W3" s="620"/>
-      <c r="X3" s="620"/>
-      <c r="Y3" s="620"/>
-      <c r="Z3" s="620"/>
-      <c r="AA3" s="621"/>
+      <c r="A3" s="748"/>
+      <c r="B3" s="749"/>
+      <c r="C3" s="749"/>
+      <c r="D3" s="749"/>
+      <c r="E3" s="749"/>
+      <c r="F3" s="749"/>
+      <c r="G3" s="749"/>
+      <c r="H3" s="749"/>
+      <c r="I3" s="749"/>
+      <c r="J3" s="749"/>
+      <c r="K3" s="749"/>
+      <c r="L3" s="749"/>
+      <c r="M3" s="749"/>
+      <c r="N3" s="749"/>
+      <c r="O3" s="749"/>
+      <c r="P3" s="749"/>
+      <c r="Q3" s="749"/>
+      <c r="R3" s="749"/>
+      <c r="S3" s="749"/>
+      <c r="T3" s="749"/>
+      <c r="U3" s="749"/>
+      <c r="V3" s="749"/>
+      <c r="W3" s="749"/>
+      <c r="X3" s="749"/>
+      <c r="Y3" s="749"/>
+      <c r="Z3" s="749"/>
+      <c r="AA3" s="750"/>
     </row>
     <row r="4" spans="1:27" ht="12" customHeight="1" thickBot="1">
-      <c r="A4" s="622"/>
-      <c r="B4" s="623"/>
-      <c r="C4" s="623"/>
-      <c r="D4" s="623"/>
-      <c r="E4" s="623"/>
-      <c r="F4" s="623"/>
-      <c r="G4" s="623"/>
-      <c r="H4" s="623"/>
-      <c r="I4" s="623"/>
-      <c r="J4" s="623"/>
-      <c r="K4" s="623"/>
-      <c r="L4" s="623"/>
-      <c r="M4" s="623"/>
-      <c r="N4" s="623"/>
-      <c r="O4" s="623"/>
-      <c r="P4" s="623"/>
-      <c r="Q4" s="623"/>
-      <c r="R4" s="623"/>
-      <c r="S4" s="623"/>
-      <c r="T4" s="623"/>
-      <c r="U4" s="623"/>
-      <c r="V4" s="623"/>
-      <c r="W4" s="623"/>
-      <c r="X4" s="623"/>
-      <c r="Y4" s="623"/>
-      <c r="Z4" s="623"/>
-      <c r="AA4" s="624"/>
+      <c r="A4" s="751"/>
+      <c r="B4" s="752"/>
+      <c r="C4" s="752"/>
+      <c r="D4" s="752"/>
+      <c r="E4" s="752"/>
+      <c r="F4" s="752"/>
+      <c r="G4" s="752"/>
+      <c r="H4" s="752"/>
+      <c r="I4" s="752"/>
+      <c r="J4" s="752"/>
+      <c r="K4" s="752"/>
+      <c r="L4" s="752"/>
+      <c r="M4" s="752"/>
+      <c r="N4" s="752"/>
+      <c r="O4" s="752"/>
+      <c r="P4" s="752"/>
+      <c r="Q4" s="752"/>
+      <c r="R4" s="752"/>
+      <c r="S4" s="752"/>
+      <c r="T4" s="752"/>
+      <c r="U4" s="752"/>
+      <c r="V4" s="752"/>
+      <c r="W4" s="752"/>
+      <c r="X4" s="752"/>
+      <c r="Y4" s="752"/>
+      <c r="Z4" s="752"/>
+      <c r="AA4" s="753"/>
     </row>
     <row r="5" spans="1:27" ht="12.75" customHeight="1">
-      <c r="A5" s="616" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="617"/>
-      <c r="C5" s="617"/>
-      <c r="D5" s="617"/>
-      <c r="E5" s="617"/>
-      <c r="F5" s="617"/>
-      <c r="G5" s="617"/>
-      <c r="H5" s="617"/>
-      <c r="I5" s="617"/>
-      <c r="J5" s="617"/>
-      <c r="K5" s="617"/>
-      <c r="L5" s="617"/>
-      <c r="M5" s="617"/>
-      <c r="N5" s="617"/>
-      <c r="O5" s="617"/>
-      <c r="P5" s="617"/>
-      <c r="Q5" s="617"/>
-      <c r="R5" s="617"/>
-      <c r="S5" s="617"/>
-      <c r="T5" s="617"/>
-      <c r="U5" s="617"/>
-      <c r="V5" s="617"/>
-      <c r="W5" s="617"/>
-      <c r="X5" s="617"/>
-      <c r="Y5" s="617"/>
-      <c r="Z5" s="617"/>
-      <c r="AA5" s="618"/>
+      <c r="A5" s="710" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="711"/>
+      <c r="C5" s="711"/>
+      <c r="D5" s="711"/>
+      <c r="E5" s="711"/>
+      <c r="F5" s="711"/>
+      <c r="G5" s="711"/>
+      <c r="H5" s="711"/>
+      <c r="I5" s="711"/>
+      <c r="J5" s="711"/>
+      <c r="K5" s="711"/>
+      <c r="L5" s="711"/>
+      <c r="M5" s="711"/>
+      <c r="N5" s="711"/>
+      <c r="O5" s="711"/>
+      <c r="P5" s="711"/>
+      <c r="Q5" s="711"/>
+      <c r="R5" s="711"/>
+      <c r="S5" s="711"/>
+      <c r="T5" s="711"/>
+      <c r="U5" s="711"/>
+      <c r="V5" s="711"/>
+      <c r="W5" s="711"/>
+      <c r="X5" s="711"/>
+      <c r="Y5" s="711"/>
+      <c r="Z5" s="711"/>
+      <c r="AA5" s="747"/>
     </row>
     <row r="6" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A6" s="625"/>
-      <c r="B6" s="626"/>
-      <c r="C6" s="626"/>
-      <c r="D6" s="626"/>
-      <c r="E6" s="626"/>
-      <c r="F6" s="626"/>
-      <c r="G6" s="626"/>
-      <c r="H6" s="626"/>
-      <c r="I6" s="626"/>
-      <c r="J6" s="626"/>
-      <c r="K6" s="626"/>
-      <c r="L6" s="626"/>
-      <c r="M6" s="626"/>
-      <c r="N6" s="626"/>
-      <c r="O6" s="626"/>
-      <c r="P6" s="626"/>
-      <c r="Q6" s="626"/>
-      <c r="R6" s="626"/>
-      <c r="S6" s="626"/>
-      <c r="T6" s="626"/>
-      <c r="U6" s="626"/>
-      <c r="V6" s="626"/>
-      <c r="W6" s="626"/>
-      <c r="X6" s="626"/>
-      <c r="Y6" s="626"/>
-      <c r="Z6" s="626"/>
-      <c r="AA6" s="627"/>
+      <c r="A6" s="754"/>
+      <c r="B6" s="755"/>
+      <c r="C6" s="755"/>
+      <c r="D6" s="755"/>
+      <c r="E6" s="755"/>
+      <c r="F6" s="755"/>
+      <c r="G6" s="755"/>
+      <c r="H6" s="755"/>
+      <c r="I6" s="755"/>
+      <c r="J6" s="755"/>
+      <c r="K6" s="755"/>
+      <c r="L6" s="755"/>
+      <c r="M6" s="755"/>
+      <c r="N6" s="755"/>
+      <c r="O6" s="755"/>
+      <c r="P6" s="755"/>
+      <c r="Q6" s="755"/>
+      <c r="R6" s="755"/>
+      <c r="S6" s="755"/>
+      <c r="T6" s="755"/>
+      <c r="U6" s="755"/>
+      <c r="V6" s="755"/>
+      <c r="W6" s="755"/>
+      <c r="X6" s="755"/>
+      <c r="Y6" s="755"/>
+      <c r="Z6" s="755"/>
+      <c r="AA6" s="756"/>
     </row>
     <row r="7" spans="1:27" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A7" s="628" t="s">
+      <c r="A7" s="757" t="s">
         <v>340</v>
       </c>
-      <c r="B7" s="629"/>
-      <c r="C7" s="629"/>
-      <c r="D7" s="629"/>
-      <c r="E7" s="629"/>
-      <c r="F7" s="629"/>
-      <c r="G7" s="629"/>
-      <c r="H7" s="629"/>
-      <c r="I7" s="629"/>
-      <c r="J7" s="629"/>
-      <c r="K7" s="629"/>
-      <c r="L7" s="629"/>
-      <c r="M7" s="629"/>
-      <c r="N7" s="629"/>
-      <c r="O7" s="629"/>
-      <c r="P7" s="630"/>
-      <c r="Q7" s="630"/>
-      <c r="R7" s="630"/>
-      <c r="S7" s="630"/>
-      <c r="T7" s="630"/>
-      <c r="U7" s="630"/>
-      <c r="V7" s="630"/>
-      <c r="W7" s="630"/>
-      <c r="X7" s="630"/>
-      <c r="Y7" s="630"/>
-      <c r="Z7" s="630"/>
-      <c r="AA7" s="631"/>
+      <c r="B7" s="758"/>
+      <c r="C7" s="758"/>
+      <c r="D7" s="758"/>
+      <c r="E7" s="758"/>
+      <c r="F7" s="758"/>
+      <c r="G7" s="758"/>
+      <c r="H7" s="758"/>
+      <c r="I7" s="758"/>
+      <c r="J7" s="758"/>
+      <c r="K7" s="758"/>
+      <c r="L7" s="758"/>
+      <c r="M7" s="758"/>
+      <c r="N7" s="758"/>
+      <c r="O7" s="758"/>
+      <c r="P7" s="759"/>
+      <c r="Q7" s="759"/>
+      <c r="R7" s="759"/>
+      <c r="S7" s="759"/>
+      <c r="T7" s="759"/>
+      <c r="U7" s="759"/>
+      <c r="V7" s="759"/>
+      <c r="W7" s="759"/>
+      <c r="X7" s="759"/>
+      <c r="Y7" s="759"/>
+      <c r="Z7" s="759"/>
+      <c r="AA7" s="760"/>
     </row>
     <row r="8" spans="1:27" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A8" s="632" t="s">
+      <c r="A8" s="761" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="633"/>
-      <c r="C8" s="633"/>
-      <c r="D8" s="633"/>
-      <c r="E8" s="633"/>
-      <c r="F8" s="633"/>
-      <c r="G8" s="633"/>
-      <c r="H8" s="633"/>
-      <c r="I8" s="633"/>
-      <c r="J8" s="633"/>
-      <c r="K8" s="633"/>
-      <c r="L8" s="633"/>
-      <c r="M8" s="633"/>
-      <c r="N8" s="634"/>
+      <c r="B8" s="762"/>
+      <c r="C8" s="762"/>
+      <c r="D8" s="762"/>
+      <c r="E8" s="762"/>
+      <c r="F8" s="762"/>
+      <c r="G8" s="762"/>
+      <c r="H8" s="762"/>
+      <c r="I8" s="762"/>
+      <c r="J8" s="762"/>
+      <c r="K8" s="762"/>
+      <c r="L8" s="762"/>
+      <c r="M8" s="762"/>
+      <c r="N8" s="763"/>
       <c r="O8" s="6"/>
-      <c r="P8" s="632" t="s">
+      <c r="P8" s="761" t="s">
         <v>2</v>
       </c>
-      <c r="Q8" s="633"/>
-      <c r="R8" s="633"/>
-      <c r="S8" s="633"/>
-      <c r="T8" s="633"/>
-      <c r="U8" s="633"/>
-      <c r="V8" s="633"/>
-      <c r="W8" s="633"/>
-      <c r="X8" s="633"/>
-      <c r="Y8" s="633"/>
-      <c r="Z8" s="633"/>
-      <c r="AA8" s="635"/>
+      <c r="Q8" s="762"/>
+      <c r="R8" s="762"/>
+      <c r="S8" s="762"/>
+      <c r="T8" s="762"/>
+      <c r="U8" s="762"/>
+      <c r="V8" s="762"/>
+      <c r="W8" s="762"/>
+      <c r="X8" s="762"/>
+      <c r="Y8" s="762"/>
+      <c r="Z8" s="762"/>
+      <c r="AA8" s="764"/>
     </row>
     <row r="9" spans="1:27" s="215" customFormat="1" ht="45.75" customHeight="1">
       <c r="A9" s="216">
@@ -22238,8 +22230,8 @@
         <v>1389237.7111820201</v>
       </c>
       <c r="M23" s="21">
-        <f>+N23*A65</f>
-        <v>0</v>
+        <f>+N23*$T$9</f>
+        <v>109763283.08334981</v>
       </c>
       <c r="N23" s="21">
         <f>+R34</f>
@@ -22354,39 +22346,39 @@
         <v>10312737.6</v>
       </c>
       <c r="R25" s="16">
-        <f>+R14*$T$9</f>
+        <f t="shared" ref="R25:Z25" si="9">+R14*$T$9</f>
         <v>15528023.280000001</v>
       </c>
       <c r="S25" s="16">
-        <f>+S14*$T$9</f>
+        <f t="shared" si="9"/>
         <v>15619344.443999998</v>
       </c>
       <c r="T25" s="16">
-        <f>+T14*$T$9</f>
+        <f t="shared" si="9"/>
         <v>17085391.666200001</v>
       </c>
       <c r="U25" s="16">
-        <f>+U14*$T$9</f>
+        <f t="shared" si="9"/>
         <v>17871153.249510001</v>
       </c>
       <c r="V25" s="16">
-        <f>+V14*$T$9</f>
+        <f t="shared" si="9"/>
         <v>17976868.911985502</v>
       </c>
       <c r="W25" s="16">
-        <f>+W14*$T$9</f>
+        <f t="shared" si="9"/>
         <v>6004225.2766402503</v>
       </c>
       <c r="X25" s="16">
-        <f>+X14*$T$9</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y25" s="16">
-        <f>+Y14*$T$9</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z25" s="16">
-        <f>+Z14*$T$9</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA25" s="25">
@@ -22433,7 +22425,7 @@
       <c r="R26" s="370"/>
       <c r="S26" s="300"/>
       <c r="T26" s="300"/>
-      <c r="V26" s="787"/>
+      <c r="V26" s="644"/>
       <c r="W26" s="300">
         <f>-Q26</f>
         <v>-12418000</v>
@@ -22645,7 +22637,7 @@
         <v>38230737.600000001</v>
       </c>
       <c r="R30" s="18">
-        <f t="shared" ref="R30:AA30" si="9">SUM(R25:R29)</f>
+        <f t="shared" ref="R30:AA30" si="10">SUM(R25:R29)</f>
         <v>27728023.280000001</v>
       </c>
       <c r="S30" s="18">
@@ -22653,35 +22645,35 @@
         <v>20819344.443999998</v>
       </c>
       <c r="T30" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>23285391.666200001</v>
       </c>
       <c r="U30" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>24071153.249510001</v>
       </c>
       <c r="V30" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>18176868.911985502</v>
       </c>
       <c r="W30" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-6413774.7233597497</v>
       </c>
       <c r="X30" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="Y30" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="Z30" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AA30" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>145897744.42833576</v>
       </c>
     </row>
@@ -22708,7 +22700,7 @@
       <c r="L31" s="20"/>
       <c r="M31" s="20">
         <f>+M23+M28</f>
-        <v>34511749.083847754</v>
+        <v>144275032.16719756</v>
       </c>
       <c r="N31" s="20">
         <f>N23+N28</f>
@@ -22716,7 +22708,6 @@
       </c>
       <c r="T31" s="2"/>
       <c r="U31" s="2"/>
-      <c r="AA31" s="749"/>
     </row>
     <row r="32" spans="1:27" ht="11" thickBot="1">
       <c r="A32" s="35" t="s">
@@ -22748,12 +22739,11 @@
       <c r="R32" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="T32" s="613" t="s">
+      <c r="T32" s="744" t="s">
         <v>53</v>
       </c>
-      <c r="U32" s="614"/>
-      <c r="V32" s="615"/>
-      <c r="AA32" s="749"/>
+      <c r="U32" s="745"/>
+      <c r="V32" s="746"/>
     </row>
     <row r="33" spans="1:27" ht="10.5">
       <c r="A33" s="37"/>
@@ -22774,7 +22764,6 @@
       <c r="V33" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="AA33" s="749"/>
     </row>
     <row r="34" spans="1:27" ht="11" thickBot="1">
       <c r="A34" s="23" t="s">
@@ -22815,7 +22804,6 @@
         <f>+U34/$T$9</f>
         <v>113483.14606741573</v>
       </c>
-      <c r="AA34" s="749"/>
     </row>
     <row r="35" spans="1:27">
       <c r="A35" s="23"/>
@@ -22842,7 +22830,6 @@
         <f>+U35/$T$9</f>
         <v>0</v>
       </c>
-      <c r="AA35" s="749"/>
     </row>
     <row r="36" spans="1:27" ht="10.5">
       <c r="A36" s="35" t="s">
@@ -22867,8 +22854,8 @@
         <f>+N32+N34</f>
         <v>1.3737862518301045</v>
       </c>
-      <c r="P36" s="785"/>
-      <c r="Q36" s="785"/>
+      <c r="P36" s="743"/>
+      <c r="Q36" s="743"/>
       <c r="T36" s="31" t="s">
         <v>59</v>
       </c>
@@ -22879,14 +22866,13 @@
         <f>+U36/$T$9</f>
         <v>0</v>
       </c>
-      <c r="AA36" s="749"/>
     </row>
     <row r="37" spans="1:27" ht="11.5">
       <c r="A37" s="37"/>
       <c r="M37" s="1"/>
       <c r="N37" s="371"/>
-      <c r="P37" s="786"/>
-      <c r="Q37" s="786"/>
+      <c r="P37" s="643"/>
+      <c r="Q37" s="643"/>
       <c r="T37" s="41" t="s">
         <v>60</v>
       </c>
@@ -22898,7 +22884,6 @@
         <f>+U37/$T$9</f>
         <v>0</v>
       </c>
-      <c r="AA37" s="749"/>
     </row>
     <row r="38" spans="1:27" ht="11" thickBot="1">
       <c r="A38" s="37"/>
@@ -22909,8 +22894,7 @@
       <c r="J38" s="364"/>
       <c r="K38" s="364"/>
       <c r="M38" s="1"/>
-      <c r="P38" s="750"/>
-      <c r="Q38" s="773"/>
+      <c r="Q38" s="228"/>
       <c r="T38" s="42" t="s">
         <v>29</v>
       </c>
@@ -22922,7 +22906,6 @@
         <f>SUM(V34:V37)</f>
         <v>113483.14606741573</v>
       </c>
-      <c r="AA38" s="749"/>
     </row>
     <row r="39" spans="1:27" ht="10.5">
       <c r="A39" s="37"/>
@@ -22934,14 +22917,12 @@
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
-      <c r="P39" s="750"/>
-      <c r="Q39" s="773"/>
+      <c r="Q39" s="228"/>
       <c r="T39" s="45" t="s">
         <v>61</v>
       </c>
       <c r="U39" s="46"/>
       <c r="V39" s="47"/>
-      <c r="AA39" s="749"/>
     </row>
     <row r="40" spans="1:27" ht="10.5">
       <c r="A40" s="37"/>
@@ -22952,8 +22933,7 @@
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
-      <c r="P40" s="750"/>
-      <c r="Q40" s="773"/>
+      <c r="Q40" s="228"/>
       <c r="T40" s="48" t="s">
         <v>62</v>
       </c>
@@ -22965,7 +22945,6 @@
         <f>+U40/$T$9</f>
         <v>0</v>
       </c>
-      <c r="AA40" s="749"/>
     </row>
     <row r="41" spans="1:27" ht="10.5">
       <c r="A41" s="37"/>
@@ -22976,8 +22955,8 @@
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
-      <c r="P41" s="773"/>
-      <c r="Q41" s="773"/>
+      <c r="P41" s="228"/>
+      <c r="Q41" s="228"/>
       <c r="T41" s="48" t="s">
         <v>63</v>
       </c>
@@ -22986,10 +22965,9 @@
         <v>500000</v>
       </c>
       <c r="V41" s="17">
-        <f t="shared" ref="V41:V42" si="10">+U41/$T$9</f>
+        <f t="shared" ref="V41:V42" si="11">+U41/$T$9</f>
         <v>4760.9979051609216</v>
       </c>
-      <c r="AA41" s="749"/>
     </row>
     <row r="42" spans="1:27" ht="11" thickBot="1">
       <c r="A42" s="37"/>
@@ -23001,8 +22979,6 @@
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
-      <c r="P42" s="750"/>
-      <c r="Q42" s="750"/>
       <c r="T42" s="32" t="s">
         <v>64</v>
       </c>
@@ -23010,10 +22986,9 @@
         <v>0</v>
       </c>
       <c r="V42" s="17">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AA42" s="749"/>
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="1:27">
       <c r="A43" s="37"/>
@@ -23024,739 +22999,483 @@
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
-      <c r="AA43" s="749"/>
     </row>
     <row r="44" spans="1:27" ht="10.5">
-      <c r="A44" s="749"/>
-      <c r="B44" s="749"/>
-      <c r="C44" s="749"/>
-      <c r="D44" s="749"/>
-      <c r="E44" s="749"/>
-      <c r="F44" s="749"/>
-      <c r="G44" s="749"/>
-      <c r="H44" s="750"/>
-      <c r="I44" s="750"/>
-      <c r="J44" s="750"/>
-      <c r="K44" s="750"/>
-      <c r="L44" s="750"/>
-      <c r="M44" s="750"/>
-      <c r="N44" s="750"/>
-      <c r="O44" s="750"/>
-      <c r="P44" s="751"/>
-      <c r="Q44" s="751"/>
-      <c r="R44" s="751"/>
-      <c r="S44" s="750"/>
-      <c r="T44" s="749"/>
-      <c r="U44" s="749"/>
-      <c r="V44" s="749"/>
-      <c r="W44" s="749"/>
-      <c r="X44" s="749"/>
-      <c r="Y44" s="749"/>
-      <c r="Z44" s="749"/>
-      <c r="AA44" s="749"/>
+      <c r="P44" s="613"/>
+      <c r="Q44" s="613"/>
+      <c r="R44" s="613"/>
     </row>
     <row r="45" spans="1:27" ht="10.5">
-      <c r="A45" s="749"/>
-      <c r="B45" s="749"/>
-      <c r="C45" s="749"/>
-      <c r="D45" s="749"/>
-      <c r="E45" s="749"/>
-      <c r="F45" s="749"/>
-      <c r="G45" s="749"/>
-      <c r="H45" s="750"/>
-      <c r="I45" s="750"/>
-      <c r="J45" s="750"/>
-      <c r="K45" s="750"/>
-      <c r="L45" s="750"/>
-      <c r="M45" s="750"/>
-      <c r="N45" s="750"/>
-      <c r="O45" s="750"/>
-      <c r="P45" s="750"/>
-      <c r="Q45" s="750"/>
-      <c r="R45" s="752"/>
-      <c r="S45" s="752"/>
-      <c r="T45" s="752"/>
-      <c r="U45" s="752"/>
-      <c r="V45" s="752"/>
-      <c r="W45" s="752"/>
-      <c r="X45" s="752"/>
-      <c r="Y45" s="752"/>
-      <c r="Z45" s="752"/>
-      <c r="AA45" s="749"/>
+      <c r="R45" s="614"/>
+      <c r="S45" s="614"/>
+      <c r="T45" s="614"/>
+      <c r="U45" s="614"/>
+      <c r="V45" s="614"/>
+      <c r="W45" s="614"/>
+      <c r="X45" s="614"/>
+      <c r="Y45" s="614"/>
+      <c r="Z45" s="614"/>
     </row>
     <row r="46" spans="1:27" ht="13">
-      <c r="A46" s="784"/>
-      <c r="B46" s="753"/>
-      <c r="C46" s="754"/>
-      <c r="D46" s="754"/>
-      <c r="E46" s="754"/>
-      <c r="F46" s="753"/>
-      <c r="G46" s="753"/>
-      <c r="H46" s="755"/>
-      <c r="I46" s="753"/>
-      <c r="J46" s="753"/>
-      <c r="K46" s="753"/>
-      <c r="L46" s="755"/>
-      <c r="M46" s="753"/>
-      <c r="N46" s="754"/>
-      <c r="O46" s="750"/>
-      <c r="P46" s="756"/>
-      <c r="Q46" s="757"/>
-      <c r="R46" s="752"/>
-      <c r="S46" s="752"/>
-      <c r="T46" s="752"/>
-      <c r="U46" s="752"/>
-      <c r="V46" s="752"/>
-      <c r="W46" s="752"/>
-      <c r="X46" s="752"/>
-      <c r="Y46" s="752"/>
-      <c r="Z46" s="752"/>
-      <c r="AA46" s="758"/>
+      <c r="A46" s="642"/>
+      <c r="B46" s="615"/>
+      <c r="C46" s="616"/>
+      <c r="D46" s="616"/>
+      <c r="E46" s="616"/>
+      <c r="F46" s="615"/>
+      <c r="G46" s="615"/>
+      <c r="H46" s="617"/>
+      <c r="I46" s="615"/>
+      <c r="J46" s="615"/>
+      <c r="K46" s="615"/>
+      <c r="L46" s="617"/>
+      <c r="M46" s="615"/>
+      <c r="N46" s="616"/>
+      <c r="P46" s="618"/>
+      <c r="Q46" s="619"/>
+      <c r="R46" s="614"/>
+      <c r="S46" s="614"/>
+      <c r="T46" s="614"/>
+      <c r="U46" s="614"/>
+      <c r="V46" s="614"/>
+      <c r="W46" s="614"/>
+      <c r="X46" s="614"/>
+      <c r="Y46" s="614"/>
+      <c r="Z46" s="614"/>
+      <c r="AA46" s="620"/>
     </row>
     <row r="47" spans="1:27" ht="12.5">
-      <c r="A47" s="759"/>
-      <c r="B47" s="760"/>
-      <c r="C47" s="760"/>
-      <c r="D47" s="760"/>
-      <c r="E47" s="760"/>
-      <c r="F47" s="760"/>
-      <c r="G47" s="761"/>
-      <c r="H47" s="749"/>
-      <c r="I47" s="749"/>
-      <c r="J47" s="749"/>
-      <c r="K47" s="749"/>
-      <c r="L47" s="749"/>
-      <c r="M47" s="749"/>
-      <c r="N47" s="750"/>
-      <c r="O47" s="750"/>
-      <c r="P47" s="751"/>
-      <c r="Q47" s="762"/>
-      <c r="R47" s="762"/>
-      <c r="S47" s="762"/>
-      <c r="T47" s="762"/>
-      <c r="U47" s="762"/>
-      <c r="V47" s="762"/>
-      <c r="W47" s="762"/>
-      <c r="X47" s="762"/>
-      <c r="Y47" s="762"/>
-      <c r="Z47" s="762"/>
-      <c r="AA47" s="762"/>
+      <c r="A47" s="621"/>
+      <c r="B47" s="622"/>
+      <c r="C47" s="622"/>
+      <c r="D47" s="622"/>
+      <c r="E47" s="622"/>
+      <c r="F47" s="622"/>
+      <c r="G47" s="623"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="P47" s="613"/>
+      <c r="Q47" s="466"/>
+      <c r="R47" s="466"/>
+      <c r="S47" s="466"/>
+      <c r="T47" s="466"/>
+      <c r="U47" s="466"/>
+      <c r="V47" s="466"/>
+      <c r="W47" s="466"/>
+      <c r="X47" s="466"/>
+      <c r="Y47" s="466"/>
+      <c r="Z47" s="466"/>
+      <c r="AA47" s="466"/>
     </row>
     <row r="48" spans="1:27" ht="12.5">
-      <c r="A48" s="759"/>
-      <c r="B48" s="750"/>
-      <c r="C48" s="750"/>
-      <c r="D48" s="750"/>
-      <c r="E48" s="750"/>
-      <c r="F48" s="750"/>
-      <c r="G48" s="761"/>
-      <c r="H48" s="749"/>
-      <c r="I48" s="749"/>
-      <c r="J48" s="749"/>
-      <c r="K48" s="749"/>
-      <c r="L48" s="749"/>
-      <c r="M48" s="750"/>
-      <c r="N48" s="750"/>
-      <c r="O48" s="763"/>
-      <c r="P48" s="764"/>
-      <c r="Q48" s="762"/>
-      <c r="R48" s="762"/>
-      <c r="S48" s="762"/>
-      <c r="T48" s="762"/>
-      <c r="U48" s="762"/>
-      <c r="V48" s="762"/>
-      <c r="W48" s="762"/>
-      <c r="X48" s="762"/>
-      <c r="Y48" s="762"/>
-      <c r="Z48" s="762"/>
-      <c r="AA48" s="762"/>
+      <c r="A48" s="621"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="623"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="O48" s="624"/>
+      <c r="P48" s="625"/>
+      <c r="Q48" s="466"/>
+      <c r="R48" s="466"/>
+      <c r="S48" s="466"/>
+      <c r="T48" s="466"/>
+      <c r="U48" s="466"/>
+      <c r="V48" s="466"/>
+      <c r="W48" s="466"/>
+      <c r="X48" s="466"/>
+      <c r="Y48" s="466"/>
+      <c r="Z48" s="466"/>
+      <c r="AA48" s="466"/>
     </row>
     <row r="49" spans="1:28" ht="12.5">
-      <c r="A49" s="749"/>
-      <c r="B49" s="750"/>
-      <c r="C49" s="750"/>
-      <c r="D49" s="750"/>
-      <c r="E49" s="750"/>
-      <c r="F49" s="750"/>
-      <c r="G49" s="761"/>
-      <c r="H49" s="749"/>
-      <c r="I49" s="750"/>
-      <c r="J49" s="750"/>
-      <c r="K49" s="749"/>
-      <c r="L49" s="749"/>
-      <c r="M49" s="750"/>
-      <c r="N49" s="750"/>
-      <c r="O49" s="763"/>
-      <c r="P49" s="750"/>
-      <c r="Q49" s="765"/>
-      <c r="R49" s="765"/>
-      <c r="S49" s="765"/>
-      <c r="T49" s="765"/>
-      <c r="U49" s="765"/>
-      <c r="V49" s="765"/>
-      <c r="W49" s="765"/>
-      <c r="X49" s="765"/>
-      <c r="Y49" s="765"/>
-      <c r="Z49" s="765"/>
-      <c r="AA49" s="762"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="623"/>
+      <c r="H49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="O49" s="624"/>
+      <c r="Q49" s="626"/>
+      <c r="R49" s="626"/>
+      <c r="S49" s="626"/>
+      <c r="T49" s="626"/>
+      <c r="U49" s="626"/>
+      <c r="V49" s="626"/>
+      <c r="W49" s="626"/>
+      <c r="X49" s="626"/>
+      <c r="Y49" s="626"/>
+      <c r="Z49" s="626"/>
+      <c r="AA49" s="466"/>
     </row>
     <row r="50" spans="1:28" ht="13">
-      <c r="A50" s="749"/>
-      <c r="B50" s="784"/>
-      <c r="C50" s="784"/>
-      <c r="D50" s="784"/>
-      <c r="E50" s="784"/>
-      <c r="F50" s="784"/>
-      <c r="G50" s="784"/>
-      <c r="H50" s="784"/>
-      <c r="I50" s="784"/>
-      <c r="J50" s="784"/>
-      <c r="K50" s="784"/>
-      <c r="L50" s="784"/>
-      <c r="M50" s="784"/>
-      <c r="N50" s="784"/>
-      <c r="O50" s="750"/>
-      <c r="P50" s="750"/>
-      <c r="Q50" s="750"/>
-      <c r="R50" s="750"/>
-      <c r="S50" s="762"/>
-      <c r="T50" s="762"/>
-      <c r="U50" s="762"/>
-      <c r="V50" s="762"/>
-      <c r="W50" s="762"/>
-      <c r="X50" s="762"/>
-      <c r="Y50" s="750"/>
-      <c r="Z50" s="750"/>
-      <c r="AA50" s="762"/>
+      <c r="B50" s="642"/>
+      <c r="C50" s="642"/>
+      <c r="D50" s="642"/>
+      <c r="E50" s="642"/>
+      <c r="F50" s="642"/>
+      <c r="G50" s="642"/>
+      <c r="H50" s="642"/>
+      <c r="I50" s="642"/>
+      <c r="J50" s="642"/>
+      <c r="K50" s="642"/>
+      <c r="L50" s="642"/>
+      <c r="M50" s="642"/>
+      <c r="N50" s="642"/>
+      <c r="S50" s="466"/>
+      <c r="T50" s="466"/>
+      <c r="U50" s="466"/>
+      <c r="V50" s="466"/>
+      <c r="W50" s="466"/>
+      <c r="X50" s="466"/>
+      <c r="Y50" s="2"/>
+      <c r="Z50" s="2"/>
+      <c r="AA50" s="466"/>
     </row>
     <row r="51" spans="1:28" ht="12.5">
-      <c r="A51" s="749"/>
-      <c r="B51" s="750"/>
-      <c r="C51" s="750"/>
-      <c r="D51" s="750"/>
-      <c r="E51" s="750"/>
-      <c r="F51" s="750"/>
-      <c r="G51" s="750"/>
-      <c r="H51" s="749"/>
-      <c r="I51" s="749"/>
-      <c r="J51" s="749"/>
-      <c r="K51" s="749"/>
-      <c r="L51" s="749"/>
-      <c r="M51" s="750"/>
-      <c r="N51" s="750"/>
-      <c r="O51" s="750"/>
-      <c r="P51" s="750"/>
-      <c r="Q51" s="762"/>
-      <c r="R51" s="750"/>
-      <c r="S51" s="750"/>
-      <c r="T51" s="749"/>
-      <c r="U51" s="749"/>
-      <c r="V51" s="749"/>
-      <c r="W51" s="749"/>
-      <c r="X51" s="749"/>
-      <c r="Y51" s="749"/>
-      <c r="Z51" s="749"/>
-      <c r="AA51" s="762"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="Q51" s="466"/>
+      <c r="AA51" s="466"/>
     </row>
     <row r="52" spans="1:28" ht="12.5">
-      <c r="A52" s="749"/>
-      <c r="B52" s="750"/>
-      <c r="C52" s="750"/>
-      <c r="D52" s="750"/>
-      <c r="E52" s="750"/>
-      <c r="F52" s="750"/>
-      <c r="G52" s="751"/>
-      <c r="H52" s="766"/>
-      <c r="I52" s="766"/>
-      <c r="J52" s="766"/>
-      <c r="K52" s="766"/>
-      <c r="L52" s="766"/>
-      <c r="M52" s="749"/>
-      <c r="N52" s="751"/>
-      <c r="O52" s="750"/>
-      <c r="P52" s="749"/>
-      <c r="Q52" s="762"/>
-      <c r="R52" s="762"/>
-      <c r="S52" s="762"/>
-      <c r="T52" s="762"/>
-      <c r="U52" s="762"/>
-      <c r="V52" s="762"/>
-      <c r="W52" s="762"/>
-      <c r="X52" s="762"/>
-      <c r="Y52" s="762"/>
-      <c r="Z52" s="762"/>
-      <c r="AA52" s="762"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="613"/>
+      <c r="H52" s="627"/>
+      <c r="I52" s="627"/>
+      <c r="J52" s="627"/>
+      <c r="K52" s="627"/>
+      <c r="L52" s="627"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="613"/>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="466"/>
+      <c r="R52" s="466"/>
+      <c r="S52" s="466"/>
+      <c r="T52" s="466"/>
+      <c r="U52" s="466"/>
+      <c r="V52" s="466"/>
+      <c r="W52" s="466"/>
+      <c r="X52" s="466"/>
+      <c r="Y52" s="466"/>
+      <c r="Z52" s="466"/>
+      <c r="AA52" s="466"/>
     </row>
     <row r="53" spans="1:28" ht="12.5">
-      <c r="A53" s="749"/>
-      <c r="B53" s="750"/>
-      <c r="C53" s="750"/>
-      <c r="D53" s="750"/>
-      <c r="E53" s="750"/>
-      <c r="F53" s="750"/>
-      <c r="G53" s="767"/>
-      <c r="H53" s="767"/>
-      <c r="I53" s="767"/>
-      <c r="J53" s="767"/>
-      <c r="K53" s="767"/>
-      <c r="L53" s="767"/>
-      <c r="M53" s="749"/>
-      <c r="N53" s="751"/>
-      <c r="O53" s="750"/>
-      <c r="P53" s="751"/>
-      <c r="Q53" s="762"/>
-      <c r="R53" s="762"/>
-      <c r="S53" s="762"/>
-      <c r="T53" s="762"/>
-      <c r="U53" s="762"/>
-      <c r="V53" s="762"/>
-      <c r="W53" s="762"/>
-      <c r="X53" s="762"/>
-      <c r="Y53" s="762"/>
-      <c r="Z53" s="762"/>
-      <c r="AA53" s="762"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="628"/>
+      <c r="H53" s="628"/>
+      <c r="I53" s="628"/>
+      <c r="J53" s="628"/>
+      <c r="K53" s="628"/>
+      <c r="L53" s="628"/>
+      <c r="M53" s="1"/>
+      <c r="N53" s="613"/>
+      <c r="P53" s="613"/>
+      <c r="Q53" s="466"/>
+      <c r="R53" s="466"/>
+      <c r="S53" s="466"/>
+      <c r="T53" s="466"/>
+      <c r="U53" s="466"/>
+      <c r="V53" s="466"/>
+      <c r="W53" s="466"/>
+      <c r="X53" s="466"/>
+      <c r="Y53" s="466"/>
+      <c r="Z53" s="466"/>
+      <c r="AA53" s="466"/>
     </row>
     <row r="54" spans="1:28">
-      <c r="A54" s="749"/>
-      <c r="B54" s="750"/>
-      <c r="C54" s="750"/>
-      <c r="D54" s="750"/>
-      <c r="E54" s="750"/>
-      <c r="F54" s="750"/>
-      <c r="G54" s="750"/>
-      <c r="H54" s="749"/>
-      <c r="I54" s="749"/>
-      <c r="J54" s="749"/>
-      <c r="K54" s="749"/>
-      <c r="L54" s="749"/>
-      <c r="M54" s="749"/>
-      <c r="N54" s="750"/>
-      <c r="O54" s="750"/>
-      <c r="P54" s="749"/>
-      <c r="Q54" s="749"/>
-      <c r="R54" s="749"/>
-      <c r="S54" s="749"/>
-      <c r="T54" s="749"/>
-      <c r="U54" s="749"/>
-      <c r="V54" s="749"/>
-      <c r="W54" s="749"/>
-      <c r="X54" s="749"/>
-      <c r="Y54" s="749"/>
-      <c r="Z54" s="749"/>
-      <c r="AA54" s="749"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="P54" s="1"/>
+      <c r="Q54" s="1"/>
+      <c r="R54" s="1"/>
+      <c r="S54" s="1"/>
     </row>
     <row r="55" spans="1:28" ht="10.5">
-      <c r="A55" s="749"/>
-      <c r="B55" s="750"/>
-      <c r="C55" s="750"/>
-      <c r="D55" s="750"/>
-      <c r="E55" s="750"/>
-      <c r="F55" s="750"/>
-      <c r="G55" s="751"/>
-      <c r="H55" s="766"/>
-      <c r="I55" s="766"/>
-      <c r="J55" s="766"/>
-      <c r="K55" s="766"/>
-      <c r="L55" s="766"/>
-      <c r="M55" s="749"/>
-      <c r="N55" s="751"/>
-      <c r="O55" s="750"/>
-      <c r="P55" s="749"/>
-      <c r="Q55" s="749"/>
-      <c r="R55" s="749"/>
-      <c r="S55" s="749"/>
-      <c r="T55" s="749"/>
-      <c r="U55" s="749"/>
-      <c r="V55" s="749"/>
-      <c r="W55" s="749"/>
-      <c r="X55" s="749"/>
-      <c r="Y55" s="749"/>
-      <c r="Z55" s="749"/>
-      <c r="AA55" s="749"/>
-      <c r="AB55" s="782"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="613"/>
+      <c r="H55" s="627"/>
+      <c r="I55" s="627"/>
+      <c r="J55" s="627"/>
+      <c r="K55" s="627"/>
+      <c r="L55" s="627"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="613"/>
+      <c r="P55" s="1"/>
+      <c r="Q55" s="1"/>
+      <c r="R55" s="1"/>
+      <c r="S55" s="1"/>
+      <c r="AB55" s="641"/>
     </row>
     <row r="56" spans="1:28" ht="13">
-      <c r="A56" s="749"/>
-      <c r="B56" s="750"/>
-      <c r="C56" s="750"/>
-      <c r="D56" s="750"/>
-      <c r="E56" s="750"/>
-      <c r="F56" s="750"/>
-      <c r="G56" s="749"/>
-      <c r="H56" s="784"/>
-      <c r="I56" s="784"/>
-      <c r="J56" s="784"/>
-      <c r="K56" s="784"/>
-      <c r="L56" s="784"/>
-      <c r="M56" s="784"/>
-      <c r="N56" s="784"/>
-      <c r="O56" s="750"/>
-      <c r="P56" s="751"/>
-      <c r="Q56" s="768"/>
-      <c r="R56" s="768"/>
-      <c r="S56" s="768"/>
-      <c r="T56" s="768"/>
-      <c r="U56" s="768"/>
-      <c r="V56" s="768"/>
-      <c r="W56" s="768"/>
-      <c r="X56" s="768"/>
-      <c r="Y56" s="768"/>
-      <c r="Z56" s="768"/>
-      <c r="AA56" s="769"/>
-      <c r="AB56" s="749"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="H56" s="642"/>
+      <c r="I56" s="642"/>
+      <c r="J56" s="642"/>
+      <c r="K56" s="642"/>
+      <c r="L56" s="642"/>
+      <c r="M56" s="642"/>
+      <c r="N56" s="642"/>
+      <c r="P56" s="613"/>
+      <c r="Q56" s="629"/>
+      <c r="R56" s="629"/>
+      <c r="S56" s="629"/>
+      <c r="T56" s="629"/>
+      <c r="U56" s="629"/>
+      <c r="V56" s="629"/>
+      <c r="W56" s="629"/>
+      <c r="X56" s="629"/>
+      <c r="Y56" s="629"/>
+      <c r="Z56" s="629"/>
+      <c r="AA56" s="630"/>
     </row>
     <row r="57" spans="1:28" ht="12.5">
-      <c r="A57" s="749"/>
-      <c r="B57" s="750"/>
-      <c r="C57" s="750"/>
-      <c r="D57" s="750"/>
-      <c r="E57" s="750"/>
-      <c r="F57" s="750"/>
-      <c r="G57" s="770"/>
-      <c r="H57" s="749"/>
-      <c r="I57" s="749"/>
-      <c r="J57" s="749"/>
-      <c r="K57" s="749"/>
-      <c r="L57" s="749"/>
-      <c r="M57" s="749"/>
-      <c r="N57" s="770"/>
-      <c r="O57" s="750"/>
-      <c r="P57" s="751"/>
-      <c r="Q57" s="762"/>
-      <c r="R57" s="762"/>
-      <c r="S57" s="762"/>
-      <c r="T57" s="762"/>
-      <c r="U57" s="762"/>
-      <c r="V57" s="762"/>
-      <c r="W57" s="762"/>
-      <c r="X57" s="762"/>
-      <c r="Y57" s="762"/>
-      <c r="Z57" s="762"/>
-      <c r="AA57" s="769"/>
-      <c r="AB57" s="771"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="631"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="631"/>
+      <c r="P57" s="613"/>
+      <c r="Q57" s="466"/>
+      <c r="R57" s="466"/>
+      <c r="S57" s="466"/>
+      <c r="T57" s="466"/>
+      <c r="U57" s="466"/>
+      <c r="V57" s="466"/>
+      <c r="W57" s="466"/>
+      <c r="X57" s="466"/>
+      <c r="Y57" s="466"/>
+      <c r="Z57" s="466"/>
+      <c r="AA57" s="630"/>
+      <c r="AB57" s="632"/>
     </row>
     <row r="58" spans="1:28" ht="10.5">
-      <c r="A58" s="764"/>
-      <c r="B58" s="750"/>
-      <c r="C58" s="750"/>
-      <c r="D58" s="750"/>
-      <c r="E58" s="750"/>
-      <c r="F58" s="750"/>
-      <c r="G58" s="750"/>
-      <c r="H58" s="749"/>
-      <c r="I58" s="749"/>
-      <c r="J58" s="749"/>
-      <c r="K58" s="749"/>
-      <c r="L58" s="749"/>
-      <c r="M58" s="749"/>
-      <c r="N58" s="750"/>
-      <c r="O58" s="750"/>
-      <c r="P58" s="763"/>
-      <c r="Q58" s="750"/>
-      <c r="R58" s="763"/>
-      <c r="S58" s="763"/>
-      <c r="T58" s="763"/>
-      <c r="U58" s="749"/>
-      <c r="V58" s="749"/>
-      <c r="W58" s="749"/>
-      <c r="X58" s="749"/>
-      <c r="Y58" s="749"/>
-      <c r="Z58" s="749"/>
-      <c r="AA58" s="771"/>
-      <c r="AB58" s="749"/>
+      <c r="A58" s="625"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="P58" s="624"/>
+      <c r="R58" s="624"/>
+      <c r="S58" s="624"/>
+      <c r="T58" s="624"/>
+      <c r="AA58" s="632"/>
     </row>
     <row r="59" spans="1:28">
-      <c r="A59" s="761"/>
-      <c r="B59" s="772"/>
-      <c r="C59" s="772"/>
-      <c r="D59" s="772"/>
-      <c r="E59" s="772"/>
-      <c r="F59" s="750"/>
-      <c r="G59" s="750"/>
-      <c r="H59" s="749"/>
-      <c r="I59" s="749"/>
-      <c r="J59" s="749"/>
-      <c r="K59" s="749"/>
-      <c r="L59" s="749"/>
-      <c r="M59" s="749"/>
-      <c r="N59" s="750"/>
-      <c r="O59" s="750"/>
-      <c r="P59" s="750"/>
-      <c r="Q59" s="750"/>
-      <c r="R59" s="750"/>
-      <c r="S59" s="750"/>
-      <c r="T59" s="750"/>
-      <c r="U59" s="749"/>
-      <c r="V59" s="749"/>
-      <c r="W59" s="749"/>
-      <c r="X59" s="773"/>
-      <c r="Y59" s="749"/>
-      <c r="Z59" s="749"/>
-      <c r="AA59" s="774"/>
-      <c r="AB59" s="783"/>
+      <c r="A59" s="623"/>
+      <c r="B59" s="633"/>
+      <c r="C59" s="633"/>
+      <c r="D59" s="633"/>
+      <c r="E59" s="633"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
+      <c r="T59" s="2"/>
+      <c r="X59" s="228"/>
+      <c r="AA59" s="634"/>
+      <c r="AB59" s="182"/>
     </row>
     <row r="60" spans="1:28">
-      <c r="A60" s="775"/>
-      <c r="B60" s="776"/>
-      <c r="C60" s="776"/>
-      <c r="D60" s="776"/>
-      <c r="E60" s="776"/>
-      <c r="F60" s="749"/>
-      <c r="G60" s="749"/>
-      <c r="H60" s="749"/>
-      <c r="I60" s="749"/>
-      <c r="J60" s="749"/>
-      <c r="K60" s="749"/>
-      <c r="L60" s="749"/>
-      <c r="M60" s="749"/>
-      <c r="N60" s="750"/>
-      <c r="O60" s="750"/>
-      <c r="P60" s="750"/>
-      <c r="Q60" s="750"/>
-      <c r="R60" s="750"/>
-      <c r="S60" s="750"/>
-      <c r="T60" s="750"/>
-      <c r="U60" s="749"/>
-      <c r="V60" s="749"/>
-      <c r="W60" s="749"/>
-      <c r="X60" s="773"/>
-      <c r="Y60" s="749"/>
-      <c r="Z60" s="749"/>
-      <c r="AA60" s="774"/>
-      <c r="AB60" s="783"/>
+      <c r="A60" s="635"/>
+      <c r="B60" s="636"/>
+      <c r="C60" s="636"/>
+      <c r="D60" s="636"/>
+      <c r="E60" s="636"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+      <c r="T60" s="2"/>
+      <c r="X60" s="228"/>
+      <c r="AA60" s="634"/>
+      <c r="AB60" s="182"/>
     </row>
     <row r="61" spans="1:28" ht="10.5">
-      <c r="A61" s="774"/>
-      <c r="B61" s="776"/>
-      <c r="C61" s="776"/>
-      <c r="D61" s="776"/>
-      <c r="E61" s="776"/>
-      <c r="F61" s="749"/>
-      <c r="G61" s="749"/>
-      <c r="H61" s="749"/>
-      <c r="I61" s="749"/>
-      <c r="J61" s="749"/>
-      <c r="K61" s="749"/>
-      <c r="L61" s="749"/>
-      <c r="M61" s="749"/>
-      <c r="N61" s="750"/>
-      <c r="O61" s="750"/>
-      <c r="P61" s="751"/>
-      <c r="Q61" s="749"/>
-      <c r="R61" s="750"/>
-      <c r="S61" s="750"/>
-      <c r="T61" s="750"/>
-      <c r="U61" s="749"/>
-      <c r="V61" s="749"/>
-      <c r="W61" s="749"/>
-      <c r="X61" s="773"/>
-      <c r="Y61" s="749"/>
-      <c r="Z61" s="749"/>
-      <c r="AA61" s="777"/>
-      <c r="AB61" s="749"/>
+      <c r="A61" s="634"/>
+      <c r="B61" s="636"/>
+      <c r="C61" s="636"/>
+      <c r="D61" s="636"/>
+      <c r="E61" s="636"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1"/>
+      <c r="P61" s="613"/>
+      <c r="Q61" s="1"/>
+      <c r="T61" s="2"/>
+      <c r="X61" s="228"/>
+      <c r="AA61" s="637"/>
     </row>
     <row r="62" spans="1:28">
-      <c r="A62" s="774"/>
-      <c r="B62" s="776"/>
-      <c r="C62" s="776"/>
-      <c r="D62" s="776"/>
-      <c r="E62" s="776"/>
-      <c r="F62" s="749"/>
-      <c r="G62" s="749"/>
-      <c r="H62" s="749"/>
-      <c r="I62" s="749"/>
-      <c r="J62" s="749"/>
-      <c r="K62" s="749"/>
-      <c r="L62" s="749"/>
-      <c r="M62" s="749"/>
-      <c r="N62" s="750"/>
-      <c r="O62" s="750"/>
-      <c r="P62" s="749"/>
-      <c r="Q62" s="749"/>
-      <c r="R62" s="749"/>
-      <c r="S62" s="749"/>
-      <c r="T62" s="749"/>
-      <c r="U62" s="749"/>
-      <c r="V62" s="749"/>
-      <c r="W62" s="749"/>
-      <c r="X62" s="749"/>
-      <c r="Y62" s="749"/>
-      <c r="Z62" s="749"/>
-      <c r="AA62" s="749"/>
+      <c r="A62" s="634"/>
+      <c r="B62" s="636"/>
+      <c r="C62" s="636"/>
+      <c r="D62" s="636"/>
+      <c r="E62" s="636"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="P62" s="1"/>
+      <c r="Q62" s="1"/>
+      <c r="R62" s="1"/>
+      <c r="S62" s="1"/>
     </row>
     <row r="63" spans="1:28">
-      <c r="A63" s="774"/>
-      <c r="B63" s="776"/>
-      <c r="C63" s="776"/>
-      <c r="D63" s="776"/>
-      <c r="E63" s="776"/>
-      <c r="F63" s="749"/>
-      <c r="G63" s="749"/>
-      <c r="H63" s="749"/>
-      <c r="I63" s="749"/>
-      <c r="J63" s="749"/>
-      <c r="K63" s="749"/>
-      <c r="L63" s="749"/>
-      <c r="M63" s="749"/>
-      <c r="N63" s="750"/>
-      <c r="O63" s="750"/>
-      <c r="P63" s="749"/>
-      <c r="Q63" s="749"/>
-      <c r="R63" s="749"/>
-      <c r="S63" s="749"/>
-      <c r="T63" s="749"/>
-      <c r="U63" s="749"/>
-      <c r="V63" s="749"/>
-      <c r="W63" s="749"/>
-      <c r="X63" s="749"/>
-      <c r="Y63" s="749"/>
-      <c r="Z63" s="749"/>
-      <c r="AA63" s="749"/>
+      <c r="A63" s="634"/>
+      <c r="B63" s="636"/>
+      <c r="C63" s="636"/>
+      <c r="D63" s="636"/>
+      <c r="E63" s="636"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
+      <c r="P63" s="1"/>
+      <c r="Q63" s="1"/>
+      <c r="R63" s="1"/>
+      <c r="S63" s="1"/>
     </row>
     <row r="64" spans="1:28">
-      <c r="A64" s="774"/>
-      <c r="B64" s="776"/>
-      <c r="C64" s="776"/>
-      <c r="D64" s="776"/>
-      <c r="E64" s="776"/>
-      <c r="F64" s="749"/>
-      <c r="G64" s="749"/>
-      <c r="H64" s="749"/>
-      <c r="I64" s="749"/>
-      <c r="J64" s="749"/>
-      <c r="K64" s="749"/>
-      <c r="L64" s="749"/>
-      <c r="M64" s="749"/>
-      <c r="N64" s="750"/>
-      <c r="O64" s="750"/>
-      <c r="P64" s="749"/>
-      <c r="Q64" s="749"/>
-      <c r="R64" s="749"/>
-      <c r="S64" s="749"/>
-      <c r="T64" s="749"/>
-      <c r="U64" s="749"/>
-      <c r="V64" s="749"/>
-      <c r="W64" s="749"/>
-      <c r="X64" s="749"/>
-      <c r="Y64" s="749"/>
-      <c r="Z64" s="749"/>
-      <c r="AA64" s="749"/>
-    </row>
-    <row r="65" spans="1:27">
-      <c r="A65" s="778"/>
-      <c r="B65" s="776"/>
-      <c r="C65" s="776"/>
-      <c r="D65" s="776"/>
-      <c r="E65" s="776"/>
-      <c r="F65" s="749"/>
-      <c r="G65" s="749"/>
-      <c r="H65" s="749"/>
-      <c r="I65" s="749"/>
-      <c r="J65" s="749"/>
-      <c r="K65" s="749"/>
-      <c r="L65" s="749"/>
-      <c r="M65" s="749"/>
-      <c r="N65" s="750"/>
-      <c r="O65" s="750"/>
-      <c r="P65" s="749"/>
-      <c r="Q65" s="749"/>
-      <c r="R65" s="749"/>
-      <c r="S65" s="749"/>
-      <c r="T65" s="749"/>
-      <c r="U65" s="749"/>
-      <c r="V65" s="749"/>
-      <c r="W65" s="749"/>
-      <c r="X65" s="749"/>
-      <c r="Y65" s="749"/>
-      <c r="Z65" s="749"/>
-      <c r="AA65" s="749"/>
-    </row>
-    <row r="66" spans="1:27">
-      <c r="A66" s="774"/>
-      <c r="B66" s="776"/>
-      <c r="C66" s="776"/>
-      <c r="D66" s="776"/>
-      <c r="E66" s="776"/>
-      <c r="F66" s="749"/>
-      <c r="G66" s="749"/>
-      <c r="H66" s="749"/>
-      <c r="I66" s="749"/>
-      <c r="J66" s="749"/>
-      <c r="K66" s="749"/>
-      <c r="L66" s="749"/>
-      <c r="M66" s="749"/>
-      <c r="N66" s="750"/>
-      <c r="O66" s="750"/>
-      <c r="P66" s="749"/>
-      <c r="Q66" s="749"/>
-      <c r="R66" s="749"/>
-      <c r="S66" s="749"/>
-      <c r="T66" s="749"/>
-      <c r="U66" s="749"/>
-      <c r="V66" s="749"/>
-      <c r="W66" s="749"/>
-      <c r="X66" s="749"/>
-      <c r="Y66" s="749"/>
-      <c r="Z66" s="749"/>
-      <c r="AA66" s="749"/>
-    </row>
-    <row r="67" spans="1:27" ht="12.75" customHeight="1">
-      <c r="A67" s="779"/>
-      <c r="B67" s="776"/>
-      <c r="C67" s="780"/>
-      <c r="D67" s="749"/>
-      <c r="E67" s="749"/>
-      <c r="F67" s="749"/>
-      <c r="G67" s="749"/>
-      <c r="H67" s="750"/>
-      <c r="I67" s="750"/>
-      <c r="J67" s="750"/>
-      <c r="K67" s="750"/>
-      <c r="L67" s="750"/>
-      <c r="M67" s="749"/>
-      <c r="N67" s="750"/>
-      <c r="O67" s="750"/>
-      <c r="P67" s="750"/>
-      <c r="Q67" s="750"/>
-      <c r="R67" s="750"/>
-      <c r="S67" s="750"/>
-      <c r="T67" s="749"/>
-      <c r="U67" s="749"/>
-      <c r="V67" s="749"/>
-      <c r="W67" s="749"/>
-      <c r="X67" s="749"/>
-      <c r="Y67" s="749"/>
-      <c r="Z67" s="749"/>
-      <c r="AA67" s="749"/>
-    </row>
-    <row r="68" spans="1:27" ht="12.75" customHeight="1">
-      <c r="A68" s="781"/>
-      <c r="B68" s="776"/>
-      <c r="C68" s="780"/>
-      <c r="D68" s="749"/>
-      <c r="E68" s="749"/>
-      <c r="F68" s="749"/>
-      <c r="G68" s="749"/>
-      <c r="H68" s="750"/>
-      <c r="I68" s="750"/>
-      <c r="J68" s="750"/>
-      <c r="K68" s="750"/>
-      <c r="L68" s="750"/>
-      <c r="M68" s="749"/>
-      <c r="N68" s="750"/>
-      <c r="O68" s="750"/>
-      <c r="P68" s="750"/>
-      <c r="Q68" s="750"/>
-      <c r="R68" s="750"/>
-      <c r="S68" s="750"/>
-      <c r="T68" s="749"/>
-      <c r="U68" s="749"/>
-      <c r="V68" s="749"/>
-      <c r="W68" s="749"/>
-      <c r="X68" s="749"/>
-      <c r="Y68" s="749"/>
-      <c r="Z68" s="749"/>
-      <c r="AA68" s="749"/>
+      <c r="A64" s="634"/>
+      <c r="B64" s="636"/>
+      <c r="C64" s="636"/>
+      <c r="D64" s="636"/>
+      <c r="E64" s="636"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1"/>
+      <c r="P64" s="1"/>
+      <c r="Q64" s="1"/>
+      <c r="R64" s="1"/>
+      <c r="S64" s="1"/>
+    </row>
+    <row r="65" spans="1:19">
+      <c r="A65" s="638"/>
+      <c r="B65" s="636"/>
+      <c r="C65" s="636"/>
+      <c r="D65" s="636"/>
+      <c r="E65" s="636"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="P65" s="1"/>
+      <c r="Q65" s="1"/>
+      <c r="R65" s="1"/>
+      <c r="S65" s="1"/>
+    </row>
+    <row r="66" spans="1:19">
+      <c r="A66" s="634"/>
+      <c r="B66" s="636"/>
+      <c r="C66" s="636"/>
+      <c r="D66" s="636"/>
+      <c r="E66" s="636"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+      <c r="P66" s="1"/>
+      <c r="Q66" s="1"/>
+      <c r="R66" s="1"/>
+      <c r="S66" s="1"/>
+    </row>
+    <row r="67" spans="1:19" ht="12.75" customHeight="1">
+      <c r="A67" s="639"/>
+      <c r="B67" s="636"/>
+      <c r="C67" s="51"/>
+      <c r="M67" s="1"/>
+    </row>
+    <row r="68" spans="1:19" ht="12.75" customHeight="1">
+      <c r="A68" s="640"/>
+      <c r="B68" s="636"/>
+      <c r="C68" s="51"/>
+      <c r="M68" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -25005,10 +24724,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13">
-      <c r="A1" s="732" t="s">
+      <c r="A1" s="766" t="s">
         <v>339</v>
       </c>
-      <c r="B1" s="732"/>
+      <c r="B1" s="766"/>
       <c r="C1" s="441">
         <f>'Rent Calculation'!G21</f>
         <v>883.96506874767749</v>
@@ -25020,28 +24739,28 @@
       <c r="H1" s="431"/>
     </row>
     <row r="2" spans="1:9" ht="39.65" customHeight="1">
-      <c r="A2" s="732" t="s">
+      <c r="A2" s="766" t="s">
         <v>335</v>
       </c>
-      <c r="B2" s="732"/>
-      <c r="C2" s="734" t="s">
+      <c r="B2" s="766"/>
+      <c r="C2" s="765" t="s">
         <v>336</v>
       </c>
-      <c r="D2" s="734"/>
-      <c r="E2" s="734" t="s">
+      <c r="D2" s="765"/>
+      <c r="E2" s="765" t="s">
         <v>337</v>
       </c>
-      <c r="F2" s="734"/>
-      <c r="G2" s="734" t="s">
+      <c r="F2" s="765"/>
+      <c r="G2" s="765" t="s">
         <v>338</v>
       </c>
-      <c r="H2" s="734"/>
+      <c r="H2" s="765"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="732" t="s">
+      <c r="A3" s="766" t="s">
         <v>332</v>
       </c>
-      <c r="B3" s="732"/>
+      <c r="B3" s="766"/>
       <c r="C3" s="431">
         <v>36</v>
       </c>
@@ -25057,10 +24776,10 @@
       </c>
     </row>
     <row r="4" spans="1:9" s="432" customFormat="1" ht="13">
-      <c r="A4" s="733" t="s">
+      <c r="A4" s="767" t="s">
         <v>146</v>
       </c>
-      <c r="B4" s="733"/>
+      <c r="B4" s="767"/>
       <c r="C4" s="442" t="s">
         <v>333</v>
       </c>
@@ -25377,10 +25096,10 @@
       <c r="I13" s="425"/>
     </row>
     <row r="14" spans="1:9" ht="13">
-      <c r="A14" s="733" t="s">
+      <c r="A14" s="767" t="s">
         <v>154</v>
       </c>
-      <c r="B14" s="733"/>
+      <c r="B14" s="767"/>
       <c r="C14" s="443"/>
       <c r="D14" s="443"/>
       <c r="E14" s="443"/>
@@ -25628,10 +25347,10 @@
       <c r="I22" s="422"/>
     </row>
     <row r="23" spans="1:9" s="432" customFormat="1" ht="13">
-      <c r="A23" s="733" t="s">
+      <c r="A23" s="767" t="s">
         <v>157</v>
       </c>
-      <c r="B23" s="733"/>
+      <c r="B23" s="767"/>
       <c r="C23" s="442">
         <f>C13+C21</f>
         <v>85866755.096998334</v>
@@ -25680,6 +25399,8 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C2:D2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="A3:B3"/>
@@ -25687,8 +25408,6 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -26365,10 +26084,10 @@
       </c>
     </row>
     <row r="11" spans="2:21" s="362" customFormat="1" ht="13" hidden="1">
-      <c r="B11" s="735" t="s">
+      <c r="B11" s="768" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="735"/>
+      <c r="C11" s="768"/>
       <c r="D11" s="391">
         <v>42</v>
       </c>
@@ -31182,10 +30901,10 @@
       </c>
     </row>
     <row r="11" spans="2:21" s="362" customFormat="1" ht="13">
-      <c r="B11" s="735" t="s">
+      <c r="B11" s="768" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="735"/>
+      <c r="C11" s="768"/>
       <c r="D11" s="391">
         <v>42</v>
       </c>
@@ -34696,27 +34415,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" xsi:nil="true"/>
-    <Status xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100907921E7373C1341A3C877D189CE8922" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2036b66ca2b7955135caa708c7901a86">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xmlns:ns3="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fed2217af4f675ffeab875e34aa73a78" ns2:_="" ns3:_="">
     <xsd:import namespace="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
@@ -34959,26 +34657,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC57694E-BA35-486E-AC74-B7B624F1FDE0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" xsi:nil="true"/>
+    <Status xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12D5BE44-B07C-4182-BC7A-71E5962390BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
-    <ds:schemaRef ds:uri="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB719E29-C329-4AB1-8ED0-5CC29C0FF757}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34997,6 +34697,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12D5BE44-B07C-4182-BC7A-71E5962390BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
+    <ds:schemaRef ds:uri="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC57694E-BA35-486E-AC74-B7B624F1FDE0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{a59b6cd5-d141-4a33-8bf1-0ca04484304f}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" removed="0"/>

--- a/artifacts/Rental Specimen.xlsx
+++ b/artifacts/Rental Specimen.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z004df5r\Documents\rental-automation\artifacts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z0050s8t\Documents\rental-automation\artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACDA933-39BE-4FA4-AE9E-256859DEA466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D6D59E-07E5-409D-9B8A-8CB82AB8DFCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="764" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="764" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="16" state="hidden" r:id="rId1"/>
@@ -6362,6 +6362,300 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="33" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="29" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6374,12 +6668,6 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6434,302 +6722,14 @@
     <xf numFmtId="167" fontId="6" fillId="0" borderId="50" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="102" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="33" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="29" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="192" fontId="54" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9685,7 +9685,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="669" t="s">
+      <c r="A1" s="742" t="s">
         <v>299</v>
       </c>
       <c r="B1" s="400" t="s">
@@ -9705,7 +9705,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="669"/>
+      <c r="A2" s="742"/>
       <c r="B2" s="403" t="s">
         <v>238</v>
       </c>
@@ -9728,23 +9728,23 @@
       </c>
       <c r="B3" s="406">
         <f>'Rent Calculation'!$G$107*'Rent Calculation'!$G$21*9</f>
-        <v>15320246.779390587</v>
+        <v>15297271.840171212</v>
       </c>
       <c r="C3" s="406">
         <f>'Rent Calculation'!$G$107*'Rent Calculation'!$G$21*12</f>
-        <v>20426995.705854118</v>
+        <v>20396362.453561615</v>
       </c>
       <c r="D3" s="406">
         <f>'Rent Calculation'!$G$107*'Rent Calculation'!$G$21*12</f>
-        <v>20426995.705854118</v>
+        <v>20396362.453561615</v>
       </c>
       <c r="E3" s="406">
         <f>'Rent Calculation'!$G$107*'Rent Calculation'!$G$21*1</f>
-        <v>1702249.6421545097</v>
+        <v>1699696.8711301347</v>
       </c>
       <c r="F3" s="406">
         <f>SUM(B3:E3)</f>
-        <v>57876487.833253331</v>
+        <v>57789693.618424572</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="B11" s="409">
         <f>'Rent Calculation'!G102*'Rent Calculation'!G21+'Rent Calculation'!F83</f>
-        <v>523170.14979219931</v>
+        <v>522664.90329219931</v>
       </c>
       <c r="C11" s="408">
         <v>0</v>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="F11" s="408">
         <f t="shared" si="2"/>
-        <v>512254.33034775488</v>
+        <v>511749.08384775487</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -10067,23 +10067,23 @@
       </c>
       <c r="B18" s="408">
         <f>B3+B14</f>
-        <v>23105506.1405017</v>
+        <v>23082531.201282326</v>
       </c>
       <c r="C18" s="408">
         <f t="shared" ref="C18:D18" si="7">C3+C14</f>
-        <v>35997514.428076342</v>
+        <v>35966881.175783843</v>
       </c>
       <c r="D18" s="408">
         <f t="shared" si="7"/>
-        <v>35997514.428076342</v>
+        <v>35966881.175783843</v>
       </c>
       <c r="E18" s="408">
         <f t="shared" ref="E18" si="8">E3+E14</f>
-        <v>2999792.8690063618</v>
+        <v>2997240.0979819866</v>
       </c>
       <c r="F18" s="408">
         <f t="shared" si="2"/>
-        <v>98100327.865660757</v>
+        <v>98013533.650831997</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -15270,18 +15270,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G3:K3"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="L3:P3"/>
+    <mergeCell ref="L4:P4"/>
     <mergeCell ref="V3:Z3"/>
     <mergeCell ref="V4:Z4"/>
     <mergeCell ref="AA3:AE3"/>
     <mergeCell ref="AA4:AE4"/>
     <mergeCell ref="Q3:U3"/>
     <mergeCell ref="Q4:U4"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G3:K3"/>
-    <mergeCell ref="G4:K4"/>
-    <mergeCell ref="L3:P3"/>
-    <mergeCell ref="L4:P4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <customProperties>
@@ -15484,62 +15484,62 @@
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1">
       <c r="A1" s="51"/>
-      <c r="B1" s="719"/>
-      <c r="C1" s="720"/>
-      <c r="D1" s="720"/>
-      <c r="E1" s="720"/>
-      <c r="F1" s="720"/>
-      <c r="G1" s="720"/>
-      <c r="H1" s="720"/>
-      <c r="I1" s="720"/>
-      <c r="J1" s="721"/>
+      <c r="B1" s="684"/>
+      <c r="C1" s="685"/>
+      <c r="D1" s="685"/>
+      <c r="E1" s="685"/>
+      <c r="F1" s="685"/>
+      <c r="G1" s="685"/>
+      <c r="H1" s="685"/>
+      <c r="I1" s="685"/>
+      <c r="J1" s="686"/>
     </row>
     <row r="2" spans="1:10" ht="14.25" customHeight="1">
       <c r="A2" s="51"/>
-      <c r="B2" s="722"/>
-      <c r="C2" s="723"/>
-      <c r="D2" s="723"/>
-      <c r="E2" s="723"/>
-      <c r="F2" s="723"/>
-      <c r="G2" s="723"/>
-      <c r="H2" s="723"/>
-      <c r="I2" s="723"/>
-      <c r="J2" s="724"/>
+      <c r="B2" s="687"/>
+      <c r="C2" s="688"/>
+      <c r="D2" s="688"/>
+      <c r="E2" s="688"/>
+      <c r="F2" s="688"/>
+      <c r="G2" s="688"/>
+      <c r="H2" s="688"/>
+      <c r="I2" s="688"/>
+      <c r="J2" s="689"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A3" s="51"/>
-      <c r="B3" s="725"/>
-      <c r="C3" s="726"/>
-      <c r="D3" s="726"/>
-      <c r="E3" s="726"/>
-      <c r="F3" s="726"/>
-      <c r="G3" s="726"/>
-      <c r="H3" s="726"/>
-      <c r="I3" s="723"/>
-      <c r="J3" s="724"/>
+      <c r="B3" s="690"/>
+      <c r="C3" s="691"/>
+      <c r="D3" s="691"/>
+      <c r="E3" s="691"/>
+      <c r="F3" s="691"/>
+      <c r="G3" s="691"/>
+      <c r="H3" s="691"/>
+      <c r="I3" s="688"/>
+      <c r="J3" s="689"/>
     </row>
     <row r="4" spans="1:10" ht="13">
       <c r="A4" s="51"/>
-      <c r="B4" s="649"/>
-      <c r="C4" s="650"/>
-      <c r="D4" s="650"/>
-      <c r="E4" s="650"/>
-      <c r="F4" s="650"/>
-      <c r="G4" s="650"/>
+      <c r="B4" s="709"/>
+      <c r="C4" s="710"/>
+      <c r="D4" s="710"/>
+      <c r="E4" s="710"/>
+      <c r="F4" s="710"/>
+      <c r="G4" s="710"/>
       <c r="H4" s="415"/>
       <c r="I4" s="416"/>
       <c r="J4" s="417"/>
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="51"/>
-      <c r="B5" s="746" t="s">
+      <c r="B5" s="711" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="747"/>
-      <c r="D5" s="747"/>
-      <c r="E5" s="747"/>
-      <c r="F5" s="747"/>
-      <c r="G5" s="748"/>
+      <c r="C5" s="712"/>
+      <c r="D5" s="712"/>
+      <c r="E5" s="712"/>
+      <c r="F5" s="712"/>
+      <c r="G5" s="713"/>
       <c r="H5" s="418"/>
       <c r="I5" s="546" t="s">
         <v>16</v>
@@ -15550,29 +15550,29 @@
     </row>
     <row r="6" spans="1:10" ht="13.5" thickBot="1">
       <c r="A6" s="51"/>
-      <c r="B6" s="749"/>
-      <c r="C6" s="750"/>
-      <c r="D6" s="751"/>
+      <c r="B6" s="714"/>
+      <c r="C6" s="715"/>
+      <c r="D6" s="716"/>
       <c r="E6" s="52"/>
-      <c r="F6" s="744">
+      <c r="F6" s="707">
         <v>10.763999999999999</v>
       </c>
-      <c r="G6" s="745"/>
+      <c r="G6" s="708"/>
       <c r="H6" s="419"/>
-      <c r="I6" s="732">
+      <c r="I6" s="698">
         <v>10.763999999999999</v>
       </c>
-      <c r="J6" s="733"/>
+      <c r="J6" s="699"/>
     </row>
     <row r="7" spans="1:10" ht="26">
       <c r="A7" s="51"/>
       <c r="B7" s="547" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="752" t="s">
+      <c r="C7" s="717" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="753"/>
+      <c r="D7" s="718"/>
       <c r="E7" s="548"/>
       <c r="F7" s="548" t="s">
         <v>475</v>
@@ -15600,23 +15600,23 @@
       <c r="C8" s="551"/>
       <c r="D8" s="552"/>
       <c r="E8" s="553"/>
-      <c r="F8" s="678" t="s">
+      <c r="F8" s="645" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="712"/>
+      <c r="G8" s="646"/>
       <c r="H8" s="418"/>
-      <c r="I8" s="713" t="s">
+      <c r="I8" s="647" t="s">
         <v>67</v>
       </c>
-      <c r="J8" s="714"/>
+      <c r="J8" s="648"/>
     </row>
     <row r="9" spans="1:10" ht="13">
       <c r="A9" s="51"/>
-      <c r="B9" s="713" t="s">
+      <c r="B9" s="647" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="712"/>
-      <c r="D9" s="679"/>
+      <c r="C9" s="646"/>
+      <c r="D9" s="662"/>
       <c r="E9" s="554"/>
       <c r="F9" s="376" t="s">
         <v>75</v>
@@ -15637,21 +15637,21 @@
       <c r="B10" s="555">
         <v>1</v>
       </c>
-      <c r="C10" s="727" t="s">
+      <c r="C10" s="692" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="686"/>
+      <c r="D10" s="693"/>
       <c r="E10" s="556"/>
-      <c r="F10" s="738" t="s">
+      <c r="F10" s="704" t="s">
         <v>468</v>
       </c>
-      <c r="G10" s="739"/>
+      <c r="G10" s="705"/>
       <c r="H10" s="418"/>
-      <c r="I10" s="734" t="str">
+      <c r="I10" s="700" t="str">
         <f>+F10</f>
         <v>Chennai</v>
       </c>
-      <c r="J10" s="735"/>
+      <c r="J10" s="701"/>
     </row>
     <row r="11" spans="1:10" ht="28.5" customHeight="1">
       <c r="A11" s="51"/>
@@ -15659,19 +15659,19 @@
         <f>1+B10</f>
         <v>2</v>
       </c>
-      <c r="C11" s="728" t="s">
+      <c r="C11" s="694" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="729"/>
+      <c r="D11" s="695"/>
       <c r="E11" s="50"/>
-      <c r="F11" s="738"/>
-      <c r="G11" s="739"/>
+      <c r="F11" s="704"/>
+      <c r="G11" s="705"/>
       <c r="H11" s="418"/>
-      <c r="I11" s="736">
+      <c r="I11" s="702">
         <f>+F11</f>
         <v>0</v>
       </c>
-      <c r="J11" s="737"/>
+      <c r="J11" s="703"/>
     </row>
     <row r="12" spans="1:10" ht="27.75" customHeight="1">
       <c r="A12" s="51"/>
@@ -15679,19 +15679,19 @@
         <f>1+B11</f>
         <v>3</v>
       </c>
-      <c r="C12" s="672" t="s">
+      <c r="C12" s="655" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="671"/>
+      <c r="D12" s="656"/>
       <c r="E12" s="557"/>
-      <c r="F12" s="740"/>
-      <c r="G12" s="741"/>
+      <c r="F12" s="683"/>
+      <c r="G12" s="678"/>
       <c r="H12" s="418"/>
-      <c r="I12" s="754">
+      <c r="I12" s="679">
         <f>+F12</f>
         <v>0</v>
       </c>
-      <c r="J12" s="755"/>
+      <c r="J12" s="680"/>
     </row>
     <row r="13" spans="1:10" ht="15.9" customHeight="1">
       <c r="A13" s="51"/>
@@ -15699,16 +15699,16 @@
         <f t="shared" ref="B13:B31" si="0">1+B12</f>
         <v>4</v>
       </c>
-      <c r="C13" s="672" t="s">
+      <c r="C13" s="655" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="671"/>
+      <c r="D13" s="656"/>
       <c r="E13" s="50"/>
-      <c r="F13" s="743"/>
-      <c r="G13" s="741"/>
+      <c r="F13" s="677"/>
+      <c r="G13" s="678"/>
       <c r="H13" s="418"/>
-      <c r="I13" s="754"/>
-      <c r="J13" s="755"/>
+      <c r="I13" s="679"/>
+      <c r="J13" s="680"/>
     </row>
     <row r="14" spans="1:10" ht="48" customHeight="1">
       <c r="A14" s="51"/>
@@ -15716,21 +15716,21 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="730" t="s">
+      <c r="C14" s="696" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="731"/>
+      <c r="D14" s="697"/>
       <c r="E14" s="539"/>
-      <c r="F14" s="740" t="s">
+      <c r="F14" s="683" t="s">
         <v>469</v>
       </c>
-      <c r="G14" s="742"/>
+      <c r="G14" s="706"/>
       <c r="H14" s="418"/>
-      <c r="I14" s="754" t="str">
+      <c r="I14" s="679" t="str">
         <f>+F14</f>
         <v>6th floor</v>
       </c>
-      <c r="J14" s="755"/>
+      <c r="J14" s="680"/>
     </row>
     <row r="15" spans="1:10" ht="51.75" customHeight="1">
       <c r="A15" s="51"/>
@@ -15738,19 +15738,19 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="672" t="s">
+      <c r="C15" s="655" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="671"/>
+      <c r="D15" s="656"/>
       <c r="E15" s="58"/>
-      <c r="F15" s="678"/>
-      <c r="G15" s="712"/>
+      <c r="F15" s="645"/>
+      <c r="G15" s="646"/>
       <c r="H15" s="418"/>
-      <c r="I15" s="713">
+      <c r="I15" s="647">
         <f>+F15</f>
         <v>0</v>
       </c>
-      <c r="J15" s="714"/>
+      <c r="J15" s="648"/>
     </row>
     <row r="16" spans="1:10" ht="15.9" customHeight="1">
       <c r="A16" s="51"/>
@@ -15758,16 +15758,16 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="672" t="s">
+      <c r="C16" s="655" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="671"/>
+      <c r="D16" s="656"/>
       <c r="E16" s="58"/>
-      <c r="F16" s="743"/>
-      <c r="G16" s="741"/>
+      <c r="F16" s="677"/>
+      <c r="G16" s="678"/>
       <c r="H16" s="418"/>
-      <c r="I16" s="754"/>
-      <c r="J16" s="755"/>
+      <c r="I16" s="679"/>
+      <c r="J16" s="680"/>
     </row>
     <row r="17" spans="1:10" ht="15.9" customHeight="1">
       <c r="A17" s="51"/>
@@ -15775,21 +15775,21 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="672" t="s">
+      <c r="C17" s="655" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="671"/>
+      <c r="D17" s="656"/>
       <c r="E17" s="58"/>
-      <c r="F17" s="740" t="s">
+      <c r="F17" s="683" t="s">
         <v>85</v>
       </c>
-      <c r="G17" s="741"/>
+      <c r="G17" s="678"/>
       <c r="H17" s="418"/>
-      <c r="I17" s="754" t="str">
+      <c r="I17" s="679" t="str">
         <f>+F17</f>
         <v>Warm Shell</v>
       </c>
-      <c r="J17" s="755"/>
+      <c r="J17" s="680"/>
     </row>
     <row r="18" spans="1:10" ht="48" customHeight="1">
       <c r="A18" s="51"/>
@@ -15797,22 +15797,22 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="672" t="s">
+      <c r="C18" s="655" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="671"/>
+      <c r="D18" s="656"/>
       <c r="E18" s="163"/>
-      <c r="F18" s="678">
+      <c r="F18" s="645">
         <f>F15</f>
         <v>0</v>
       </c>
-      <c r="G18" s="712"/>
+      <c r="G18" s="646"/>
       <c r="H18" s="418"/>
-      <c r="I18" s="713">
+      <c r="I18" s="647">
         <f>+F18</f>
         <v>0</v>
       </c>
-      <c r="J18" s="714"/>
+      <c r="J18" s="648"/>
     </row>
     <row r="19" spans="1:10" ht="15.9" customHeight="1">
       <c r="A19" s="51"/>
@@ -15820,16 +15820,16 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="672" t="s">
+      <c r="C19" s="655" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="671"/>
+      <c r="D19" s="656"/>
       <c r="E19" s="163"/>
-      <c r="F19" s="743"/>
-      <c r="G19" s="741"/>
+      <c r="F19" s="677"/>
+      <c r="G19" s="678"/>
       <c r="H19" s="418"/>
-      <c r="I19" s="754"/>
-      <c r="J19" s="755"/>
+      <c r="I19" s="679"/>
+      <c r="J19" s="680"/>
     </row>
     <row r="20" spans="1:10" ht="15.9" customHeight="1">
       <c r="A20" s="51"/>
@@ -15837,10 +15837,10 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="670" t="s">
+      <c r="C20" s="649" t="s">
         <v>88</v>
       </c>
-      <c r="D20" s="671"/>
+      <c r="D20" s="656"/>
       <c r="E20" s="559"/>
       <c r="F20" s="56"/>
       <c r="G20" s="388"/>
@@ -15860,10 +15860,10 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="672" t="s">
+      <c r="C21" s="655" t="s">
         <v>89</v>
       </c>
-      <c r="D21" s="671"/>
+      <c r="D21" s="656"/>
       <c r="E21" s="559"/>
       <c r="F21" s="56">
         <f>Main!B3</f>
@@ -15889,10 +15889,10 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="670" t="s">
+      <c r="C22" s="649" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="671"/>
+      <c r="D22" s="656"/>
       <c r="E22" s="559"/>
       <c r="F22" s="56">
         <v>0</v>
@@ -15916,10 +15916,10 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="672" t="s">
+      <c r="C23" s="655" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="671"/>
+      <c r="D23" s="656"/>
       <c r="E23" s="559"/>
       <c r="F23" s="56">
         <f>+F21+F22</f>
@@ -15945,10 +15945,10 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="672" t="s">
+      <c r="C24" s="655" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="671"/>
+      <c r="D24" s="656"/>
       <c r="E24" s="59"/>
       <c r="F24" s="56"/>
       <c r="G24" s="388">
@@ -15971,10 +15971,10 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="672" t="s">
+      <c r="C25" s="655" t="s">
         <v>93</v>
       </c>
-      <c r="D25" s="671"/>
+      <c r="D25" s="656"/>
       <c r="E25" s="59"/>
       <c r="F25" s="56">
         <v>0</v>
@@ -15999,10 +15999,10 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="672" t="s">
+      <c r="C26" s="655" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="671"/>
+      <c r="D26" s="656"/>
       <c r="E26" s="60"/>
       <c r="F26" s="61">
         <f>F25/F23</f>
@@ -16028,10 +16028,10 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="670" t="s">
+      <c r="C27" s="649" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="671"/>
+      <c r="D27" s="656"/>
       <c r="E27" s="58"/>
       <c r="F27" s="293">
         <v>72</v>
@@ -16056,10 +16056,10 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="670" t="s">
+      <c r="C28" s="649" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="671"/>
+      <c r="D28" s="656"/>
       <c r="E28" s="58"/>
       <c r="F28" s="293">
         <f>'CAPEX and PM'!E3</f>
@@ -16085,10 +16085,10 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="670" t="s">
+      <c r="C29" s="649" t="s">
         <v>97</v>
       </c>
-      <c r="D29" s="671"/>
+      <c r="D29" s="656"/>
       <c r="E29" s="64"/>
       <c r="F29" s="64">
         <f>Main!B12</f>
@@ -16114,10 +16114,10 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="670" t="s">
+      <c r="C30" s="649" t="s">
         <v>98</v>
       </c>
-      <c r="D30" s="671"/>
+      <c r="D30" s="656"/>
       <c r="E30" s="64"/>
       <c r="F30" s="60">
         <f>Main!B13</f>
@@ -16143,10 +16143,10 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="672" t="s">
+      <c r="C31" s="655" t="s">
         <v>99</v>
       </c>
-      <c r="D31" s="671"/>
+      <c r="D31" s="656"/>
       <c r="E31" s="58"/>
       <c r="F31" s="56">
         <v>0</v>
@@ -16167,11 +16167,11 @@
     </row>
     <row r="32" spans="1:10" ht="15.9" customHeight="1">
       <c r="A32" s="51"/>
-      <c r="B32" s="756" t="s">
+      <c r="B32" s="674" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="757"/>
-      <c r="D32" s="758"/>
+      <c r="C32" s="675"/>
+      <c r="D32" s="676"/>
       <c r="E32" s="562"/>
       <c r="F32" s="376" t="s">
         <v>75</v>
@@ -16192,10 +16192,10 @@
       <c r="B33" s="162">
         <v>1</v>
       </c>
-      <c r="C33" s="670" t="s">
+      <c r="C33" s="649" t="s">
         <v>101</v>
       </c>
-      <c r="D33" s="671"/>
+      <c r="D33" s="656"/>
       <c r="E33" s="59"/>
       <c r="F33" s="56">
         <f>Main!B9/(Main!B3*Main!B7)</f>
@@ -16221,10 +16221,10 @@
         <f>1+B33</f>
         <v>2</v>
       </c>
-      <c r="C34" s="670" t="s">
+      <c r="C34" s="649" t="s">
         <v>102</v>
       </c>
-      <c r="D34" s="671"/>
+      <c r="D34" s="656"/>
       <c r="E34" s="59"/>
       <c r="F34" s="56">
         <v>0</v>
@@ -16248,10 +16248,10 @@
         <f t="shared" ref="B35:B48" si="1">1+B34</f>
         <v>3</v>
       </c>
-      <c r="C35" s="670" t="s">
+      <c r="C35" s="649" t="s">
         <v>103</v>
       </c>
-      <c r="D35" s="671"/>
+      <c r="D35" s="656"/>
       <c r="E35" s="59"/>
       <c r="F35" s="56">
         <v>0</v>
@@ -16276,10 +16276,10 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="C36" s="672" t="s">
+      <c r="C36" s="655" t="s">
         <v>104</v>
       </c>
-      <c r="D36" s="671"/>
+      <c r="D36" s="656"/>
       <c r="E36" s="563"/>
       <c r="F36" s="68">
         <v>0</v>
@@ -16301,10 +16301,10 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="C37" s="670" t="s">
+      <c r="C37" s="649" t="s">
         <v>105</v>
       </c>
-      <c r="D37" s="671"/>
+      <c r="D37" s="656"/>
       <c r="E37" s="563"/>
       <c r="F37" s="70">
         <f>'Lease Rent'!H37</f>
@@ -16330,10 +16330,10 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="C38" s="670" t="s">
+      <c r="C38" s="649" t="s">
         <v>106</v>
       </c>
-      <c r="D38" s="671"/>
+      <c r="D38" s="656"/>
       <c r="E38" s="563"/>
       <c r="F38" s="70"/>
       <c r="G38" s="204">
@@ -16350,10 +16350,10 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="C39" s="670" t="s">
+      <c r="C39" s="649" t="s">
         <v>107</v>
       </c>
-      <c r="D39" s="671"/>
+      <c r="D39" s="656"/>
       <c r="E39" s="71"/>
       <c r="F39" s="70">
         <f>'Lease Rent'!J31</f>
@@ -16379,10 +16379,10 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="C40" s="670" t="s">
+      <c r="C40" s="649" t="s">
         <v>108</v>
       </c>
-      <c r="D40" s="671"/>
+      <c r="D40" s="656"/>
       <c r="E40" s="563"/>
       <c r="F40" s="70">
         <f>F37</f>
@@ -16408,10 +16408,10 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="C41" s="670" t="s">
+      <c r="C41" s="649" t="s">
         <v>109</v>
       </c>
-      <c r="D41" s="671"/>
+      <c r="D41" s="656"/>
       <c r="E41" s="563"/>
       <c r="F41" s="70">
         <v>0</v>
@@ -16436,10 +16436,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="C42" s="670" t="s">
+      <c r="C42" s="649" t="s">
         <v>110</v>
       </c>
-      <c r="D42" s="671"/>
+      <c r="D42" s="656"/>
       <c r="E42" s="58"/>
       <c r="F42" s="114">
         <f>F39</f>
@@ -16465,10 +16465,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="C43" s="672" t="s">
+      <c r="C43" s="655" t="s">
         <v>111</v>
       </c>
-      <c r="D43" s="671"/>
+      <c r="D43" s="656"/>
       <c r="E43" s="59"/>
       <c r="F43" s="109">
         <v>0</v>
@@ -16493,10 +16493,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="C44" s="672" t="s">
+      <c r="C44" s="655" t="s">
         <v>112</v>
       </c>
-      <c r="D44" s="671"/>
+      <c r="D44" s="656"/>
       <c r="E44" s="73"/>
       <c r="F44" s="68">
         <v>0</v>
@@ -16521,10 +16521,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="C45" s="672" t="s">
+      <c r="C45" s="655" t="s">
         <v>113</v>
       </c>
-      <c r="D45" s="671"/>
+      <c r="D45" s="656"/>
       <c r="E45" s="59"/>
       <c r="F45" s="56">
         <f>'Lease Rent'!C22</f>
@@ -16550,10 +16550,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="C46" s="670" t="s">
+      <c r="C46" s="649" t="s">
         <v>114</v>
       </c>
-      <c r="D46" s="671"/>
+      <c r="D46" s="656"/>
       <c r="E46" s="59"/>
       <c r="F46" s="109">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="C47" s="672" t="s">
+      <c r="C47" s="655" t="s">
         <v>112</v>
       </c>
-      <c r="D47" s="671"/>
+      <c r="D47" s="656"/>
       <c r="E47" s="59"/>
       <c r="F47" s="56">
         <f>'Lease Rent'!D23</f>
@@ -16595,10 +16595,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="C48" s="672" t="s">
+      <c r="C48" s="655" t="s">
         <v>113</v>
       </c>
-      <c r="D48" s="671"/>
+      <c r="D48" s="656"/>
       <c r="E48" s="59"/>
       <c r="F48" s="56">
         <f>'Lease Rent'!C23</f>
@@ -16611,46 +16611,46 @@
     </row>
     <row r="49" spans="1:18" ht="28.5" customHeight="1">
       <c r="A49" s="51"/>
-      <c r="B49" s="717">
+      <c r="B49" s="721">
         <f>1+B48</f>
         <v>17</v>
       </c>
-      <c r="C49" s="670" t="s">
+      <c r="C49" s="649" t="s">
         <v>115</v>
       </c>
-      <c r="D49" s="671"/>
+      <c r="D49" s="656"/>
       <c r="E49" s="73"/>
-      <c r="F49" s="761" t="str">
+      <c r="F49" s="665" t="str">
         <f>Main!B14</f>
         <v>15% every 3 years</v>
       </c>
-      <c r="G49" s="762"/>
+      <c r="G49" s="666"/>
       <c r="H49" s="418"/>
-      <c r="I49" s="754" t="str">
+      <c r="I49" s="679" t="str">
         <f>+F49</f>
         <v>15% every 3 years</v>
       </c>
-      <c r="J49" s="755"/>
+      <c r="J49" s="680"/>
     </row>
     <row r="50" spans="1:18" ht="15.9" customHeight="1">
       <c r="A50" s="51"/>
-      <c r="B50" s="718"/>
-      <c r="C50" s="670" t="s">
+      <c r="B50" s="722"/>
+      <c r="C50" s="649" t="s">
         <v>116</v>
       </c>
-      <c r="D50" s="671"/>
+      <c r="D50" s="656"/>
       <c r="E50" s="73"/>
-      <c r="F50" s="761" t="str">
+      <c r="F50" s="665" t="str">
         <f>Main!B15</f>
         <v>5% every years</v>
       </c>
-      <c r="G50" s="762"/>
+      <c r="G50" s="666"/>
       <c r="H50" s="418"/>
-      <c r="I50" s="759" t="str">
+      <c r="I50" s="681" t="str">
         <f t="shared" ref="I50:I57" si="2">F50</f>
         <v>5% every years</v>
       </c>
-      <c r="J50" s="760"/>
+      <c r="J50" s="682"/>
     </row>
     <row r="51" spans="1:18" ht="15.9" customHeight="1">
       <c r="A51" s="51"/>
@@ -16658,22 +16658,22 @@
         <f>1+B49</f>
         <v>18</v>
       </c>
-      <c r="C51" s="672" t="s">
+      <c r="C51" s="655" t="s">
         <v>117</v>
       </c>
-      <c r="D51" s="671"/>
+      <c r="D51" s="656"/>
       <c r="E51" s="73"/>
-      <c r="F51" s="708">
+      <c r="F51" s="663">
         <f>'Lease Rent'!B31</f>
         <v>46023</v>
       </c>
-      <c r="G51" s="709"/>
+      <c r="G51" s="664"/>
       <c r="H51" s="418"/>
-      <c r="I51" s="710">
+      <c r="I51" s="672">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J51" s="711"/>
+      <c r="J51" s="673"/>
     </row>
     <row r="52" spans="1:18" ht="15.9" customHeight="1">
       <c r="A52" s="51"/>
@@ -16681,22 +16681,22 @@
         <f t="shared" ref="B52:B58" si="3">1+B51</f>
         <v>19</v>
       </c>
-      <c r="C52" s="670" t="s">
+      <c r="C52" s="649" t="s">
         <v>118</v>
       </c>
-      <c r="D52" s="671"/>
+      <c r="D52" s="656"/>
       <c r="E52" s="73"/>
-      <c r="F52" s="708">
+      <c r="F52" s="663">
         <f>'Lease Rent'!C102</f>
         <v>48213</v>
       </c>
-      <c r="G52" s="709"/>
+      <c r="G52" s="664"/>
       <c r="H52" s="418"/>
-      <c r="I52" s="710">
+      <c r="I52" s="672">
         <f>F52</f>
         <v>48213</v>
       </c>
-      <c r="J52" s="711"/>
+      <c r="J52" s="673"/>
     </row>
     <row r="53" spans="1:18" ht="15.9" customHeight="1">
       <c r="A53" s="51"/>
@@ -16704,22 +16704,22 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="C53" s="670" t="s">
+      <c r="C53" s="649" t="s">
         <v>119</v>
       </c>
-      <c r="D53" s="680"/>
+      <c r="D53" s="650"/>
       <c r="E53" s="73"/>
-      <c r="F53" s="708">
+      <c r="F53" s="663">
         <f>F51</f>
         <v>46023</v>
       </c>
-      <c r="G53" s="709"/>
+      <c r="G53" s="664"/>
       <c r="H53" s="418"/>
-      <c r="I53" s="710">
+      <c r="I53" s="672">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J53" s="711"/>
+      <c r="J53" s="673"/>
     </row>
     <row r="54" spans="1:18" ht="15.9" customHeight="1">
       <c r="A54" s="51"/>
@@ -16727,21 +16727,21 @@
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="C54" s="670" t="s">
+      <c r="C54" s="649" t="s">
         <v>120</v>
       </c>
-      <c r="D54" s="680"/>
+      <c r="D54" s="650"/>
       <c r="E54" s="73"/>
-      <c r="F54" s="678">
-        <v>0</v>
-      </c>
-      <c r="G54" s="712"/>
+      <c r="F54" s="645">
+        <v>0</v>
+      </c>
+      <c r="G54" s="646"/>
       <c r="H54" s="418"/>
-      <c r="I54" s="713">
+      <c r="I54" s="647">
         <f>+F54</f>
         <v>0</v>
       </c>
-      <c r="J54" s="714"/>
+      <c r="J54" s="648"/>
     </row>
     <row r="55" spans="1:18" ht="15.9" customHeight="1">
       <c r="A55" s="51"/>
@@ -16749,10 +16749,10 @@
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="C55" s="672" t="s">
+      <c r="C55" s="655" t="s">
         <v>121</v>
       </c>
-      <c r="D55" s="671"/>
+      <c r="D55" s="656"/>
       <c r="E55" s="58"/>
       <c r="F55" s="56">
         <f>(F52-F51)/365*12</f>
@@ -16779,10 +16779,10 @@
         <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="C56" s="672" t="s">
+      <c r="C56" s="655" t="s">
         <v>122</v>
       </c>
-      <c r="D56" s="671"/>
+      <c r="D56" s="656"/>
       <c r="E56" s="71"/>
       <c r="F56" s="56">
         <v>0</v>
@@ -16808,10 +16808,10 @@
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="C57" s="672" t="s">
+      <c r="C57" s="655" t="s">
         <v>123</v>
       </c>
-      <c r="D57" s="671"/>
+      <c r="D57" s="656"/>
       <c r="E57" s="71"/>
       <c r="F57" s="302" t="s">
         <v>68</v>
@@ -16837,10 +16837,10 @@
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="C58" s="672" t="s">
+      <c r="C58" s="655" t="s">
         <v>124</v>
       </c>
-      <c r="D58" s="671"/>
+      <c r="D58" s="656"/>
       <c r="E58" s="71"/>
       <c r="F58" s="56"/>
       <c r="G58" s="388"/>
@@ -16855,23 +16855,23 @@
       <c r="C59" s="74"/>
       <c r="D59" s="74"/>
       <c r="E59" s="58"/>
-      <c r="F59" s="678" t="s">
+      <c r="F59" s="645" t="s">
         <v>73</v>
       </c>
-      <c r="G59" s="712"/>
+      <c r="G59" s="646"/>
       <c r="H59" s="418"/>
-      <c r="I59" s="713" t="s">
+      <c r="I59" s="647" t="s">
         <v>67</v>
       </c>
-      <c r="J59" s="714"/>
+      <c r="J59" s="648"/>
     </row>
     <row r="60" spans="1:18" ht="15.9" customHeight="1">
       <c r="A60" s="51"/>
-      <c r="B60" s="715" t="s">
+      <c r="B60" s="719" t="s">
         <v>125</v>
       </c>
-      <c r="C60" s="716"/>
-      <c r="D60" s="716"/>
+      <c r="C60" s="720"/>
+      <c r="D60" s="720"/>
       <c r="E60" s="562"/>
       <c r="F60" s="376" t="s">
         <v>75</v>
@@ -16892,27 +16892,27 @@
       <c r="B61" s="162">
         <v>1</v>
       </c>
-      <c r="C61" s="670" t="s">
+      <c r="C61" s="649" t="s">
         <v>126</v>
       </c>
-      <c r="D61" s="671"/>
+      <c r="D61" s="656"/>
       <c r="E61" s="564"/>
       <c r="F61" s="70">
         <f>C221/F21/F27</f>
-        <v>129.25</v>
+        <v>129</v>
       </c>
       <c r="G61" s="388">
         <f>+F61*F6</f>
-        <v>1391.2469999999998</v>
+        <v>1388.5559999999998</v>
       </c>
       <c r="H61" s="418"/>
       <c r="I61" s="138">
         <f>+F61/$J$5</f>
-        <v>1.2307179584840984</v>
+        <v>1.228337459531518</v>
       </c>
       <c r="J61" s="57">
         <f>+I61*$I$6</f>
-        <v>13.247448105122833</v>
+        <v>13.221824414397259</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="15.9" customHeight="1">
@@ -16921,10 +16921,10 @@
         <f>1+B61</f>
         <v>2</v>
       </c>
-      <c r="C62" s="670" t="s">
+      <c r="C62" s="649" t="s">
         <v>127</v>
       </c>
-      <c r="D62" s="671"/>
+      <c r="D62" s="656"/>
       <c r="E62" s="564"/>
       <c r="F62" s="70">
         <v>0</v>
@@ -16948,27 +16948,27 @@
         <f t="shared" ref="B63:B84" si="4">1+B62</f>
         <v>3</v>
       </c>
-      <c r="C63" s="673" t="s">
+      <c r="C63" s="651" t="s">
         <v>128</v>
       </c>
-      <c r="D63" s="674"/>
+      <c r="D63" s="652"/>
       <c r="E63" s="75"/>
       <c r="F63" s="76">
         <f>F61+F62</f>
-        <v>129.25</v>
+        <v>129</v>
       </c>
       <c r="G63" s="206">
         <f>+G61+G62</f>
-        <v>1391.2469999999998</v>
+        <v>1388.5559999999998</v>
       </c>
       <c r="H63" s="418"/>
       <c r="I63" s="139">
         <f>I61+I62</f>
-        <v>1.2307179584840984</v>
+        <v>1.228337459531518</v>
       </c>
       <c r="J63" s="55">
         <f>+J61+J62</f>
-        <v>13.247448105122833</v>
+        <v>13.221824414397259</v>
       </c>
     </row>
     <row r="64" spans="1:18" ht="15.9" customHeight="1">
@@ -16977,27 +16977,27 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="C64" s="670" t="s">
+      <c r="C64" s="649" t="s">
         <v>493</v>
       </c>
-      <c r="D64" s="671"/>
+      <c r="D64" s="656"/>
       <c r="E64" s="56"/>
       <c r="F64" s="54">
         <f>F63*F21</f>
-        <v>1229813.75</v>
+        <v>1227435</v>
       </c>
       <c r="G64" s="385">
         <f>+F64</f>
-        <v>1229813.75</v>
+        <v>1227435</v>
       </c>
       <c r="H64" s="418"/>
       <c r="I64" s="132">
         <f>+F64/$J$5</f>
-        <v>11710.281374976195</v>
+        <v>11687.630927442393</v>
       </c>
       <c r="J64" s="55">
         <f>+I64</f>
-        <v>11710.281374976195</v>
+        <v>11687.630927442393</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="15.9" customHeight="1">
@@ -17006,10 +17006,10 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="C65" s="670" t="s">
+      <c r="C65" s="649" t="s">
         <v>129</v>
       </c>
-      <c r="D65" s="671"/>
+      <c r="D65" s="656"/>
       <c r="E65" s="56"/>
       <c r="F65" s="70">
         <f>(I221/F21/F27)*(1+L1)</f>
@@ -17035,10 +17035,10 @@
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="C66" s="672" t="s">
+      <c r="C66" s="655" t="s">
         <v>494</v>
       </c>
-      <c r="D66" s="671"/>
+      <c r="D66" s="656"/>
       <c r="E66" s="71"/>
       <c r="F66" s="54">
         <f>+F65*F21*(1+L1)</f>
@@ -17064,10 +17064,10 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="C67" s="672" t="s">
+      <c r="C67" s="655" t="s">
         <v>495</v>
       </c>
-      <c r="D67" s="671"/>
+      <c r="D67" s="656"/>
       <c r="E67" s="59"/>
       <c r="F67" s="56">
         <f>(+G221/F27)*(1+L1)</f>
@@ -17093,10 +17093,10 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="C68" s="672" t="s">
+      <c r="C68" s="655" t="s">
         <v>130</v>
       </c>
-      <c r="D68" s="671"/>
+      <c r="D68" s="656"/>
       <c r="E68" s="56"/>
       <c r="F68" s="56">
         <v>11418000</v>
@@ -17121,10 +17121,10 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="C69" s="672" t="s">
+      <c r="C69" s="655" t="s">
         <v>131</v>
       </c>
-      <c r="D69" s="671"/>
+      <c r="D69" s="656"/>
       <c r="E69" s="56"/>
       <c r="F69" s="56">
         <v>0</v>
@@ -17149,10 +17149,10 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="C70" s="670" t="s">
+      <c r="C70" s="649" t="s">
         <v>132</v>
       </c>
-      <c r="D70" s="671"/>
+      <c r="D70" s="656"/>
       <c r="E70" s="56"/>
       <c r="F70" s="56">
         <v>500000</v>
@@ -17177,10 +17177,10 @@
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="C71" s="672" t="s">
+      <c r="C71" s="655" t="s">
         <v>133</v>
       </c>
-      <c r="D71" s="671"/>
+      <c r="D71" s="656"/>
       <c r="E71" s="56"/>
       <c r="F71" s="54">
         <v>0</v>
@@ -17202,10 +17202,10 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="C72" s="672" t="s">
+      <c r="C72" s="655" t="s">
         <v>134</v>
       </c>
-      <c r="D72" s="671"/>
+      <c r="D72" s="656"/>
       <c r="E72" s="56"/>
       <c r="F72" s="54">
         <f>F39*F23*F34</f>
@@ -17231,10 +17231,10 @@
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="C73" s="672" t="s">
+      <c r="C73" s="655" t="s">
         <v>135</v>
       </c>
-      <c r="D73" s="671"/>
+      <c r="D73" s="656"/>
       <c r="E73" s="56"/>
       <c r="F73" s="56">
         <v>0</v>
@@ -17259,10 +17259,10 @@
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="C74" s="670" t="s">
+      <c r="C74" s="649" t="s">
         <v>136</v>
       </c>
-      <c r="D74" s="671"/>
+      <c r="D74" s="656"/>
       <c r="E74" s="563"/>
       <c r="F74" s="68">
         <f>+F36*F64</f>
@@ -17316,10 +17316,10 @@
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="C76" s="670" t="s">
+      <c r="C76" s="649" t="s">
         <v>138</v>
       </c>
-      <c r="D76" s="671"/>
+      <c r="D76" s="656"/>
       <c r="E76" s="59"/>
       <c r="F76" s="56">
         <f>+F78/F23</f>
@@ -17345,10 +17345,10 @@
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="C77" s="670" t="s">
+      <c r="C77" s="649" t="s">
         <v>139</v>
       </c>
-      <c r="D77" s="671"/>
+      <c r="D77" s="656"/>
       <c r="E77" s="71"/>
       <c r="F77" s="51"/>
       <c r="G77" s="558"/>
@@ -17368,10 +17368,10 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="C78" s="670" t="s">
+      <c r="C78" s="649" t="s">
         <v>140</v>
       </c>
-      <c r="D78" s="671"/>
+      <c r="D78" s="656"/>
       <c r="E78" s="71"/>
       <c r="F78" s="56">
         <f>'CAPEX and PM'!B6</f>
@@ -17397,10 +17397,10 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="C79" s="670" t="s">
+      <c r="C79" s="649" t="s">
         <v>141</v>
       </c>
-      <c r="D79" s="671"/>
+      <c r="D79" s="656"/>
       <c r="E79" s="71"/>
       <c r="F79" s="56">
         <f>'CAPEX and PM'!B37</f>
@@ -17426,10 +17426,10 @@
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="C80" s="670" t="s">
+      <c r="C80" s="649" t="s">
         <v>142</v>
       </c>
-      <c r="D80" s="671"/>
+      <c r="D80" s="656"/>
       <c r="E80" s="71"/>
       <c r="F80" s="56">
         <f>+'CAPEX and PM'!B95</f>
@@ -17455,10 +17455,10 @@
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="C81" s="670" t="s">
+      <c r="C81" s="649" t="s">
         <v>143</v>
       </c>
-      <c r="D81" s="671"/>
+      <c r="D81" s="656"/>
       <c r="E81" s="71"/>
       <c r="F81" s="56"/>
       <c r="G81" s="388"/>
@@ -17478,10 +17478,10 @@
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="C82" s="670" t="s">
+      <c r="C82" s="649" t="s">
         <v>144</v>
       </c>
-      <c r="D82" s="680"/>
+      <c r="D82" s="650"/>
       <c r="E82" s="71"/>
       <c r="F82" s="56"/>
       <c r="G82" s="388"/>
@@ -17501,27 +17501,27 @@
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="C83" s="670" t="s">
+      <c r="C83" s="649" t="s">
         <v>145</v>
       </c>
-      <c r="D83" s="671"/>
+      <c r="D83" s="656"/>
       <c r="E83" s="59"/>
       <c r="F83" s="56">
         <f>+G208</f>
-        <v>512254.33034775488</v>
+        <v>511749.08384775487</v>
       </c>
       <c r="G83" s="388">
         <f>+F83</f>
-        <v>512254.33034775488</v>
+        <v>511749.08384775487</v>
       </c>
       <c r="H83" s="418"/>
       <c r="I83" s="133">
         <f t="shared" si="5"/>
-        <v>4877.6835873905438</v>
+        <v>4872.8726323343635</v>
       </c>
       <c r="J83" s="57">
         <f>G83/J5</f>
-        <v>4877.6835873905438</v>
+        <v>4872.8726323343635</v>
       </c>
     </row>
     <row r="84" spans="1:24" ht="22.5" customHeight="1">
@@ -17530,10 +17530,10 @@
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="C84" s="670" t="s">
+      <c r="C84" s="649" t="s">
         <v>496</v>
       </c>
-      <c r="D84" s="671"/>
+      <c r="D84" s="656"/>
       <c r="E84" s="563"/>
       <c r="F84" s="56">
         <f>+F31</f>
@@ -17566,11 +17566,11 @@
     </row>
     <row r="86" spans="1:24" ht="15.9" customHeight="1">
       <c r="A86" s="51"/>
-      <c r="B86" s="692" t="s">
+      <c r="B86" s="657" t="s">
         <v>146</v>
       </c>
-      <c r="C86" s="693"/>
-      <c r="D86" s="694"/>
+      <c r="C86" s="658"/>
+      <c r="D86" s="659"/>
       <c r="E86" s="389"/>
       <c r="F86" s="161" t="s">
         <v>75</v>
@@ -17591,27 +17591,27 @@
       <c r="B87" s="162">
         <v>1</v>
       </c>
-      <c r="C87" s="670" t="s">
+      <c r="C87" s="649" t="s">
         <v>147</v>
       </c>
-      <c r="D87" s="671"/>
+      <c r="D87" s="656"/>
       <c r="E87" s="71"/>
       <c r="F87" s="70">
         <f>+F63</f>
-        <v>129.25</v>
+        <v>129</v>
       </c>
       <c r="G87" s="204">
         <f>+G63</f>
-        <v>1391.2469999999998</v>
+        <v>1388.5559999999998</v>
       </c>
       <c r="H87" s="418"/>
       <c r="I87" s="138">
         <f>+F87/J5</f>
-        <v>1.2307179584840984</v>
+        <v>1.228337459531518</v>
       </c>
       <c r="J87" s="72">
         <f>G87/J5</f>
-        <v>13.247448105122833</v>
+        <v>13.221824414397256</v>
       </c>
       <c r="S87" s="414"/>
       <c r="T87" s="414"/>
@@ -17623,10 +17623,10 @@
         <f>1+B87</f>
         <v>2</v>
       </c>
-      <c r="C88" s="672" t="s">
+      <c r="C88" s="655" t="s">
         <v>148</v>
       </c>
-      <c r="D88" s="671"/>
+      <c r="D88" s="656"/>
       <c r="E88" s="73"/>
       <c r="F88" s="56">
         <v>0</v>
@@ -17649,10 +17649,10 @@
         <f t="shared" ref="B89:B95" si="7">+B88+1</f>
         <v>3</v>
       </c>
-      <c r="C89" s="672" t="s">
+      <c r="C89" s="655" t="s">
         <v>149</v>
       </c>
-      <c r="D89" s="671"/>
+      <c r="D89" s="656"/>
       <c r="E89" s="73"/>
       <c r="F89" s="70">
         <f>(F67/F23)</f>
@@ -17680,10 +17680,10 @@
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="C90" s="672" t="s">
+      <c r="C90" s="655" t="s">
         <v>150</v>
       </c>
-      <c r="D90" s="671"/>
+      <c r="D90" s="656"/>
       <c r="E90" s="73"/>
       <c r="F90" s="66">
         <f>'Security Deposit'!C17</f>
@@ -17711,10 +17711,10 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="C91" s="672" t="s">
+      <c r="C91" s="655" t="s">
         <v>324</v>
       </c>
-      <c r="D91" s="671"/>
+      <c r="D91" s="656"/>
       <c r="E91" s="73"/>
       <c r="F91" s="202">
         <f>+F65</f>
@@ -17742,10 +17742,10 @@
         <f>+B90+1</f>
         <v>5</v>
       </c>
-      <c r="C92" s="672" t="s">
+      <c r="C92" s="655" t="s">
         <v>151</v>
       </c>
-      <c r="D92" s="671"/>
+      <c r="D92" s="656"/>
       <c r="E92" s="73"/>
       <c r="F92" s="66">
         <f>(+F84/F21/F27)</f>
@@ -17772,27 +17772,27 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="C93" s="672" t="s">
+      <c r="C93" s="655" t="s">
         <v>152</v>
       </c>
-      <c r="D93" s="671"/>
+      <c r="D93" s="656"/>
       <c r="E93" s="73"/>
       <c r="F93" s="66">
         <f>F83/F21/F27</f>
-        <v>0.74772921461399378</v>
+        <v>0.74699171461399372</v>
       </c>
       <c r="G93" s="202">
         <f>G83/G21/G27</f>
-        <v>8.0485572661050284</v>
+        <v>8.0406188161050292</v>
       </c>
       <c r="H93" s="418"/>
       <c r="I93" s="138">
         <f>+F93/J5</f>
-        <v>7.1198744488096917E-3</v>
+        <v>7.1128519768995785E-3</v>
       </c>
       <c r="J93" s="72">
         <f>+I93*$I$6</f>
-        <v>7.6638328566987518E-2</v>
+        <v>7.6562738679347056E-2</v>
       </c>
       <c r="S93" s="414"/>
       <c r="T93" s="414"/>
@@ -17803,27 +17803,27 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="C94" s="670" t="s">
+      <c r="C94" s="649" t="s">
         <v>153</v>
       </c>
-      <c r="D94" s="671"/>
+      <c r="D94" s="656"/>
       <c r="E94" s="71"/>
       <c r="F94" s="66">
         <f>+G94/F6</f>
-        <v>20.625132066972007</v>
+        <v>20.607580441972008</v>
       </c>
       <c r="G94" s="202">
         <f>(+SUM(G87:G93)+G104)*7%</f>
-        <v>222.00892156888668</v>
+        <v>221.81999587738667</v>
       </c>
       <c r="H94" s="418"/>
       <c r="I94" s="138">
         <f>+F94/J5</f>
-        <v>0.19639242112904218</v>
+        <v>0.19622529462932783</v>
       </c>
       <c r="J94" s="67">
         <f>I94*I6</f>
-        <v>2.1139680210330098</v>
+        <v>2.1121690713900847</v>
       </c>
       <c r="S94" s="414"/>
       <c r="T94" s="414"/>
@@ -17834,27 +17834,27 @@
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="C95" s="673" t="s">
+      <c r="C95" s="651" t="s">
         <v>69</v>
       </c>
-      <c r="D95" s="674"/>
+      <c r="D95" s="652"/>
       <c r="E95" s="78"/>
       <c r="F95" s="213">
         <f>SUM(F87:F94)</f>
-        <v>178.90169649548184</v>
+        <v>178.63340737048182</v>
       </c>
       <c r="G95" s="54">
         <f>SUM(G87:G94)</f>
-        <v>1925.6978610773665</v>
+        <v>1922.8099969358664</v>
       </c>
       <c r="H95" s="424"/>
       <c r="I95" s="191">
         <f>SUM(I87:I94)</f>
-        <v>1.7035012044894482</v>
+        <v>1.7009465565652433</v>
       </c>
       <c r="J95" s="192">
         <f>SUM(J87:J94)</f>
-        <v>18.336486965124415</v>
+        <v>18.308988734868276</v>
       </c>
       <c r="S95" s="414"/>
       <c r="T95" s="414"/>
@@ -17862,8 +17862,8 @@
     <row r="96" spans="1:24" ht="15.9" customHeight="1">
       <c r="A96" s="51"/>
       <c r="B96" s="381"/>
-      <c r="C96" s="712"/>
-      <c r="D96" s="712"/>
+      <c r="C96" s="646"/>
+      <c r="D96" s="646"/>
       <c r="E96" s="84"/>
       <c r="F96" s="85"/>
       <c r="G96" s="85"/>
@@ -17873,11 +17873,11 @@
     </row>
     <row r="97" spans="1:26" ht="15.9" customHeight="1">
       <c r="A97" s="51"/>
-      <c r="B97" s="675" t="s">
+      <c r="B97" s="653" t="s">
         <v>154</v>
       </c>
-      <c r="C97" s="676"/>
-      <c r="D97" s="676"/>
+      <c r="C97" s="654"/>
+      <c r="D97" s="654"/>
       <c r="E97" s="87"/>
       <c r="F97" s="161" t="s">
         <v>75</v>
@@ -17899,11 +17899,11 @@
       <c r="B98" s="162">
         <v>1</v>
       </c>
-      <c r="C98" s="672" t="str">
+      <c r="C98" s="655" t="str">
         <f>+C77</f>
         <v>Siemens Standard Fitout (Existing)</v>
       </c>
-      <c r="D98" s="671"/>
+      <c r="D98" s="656"/>
       <c r="E98" s="88"/>
       <c r="F98" s="66">
         <v>0</v>
@@ -17928,11 +17928,11 @@
         <f t="shared" ref="B99:B104" si="8">+B98+1</f>
         <v>2</v>
       </c>
-      <c r="C99" s="672" t="str">
+      <c r="C99" s="655" t="str">
         <f>+C78</f>
         <v>Siemens Standard Fitout (New)</v>
       </c>
-      <c r="D99" s="671"/>
+      <c r="D99" s="656"/>
       <c r="E99" s="71"/>
       <c r="F99" s="66">
         <f>'CAPEX and PM'!B29</f>
@@ -17960,11 +17960,11 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="C100" s="672" t="str">
+      <c r="C100" s="655" t="str">
         <f>+C79</f>
         <v>Capex over the period of lease period</v>
       </c>
-      <c r="D100" s="671"/>
+      <c r="D100" s="656"/>
       <c r="E100" s="71"/>
       <c r="F100" s="66">
         <f>'CAPEX and PM'!B89</f>
@@ -17992,11 +17992,11 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="C101" s="672" t="str">
+      <c r="C101" s="655" t="str">
         <f>+C80</f>
         <v>PM cost over the period of lease period</v>
       </c>
-      <c r="D101" s="671"/>
+      <c r="D101" s="656"/>
       <c r="E101" s="71"/>
       <c r="F101" s="66">
         <f>+'CAPEX and PM'!B96</f>
@@ -18024,11 +18024,11 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="C102" s="672" t="str">
+      <c r="C102" s="655" t="str">
         <f>+C81</f>
         <v>Asset Retirement Obligation ( Removal &amp; Restoration Obligation)</v>
       </c>
-      <c r="D102" s="671"/>
+      <c r="D102" s="656"/>
       <c r="E102" s="71"/>
       <c r="F102" s="66">
         <f>'Security Deposit'!D25</f>
@@ -18059,10 +18059,10 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="C103" s="670" t="s">
+      <c r="C103" s="649" t="s">
         <v>155</v>
       </c>
-      <c r="D103" s="671"/>
+      <c r="D103" s="656"/>
       <c r="E103" s="73"/>
       <c r="F103" s="66">
         <f>+F82/F21/F28</f>
@@ -18090,10 +18090,10 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="C104" s="673" t="s">
+      <c r="C104" s="651" t="s">
         <v>156</v>
       </c>
-      <c r="D104" s="674"/>
+      <c r="D104" s="652"/>
       <c r="E104" s="78"/>
       <c r="F104" s="54">
         <f>SUM(F98:F103)</f>
@@ -18130,11 +18130,11 @@
     </row>
     <row r="106" spans="1:26" ht="15.9" customHeight="1">
       <c r="A106" s="51"/>
-      <c r="B106" s="764" t="s">
+      <c r="B106" s="660" t="s">
         <v>157</v>
       </c>
-      <c r="C106" s="687"/>
-      <c r="D106" s="687"/>
+      <c r="C106" s="661"/>
+      <c r="D106" s="661"/>
       <c r="E106" s="87"/>
       <c r="F106" s="161" t="s">
         <v>75</v>
@@ -18155,27 +18155,27 @@
       <c r="B107" s="162">
         <v>1</v>
       </c>
-      <c r="C107" s="670" t="s">
+      <c r="C107" s="649" t="s">
         <v>69</v>
       </c>
-      <c r="D107" s="671"/>
+      <c r="D107" s="656"/>
       <c r="E107" s="71"/>
       <c r="F107" s="56">
         <f>+F95</f>
-        <v>178.90169649548184</v>
+        <v>178.63340737048182</v>
       </c>
       <c r="G107" s="56">
         <f>+G95</f>
-        <v>1925.6978610773665</v>
+        <v>1922.8099969358664</v>
       </c>
       <c r="H107" s="418"/>
       <c r="I107" s="136">
         <f>+I95</f>
-        <v>1.7035012044894482</v>
+        <v>1.7009465565652433</v>
       </c>
       <c r="J107" s="72">
         <f>+J95</f>
-        <v>18.336486965124415</v>
+        <v>18.308988734868276</v>
       </c>
       <c r="S107" s="414"/>
       <c r="T107" s="414"/>
@@ -18186,10 +18186,10 @@
         <f>+B107+1</f>
         <v>2</v>
       </c>
-      <c r="C108" s="670" t="s">
+      <c r="C108" s="649" t="s">
         <v>156</v>
       </c>
-      <c r="D108" s="680"/>
+      <c r="D108" s="650"/>
       <c r="E108" s="71"/>
       <c r="F108" s="56">
         <f>+F104</f>
@@ -18217,27 +18217,27 @@
         <f>+B108+1</f>
         <v>3</v>
       </c>
-      <c r="C109" s="673" t="s">
+      <c r="C109" s="651" t="s">
         <v>158</v>
       </c>
-      <c r="D109" s="674"/>
+      <c r="D109" s="652"/>
       <c r="E109" s="78"/>
       <c r="F109" s="54">
         <f>SUM(F107:F108)</f>
-        <v>315.26987588085774</v>
+        <v>315.00158675585772</v>
       </c>
       <c r="G109" s="54">
         <f>SUM(G107:G108)</f>
-        <v>3393.5649439815534</v>
+        <v>3390.677079840053</v>
       </c>
       <c r="H109" s="418"/>
       <c r="I109" s="191">
         <f>SUM(I107:I108)</f>
-        <v>3.0019984372582154</v>
+        <v>2.9994437893340105</v>
       </c>
       <c r="J109" s="82">
         <f>SUM(J107:J108)</f>
-        <v>32.313511178647424</v>
+        <v>32.286012948391289</v>
       </c>
       <c r="S109" s="414"/>
       <c r="T109" s="414"/>
@@ -18249,11 +18249,11 @@
     </row>
     <row r="110" spans="1:26" ht="15.9" customHeight="1">
       <c r="A110" s="51"/>
-      <c r="B110" s="675" t="s">
+      <c r="B110" s="653" t="s">
         <v>159</v>
       </c>
-      <c r="C110" s="676"/>
-      <c r="D110" s="676"/>
+      <c r="C110" s="654"/>
+      <c r="D110" s="654"/>
       <c r="E110" s="89"/>
       <c r="F110" s="161" t="s">
         <v>75</v>
@@ -18275,10 +18275,10 @@
       <c r="B111" s="249">
         <v>1</v>
       </c>
-      <c r="C111" s="670" t="s">
+      <c r="C111" s="649" t="s">
         <v>160</v>
       </c>
-      <c r="D111" s="680"/>
+      <c r="D111" s="650"/>
       <c r="E111" s="83"/>
       <c r="F111" s="376"/>
       <c r="G111" s="376"/>
@@ -18292,10 +18292,10 @@
         <f t="shared" ref="B112:B120" si="9">1+B111</f>
         <v>2</v>
       </c>
-      <c r="C112" s="670" t="s">
+      <c r="C112" s="649" t="s">
         <v>161</v>
       </c>
-      <c r="D112" s="680"/>
+      <c r="D112" s="650"/>
       <c r="E112" s="83"/>
       <c r="F112" s="376"/>
       <c r="G112" s="376"/>
@@ -18311,10 +18311,10 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="C113" s="670" t="s">
+      <c r="C113" s="649" t="s">
         <v>162</v>
       </c>
-      <c r="D113" s="680"/>
+      <c r="D113" s="650"/>
       <c r="E113" s="83"/>
       <c r="F113" s="388">
         <f>+F65*0</f>
@@ -18342,10 +18342,10 @@
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="C114" s="670" t="s">
+      <c r="C114" s="649" t="s">
         <v>163</v>
       </c>
-      <c r="D114" s="680"/>
+      <c r="D114" s="650"/>
       <c r="E114" s="83"/>
       <c r="F114" s="376"/>
       <c r="G114" s="376"/>
@@ -18359,10 +18359,10 @@
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="C115" s="670" t="s">
+      <c r="C115" s="649" t="s">
         <v>164</v>
       </c>
-      <c r="D115" s="680"/>
+      <c r="D115" s="650"/>
       <c r="E115" s="83"/>
       <c r="F115" s="376"/>
       <c r="G115" s="376"/>
@@ -18376,10 +18376,10 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="C116" s="670" t="s">
+      <c r="C116" s="649" t="s">
         <v>165</v>
       </c>
-      <c r="D116" s="680"/>
+      <c r="D116" s="650"/>
       <c r="E116" s="83"/>
       <c r="F116" s="376"/>
       <c r="G116" s="376"/>
@@ -18393,10 +18393,10 @@
         <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="C117" s="670" t="s">
+      <c r="C117" s="649" t="s">
         <v>166</v>
       </c>
-      <c r="D117" s="680"/>
+      <c r="D117" s="650"/>
       <c r="E117" s="83"/>
       <c r="F117" s="376"/>
       <c r="G117" s="376"/>
@@ -18410,10 +18410,10 @@
         <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="C118" s="670" t="s">
+      <c r="C118" s="649" t="s">
         <v>167</v>
       </c>
-      <c r="D118" s="671"/>
+      <c r="D118" s="656"/>
       <c r="E118" s="252"/>
       <c r="F118" s="360"/>
       <c r="G118" s="207">
@@ -18436,10 +18436,10 @@
         <f t="shared" si="9"/>
         <v>9</v>
       </c>
-      <c r="C119" s="670" t="s">
+      <c r="C119" s="649" t="s">
         <v>168</v>
       </c>
-      <c r="D119" s="680"/>
+      <c r="D119" s="650"/>
       <c r="E119" s="252"/>
       <c r="F119" s="90"/>
       <c r="G119" s="90">
@@ -18462,10 +18462,10 @@
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="C120" s="673" t="s">
+      <c r="C120" s="651" t="s">
         <v>169</v>
       </c>
-      <c r="D120" s="674"/>
+      <c r="D120" s="652"/>
       <c r="E120" s="253"/>
       <c r="F120" s="54">
         <f>SUM(F111:F119)</f>
@@ -18491,8 +18491,8 @@
     <row r="121" spans="1:26" ht="15.9" customHeight="1">
       <c r="A121" s="77"/>
       <c r="B121" s="162"/>
-      <c r="C121" s="678"/>
-      <c r="D121" s="679"/>
+      <c r="C121" s="645"/>
+      <c r="D121" s="662"/>
       <c r="E121" s="78"/>
       <c r="F121" s="54"/>
       <c r="G121" s="385"/>
@@ -18506,11 +18506,11 @@
     </row>
     <row r="122" spans="1:26" ht="15.9" customHeight="1">
       <c r="A122" s="77"/>
-      <c r="B122" s="675" t="s">
+      <c r="B122" s="653" t="s">
         <v>170</v>
       </c>
-      <c r="C122" s="676"/>
-      <c r="D122" s="676"/>
+      <c r="C122" s="654"/>
+      <c r="D122" s="654"/>
       <c r="E122" s="89"/>
       <c r="F122" s="161" t="s">
         <v>75</v>
@@ -18533,10 +18533,10 @@
       <c r="B123" s="251">
         <v>1</v>
       </c>
-      <c r="C123" s="670" t="s">
+      <c r="C123" s="649" t="s">
         <v>171</v>
       </c>
-      <c r="D123" s="680"/>
+      <c r="D123" s="650"/>
       <c r="E123" s="78"/>
       <c r="F123" s="54"/>
       <c r="G123" s="385"/>
@@ -18549,10 +18549,10 @@
       <c r="B124" s="162">
         <v>2</v>
       </c>
-      <c r="C124" s="673" t="s">
+      <c r="C124" s="651" t="s">
         <v>172</v>
       </c>
-      <c r="D124" s="674"/>
+      <c r="D124" s="652"/>
       <c r="E124" s="78"/>
       <c r="F124" s="54">
         <f>SUM(F123)</f>
@@ -18575,8 +18575,8 @@
     <row r="125" spans="1:26" ht="15.9" customHeight="1">
       <c r="A125" s="77"/>
       <c r="B125" s="162"/>
-      <c r="C125" s="678"/>
-      <c r="D125" s="679"/>
+      <c r="C125" s="645"/>
+      <c r="D125" s="662"/>
       <c r="E125" s="63"/>
       <c r="F125" s="54"/>
       <c r="G125" s="385"/>
@@ -18586,11 +18586,11 @@
     </row>
     <row r="126" spans="1:26" ht="15.9" customHeight="1">
       <c r="A126" s="77"/>
-      <c r="B126" s="675" t="s">
+      <c r="B126" s="653" t="s">
         <v>173</v>
       </c>
-      <c r="C126" s="676"/>
-      <c r="D126" s="676"/>
+      <c r="C126" s="654"/>
+      <c r="D126" s="654"/>
       <c r="E126" s="89"/>
       <c r="F126" s="161" t="s">
         <v>75</v>
@@ -18611,10 +18611,10 @@
       <c r="B127" s="249">
         <v>1</v>
       </c>
-      <c r="C127" s="670" t="s">
+      <c r="C127" s="649" t="s">
         <v>174</v>
       </c>
-      <c r="D127" s="680"/>
+      <c r="D127" s="650"/>
       <c r="E127" s="250"/>
       <c r="F127" s="385"/>
       <c r="G127" s="385"/>
@@ -18628,10 +18628,10 @@
         <f>1+B127</f>
         <v>2</v>
       </c>
-      <c r="C128" s="670" t="s">
+      <c r="C128" s="649" t="s">
         <v>175</v>
       </c>
-      <c r="D128" s="680"/>
+      <c r="D128" s="650"/>
       <c r="E128" s="250"/>
       <c r="F128" s="385"/>
       <c r="G128" s="385"/>
@@ -18645,10 +18645,10 @@
         <f>1+B128</f>
         <v>3</v>
       </c>
-      <c r="C129" s="670" t="s">
+      <c r="C129" s="649" t="s">
         <v>176</v>
       </c>
-      <c r="D129" s="680"/>
+      <c r="D129" s="650"/>
       <c r="E129" s="250"/>
       <c r="F129" s="385"/>
       <c r="G129" s="385"/>
@@ -18662,10 +18662,10 @@
         <f>1+B129</f>
         <v>4</v>
       </c>
-      <c r="C130" s="670" t="s">
+      <c r="C130" s="649" t="s">
         <v>177</v>
       </c>
-      <c r="D130" s="680"/>
+      <c r="D130" s="650"/>
       <c r="E130" s="250"/>
       <c r="F130" s="385"/>
       <c r="G130" s="385"/>
@@ -18679,10 +18679,10 @@
         <f>1+B130</f>
         <v>5</v>
       </c>
-      <c r="C131" s="670" t="s">
+      <c r="C131" s="649" t="s">
         <v>178</v>
       </c>
-      <c r="D131" s="680"/>
+      <c r="D131" s="650"/>
       <c r="E131" s="250"/>
       <c r="F131" s="385"/>
       <c r="G131" s="385"/>
@@ -18696,10 +18696,10 @@
         <f>1+B131</f>
         <v>6</v>
       </c>
-      <c r="C132" s="670" t="s">
+      <c r="C132" s="649" t="s">
         <v>179</v>
       </c>
-      <c r="D132" s="680"/>
+      <c r="D132" s="650"/>
       <c r="E132" s="250"/>
       <c r="F132" s="385"/>
       <c r="G132" s="385"/>
@@ -18712,10 +18712,10 @@
       <c r="B133" s="381">
         <v>7</v>
       </c>
-      <c r="C133" s="673" t="s">
+      <c r="C133" s="651" t="s">
         <v>180</v>
       </c>
-      <c r="D133" s="674"/>
+      <c r="D133" s="652"/>
       <c r="E133" s="250"/>
       <c r="F133" s="385">
         <f>SUM(F127:F132)</f>
@@ -18738,8 +18738,8 @@
     <row r="134" spans="1:20" ht="15.9" customHeight="1">
       <c r="A134" s="77"/>
       <c r="B134" s="162"/>
-      <c r="C134" s="712"/>
-      <c r="D134" s="679"/>
+      <c r="C134" s="646"/>
+      <c r="D134" s="662"/>
       <c r="E134" s="250"/>
       <c r="F134" s="385"/>
       <c r="G134" s="385"/>
@@ -18749,11 +18749,11 @@
     </row>
     <row r="135" spans="1:20" ht="15.9" customHeight="1">
       <c r="A135" s="51"/>
-      <c r="B135" s="675" t="s">
+      <c r="B135" s="653" t="s">
         <v>181</v>
       </c>
-      <c r="C135" s="676"/>
-      <c r="D135" s="676"/>
+      <c r="C135" s="654"/>
+      <c r="D135" s="654"/>
       <c r="E135" s="89"/>
       <c r="F135" s="161" t="s">
         <v>75</v>
@@ -18774,27 +18774,27 @@
       <c r="B136" s="162">
         <v>1</v>
       </c>
-      <c r="C136" s="673" t="s">
+      <c r="C136" s="651" t="s">
         <v>182</v>
       </c>
-      <c r="D136" s="674"/>
+      <c r="D136" s="652"/>
       <c r="E136" s="78"/>
       <c r="F136" s="54">
         <f>F120+F109+F124+F133</f>
-        <v>315.26987588085774</v>
+        <v>315.00158675585772</v>
       </c>
       <c r="G136" s="385">
         <f>G120+G109+G124+G133</f>
-        <v>4093.3449439815531</v>
+        <v>4090.4570798400528</v>
       </c>
       <c r="H136" s="418"/>
       <c r="I136" s="191">
         <f>I120+I109+I124+I133</f>
-        <v>3.0019984372582154</v>
+        <v>2.9994437893340105</v>
       </c>
       <c r="J136" s="192">
         <f>J120+J109+J124+J133</f>
-        <v>38.976813406794442</v>
+        <v>38.949315176538306</v>
       </c>
       <c r="S136" s="422"/>
       <c r="T136" s="420"/>
@@ -18802,8 +18802,8 @@
     <row r="137" spans="1:20" ht="15.9" customHeight="1">
       <c r="A137" s="77"/>
       <c r="B137" s="162"/>
-      <c r="C137" s="678"/>
-      <c r="D137" s="679"/>
+      <c r="C137" s="645"/>
+      <c r="D137" s="662"/>
       <c r="E137" s="78"/>
       <c r="F137" s="54"/>
       <c r="G137" s="385"/>
@@ -18817,23 +18817,23 @@
       <c r="C138" s="380"/>
       <c r="D138" s="377"/>
       <c r="E138" s="167"/>
-      <c r="F138" s="678" t="s">
+      <c r="F138" s="645" t="s">
         <v>73</v>
       </c>
-      <c r="G138" s="712"/>
+      <c r="G138" s="646"/>
       <c r="H138" s="418"/>
-      <c r="I138" s="713" t="s">
+      <c r="I138" s="647" t="s">
         <v>67</v>
       </c>
-      <c r="J138" s="714"/>
+      <c r="J138" s="648"/>
     </row>
     <row r="139" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A139" s="51"/>
-      <c r="B139" s="675" t="s">
+      <c r="B139" s="653" t="s">
         <v>183</v>
       </c>
-      <c r="C139" s="676"/>
-      <c r="D139" s="677"/>
+      <c r="C139" s="654"/>
+      <c r="D139" s="669"/>
       <c r="E139" s="161"/>
       <c r="F139" s="161" t="s">
         <v>75</v>
@@ -18852,8 +18852,8 @@
     <row r="140" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A140" s="51"/>
       <c r="B140" s="91"/>
-      <c r="C140" s="681"/>
-      <c r="D140" s="682"/>
+      <c r="C140" s="670"/>
+      <c r="D140" s="671"/>
       <c r="E140" s="163"/>
       <c r="F140" s="54"/>
       <c r="G140" s="385"/>
@@ -18864,10 +18864,10 @@
     <row r="141" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A141" s="51"/>
       <c r="B141" s="91"/>
-      <c r="C141" s="670" t="s">
+      <c r="C141" s="649" t="s">
         <v>184</v>
       </c>
-      <c r="D141" s="671"/>
+      <c r="D141" s="656"/>
       <c r="E141" s="58"/>
       <c r="F141" s="243">
         <f>F21</f>
@@ -18890,10 +18890,10 @@
     <row r="142" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A142" s="51"/>
       <c r="B142" s="91"/>
-      <c r="C142" s="672" t="s">
+      <c r="C142" s="655" t="s">
         <v>185</v>
       </c>
-      <c r="D142" s="671"/>
+      <c r="D142" s="656"/>
       <c r="E142" s="59"/>
       <c r="F142" s="56">
         <f>F24</f>
@@ -18916,10 +18916,10 @@
     <row r="143" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A143" s="51"/>
       <c r="B143" s="91"/>
-      <c r="C143" s="672" t="s">
+      <c r="C143" s="655" t="s">
         <v>186</v>
       </c>
-      <c r="D143" s="671"/>
+      <c r="D143" s="656"/>
       <c r="E143" s="73"/>
       <c r="F143" s="56" t="e">
         <f>+#REF!</f>
@@ -18942,36 +18942,36 @@
     <row r="144" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A144" s="51"/>
       <c r="B144" s="91"/>
-      <c r="C144" s="670" t="s">
+      <c r="C144" s="649" t="s">
         <v>187</v>
       </c>
-      <c r="D144" s="671"/>
+      <c r="D144" s="656"/>
       <c r="E144" s="73"/>
       <c r="F144" s="56">
         <f>F109</f>
-        <v>315.26987588085774</v>
+        <v>315.00158675585772</v>
       </c>
       <c r="G144" s="388">
         <f>+G109</f>
-        <v>3393.5649439815534</v>
+        <v>3390.677079840053</v>
       </c>
       <c r="H144" s="418"/>
       <c r="I144" s="133">
         <f>I109</f>
-        <v>3.0019984372582154</v>
+        <v>2.9994437893340105</v>
       </c>
       <c r="J144" s="72">
         <f>+J109</f>
-        <v>32.313511178647424</v>
+        <v>32.286012948391289</v>
       </c>
     </row>
     <row r="145" spans="1:10" ht="15.9" hidden="1" customHeight="1">
       <c r="A145" s="51"/>
       <c r="B145" s="91"/>
-      <c r="C145" s="700" t="s">
+      <c r="C145" s="740" t="s">
         <v>188</v>
       </c>
-      <c r="D145" s="701"/>
+      <c r="D145" s="741"/>
       <c r="E145" s="92"/>
       <c r="F145" s="93">
         <f>F120</f>
@@ -18994,10 +18994,10 @@
     <row r="146" spans="1:10" ht="15.9" hidden="1" customHeight="1">
       <c r="A146" s="77"/>
       <c r="B146" s="162"/>
-      <c r="C146" s="673" t="s">
+      <c r="C146" s="651" t="s">
         <v>189</v>
       </c>
-      <c r="D146" s="674"/>
+      <c r="D146" s="652"/>
       <c r="E146" s="78"/>
       <c r="F146" s="245" t="e">
         <f>F136*#REF!</f>
@@ -19031,11 +19031,11 @@
     </row>
     <row r="148" spans="1:10" ht="15.9" customHeight="1">
       <c r="A148" s="77"/>
-      <c r="B148" s="675" t="s">
+      <c r="B148" s="653" t="s">
         <v>190</v>
       </c>
-      <c r="C148" s="676"/>
-      <c r="D148" s="677"/>
+      <c r="C148" s="654"/>
+      <c r="D148" s="669"/>
       <c r="E148" s="379"/>
       <c r="F148" s="379" t="s">
         <v>191</v>
@@ -19054,8 +19054,8 @@
     <row r="149" spans="1:10" ht="15.9" customHeight="1">
       <c r="A149" s="51"/>
       <c r="B149" s="99"/>
-      <c r="C149" s="681"/>
-      <c r="D149" s="682"/>
+      <c r="C149" s="670"/>
+      <c r="D149" s="671"/>
       <c r="E149" s="100"/>
       <c r="F149" s="101"/>
       <c r="G149" s="209"/>
@@ -19066,36 +19066,36 @@
     <row r="150" spans="1:10" ht="15.9" customHeight="1">
       <c r="A150" s="51"/>
       <c r="B150" s="99"/>
-      <c r="C150" s="672" t="s">
+      <c r="C150" s="655" t="s">
         <v>192</v>
       </c>
-      <c r="D150" s="671"/>
+      <c r="D150" s="656"/>
       <c r="E150" s="100"/>
       <c r="F150" s="101">
         <f>(+F64/(1+L1))*115%</f>
-        <v>1414285.8125</v>
+        <v>1411550.25</v>
       </c>
       <c r="G150" s="101">
         <f>+F150</f>
-        <v>1414285.8125</v>
+        <v>1411550.25</v>
       </c>
       <c r="H150" s="418"/>
       <c r="I150" s="143">
         <f>F150/$J$5</f>
-        <v>13466.823581222625</v>
+        <v>13440.775566558752</v>
       </c>
       <c r="J150" s="102">
         <f>+I150</f>
-        <v>13466.823581222625</v>
+        <v>13440.775566558752</v>
       </c>
     </row>
     <row r="151" spans="1:10" ht="15.9" customHeight="1">
       <c r="A151" s="51"/>
       <c r="B151" s="99"/>
-      <c r="C151" s="672" t="s">
+      <c r="C151" s="655" t="s">
         <v>193</v>
       </c>
-      <c r="D151" s="671"/>
+      <c r="D151" s="656"/>
       <c r="E151" s="100"/>
       <c r="F151" s="101">
         <v>0</v>
@@ -19114,10 +19114,10 @@
     <row r="152" spans="1:10" ht="15.9" customHeight="1">
       <c r="A152" s="51"/>
       <c r="B152" s="99"/>
-      <c r="C152" s="672" t="s">
+      <c r="C152" s="655" t="s">
         <v>194</v>
       </c>
-      <c r="D152" s="671"/>
+      <c r="D152" s="656"/>
       <c r="E152" s="100"/>
       <c r="F152" s="101">
         <f>(+F66/(1+L1))*115%</f>
@@ -19140,10 +19140,10 @@
     <row r="153" spans="1:10" ht="15.9" customHeight="1">
       <c r="A153" s="51"/>
       <c r="B153" s="99"/>
-      <c r="C153" s="672" t="s">
+      <c r="C153" s="655" t="s">
         <v>195</v>
       </c>
-      <c r="D153" s="671"/>
+      <c r="D153" s="656"/>
       <c r="E153" s="100"/>
       <c r="F153" s="101">
         <f>(+F67/(1+L1))*115%</f>
@@ -19166,60 +19166,60 @@
     <row r="154" spans="1:10" ht="15.9" customHeight="1">
       <c r="A154" s="51"/>
       <c r="B154" s="99"/>
-      <c r="C154" s="670" t="s">
+      <c r="C154" s="649" t="s">
         <v>196</v>
       </c>
-      <c r="D154" s="671"/>
+      <c r="D154" s="656"/>
       <c r="E154" s="103"/>
       <c r="F154" s="104">
         <f>SUM(F150:F153)</f>
-        <v>1606310.6471192515</v>
+        <v>1603575.0846192515</v>
       </c>
       <c r="G154" s="210">
         <f>SUM(G150:G153)</f>
-        <v>1606310.6471192515</v>
+        <v>1603575.0846192515</v>
       </c>
       <c r="H154" s="418"/>
       <c r="I154" s="523">
         <f>SUM(I150:I153)</f>
-        <v>15295.283251944884</v>
+        <v>15269.235237281011</v>
       </c>
       <c r="J154" s="524">
         <f>SUM(J150:J153)</f>
-        <v>15295.283251944884</v>
+        <v>15269.235237281011</v>
       </c>
     </row>
     <row r="155" spans="1:10" ht="15.9" customHeight="1">
       <c r="A155" s="51"/>
       <c r="B155" s="99"/>
-      <c r="C155" s="670" t="s">
+      <c r="C155" s="649" t="s">
         <v>197</v>
       </c>
-      <c r="D155" s="671"/>
+      <c r="D155" s="656"/>
       <c r="E155" s="105"/>
       <c r="F155" s="101">
         <f>+F154*12</f>
-        <v>19275727.765431017</v>
+        <v>19242901.015431017</v>
       </c>
       <c r="G155" s="209">
         <f>+G154*12</f>
-        <v>19275727.765431017</v>
+        <v>19242901.015431017</v>
       </c>
       <c r="H155" s="418"/>
       <c r="I155" s="143">
         <f>+I154*12</f>
-        <v>183543.3990233386</v>
+        <v>183230.82284737212</v>
       </c>
       <c r="J155" s="102">
         <f>+J154*12</f>
-        <v>183543.3990233386</v>
+        <v>183230.82284737212</v>
       </c>
     </row>
     <row r="156" spans="1:10" ht="15.9" customHeight="1">
       <c r="A156" s="51"/>
       <c r="B156" s="99"/>
-      <c r="C156" s="681"/>
-      <c r="D156" s="682"/>
+      <c r="C156" s="670"/>
+      <c r="D156" s="671"/>
       <c r="E156" s="105"/>
       <c r="F156" s="101"/>
       <c r="G156" s="209"/>
@@ -19229,11 +19229,11 @@
     </row>
     <row r="157" spans="1:10" ht="15.9" customHeight="1">
       <c r="A157" s="51"/>
-      <c r="B157" s="675" t="s">
+      <c r="B157" s="653" t="s">
         <v>198</v>
       </c>
-      <c r="C157" s="676"/>
-      <c r="D157" s="677"/>
+      <c r="C157" s="654"/>
+      <c r="D157" s="669"/>
       <c r="E157" s="375"/>
       <c r="F157" s="379" t="s">
         <v>191</v>
@@ -19252,8 +19252,8 @@
     <row r="158" spans="1:10" ht="15.9" customHeight="1">
       <c r="A158" s="51"/>
       <c r="B158" s="99"/>
-      <c r="C158" s="681"/>
-      <c r="D158" s="682"/>
+      <c r="C158" s="670"/>
+      <c r="D158" s="671"/>
       <c r="E158" s="105"/>
       <c r="F158" s="101"/>
       <c r="G158" s="209"/>
@@ -19264,10 +19264,10 @@
     <row r="159" spans="1:10" ht="15.9" customHeight="1">
       <c r="A159" s="51"/>
       <c r="B159" s="99"/>
-      <c r="C159" s="698" t="s">
+      <c r="C159" s="738" t="s">
         <v>199</v>
       </c>
-      <c r="D159" s="699"/>
+      <c r="D159" s="739"/>
       <c r="E159" s="105"/>
       <c r="F159" s="101">
         <f t="shared" ref="F159:G161" si="10">+F78</f>
@@ -19290,10 +19290,10 @@
     <row r="160" spans="1:10" ht="15.9" customHeight="1">
       <c r="A160" s="51"/>
       <c r="B160" s="99"/>
-      <c r="C160" s="670" t="s">
+      <c r="C160" s="649" t="s">
         <v>200</v>
       </c>
-      <c r="D160" s="680"/>
+      <c r="D160" s="650"/>
       <c r="E160" s="105"/>
       <c r="F160" s="101">
         <f t="shared" si="10"/>
@@ -19316,10 +19316,10 @@
     <row r="161" spans="1:22" ht="15.9" customHeight="1">
       <c r="A161" s="51"/>
       <c r="B161" s="99"/>
-      <c r="C161" s="670" t="s">
+      <c r="C161" s="649" t="s">
         <v>201</v>
       </c>
-      <c r="D161" s="680"/>
+      <c r="D161" s="650"/>
       <c r="E161" s="105"/>
       <c r="F161" s="101">
         <f t="shared" si="10"/>
@@ -19342,10 +19342,10 @@
     <row r="162" spans="1:22" ht="15.9" customHeight="1">
       <c r="A162" s="51"/>
       <c r="B162" s="99"/>
-      <c r="C162" s="673" t="s">
+      <c r="C162" s="651" t="s">
         <v>29</v>
       </c>
-      <c r="D162" s="674"/>
+      <c r="D162" s="652"/>
       <c r="E162" s="105"/>
       <c r="F162" s="237">
         <f>SUM(F159:F161)</f>
@@ -19368,8 +19368,8 @@
     <row r="163" spans="1:22" ht="15.9" customHeight="1">
       <c r="A163" s="51"/>
       <c r="B163" s="99"/>
-      <c r="C163" s="681"/>
-      <c r="D163" s="682"/>
+      <c r="C163" s="670"/>
+      <c r="D163" s="671"/>
       <c r="E163" s="105"/>
       <c r="F163" s="101"/>
       <c r="G163" s="209"/>
@@ -19379,12 +19379,12 @@
     </row>
     <row r="164" spans="1:22" ht="15.9" customHeight="1">
       <c r="A164" s="106"/>
-      <c r="B164" s="692" t="s">
+      <c r="B164" s="657" t="s">
         <v>202</v>
       </c>
-      <c r="C164" s="693"/>
-      <c r="D164" s="694"/>
-      <c r="E164" s="763"/>
+      <c r="C164" s="658"/>
+      <c r="D164" s="659"/>
+      <c r="E164" s="667"/>
       <c r="F164" s="161" t="s">
         <v>75</v>
       </c>
@@ -19401,10 +19401,10 @@
     </row>
     <row r="165" spans="1:22" ht="15.9" customHeight="1">
       <c r="A165" s="106"/>
-      <c r="B165" s="695"/>
-      <c r="C165" s="696"/>
-      <c r="D165" s="697"/>
-      <c r="E165" s="685"/>
+      <c r="B165" s="735"/>
+      <c r="C165" s="736"/>
+      <c r="D165" s="737"/>
+      <c r="E165" s="668"/>
       <c r="F165" s="161" t="s">
         <v>73</v>
       </c>
@@ -19422,8 +19422,8 @@
     <row r="166" spans="1:22" ht="15.9" customHeight="1">
       <c r="A166" s="107"/>
       <c r="B166" s="99"/>
-      <c r="C166" s="681"/>
-      <c r="D166" s="682"/>
+      <c r="C166" s="670"/>
+      <c r="D166" s="671"/>
       <c r="E166" s="59"/>
       <c r="F166" s="56"/>
       <c r="G166" s="388"/>
@@ -19434,39 +19434,39 @@
     <row r="167" spans="1:22" ht="15.9" customHeight="1">
       <c r="A167" s="107"/>
       <c r="B167" s="99"/>
-      <c r="C167" s="683" t="str">
+      <c r="C167" s="733" t="str">
         <f>+C107</f>
         <v>Net Rent I</v>
       </c>
-      <c r="D167" s="684"/>
+      <c r="D167" s="734"/>
       <c r="E167" s="59"/>
       <c r="F167" s="56">
         <f>+F107</f>
-        <v>178.90169649548184</v>
+        <v>178.63340737048182</v>
       </c>
       <c r="G167" s="388">
         <f>+G107</f>
-        <v>1925.6978610773665</v>
+        <v>1922.8099969358664</v>
       </c>
       <c r="H167" s="418"/>
       <c r="I167" s="136">
         <f>+I107</f>
-        <v>1.7035012044894482</v>
+        <v>1.7009465565652433</v>
       </c>
       <c r="J167" s="67">
         <f>+J107</f>
-        <v>18.336486965124415</v>
+        <v>18.308988734868276</v>
       </c>
       <c r="T167" s="423"/>
     </row>
     <row r="168" spans="1:22" ht="15.9" customHeight="1">
       <c r="A168" s="107"/>
       <c r="B168" s="99"/>
-      <c r="C168" s="683" t="str">
+      <c r="C168" s="733" t="str">
         <f>+C108</f>
         <v>Net Rent II</v>
       </c>
-      <c r="D168" s="684"/>
+      <c r="D168" s="734"/>
       <c r="E168" s="59"/>
       <c r="F168" s="56">
         <f>+F108</f>
@@ -19490,27 +19490,27 @@
     <row r="169" spans="1:22" ht="15.9" customHeight="1">
       <c r="A169" s="107"/>
       <c r="B169" s="147"/>
-      <c r="C169" s="688" t="s">
+      <c r="C169" s="729" t="s">
         <v>203</v>
       </c>
-      <c r="D169" s="689"/>
+      <c r="D169" s="730"/>
       <c r="E169" s="148"/>
       <c r="F169" s="149">
         <f>SUM(F167:F168)</f>
-        <v>315.26987588085774</v>
+        <v>315.00158675585772</v>
       </c>
       <c r="G169" s="211">
         <f>SUM(G167:G168)</f>
-        <v>3393.5649439815534</v>
+        <v>3390.677079840053</v>
       </c>
       <c r="H169" s="212"/>
       <c r="I169" s="234">
         <f>SUM(I167:I168)</f>
-        <v>3.0019984372582154</v>
+        <v>2.9994437893340105</v>
       </c>
       <c r="J169" s="214">
         <f>SUM(J167:J168)</f>
-        <v>32.313511178647424</v>
+        <v>32.286012948391289</v>
       </c>
       <c r="T169" s="423"/>
       <c r="V169" s="423"/>
@@ -19518,8 +19518,8 @@
     <row r="170" spans="1:22" ht="15.9" customHeight="1">
       <c r="A170" s="107"/>
       <c r="B170" s="162"/>
-      <c r="C170" s="690"/>
-      <c r="D170" s="691"/>
+      <c r="C170" s="731"/>
+      <c r="D170" s="732"/>
       <c r="E170" s="75"/>
       <c r="F170" s="54"/>
       <c r="G170" s="385"/>
@@ -19532,11 +19532,11 @@
     <row r="171" spans="1:22" ht="15.9" customHeight="1">
       <c r="A171" s="107"/>
       <c r="B171" s="99"/>
-      <c r="C171" s="683" t="str">
+      <c r="C171" s="733" t="str">
         <f>+C120</f>
         <v xml:space="preserve">OpEx I </v>
       </c>
-      <c r="D171" s="684"/>
+      <c r="D171" s="734"/>
       <c r="E171" s="59"/>
       <c r="F171" s="56">
         <f>+F120</f>
@@ -19560,11 +19560,11 @@
     <row r="172" spans="1:22" ht="15.9" customHeight="1">
       <c r="A172" s="107"/>
       <c r="B172" s="99"/>
-      <c r="C172" s="683" t="str">
+      <c r="C172" s="733" t="str">
         <f>+C124</f>
         <v xml:space="preserve">OpEx II </v>
       </c>
-      <c r="D172" s="684"/>
+      <c r="D172" s="734"/>
       <c r="E172" s="59"/>
       <c r="F172" s="56">
         <f>+F124</f>
@@ -19587,10 +19587,10 @@
     <row r="173" spans="1:22" ht="15.9" customHeight="1">
       <c r="A173" s="107"/>
       <c r="B173" s="150"/>
-      <c r="C173" s="688" t="s">
+      <c r="C173" s="729" t="s">
         <v>204</v>
       </c>
-      <c r="D173" s="689"/>
+      <c r="D173" s="730"/>
       <c r="E173" s="151"/>
       <c r="F173" s="152">
         <f>SUM(F171:F172)</f>
@@ -19625,11 +19625,11 @@
     <row r="175" spans="1:22" ht="15.9" customHeight="1">
       <c r="A175" s="107"/>
       <c r="B175" s="99"/>
-      <c r="C175" s="683" t="str">
+      <c r="C175" s="733" t="str">
         <f>+C133</f>
         <v xml:space="preserve">Services </v>
       </c>
-      <c r="D175" s="684"/>
+      <c r="D175" s="734"/>
       <c r="E175" s="59"/>
       <c r="F175" s="56">
         <f>+F133</f>
@@ -19652,10 +19652,10 @@
     <row r="176" spans="1:22" ht="15.9" customHeight="1">
       <c r="A176" s="107"/>
       <c r="B176" s="150"/>
-      <c r="C176" s="688" t="s">
+      <c r="C176" s="729" t="s">
         <v>205</v>
       </c>
-      <c r="D176" s="689"/>
+      <c r="D176" s="730"/>
       <c r="E176" s="151"/>
       <c r="F176" s="152">
         <f>SUM(F175)</f>
@@ -19678,8 +19678,8 @@
     <row r="177" spans="1:19" ht="15.9" customHeight="1">
       <c r="A177" s="107"/>
       <c r="B177" s="99"/>
-      <c r="C177" s="681"/>
-      <c r="D177" s="682"/>
+      <c r="C177" s="670"/>
+      <c r="D177" s="671"/>
       <c r="E177" s="59"/>
       <c r="F177" s="56"/>
       <c r="G177" s="388"/>
@@ -19690,27 +19690,27 @@
     <row r="178" spans="1:19" ht="15.9" customHeight="1">
       <c r="A178" s="107"/>
       <c r="B178" s="150"/>
-      <c r="C178" s="688" t="s">
+      <c r="C178" s="729" t="s">
         <v>206</v>
       </c>
-      <c r="D178" s="689"/>
+      <c r="D178" s="730"/>
       <c r="E178" s="154"/>
       <c r="F178" s="149">
         <f>+F169+F173+F176</f>
-        <v>315.26987588085774</v>
+        <v>315.00158675585772</v>
       </c>
       <c r="G178" s="211">
         <f>+G169+G173+G176</f>
-        <v>4093.3449439815531</v>
+        <v>4090.4570798400528</v>
       </c>
       <c r="H178" s="430"/>
       <c r="I178" s="234">
         <f>+I169+I173+I176</f>
-        <v>3.0019984372582154</v>
+        <v>2.9994437893340105</v>
       </c>
       <c r="J178" s="214">
         <f>+J169+J173+J176</f>
-        <v>38.976813406794442</v>
+        <v>38.949315176538306</v>
       </c>
       <c r="S178" s="422"/>
     </row>
@@ -19728,11 +19728,11 @@
     </row>
     <row r="180" spans="1:19" ht="15.9" customHeight="1">
       <c r="A180" s="107"/>
-      <c r="B180" s="675" t="s">
+      <c r="B180" s="653" t="s">
         <v>207</v>
       </c>
-      <c r="C180" s="676"/>
-      <c r="D180" s="677"/>
+      <c r="C180" s="654"/>
+      <c r="D180" s="669"/>
       <c r="E180" s="379"/>
       <c r="F180" s="379" t="s">
         <v>191</v>
@@ -19751,8 +19751,8 @@
     <row r="181" spans="1:19" ht="15.9" customHeight="1">
       <c r="A181" s="107"/>
       <c r="B181" s="99"/>
-      <c r="C181" s="681"/>
-      <c r="D181" s="682"/>
+      <c r="C181" s="670"/>
+      <c r="D181" s="671"/>
       <c r="E181" s="59"/>
       <c r="F181" s="56"/>
       <c r="G181" s="388"/>
@@ -19763,30 +19763,30 @@
     <row r="182" spans="1:19" ht="15.9" customHeight="1">
       <c r="A182" s="107"/>
       <c r="B182" s="99"/>
-      <c r="C182" s="672" t="s">
+      <c r="C182" s="655" t="s">
         <v>208</v>
       </c>
-      <c r="D182" s="671"/>
+      <c r="D182" s="656"/>
       <c r="E182" s="100"/>
       <c r="F182" s="101"/>
       <c r="G182" s="209">
         <f>+G169*G21</f>
-        <v>2999792.8690063623</v>
+        <v>2997240.0979819871</v>
       </c>
       <c r="H182" s="418"/>
       <c r="I182" s="143"/>
       <c r="J182" s="102">
         <f>+G182/$J$5</f>
-        <v>28564.015130511925</v>
+        <v>28539.707655513113</v>
       </c>
     </row>
     <row r="183" spans="1:19" ht="15.9" customHeight="1">
       <c r="A183" s="107"/>
       <c r="B183" s="99"/>
-      <c r="C183" s="670" t="s">
+      <c r="C183" s="649" t="s">
         <v>209</v>
       </c>
-      <c r="D183" s="671"/>
+      <c r="D183" s="656"/>
       <c r="E183" s="100"/>
       <c r="F183" s="101"/>
       <c r="G183" s="209">
@@ -19803,10 +19803,10 @@
     <row r="184" spans="1:19" ht="15.9" customHeight="1">
       <c r="A184" s="107"/>
       <c r="B184" s="99"/>
-      <c r="C184" s="670" t="s">
+      <c r="C184" s="649" t="s">
         <v>210</v>
       </c>
-      <c r="D184" s="680"/>
+      <c r="D184" s="650"/>
       <c r="E184" s="100"/>
       <c r="F184" s="101"/>
       <c r="G184" s="209">
@@ -19820,41 +19820,41 @@
     <row r="185" spans="1:19" ht="15.9" customHeight="1">
       <c r="A185" s="107"/>
       <c r="B185" s="99"/>
-      <c r="C185" s="670" t="s">
+      <c r="C185" s="649" t="s">
         <v>211</v>
       </c>
-      <c r="D185" s="671"/>
+      <c r="D185" s="656"/>
       <c r="E185" s="100"/>
       <c r="F185" s="101"/>
       <c r="G185" s="209">
         <f>SUM(G182:G184)</f>
-        <v>3618373.9448146122</v>
+        <v>3615821.1737902369</v>
       </c>
       <c r="H185" s="418"/>
       <c r="I185" s="143"/>
       <c r="J185" s="102">
         <f>SUM(J182:J184)</f>
-        <v>34454.141542702462</v>
+        <v>34429.834067703647</v>
       </c>
     </row>
     <row r="186" spans="1:19" ht="15.9" customHeight="1">
       <c r="A186" s="107"/>
       <c r="B186" s="99"/>
-      <c r="C186" s="670" t="s">
+      <c r="C186" s="649" t="s">
         <v>212</v>
       </c>
-      <c r="D186" s="671"/>
+      <c r="D186" s="656"/>
       <c r="E186" s="100"/>
       <c r="F186" s="101"/>
       <c r="G186" s="209">
         <f>+G185*12</f>
-        <v>43420487.33777535</v>
+        <v>43389854.085482843</v>
       </c>
       <c r="H186" s="418"/>
       <c r="I186" s="143"/>
       <c r="J186" s="102">
         <f>+J185*12</f>
-        <v>413449.69851242955</v>
+        <v>413158.00881244376</v>
       </c>
     </row>
     <row r="187" spans="1:19" ht="15.9" customHeight="1" thickBot="1">
@@ -19871,25 +19871,25 @@
     </row>
     <row r="188" spans="1:19" ht="15.9" customHeight="1" thickBot="1">
       <c r="A188" s="107"/>
-      <c r="B188" s="705" t="s">
+      <c r="B188" s="726" t="s">
         <v>213</v>
       </c>
-      <c r="C188" s="706"/>
-      <c r="D188" s="706"/>
-      <c r="E188" s="706"/>
-      <c r="F188" s="706"/>
-      <c r="G188" s="706"/>
-      <c r="H188" s="706"/>
-      <c r="I188" s="706"/>
-      <c r="J188" s="707"/>
+      <c r="C188" s="727"/>
+      <c r="D188" s="727"/>
+      <c r="E188" s="727"/>
+      <c r="F188" s="727"/>
+      <c r="G188" s="727"/>
+      <c r="H188" s="727"/>
+      <c r="I188" s="727"/>
+      <c r="J188" s="728"/>
     </row>
     <row r="189" spans="1:19" ht="15.9" customHeight="1">
       <c r="A189" s="51"/>
       <c r="B189" s="164"/>
-      <c r="C189" s="685" t="s">
+      <c r="C189" s="668" t="s">
         <v>214</v>
       </c>
-      <c r="D189" s="685"/>
+      <c r="D189" s="668"/>
       <c r="E189" s="378"/>
       <c r="F189" s="378" t="s">
         <v>191</v>
@@ -19897,7 +19897,7 @@
       <c r="G189" s="168" t="s">
         <v>191</v>
       </c>
-      <c r="H189" s="702"/>
+      <c r="H189" s="723"/>
       <c r="I189" s="229" t="s">
         <v>67</v>
       </c>
@@ -19908,17 +19908,17 @@
     <row r="190" spans="1:19" ht="15.9" customHeight="1">
       <c r="A190" s="51"/>
       <c r="B190" s="162"/>
-      <c r="C190" s="672" t="s">
+      <c r="C190" s="655" t="s">
         <v>215</v>
       </c>
-      <c r="D190" s="671"/>
+      <c r="D190" s="656"/>
       <c r="E190" s="163"/>
       <c r="F190" s="163"/>
       <c r="G190" s="102">
         <f>+G20</f>
         <v>0</v>
       </c>
-      <c r="H190" s="703"/>
+      <c r="H190" s="724"/>
       <c r="I190" s="162"/>
       <c r="J190" s="102">
         <f>+G190/J5</f>
@@ -19928,17 +19928,17 @@
     <row r="191" spans="1:19" ht="15.9" customHeight="1">
       <c r="A191" s="51"/>
       <c r="B191" s="162"/>
-      <c r="C191" s="672" t="s">
+      <c r="C191" s="655" t="s">
         <v>216</v>
       </c>
-      <c r="D191" s="671"/>
+      <c r="D191" s="656"/>
       <c r="E191" s="163"/>
       <c r="F191" s="163"/>
       <c r="G191" s="102">
         <f>+G190*G23</f>
         <v>0</v>
       </c>
-      <c r="H191" s="703"/>
+      <c r="H191" s="724"/>
       <c r="I191" s="162"/>
       <c r="J191" s="102">
         <f>+J190*J23</f>
@@ -19948,17 +19948,17 @@
     <row r="192" spans="1:19" ht="15.9" customHeight="1">
       <c r="A192" s="51"/>
       <c r="B192" s="162"/>
-      <c r="C192" s="686" t="s">
+      <c r="C192" s="693" t="s">
         <v>217</v>
       </c>
-      <c r="D192" s="686"/>
+      <c r="D192" s="693"/>
       <c r="E192" s="163"/>
       <c r="F192" s="163"/>
       <c r="G192" s="102">
         <f>+G191*25%</f>
         <v>0</v>
       </c>
-      <c r="H192" s="703"/>
+      <c r="H192" s="724"/>
       <c r="I192" s="162"/>
       <c r="J192" s="102">
         <f>+J191*25%</f>
@@ -19968,17 +19968,17 @@
     <row r="193" spans="1:20" ht="15.9" customHeight="1">
       <c r="A193" s="51"/>
       <c r="B193" s="162"/>
-      <c r="C193" s="670" t="s">
+      <c r="C193" s="649" t="s">
         <v>218</v>
       </c>
-      <c r="D193" s="671"/>
+      <c r="D193" s="656"/>
       <c r="E193" s="163"/>
       <c r="F193" s="163"/>
       <c r="G193" s="102">
         <f>+G192*1%</f>
         <v>0</v>
       </c>
-      <c r="H193" s="703"/>
+      <c r="H193" s="724"/>
       <c r="I193" s="162"/>
       <c r="J193" s="102">
         <f>G193/J5</f>
@@ -19988,17 +19988,17 @@
     <row r="194" spans="1:20" ht="15.9" customHeight="1">
       <c r="A194" s="51"/>
       <c r="B194" s="162"/>
-      <c r="C194" s="670" t="s">
+      <c r="C194" s="649" t="s">
         <v>219</v>
       </c>
-      <c r="D194" s="671"/>
+      <c r="D194" s="656"/>
       <c r="E194" s="163"/>
       <c r="F194" s="163"/>
       <c r="G194" s="102">
         <f>G193*0.5</f>
         <v>0</v>
       </c>
-      <c r="H194" s="703"/>
+      <c r="H194" s="724"/>
       <c r="I194" s="162"/>
       <c r="J194" s="102">
         <f>G194/J5</f>
@@ -20008,17 +20008,17 @@
     <row r="195" spans="1:20" ht="15.9" customHeight="1" thickBot="1">
       <c r="A195" s="51"/>
       <c r="B195" s="162"/>
-      <c r="C195" s="686" t="s">
+      <c r="C195" s="693" t="s">
         <v>220</v>
       </c>
-      <c r="D195" s="686"/>
+      <c r="D195" s="693"/>
       <c r="E195" s="163"/>
       <c r="F195" s="163"/>
       <c r="G195" s="110">
         <f>G83</f>
-        <v>512254.33034775488</v>
-      </c>
-      <c r="H195" s="703"/>
+        <v>511749.08384775487</v>
+      </c>
+      <c r="H195" s="724"/>
       <c r="I195" s="162"/>
       <c r="J195" s="110">
         <f>+J193+J194</f>
@@ -20028,8 +20028,8 @@
     <row r="196" spans="1:20" ht="15.9" customHeight="1">
       <c r="A196" s="166"/>
       <c r="B196" s="382"/>
-      <c r="C196" s="687"/>
-      <c r="D196" s="687"/>
+      <c r="C196" s="661"/>
+      <c r="D196" s="661"/>
       <c r="E196" s="379"/>
       <c r="F196" s="379" t="s">
         <v>191</v>
@@ -20037,7 +20037,7 @@
       <c r="G196" s="53" t="s">
         <v>191</v>
       </c>
-      <c r="H196" s="703"/>
+      <c r="H196" s="724"/>
       <c r="I196" s="229" t="s">
         <v>67</v>
       </c>
@@ -20048,17 +20048,17 @@
     <row r="197" spans="1:20" ht="15.9" customHeight="1">
       <c r="A197" s="74"/>
       <c r="B197" s="99"/>
-      <c r="C197" s="672" t="s">
+      <c r="C197" s="655" t="s">
         <v>221</v>
       </c>
-      <c r="D197" s="671"/>
+      <c r="D197" s="656"/>
       <c r="E197" s="58"/>
       <c r="F197" s="50"/>
       <c r="G197" s="102">
         <f>+G55</f>
         <v>72</v>
       </c>
-      <c r="H197" s="703"/>
+      <c r="H197" s="724"/>
       <c r="I197" s="91"/>
       <c r="J197" s="102">
         <f>+J55</f>
@@ -20068,17 +20068,17 @@
     <row r="198" spans="1:20" ht="15.9" customHeight="1">
       <c r="A198" s="74"/>
       <c r="B198" s="99"/>
-      <c r="C198" s="672" t="s">
+      <c r="C198" s="655" t="s">
         <v>222</v>
       </c>
-      <c r="D198" s="671"/>
+      <c r="D198" s="656"/>
       <c r="E198" s="58"/>
       <c r="F198" s="50"/>
       <c r="G198" s="102">
         <f>F141</f>
         <v>9515</v>
       </c>
-      <c r="H198" s="703"/>
+      <c r="H198" s="724"/>
       <c r="I198" s="91"/>
       <c r="J198" s="102">
         <f>I141</f>
@@ -20088,77 +20088,77 @@
     <row r="199" spans="1:20" ht="15.9" customHeight="1">
       <c r="A199" s="120"/>
       <c r="B199" s="99"/>
-      <c r="C199" s="672" t="s">
+      <c r="C199" s="655" t="s">
         <v>223</v>
       </c>
-      <c r="D199" s="671"/>
+      <c r="D199" s="656"/>
       <c r="E199" s="58"/>
       <c r="F199" s="50"/>
       <c r="G199" s="111">
         <f>+F61</f>
-        <v>129.25</v>
-      </c>
-      <c r="H199" s="703"/>
+        <v>129</v>
+      </c>
+      <c r="H199" s="724"/>
       <c r="I199" s="91"/>
       <c r="J199" s="111">
         <f>+I61</f>
-        <v>1.2307179584840984</v>
+        <v>1.228337459531518</v>
       </c>
     </row>
     <row r="200" spans="1:20" ht="15.9" customHeight="1">
       <c r="A200" s="74"/>
       <c r="B200" s="99"/>
-      <c r="C200" s="672" t="s">
+      <c r="C200" s="655" t="s">
         <v>223</v>
       </c>
-      <c r="D200" s="671"/>
+      <c r="D200" s="656"/>
       <c r="E200" s="58"/>
       <c r="F200" s="50"/>
       <c r="G200" s="102">
         <f>(G198*G199*G197)</f>
-        <v>88546590</v>
-      </c>
-      <c r="H200" s="703"/>
+        <v>88375320</v>
+      </c>
+      <c r="H200" s="724"/>
       <c r="I200" s="91"/>
       <c r="J200" s="102">
         <f>+G200/$J$5</f>
-        <v>843140.2589982861</v>
+        <v>841509.42677585222</v>
       </c>
     </row>
     <row r="201" spans="1:20" ht="15.9" customHeight="1">
       <c r="A201" s="74"/>
       <c r="B201" s="99"/>
-      <c r="C201" s="672" t="s">
+      <c r="C201" s="655" t="s">
         <v>224</v>
       </c>
-      <c r="D201" s="671"/>
+      <c r="D201" s="656"/>
       <c r="E201" s="58"/>
       <c r="F201" s="50"/>
       <c r="G201" s="102">
         <f>G200/G197*12</f>
-        <v>14757765</v>
-      </c>
-      <c r="H201" s="703"/>
+        <v>14729220</v>
+      </c>
+      <c r="H201" s="724"/>
       <c r="I201" s="91"/>
       <c r="J201" s="102">
         <f>+G201/$J$5</f>
-        <v>140523.37649971436</v>
+        <v>140251.57112930872</v>
       </c>
     </row>
     <row r="202" spans="1:20" ht="15.9" customHeight="1">
       <c r="A202" s="74"/>
       <c r="B202" s="99"/>
-      <c r="C202" s="672" t="s">
+      <c r="C202" s="655" t="s">
         <v>225</v>
       </c>
-      <c r="D202" s="671"/>
+      <c r="D202" s="656"/>
       <c r="E202" s="58"/>
       <c r="F202" s="50"/>
       <c r="G202" s="102">
         <f>(+G221*115%)/5</f>
         <v>0</v>
       </c>
-      <c r="H202" s="703"/>
+      <c r="H202" s="724"/>
       <c r="I202" s="91"/>
       <c r="J202" s="102">
         <f>+G202/$J$5</f>
@@ -20168,17 +20168,17 @@
     <row r="203" spans="1:20" ht="15.9" customHeight="1">
       <c r="A203" s="74"/>
       <c r="B203" s="99"/>
-      <c r="C203" s="672" t="s">
+      <c r="C203" s="655" t="s">
         <v>226</v>
       </c>
-      <c r="D203" s="671"/>
+      <c r="D203" s="656"/>
       <c r="E203" s="58"/>
       <c r="F203" s="50"/>
       <c r="G203" s="102">
         <f>(+I221*115%)/5</f>
         <v>2765157.6185172233</v>
       </c>
-      <c r="H203" s="703"/>
+      <c r="H203" s="724"/>
       <c r="I203" s="91"/>
       <c r="J203" s="102">
         <f>+G203/$J$5</f>
@@ -20188,17 +20188,17 @@
     <row r="204" spans="1:20" ht="15.9" customHeight="1">
       <c r="A204" s="74"/>
       <c r="B204" s="99"/>
-      <c r="C204" s="672" t="s">
+      <c r="C204" s="655" t="s">
         <v>36</v>
       </c>
-      <c r="D204" s="671"/>
+      <c r="D204" s="656"/>
       <c r="E204" s="58"/>
       <c r="F204" s="50"/>
       <c r="G204" s="102">
         <f>+G68</f>
         <v>11418000</v>
       </c>
-      <c r="H204" s="703"/>
+      <c r="H204" s="724"/>
       <c r="I204" s="91"/>
       <c r="J204" s="102">
         <f>+G204/$J$5</f>
@@ -20208,77 +20208,77 @@
     <row r="205" spans="1:20" ht="15.9" customHeight="1">
       <c r="A205" s="74"/>
       <c r="B205" s="99"/>
-      <c r="C205" s="670" t="s">
+      <c r="C205" s="649" t="s">
         <v>227</v>
       </c>
-      <c r="D205" s="671"/>
+      <c r="D205" s="656"/>
       <c r="E205" s="58"/>
       <c r="F205" s="50"/>
       <c r="G205" s="102">
         <f>(G201+G202+G203+G204)*1.18</f>
-        <v>34150288.689850323</v>
-      </c>
-      <c r="H205" s="703"/>
+        <v>34116605.589850321</v>
+      </c>
+      <c r="H205" s="724"/>
       <c r="I205" s="91"/>
       <c r="J205" s="102">
         <f>+J201+J202+J203+J204</f>
-        <v>275575.34392036969</v>
+        <v>275303.53854996408</v>
       </c>
     </row>
     <row r="206" spans="1:20" ht="15.9" customHeight="1">
       <c r="A206" s="74"/>
       <c r="B206" s="99"/>
-      <c r="C206" s="670" t="s">
+      <c r="C206" s="649" t="s">
         <v>228</v>
       </c>
-      <c r="D206" s="671"/>
+      <c r="D206" s="656"/>
       <c r="E206" s="58"/>
       <c r="F206" s="50"/>
       <c r="G206" s="102">
         <f>G205*1%</f>
-        <v>341502.88689850323</v>
-      </c>
-      <c r="H206" s="703"/>
+        <v>341166.05589850323</v>
+      </c>
+      <c r="H206" s="724"/>
       <c r="I206" s="91"/>
       <c r="J206" s="102">
         <f>J205*1%</f>
-        <v>2755.7534392036969</v>
+        <v>2753.0353854996411</v>
       </c>
     </row>
     <row r="207" spans="1:20" ht="15.9" customHeight="1">
       <c r="A207" s="74"/>
       <c r="B207" s="99"/>
-      <c r="C207" s="672" t="s">
+      <c r="C207" s="655" t="s">
         <v>229</v>
       </c>
-      <c r="D207" s="671"/>
+      <c r="D207" s="656"/>
       <c r="E207" s="58"/>
       <c r="F207" s="50"/>
       <c r="G207" s="102">
         <f>G205*0.5%</f>
-        <v>170751.44344925162</v>
-      </c>
-      <c r="H207" s="703"/>
+        <v>170583.02794925161</v>
+      </c>
+      <c r="H207" s="724"/>
       <c r="I207" s="91"/>
       <c r="J207" s="102">
         <f>J205*0.5%</f>
-        <v>1377.8767196018484</v>
+        <v>1376.5176927498205</v>
       </c>
     </row>
     <row r="208" spans="1:20" ht="15.9" customHeight="1">
       <c r="A208" s="74"/>
       <c r="B208" s="99"/>
-      <c r="C208" s="673" t="s">
+      <c r="C208" s="651" t="s">
         <v>220</v>
       </c>
-      <c r="D208" s="674"/>
+      <c r="D208" s="652"/>
       <c r="E208" s="58"/>
       <c r="F208" s="50"/>
       <c r="G208" s="102">
         <f>G206+G207</f>
-        <v>512254.33034775488</v>
-      </c>
-      <c r="H208" s="703"/>
+        <v>511749.08384775487</v>
+      </c>
+      <c r="H208" s="724"/>
       <c r="I208" s="91"/>
       <c r="J208" s="102">
         <v>0</v>
@@ -20293,7 +20293,7 @@
       <c r="E209" s="80"/>
       <c r="F209" s="51"/>
       <c r="G209" s="337"/>
-      <c r="H209" s="703"/>
+      <c r="H209" s="724"/>
       <c r="I209" s="94"/>
       <c r="J209" s="81"/>
     </row>
@@ -20315,7 +20315,7 @@
       <c r="G210" s="161" t="s">
         <v>234</v>
       </c>
-      <c r="H210" s="703"/>
+      <c r="H210" s="724"/>
       <c r="I210" s="379" t="s">
         <v>235</v>
       </c>
@@ -20340,7 +20340,7 @@
       <c r="G211" s="101">
         <v>0</v>
       </c>
-      <c r="H211" s="703"/>
+      <c r="H211" s="724"/>
       <c r="I211" s="101">
         <f>'Lease Rent'!O39</f>
         <v>1178337.5999999999</v>
@@ -20369,7 +20369,7 @@
       <c r="G212" s="101">
         <v>0</v>
       </c>
-      <c r="H212" s="703"/>
+      <c r="H212" s="724"/>
       <c r="I212" s="101">
         <f>'Lease Rent'!O51</f>
         <v>1826423.2800000005</v>
@@ -20397,7 +20397,7 @@
       <c r="G213" s="101">
         <v>0</v>
       </c>
-      <c r="H213" s="703"/>
+      <c r="H213" s="724"/>
       <c r="I213" s="101">
         <f>'Lease Rent'!O63</f>
         <v>1917744.4440000001</v>
@@ -20414,7 +20414,7 @@
       </c>
       <c r="C214" s="101">
         <f>'Lease Rent'!N75</f>
-        <v>15243030</v>
+        <v>15071760</v>
       </c>
       <c r="D214" s="281"/>
       <c r="E214" s="58"/>
@@ -20425,7 +20425,7 @@
       <c r="G214" s="101">
         <v>0</v>
       </c>
-      <c r="H214" s="703"/>
+      <c r="H214" s="724"/>
       <c r="I214" s="101">
         <f>'Lease Rent'!O75</f>
         <v>2013631.6662000006</v>
@@ -20453,7 +20453,7 @@
       <c r="G215" s="101">
         <v>0</v>
       </c>
-      <c r="H215" s="703"/>
+      <c r="H215" s="724"/>
       <c r="I215" s="101">
         <f>'Lease Rent'!O87</f>
         <v>2114313.2495100005</v>
@@ -20479,7 +20479,7 @@
         <v>0</v>
       </c>
       <c r="G216" s="113"/>
-      <c r="H216" s="703"/>
+      <c r="H216" s="724"/>
       <c r="I216" s="101">
         <f>'Lease Rent'!O99</f>
         <v>2220028.9119855007</v>
@@ -20507,7 +20507,7 @@
         <f>'Lease Rent'!R9</f>
         <v>0</v>
       </c>
-      <c r="H217" s="703"/>
+      <c r="H217" s="724"/>
       <c r="I217" s="101">
         <f>'Lease Rent'!O103</f>
         <v>751945.27664025011</v>
@@ -20530,7 +20530,7 @@
         <f>'Lease Rent'!R10</f>
         <v>0</v>
       </c>
-      <c r="H218" s="703"/>
+      <c r="H218" s="724"/>
       <c r="I218" s="301"/>
       <c r="J218" s="111"/>
     </row>
@@ -20547,7 +20547,7 @@
         <v>0</v>
       </c>
       <c r="G219" s="118"/>
-      <c r="H219" s="703"/>
+      <c r="H219" s="724"/>
       <c r="I219" s="101"/>
       <c r="J219" s="111"/>
     </row>
@@ -20561,7 +20561,7 @@
       <c r="E220" s="117"/>
       <c r="F220" s="232"/>
       <c r="G220" s="118"/>
-      <c r="H220" s="703"/>
+      <c r="H220" s="724"/>
       <c r="I220" s="101"/>
       <c r="J220" s="111"/>
     </row>
@@ -20572,7 +20572,7 @@
       </c>
       <c r="C221" s="283">
         <f>SUM(C211:C220)</f>
-        <v>88546590</v>
+        <v>88375320</v>
       </c>
       <c r="D221" s="283"/>
       <c r="E221" s="52"/>
@@ -20584,7 +20584,7 @@
         <f>SUM(G211:G220)</f>
         <v>0</v>
       </c>
-      <c r="H221" s="704"/>
+      <c r="H221" s="725"/>
       <c r="I221" s="283">
         <f>SUM(I211:I220)</f>
         <v>12022424.428335754</v>
@@ -20654,35 +20654,191 @@
     </row>
   </sheetData>
   <mergeCells count="238">
-    <mergeCell ref="F138:G138"/>
-    <mergeCell ref="I138:J138"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="B110:D110"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="B135:D135"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C120:D120"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="C125:D125"/>
-    <mergeCell ref="C118:D118"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C205:D205"/>
+    <mergeCell ref="C204:D204"/>
+    <mergeCell ref="C162:D162"/>
+    <mergeCell ref="B139:D139"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="C193:D193"/>
+    <mergeCell ref="C194:D194"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="C190:D190"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C161:D161"/>
+    <mergeCell ref="C191:D191"/>
+    <mergeCell ref="B180:D180"/>
+    <mergeCell ref="C163:D163"/>
+    <mergeCell ref="C166:D166"/>
+    <mergeCell ref="C206:D206"/>
+    <mergeCell ref="C207:D207"/>
+    <mergeCell ref="C208:D208"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C175:D175"/>
+    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="C143:D143"/>
+    <mergeCell ref="C200:D200"/>
+    <mergeCell ref="C201:D201"/>
+    <mergeCell ref="C202:D202"/>
+    <mergeCell ref="C203:D203"/>
+    <mergeCell ref="C189:D189"/>
+    <mergeCell ref="C192:D192"/>
+    <mergeCell ref="C195:D195"/>
+    <mergeCell ref="C196:D196"/>
+    <mergeCell ref="C197:D197"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C182:D182"/>
+    <mergeCell ref="C186:D186"/>
+    <mergeCell ref="C169:D169"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="C170:D170"/>
+    <mergeCell ref="C184:D184"/>
+    <mergeCell ref="C171:D171"/>
+    <mergeCell ref="C141:D141"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="C123:D123"/>
+    <mergeCell ref="C172:D172"/>
+    <mergeCell ref="C168:D168"/>
+    <mergeCell ref="B148:D148"/>
+    <mergeCell ref="B164:D165"/>
+    <mergeCell ref="B126:D126"/>
+    <mergeCell ref="C159:D159"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="C156:D156"/>
+    <mergeCell ref="C145:D145"/>
+    <mergeCell ref="C140:D140"/>
+    <mergeCell ref="C167:D167"/>
+    <mergeCell ref="C183:D183"/>
+    <mergeCell ref="H189:H221"/>
+    <mergeCell ref="C160:D160"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B188:J188"/>
+    <mergeCell ref="C173:D173"/>
+    <mergeCell ref="C177:D177"/>
+    <mergeCell ref="C178:D178"/>
+    <mergeCell ref="C181:D181"/>
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="C199:D199"/>
+    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="C150:D150"/>
+    <mergeCell ref="C151:D151"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="B122:D122"/>
+    <mergeCell ref="C144:D144"/>
+    <mergeCell ref="C185:D185"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B1:J3"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C49:D49"/>
     <mergeCell ref="F53:G53"/>
     <mergeCell ref="F49:G49"/>
     <mergeCell ref="F50:G50"/>
@@ -20707,191 +20863,35 @@
     <mergeCell ref="C136:D136"/>
     <mergeCell ref="C137:D137"/>
     <mergeCell ref="C134:D134"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B1:J3"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="H189:H221"/>
-    <mergeCell ref="C160:D160"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B188:J188"/>
-    <mergeCell ref="C173:D173"/>
-    <mergeCell ref="C177:D177"/>
-    <mergeCell ref="C178:D178"/>
-    <mergeCell ref="C181:D181"/>
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="C199:D199"/>
-    <mergeCell ref="C176:D176"/>
-    <mergeCell ref="C150:D150"/>
-    <mergeCell ref="C151:D151"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="I59:J59"/>
-    <mergeCell ref="B122:D122"/>
-    <mergeCell ref="C144:D144"/>
-    <mergeCell ref="C185:D185"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C182:D182"/>
-    <mergeCell ref="C186:D186"/>
-    <mergeCell ref="C169:D169"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="C170:D170"/>
-    <mergeCell ref="C184:D184"/>
-    <mergeCell ref="C171:D171"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="C123:D123"/>
-    <mergeCell ref="C172:D172"/>
-    <mergeCell ref="C168:D168"/>
-    <mergeCell ref="B148:D148"/>
-    <mergeCell ref="B164:D165"/>
-    <mergeCell ref="B126:D126"/>
-    <mergeCell ref="C159:D159"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="C156:D156"/>
-    <mergeCell ref="C145:D145"/>
-    <mergeCell ref="C140:D140"/>
-    <mergeCell ref="C167:D167"/>
-    <mergeCell ref="C183:D183"/>
-    <mergeCell ref="C206:D206"/>
-    <mergeCell ref="C207:D207"/>
-    <mergeCell ref="C208:D208"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C175:D175"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="C143:D143"/>
-    <mergeCell ref="C200:D200"/>
-    <mergeCell ref="C201:D201"/>
-    <mergeCell ref="C202:D202"/>
-    <mergeCell ref="C203:D203"/>
-    <mergeCell ref="C189:D189"/>
-    <mergeCell ref="C192:D192"/>
-    <mergeCell ref="C195:D195"/>
-    <mergeCell ref="C196:D196"/>
-    <mergeCell ref="C197:D197"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C205:D205"/>
-    <mergeCell ref="C204:D204"/>
-    <mergeCell ref="C162:D162"/>
-    <mergeCell ref="B139:D139"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="C121:D121"/>
-    <mergeCell ref="C193:D193"/>
-    <mergeCell ref="C194:D194"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="C190:D190"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="C161:D161"/>
-    <mergeCell ref="C191:D191"/>
-    <mergeCell ref="B180:D180"/>
-    <mergeCell ref="C163:D163"/>
-    <mergeCell ref="C166:D166"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="B135:D135"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C120:D120"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="C125:D125"/>
+    <mergeCell ref="C118:D118"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="F138:G138"/>
+    <mergeCell ref="I138:J138"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="B110:D110"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C108:D108"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.25" top="0.75" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="58" orientation="portrait" r:id="rId1"/>
@@ -20965,215 +20965,215 @@
       <c r="S1" s="1"/>
     </row>
     <row r="2" spans="1:27" ht="11.25" customHeight="1">
-      <c r="A2" s="649"/>
-      <c r="B2" s="650"/>
-      <c r="C2" s="650"/>
-      <c r="D2" s="650"/>
-      <c r="E2" s="650"/>
-      <c r="F2" s="650"/>
-      <c r="G2" s="650"/>
-      <c r="H2" s="650"/>
-      <c r="I2" s="650"/>
-      <c r="J2" s="650"/>
-      <c r="K2" s="650"/>
-      <c r="L2" s="650"/>
-      <c r="M2" s="650"/>
-      <c r="N2" s="650"/>
-      <c r="O2" s="650"/>
-      <c r="P2" s="650"/>
-      <c r="Q2" s="650"/>
-      <c r="R2" s="650"/>
-      <c r="S2" s="650"/>
-      <c r="T2" s="650"/>
-      <c r="U2" s="650"/>
-      <c r="V2" s="650"/>
-      <c r="W2" s="650"/>
-      <c r="X2" s="650"/>
-      <c r="Y2" s="650"/>
-      <c r="Z2" s="650"/>
-      <c r="AA2" s="651"/>
+      <c r="A2" s="709"/>
+      <c r="B2" s="710"/>
+      <c r="C2" s="710"/>
+      <c r="D2" s="710"/>
+      <c r="E2" s="710"/>
+      <c r="F2" s="710"/>
+      <c r="G2" s="710"/>
+      <c r="H2" s="710"/>
+      <c r="I2" s="710"/>
+      <c r="J2" s="710"/>
+      <c r="K2" s="710"/>
+      <c r="L2" s="710"/>
+      <c r="M2" s="710"/>
+      <c r="N2" s="710"/>
+      <c r="O2" s="710"/>
+      <c r="P2" s="710"/>
+      <c r="Q2" s="710"/>
+      <c r="R2" s="710"/>
+      <c r="S2" s="710"/>
+      <c r="T2" s="710"/>
+      <c r="U2" s="710"/>
+      <c r="V2" s="710"/>
+      <c r="W2" s="710"/>
+      <c r="X2" s="710"/>
+      <c r="Y2" s="710"/>
+      <c r="Z2" s="710"/>
+      <c r="AA2" s="747"/>
     </row>
     <row r="3" spans="1:27" ht="11.25" customHeight="1">
-      <c r="A3" s="652"/>
-      <c r="B3" s="653"/>
-      <c r="C3" s="653"/>
-      <c r="D3" s="653"/>
-      <c r="E3" s="653"/>
-      <c r="F3" s="653"/>
-      <c r="G3" s="653"/>
-      <c r="H3" s="653"/>
-      <c r="I3" s="653"/>
-      <c r="J3" s="653"/>
-      <c r="K3" s="653"/>
-      <c r="L3" s="653"/>
-      <c r="M3" s="653"/>
-      <c r="N3" s="653"/>
-      <c r="O3" s="653"/>
-      <c r="P3" s="653"/>
-      <c r="Q3" s="653"/>
-      <c r="R3" s="653"/>
-      <c r="S3" s="653"/>
-      <c r="T3" s="653"/>
-      <c r="U3" s="653"/>
-      <c r="V3" s="653"/>
-      <c r="W3" s="653"/>
-      <c r="X3" s="653"/>
-      <c r="Y3" s="653"/>
-      <c r="Z3" s="653"/>
-      <c r="AA3" s="654"/>
+      <c r="A3" s="748"/>
+      <c r="B3" s="749"/>
+      <c r="C3" s="749"/>
+      <c r="D3" s="749"/>
+      <c r="E3" s="749"/>
+      <c r="F3" s="749"/>
+      <c r="G3" s="749"/>
+      <c r="H3" s="749"/>
+      <c r="I3" s="749"/>
+      <c r="J3" s="749"/>
+      <c r="K3" s="749"/>
+      <c r="L3" s="749"/>
+      <c r="M3" s="749"/>
+      <c r="N3" s="749"/>
+      <c r="O3" s="749"/>
+      <c r="P3" s="749"/>
+      <c r="Q3" s="749"/>
+      <c r="R3" s="749"/>
+      <c r="S3" s="749"/>
+      <c r="T3" s="749"/>
+      <c r="U3" s="749"/>
+      <c r="V3" s="749"/>
+      <c r="W3" s="749"/>
+      <c r="X3" s="749"/>
+      <c r="Y3" s="749"/>
+      <c r="Z3" s="749"/>
+      <c r="AA3" s="750"/>
     </row>
     <row r="4" spans="1:27" ht="12" customHeight="1" thickBot="1">
-      <c r="A4" s="655"/>
-      <c r="B4" s="656"/>
-      <c r="C4" s="656"/>
-      <c r="D4" s="656"/>
-      <c r="E4" s="656"/>
-      <c r="F4" s="656"/>
-      <c r="G4" s="656"/>
-      <c r="H4" s="656"/>
-      <c r="I4" s="656"/>
-      <c r="J4" s="656"/>
-      <c r="K4" s="656"/>
-      <c r="L4" s="656"/>
-      <c r="M4" s="656"/>
-      <c r="N4" s="656"/>
-      <c r="O4" s="656"/>
-      <c r="P4" s="656"/>
-      <c r="Q4" s="656"/>
-      <c r="R4" s="656"/>
-      <c r="S4" s="656"/>
-      <c r="T4" s="656"/>
-      <c r="U4" s="656"/>
-      <c r="V4" s="656"/>
-      <c r="W4" s="656"/>
-      <c r="X4" s="656"/>
-      <c r="Y4" s="656"/>
-      <c r="Z4" s="656"/>
-      <c r="AA4" s="657"/>
+      <c r="A4" s="751"/>
+      <c r="B4" s="752"/>
+      <c r="C4" s="752"/>
+      <c r="D4" s="752"/>
+      <c r="E4" s="752"/>
+      <c r="F4" s="752"/>
+      <c r="G4" s="752"/>
+      <c r="H4" s="752"/>
+      <c r="I4" s="752"/>
+      <c r="J4" s="752"/>
+      <c r="K4" s="752"/>
+      <c r="L4" s="752"/>
+      <c r="M4" s="752"/>
+      <c r="N4" s="752"/>
+      <c r="O4" s="752"/>
+      <c r="P4" s="752"/>
+      <c r="Q4" s="752"/>
+      <c r="R4" s="752"/>
+      <c r="S4" s="752"/>
+      <c r="T4" s="752"/>
+      <c r="U4" s="752"/>
+      <c r="V4" s="752"/>
+      <c r="W4" s="752"/>
+      <c r="X4" s="752"/>
+      <c r="Y4" s="752"/>
+      <c r="Z4" s="752"/>
+      <c r="AA4" s="753"/>
     </row>
     <row r="5" spans="1:27" ht="12.75" customHeight="1">
-      <c r="A5" s="649" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="650"/>
-      <c r="C5" s="650"/>
-      <c r="D5" s="650"/>
-      <c r="E5" s="650"/>
-      <c r="F5" s="650"/>
-      <c r="G5" s="650"/>
-      <c r="H5" s="650"/>
-      <c r="I5" s="650"/>
-      <c r="J5" s="650"/>
-      <c r="K5" s="650"/>
-      <c r="L5" s="650"/>
-      <c r="M5" s="650"/>
-      <c r="N5" s="650"/>
-      <c r="O5" s="650"/>
-      <c r="P5" s="650"/>
-      <c r="Q5" s="650"/>
-      <c r="R5" s="650"/>
-      <c r="S5" s="650"/>
-      <c r="T5" s="650"/>
-      <c r="U5" s="650"/>
-      <c r="V5" s="650"/>
-      <c r="W5" s="650"/>
-      <c r="X5" s="650"/>
-      <c r="Y5" s="650"/>
-      <c r="Z5" s="650"/>
-      <c r="AA5" s="651"/>
+      <c r="A5" s="709" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="710"/>
+      <c r="C5" s="710"/>
+      <c r="D5" s="710"/>
+      <c r="E5" s="710"/>
+      <c r="F5" s="710"/>
+      <c r="G5" s="710"/>
+      <c r="H5" s="710"/>
+      <c r="I5" s="710"/>
+      <c r="J5" s="710"/>
+      <c r="K5" s="710"/>
+      <c r="L5" s="710"/>
+      <c r="M5" s="710"/>
+      <c r="N5" s="710"/>
+      <c r="O5" s="710"/>
+      <c r="P5" s="710"/>
+      <c r="Q5" s="710"/>
+      <c r="R5" s="710"/>
+      <c r="S5" s="710"/>
+      <c r="T5" s="710"/>
+      <c r="U5" s="710"/>
+      <c r="V5" s="710"/>
+      <c r="W5" s="710"/>
+      <c r="X5" s="710"/>
+      <c r="Y5" s="710"/>
+      <c r="Z5" s="710"/>
+      <c r="AA5" s="747"/>
     </row>
     <row r="6" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A6" s="658"/>
-      <c r="B6" s="659"/>
-      <c r="C6" s="659"/>
-      <c r="D6" s="659"/>
-      <c r="E6" s="659"/>
-      <c r="F6" s="659"/>
-      <c r="G6" s="659"/>
-      <c r="H6" s="659"/>
-      <c r="I6" s="659"/>
-      <c r="J6" s="659"/>
-      <c r="K6" s="659"/>
-      <c r="L6" s="659"/>
-      <c r="M6" s="659"/>
-      <c r="N6" s="659"/>
-      <c r="O6" s="659"/>
-      <c r="P6" s="659"/>
-      <c r="Q6" s="659"/>
-      <c r="R6" s="659"/>
-      <c r="S6" s="659"/>
-      <c r="T6" s="659"/>
-      <c r="U6" s="659"/>
-      <c r="V6" s="659"/>
-      <c r="W6" s="659"/>
-      <c r="X6" s="659"/>
-      <c r="Y6" s="659"/>
-      <c r="Z6" s="659"/>
-      <c r="AA6" s="660"/>
+      <c r="A6" s="754"/>
+      <c r="B6" s="755"/>
+      <c r="C6" s="755"/>
+      <c r="D6" s="755"/>
+      <c r="E6" s="755"/>
+      <c r="F6" s="755"/>
+      <c r="G6" s="755"/>
+      <c r="H6" s="755"/>
+      <c r="I6" s="755"/>
+      <c r="J6" s="755"/>
+      <c r="K6" s="755"/>
+      <c r="L6" s="755"/>
+      <c r="M6" s="755"/>
+      <c r="N6" s="755"/>
+      <c r="O6" s="755"/>
+      <c r="P6" s="755"/>
+      <c r="Q6" s="755"/>
+      <c r="R6" s="755"/>
+      <c r="S6" s="755"/>
+      <c r="T6" s="755"/>
+      <c r="U6" s="755"/>
+      <c r="V6" s="755"/>
+      <c r="W6" s="755"/>
+      <c r="X6" s="755"/>
+      <c r="Y6" s="755"/>
+      <c r="Z6" s="755"/>
+      <c r="AA6" s="756"/>
     </row>
     <row r="7" spans="1:27" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A7" s="661" t="s">
+      <c r="A7" s="757" t="s">
         <v>339</v>
       </c>
-      <c r="B7" s="662"/>
-      <c r="C7" s="662"/>
-      <c r="D7" s="662"/>
-      <c r="E7" s="662"/>
-      <c r="F7" s="662"/>
-      <c r="G7" s="662"/>
-      <c r="H7" s="662"/>
-      <c r="I7" s="662"/>
-      <c r="J7" s="662"/>
-      <c r="K7" s="662"/>
-      <c r="L7" s="662"/>
-      <c r="M7" s="662"/>
-      <c r="N7" s="662"/>
-      <c r="O7" s="662"/>
-      <c r="P7" s="663"/>
-      <c r="Q7" s="663"/>
-      <c r="R7" s="663"/>
-      <c r="S7" s="663"/>
-      <c r="T7" s="663"/>
-      <c r="U7" s="663"/>
-      <c r="V7" s="663"/>
-      <c r="W7" s="663"/>
-      <c r="X7" s="663"/>
-      <c r="Y7" s="663"/>
-      <c r="Z7" s="663"/>
-      <c r="AA7" s="664"/>
+      <c r="B7" s="758"/>
+      <c r="C7" s="758"/>
+      <c r="D7" s="758"/>
+      <c r="E7" s="758"/>
+      <c r="F7" s="758"/>
+      <c r="G7" s="758"/>
+      <c r="H7" s="758"/>
+      <c r="I7" s="758"/>
+      <c r="J7" s="758"/>
+      <c r="K7" s="758"/>
+      <c r="L7" s="758"/>
+      <c r="M7" s="758"/>
+      <c r="N7" s="758"/>
+      <c r="O7" s="758"/>
+      <c r="P7" s="759"/>
+      <c r="Q7" s="759"/>
+      <c r="R7" s="759"/>
+      <c r="S7" s="759"/>
+      <c r="T7" s="759"/>
+      <c r="U7" s="759"/>
+      <c r="V7" s="759"/>
+      <c r="W7" s="759"/>
+      <c r="X7" s="759"/>
+      <c r="Y7" s="759"/>
+      <c r="Z7" s="759"/>
+      <c r="AA7" s="760"/>
     </row>
     <row r="8" spans="1:27" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A8" s="665" t="s">
+      <c r="A8" s="761" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="666"/>
-      <c r="C8" s="666"/>
-      <c r="D8" s="666"/>
-      <c r="E8" s="666"/>
-      <c r="F8" s="666"/>
-      <c r="G8" s="666"/>
-      <c r="H8" s="666"/>
-      <c r="I8" s="666"/>
-      <c r="J8" s="666"/>
-      <c r="K8" s="666"/>
-      <c r="L8" s="666"/>
-      <c r="M8" s="666"/>
-      <c r="N8" s="667"/>
+      <c r="B8" s="762"/>
+      <c r="C8" s="762"/>
+      <c r="D8" s="762"/>
+      <c r="E8" s="762"/>
+      <c r="F8" s="762"/>
+      <c r="G8" s="762"/>
+      <c r="H8" s="762"/>
+      <c r="I8" s="762"/>
+      <c r="J8" s="762"/>
+      <c r="K8" s="762"/>
+      <c r="L8" s="762"/>
+      <c r="M8" s="762"/>
+      <c r="N8" s="763"/>
       <c r="O8" s="6"/>
-      <c r="P8" s="665" t="s">
+      <c r="P8" s="761" t="s">
         <v>2</v>
       </c>
-      <c r="Q8" s="666"/>
-      <c r="R8" s="666"/>
-      <c r="S8" s="666"/>
-      <c r="T8" s="666"/>
-      <c r="U8" s="666"/>
-      <c r="V8" s="666"/>
-      <c r="W8" s="666"/>
-      <c r="X8" s="666"/>
-      <c r="Y8" s="666"/>
-      <c r="Z8" s="666"/>
-      <c r="AA8" s="668"/>
+      <c r="Q8" s="762"/>
+      <c r="R8" s="762"/>
+      <c r="S8" s="762"/>
+      <c r="T8" s="762"/>
+      <c r="U8" s="762"/>
+      <c r="V8" s="762"/>
+      <c r="W8" s="762"/>
+      <c r="X8" s="762"/>
+      <c r="Y8" s="762"/>
+      <c r="Z8" s="762"/>
+      <c r="AA8" s="764"/>
     </row>
     <row r="9" spans="1:27" s="215" customFormat="1" ht="45.75" customHeight="1">
       <c r="A9" s="216">
@@ -21560,7 +21560,7 @@
       </c>
       <c r="T14" s="16">
         <f>H15</f>
-        <v>164317.86008569799</v>
+        <v>162687.02786326414</v>
       </c>
       <c r="U14" s="16">
         <f>+H16</f>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="AA14" s="17">
         <f>SUM(Q14:Z14)</f>
-        <v>957617.7340348101</v>
+        <v>955986.90181237622</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="B15" s="9">
         <f>+'Rent Calculation'!C214</f>
-        <v>15243030</v>
+        <v>15071760</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9">
@@ -21614,11 +21614,11 @@
       </c>
       <c r="G15" s="9">
         <f t="shared" si="0"/>
-        <v>17256661.666200001</v>
+        <v>17085391.666200001</v>
       </c>
       <c r="H15" s="5">
         <f t="shared" si="3"/>
-        <v>164317.86008569799</v>
+        <v>162687.02786326414</v>
       </c>
       <c r="I15" s="357">
         <f>+T28</f>
@@ -21630,11 +21630,11 @@
       </c>
       <c r="K15" s="5">
         <f t="shared" si="1"/>
-        <v>23456661.666200001</v>
+        <v>23285391.666200001</v>
       </c>
       <c r="L15" s="357">
         <f t="shared" si="2"/>
-        <v>223354.23410969341</v>
+        <v>221723.40188725959</v>
       </c>
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
@@ -22150,7 +22150,7 @@
       </c>
       <c r="T22" s="19">
         <f t="shared" si="7"/>
-        <v>223354.23410969341</v>
+        <v>221723.40188725956</v>
       </c>
       <c r="U22" s="19">
         <f t="shared" si="7"/>
@@ -22178,7 +22178,7 @@
       </c>
       <c r="AA22" s="227">
         <f t="shared" si="7"/>
-        <v>1390868.5434044539</v>
+        <v>1389237.7111820201</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -22187,7 +22187,7 @@
       </c>
       <c r="B23" s="20">
         <f t="shared" ref="B23:L23" si="8">SUM(B12:B22)</f>
-        <v>88546590</v>
+        <v>88375320</v>
       </c>
       <c r="C23" s="20">
         <f t="shared" si="8"/>
@@ -22207,11 +22207,11 @@
       </c>
       <c r="G23" s="20">
         <f t="shared" si="8"/>
-        <v>100569014.42833576</v>
+        <v>100397744.42833576</v>
       </c>
       <c r="H23" s="20">
         <f t="shared" si="8"/>
-        <v>957617.7340348101</v>
+        <v>955986.90181237622</v>
       </c>
       <c r="I23" s="20">
         <f t="shared" si="8"/>
@@ -22223,19 +22223,19 @@
       </c>
       <c r="K23" s="20">
         <f t="shared" si="8"/>
-        <v>146069014.42833573</v>
+        <v>145897744.42833573</v>
       </c>
       <c r="L23" s="20">
         <f t="shared" si="8"/>
-        <v>1390868.5434044539</v>
+        <v>1389237.7111820201</v>
       </c>
       <c r="M23" s="21">
         <f>+N23*$T$9</f>
-        <v>109878159.84532638</v>
+        <v>109763283.08334981</v>
       </c>
       <c r="N23" s="21">
         <f>+R34</f>
-        <v>1046259.3776930716</v>
+        <v>1045165.5216468275</v>
       </c>
       <c r="Q23" s="2">
         <f>Q22/1.105</f>
@@ -22251,7 +22251,7 @@
       </c>
       <c r="T23" s="2">
         <f>T22/1.105^4</f>
-        <v>149811.47421191164</v>
+        <v>148717.61816566758</v>
       </c>
       <c r="U23" s="2">
         <f>U22/1.105^5</f>
@@ -22273,7 +22273,7 @@
       <c r="K24" s="10"/>
       <c r="L24" s="10">
         <f>L23-H23</f>
-        <v>433250.8093696438</v>
+        <v>433250.80936964392</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
@@ -22323,17 +22323,17 @@
       <c r="F25" s="5"/>
       <c r="G25" s="357">
         <f>+'Rent Calculation'!G195+'Rent Calculation'!F31</f>
-        <v>512254.33034775488</v>
+        <v>511749.08384775487</v>
       </c>
       <c r="H25" s="10">
         <f>G25/$T$9</f>
-        <v>4877.6835873905438</v>
+        <v>4872.8726323343635</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
       <c r="K25" s="5">
         <f>+G25+I25+J25</f>
-        <v>512254.33034775488</v>
+        <v>511749.08384775487</v>
       </c>
       <c r="L25" s="10"/>
       <c r="M25" s="10"/>
@@ -22355,7 +22355,7 @@
       </c>
       <c r="T25" s="16">
         <f t="shared" si="9"/>
-        <v>17256661.666200001</v>
+        <v>17085391.666200001</v>
       </c>
       <c r="U25" s="16">
         <f t="shared" si="9"/>
@@ -22383,7 +22383,7 @@
       </c>
       <c r="AA25" s="25">
         <f>SUM(Q25:Z25)</f>
-        <v>100569014.42833576</v>
+        <v>100397744.42833576</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="10.5">
@@ -22514,11 +22514,11 @@
       <c r="F28" s="20"/>
       <c r="G28" s="20">
         <f>SUM(G25:G27)</f>
-        <v>34512254.330347754</v>
+        <v>34511749.083847754</v>
       </c>
       <c r="H28" s="20">
         <f>SUM(H25:H27)</f>
-        <v>328625.54113833321</v>
+        <v>328620.73018327705</v>
       </c>
       <c r="I28" s="20">
         <f>SUM(I25:I27)</f>
@@ -22527,16 +22527,16 @@
       <c r="J28" s="20"/>
       <c r="K28" s="20">
         <f>SUM(K25:K27)</f>
-        <v>54512254.330347754</v>
+        <v>54511749.083847754</v>
       </c>
       <c r="L28" s="20"/>
       <c r="M28" s="20">
         <f>+N28*T9</f>
-        <v>34512254.330347754</v>
+        <v>34511749.083847754</v>
       </c>
       <c r="N28" s="20">
         <f>+H28</f>
-        <v>328625.54113833321</v>
+        <v>328620.73018327705</v>
       </c>
       <c r="P28" s="10" t="s">
         <v>40</v>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="T30" s="18">
         <f t="shared" si="10"/>
-        <v>23456661.666200001</v>
+        <v>23285391.666200001</v>
       </c>
       <c r="U30" s="18">
         <f t="shared" si="10"/>
@@ -22674,7 +22674,7 @@
       </c>
       <c r="AA30" s="25">
         <f t="shared" si="10"/>
-        <v>146069014.42833576</v>
+        <v>145897744.42833576</v>
       </c>
     </row>
     <row r="31" spans="1:27" ht="10.5" thickBot="1">
@@ -22688,11 +22688,11 @@
       <c r="F31" s="20"/>
       <c r="G31" s="20">
         <f>+K23+G28</f>
-        <v>180581268.75868347</v>
+        <v>180409493.51218349</v>
       </c>
       <c r="H31" s="20">
         <f>+L23+H28</f>
-        <v>1719494.0845427872</v>
+        <v>1717858.4413652972</v>
       </c>
       <c r="I31" s="20"/>
       <c r="J31" s="20"/>
@@ -22700,11 +22700,11 @@
       <c r="L31" s="20"/>
       <c r="M31" s="20">
         <f>+M23+M28</f>
-        <v>144390414.17567414</v>
+        <v>144275032.16719756</v>
       </c>
       <c r="N31" s="20">
         <f>N23+N28</f>
-        <v>1374884.9188314048</v>
+        <v>1373786.2518301045</v>
       </c>
       <c r="T31" s="2"/>
       <c r="U31" s="2"/>
@@ -22721,7 +22721,7 @@
       <c r="G32" s="3"/>
       <c r="H32" s="157">
         <f>+H31/1000000</f>
-        <v>1.7194940845427871</v>
+        <v>1.7178584413652971</v>
       </c>
       <c r="I32" s="157"/>
       <c r="J32" s="157"/>
@@ -22730,7 +22730,7 @@
       <c r="M32" s="36"/>
       <c r="N32" s="157">
         <f>+N31/1000000</f>
-        <v>1.3748849188314047</v>
+        <v>1.3737862518301045</v>
       </c>
       <c r="P32" s="28"/>
       <c r="Q32" s="29" t="s">
@@ -22739,11 +22739,11 @@
       <c r="R32" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="T32" s="646" t="s">
+      <c r="T32" s="744" t="s">
         <v>53</v>
       </c>
-      <c r="U32" s="647"/>
-      <c r="V32" s="648"/>
+      <c r="U32" s="745"/>
+      <c r="V32" s="746"/>
     </row>
     <row r="33" spans="1:27" ht="10.5">
       <c r="A33" s="37"/>
@@ -22787,11 +22787,11 @@
       </c>
       <c r="Q34" s="33">
         <f>+NPV(Q9,Q30,R30,S30,T30,U30,V30,W30,X30,Y30,Z30)</f>
-        <v>109878159.84532636</v>
+        <v>109763283.08334982</v>
       </c>
       <c r="R34" s="34">
         <f>+NPV(Q9,Q22:Z22)</f>
-        <v>1046259.3776930716</v>
+        <v>1045165.5216468275</v>
       </c>
       <c r="T34" s="23" t="s">
         <v>56</v>
@@ -22843,7 +22843,7 @@
       <c r="G36" s="3"/>
       <c r="H36" s="160">
         <f>+H32+H34</f>
-        <v>1.7194940845427871</v>
+        <v>1.7178584413652971</v>
       </c>
       <c r="I36" s="160"/>
       <c r="J36" s="160"/>
@@ -22852,10 +22852,10 @@
       <c r="M36" s="3"/>
       <c r="N36" s="160">
         <f>+N32+N34</f>
-        <v>1.3748849188314047</v>
-      </c>
-      <c r="P36" s="645"/>
-      <c r="Q36" s="645"/>
+        <v>1.3737862518301045</v>
+      </c>
+      <c r="P36" s="743"/>
+      <c r="Q36" s="743"/>
       <c r="T36" s="31" t="s">
         <v>59</v>
       </c>
@@ -24724,10 +24724,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13">
-      <c r="A1" s="767" t="s">
+      <c r="A1" s="765" t="s">
         <v>338</v>
       </c>
-      <c r="B1" s="767"/>
+      <c r="B1" s="765"/>
       <c r="C1" s="441">
         <f>'Rent Calculation'!G21</f>
         <v>883.96506874767749</v>
@@ -24739,28 +24739,28 @@
       <c r="H1" s="431"/>
     </row>
     <row r="2" spans="1:9" ht="39.65" customHeight="1">
-      <c r="A2" s="767" t="s">
+      <c r="A2" s="765" t="s">
         <v>334</v>
       </c>
-      <c r="B2" s="767"/>
-      <c r="C2" s="766" t="s">
+      <c r="B2" s="765"/>
+      <c r="C2" s="767" t="s">
         <v>335</v>
       </c>
-      <c r="D2" s="766"/>
-      <c r="E2" s="766" t="s">
+      <c r="D2" s="767"/>
+      <c r="E2" s="767" t="s">
         <v>336</v>
       </c>
-      <c r="F2" s="766"/>
-      <c r="G2" s="766" t="s">
+      <c r="F2" s="767"/>
+      <c r="G2" s="767" t="s">
         <v>337</v>
       </c>
-      <c r="H2" s="766"/>
+      <c r="H2" s="767"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="767" t="s">
+      <c r="A3" s="765" t="s">
         <v>331</v>
       </c>
-      <c r="B3" s="767"/>
+      <c r="B3" s="765"/>
       <c r="C3" s="431">
         <v>36</v>
       </c>
@@ -24776,10 +24776,10 @@
       </c>
     </row>
     <row r="4" spans="1:9" s="432" customFormat="1" ht="13">
-      <c r="A4" s="765" t="s">
+      <c r="A4" s="766" t="s">
         <v>146</v>
       </c>
-      <c r="B4" s="765"/>
+      <c r="B4" s="766"/>
       <c r="C4" s="442" t="s">
         <v>332</v>
       </c>
@@ -25005,27 +25005,27 @@
       </c>
       <c r="C11" s="443">
         <f>'Rent Calculation'!$F$83/'FY wise Rental'!$H$3*'FY wise Rental'!C$3</f>
-        <v>384190.74776081613</v>
+        <v>383811.81288581615</v>
       </c>
       <c r="D11" s="443">
         <f t="shared" si="0"/>
-        <v>12.072835899157543</v>
+        <v>12.060928224157543</v>
       </c>
       <c r="E11" s="443">
         <f>'Rent Calculation'!$F$83/'FY wise Rental'!$H$3*'FY wise Rental'!E$3</f>
-        <v>128063.58258693872</v>
+        <v>127937.27096193872</v>
       </c>
       <c r="F11" s="443">
         <f t="shared" si="1"/>
-        <v>12.072835899157544</v>
+        <v>12.060928224157543</v>
       </c>
       <c r="G11" s="443">
         <f t="shared" si="2"/>
-        <v>512254.33034775488</v>
+        <v>511749.08384775487</v>
       </c>
       <c r="H11" s="443">
         <f t="shared" si="3"/>
-        <v>12.072835899157544</v>
+        <v>12.060928224157543</v>
       </c>
       <c r="I11" s="422"/>
     </row>
@@ -25038,27 +25038,27 @@
       </c>
       <c r="C12" s="443">
         <f>(SUM(C5:C11)+C21)*7%</f>
-        <v>5617477.7934691794</v>
+        <v>5617451.2680279287</v>
       </c>
       <c r="D12" s="443">
         <f>C12/$C$1/C$3</f>
-        <v>176.52400002598893</v>
+        <v>176.52316648873889</v>
       </c>
       <c r="E12" s="443">
         <f>(SUM(E5:E11)+E21)*7%</f>
-        <v>790108.08328108583</v>
+        <v>790099.24146733573</v>
       </c>
       <c r="F12" s="443">
         <f>E12/$C$1/E$3</f>
-        <v>74.485228660339871</v>
+        <v>74.484395123089868</v>
       </c>
       <c r="G12" s="443">
         <f>(SUM(G5:G11)+G21)*7%</f>
-        <v>6407585.8767502643</v>
+        <v>6407550.5094952649</v>
       </c>
       <c r="H12" s="443">
         <f>G12/$C$1/H$3</f>
-        <v>151.01430718457664</v>
+        <v>151.01347364732666</v>
       </c>
       <c r="I12" s="422"/>
     </row>
@@ -25071,35 +25071,35 @@
       </c>
       <c r="C13" s="442">
         <f>SUM(C5:C12)</f>
-        <v>57902706.30731459</v>
+        <v>57902300.846998334</v>
       </c>
       <c r="D13" s="445">
         <f t="shared" ref="D13:H13" si="4">SUM(D5:D12)</f>
-        <v>1819.5385376654817</v>
+        <v>1819.5257964532318</v>
       </c>
       <c r="E13" s="442">
         <f t="shared" si="4"/>
-        <v>2755881.6658680243</v>
+        <v>2755746.5124292746</v>
       </c>
       <c r="F13" s="445">
         <f t="shared" si="4"/>
-        <v>259.80303250484684</v>
+        <v>259.79029129259686</v>
       </c>
       <c r="G13" s="442">
         <f t="shared" si="4"/>
-        <v>60658587.973182604</v>
+        <v>60658047.359427609</v>
       </c>
       <c r="H13" s="442">
         <f t="shared" si="4"/>
-        <v>1429.6046613753231</v>
+        <v>1429.5919201630732</v>
       </c>
       <c r="I13" s="425"/>
     </row>
     <row r="14" spans="1:9" ht="13">
-      <c r="A14" s="765" t="s">
+      <c r="A14" s="766" t="s">
         <v>154</v>
       </c>
-      <c r="B14" s="765"/>
+      <c r="B14" s="766"/>
       <c r="C14" s="443"/>
       <c r="D14" s="443"/>
       <c r="E14" s="443"/>
@@ -25347,33 +25347,33 @@
       <c r="I22" s="422"/>
     </row>
     <row r="23" spans="1:9" s="432" customFormat="1" ht="13">
-      <c r="A23" s="765" t="s">
+      <c r="A23" s="766" t="s">
         <v>157</v>
       </c>
-      <c r="B23" s="765"/>
+      <c r="B23" s="766"/>
       <c r="C23" s="442">
         <f>C13+C21</f>
-        <v>85867160.55731459</v>
+        <v>85866755.096998334</v>
       </c>
       <c r="D23" s="445">
         <f t="shared" ref="D23:H23" si="10">D13+D21</f>
-        <v>2698.2954289686872</v>
+        <v>2698.2826877564371</v>
       </c>
       <c r="E23" s="442">
         <f t="shared" si="10"/>
-        <v>12077366.415868025</v>
+        <v>12077231.262429275</v>
       </c>
       <c r="F23" s="445">
         <f t="shared" si="10"/>
-        <v>1138.5599238080522</v>
+        <v>1138.5471825958023</v>
       </c>
       <c r="G23" s="442">
         <f t="shared" si="10"/>
-        <v>97944526.973182604</v>
+        <v>97943986.359427601</v>
       </c>
       <c r="H23" s="442">
         <f t="shared" si="10"/>
-        <v>2308.3615526785284</v>
+        <v>2308.3488114662787</v>
       </c>
       <c r="I23" s="425"/>
     </row>
@@ -25399,15 +25399,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A14:B14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -26378,7 +26378,7 @@
       </c>
       <c r="I22" s="155">
         <f t="shared" ca="1" si="21"/>
-        <v>15243030</v>
+        <v>15071760</v>
       </c>
       <c r="J22" s="155">
         <f t="shared" ca="1" si="22"/>
@@ -26386,7 +26386,7 @@
       </c>
       <c r="K22" s="240">
         <f t="shared" ca="1" si="23"/>
-        <v>17256661.666200001</v>
+        <v>17085391.666200001</v>
       </c>
       <c r="L22" s="339"/>
       <c r="M22" s="339"/>
@@ -26535,7 +26535,7 @@
       </c>
       <c r="I26" s="188">
         <f ca="1">SUM(I19:I25)</f>
-        <v>88546590</v>
+        <v>88375320</v>
       </c>
       <c r="J26" s="188">
         <f t="shared" ref="J26:K26" ca="1" si="25">SUM(J19:J25)</f>
@@ -26543,7 +26543,7 @@
       </c>
       <c r="K26" s="188">
         <f t="shared" ca="1" si="25"/>
-        <v>100569014.42833576</v>
+        <v>100397744.42833576</v>
       </c>
       <c r="L26" s="339"/>
       <c r="M26" s="339"/>
@@ -28410,8 +28410,8 @@
         <v>883.96506874767749</v>
       </c>
       <c r="H66" s="486">
-        <f>H65*1.15</f>
-        <v>138</v>
+        <f>H65</f>
+        <v>120</v>
       </c>
       <c r="I66" s="485"/>
       <c r="J66" s="469">
@@ -28420,7 +28420,7 @@
       </c>
       <c r="K66" s="485">
         <f t="shared" si="43"/>
-        <v>1313070</v>
+        <v>1141800</v>
       </c>
       <c r="L66" s="486">
         <f t="shared" si="44"/>
@@ -28428,7 +28428,7 @@
       </c>
       <c r="M66" s="467">
         <f t="shared" si="35"/>
-        <v>1475459.6505</v>
+        <v>1304189.6505</v>
       </c>
       <c r="N66" s="485"/>
       <c r="O66" s="504"/>
@@ -28459,7 +28459,7 @@
         <v>883.96506874767749</v>
       </c>
       <c r="H67" s="486">
-        <f>H66</f>
+        <f>H66*1.15</f>
         <v>138</v>
       </c>
       <c r="I67" s="485"/>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="N75" s="485">
         <f>SUM(K63:K74)</f>
-        <v>15243030</v>
+        <v>15071760</v>
       </c>
       <c r="O75" s="504">
         <f>SUM(L63:L74)</f>
@@ -30236,7 +30236,7 @@
     <row r="104" spans="1:18">
       <c r="K104" s="471">
         <f>SUM(K31:K102)</f>
-        <v>88546590</v>
+        <v>88375320</v>
       </c>
       <c r="L104" s="471">
         <f>SUM(L31:L102)</f>
@@ -30244,11 +30244,11 @@
       </c>
       <c r="M104" s="471">
         <f>SUM(M31:M102)</f>
-        <v>100569014.42833562</v>
+        <v>100397744.42833562</v>
       </c>
       <c r="N104" s="471">
         <f>SUM(N31:N103)</f>
-        <v>88546590</v>
+        <v>88375320</v>
       </c>
       <c r="O104" s="575">
         <f>SUM(O31:O103)</f>
@@ -34450,27 +34450,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" xsi:nil="true"/>
-    <Status xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100907921E7373C1341A3C877D189CE8922" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2036b66ca2b7955135caa708c7901a86">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xmlns:ns3="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fed2217af4f675ffeab875e34aa73a78" ns2:_="" ns3:_="">
     <xsd:import namespace="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
@@ -34713,26 +34692,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC57694E-BA35-486E-AC74-B7B624F1FDE0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" xsi:nil="true"/>
+    <Status xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12D5BE44-B07C-4182-BC7A-71E5962390BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
-    <ds:schemaRef ds:uri="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB719E29-C329-4AB1-8ED0-5CC29C0FF757}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34751,6 +34732,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12D5BE44-B07C-4182-BC7A-71E5962390BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
+    <ds:schemaRef ds:uri="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC57694E-BA35-486E-AC74-B7B624F1FDE0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{a59b6cd5-d141-4a33-8bf1-0ca04484304f}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" removed="0"/>

--- a/artifacts/Rental Specimen.xlsx
+++ b/artifacts/Rental Specimen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z0050s8t\Documents\rental-automation\artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D6D59E-07E5-409D-9B8A-8CB82AB8DFCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68731A05-8D14-4278-9705-47D3B10FAA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="764" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="764" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="16" state="hidden" r:id="rId1"/>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="502">
   <si>
     <t>RENTAL CALCULATION FOR NEW LEASE</t>
   </si>
@@ -1757,6 +1757,14 @@
   </si>
   <si>
     <t>PM per sq. mtr. per month</t>
+  </si>
+  <si>
+    <t>Rental 
+SQF</t>
+  </si>
+  <si>
+    <t>CAM 
+SQF</t>
   </si>
 </sst>
 </file>
@@ -26632,10 +26640,10 @@
         <v>66</v>
       </c>
       <c r="K30" s="590" t="s">
-        <v>252</v>
+        <v>500</v>
       </c>
       <c r="L30" s="590" t="s">
-        <v>254</v>
+        <v>501</v>
       </c>
       <c r="M30" s="591" t="s">
         <v>29</v>
@@ -26685,11 +26693,11 @@
         <v>1141800</v>
       </c>
       <c r="L31" s="481">
-        <f t="shared" ref="L31:L62" si="27">J31*E31</f>
+        <f>J31*E31</f>
         <v>147292.20000000001</v>
       </c>
       <c r="M31" s="483">
-        <f t="shared" ref="M31:M36" si="28">I31+K31+L31</f>
+        <f t="shared" ref="M31:M36" si="27">I31+K31+L31</f>
         <v>1289092.2</v>
       </c>
       <c r="N31" s="501"/>
@@ -26732,11 +26740,11 @@
         <v>1141800</v>
       </c>
       <c r="L32" s="486">
+        <f t="shared" ref="L31:L62" si="28">J32*E32</f>
+        <v>147292.20000000001</v>
+      </c>
+      <c r="M32" s="467">
         <f t="shared" si="27"/>
-        <v>147292.20000000001</v>
-      </c>
-      <c r="M32" s="467">
-        <f t="shared" si="28"/>
         <v>1289092.2</v>
       </c>
       <c r="N32" s="465"/>
@@ -26782,11 +26790,11 @@
         <v>1141800</v>
       </c>
       <c r="L33" s="486">
+        <f t="shared" si="28"/>
+        <v>147292.20000000001</v>
+      </c>
+      <c r="M33" s="467">
         <f t="shared" si="27"/>
-        <v>147292.20000000001</v>
-      </c>
-      <c r="M33" s="467">
-        <f t="shared" si="28"/>
         <v>1289092.2</v>
       </c>
       <c r="N33" s="465"/>
@@ -26832,11 +26840,11 @@
         <v>1141800</v>
       </c>
       <c r="L34" s="486">
+        <f t="shared" si="28"/>
+        <v>147292.20000000001</v>
+      </c>
+      <c r="M34" s="467">
         <f t="shared" si="27"/>
-        <v>147292.20000000001</v>
-      </c>
-      <c r="M34" s="467">
-        <f t="shared" si="28"/>
         <v>1289092.2</v>
       </c>
       <c r="N34" s="465"/>
@@ -26882,11 +26890,11 @@
         <v>1141800</v>
       </c>
       <c r="L35" s="486">
+        <f t="shared" si="28"/>
+        <v>147292.20000000001</v>
+      </c>
+      <c r="M35" s="467">
         <f t="shared" si="27"/>
-        <v>147292.20000000001</v>
-      </c>
-      <c r="M35" s="467">
-        <f t="shared" si="28"/>
         <v>1289092.2</v>
       </c>
       <c r="N35" s="465"/>
@@ -26932,11 +26940,11 @@
         <v>1141800</v>
       </c>
       <c r="L36" s="486">
+        <f t="shared" si="28"/>
+        <v>147292.20000000001</v>
+      </c>
+      <c r="M36" s="467">
         <f t="shared" si="27"/>
-        <v>147292.20000000001</v>
-      </c>
-      <c r="M36" s="467">
-        <f t="shared" si="28"/>
         <v>1289092.2</v>
       </c>
       <c r="N36" s="465"/>
@@ -26981,7 +26989,7 @@
         <v>1141800</v>
       </c>
       <c r="L37" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>147292.20000000001</v>
       </c>
       <c r="M37" s="467">
@@ -27031,7 +27039,7 @@
         <v>1141800</v>
       </c>
       <c r="L38" s="491">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>147292.20000000001</v>
       </c>
       <c r="M38" s="493">
@@ -27080,7 +27088,7 @@
         <v>1141800</v>
       </c>
       <c r="L39" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>147292.20000000001</v>
       </c>
       <c r="M39" s="467">
@@ -27135,7 +27143,7 @@
         <v>1141800</v>
       </c>
       <c r="L40" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>147292.20000000001</v>
       </c>
       <c r="M40" s="467">
@@ -27184,7 +27192,7 @@
         <v>1141800</v>
       </c>
       <c r="L41" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>147292.20000000001</v>
       </c>
       <c r="M41" s="467">
@@ -27233,7 +27241,7 @@
         <v>1141800</v>
       </c>
       <c r="L42" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>147292.20000000001</v>
       </c>
       <c r="M42" s="467">
@@ -27282,7 +27290,7 @@
         <v>1141800</v>
       </c>
       <c r="L43" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M43" s="467">
@@ -27331,7 +27339,7 @@
         <v>1141800</v>
       </c>
       <c r="L44" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M44" s="467">
@@ -27380,7 +27388,7 @@
         <v>1141800</v>
       </c>
       <c r="L45" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M45" s="467">
@@ -27429,7 +27437,7 @@
         <v>1141800</v>
       </c>
       <c r="L46" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M46" s="467">
@@ -27478,7 +27486,7 @@
         <v>1141800</v>
       </c>
       <c r="L47" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M47" s="467">
@@ -27527,7 +27535,7 @@
         <v>1141800</v>
       </c>
       <c r="L48" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M48" s="467">
@@ -27576,7 +27584,7 @@
         <v>1141800</v>
       </c>
       <c r="L49" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M49" s="467">
@@ -27626,7 +27634,7 @@
         <v>1141800</v>
       </c>
       <c r="L50" s="491">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M50" s="493">
@@ -27675,7 +27683,7 @@
         <v>1141800</v>
       </c>
       <c r="L51" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M51" s="467">
@@ -27730,7 +27738,7 @@
         <v>1141800</v>
       </c>
       <c r="L52" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M52" s="467">
@@ -27779,7 +27787,7 @@
         <v>1141800</v>
       </c>
       <c r="L53" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M53" s="467">
@@ -27828,7 +27836,7 @@
         <v>1141800</v>
       </c>
       <c r="L54" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>154656.81000000003</v>
       </c>
       <c r="M54" s="467">
@@ -27877,7 +27885,7 @@
         <v>1141800</v>
       </c>
       <c r="L55" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>162389.65050000002</v>
       </c>
       <c r="M55" s="467">
@@ -27926,7 +27934,7 @@
         <v>1141800</v>
       </c>
       <c r="L56" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>162389.65050000002</v>
       </c>
       <c r="M56" s="467">
@@ -27975,7 +27983,7 @@
         <v>1141800</v>
       </c>
       <c r="L57" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>162389.65050000002</v>
       </c>
       <c r="M57" s="467">
@@ -28024,7 +28032,7 @@
         <v>1141800</v>
       </c>
       <c r="L58" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>162389.65050000002</v>
       </c>
       <c r="M58" s="467">
@@ -28073,7 +28081,7 @@
         <v>1141800</v>
       </c>
       <c r="L59" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>162389.65050000002</v>
       </c>
       <c r="M59" s="467">
@@ -28122,7 +28130,7 @@
         <v>1141800</v>
       </c>
       <c r="L60" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>162389.65050000002</v>
       </c>
       <c r="M60" s="467">
@@ -28171,7 +28179,7 @@
         <v>1141800</v>
       </c>
       <c r="L61" s="486">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>162389.65050000002</v>
       </c>
       <c r="M61" s="467">
@@ -28221,7 +28229,7 @@
         <v>1141800</v>
       </c>
       <c r="L62" s="491">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>162389.65050000002</v>
       </c>
       <c r="M62" s="493">

--- a/artifacts/Rental Specimen.xlsx
+++ b/artifacts/Rental Specimen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z0050s8t\Documents\rental-automation\artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C3A8A9-88EB-4D95-BDA7-DB707B27E21A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC8A485-B31D-4E94-A60E-78814B00A0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="764" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,64 +42,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>in219907</author>
-  </authors>
-  <commentList>
-    <comment ref="G191" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>in219907:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Assumed that Agreement will be of 10yrs hence MV tkn @ 25% which wil be devided equally over a period of 10yrs</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J191" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>in219907:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Assumed that Agreement will be of 10yrs hence MV tkn @ 25% which wil be devided equally over a period of 10yrs</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1272,7 +1214,7 @@
     <numFmt numFmtId="231" formatCode="\V\F\ \ #\-#\-##"/>
     <numFmt numFmtId="232" formatCode="00"/>
   </numFmts>
-  <fonts count="104">
+  <fonts count="102">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1348,19 +1290,6 @@
       <b/>
       <sz val="10"/>
       <name val="Arial Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
     <font>
@@ -3171,42 +3100,42 @@
   </borders>
   <cellStyleXfs count="1012">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="4" fontId="46" fillId="2" borderId="1">
+    <xf numFmtId="4" fontId="44" fillId="2" borderId="1">
       <alignment readingOrder="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="175" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="175" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFill="0" applyBorder="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="21" fillId="0" borderId="2">
+    <xf numFmtId="177" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="19" fillId="0" borderId="2">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3219,10 +3148,10 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="181" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3233,70 +3162,70 @@
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="37" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="182" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="182" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="40" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="40" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="37" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3310,47 +3239,47 @@
     <xf numFmtId="184" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="184" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="185" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="177" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="185" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="177" fontId="24" fillId="0" borderId="3" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="186" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="2" fontId="27" fillId="0" borderId="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="186" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="2" fontId="25" fillId="0" borderId="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="29" fillId="0" borderId="5">
+    <xf numFmtId="168" fontId="27" fillId="0" borderId="5">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="38" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -3359,20 +3288,20 @@
     </xf>
     <xf numFmtId="10" fontId="5" fillId="4" borderId="8" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="177" fontId="10" fillId="5" borderId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="37" fontId="34" fillId="0" borderId="0"/>
-    <xf numFmtId="187" fontId="35" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
+    <xf numFmtId="37" fontId="32" fillId="0" borderId="0"/>
+    <xf numFmtId="187" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -3380,9 +3309,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -3390,95 +3319,95 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="175" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="48" fillId="0" borderId="0"/>
-    <xf numFmtId="175" fontId="48" fillId="0" borderId="0"/>
+    <xf numFmtId="175" fontId="46" fillId="0" borderId="0"/>
+    <xf numFmtId="175" fontId="46" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="37" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="46" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyFont="0"/>
-    <xf numFmtId="188" fontId="37" fillId="5" borderId="0"/>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyFont="0"/>
+    <xf numFmtId="188" fontId="35" fillId="5" borderId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="9">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="1" borderId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="1" borderId="10">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="8">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="6" borderId="9">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="1" borderId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="1" borderId="10">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="6" borderId="8">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="189" fontId="38" fillId="0" borderId="0">
+    <xf numFmtId="189" fontId="36" fillId="0" borderId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0">
       <alignment horizontal="centerContinuous" vertical="top"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="21" fillId="0" borderId="0" applyBorder="0">
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="0" applyBorder="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
-    <xf numFmtId="40" fontId="43" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="40" fontId="41" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="190" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="49" fontId="45" fillId="7" borderId="0">
+    <xf numFmtId="49" fontId="43" fillId="7" borderId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3519,10 +3448,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="53" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="51" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="57" fillId="3" borderId="1" applyNumberFormat="0">
+    <xf numFmtId="0" fontId="55" fillId="3" borderId="1" applyNumberFormat="0">
       <alignment readingOrder="1"/>
       <protection locked="0"/>
     </xf>
@@ -3547,257 +3476,257 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="8">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="56" fillId="20" borderId="61" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="54" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="54" fillId="20" borderId="61" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="53" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="53" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="51" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="51" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="193" fontId="4" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="194" fontId="4" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="40" fontId="4" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="195" fontId="4" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="61" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="59" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="5" fillId="45" borderId="62">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="196" fontId="5" fillId="45" borderId="63">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="62" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="62" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="62" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="62" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="62" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="197" fontId="56" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="64" fillId="30" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="30" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="30" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="30" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="30" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="30" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="22" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="64" fillId="22" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="46" borderId="64" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="46" borderId="64" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="46" borderId="64" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="46" borderId="64" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="46" borderId="64" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="46" borderId="64" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="46" borderId="64" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="66" fillId="46" borderId="64" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="60" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="197" fontId="54" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="62" fillId="30" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="62" fillId="30" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="62" fillId="30" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="62" fillId="30" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="62" fillId="30" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="62" fillId="30" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="62" fillId="22" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="62" fillId="22" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="46" borderId="64" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="46" borderId="64" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="46" borderId="64" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="46" borderId="64" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="46" borderId="64" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="46" borderId="64" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="46" borderId="64" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="64" fillId="46" borderId="64" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="198" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" applyNumberFormat="0" applyAlignment="0">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" applyNumberFormat="0" applyAlignment="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="199" fontId="68" fillId="47" borderId="0" applyFill="0">
+    <xf numFmtId="199" fontId="66" fillId="47" borderId="0" applyFill="0">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -3806,7 +3735,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="200" fontId="4" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="202" fontId="69" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0">
+    <xf numFmtId="202" fontId="67" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -3818,22 +3747,22 @@
     <xf numFmtId="208" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="209" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="210" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" applyNumberFormat="0" applyAlignment="0">
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" applyNumberFormat="0" applyAlignment="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="211" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="211" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="212" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="212" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="213" fontId="4" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
@@ -3855,7 +3784,7 @@
     <xf numFmtId="213" fontId="4" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="214" fontId="69" fillId="0" borderId="0" applyFont="0">
+    <xf numFmtId="214" fontId="67" fillId="0" borderId="0" applyFont="0">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -3865,342 +3794,342 @@
     <xf numFmtId="218" fontId="5" fillId="45" borderId="63">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="72" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="199" fontId="73" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="70" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="70" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="199" fontId="71" fillId="0" borderId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="65" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="65" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="65" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="65" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="65" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="65" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="66" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="66" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="67" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="67" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="67" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="67" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="67" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="67" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="67" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="67" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="68" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="68" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="68" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="68" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="68" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="68" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="69" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="69" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="80" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="199" fontId="69" fillId="0" borderId="0" applyFont="0">
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="65" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="65" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="65" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="65" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="65" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="65" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="66" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="66" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="67" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="67" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="67" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="67" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="67" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="67" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="67" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="67" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="68" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="68" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="68" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="68" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="68" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="68" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="69" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="69" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="78" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="78" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="78" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="78" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="78" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="78" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="78" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="78" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="199" fontId="67" fillId="0" borderId="0" applyFont="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="199" fontId="69" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0">
+    <xf numFmtId="199" fontId="67" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="40" fontId="5" fillId="0" borderId="0" applyFont="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="70" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="70" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="70" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="70" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="70" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="70" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="70" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="70" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="199" fontId="69" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0">
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="70" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="70" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="70" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="70" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="70" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="70" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="70" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="70" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="199" fontId="67" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="199" fontId="69" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0">
+    <xf numFmtId="199" fontId="67" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="202" fontId="82" fillId="0" borderId="0">
+    <xf numFmtId="202" fontId="80" fillId="0" borderId="0">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="202" fontId="5" fillId="0" borderId="0" applyFont="0"/>
-    <xf numFmtId="41" fontId="56" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="54" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="219" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="4" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="199" fontId="69" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0">
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="199" fontId="67" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="26"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="26"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="220" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="199" fontId="69" fillId="0" borderId="0" applyFont="0">
+    <xf numFmtId="220" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="199" fontId="67" fillId="0" borderId="0" applyFont="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="84" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="84" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="84" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="84" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="84" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="84" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="84" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="84" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="221" fontId="85" fillId="0" borderId="0"/>
-    <xf numFmtId="221" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="82" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="82" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="82" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="82" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="82" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="82" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="82" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="221" fontId="83" fillId="0" borderId="0"/>
+    <xf numFmtId="221" fontId="83" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="71" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="71" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="71" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="71" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="71" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="71" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="71" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="71" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="71" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="71" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="71" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="71" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="71" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="71" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="71" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="71" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="214" fontId="5" fillId="0" borderId="0" applyFont="0">
       <protection locked="0"/>
     </xf>
@@ -4211,14 +4140,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="30" borderId="72" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="30" borderId="72" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="30" borderId="72" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="30" borderId="72" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="30" borderId="72" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="30" borderId="72" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="22" borderId="72" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="22" borderId="72" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="86" fillId="30" borderId="72" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="86" fillId="30" borderId="72" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="86" fillId="30" borderId="72" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="86" fillId="30" borderId="72" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="86" fillId="30" borderId="72" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="86" fillId="30" borderId="72" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="86" fillId="22" borderId="72" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="86" fillId="22" borderId="72" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="222" fontId="5" fillId="45" borderId="63">
@@ -4227,16 +4156,16 @@
     <xf numFmtId="223" fontId="5" fillId="45" borderId="73">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="40" fontId="69" fillId="0" borderId="0" applyFont="0">
+    <xf numFmtId="40" fontId="67" fillId="0" borderId="0" applyFont="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="40" fontId="73" fillId="0" borderId="0" applyFont="0">
+    <xf numFmtId="40" fontId="71" fillId="0" borderId="0" applyFont="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="224" fontId="89" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="224" fontId="87" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="202" fontId="90" fillId="0" borderId="0" applyFont="0">
+    <xf numFmtId="202" fontId="88" fillId="0" borderId="0" applyFont="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -4244,18 +4173,18 @@
       <alignment horizontal="right" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="40" fontId="92" fillId="0" borderId="0" applyBorder="0">
+    <xf numFmtId="40" fontId="90" fillId="0" borderId="0" applyBorder="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="202" fontId="69" fillId="0" borderId="0" applyFont="0">
+    <xf numFmtId="202" fontId="67" fillId="0" borderId="0" applyFont="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="202" fontId="69" fillId="0" borderId="0" applyFill="0" applyProtection="0">
+    <xf numFmtId="202" fontId="67" fillId="0" borderId="0" applyFill="0" applyProtection="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="199" fontId="10" fillId="48" borderId="0" applyNumberFormat="0" applyAlignment="0">
@@ -4268,58 +4197,58 @@
     <xf numFmtId="228" fontId="5" fillId="45" borderId="63">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="199" fontId="95" fillId="0" borderId="41" applyNumberFormat="0" applyFill="0" applyProtection="0">
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="199" fontId="93" fillId="0" borderId="41" applyNumberFormat="0" applyFill="0" applyProtection="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="74" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="74" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="74" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="74" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="74" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="74" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="75" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="75" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="202" fontId="73" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="74" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="74" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="74" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="74" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="74" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="74" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="75" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="75" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="202" fontId="71" fillId="0" borderId="0"/>
     <xf numFmtId="218" fontId="5" fillId="45" borderId="63">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="229" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="230" fontId="69" fillId="0" borderId="0" applyFill="0">
+    <xf numFmtId="230" fontId="67" fillId="0" borderId="0" applyFill="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="202" fontId="69" fillId="0" borderId="0" applyFont="0">
+    <xf numFmtId="202" fontId="67" fillId="0" borderId="0" applyFont="0">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="187" fontId="82" fillId="0" borderId="8">
+    <xf numFmtId="187" fontId="80" fillId="0" borderId="8">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="82" fillId="0" borderId="8">
+    <xf numFmtId="187" fontId="80" fillId="0" borderId="8">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="56" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="54" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="35" applyBorder="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="231" fontId="5" fillId="45" borderId="63">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -4328,7 +4257,7 @@
     </xf>
     <xf numFmtId="40" fontId="4" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0"/>
     <xf numFmtId="194" fontId="4" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="193" fontId="4" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
@@ -4375,7 +4304,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="714">
+  <cellXfs count="715">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4817,11 +4746,11 @@
     <xf numFmtId="10" fontId="4" fillId="0" borderId="11" xfId="207" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="190"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="190"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="21" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="190" applyFont="1"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="16" fillId="0" borderId="0" xfId="190" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="190" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="6" fillId="0" borderId="11" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4833,7 +4762,7 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="190" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="190" applyBorder="1"/>
     <xf numFmtId="171" fontId="4" fillId="14" borderId="12" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5063,7 +4992,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="190" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="190" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="190" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="8" xfId="190" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -5072,7 +5001,7 @@
     <xf numFmtId="191" fontId="4" fillId="0" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="16" fillId="0" borderId="0" xfId="190" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" xfId="190" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5128,60 +5057,60 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="55" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="54" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="53" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="52" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="192" fontId="55" fillId="15" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="192" fontId="53" fillId="15" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="192" fontId="55" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="55" fillId="15" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="55" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="55" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="55" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="55" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="55" fillId="0" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="192" fontId="53" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="53" fillId="15" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="53" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="53" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="53" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="53" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="53" fillId="0" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="55" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="53" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="52" fillId="0" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="50" fillId="0" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="57" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="184" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="52" fillId="14" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="50" fillId="14" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="53" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="51" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="99" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="97" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="21"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="21" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -5235,18 +5164,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="8" xfId="190" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="54" fillId="15" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="54" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="54" fillId="15" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="101" fillId="0" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="52" fillId="15" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="52" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="52" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="52" fillId="15" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="99" fillId="0" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="54" fillId="0" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="52" fillId="0" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="55" fillId="15" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="54" fillId="15" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="53" fillId="15" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="52" fillId="15" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -5310,7 +5239,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="21" applyFont="1"/>
     <xf numFmtId="43" fontId="6" fillId="13" borderId="0" xfId="21" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="192" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="55" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="53" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="4" fillId="7" borderId="9" xfId="184" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="172" fontId="4" fillId="7" borderId="9" xfId="187" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="7" borderId="9" xfId="187" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -5338,23 +5267,23 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="26" xfId="21" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="54" fillId="18" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="52" fillId="18" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="55" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="53" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="55" fillId="15" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="53" fillId="15" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="54" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="54" fillId="15" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="52" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="52" fillId="15" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="41" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="52" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="50" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="22" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5373,16 +5302,16 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="190" applyFont="1"/>
-    <xf numFmtId="43" fontId="52" fillId="0" borderId="0" xfId="21" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="50" fillId="0" borderId="0" xfId="21" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="4" fillId="7" borderId="9" xfId="187" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="55" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="55" fillId="0" borderId="0" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="53" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="53" fillId="0" borderId="0" xfId="21" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -5397,10 +5326,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5466,12 +5395,12 @@
     <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="4" fillId="7" borderId="8" xfId="21" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="4" fillId="7" borderId="12" xfId="21" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="103" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="101" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="192" applyNumberFormat="1"/>
@@ -5489,22 +5418,22 @@
     <xf numFmtId="14" fontId="0" fillId="49" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="49" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="49" borderId="44" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="102" fillId="49" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="100" fillId="49" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="102" fillId="49" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="100" fillId="49" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="102" fillId="49" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="100" fillId="49" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="102" fillId="49" borderId="17" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="100" fillId="49" borderId="17" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="102" fillId="49" borderId="44" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="100" fillId="49" borderId="44" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="49" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="49" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="14" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -5521,7 +5450,7 @@
     <xf numFmtId="0" fontId="4" fillId="14" borderId="17" xfId="184" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="18" xfId="184" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="184" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="50" borderId="8" xfId="190" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="8" xfId="190" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="50" borderId="8" xfId="190" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="50" borderId="8" xfId="190" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5591,15 +5520,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="102" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="100" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="102" fillId="0" borderId="41" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="100" fillId="0" borderId="41" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -5607,7 +5536,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="102" fillId="49" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="100" fillId="49" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -5758,28 +5687,28 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5797,10 +5726,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5833,10 +5762,10 @@
     <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5845,13 +5774,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5935,13 +5864,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="25" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5968,26 +5897,29 @@
     <xf numFmtId="167" fontId="6" fillId="0" borderId="50" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="192" fontId="54" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="192" fontId="52" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="54" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="37" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1012">
@@ -7503,7 +7435,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
@@ -12515,7 +12447,7 @@
         <f>+F214</f>
         <v>0</v>
       </c>
-      <c r="G215" s="113">
+      <c r="G215" s="714">
         <f>'Lease Rent'!P99</f>
         <v>2345999.9999999995</v>
       </c>
@@ -12543,7 +12475,7 @@
         <f>+F215*115%</f>
         <v>0</v>
       </c>
-      <c r="G216" s="113">
+      <c r="G216" s="714">
         <f>'Lease Rent'!P103</f>
         <v>781999.99999999988</v>
       </c>
@@ -12948,7 +12880,6 @@
     <customPr name="_pios_id" r:id="rId2"/>
     <customPr name="EpmWorksheetKeyString_GUID" r:id="rId3"/>
   </customProperties>
-  <legacyDrawing r:id="rId4"/>
 </worksheet>
 </file>
 

--- a/artifacts/Rental Specimen.xlsx
+++ b/artifacts/Rental Specimen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z0050s8t\Documents\rental-automation\artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC8A485-B31D-4E94-A60E-78814B00A0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72332E7-6E31-4CF6-A7F6-E84CA173A329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="764" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="26" r:id="rId1"/>
@@ -4304,7 +4304,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="715">
+  <cellXfs count="716">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -5540,6 +5540,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="37" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5918,9 +5921,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="37" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="8" xfId="190" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1012">
     <cellStyle name="??" xfId="303" xr:uid="{91225FB4-C7AB-4245-B40E-51FA489A4ADF}"/>
@@ -7470,62 +7471,62 @@
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1">
       <c r="A1" s="51"/>
-      <c r="B1" s="637"/>
-      <c r="C1" s="638"/>
-      <c r="D1" s="638"/>
-      <c r="E1" s="638"/>
-      <c r="F1" s="638"/>
-      <c r="G1" s="638"/>
-      <c r="H1" s="638"/>
-      <c r="I1" s="638"/>
-      <c r="J1" s="639"/>
+      <c r="B1" s="638"/>
+      <c r="C1" s="639"/>
+      <c r="D1" s="639"/>
+      <c r="E1" s="639"/>
+      <c r="F1" s="639"/>
+      <c r="G1" s="639"/>
+      <c r="H1" s="639"/>
+      <c r="I1" s="639"/>
+      <c r="J1" s="640"/>
     </row>
     <row r="2" spans="1:10" ht="14.25" customHeight="1">
       <c r="A2" s="51"/>
-      <c r="B2" s="640"/>
-      <c r="C2" s="641"/>
-      <c r="D2" s="641"/>
-      <c r="E2" s="641"/>
-      <c r="F2" s="641"/>
-      <c r="G2" s="641"/>
-      <c r="H2" s="641"/>
-      <c r="I2" s="641"/>
-      <c r="J2" s="642"/>
+      <c r="B2" s="641"/>
+      <c r="C2" s="642"/>
+      <c r="D2" s="642"/>
+      <c r="E2" s="642"/>
+      <c r="F2" s="642"/>
+      <c r="G2" s="642"/>
+      <c r="H2" s="642"/>
+      <c r="I2" s="642"/>
+      <c r="J2" s="643"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A3" s="51"/>
-      <c r="B3" s="643"/>
-      <c r="C3" s="644"/>
-      <c r="D3" s="644"/>
-      <c r="E3" s="644"/>
-      <c r="F3" s="644"/>
-      <c r="G3" s="644"/>
-      <c r="H3" s="644"/>
-      <c r="I3" s="641"/>
-      <c r="J3" s="642"/>
+      <c r="B3" s="644"/>
+      <c r="C3" s="645"/>
+      <c r="D3" s="645"/>
+      <c r="E3" s="645"/>
+      <c r="F3" s="645"/>
+      <c r="G3" s="645"/>
+      <c r="H3" s="645"/>
+      <c r="I3" s="642"/>
+      <c r="J3" s="643"/>
     </row>
     <row r="4" spans="1:10" ht="13">
       <c r="A4" s="51"/>
-      <c r="B4" s="664"/>
-      <c r="C4" s="665"/>
-      <c r="D4" s="665"/>
-      <c r="E4" s="665"/>
-      <c r="F4" s="665"/>
-      <c r="G4" s="665"/>
+      <c r="B4" s="665"/>
+      <c r="C4" s="666"/>
+      <c r="D4" s="666"/>
+      <c r="E4" s="666"/>
+      <c r="F4" s="666"/>
+      <c r="G4" s="666"/>
       <c r="H4" s="401"/>
       <c r="I4" s="402"/>
       <c r="J4" s="403"/>
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="51"/>
-      <c r="B5" s="666" t="s">
+      <c r="B5" s="667" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="667"/>
-      <c r="D5" s="667"/>
-      <c r="E5" s="667"/>
-      <c r="F5" s="667"/>
-      <c r="G5" s="668"/>
+      <c r="C5" s="668"/>
+      <c r="D5" s="668"/>
+      <c r="E5" s="668"/>
+      <c r="F5" s="668"/>
+      <c r="G5" s="669"/>
       <c r="H5" s="404"/>
       <c r="I5" s="481" t="s">
         <v>16</v>
@@ -7536,29 +7537,29 @@
     </row>
     <row r="6" spans="1:10" ht="13.5" thickBot="1">
       <c r="A6" s="51"/>
-      <c r="B6" s="669"/>
-      <c r="C6" s="670"/>
-      <c r="D6" s="671"/>
+      <c r="B6" s="670"/>
+      <c r="C6" s="671"/>
+      <c r="D6" s="672"/>
       <c r="E6" s="52"/>
-      <c r="F6" s="662">
+      <c r="F6" s="663">
         <v>10.763999999999999</v>
       </c>
-      <c r="G6" s="663"/>
+      <c r="G6" s="664"/>
       <c r="H6" s="405"/>
-      <c r="I6" s="650">
+      <c r="I6" s="651">
         <v>10.763999999999999</v>
       </c>
-      <c r="J6" s="651"/>
+      <c r="J6" s="652"/>
     </row>
     <row r="7" spans="1:10" ht="26">
       <c r="A7" s="51"/>
       <c r="B7" s="482" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="672" t="s">
+      <c r="C7" s="673" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="673"/>
+      <c r="D7" s="674"/>
       <c r="E7" s="483"/>
       <c r="F7" s="483" t="s">
         <v>303</v>
@@ -7586,23 +7587,23 @@
       <c r="C8" s="486"/>
       <c r="D8" s="487"/>
       <c r="E8" s="488"/>
-      <c r="F8" s="596" t="s">
+      <c r="F8" s="597" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="630"/>
+      <c r="G8" s="631"/>
       <c r="H8" s="404"/>
-      <c r="I8" s="631" t="s">
+      <c r="I8" s="632" t="s">
         <v>67</v>
       </c>
-      <c r="J8" s="632"/>
+      <c r="J8" s="633"/>
     </row>
     <row r="9" spans="1:10" ht="13">
       <c r="A9" s="51"/>
-      <c r="B9" s="631" t="s">
+      <c r="B9" s="632" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="630"/>
-      <c r="D9" s="597"/>
+      <c r="C9" s="631"/>
+      <c r="D9" s="598"/>
       <c r="E9" s="489"/>
       <c r="F9" s="376" t="s">
         <v>75</v>
@@ -7623,21 +7624,21 @@
       <c r="B10" s="490">
         <v>1</v>
       </c>
-      <c r="C10" s="645" t="s">
+      <c r="C10" s="646" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="604"/>
+      <c r="D10" s="605"/>
       <c r="E10" s="491"/>
-      <c r="F10" s="656" t="s">
+      <c r="F10" s="657" t="s">
         <v>299</v>
       </c>
-      <c r="G10" s="657"/>
+      <c r="G10" s="658"/>
       <c r="H10" s="404"/>
-      <c r="I10" s="652" t="str">
+      <c r="I10" s="653" t="str">
         <f>+F10</f>
         <v>Chennai</v>
       </c>
-      <c r="J10" s="653"/>
+      <c r="J10" s="654"/>
     </row>
     <row r="11" spans="1:10" ht="28.5" customHeight="1">
       <c r="A11" s="51"/>
@@ -7645,19 +7646,19 @@
         <f>1+B10</f>
         <v>2</v>
       </c>
-      <c r="C11" s="646" t="s">
+      <c r="C11" s="647" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="647"/>
+      <c r="D11" s="648"/>
       <c r="E11" s="50"/>
-      <c r="F11" s="656"/>
-      <c r="G11" s="657"/>
+      <c r="F11" s="657"/>
+      <c r="G11" s="658"/>
       <c r="H11" s="404"/>
-      <c r="I11" s="654">
+      <c r="I11" s="655">
         <f>+F11</f>
         <v>0</v>
       </c>
-      <c r="J11" s="655"/>
+      <c r="J11" s="656"/>
     </row>
     <row r="12" spans="1:10" ht="27.75" customHeight="1">
       <c r="A12" s="51"/>
@@ -7665,19 +7666,19 @@
         <f>1+B11</f>
         <v>3</v>
       </c>
-      <c r="C12" s="590" t="s">
+      <c r="C12" s="591" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="589"/>
+      <c r="D12" s="590"/>
       <c r="E12" s="492"/>
-      <c r="F12" s="658"/>
-      <c r="G12" s="659"/>
+      <c r="F12" s="659"/>
+      <c r="G12" s="660"/>
       <c r="H12" s="404"/>
-      <c r="I12" s="674">
+      <c r="I12" s="675">
         <f>+F12</f>
         <v>0</v>
       </c>
-      <c r="J12" s="675"/>
+      <c r="J12" s="676"/>
     </row>
     <row r="13" spans="1:10" ht="15.9" customHeight="1">
       <c r="A13" s="51"/>
@@ -7685,16 +7686,16 @@
         <f t="shared" ref="B13:B30" si="0">1+B12</f>
         <v>4</v>
       </c>
-      <c r="C13" s="590" t="s">
+      <c r="C13" s="591" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="589"/>
+      <c r="D13" s="590"/>
       <c r="E13" s="50"/>
-      <c r="F13" s="661"/>
-      <c r="G13" s="659"/>
+      <c r="F13" s="662"/>
+      <c r="G13" s="660"/>
       <c r="H13" s="404"/>
-      <c r="I13" s="674"/>
-      <c r="J13" s="675"/>
+      <c r="I13" s="675"/>
+      <c r="J13" s="676"/>
     </row>
     <row r="14" spans="1:10" ht="48" customHeight="1">
       <c r="A14" s="51"/>
@@ -7702,21 +7703,21 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="648" t="s">
+      <c r="C14" s="649" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="649"/>
+      <c r="D14" s="650"/>
       <c r="E14" s="476"/>
-      <c r="F14" s="658" t="s">
+      <c r="F14" s="659" t="s">
         <v>300</v>
       </c>
-      <c r="G14" s="660"/>
+      <c r="G14" s="661"/>
       <c r="H14" s="404"/>
-      <c r="I14" s="674" t="str">
+      <c r="I14" s="675" t="str">
         <f>+F14</f>
         <v>6th floor</v>
       </c>
-      <c r="J14" s="675"/>
+      <c r="J14" s="676"/>
     </row>
     <row r="15" spans="1:10" ht="51.75" customHeight="1">
       <c r="A15" s="51"/>
@@ -7724,19 +7725,19 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="590" t="s">
+      <c r="C15" s="591" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="589"/>
+      <c r="D15" s="590"/>
       <c r="E15" s="58"/>
-      <c r="F15" s="596"/>
-      <c r="G15" s="630"/>
+      <c r="F15" s="597"/>
+      <c r="G15" s="631"/>
       <c r="H15" s="404"/>
-      <c r="I15" s="631">
+      <c r="I15" s="632">
         <f>+F15</f>
         <v>0</v>
       </c>
-      <c r="J15" s="632"/>
+      <c r="J15" s="633"/>
     </row>
     <row r="16" spans="1:10" ht="15.9" customHeight="1">
       <c r="A16" s="51"/>
@@ -7744,16 +7745,16 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="590" t="s">
+      <c r="C16" s="591" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="589"/>
+      <c r="D16" s="590"/>
       <c r="E16" s="58"/>
-      <c r="F16" s="661"/>
-      <c r="G16" s="659"/>
+      <c r="F16" s="662"/>
+      <c r="G16" s="660"/>
       <c r="H16" s="404"/>
-      <c r="I16" s="674"/>
-      <c r="J16" s="675"/>
+      <c r="I16" s="675"/>
+      <c r="J16" s="676"/>
     </row>
     <row r="17" spans="1:10" ht="15.9" customHeight="1">
       <c r="A17" s="51"/>
@@ -7761,21 +7762,21 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="590" t="s">
+      <c r="C17" s="591" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="589"/>
+      <c r="D17" s="590"/>
       <c r="E17" s="58"/>
-      <c r="F17" s="658" t="s">
+      <c r="F17" s="659" t="s">
         <v>85</v>
       </c>
-      <c r="G17" s="659"/>
+      <c r="G17" s="660"/>
       <c r="H17" s="404"/>
-      <c r="I17" s="674" t="str">
+      <c r="I17" s="675" t="str">
         <f>+F17</f>
         <v>Warm Shell</v>
       </c>
-      <c r="J17" s="675"/>
+      <c r="J17" s="676"/>
     </row>
     <row r="18" spans="1:10" ht="48" customHeight="1">
       <c r="A18" s="51"/>
@@ -7783,22 +7784,22 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="590" t="s">
+      <c r="C18" s="591" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="589"/>
+      <c r="D18" s="590"/>
       <c r="E18" s="163"/>
-      <c r="F18" s="596">
+      <c r="F18" s="597">
         <f>F15</f>
         <v>0</v>
       </c>
-      <c r="G18" s="630"/>
+      <c r="G18" s="631"/>
       <c r="H18" s="404"/>
-      <c r="I18" s="631">
+      <c r="I18" s="632">
         <f>+F18</f>
         <v>0</v>
       </c>
-      <c r="J18" s="632"/>
+      <c r="J18" s="633"/>
     </row>
     <row r="19" spans="1:10" ht="15.9" customHeight="1">
       <c r="A19" s="51"/>
@@ -7806,16 +7807,16 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="590" t="s">
+      <c r="C19" s="591" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="589"/>
+      <c r="D19" s="590"/>
       <c r="E19" s="163"/>
-      <c r="F19" s="661"/>
-      <c r="G19" s="659"/>
+      <c r="F19" s="662"/>
+      <c r="G19" s="660"/>
       <c r="H19" s="404"/>
-      <c r="I19" s="674"/>
-      <c r="J19" s="675"/>
+      <c r="I19" s="675"/>
+      <c r="J19" s="676"/>
     </row>
     <row r="20" spans="1:10" ht="15.9" customHeight="1">
       <c r="A20" s="51"/>
@@ -7823,10 +7824,10 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="588" t="s">
+      <c r="C20" s="589" t="s">
         <v>88</v>
       </c>
-      <c r="D20" s="589"/>
+      <c r="D20" s="590"/>
       <c r="E20" s="494"/>
       <c r="F20" s="56"/>
       <c r="G20" s="388"/>
@@ -7846,10 +7847,10 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="590" t="s">
+      <c r="C21" s="591" t="s">
         <v>89</v>
       </c>
-      <c r="D21" s="589"/>
+      <c r="D21" s="590"/>
       <c r="E21" s="494"/>
       <c r="F21" s="56">
         <f>Main!B3</f>
@@ -7875,10 +7876,10 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="588" t="s">
+      <c r="C22" s="589" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="589"/>
+      <c r="D22" s="590"/>
       <c r="E22" s="494"/>
       <c r="F22" s="56">
         <v>0</v>
@@ -7902,10 +7903,10 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="590" t="s">
+      <c r="C23" s="591" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="589"/>
+      <c r="D23" s="590"/>
       <c r="E23" s="494"/>
       <c r="F23" s="56">
         <f>+F21+F22</f>
@@ -7931,10 +7932,10 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="590" t="s">
+      <c r="C24" s="591" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="589"/>
+      <c r="D24" s="590"/>
       <c r="E24" s="59"/>
       <c r="F24" s="56"/>
       <c r="G24" s="388">
@@ -7957,10 +7958,10 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="590" t="s">
+      <c r="C25" s="591" t="s">
         <v>93</v>
       </c>
-      <c r="D25" s="589"/>
+      <c r="D25" s="590"/>
       <c r="E25" s="59"/>
       <c r="F25" s="56">
         <v>0</v>
@@ -7985,10 +7986,10 @@
         <f>1+B25</f>
         <v>17</v>
       </c>
-      <c r="C26" s="590" t="s">
+      <c r="C26" s="591" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="589"/>
+      <c r="D26" s="590"/>
       <c r="E26" s="60"/>
       <c r="F26" s="61">
         <f>F25/F23</f>
@@ -8014,10 +8015,10 @@
         <f>1+B26</f>
         <v>18</v>
       </c>
-      <c r="C27" s="588" t="s">
+      <c r="C27" s="589" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="589"/>
+      <c r="D27" s="590"/>
       <c r="E27" s="58"/>
       <c r="F27" s="293">
         <f>'CAPEX and PM'!E3</f>
@@ -8043,10 +8044,10 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="588" t="s">
+      <c r="C28" s="589" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="589"/>
+      <c r="D28" s="590"/>
       <c r="E28" s="64"/>
       <c r="F28" s="64">
         <f>Main!B12</f>
@@ -8072,10 +8073,10 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="588" t="s">
+      <c r="C29" s="589" t="s">
         <v>97</v>
       </c>
-      <c r="D29" s="589"/>
+      <c r="D29" s="590"/>
       <c r="E29" s="64"/>
       <c r="F29" s="60">
         <f>Main!B13</f>
@@ -8101,10 +8102,10 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="590" t="s">
+      <c r="C30" s="591" t="s">
         <v>98</v>
       </c>
-      <c r="D30" s="589"/>
+      <c r="D30" s="590"/>
       <c r="E30" s="58"/>
       <c r="F30" s="56">
         <v>0</v>
@@ -8125,11 +8126,11 @@
     </row>
     <row r="31" spans="1:10" ht="15.9" customHeight="1">
       <c r="A31" s="51"/>
-      <c r="B31" s="676" t="s">
+      <c r="B31" s="677" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="677"/>
-      <c r="D31" s="678"/>
+      <c r="C31" s="678"/>
+      <c r="D31" s="679"/>
       <c r="E31" s="497"/>
       <c r="F31" s="376" t="s">
         <v>75</v>
@@ -8150,10 +8151,10 @@
       <c r="B32" s="162">
         <v>1</v>
       </c>
-      <c r="C32" s="588" t="s">
+      <c r="C32" s="589" t="s">
         <v>100</v>
       </c>
-      <c r="D32" s="589"/>
+      <c r="D32" s="590"/>
       <c r="E32" s="59"/>
       <c r="F32" s="56">
         <f>Main!B9/(Main!B3*Main!B7)</f>
@@ -8179,10 +8180,10 @@
         <f>1+B32</f>
         <v>2</v>
       </c>
-      <c r="C33" s="588" t="s">
+      <c r="C33" s="589" t="s">
         <v>101</v>
       </c>
-      <c r="D33" s="589"/>
+      <c r="D33" s="590"/>
       <c r="E33" s="59"/>
       <c r="F33" s="56">
         <v>0</v>
@@ -8206,10 +8207,10 @@
         <f t="shared" ref="B34:B47" si="1">1+B33</f>
         <v>3</v>
       </c>
-      <c r="C34" s="588" t="s">
+      <c r="C34" s="589" t="s">
         <v>102</v>
       </c>
-      <c r="D34" s="589"/>
+      <c r="D34" s="590"/>
       <c r="E34" s="59"/>
       <c r="F34" s="56">
         <v>0</v>
@@ -8234,10 +8235,10 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="C35" s="590" t="s">
+      <c r="C35" s="591" t="s">
         <v>103</v>
       </c>
-      <c r="D35" s="589"/>
+      <c r="D35" s="590"/>
       <c r="E35" s="498"/>
       <c r="F35" s="68">
         <v>0</v>
@@ -8259,10 +8260,10 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="C36" s="588" t="s">
+      <c r="C36" s="589" t="s">
         <v>104</v>
       </c>
-      <c r="D36" s="589"/>
+      <c r="D36" s="590"/>
       <c r="E36" s="498"/>
       <c r="F36" s="70">
         <f>'Lease Rent'!H37</f>
@@ -8288,10 +8289,10 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="C37" s="588" t="s">
+      <c r="C37" s="589" t="s">
         <v>105</v>
       </c>
-      <c r="D37" s="589"/>
+      <c r="D37" s="590"/>
       <c r="E37" s="498"/>
       <c r="F37" s="70"/>
       <c r="G37" s="204">
@@ -8308,10 +8309,10 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="C38" s="588" t="s">
+      <c r="C38" s="589" t="s">
         <v>106</v>
       </c>
-      <c r="D38" s="589"/>
+      <c r="D38" s="590"/>
       <c r="E38" s="71"/>
       <c r="F38" s="70">
         <f>'Lease Rent'!J31</f>
@@ -8337,10 +8338,10 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="C39" s="588" t="s">
+      <c r="C39" s="589" t="s">
         <v>107</v>
       </c>
-      <c r="D39" s="589"/>
+      <c r="D39" s="590"/>
       <c r="E39" s="498"/>
       <c r="F39" s="70">
         <f>F36</f>
@@ -8366,10 +8367,10 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="C40" s="588" t="s">
+      <c r="C40" s="589" t="s">
         <v>108</v>
       </c>
-      <c r="D40" s="589"/>
+      <c r="D40" s="590"/>
       <c r="E40" s="498"/>
       <c r="F40" s="70">
         <v>0</v>
@@ -8394,10 +8395,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="C41" s="588" t="s">
+      <c r="C41" s="589" t="s">
         <v>109</v>
       </c>
-      <c r="D41" s="589"/>
+      <c r="D41" s="590"/>
       <c r="E41" s="58"/>
       <c r="F41" s="114">
         <f>F38</f>
@@ -8423,10 +8424,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="C42" s="590" t="s">
+      <c r="C42" s="591" t="s">
         <v>110</v>
       </c>
-      <c r="D42" s="589"/>
+      <c r="D42" s="590"/>
       <c r="E42" s="59"/>
       <c r="F42" s="109">
         <v>0</v>
@@ -8451,10 +8452,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="C43" s="590" t="s">
+      <c r="C43" s="591" t="s">
         <v>111</v>
       </c>
-      <c r="D43" s="589"/>
+      <c r="D43" s="590"/>
       <c r="E43" s="73"/>
       <c r="F43" s="68">
         <v>0</v>
@@ -8479,10 +8480,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="C44" s="590" t="s">
+      <c r="C44" s="591" t="s">
         <v>112</v>
       </c>
-      <c r="D44" s="589"/>
+      <c r="D44" s="590"/>
       <c r="E44" s="59"/>
       <c r="F44" s="56">
         <f>'Lease Rent'!C22</f>
@@ -8508,10 +8509,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="C45" s="588" t="s">
+      <c r="C45" s="589" t="s">
         <v>113</v>
       </c>
-      <c r="D45" s="589"/>
+      <c r="D45" s="590"/>
       <c r="E45" s="59"/>
       <c r="F45" s="109">
         <v>0</v>
@@ -8533,10 +8534,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="C46" s="590" t="s">
+      <c r="C46" s="591" t="s">
         <v>111</v>
       </c>
-      <c r="D46" s="589"/>
+      <c r="D46" s="590"/>
       <c r="E46" s="59"/>
       <c r="F46" s="56">
         <f>'Lease Rent'!D23</f>
@@ -8553,10 +8554,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="C47" s="590" t="s">
+      <c r="C47" s="591" t="s">
         <v>112</v>
       </c>
-      <c r="D47" s="589"/>
+      <c r="D47" s="590"/>
       <c r="E47" s="59"/>
       <c r="F47" s="56">
         <f>'Lease Rent'!C23</f>
@@ -8569,46 +8570,46 @@
     </row>
     <row r="48" spans="1:10" ht="28.5" customHeight="1">
       <c r="A48" s="51"/>
-      <c r="B48" s="635">
+      <c r="B48" s="636">
         <f>1+B47</f>
         <v>17</v>
       </c>
-      <c r="C48" s="588" t="s">
+      <c r="C48" s="589" t="s">
         <v>114</v>
       </c>
-      <c r="D48" s="589"/>
+      <c r="D48" s="590"/>
       <c r="E48" s="73"/>
-      <c r="F48" s="681" t="str">
+      <c r="F48" s="682" t="str">
         <f>Main!B14</f>
         <v>15% every 3 years</v>
       </c>
-      <c r="G48" s="682"/>
+      <c r="G48" s="683"/>
       <c r="H48" s="404"/>
-      <c r="I48" s="674" t="str">
+      <c r="I48" s="675" t="str">
         <f>+F48</f>
         <v>15% every 3 years</v>
       </c>
-      <c r="J48" s="675"/>
+      <c r="J48" s="676"/>
     </row>
     <row r="49" spans="1:18" ht="15.9" customHeight="1">
       <c r="A49" s="51"/>
-      <c r="B49" s="636"/>
-      <c r="C49" s="588" t="s">
+      <c r="B49" s="637"/>
+      <c r="C49" s="589" t="s">
         <v>115</v>
       </c>
-      <c r="D49" s="589"/>
+      <c r="D49" s="590"/>
       <c r="E49" s="73"/>
-      <c r="F49" s="681" t="str">
+      <c r="F49" s="682" t="str">
         <f>Main!B15</f>
         <v>5% every years</v>
       </c>
-      <c r="G49" s="682"/>
+      <c r="G49" s="683"/>
       <c r="H49" s="404"/>
-      <c r="I49" s="679" t="str">
+      <c r="I49" s="680" t="str">
         <f t="shared" ref="I49:I56" si="2">F49</f>
         <v>5% every years</v>
       </c>
-      <c r="J49" s="680"/>
+      <c r="J49" s="681"/>
     </row>
     <row r="50" spans="1:18" ht="15.9" customHeight="1">
       <c r="A50" s="51"/>
@@ -8616,22 +8617,22 @@
         <f>1+B48</f>
         <v>18</v>
       </c>
-      <c r="C50" s="590" t="s">
+      <c r="C50" s="591" t="s">
         <v>116</v>
       </c>
-      <c r="D50" s="589"/>
+      <c r="D50" s="590"/>
       <c r="E50" s="73"/>
-      <c r="F50" s="626">
+      <c r="F50" s="627">
         <f>'Lease Rent'!B31</f>
         <v>46023</v>
       </c>
-      <c r="G50" s="627"/>
+      <c r="G50" s="628"/>
       <c r="H50" s="404"/>
-      <c r="I50" s="628">
+      <c r="I50" s="629">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J50" s="629"/>
+      <c r="J50" s="630"/>
     </row>
     <row r="51" spans="1:18" ht="15.9" customHeight="1">
       <c r="A51" s="51"/>
@@ -8639,22 +8640,22 @@
         <f t="shared" ref="B51:B57" si="3">1+B50</f>
         <v>19</v>
       </c>
-      <c r="C51" s="588" t="s">
+      <c r="C51" s="589" t="s">
         <v>117</v>
       </c>
-      <c r="D51" s="589"/>
+      <c r="D51" s="590"/>
       <c r="E51" s="73"/>
-      <c r="F51" s="626">
+      <c r="F51" s="627">
         <f>'Lease Rent'!C102</f>
         <v>48213</v>
       </c>
-      <c r="G51" s="627"/>
+      <c r="G51" s="628"/>
       <c r="H51" s="404"/>
-      <c r="I51" s="628">
+      <c r="I51" s="629">
         <f>F51</f>
         <v>48213</v>
       </c>
-      <c r="J51" s="629"/>
+      <c r="J51" s="630"/>
     </row>
     <row r="52" spans="1:18" ht="15.9" customHeight="1">
       <c r="A52" s="51"/>
@@ -8662,22 +8663,22 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="C52" s="588" t="s">
+      <c r="C52" s="589" t="s">
         <v>118</v>
       </c>
-      <c r="D52" s="598"/>
+      <c r="D52" s="599"/>
       <c r="E52" s="73"/>
-      <c r="F52" s="626">
+      <c r="F52" s="627">
         <f>F50</f>
         <v>46023</v>
       </c>
-      <c r="G52" s="627"/>
+      <c r="G52" s="628"/>
       <c r="H52" s="404"/>
-      <c r="I52" s="628">
+      <c r="I52" s="629">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J52" s="629"/>
+      <c r="J52" s="630"/>
     </row>
     <row r="53" spans="1:18" ht="15.9" customHeight="1">
       <c r="A53" s="51"/>
@@ -8685,21 +8686,21 @@
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="C53" s="588" t="s">
+      <c r="C53" s="589" t="s">
         <v>119</v>
       </c>
-      <c r="D53" s="598"/>
+      <c r="D53" s="599"/>
       <c r="E53" s="73"/>
-      <c r="F53" s="596">
-        <v>0</v>
-      </c>
-      <c r="G53" s="630"/>
+      <c r="F53" s="597">
+        <v>0</v>
+      </c>
+      <c r="G53" s="631"/>
       <c r="H53" s="404"/>
-      <c r="I53" s="631">
+      <c r="I53" s="632">
         <f>+F53</f>
         <v>0</v>
       </c>
-      <c r="J53" s="632"/>
+      <c r="J53" s="633"/>
     </row>
     <row r="54" spans="1:18" ht="15.9" customHeight="1">
       <c r="A54" s="51"/>
@@ -8707,10 +8708,10 @@
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="C54" s="590" t="s">
+      <c r="C54" s="591" t="s">
         <v>120</v>
       </c>
-      <c r="D54" s="589"/>
+      <c r="D54" s="590"/>
       <c r="E54" s="58"/>
       <c r="F54" s="56">
         <f>(F51-F50)/365*12</f>
@@ -8737,10 +8738,10 @@
         <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="C55" s="590" t="s">
+      <c r="C55" s="591" t="s">
         <v>121</v>
       </c>
-      <c r="D55" s="589"/>
+      <c r="D55" s="590"/>
       <c r="E55" s="71"/>
       <c r="F55" s="56">
         <v>0</v>
@@ -8766,10 +8767,10 @@
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="C56" s="590" t="s">
+      <c r="C56" s="591" t="s">
         <v>122</v>
       </c>
-      <c r="D56" s="589"/>
+      <c r="D56" s="590"/>
       <c r="E56" s="71"/>
       <c r="F56" s="302" t="s">
         <v>68</v>
@@ -8795,10 +8796,10 @@
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="C57" s="590" t="s">
+      <c r="C57" s="591" t="s">
         <v>123</v>
       </c>
-      <c r="D57" s="589"/>
+      <c r="D57" s="590"/>
       <c r="E57" s="71"/>
       <c r="F57" s="56"/>
       <c r="G57" s="388"/>
@@ -8813,23 +8814,23 @@
       <c r="C58" s="74"/>
       <c r="D58" s="74"/>
       <c r="E58" s="58"/>
-      <c r="F58" s="596" t="s">
+      <c r="F58" s="597" t="s">
         <v>73</v>
       </c>
-      <c r="G58" s="630"/>
+      <c r="G58" s="631"/>
       <c r="H58" s="404"/>
-      <c r="I58" s="631" t="s">
+      <c r="I58" s="632" t="s">
         <v>67</v>
       </c>
-      <c r="J58" s="632"/>
+      <c r="J58" s="633"/>
     </row>
     <row r="59" spans="1:18" ht="15.9" customHeight="1">
       <c r="A59" s="51"/>
-      <c r="B59" s="633" t="s">
+      <c r="B59" s="634" t="s">
         <v>124</v>
       </c>
-      <c r="C59" s="634"/>
-      <c r="D59" s="634"/>
+      <c r="C59" s="635"/>
+      <c r="D59" s="635"/>
       <c r="E59" s="497"/>
       <c r="F59" s="376" t="s">
         <v>75</v>
@@ -8850,10 +8851,10 @@
       <c r="B60" s="162">
         <v>1</v>
       </c>
-      <c r="C60" s="588" t="s">
+      <c r="C60" s="589" t="s">
         <v>125</v>
       </c>
-      <c r="D60" s="589"/>
+      <c r="D60" s="590"/>
       <c r="E60" s="499"/>
       <c r="F60" s="70">
         <f>C220/F21/F54</f>
@@ -8879,10 +8880,10 @@
         <f>1+B60</f>
         <v>2</v>
       </c>
-      <c r="C61" s="588" t="s">
+      <c r="C61" s="589" t="s">
         <v>126</v>
       </c>
-      <c r="D61" s="589"/>
+      <c r="D61" s="590"/>
       <c r="E61" s="499"/>
       <c r="F61" s="70">
         <v>0</v>
@@ -8906,10 +8907,10 @@
         <f t="shared" ref="B62:B83" si="4">1+B61</f>
         <v>3</v>
       </c>
-      <c r="C62" s="591" t="s">
+      <c r="C62" s="592" t="s">
         <v>127</v>
       </c>
-      <c r="D62" s="592"/>
+      <c r="D62" s="593"/>
       <c r="E62" s="75"/>
       <c r="F62" s="76">
         <f>F60+F61</f>
@@ -8935,10 +8936,10 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="C63" s="588" t="s">
+      <c r="C63" s="589" t="s">
         <v>321</v>
       </c>
-      <c r="D63" s="589"/>
+      <c r="D63" s="590"/>
       <c r="E63" s="56"/>
       <c r="F63" s="54">
         <f>F62*F21</f>
@@ -8964,10 +8965,10 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="C64" s="588" t="s">
+      <c r="C64" s="589" t="s">
         <v>128</v>
       </c>
-      <c r="D64" s="589"/>
+      <c r="D64" s="590"/>
       <c r="E64" s="56"/>
       <c r="F64" s="70">
         <f>I220/F21/F54</f>
@@ -8993,10 +8994,10 @@
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="C65" s="590" t="s">
+      <c r="C65" s="591" t="s">
         <v>322</v>
       </c>
-      <c r="D65" s="589"/>
+      <c r="D65" s="590"/>
       <c r="E65" s="71"/>
       <c r="F65" s="54">
         <f>+F64*F21</f>
@@ -9022,10 +9023,10 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="C66" s="590" t="s">
+      <c r="C66" s="591" t="s">
         <v>323</v>
       </c>
-      <c r="D66" s="589"/>
+      <c r="D66" s="590"/>
       <c r="E66" s="59"/>
       <c r="F66" s="56">
         <f>(+G220/F54)</f>
@@ -9051,10 +9052,10 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="C67" s="590" t="s">
+      <c r="C67" s="591" t="s">
         <v>129</v>
       </c>
-      <c r="D67" s="589"/>
+      <c r="D67" s="590"/>
       <c r="E67" s="56"/>
       <c r="F67" s="56">
         <f>Main!B9</f>
@@ -9080,10 +9081,10 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="C68" s="590" t="s">
+      <c r="C68" s="591" t="s">
         <v>130</v>
       </c>
-      <c r="D68" s="589"/>
+      <c r="D68" s="590"/>
       <c r="E68" s="56"/>
       <c r="F68" s="56">
         <v>0</v>
@@ -9108,10 +9109,10 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="C69" s="588" t="s">
+      <c r="C69" s="589" t="s">
         <v>131</v>
       </c>
-      <c r="D69" s="589"/>
+      <c r="D69" s="590"/>
       <c r="E69" s="56"/>
       <c r="F69" s="56">
         <v>500000</v>
@@ -9136,10 +9137,10 @@
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="C70" s="590" t="s">
+      <c r="C70" s="591" t="s">
         <v>132</v>
       </c>
-      <c r="D70" s="589"/>
+      <c r="D70" s="590"/>
       <c r="E70" s="56"/>
       <c r="F70" s="54">
         <v>0</v>
@@ -9161,10 +9162,10 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="C71" s="590" t="s">
+      <c r="C71" s="591" t="s">
         <v>133</v>
       </c>
-      <c r="D71" s="589"/>
+      <c r="D71" s="590"/>
       <c r="E71" s="56"/>
       <c r="F71" s="54">
         <f>F38*F23*F33</f>
@@ -9190,10 +9191,10 @@
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="C72" s="590" t="s">
+      <c r="C72" s="591" t="s">
         <v>134</v>
       </c>
-      <c r="D72" s="589"/>
+      <c r="D72" s="590"/>
       <c r="E72" s="56"/>
       <c r="F72" s="56">
         <v>0</v>
@@ -9218,10 +9219,10 @@
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="C73" s="588" t="s">
+      <c r="C73" s="589" t="s">
         <v>135</v>
       </c>
-      <c r="D73" s="589"/>
+      <c r="D73" s="590"/>
       <c r="E73" s="498"/>
       <c r="F73" s="68">
         <f>+F35*F63</f>
@@ -9275,10 +9276,10 @@
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="C75" s="588" t="s">
+      <c r="C75" s="589" t="s">
         <v>137</v>
       </c>
-      <c r="D75" s="589"/>
+      <c r="D75" s="590"/>
       <c r="E75" s="59"/>
       <c r="F75" s="56">
         <f>+F77/F23</f>
@@ -9304,10 +9305,10 @@
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="C76" s="588" t="s">
+      <c r="C76" s="589" t="s">
         <v>138</v>
       </c>
-      <c r="D76" s="589"/>
+      <c r="D76" s="590"/>
       <c r="E76" s="71"/>
       <c r="F76" s="51"/>
       <c r="G76" s="493"/>
@@ -9327,10 +9328,10 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="C77" s="588" t="s">
+      <c r="C77" s="589" t="s">
         <v>139</v>
       </c>
-      <c r="D77" s="589"/>
+      <c r="D77" s="590"/>
       <c r="E77" s="71"/>
       <c r="F77" s="56">
         <f>'CAPEX and PM'!B6</f>
@@ -9356,10 +9357,10 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="C78" s="588" t="s">
+      <c r="C78" s="589" t="s">
         <v>140</v>
       </c>
-      <c r="D78" s="589"/>
+      <c r="D78" s="590"/>
       <c r="E78" s="71"/>
       <c r="F78" s="56">
         <f>'CAPEX and PM'!B37</f>
@@ -9385,10 +9386,10 @@
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="C79" s="588" t="s">
+      <c r="C79" s="589" t="s">
         <v>141</v>
       </c>
-      <c r="D79" s="589"/>
+      <c r="D79" s="590"/>
       <c r="E79" s="71"/>
       <c r="F79" s="56">
         <f>+'CAPEX and PM'!B95</f>
@@ -9414,10 +9415,10 @@
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="C80" s="588" t="s">
+      <c r="C80" s="589" t="s">
         <v>142</v>
       </c>
-      <c r="D80" s="589"/>
+      <c r="D80" s="590"/>
       <c r="E80" s="71"/>
       <c r="F80" s="56"/>
       <c r="G80" s="388"/>
@@ -9437,10 +9438,10 @@
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="C81" s="588" t="s">
+      <c r="C81" s="589" t="s">
         <v>143</v>
       </c>
-      <c r="D81" s="598"/>
+      <c r="D81" s="599"/>
       <c r="E81" s="71"/>
       <c r="F81" s="56"/>
       <c r="G81" s="388"/>
@@ -9460,10 +9461,10 @@
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="C82" s="588" t="s">
+      <c r="C82" s="589" t="s">
         <v>144</v>
       </c>
-      <c r="D82" s="589"/>
+      <c r="D82" s="590"/>
       <c r="E82" s="59"/>
       <c r="F82" s="56">
         <f>+G207</f>
@@ -9489,10 +9490,10 @@
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="C83" s="588" t="s">
+      <c r="C83" s="589" t="s">
         <v>324</v>
       </c>
-      <c r="D83" s="589"/>
+      <c r="D83" s="590"/>
       <c r="E83" s="498"/>
       <c r="F83" s="56">
         <f>+F30</f>
@@ -9525,11 +9526,11 @@
     </row>
     <row r="85" spans="1:24" ht="15.9" customHeight="1">
       <c r="A85" s="51"/>
-      <c r="B85" s="610" t="s">
+      <c r="B85" s="611" t="s">
         <v>145</v>
       </c>
-      <c r="C85" s="611"/>
-      <c r="D85" s="612"/>
+      <c r="C85" s="612"/>
+      <c r="D85" s="613"/>
       <c r="E85" s="389"/>
       <c r="F85" s="161" t="s">
         <v>75</v>
@@ -9550,10 +9551,10 @@
       <c r="B86" s="162">
         <v>1</v>
       </c>
-      <c r="C86" s="588" t="s">
+      <c r="C86" s="589" t="s">
         <v>146</v>
       </c>
-      <c r="D86" s="589"/>
+      <c r="D86" s="590"/>
       <c r="E86" s="71"/>
       <c r="F86" s="70">
         <f>+F62</f>
@@ -9582,10 +9583,10 @@
         <f>1+B86</f>
         <v>2</v>
       </c>
-      <c r="C87" s="590" t="s">
+      <c r="C87" s="591" t="s">
         <v>147</v>
       </c>
-      <c r="D87" s="589"/>
+      <c r="D87" s="590"/>
       <c r="E87" s="73"/>
       <c r="F87" s="56">
         <v>0</v>
@@ -9608,10 +9609,10 @@
         <f t="shared" ref="B88:B94" si="7">+B87+1</f>
         <v>3</v>
       </c>
-      <c r="C88" s="590" t="s">
+      <c r="C88" s="591" t="s">
         <v>148</v>
       </c>
-      <c r="D88" s="589"/>
+      <c r="D88" s="590"/>
       <c r="E88" s="73"/>
       <c r="F88" s="70">
         <f>(F66/F23)</f>
@@ -9639,10 +9640,10 @@
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="C89" s="590" t="s">
+      <c r="C89" s="591" t="s">
         <v>149</v>
       </c>
-      <c r="D89" s="589"/>
+      <c r="D89" s="590"/>
       <c r="E89" s="73"/>
       <c r="F89" s="66">
         <f>'Security Deposit'!C17</f>
@@ -9670,10 +9671,10 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="C90" s="590" t="s">
+      <c r="C90" s="591" t="s">
         <v>289</v>
       </c>
-      <c r="D90" s="589"/>
+      <c r="D90" s="590"/>
       <c r="E90" s="73"/>
       <c r="F90" s="202">
         <f>+F64</f>
@@ -9701,10 +9702,10 @@
         <f>+B89+1</f>
         <v>5</v>
       </c>
-      <c r="C91" s="590" t="s">
+      <c r="C91" s="591" t="s">
         <v>150</v>
       </c>
-      <c r="D91" s="589"/>
+      <c r="D91" s="590"/>
       <c r="E91" s="73"/>
       <c r="F91" s="66">
         <f>(+F83/F21/F54)</f>
@@ -9731,10 +9732,10 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="C92" s="590" t="s">
+      <c r="C92" s="591" t="s">
         <v>151</v>
       </c>
-      <c r="D92" s="589"/>
+      <c r="D92" s="590"/>
       <c r="E92" s="73"/>
       <c r="F92" s="66">
         <f>F82/F21/F54</f>
@@ -9762,27 +9763,27 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="C93" s="588" t="s">
+      <c r="C93" s="589" t="s">
         <v>152</v>
       </c>
-      <c r="D93" s="589"/>
+      <c r="D93" s="590"/>
       <c r="E93" s="71"/>
       <c r="F93" s="66">
         <f>+G93/F6</f>
-        <v>26.005950294534241</v>
+        <v>21.957509844757084</v>
       </c>
       <c r="G93" s="202">
         <f>(+SUM(G86:G92)+G103)*7%</f>
-        <v>279.92804897036655</v>
+        <v>236.35063596896524</v>
       </c>
       <c r="H93" s="404"/>
       <c r="I93" s="138">
         <f>+F93/J5</f>
-        <v>0.24762854974799317</v>
+        <v>0.2090793167468776</v>
       </c>
       <c r="J93" s="67">
         <f>I93*I6</f>
-        <v>2.6654737094873981</v>
+        <v>2.2505297654633902</v>
       </c>
       <c r="S93" s="400"/>
       <c r="T93" s="400"/>
@@ -9793,27 +9794,27 @@
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="C94" s="591" t="s">
+      <c r="C94" s="592" t="s">
         <v>69</v>
       </c>
-      <c r="D94" s="592"/>
+      <c r="D94" s="593"/>
       <c r="E94" s="78"/>
       <c r="F94" s="213">
         <f>SUM(F86:F93)</f>
-        <v>203.31648297711658</v>
+        <v>199.26804252733942</v>
       </c>
       <c r="G94" s="54">
         <f>SUM(G86:G93)</f>
-        <v>2188.4986227656827</v>
+        <v>2144.9212097642817</v>
       </c>
       <c r="H94" s="410"/>
       <c r="I94" s="191">
         <f>SUM(I86:I93)</f>
-        <v>1.9359786990774766</v>
+        <v>1.8974294660763611</v>
       </c>
       <c r="J94" s="192">
         <f>SUM(J86:J93)</f>
-        <v>20.838874716869956</v>
+        <v>20.423930772845949</v>
       </c>
       <c r="S94" s="400"/>
       <c r="T94" s="400"/>
@@ -9821,8 +9822,8 @@
     <row r="95" spans="1:24" ht="15.9" customHeight="1">
       <c r="A95" s="51"/>
       <c r="B95" s="381"/>
-      <c r="C95" s="630"/>
-      <c r="D95" s="630"/>
+      <c r="C95" s="631"/>
+      <c r="D95" s="631"/>
       <c r="E95" s="84"/>
       <c r="F95" s="85"/>
       <c r="G95" s="85"/>
@@ -9832,11 +9833,11 @@
     </row>
     <row r="96" spans="1:24" ht="15.9" customHeight="1">
       <c r="A96" s="51"/>
-      <c r="B96" s="593" t="s">
+      <c r="B96" s="594" t="s">
         <v>153</v>
       </c>
-      <c r="C96" s="594"/>
-      <c r="D96" s="594"/>
+      <c r="C96" s="595"/>
+      <c r="D96" s="595"/>
       <c r="E96" s="87"/>
       <c r="F96" s="161" t="s">
         <v>75</v>
@@ -9858,28 +9859,27 @@
       <c r="B97" s="162">
         <v>1</v>
       </c>
-      <c r="C97" s="590" t="str">
+      <c r="C97" s="591" t="str">
         <f>+C76</f>
         <v>Siemens Standard Fitout (Existing)</v>
       </c>
-      <c r="D97" s="589"/>
+      <c r="D97" s="590"/>
       <c r="E97" s="88"/>
       <c r="F97" s="66">
-        <f>'CAPEX and PM'!B29</f>
-        <v>57.834863568245076</v>
+        <v>0</v>
       </c>
       <c r="G97" s="204">
         <f>+F97*F6</f>
-        <v>622.53447144859001</v>
+        <v>0</v>
       </c>
       <c r="H97" s="404"/>
       <c r="I97" s="133">
         <f>F97/J5</f>
-        <v>0.55070332858736504</v>
+        <v>0</v>
       </c>
       <c r="J97" s="57">
         <f>+I97*I6</f>
-        <v>5.9277706289143968</v>
+        <v>0</v>
       </c>
       <c r="Z97" s="465"/>
     </row>
@@ -9889,11 +9889,11 @@
         <f t="shared" ref="B98:B103" si="8">+B97+1</f>
         <v>2</v>
       </c>
-      <c r="C98" s="590" t="str">
+      <c r="C98" s="591" t="str">
         <f>+C77</f>
         <v>Siemens Standard Fitout (New)</v>
       </c>
-      <c r="D98" s="589"/>
+      <c r="D98" s="590"/>
       <c r="E98" s="71"/>
       <c r="F98" s="66">
         <f>'CAPEX and PM'!B29</f>
@@ -9921,11 +9921,11 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="C99" s="590" t="str">
+      <c r="C99" s="591" t="str">
         <f>+C78</f>
         <v>Capex over the period of lease period</v>
       </c>
-      <c r="D99" s="589"/>
+      <c r="D99" s="590"/>
       <c r="E99" s="71"/>
       <c r="F99" s="66">
         <f>'CAPEX and PM'!B89</f>
@@ -9953,11 +9953,11 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="C100" s="590" t="str">
+      <c r="C100" s="591" t="str">
         <f>+C79</f>
         <v>PM cost over the period of lease period</v>
       </c>
-      <c r="D100" s="589"/>
+      <c r="D100" s="590"/>
       <c r="E100" s="71"/>
       <c r="F100" s="66">
         <f>+'CAPEX and PM'!B96</f>
@@ -9985,11 +9985,11 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="C101" s="590" t="str">
+      <c r="C101" s="591" t="str">
         <f>+C80</f>
         <v>Asset Retirement Obligation ( Removal &amp; Restoration Obligation)</v>
       </c>
-      <c r="D101" s="589"/>
+      <c r="D101" s="590"/>
       <c r="E101" s="71"/>
       <c r="F101" s="66">
         <f>'Security Deposit'!D25</f>
@@ -10020,10 +10020,10 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="C102" s="588" t="s">
+      <c r="C102" s="589" t="s">
         <v>154</v>
       </c>
-      <c r="D102" s="589"/>
+      <c r="D102" s="590"/>
       <c r="E102" s="73"/>
       <c r="F102" s="66">
         <f>+F81/F21/F27</f>
@@ -10051,27 +10051,27 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="C103" s="591" t="s">
+      <c r="C103" s="592" t="s">
         <v>155</v>
       </c>
-      <c r="D103" s="592"/>
+      <c r="D103" s="593"/>
       <c r="E103" s="78"/>
       <c r="F103" s="54">
         <f>SUM(F97:F102)</f>
-        <v>194.20304295362101</v>
+        <v>136.36817938537592</v>
       </c>
       <c r="G103" s="54">
         <f>SUM(G97:G102)</f>
-        <v>2090.4015543527767</v>
+        <v>1467.8670829041866</v>
       </c>
       <c r="H103" s="404"/>
       <c r="I103" s="139">
         <f>SUM(I97:I102)</f>
-        <v>1.8492005613561322</v>
+        <v>1.2984972327687672</v>
       </c>
       <c r="J103" s="139">
         <f>SUM(J97:J102)</f>
-        <v>19.904794842437404</v>
+        <v>13.977024213523011</v>
       </c>
       <c r="S103" s="400"/>
       <c r="T103" s="400"/>
@@ -10091,11 +10091,11 @@
     </row>
     <row r="105" spans="1:26" ht="15.9" customHeight="1">
       <c r="A105" s="51"/>
-      <c r="B105" s="684" t="s">
+      <c r="B105" s="685" t="s">
         <v>156</v>
       </c>
-      <c r="C105" s="605"/>
-      <c r="D105" s="605"/>
+      <c r="C105" s="606"/>
+      <c r="D105" s="606"/>
       <c r="E105" s="87"/>
       <c r="F105" s="161" t="s">
         <v>75</v>
@@ -10116,27 +10116,27 @@
       <c r="B106" s="162">
         <v>1</v>
       </c>
-      <c r="C106" s="588" t="s">
+      <c r="C106" s="589" t="s">
         <v>69</v>
       </c>
-      <c r="D106" s="589"/>
+      <c r="D106" s="590"/>
       <c r="E106" s="71"/>
       <c r="F106" s="56">
         <f>+F94</f>
-        <v>203.31648297711658</v>
+        <v>199.26804252733942</v>
       </c>
       <c r="G106" s="56">
         <f>+G94</f>
-        <v>2188.4986227656827</v>
+        <v>2144.9212097642817</v>
       </c>
       <c r="H106" s="404"/>
       <c r="I106" s="136">
         <f>+I94</f>
-        <v>1.9359786990774766</v>
+        <v>1.8974294660763611</v>
       </c>
       <c r="J106" s="72">
         <f>+J94</f>
-        <v>20.838874716869956</v>
+        <v>20.423930772845949</v>
       </c>
       <c r="S106" s="400"/>
       <c r="T106" s="400"/>
@@ -10147,27 +10147,27 @@
         <f>+B106+1</f>
         <v>2</v>
       </c>
-      <c r="C107" s="588" t="s">
+      <c r="C107" s="589" t="s">
         <v>155</v>
       </c>
-      <c r="D107" s="598"/>
+      <c r="D107" s="599"/>
       <c r="E107" s="71"/>
       <c r="F107" s="56">
         <f>+F103</f>
-        <v>194.20304295362101</v>
+        <v>136.36817938537592</v>
       </c>
       <c r="G107" s="388">
         <f>+G103</f>
-        <v>2090.4015543527767</v>
+        <v>1467.8670829041866</v>
       </c>
       <c r="H107" s="404"/>
       <c r="I107" s="136">
         <f>+I103</f>
-        <v>1.8492005613561322</v>
+        <v>1.2984972327687672</v>
       </c>
       <c r="J107" s="72">
         <f>+J103</f>
-        <v>19.904794842437404</v>
+        <v>13.977024213523011</v>
       </c>
       <c r="S107" s="400"/>
       <c r="W107" s="463"/>
@@ -10178,27 +10178,27 @@
         <f>+B107+1</f>
         <v>3</v>
       </c>
-      <c r="C108" s="591" t="s">
+      <c r="C108" s="592" t="s">
         <v>157</v>
       </c>
-      <c r="D108" s="592"/>
+      <c r="D108" s="593"/>
       <c r="E108" s="78"/>
       <c r="F108" s="54">
         <f>SUM(F106:F107)</f>
-        <v>397.51952593073759</v>
+        <v>335.63622191271531</v>
       </c>
       <c r="G108" s="54">
         <f>SUM(G106:G107)</f>
-        <v>4278.9001771184594</v>
+        <v>3612.7882926684683</v>
       </c>
       <c r="H108" s="404"/>
       <c r="I108" s="191">
         <f>SUM(I106:I107)</f>
-        <v>3.7851792604336087</v>
+        <v>3.1959266988451285</v>
       </c>
       <c r="J108" s="82">
         <f>SUM(J106:J107)</f>
-        <v>40.743669559307364</v>
+        <v>34.400954986368959</v>
       </c>
       <c r="S108" s="400"/>
       <c r="T108" s="400"/>
@@ -10210,11 +10210,11 @@
     </row>
     <row r="109" spans="1:26" ht="15.9" customHeight="1">
       <c r="A109" s="51"/>
-      <c r="B109" s="593" t="s">
+      <c r="B109" s="594" t="s">
         <v>158</v>
       </c>
-      <c r="C109" s="594"/>
-      <c r="D109" s="594"/>
+      <c r="C109" s="595"/>
+      <c r="D109" s="595"/>
       <c r="E109" s="89"/>
       <c r="F109" s="161" t="s">
         <v>75</v>
@@ -10236,10 +10236,10 @@
       <c r="B110" s="249">
         <v>1</v>
       </c>
-      <c r="C110" s="588" t="s">
+      <c r="C110" s="589" t="s">
         <v>159</v>
       </c>
-      <c r="D110" s="598"/>
+      <c r="D110" s="599"/>
       <c r="E110" s="83"/>
       <c r="F110" s="376"/>
       <c r="G110" s="376"/>
@@ -10253,10 +10253,10 @@
         <f t="shared" ref="B111:B119" si="9">1+B110</f>
         <v>2</v>
       </c>
-      <c r="C111" s="588" t="s">
+      <c r="C111" s="589" t="s">
         <v>160</v>
       </c>
-      <c r="D111" s="598"/>
+      <c r="D111" s="599"/>
       <c r="E111" s="83"/>
       <c r="F111" s="376"/>
       <c r="G111" s="376"/>
@@ -10272,10 +10272,10 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="C112" s="588" t="s">
+      <c r="C112" s="589" t="s">
         <v>161</v>
       </c>
-      <c r="D112" s="598"/>
+      <c r="D112" s="599"/>
       <c r="E112" s="83"/>
       <c r="F112" s="388">
         <f>+F64*0</f>
@@ -10303,10 +10303,10 @@
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="C113" s="588" t="s">
+      <c r="C113" s="589" t="s">
         <v>162</v>
       </c>
-      <c r="D113" s="598"/>
+      <c r="D113" s="599"/>
       <c r="E113" s="83"/>
       <c r="F113" s="376"/>
       <c r="G113" s="376"/>
@@ -10320,10 +10320,10 @@
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="C114" s="588" t="s">
+      <c r="C114" s="589" t="s">
         <v>163</v>
       </c>
-      <c r="D114" s="598"/>
+      <c r="D114" s="599"/>
       <c r="E114" s="83"/>
       <c r="F114" s="376"/>
       <c r="G114" s="376"/>
@@ -10337,10 +10337,10 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="C115" s="588" t="s">
+      <c r="C115" s="589" t="s">
         <v>164</v>
       </c>
-      <c r="D115" s="598"/>
+      <c r="D115" s="599"/>
       <c r="E115" s="83"/>
       <c r="F115" s="376"/>
       <c r="G115" s="376"/>
@@ -10354,10 +10354,10 @@
         <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="C116" s="588" t="s">
+      <c r="C116" s="589" t="s">
         <v>165</v>
       </c>
-      <c r="D116" s="598"/>
+      <c r="D116" s="599"/>
       <c r="E116" s="83"/>
       <c r="F116" s="376"/>
       <c r="G116" s="376"/>
@@ -10371,10 +10371,10 @@
         <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="C117" s="588" t="s">
+      <c r="C117" s="589" t="s">
         <v>166</v>
       </c>
-      <c r="D117" s="589"/>
+      <c r="D117" s="590"/>
       <c r="E117" s="252"/>
       <c r="F117" s="360">
         <v>654</v>
@@ -10400,10 +10400,10 @@
         <f t="shared" si="9"/>
         <v>9</v>
       </c>
-      <c r="C118" s="588" t="s">
+      <c r="C118" s="589" t="s">
         <v>167</v>
       </c>
-      <c r="D118" s="598"/>
+      <c r="D118" s="599"/>
       <c r="E118" s="252"/>
       <c r="F118" s="90"/>
       <c r="G118" s="90">
@@ -10426,10 +10426,10 @@
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="C119" s="591" t="s">
+      <c r="C119" s="592" t="s">
         <v>168</v>
       </c>
-      <c r="D119" s="592"/>
+      <c r="D119" s="593"/>
       <c r="E119" s="253"/>
       <c r="F119" s="54">
         <f>SUM(F110:F118)</f>
@@ -10455,8 +10455,8 @@
     <row r="120" spans="1:26" ht="15.9" customHeight="1">
       <c r="A120" s="77"/>
       <c r="B120" s="162"/>
-      <c r="C120" s="596"/>
-      <c r="D120" s="597"/>
+      <c r="C120" s="597"/>
+      <c r="D120" s="598"/>
       <c r="E120" s="78"/>
       <c r="F120" s="54"/>
       <c r="G120" s="385"/>
@@ -10470,11 +10470,11 @@
     </row>
     <row r="121" spans="1:26" ht="15.9" customHeight="1">
       <c r="A121" s="77"/>
-      <c r="B121" s="593" t="s">
+      <c r="B121" s="594" t="s">
         <v>169</v>
       </c>
-      <c r="C121" s="594"/>
-      <c r="D121" s="594"/>
+      <c r="C121" s="595"/>
+      <c r="D121" s="595"/>
       <c r="E121" s="89"/>
       <c r="F121" s="161" t="s">
         <v>75</v>
@@ -10497,10 +10497,10 @@
       <c r="B122" s="251">
         <v>1</v>
       </c>
-      <c r="C122" s="588" t="s">
+      <c r="C122" s="589" t="s">
         <v>170</v>
       </c>
-      <c r="D122" s="598"/>
+      <c r="D122" s="599"/>
       <c r="E122" s="78"/>
       <c r="F122" s="54"/>
       <c r="G122" s="385"/>
@@ -10513,10 +10513,10 @@
       <c r="B123" s="162">
         <v>2</v>
       </c>
-      <c r="C123" s="591" t="s">
+      <c r="C123" s="592" t="s">
         <v>171</v>
       </c>
-      <c r="D123" s="592"/>
+      <c r="D123" s="593"/>
       <c r="E123" s="78"/>
       <c r="F123" s="54">
         <f>SUM(F122)</f>
@@ -10539,8 +10539,8 @@
     <row r="124" spans="1:26" ht="15.9" customHeight="1">
       <c r="A124" s="77"/>
       <c r="B124" s="162"/>
-      <c r="C124" s="596"/>
-      <c r="D124" s="597"/>
+      <c r="C124" s="597"/>
+      <c r="D124" s="598"/>
       <c r="E124" s="63"/>
       <c r="F124" s="54"/>
       <c r="G124" s="385"/>
@@ -10550,11 +10550,11 @@
     </row>
     <row r="125" spans="1:26" ht="15.9" customHeight="1">
       <c r="A125" s="77"/>
-      <c r="B125" s="593" t="s">
+      <c r="B125" s="594" t="s">
         <v>172</v>
       </c>
-      <c r="C125" s="594"/>
-      <c r="D125" s="594"/>
+      <c r="C125" s="595"/>
+      <c r="D125" s="595"/>
       <c r="E125" s="89"/>
       <c r="F125" s="161" t="s">
         <v>75</v>
@@ -10575,10 +10575,10 @@
       <c r="B126" s="249">
         <v>1</v>
       </c>
-      <c r="C126" s="588" t="s">
+      <c r="C126" s="589" t="s">
         <v>173</v>
       </c>
-      <c r="D126" s="598"/>
+      <c r="D126" s="599"/>
       <c r="E126" s="250"/>
       <c r="F126" s="385"/>
       <c r="G126" s="385"/>
@@ -10592,10 +10592,10 @@
         <f>1+B126</f>
         <v>2</v>
       </c>
-      <c r="C127" s="588" t="s">
+      <c r="C127" s="589" t="s">
         <v>174</v>
       </c>
-      <c r="D127" s="598"/>
+      <c r="D127" s="599"/>
       <c r="E127" s="250"/>
       <c r="F127" s="385"/>
       <c r="G127" s="385"/>
@@ -10609,10 +10609,10 @@
         <f>1+B127</f>
         <v>3</v>
       </c>
-      <c r="C128" s="588" t="s">
+      <c r="C128" s="589" t="s">
         <v>175</v>
       </c>
-      <c r="D128" s="598"/>
+      <c r="D128" s="599"/>
       <c r="E128" s="250"/>
       <c r="F128" s="385"/>
       <c r="G128" s="385"/>
@@ -10626,10 +10626,10 @@
         <f>1+B128</f>
         <v>4</v>
       </c>
-      <c r="C129" s="588" t="s">
+      <c r="C129" s="589" t="s">
         <v>176</v>
       </c>
-      <c r="D129" s="598"/>
+      <c r="D129" s="599"/>
       <c r="E129" s="250"/>
       <c r="F129" s="385"/>
       <c r="G129" s="385"/>
@@ -10643,10 +10643,10 @@
         <f>1+B129</f>
         <v>5</v>
       </c>
-      <c r="C130" s="588" t="s">
+      <c r="C130" s="589" t="s">
         <v>177</v>
       </c>
-      <c r="D130" s="598"/>
+      <c r="D130" s="599"/>
       <c r="E130" s="250"/>
       <c r="F130" s="385"/>
       <c r="G130" s="385"/>
@@ -10660,10 +10660,10 @@
         <f>1+B130</f>
         <v>6</v>
       </c>
-      <c r="C131" s="588" t="s">
+      <c r="C131" s="589" t="s">
         <v>178</v>
       </c>
-      <c r="D131" s="598"/>
+      <c r="D131" s="599"/>
       <c r="E131" s="250"/>
       <c r="F131" s="385"/>
       <c r="G131" s="385"/>
@@ -10676,10 +10676,10 @@
       <c r="B132" s="381">
         <v>7</v>
       </c>
-      <c r="C132" s="591" t="s">
+      <c r="C132" s="592" t="s">
         <v>179</v>
       </c>
-      <c r="D132" s="592"/>
+      <c r="D132" s="593"/>
       <c r="E132" s="250"/>
       <c r="F132" s="385">
         <f>SUM(F126:F131)</f>
@@ -10702,8 +10702,8 @@
     <row r="133" spans="1:20" ht="15.9" customHeight="1">
       <c r="A133" s="77"/>
       <c r="B133" s="162"/>
-      <c r="C133" s="630"/>
-      <c r="D133" s="597"/>
+      <c r="C133" s="631"/>
+      <c r="D133" s="598"/>
       <c r="E133" s="250"/>
       <c r="F133" s="385"/>
       <c r="G133" s="385"/>
@@ -10713,11 +10713,11 @@
     </row>
     <row r="134" spans="1:20" ht="15.9" customHeight="1">
       <c r="A134" s="51"/>
-      <c r="B134" s="593" t="s">
+      <c r="B134" s="594" t="s">
         <v>180</v>
       </c>
-      <c r="C134" s="594"/>
-      <c r="D134" s="594"/>
+      <c r="C134" s="595"/>
+      <c r="D134" s="595"/>
       <c r="E134" s="89"/>
       <c r="F134" s="161" t="s">
         <v>75</v>
@@ -10738,27 +10738,27 @@
       <c r="B135" s="162">
         <v>1</v>
       </c>
-      <c r="C135" s="591" t="s">
+      <c r="C135" s="592" t="s">
         <v>181</v>
       </c>
-      <c r="D135" s="592"/>
+      <c r="D135" s="593"/>
       <c r="E135" s="78"/>
       <c r="F135" s="54">
         <f>F119+F108+F123+F132</f>
-        <v>1051.5195259307375</v>
+        <v>989.63622191271531</v>
       </c>
       <c r="G135" s="385">
         <f>G119+G108+G123+G132</f>
-        <v>4978.6801771184591</v>
+        <v>4312.5682926684685</v>
       </c>
       <c r="H135" s="404"/>
       <c r="I135" s="191">
         <f>I119+I108+I123+I132</f>
-        <v>10.012564520384094</v>
+        <v>9.4233119587956153</v>
       </c>
       <c r="J135" s="192">
         <f>J119+J108+J123+J132</f>
-        <v>47.406971787454381</v>
+        <v>41.064257214515976</v>
       </c>
       <c r="S135" s="408"/>
       <c r="T135" s="406"/>
@@ -10766,8 +10766,8 @@
     <row r="136" spans="1:20" ht="15.9" customHeight="1">
       <c r="A136" s="77"/>
       <c r="B136" s="162"/>
-      <c r="C136" s="596"/>
-      <c r="D136" s="597"/>
+      <c r="C136" s="597"/>
+      <c r="D136" s="598"/>
       <c r="E136" s="78"/>
       <c r="F136" s="54"/>
       <c r="G136" s="385"/>
@@ -10781,23 +10781,23 @@
       <c r="C137" s="380"/>
       <c r="D137" s="377"/>
       <c r="E137" s="167"/>
-      <c r="F137" s="596" t="s">
+      <c r="F137" s="597" t="s">
         <v>73</v>
       </c>
-      <c r="G137" s="630"/>
+      <c r="G137" s="631"/>
       <c r="H137" s="404"/>
-      <c r="I137" s="631" t="s">
+      <c r="I137" s="632" t="s">
         <v>67</v>
       </c>
-      <c r="J137" s="632"/>
+      <c r="J137" s="633"/>
     </row>
     <row r="138" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A138" s="51"/>
-      <c r="B138" s="593" t="s">
+      <c r="B138" s="594" t="s">
         <v>182</v>
       </c>
-      <c r="C138" s="594"/>
-      <c r="D138" s="595"/>
+      <c r="C138" s="595"/>
+      <c r="D138" s="596"/>
       <c r="E138" s="161"/>
       <c r="F138" s="161" t="s">
         <v>75</v>
@@ -10816,8 +10816,8 @@
     <row r="139" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A139" s="51"/>
       <c r="B139" s="91"/>
-      <c r="C139" s="599"/>
-      <c r="D139" s="600"/>
+      <c r="C139" s="600"/>
+      <c r="D139" s="601"/>
       <c r="E139" s="163"/>
       <c r="F139" s="54"/>
       <c r="G139" s="385"/>
@@ -10828,10 +10828,10 @@
     <row r="140" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A140" s="51"/>
       <c r="B140" s="91"/>
-      <c r="C140" s="588" t="s">
+      <c r="C140" s="589" t="s">
         <v>183</v>
       </c>
-      <c r="D140" s="589"/>
+      <c r="D140" s="590"/>
       <c r="E140" s="58"/>
       <c r="F140" s="243">
         <f>F21</f>
@@ -10854,10 +10854,10 @@
     <row r="141" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A141" s="51"/>
       <c r="B141" s="91"/>
-      <c r="C141" s="590" t="s">
+      <c r="C141" s="591" t="s">
         <v>184</v>
       </c>
-      <c r="D141" s="589"/>
+      <c r="D141" s="590"/>
       <c r="E141" s="59"/>
       <c r="F141" s="56">
         <f>F24</f>
@@ -10880,10 +10880,10 @@
     <row r="142" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A142" s="51"/>
       <c r="B142" s="91"/>
-      <c r="C142" s="590" t="s">
+      <c r="C142" s="591" t="s">
         <v>185</v>
       </c>
-      <c r="D142" s="589"/>
+      <c r="D142" s="590"/>
       <c r="E142" s="73"/>
       <c r="F142" s="56" t="e">
         <f>+#REF!</f>
@@ -10906,36 +10906,36 @@
     <row r="143" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A143" s="51"/>
       <c r="B143" s="91"/>
-      <c r="C143" s="588" t="s">
+      <c r="C143" s="589" t="s">
         <v>186</v>
       </c>
-      <c r="D143" s="589"/>
+      <c r="D143" s="590"/>
       <c r="E143" s="73"/>
       <c r="F143" s="56">
         <f>F108</f>
-        <v>397.51952593073759</v>
+        <v>335.63622191271531</v>
       </c>
       <c r="G143" s="388">
         <f>+G108</f>
-        <v>4278.9001771184594</v>
+        <v>3612.7882926684683</v>
       </c>
       <c r="H143" s="404"/>
       <c r="I143" s="133">
         <f>I108</f>
-        <v>3.7851792604336087</v>
+        <v>3.1959266988451285</v>
       </c>
       <c r="J143" s="72">
         <f>+J108</f>
-        <v>40.743669559307364</v>
+        <v>34.400954986368959</v>
       </c>
     </row>
     <row r="144" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A144" s="51"/>
       <c r="B144" s="91"/>
-      <c r="C144" s="618" t="s">
+      <c r="C144" s="619" t="s">
         <v>187</v>
       </c>
-      <c r="D144" s="619"/>
+      <c r="D144" s="620"/>
       <c r="E144" s="92"/>
       <c r="F144" s="93">
         <f>F119</f>
@@ -10958,10 +10958,10 @@
     <row r="145" spans="1:10" ht="15.9" hidden="1" customHeight="1">
       <c r="A145" s="77"/>
       <c r="B145" s="162"/>
-      <c r="C145" s="591" t="s">
+      <c r="C145" s="592" t="s">
         <v>188</v>
       </c>
-      <c r="D145" s="592"/>
+      <c r="D145" s="593"/>
       <c r="E145" s="78"/>
       <c r="F145" s="245" t="e">
         <f>F135*#REF!</f>
@@ -10995,11 +10995,11 @@
     </row>
     <row r="147" spans="1:10" ht="15.9" customHeight="1">
       <c r="A147" s="77"/>
-      <c r="B147" s="593" t="s">
+      <c r="B147" s="594" t="s">
         <v>189</v>
       </c>
-      <c r="C147" s="594"/>
-      <c r="D147" s="595"/>
+      <c r="C147" s="595"/>
+      <c r="D147" s="596"/>
       <c r="E147" s="379"/>
       <c r="F147" s="379" t="s">
         <v>190</v>
@@ -11018,8 +11018,8 @@
     <row r="148" spans="1:10" ht="15.9" customHeight="1">
       <c r="A148" s="51"/>
       <c r="B148" s="99"/>
-      <c r="C148" s="599"/>
-      <c r="D148" s="600"/>
+      <c r="C148" s="600"/>
+      <c r="D148" s="601"/>
       <c r="E148" s="100"/>
       <c r="F148" s="101"/>
       <c r="G148" s="209"/>
@@ -11030,10 +11030,10 @@
     <row r="149" spans="1:10" ht="15.9" customHeight="1">
       <c r="A149" s="51"/>
       <c r="B149" s="99"/>
-      <c r="C149" s="590" t="s">
+      <c r="C149" s="591" t="s">
         <v>191</v>
       </c>
-      <c r="D149" s="589"/>
+      <c r="D149" s="590"/>
       <c r="E149" s="100"/>
       <c r="F149" s="101">
         <f>(+F63)*115%</f>
@@ -11056,10 +11056,10 @@
     <row r="150" spans="1:10" ht="15.9" customHeight="1">
       <c r="A150" s="51"/>
       <c r="B150" s="99"/>
-      <c r="C150" s="590" t="s">
+      <c r="C150" s="591" t="s">
         <v>192</v>
       </c>
-      <c r="D150" s="589"/>
+      <c r="D150" s="590"/>
       <c r="E150" s="100"/>
       <c r="F150" s="101">
         <v>0</v>
@@ -11078,10 +11078,10 @@
     <row r="151" spans="1:10" ht="15.9" customHeight="1">
       <c r="A151" s="51"/>
       <c r="B151" s="99"/>
-      <c r="C151" s="590" t="s">
+      <c r="C151" s="591" t="s">
         <v>193</v>
       </c>
-      <c r="D151" s="589"/>
+      <c r="D151" s="590"/>
       <c r="E151" s="100"/>
       <c r="F151" s="101">
         <f>(+F65)*115%</f>
@@ -11104,10 +11104,10 @@
     <row r="152" spans="1:10" ht="15.9" customHeight="1">
       <c r="A152" s="51"/>
       <c r="B152" s="99"/>
-      <c r="C152" s="590" t="s">
+      <c r="C152" s="591" t="s">
         <v>194</v>
       </c>
-      <c r="D152" s="589"/>
+      <c r="D152" s="590"/>
       <c r="E152" s="100"/>
       <c r="F152" s="101">
         <f>(+F66)*115%</f>
@@ -11130,10 +11130,10 @@
     <row r="153" spans="1:10" ht="15.9" customHeight="1">
       <c r="A153" s="51"/>
       <c r="B153" s="99"/>
-      <c r="C153" s="588" t="s">
+      <c r="C153" s="589" t="s">
         <v>195</v>
       </c>
-      <c r="D153" s="589"/>
+      <c r="D153" s="590"/>
       <c r="E153" s="103"/>
       <c r="F153" s="104">
         <f>SUM(F149:F152)</f>
@@ -11156,10 +11156,10 @@
     <row r="154" spans="1:10" ht="15.9" customHeight="1">
       <c r="A154" s="51"/>
       <c r="B154" s="99"/>
-      <c r="C154" s="588" t="s">
+      <c r="C154" s="589" t="s">
         <v>196</v>
       </c>
-      <c r="D154" s="589"/>
+      <c r="D154" s="590"/>
       <c r="E154" s="105"/>
       <c r="F154" s="101">
         <f>+F153*12</f>
@@ -11182,8 +11182,8 @@
     <row r="155" spans="1:10" ht="15.9" customHeight="1">
       <c r="A155" s="51"/>
       <c r="B155" s="99"/>
-      <c r="C155" s="599"/>
-      <c r="D155" s="600"/>
+      <c r="C155" s="600"/>
+      <c r="D155" s="601"/>
       <c r="E155" s="105"/>
       <c r="F155" s="101"/>
       <c r="G155" s="209"/>
@@ -11193,11 +11193,11 @@
     </row>
     <row r="156" spans="1:10" ht="15.9" customHeight="1">
       <c r="A156" s="51"/>
-      <c r="B156" s="593" t="s">
+      <c r="B156" s="594" t="s">
         <v>197</v>
       </c>
-      <c r="C156" s="594"/>
-      <c r="D156" s="595"/>
+      <c r="C156" s="595"/>
+      <c r="D156" s="596"/>
       <c r="E156" s="375"/>
       <c r="F156" s="379" t="s">
         <v>190</v>
@@ -11216,8 +11216,8 @@
     <row r="157" spans="1:10" ht="15.9" customHeight="1">
       <c r="A157" s="51"/>
       <c r="B157" s="99"/>
-      <c r="C157" s="599"/>
-      <c r="D157" s="600"/>
+      <c r="C157" s="600"/>
+      <c r="D157" s="601"/>
       <c r="E157" s="105"/>
       <c r="F157" s="101"/>
       <c r="G157" s="209"/>
@@ -11228,10 +11228,10 @@
     <row r="158" spans="1:10" ht="15.9" customHeight="1">
       <c r="A158" s="51"/>
       <c r="B158" s="99"/>
-      <c r="C158" s="616" t="s">
+      <c r="C158" s="617" t="s">
         <v>198</v>
       </c>
-      <c r="D158" s="617"/>
+      <c r="D158" s="618"/>
       <c r="E158" s="105"/>
       <c r="F158" s="101">
         <f t="shared" ref="F158:G160" si="10">+F77</f>
@@ -11254,10 +11254,10 @@
     <row r="159" spans="1:10" ht="15.9" customHeight="1">
       <c r="A159" s="51"/>
       <c r="B159" s="99"/>
-      <c r="C159" s="588" t="s">
+      <c r="C159" s="589" t="s">
         <v>199</v>
       </c>
-      <c r="D159" s="598"/>
+      <c r="D159" s="599"/>
       <c r="E159" s="105"/>
       <c r="F159" s="101">
         <f t="shared" si="10"/>
@@ -11280,10 +11280,10 @@
     <row r="160" spans="1:10" ht="15.9" customHeight="1">
       <c r="A160" s="51"/>
       <c r="B160" s="99"/>
-      <c r="C160" s="588" t="s">
+      <c r="C160" s="589" t="s">
         <v>200</v>
       </c>
-      <c r="D160" s="598"/>
+      <c r="D160" s="599"/>
       <c r="E160" s="105"/>
       <c r="F160" s="101">
         <f t="shared" si="10"/>
@@ -11306,10 +11306,10 @@
     <row r="161" spans="1:22" ht="15.9" customHeight="1">
       <c r="A161" s="51"/>
       <c r="B161" s="99"/>
-      <c r="C161" s="591" t="s">
+      <c r="C161" s="592" t="s">
         <v>29</v>
       </c>
-      <c r="D161" s="592"/>
+      <c r="D161" s="593"/>
       <c r="E161" s="105"/>
       <c r="F161" s="237">
         <f>SUM(F158:F160)</f>
@@ -11332,8 +11332,8 @@
     <row r="162" spans="1:22" ht="15.9" customHeight="1">
       <c r="A162" s="51"/>
       <c r="B162" s="99"/>
-      <c r="C162" s="599"/>
-      <c r="D162" s="600"/>
+      <c r="C162" s="600"/>
+      <c r="D162" s="601"/>
       <c r="E162" s="105"/>
       <c r="F162" s="101"/>
       <c r="G162" s="209"/>
@@ -11343,12 +11343,12 @@
     </row>
     <row r="163" spans="1:22" ht="15.9" customHeight="1">
       <c r="A163" s="106"/>
-      <c r="B163" s="610" t="s">
+      <c r="B163" s="611" t="s">
         <v>201</v>
       </c>
-      <c r="C163" s="611"/>
-      <c r="D163" s="612"/>
-      <c r="E163" s="683"/>
+      <c r="C163" s="612"/>
+      <c r="D163" s="613"/>
+      <c r="E163" s="684"/>
       <c r="F163" s="161" t="s">
         <v>75</v>
       </c>
@@ -11365,10 +11365,10 @@
     </row>
     <row r="164" spans="1:22" ht="15.9" customHeight="1">
       <c r="A164" s="106"/>
-      <c r="B164" s="613"/>
-      <c r="C164" s="614"/>
-      <c r="D164" s="615"/>
-      <c r="E164" s="603"/>
+      <c r="B164" s="614"/>
+      <c r="C164" s="615"/>
+      <c r="D164" s="616"/>
+      <c r="E164" s="604"/>
       <c r="F164" s="161" t="s">
         <v>73</v>
       </c>
@@ -11386,8 +11386,8 @@
     <row r="165" spans="1:22" ht="15.9" customHeight="1">
       <c r="A165" s="107"/>
       <c r="B165" s="99"/>
-      <c r="C165" s="599"/>
-      <c r="D165" s="600"/>
+      <c r="C165" s="600"/>
+      <c r="D165" s="601"/>
       <c r="E165" s="59"/>
       <c r="F165" s="56"/>
       <c r="G165" s="388"/>
@@ -11398,83 +11398,83 @@
     <row r="166" spans="1:22" ht="15.9" customHeight="1">
       <c r="A166" s="107"/>
       <c r="B166" s="99"/>
-      <c r="C166" s="601" t="str">
+      <c r="C166" s="602" t="str">
         <f>+C106</f>
         <v>Net Rent I</v>
       </c>
-      <c r="D166" s="602"/>
+      <c r="D166" s="603"/>
       <c r="E166" s="59"/>
       <c r="F166" s="56">
         <f>+F106</f>
-        <v>203.31648297711658</v>
+        <v>199.26804252733942</v>
       </c>
       <c r="G166" s="388">
         <f>+G106</f>
-        <v>2188.4986227656827</v>
+        <v>2144.9212097642817</v>
       </c>
       <c r="H166" s="404"/>
       <c r="I166" s="136">
         <f>+I106</f>
-        <v>1.9359786990774766</v>
+        <v>1.8974294660763611</v>
       </c>
       <c r="J166" s="67">
         <f>+J106</f>
-        <v>20.838874716869956</v>
+        <v>20.423930772845949</v>
       </c>
       <c r="T166" s="409"/>
     </row>
     <row r="167" spans="1:22" ht="15.9" customHeight="1">
       <c r="A167" s="107"/>
       <c r="B167" s="99"/>
-      <c r="C167" s="601" t="str">
+      <c r="C167" s="602" t="str">
         <f>+C107</f>
         <v>Net Rent II</v>
       </c>
-      <c r="D167" s="602"/>
+      <c r="D167" s="603"/>
       <c r="E167" s="59"/>
       <c r="F167" s="56">
         <f>+F107</f>
-        <v>194.20304295362101</v>
+        <v>136.36817938537592</v>
       </c>
       <c r="G167" s="388">
         <f>+G107</f>
-        <v>2090.4015543527767</v>
+        <v>1467.8670829041866</v>
       </c>
       <c r="H167" s="404"/>
       <c r="I167" s="136">
         <f>+I107</f>
-        <v>1.8492005613561322</v>
+        <v>1.2984972327687672</v>
       </c>
       <c r="J167" s="67">
         <f>+J107</f>
-        <v>19.904794842437404</v>
+        <v>13.977024213523011</v>
       </c>
       <c r="T167" s="409"/>
     </row>
     <row r="168" spans="1:22" ht="15.9" customHeight="1">
       <c r="A168" s="107"/>
       <c r="B168" s="147"/>
-      <c r="C168" s="606" t="s">
+      <c r="C168" s="607" t="s">
         <v>202</v>
       </c>
-      <c r="D168" s="607"/>
+      <c r="D168" s="608"/>
       <c r="E168" s="148"/>
       <c r="F168" s="149">
         <f>SUM(F166:F167)</f>
-        <v>397.51952593073759</v>
+        <v>335.63622191271531</v>
       </c>
       <c r="G168" s="211">
         <f>SUM(G166:G167)</f>
-        <v>4278.9001771184594</v>
+        <v>3612.7882926684683</v>
       </c>
       <c r="H168" s="212"/>
       <c r="I168" s="234">
         <f>SUM(I166:I167)</f>
-        <v>3.7851792604336087</v>
+        <v>3.1959266988451285</v>
       </c>
       <c r="J168" s="214">
         <f>SUM(J166:J167)</f>
-        <v>40.743669559307364</v>
+        <v>34.400954986368959</v>
       </c>
       <c r="T168" s="409"/>
       <c r="V168" s="409"/>
@@ -11482,8 +11482,8 @@
     <row r="169" spans="1:22" ht="15.9" customHeight="1">
       <c r="A169" s="107"/>
       <c r="B169" s="162"/>
-      <c r="C169" s="608"/>
-      <c r="D169" s="609"/>
+      <c r="C169" s="609"/>
+      <c r="D169" s="610"/>
       <c r="E169" s="75"/>
       <c r="F169" s="54"/>
       <c r="G169" s="385"/>
@@ -11496,11 +11496,11 @@
     <row r="170" spans="1:22" ht="15.9" customHeight="1">
       <c r="A170" s="107"/>
       <c r="B170" s="99"/>
-      <c r="C170" s="601" t="str">
+      <c r="C170" s="602" t="str">
         <f>+C119</f>
         <v xml:space="preserve">OpEx I </v>
       </c>
-      <c r="D170" s="602"/>
+      <c r="D170" s="603"/>
       <c r="E170" s="59"/>
       <c r="F170" s="56">
         <f>+F119</f>
@@ -11524,11 +11524,11 @@
     <row r="171" spans="1:22" ht="15.9" customHeight="1">
       <c r="A171" s="107"/>
       <c r="B171" s="99"/>
-      <c r="C171" s="601" t="str">
+      <c r="C171" s="602" t="str">
         <f>+C123</f>
         <v xml:space="preserve">OpEx II </v>
       </c>
-      <c r="D171" s="602"/>
+      <c r="D171" s="603"/>
       <c r="E171" s="59"/>
       <c r="F171" s="56">
         <f>+F123</f>
@@ -11551,10 +11551,10 @@
     <row r="172" spans="1:22" ht="15.9" customHeight="1">
       <c r="A172" s="107"/>
       <c r="B172" s="150"/>
-      <c r="C172" s="606" t="s">
+      <c r="C172" s="607" t="s">
         <v>203</v>
       </c>
-      <c r="D172" s="607"/>
+      <c r="D172" s="608"/>
       <c r="E172" s="151"/>
       <c r="F172" s="152">
         <f>SUM(F170:F171)</f>
@@ -11589,11 +11589,11 @@
     <row r="174" spans="1:22" ht="15.9" customHeight="1">
       <c r="A174" s="107"/>
       <c r="B174" s="99"/>
-      <c r="C174" s="601" t="str">
+      <c r="C174" s="602" t="str">
         <f>+C132</f>
         <v xml:space="preserve">Services </v>
       </c>
-      <c r="D174" s="602"/>
+      <c r="D174" s="603"/>
       <c r="E174" s="59"/>
       <c r="F174" s="56">
         <f>+F132</f>
@@ -11616,10 +11616,10 @@
     <row r="175" spans="1:22" ht="15.9" customHeight="1">
       <c r="A175" s="107"/>
       <c r="B175" s="150"/>
-      <c r="C175" s="606" t="s">
+      <c r="C175" s="607" t="s">
         <v>204</v>
       </c>
-      <c r="D175" s="607"/>
+      <c r="D175" s="608"/>
       <c r="E175" s="151"/>
       <c r="F175" s="152">
         <f>SUM(F174)</f>
@@ -11642,8 +11642,8 @@
     <row r="176" spans="1:22" ht="15.9" customHeight="1">
       <c r="A176" s="107"/>
       <c r="B176" s="99"/>
-      <c r="C176" s="599"/>
-      <c r="D176" s="600"/>
+      <c r="C176" s="600"/>
+      <c r="D176" s="601"/>
       <c r="E176" s="59"/>
       <c r="F176" s="56"/>
       <c r="G176" s="388"/>
@@ -11654,27 +11654,27 @@
     <row r="177" spans="1:19" ht="15.9" customHeight="1">
       <c r="A177" s="107"/>
       <c r="B177" s="150"/>
-      <c r="C177" s="606" t="s">
+      <c r="C177" s="607" t="s">
         <v>205</v>
       </c>
-      <c r="D177" s="607"/>
+      <c r="D177" s="608"/>
       <c r="E177" s="154"/>
       <c r="F177" s="149">
         <f>+F168+F172+F175</f>
-        <v>1051.5195259307375</v>
+        <v>989.63622191271531</v>
       </c>
       <c r="G177" s="211">
         <f>+G168+G172+G175</f>
-        <v>4978.6801771184591</v>
+        <v>4312.5682926684685</v>
       </c>
       <c r="H177" s="415"/>
       <c r="I177" s="234">
         <f>+I168+I172+I175</f>
-        <v>10.012564520384094</v>
+        <v>9.4233119587956153</v>
       </c>
       <c r="J177" s="214">
         <f>+J168+J172+J175</f>
-        <v>47.406971787454381</v>
+        <v>41.064257214515976</v>
       </c>
       <c r="S177" s="408"/>
     </row>
@@ -11692,11 +11692,11 @@
     </row>
     <row r="179" spans="1:19" ht="15.9" customHeight="1">
       <c r="A179" s="107"/>
-      <c r="B179" s="593" t="s">
+      <c r="B179" s="594" t="s">
         <v>206</v>
       </c>
-      <c r="C179" s="594"/>
-      <c r="D179" s="595"/>
+      <c r="C179" s="595"/>
+      <c r="D179" s="596"/>
       <c r="E179" s="379"/>
       <c r="F179" s="379" t="s">
         <v>190</v>
@@ -11715,8 +11715,8 @@
     <row r="180" spans="1:19" ht="15.9" customHeight="1">
       <c r="A180" s="107"/>
       <c r="B180" s="99"/>
-      <c r="C180" s="599"/>
-      <c r="D180" s="600"/>
+      <c r="C180" s="600"/>
+      <c r="D180" s="601"/>
       <c r="E180" s="59"/>
       <c r="F180" s="56"/>
       <c r="G180" s="388"/>
@@ -11727,30 +11727,30 @@
     <row r="181" spans="1:19" ht="15.9" customHeight="1">
       <c r="A181" s="107"/>
       <c r="B181" s="99"/>
-      <c r="C181" s="590" t="s">
+      <c r="C181" s="591" t="s">
         <v>207</v>
       </c>
-      <c r="D181" s="589"/>
+      <c r="D181" s="590"/>
       <c r="E181" s="100"/>
       <c r="F181" s="101"/>
       <c r="G181" s="209">
         <f>+G168*G21</f>
-        <v>3782398.2892309683</v>
+        <v>3193578.651499487</v>
       </c>
       <c r="H181" s="404"/>
       <c r="I181" s="143"/>
       <c r="J181" s="102">
         <f>+G181/$J$5</f>
-        <v>36015.980663025788</v>
+        <v>30409.242539511401</v>
       </c>
     </row>
     <row r="182" spans="1:19" ht="15.9" customHeight="1">
       <c r="A182" s="107"/>
       <c r="B182" s="99"/>
-      <c r="C182" s="588" t="s">
+      <c r="C182" s="589" t="s">
         <v>208</v>
       </c>
-      <c r="D182" s="589"/>
+      <c r="D182" s="590"/>
       <c r="E182" s="100"/>
       <c r="F182" s="101"/>
       <c r="G182" s="209">
@@ -11767,10 +11767,10 @@
     <row r="183" spans="1:19" ht="15.9" customHeight="1">
       <c r="A183" s="107"/>
       <c r="B183" s="99"/>
-      <c r="C183" s="588" t="s">
+      <c r="C183" s="589" t="s">
         <v>209</v>
       </c>
-      <c r="D183" s="598"/>
+      <c r="D183" s="599"/>
       <c r="E183" s="100"/>
       <c r="F183" s="101"/>
       <c r="G183" s="209">
@@ -11784,41 +11784,41 @@
     <row r="184" spans="1:19" ht="15.9" customHeight="1">
       <c r="A184" s="107"/>
       <c r="B184" s="99"/>
-      <c r="C184" s="588" t="s">
+      <c r="C184" s="589" t="s">
         <v>210</v>
       </c>
-      <c r="D184" s="589"/>
+      <c r="D184" s="590"/>
       <c r="E184" s="100"/>
       <c r="F184" s="101"/>
       <c r="G184" s="209">
         <f>SUM(G181:G183)</f>
-        <v>4400979.3650392182</v>
+        <v>3812159.7273077369</v>
       </c>
       <c r="H184" s="404"/>
       <c r="I184" s="143"/>
       <c r="J184" s="102">
         <f>SUM(J181:J183)</f>
-        <v>41906.107075216321</v>
+        <v>36299.368951701937</v>
       </c>
     </row>
     <row r="185" spans="1:19" ht="15.9" customHeight="1">
       <c r="A185" s="107"/>
       <c r="B185" s="99"/>
-      <c r="C185" s="588" t="s">
+      <c r="C185" s="589" t="s">
         <v>211</v>
       </c>
-      <c r="D185" s="589"/>
+      <c r="D185" s="590"/>
       <c r="E185" s="100"/>
       <c r="F185" s="101"/>
       <c r="G185" s="209">
         <f>+G184*12</f>
-        <v>52811752.380470619</v>
+        <v>45745916.727692842</v>
       </c>
       <c r="H185" s="404"/>
       <c r="I185" s="143"/>
       <c r="J185" s="102">
         <f>+J184*12</f>
-        <v>502873.28490259586</v>
+        <v>435592.42742042325</v>
       </c>
     </row>
     <row r="186" spans="1:19" ht="15.9" customHeight="1" thickBot="1">
@@ -11835,25 +11835,25 @@
     </row>
     <row r="187" spans="1:19" ht="15.9" customHeight="1" thickBot="1">
       <c r="A187" s="107"/>
-      <c r="B187" s="623" t="s">
+      <c r="B187" s="624" t="s">
         <v>212</v>
       </c>
-      <c r="C187" s="624"/>
-      <c r="D187" s="624"/>
-      <c r="E187" s="624"/>
-      <c r="F187" s="624"/>
-      <c r="G187" s="624"/>
-      <c r="H187" s="624"/>
-      <c r="I187" s="624"/>
-      <c r="J187" s="625"/>
+      <c r="C187" s="625"/>
+      <c r="D187" s="625"/>
+      <c r="E187" s="625"/>
+      <c r="F187" s="625"/>
+      <c r="G187" s="625"/>
+      <c r="H187" s="625"/>
+      <c r="I187" s="625"/>
+      <c r="J187" s="626"/>
     </row>
     <row r="188" spans="1:19" ht="15.9" customHeight="1">
       <c r="A188" s="51"/>
       <c r="B188" s="164"/>
-      <c r="C188" s="603" t="s">
+      <c r="C188" s="604" t="s">
         <v>213</v>
       </c>
-      <c r="D188" s="603"/>
+      <c r="D188" s="604"/>
       <c r="E188" s="378"/>
       <c r="F188" s="378" t="s">
         <v>190</v>
@@ -11861,7 +11861,7 @@
       <c r="G188" s="168" t="s">
         <v>190</v>
       </c>
-      <c r="H188" s="620"/>
+      <c r="H188" s="621"/>
       <c r="I188" s="229" t="s">
         <v>67</v>
       </c>
@@ -11872,17 +11872,17 @@
     <row r="189" spans="1:19" ht="15.9" customHeight="1">
       <c r="A189" s="51"/>
       <c r="B189" s="162"/>
-      <c r="C189" s="590" t="s">
+      <c r="C189" s="591" t="s">
         <v>214</v>
       </c>
-      <c r="D189" s="589"/>
+      <c r="D189" s="590"/>
       <c r="E189" s="163"/>
       <c r="F189" s="163"/>
       <c r="G189" s="102">
         <f>+G20</f>
         <v>0</v>
       </c>
-      <c r="H189" s="621"/>
+      <c r="H189" s="622"/>
       <c r="I189" s="162"/>
       <c r="J189" s="102">
         <f>+G189/J5</f>
@@ -11892,17 +11892,17 @@
     <row r="190" spans="1:19" ht="15.9" customHeight="1">
       <c r="A190" s="51"/>
       <c r="B190" s="162"/>
-      <c r="C190" s="590" t="s">
+      <c r="C190" s="591" t="s">
         <v>215</v>
       </c>
-      <c r="D190" s="589"/>
+      <c r="D190" s="590"/>
       <c r="E190" s="163"/>
       <c r="F190" s="163"/>
       <c r="G190" s="102">
         <f>+G189*G23</f>
         <v>0</v>
       </c>
-      <c r="H190" s="621"/>
+      <c r="H190" s="622"/>
       <c r="I190" s="162"/>
       <c r="J190" s="102">
         <f>+J189*J23</f>
@@ -11912,17 +11912,17 @@
     <row r="191" spans="1:19" ht="15.9" customHeight="1">
       <c r="A191" s="51"/>
       <c r="B191" s="162"/>
-      <c r="C191" s="604" t="s">
+      <c r="C191" s="605" t="s">
         <v>216</v>
       </c>
-      <c r="D191" s="604"/>
+      <c r="D191" s="605"/>
       <c r="E191" s="163"/>
       <c r="F191" s="163"/>
       <c r="G191" s="102">
         <f>+G190*25%</f>
         <v>0</v>
       </c>
-      <c r="H191" s="621"/>
+      <c r="H191" s="622"/>
       <c r="I191" s="162"/>
       <c r="J191" s="102">
         <f>+J190*25%</f>
@@ -11932,17 +11932,17 @@
     <row r="192" spans="1:19" ht="15.9" customHeight="1">
       <c r="A192" s="51"/>
       <c r="B192" s="162"/>
-      <c r="C192" s="588" t="s">
+      <c r="C192" s="589" t="s">
         <v>217</v>
       </c>
-      <c r="D192" s="589"/>
+      <c r="D192" s="590"/>
       <c r="E192" s="163"/>
       <c r="F192" s="163"/>
       <c r="G192" s="102">
         <f>+G191*1%</f>
         <v>0</v>
       </c>
-      <c r="H192" s="621"/>
+      <c r="H192" s="622"/>
       <c r="I192" s="162"/>
       <c r="J192" s="102">
         <f>G192/J5</f>
@@ -11952,17 +11952,17 @@
     <row r="193" spans="1:20" ht="15.9" customHeight="1">
       <c r="A193" s="51"/>
       <c r="B193" s="162"/>
-      <c r="C193" s="588" t="s">
+      <c r="C193" s="589" t="s">
         <v>218</v>
       </c>
-      <c r="D193" s="589"/>
+      <c r="D193" s="590"/>
       <c r="E193" s="163"/>
       <c r="F193" s="163"/>
       <c r="G193" s="102">
         <f>G192*0.5</f>
         <v>0</v>
       </c>
-      <c r="H193" s="621"/>
+      <c r="H193" s="622"/>
       <c r="I193" s="162"/>
       <c r="J193" s="102">
         <f>G193/J5</f>
@@ -11972,17 +11972,17 @@
     <row r="194" spans="1:20" ht="15.9" customHeight="1" thickBot="1">
       <c r="A194" s="51"/>
       <c r="B194" s="162"/>
-      <c r="C194" s="604" t="s">
+      <c r="C194" s="605" t="s">
         <v>219</v>
       </c>
-      <c r="D194" s="604"/>
+      <c r="D194" s="605"/>
       <c r="E194" s="163"/>
       <c r="F194" s="163"/>
       <c r="G194" s="110">
         <f>G82</f>
         <v>565315.30184775486</v>
       </c>
-      <c r="H194" s="621"/>
+      <c r="H194" s="622"/>
       <c r="I194" s="162"/>
       <c r="J194" s="110">
         <f>+J192+J193</f>
@@ -11992,8 +11992,8 @@
     <row r="195" spans="1:20" ht="15.9" customHeight="1">
       <c r="A195" s="166"/>
       <c r="B195" s="382"/>
-      <c r="C195" s="605"/>
-      <c r="D195" s="605"/>
+      <c r="C195" s="606"/>
+      <c r="D195" s="606"/>
       <c r="E195" s="379"/>
       <c r="F195" s="379" t="s">
         <v>190</v>
@@ -12001,7 +12001,7 @@
       <c r="G195" s="53" t="s">
         <v>190</v>
       </c>
-      <c r="H195" s="621"/>
+      <c r="H195" s="622"/>
       <c r="I195" s="229" t="s">
         <v>67</v>
       </c>
@@ -12012,17 +12012,17 @@
     <row r="196" spans="1:20" ht="15.9" customHeight="1">
       <c r="A196" s="74"/>
       <c r="B196" s="99"/>
-      <c r="C196" s="590" t="s">
+      <c r="C196" s="591" t="s">
         <v>220</v>
       </c>
-      <c r="D196" s="589"/>
+      <c r="D196" s="590"/>
       <c r="E196" s="58"/>
       <c r="F196" s="50"/>
       <c r="G196" s="102">
         <f>+G54</f>
         <v>72</v>
       </c>
-      <c r="H196" s="621"/>
+      <c r="H196" s="622"/>
       <c r="I196" s="91"/>
       <c r="J196" s="102">
         <f>+J54</f>
@@ -12032,17 +12032,17 @@
     <row r="197" spans="1:20" ht="15.9" customHeight="1">
       <c r="A197" s="74"/>
       <c r="B197" s="99"/>
-      <c r="C197" s="590" t="s">
+      <c r="C197" s="591" t="s">
         <v>221</v>
       </c>
-      <c r="D197" s="589"/>
+      <c r="D197" s="590"/>
       <c r="E197" s="58"/>
       <c r="F197" s="50"/>
       <c r="G197" s="102">
         <f>F140</f>
         <v>9515</v>
       </c>
-      <c r="H197" s="621"/>
+      <c r="H197" s="622"/>
       <c r="I197" s="91"/>
       <c r="J197" s="102">
         <f>I140</f>
@@ -12052,17 +12052,17 @@
     <row r="198" spans="1:20" ht="15.9" customHeight="1">
       <c r="A198" s="120"/>
       <c r="B198" s="99"/>
-      <c r="C198" s="590" t="s">
+      <c r="C198" s="591" t="s">
         <v>222</v>
       </c>
-      <c r="D198" s="589"/>
+      <c r="D198" s="590"/>
       <c r="E198" s="58"/>
       <c r="F198" s="50"/>
       <c r="G198" s="111">
         <f>+F60</f>
         <v>129</v>
       </c>
-      <c r="H198" s="621"/>
+      <c r="H198" s="622"/>
       <c r="I198" s="91"/>
       <c r="J198" s="111">
         <f>+I60</f>
@@ -12072,17 +12072,17 @@
     <row r="199" spans="1:20" ht="15.9" customHeight="1">
       <c r="A199" s="74"/>
       <c r="B199" s="99"/>
-      <c r="C199" s="590" t="s">
+      <c r="C199" s="591" t="s">
         <v>222</v>
       </c>
-      <c r="D199" s="589"/>
+      <c r="D199" s="590"/>
       <c r="E199" s="58"/>
       <c r="F199" s="50"/>
       <c r="G199" s="102">
         <f>(G197*G198*G196)</f>
         <v>88375320</v>
       </c>
-      <c r="H199" s="621"/>
+      <c r="H199" s="622"/>
       <c r="I199" s="91"/>
       <c r="J199" s="102">
         <f>+G199/$J$5</f>
@@ -12092,17 +12092,17 @@
     <row r="200" spans="1:20" ht="15.9" customHeight="1">
       <c r="A200" s="74"/>
       <c r="B200" s="99"/>
-      <c r="C200" s="590" t="s">
+      <c r="C200" s="591" t="s">
         <v>223</v>
       </c>
-      <c r="D200" s="589"/>
+      <c r="D200" s="590"/>
       <c r="E200" s="58"/>
       <c r="F200" s="50"/>
       <c r="G200" s="102">
         <f>G199/G196*12</f>
         <v>14729220</v>
       </c>
-      <c r="H200" s="621"/>
+      <c r="H200" s="622"/>
       <c r="I200" s="91"/>
       <c r="J200" s="102">
         <f>+G200/$J$5</f>
@@ -12112,17 +12112,17 @@
     <row r="201" spans="1:20" ht="15.9" customHeight="1">
       <c r="A201" s="74"/>
       <c r="B201" s="99"/>
-      <c r="C201" s="590" t="s">
+      <c r="C201" s="591" t="s">
         <v>224</v>
       </c>
-      <c r="D201" s="589"/>
+      <c r="D201" s="590"/>
       <c r="E201" s="58"/>
       <c r="F201" s="50"/>
       <c r="G201" s="102">
         <f>(+G220*115%)/5</f>
         <v>3026339.9999999995</v>
       </c>
-      <c r="H201" s="621"/>
+      <c r="H201" s="622"/>
       <c r="I201" s="91"/>
       <c r="J201" s="102">
         <f>+G201/$J$5</f>
@@ -12132,17 +12132,17 @@
     <row r="202" spans="1:20" ht="15.9" customHeight="1">
       <c r="A202" s="74"/>
       <c r="B202" s="99"/>
-      <c r="C202" s="590" t="s">
+      <c r="C202" s="591" t="s">
         <v>225</v>
       </c>
-      <c r="D202" s="589"/>
+      <c r="D202" s="590"/>
       <c r="E202" s="58"/>
       <c r="F202" s="50"/>
       <c r="G202" s="102">
         <f>(+I220*115%)/5</f>
         <v>2765157.6185172233</v>
       </c>
-      <c r="H202" s="621"/>
+      <c r="H202" s="622"/>
       <c r="I202" s="91"/>
       <c r="J202" s="102">
         <f>+G202/$J$5</f>
@@ -12152,17 +12152,17 @@
     <row r="203" spans="1:20" ht="15.9" customHeight="1">
       <c r="A203" s="74"/>
       <c r="B203" s="99"/>
-      <c r="C203" s="590" t="s">
+      <c r="C203" s="591" t="s">
         <v>36</v>
       </c>
-      <c r="D203" s="589"/>
+      <c r="D203" s="590"/>
       <c r="E203" s="58"/>
       <c r="F203" s="50"/>
       <c r="G203" s="102">
         <f>+G67</f>
         <v>11418000</v>
       </c>
-      <c r="H203" s="621"/>
+      <c r="H203" s="622"/>
       <c r="I203" s="91"/>
       <c r="J203" s="102">
         <f>+G203/$J$5</f>
@@ -12172,17 +12172,17 @@
     <row r="204" spans="1:20" ht="15.9" customHeight="1">
       <c r="A204" s="74"/>
       <c r="B204" s="99"/>
-      <c r="C204" s="588" t="s">
+      <c r="C204" s="589" t="s">
         <v>226</v>
       </c>
-      <c r="D204" s="589"/>
+      <c r="D204" s="590"/>
       <c r="E204" s="58"/>
       <c r="F204" s="50"/>
       <c r="G204" s="102">
         <f>(G200+G201+G202+G203)*1.18</f>
         <v>37687686.789850324</v>
       </c>
-      <c r="H204" s="621"/>
+      <c r="H204" s="622"/>
       <c r="I204" s="91"/>
       <c r="J204" s="102">
         <f>+J200+J201+J202+J203</f>
@@ -12192,17 +12192,17 @@
     <row r="205" spans="1:20" ht="15.9" customHeight="1">
       <c r="A205" s="74"/>
       <c r="B205" s="99"/>
-      <c r="C205" s="588" t="s">
+      <c r="C205" s="589" t="s">
         <v>227</v>
       </c>
-      <c r="D205" s="589"/>
+      <c r="D205" s="590"/>
       <c r="E205" s="58"/>
       <c r="F205" s="50"/>
       <c r="G205" s="102">
         <f>G204*1%</f>
         <v>376876.86789850326</v>
       </c>
-      <c r="H205" s="621"/>
+      <c r="H205" s="622"/>
       <c r="I205" s="91"/>
       <c r="J205" s="102">
         <f>J204*1%</f>
@@ -12212,17 +12212,17 @@
     <row r="206" spans="1:20" ht="15.9" customHeight="1">
       <c r="A206" s="74"/>
       <c r="B206" s="99"/>
-      <c r="C206" s="590" t="s">
+      <c r="C206" s="591" t="s">
         <v>228</v>
       </c>
-      <c r="D206" s="589"/>
+      <c r="D206" s="590"/>
       <c r="E206" s="58"/>
       <c r="F206" s="50"/>
       <c r="G206" s="102">
         <f>G204*0.5%</f>
         <v>188438.43394925163</v>
       </c>
-      <c r="H206" s="621"/>
+      <c r="H206" s="622"/>
       <c r="I206" s="91"/>
       <c r="J206" s="102">
         <f>J204*0.5%</f>
@@ -12232,17 +12232,17 @@
     <row r="207" spans="1:20" ht="15.9" customHeight="1">
       <c r="A207" s="74"/>
       <c r="B207" s="99"/>
-      <c r="C207" s="591" t="s">
+      <c r="C207" s="592" t="s">
         <v>219</v>
       </c>
-      <c r="D207" s="592"/>
+      <c r="D207" s="593"/>
       <c r="E207" s="58"/>
       <c r="F207" s="50"/>
       <c r="G207" s="102">
         <f>G205+G206</f>
         <v>565315.30184775486</v>
       </c>
-      <c r="H207" s="621"/>
+      <c r="H207" s="622"/>
       <c r="I207" s="91"/>
       <c r="J207" s="102">
         <v>0</v>
@@ -12257,7 +12257,7 @@
       <c r="E208" s="80"/>
       <c r="F208" s="51"/>
       <c r="G208" s="337"/>
-      <c r="H208" s="621"/>
+      <c r="H208" s="622"/>
       <c r="I208" s="94"/>
       <c r="J208" s="81"/>
     </row>
@@ -12279,7 +12279,7 @@
       <c r="G209" s="161" t="s">
         <v>233</v>
       </c>
-      <c r="H209" s="621"/>
+      <c r="H209" s="622"/>
       <c r="I209" s="379" t="s">
         <v>234</v>
       </c>
@@ -12305,7 +12305,7 @@
         <f>'Lease Rent'!P39</f>
         <v>1360000</v>
       </c>
-      <c r="H210" s="621"/>
+      <c r="H210" s="622"/>
       <c r="I210" s="101">
         <f>'Lease Rent'!O39</f>
         <v>1178337.5999999999</v>
@@ -12335,7 +12335,7 @@
         <f>'Lease Rent'!P51</f>
         <v>2040000</v>
       </c>
-      <c r="H211" s="621"/>
+      <c r="H211" s="622"/>
       <c r="I211" s="101">
         <f>'Lease Rent'!O51</f>
         <v>1826423.2800000005</v>
@@ -12364,7 +12364,7 @@
         <f>'Lease Rent'!P63</f>
         <v>2040000</v>
       </c>
-      <c r="H212" s="621"/>
+      <c r="H212" s="622"/>
       <c r="I212" s="101">
         <f>'Lease Rent'!O63</f>
         <v>1917744.4440000001</v>
@@ -12393,7 +12393,7 @@
         <f>'Lease Rent'!P75</f>
         <v>2244000</v>
       </c>
-      <c r="H213" s="621"/>
+      <c r="H213" s="622"/>
       <c r="I213" s="101">
         <f>'Lease Rent'!O75</f>
         <v>2013631.6662000006</v>
@@ -12422,7 +12422,7 @@
         <f>'Lease Rent'!P87</f>
         <v>2345999.9999999995</v>
       </c>
-      <c r="H214" s="621"/>
+      <c r="H214" s="622"/>
       <c r="I214" s="101">
         <f>'Lease Rent'!O87</f>
         <v>2114313.2495100005</v>
@@ -12447,11 +12447,11 @@
         <f>+F214</f>
         <v>0</v>
       </c>
-      <c r="G215" s="714">
+      <c r="G215" s="588">
         <f>'Lease Rent'!P99</f>
         <v>2345999.9999999995</v>
       </c>
-      <c r="H215" s="621"/>
+      <c r="H215" s="622"/>
       <c r="I215" s="101">
         <f>'Lease Rent'!O99</f>
         <v>2220028.9119855007</v>
@@ -12475,11 +12475,11 @@
         <f>+F215*115%</f>
         <v>0</v>
       </c>
-      <c r="G216" s="714">
+      <c r="G216" s="588">
         <f>'Lease Rent'!P103</f>
         <v>781999.99999999988</v>
       </c>
-      <c r="H216" s="621"/>
+      <c r="H216" s="622"/>
       <c r="I216" s="101">
         <f>'Lease Rent'!O103</f>
         <v>751945.27664025011</v>
@@ -12502,7 +12502,7 @@
         <f>'Lease Rent'!R10</f>
         <v>0</v>
       </c>
-      <c r="H217" s="621"/>
+      <c r="H217" s="622"/>
       <c r="I217" s="301"/>
       <c r="J217" s="111"/>
     </row>
@@ -12519,7 +12519,7 @@
         <v>0</v>
       </c>
       <c r="G218" s="118"/>
-      <c r="H218" s="621"/>
+      <c r="H218" s="622"/>
       <c r="I218" s="101"/>
       <c r="J218" s="111"/>
     </row>
@@ -12533,7 +12533,7 @@
       <c r="E219" s="117"/>
       <c r="F219" s="232"/>
       <c r="G219" s="118"/>
-      <c r="H219" s="621"/>
+      <c r="H219" s="622"/>
       <c r="I219" s="101"/>
       <c r="J219" s="111"/>
     </row>
@@ -12556,7 +12556,7 @@
         <f>SUM(G210:G219)</f>
         <v>13158000</v>
       </c>
-      <c r="H220" s="622"/>
+      <c r="H220" s="623"/>
       <c r="I220" s="283">
         <f>SUM(I210:I219)</f>
         <v>12022424.428335754</v>
@@ -12935,215 +12935,215 @@
       <c r="S1" s="1"/>
     </row>
     <row r="2" spans="1:27" ht="11.25" customHeight="1">
-      <c r="A2" s="664"/>
-      <c r="B2" s="665"/>
-      <c r="C2" s="665"/>
-      <c r="D2" s="665"/>
-      <c r="E2" s="665"/>
-      <c r="F2" s="665"/>
-      <c r="G2" s="665"/>
-      <c r="H2" s="665"/>
-      <c r="I2" s="665"/>
-      <c r="J2" s="665"/>
-      <c r="K2" s="665"/>
-      <c r="L2" s="665"/>
-      <c r="M2" s="665"/>
-      <c r="N2" s="665"/>
-      <c r="O2" s="665"/>
-      <c r="P2" s="665"/>
-      <c r="Q2" s="665"/>
-      <c r="R2" s="665"/>
-      <c r="S2" s="665"/>
-      <c r="T2" s="665"/>
-      <c r="U2" s="665"/>
-      <c r="V2" s="665"/>
-      <c r="W2" s="665"/>
-      <c r="X2" s="665"/>
-      <c r="Y2" s="665"/>
-      <c r="Z2" s="665"/>
-      <c r="AA2" s="689"/>
+      <c r="A2" s="665"/>
+      <c r="B2" s="666"/>
+      <c r="C2" s="666"/>
+      <c r="D2" s="666"/>
+      <c r="E2" s="666"/>
+      <c r="F2" s="666"/>
+      <c r="G2" s="666"/>
+      <c r="H2" s="666"/>
+      <c r="I2" s="666"/>
+      <c r="J2" s="666"/>
+      <c r="K2" s="666"/>
+      <c r="L2" s="666"/>
+      <c r="M2" s="666"/>
+      <c r="N2" s="666"/>
+      <c r="O2" s="666"/>
+      <c r="P2" s="666"/>
+      <c r="Q2" s="666"/>
+      <c r="R2" s="666"/>
+      <c r="S2" s="666"/>
+      <c r="T2" s="666"/>
+      <c r="U2" s="666"/>
+      <c r="V2" s="666"/>
+      <c r="W2" s="666"/>
+      <c r="X2" s="666"/>
+      <c r="Y2" s="666"/>
+      <c r="Z2" s="666"/>
+      <c r="AA2" s="690"/>
     </row>
     <row r="3" spans="1:27" ht="11.25" customHeight="1">
-      <c r="A3" s="690"/>
-      <c r="B3" s="691"/>
-      <c r="C3" s="691"/>
-      <c r="D3" s="691"/>
-      <c r="E3" s="691"/>
-      <c r="F3" s="691"/>
-      <c r="G3" s="691"/>
-      <c r="H3" s="691"/>
-      <c r="I3" s="691"/>
-      <c r="J3" s="691"/>
-      <c r="K3" s="691"/>
-      <c r="L3" s="691"/>
-      <c r="M3" s="691"/>
-      <c r="N3" s="691"/>
-      <c r="O3" s="691"/>
-      <c r="P3" s="691"/>
-      <c r="Q3" s="691"/>
-      <c r="R3" s="691"/>
-      <c r="S3" s="691"/>
-      <c r="T3" s="691"/>
-      <c r="U3" s="691"/>
-      <c r="V3" s="691"/>
-      <c r="W3" s="691"/>
-      <c r="X3" s="691"/>
-      <c r="Y3" s="691"/>
-      <c r="Z3" s="691"/>
-      <c r="AA3" s="692"/>
+      <c r="A3" s="691"/>
+      <c r="B3" s="692"/>
+      <c r="C3" s="692"/>
+      <c r="D3" s="692"/>
+      <c r="E3" s="692"/>
+      <c r="F3" s="692"/>
+      <c r="G3" s="692"/>
+      <c r="H3" s="692"/>
+      <c r="I3" s="692"/>
+      <c r="J3" s="692"/>
+      <c r="K3" s="692"/>
+      <c r="L3" s="692"/>
+      <c r="M3" s="692"/>
+      <c r="N3" s="692"/>
+      <c r="O3" s="692"/>
+      <c r="P3" s="692"/>
+      <c r="Q3" s="692"/>
+      <c r="R3" s="692"/>
+      <c r="S3" s="692"/>
+      <c r="T3" s="692"/>
+      <c r="U3" s="692"/>
+      <c r="V3" s="692"/>
+      <c r="W3" s="692"/>
+      <c r="X3" s="692"/>
+      <c r="Y3" s="692"/>
+      <c r="Z3" s="692"/>
+      <c r="AA3" s="693"/>
     </row>
     <row r="4" spans="1:27" ht="12" customHeight="1" thickBot="1">
-      <c r="A4" s="693"/>
-      <c r="B4" s="694"/>
-      <c r="C4" s="694"/>
-      <c r="D4" s="694"/>
-      <c r="E4" s="694"/>
-      <c r="F4" s="694"/>
-      <c r="G4" s="694"/>
-      <c r="H4" s="694"/>
-      <c r="I4" s="694"/>
-      <c r="J4" s="694"/>
-      <c r="K4" s="694"/>
-      <c r="L4" s="694"/>
-      <c r="M4" s="694"/>
-      <c r="N4" s="694"/>
-      <c r="O4" s="694"/>
-      <c r="P4" s="694"/>
-      <c r="Q4" s="694"/>
-      <c r="R4" s="694"/>
-      <c r="S4" s="694"/>
-      <c r="T4" s="694"/>
-      <c r="U4" s="694"/>
-      <c r="V4" s="694"/>
-      <c r="W4" s="694"/>
-      <c r="X4" s="694"/>
-      <c r="Y4" s="694"/>
-      <c r="Z4" s="694"/>
-      <c r="AA4" s="695"/>
+      <c r="A4" s="694"/>
+      <c r="B4" s="695"/>
+      <c r="C4" s="695"/>
+      <c r="D4" s="695"/>
+      <c r="E4" s="695"/>
+      <c r="F4" s="695"/>
+      <c r="G4" s="695"/>
+      <c r="H4" s="695"/>
+      <c r="I4" s="695"/>
+      <c r="J4" s="695"/>
+      <c r="K4" s="695"/>
+      <c r="L4" s="695"/>
+      <c r="M4" s="695"/>
+      <c r="N4" s="695"/>
+      <c r="O4" s="695"/>
+      <c r="P4" s="695"/>
+      <c r="Q4" s="695"/>
+      <c r="R4" s="695"/>
+      <c r="S4" s="695"/>
+      <c r="T4" s="695"/>
+      <c r="U4" s="695"/>
+      <c r="V4" s="695"/>
+      <c r="W4" s="695"/>
+      <c r="X4" s="695"/>
+      <c r="Y4" s="695"/>
+      <c r="Z4" s="695"/>
+      <c r="AA4" s="696"/>
     </row>
     <row r="5" spans="1:27" ht="12.75" customHeight="1">
-      <c r="A5" s="664" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="665"/>
-      <c r="C5" s="665"/>
-      <c r="D5" s="665"/>
-      <c r="E5" s="665"/>
-      <c r="F5" s="665"/>
-      <c r="G5" s="665"/>
-      <c r="H5" s="665"/>
-      <c r="I5" s="665"/>
-      <c r="J5" s="665"/>
-      <c r="K5" s="665"/>
-      <c r="L5" s="665"/>
-      <c r="M5" s="665"/>
-      <c r="N5" s="665"/>
-      <c r="O5" s="665"/>
-      <c r="P5" s="665"/>
-      <c r="Q5" s="665"/>
-      <c r="R5" s="665"/>
-      <c r="S5" s="665"/>
-      <c r="T5" s="665"/>
-      <c r="U5" s="665"/>
-      <c r="V5" s="665"/>
-      <c r="W5" s="665"/>
-      <c r="X5" s="665"/>
-      <c r="Y5" s="665"/>
-      <c r="Z5" s="665"/>
-      <c r="AA5" s="689"/>
+      <c r="A5" s="665" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="666"/>
+      <c r="C5" s="666"/>
+      <c r="D5" s="666"/>
+      <c r="E5" s="666"/>
+      <c r="F5" s="666"/>
+      <c r="G5" s="666"/>
+      <c r="H5" s="666"/>
+      <c r="I5" s="666"/>
+      <c r="J5" s="666"/>
+      <c r="K5" s="666"/>
+      <c r="L5" s="666"/>
+      <c r="M5" s="666"/>
+      <c r="N5" s="666"/>
+      <c r="O5" s="666"/>
+      <c r="P5" s="666"/>
+      <c r="Q5" s="666"/>
+      <c r="R5" s="666"/>
+      <c r="S5" s="666"/>
+      <c r="T5" s="666"/>
+      <c r="U5" s="666"/>
+      <c r="V5" s="666"/>
+      <c r="W5" s="666"/>
+      <c r="X5" s="666"/>
+      <c r="Y5" s="666"/>
+      <c r="Z5" s="666"/>
+      <c r="AA5" s="690"/>
     </row>
     <row r="6" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A6" s="696"/>
-      <c r="B6" s="697"/>
-      <c r="C6" s="697"/>
-      <c r="D6" s="697"/>
-      <c r="E6" s="697"/>
-      <c r="F6" s="697"/>
-      <c r="G6" s="697"/>
-      <c r="H6" s="697"/>
-      <c r="I6" s="697"/>
-      <c r="J6" s="697"/>
-      <c r="K6" s="697"/>
-      <c r="L6" s="697"/>
-      <c r="M6" s="697"/>
-      <c r="N6" s="697"/>
-      <c r="O6" s="697"/>
-      <c r="P6" s="697"/>
-      <c r="Q6" s="697"/>
-      <c r="R6" s="697"/>
-      <c r="S6" s="697"/>
-      <c r="T6" s="697"/>
-      <c r="U6" s="697"/>
-      <c r="V6" s="697"/>
-      <c r="W6" s="697"/>
-      <c r="X6" s="697"/>
-      <c r="Y6" s="697"/>
-      <c r="Z6" s="697"/>
-      <c r="AA6" s="698"/>
+      <c r="A6" s="697"/>
+      <c r="B6" s="698"/>
+      <c r="C6" s="698"/>
+      <c r="D6" s="698"/>
+      <c r="E6" s="698"/>
+      <c r="F6" s="698"/>
+      <c r="G6" s="698"/>
+      <c r="H6" s="698"/>
+      <c r="I6" s="698"/>
+      <c r="J6" s="698"/>
+      <c r="K6" s="698"/>
+      <c r="L6" s="698"/>
+      <c r="M6" s="698"/>
+      <c r="N6" s="698"/>
+      <c r="O6" s="698"/>
+      <c r="P6" s="698"/>
+      <c r="Q6" s="698"/>
+      <c r="R6" s="698"/>
+      <c r="S6" s="698"/>
+      <c r="T6" s="698"/>
+      <c r="U6" s="698"/>
+      <c r="V6" s="698"/>
+      <c r="W6" s="698"/>
+      <c r="X6" s="698"/>
+      <c r="Y6" s="698"/>
+      <c r="Z6" s="698"/>
+      <c r="AA6" s="699"/>
     </row>
     <row r="7" spans="1:27" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A7" s="699" t="s">
+      <c r="A7" s="700" t="s">
         <v>296</v>
       </c>
-      <c r="B7" s="700"/>
-      <c r="C7" s="700"/>
-      <c r="D7" s="700"/>
-      <c r="E7" s="700"/>
-      <c r="F7" s="700"/>
-      <c r="G7" s="700"/>
-      <c r="H7" s="700"/>
-      <c r="I7" s="700"/>
-      <c r="J7" s="700"/>
-      <c r="K7" s="700"/>
-      <c r="L7" s="700"/>
-      <c r="M7" s="700"/>
-      <c r="N7" s="700"/>
-      <c r="O7" s="700"/>
-      <c r="P7" s="701"/>
-      <c r="Q7" s="701"/>
-      <c r="R7" s="701"/>
-      <c r="S7" s="701"/>
-      <c r="T7" s="701"/>
-      <c r="U7" s="701"/>
-      <c r="V7" s="701"/>
-      <c r="W7" s="701"/>
-      <c r="X7" s="701"/>
-      <c r="Y7" s="701"/>
-      <c r="Z7" s="701"/>
-      <c r="AA7" s="702"/>
+      <c r="B7" s="701"/>
+      <c r="C7" s="701"/>
+      <c r="D7" s="701"/>
+      <c r="E7" s="701"/>
+      <c r="F7" s="701"/>
+      <c r="G7" s="701"/>
+      <c r="H7" s="701"/>
+      <c r="I7" s="701"/>
+      <c r="J7" s="701"/>
+      <c r="K7" s="701"/>
+      <c r="L7" s="701"/>
+      <c r="M7" s="701"/>
+      <c r="N7" s="701"/>
+      <c r="O7" s="701"/>
+      <c r="P7" s="702"/>
+      <c r="Q7" s="702"/>
+      <c r="R7" s="702"/>
+      <c r="S7" s="702"/>
+      <c r="T7" s="702"/>
+      <c r="U7" s="702"/>
+      <c r="V7" s="702"/>
+      <c r="W7" s="702"/>
+      <c r="X7" s="702"/>
+      <c r="Y7" s="702"/>
+      <c r="Z7" s="702"/>
+      <c r="AA7" s="703"/>
     </row>
     <row r="8" spans="1:27" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A8" s="703" t="s">
+      <c r="A8" s="704" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="704"/>
-      <c r="C8" s="704"/>
-      <c r="D8" s="704"/>
-      <c r="E8" s="704"/>
-      <c r="F8" s="704"/>
-      <c r="G8" s="704"/>
-      <c r="H8" s="704"/>
-      <c r="I8" s="704"/>
-      <c r="J8" s="704"/>
-      <c r="K8" s="704"/>
-      <c r="L8" s="704"/>
-      <c r="M8" s="704"/>
-      <c r="N8" s="705"/>
+      <c r="B8" s="705"/>
+      <c r="C8" s="705"/>
+      <c r="D8" s="705"/>
+      <c r="E8" s="705"/>
+      <c r="F8" s="705"/>
+      <c r="G8" s="705"/>
+      <c r="H8" s="705"/>
+      <c r="I8" s="705"/>
+      <c r="J8" s="705"/>
+      <c r="K8" s="705"/>
+      <c r="L8" s="705"/>
+      <c r="M8" s="705"/>
+      <c r="N8" s="706"/>
       <c r="O8" s="6"/>
-      <c r="P8" s="703" t="s">
+      <c r="P8" s="704" t="s">
         <v>2</v>
       </c>
-      <c r="Q8" s="704"/>
-      <c r="R8" s="704"/>
-      <c r="S8" s="704"/>
-      <c r="T8" s="704"/>
-      <c r="U8" s="704"/>
-      <c r="V8" s="704"/>
-      <c r="W8" s="704"/>
-      <c r="X8" s="704"/>
-      <c r="Y8" s="704"/>
-      <c r="Z8" s="704"/>
-      <c r="AA8" s="706"/>
+      <c r="Q8" s="705"/>
+      <c r="R8" s="705"/>
+      <c r="S8" s="705"/>
+      <c r="T8" s="705"/>
+      <c r="U8" s="705"/>
+      <c r="V8" s="705"/>
+      <c r="W8" s="705"/>
+      <c r="X8" s="705"/>
+      <c r="Y8" s="705"/>
+      <c r="Z8" s="705"/>
+      <c r="AA8" s="707"/>
     </row>
     <row r="9" spans="1:27" s="215" customFormat="1" ht="45.75" customHeight="1">
       <c r="A9" s="216">
@@ -14709,11 +14709,11 @@
       <c r="R32" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="T32" s="686" t="s">
+      <c r="T32" s="687" t="s">
         <v>53</v>
       </c>
-      <c r="U32" s="687"/>
-      <c r="V32" s="688"/>
+      <c r="U32" s="688"/>
+      <c r="V32" s="689"/>
     </row>
     <row r="33" spans="1:27" ht="10.5">
       <c r="A33" s="37"/>
@@ -14824,8 +14824,8 @@
         <f>+N32+N34</f>
         <v>1.4601854336242732</v>
       </c>
-      <c r="P36" s="685"/>
-      <c r="Q36" s="685"/>
+      <c r="P36" s="686"/>
+      <c r="Q36" s="686"/>
       <c r="T36" s="31" t="s">
         <v>59</v>
       </c>
@@ -16142,10 +16142,10 @@
       </c>
     </row>
     <row r="11" spans="2:21" s="362" customFormat="1" ht="13" hidden="1">
-      <c r="B11" s="707" t="s">
+      <c r="B11" s="708" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="707"/>
+      <c r="C11" s="708"/>
       <c r="D11" s="391">
         <v>42</v>
       </c>
@@ -20609,22 +20609,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="16" thickBot="1">
-      <c r="A1" s="708" t="s">
+      <c r="A1" s="709" t="s">
         <v>256</v>
       </c>
-      <c r="B1" s="709"/>
-      <c r="C1" s="709"/>
-      <c r="D1" s="709"/>
-      <c r="E1" s="709"/>
-      <c r="F1" s="709"/>
-      <c r="G1" s="709"/>
-      <c r="H1" s="709"/>
-      <c r="I1" s="709"/>
-      <c r="J1" s="709"/>
-      <c r="K1" s="709"/>
-      <c r="L1" s="709"/>
-      <c r="M1" s="709"/>
-      <c r="N1" s="710"/>
+      <c r="B1" s="710"/>
+      <c r="C1" s="710"/>
+      <c r="D1" s="710"/>
+      <c r="E1" s="710"/>
+      <c r="F1" s="710"/>
+      <c r="G1" s="710"/>
+      <c r="H1" s="710"/>
+      <c r="I1" s="710"/>
+      <c r="J1" s="710"/>
+      <c r="K1" s="710"/>
+      <c r="L1" s="710"/>
+      <c r="M1" s="710"/>
+      <c r="N1" s="711"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="178" t="s">
@@ -21650,21 +21650,21 @@
       <c r="I34" s="358"/>
     </row>
     <row r="35" spans="1:15" ht="16" outlineLevel="1" thickBot="1">
-      <c r="A35" s="708"/>
-      <c r="B35" s="709"/>
-      <c r="C35" s="709"/>
-      <c r="D35" s="709"/>
-      <c r="E35" s="709"/>
-      <c r="F35" s="709"/>
-      <c r="G35" s="709"/>
-      <c r="H35" s="709"/>
-      <c r="I35" s="709"/>
-      <c r="J35" s="709"/>
-      <c r="K35" s="709"/>
-      <c r="L35" s="709"/>
-      <c r="M35" s="709"/>
-      <c r="N35" s="709"/>
-      <c r="O35" s="710"/>
+      <c r="A35" s="709"/>
+      <c r="B35" s="710"/>
+      <c r="C35" s="710"/>
+      <c r="D35" s="710"/>
+      <c r="E35" s="710"/>
+      <c r="F35" s="710"/>
+      <c r="G35" s="710"/>
+      <c r="H35" s="710"/>
+      <c r="I35" s="710"/>
+      <c r="J35" s="710"/>
+      <c r="K35" s="710"/>
+      <c r="L35" s="710"/>
+      <c r="M35" s="710"/>
+      <c r="N35" s="710"/>
+      <c r="O35" s="711"/>
     </row>
     <row r="36" spans="1:15" outlineLevel="1">
       <c r="A36" s="306" t="s">
@@ -23454,21 +23454,21 @@
       <c r="I91" s="186"/>
     </row>
     <row r="92" spans="1:15" ht="16" thickBot="1">
-      <c r="A92" s="711"/>
-      <c r="B92" s="712"/>
-      <c r="C92" s="712"/>
-      <c r="D92" s="712"/>
-      <c r="E92" s="712"/>
-      <c r="F92" s="712"/>
-      <c r="G92" s="712"/>
-      <c r="H92" s="712"/>
-      <c r="I92" s="712"/>
-      <c r="J92" s="712"/>
-      <c r="K92" s="712"/>
-      <c r="L92" s="712"/>
-      <c r="M92" s="712"/>
-      <c r="N92" s="712"/>
-      <c r="O92" s="713"/>
+      <c r="A92" s="712"/>
+      <c r="B92" s="713"/>
+      <c r="C92" s="713"/>
+      <c r="D92" s="713"/>
+      <c r="E92" s="713"/>
+      <c r="F92" s="713"/>
+      <c r="G92" s="713"/>
+      <c r="H92" s="713"/>
+      <c r="I92" s="713"/>
+      <c r="J92" s="713"/>
+      <c r="K92" s="713"/>
+      <c r="L92" s="713"/>
+      <c r="M92" s="713"/>
+      <c r="N92" s="713"/>
+      <c r="O92" s="714"/>
     </row>
     <row r="93" spans="1:15">
       <c r="A93" s="178"/>
@@ -23792,7 +23792,7 @@
       <c r="A16" s="197" t="s">
         <v>286</v>
       </c>
-      <c r="B16" s="197">
+      <c r="B16" s="715">
         <f>'Rent Calculation'!F54</f>
         <v>72</v>
       </c>

--- a/artifacts/Rental Specimen.xlsx
+++ b/artifacts/Rental Specimen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z0050s8t\Documents\rental-automation\artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72332E7-6E31-4CF6-A7F6-E84CA173A329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF91041-4CA4-40B4-B6D4-80B5A323F3D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="764" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="26" r:id="rId1"/>
@@ -4304,7 +4304,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="716">
+  <cellXfs count="718">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -5543,81 +5543,277 @@
     <xf numFmtId="37" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="8" xfId="190" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="33" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="29" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5639,201 +5835,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="33" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="29" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5921,7 +5922,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="8" xfId="190" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1012">
     <cellStyle name="??" xfId="303" xr:uid="{91225FB4-C7AB-4245-B40E-51FA489A4ADF}"/>
@@ -7471,62 +7473,62 @@
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1">
       <c r="A1" s="51"/>
-      <c r="B1" s="638"/>
-      <c r="C1" s="639"/>
-      <c r="D1" s="639"/>
-      <c r="E1" s="639"/>
-      <c r="F1" s="639"/>
-      <c r="G1" s="639"/>
-      <c r="H1" s="639"/>
-      <c r="I1" s="639"/>
-      <c r="J1" s="640"/>
+      <c r="B1" s="629"/>
+      <c r="C1" s="630"/>
+      <c r="D1" s="630"/>
+      <c r="E1" s="630"/>
+      <c r="F1" s="630"/>
+      <c r="G1" s="630"/>
+      <c r="H1" s="630"/>
+      <c r="I1" s="630"/>
+      <c r="J1" s="631"/>
     </row>
     <row r="2" spans="1:10" ht="14.25" customHeight="1">
       <c r="A2" s="51"/>
-      <c r="B2" s="641"/>
-      <c r="C2" s="642"/>
-      <c r="D2" s="642"/>
-      <c r="E2" s="642"/>
-      <c r="F2" s="642"/>
-      <c r="G2" s="642"/>
-      <c r="H2" s="642"/>
-      <c r="I2" s="642"/>
-      <c r="J2" s="643"/>
+      <c r="B2" s="632"/>
+      <c r="C2" s="633"/>
+      <c r="D2" s="633"/>
+      <c r="E2" s="633"/>
+      <c r="F2" s="633"/>
+      <c r="G2" s="633"/>
+      <c r="H2" s="633"/>
+      <c r="I2" s="633"/>
+      <c r="J2" s="634"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A3" s="51"/>
-      <c r="B3" s="644"/>
-      <c r="C3" s="645"/>
-      <c r="D3" s="645"/>
-      <c r="E3" s="645"/>
-      <c r="F3" s="645"/>
-      <c r="G3" s="645"/>
-      <c r="H3" s="645"/>
-      <c r="I3" s="642"/>
-      <c r="J3" s="643"/>
+      <c r="B3" s="635"/>
+      <c r="C3" s="636"/>
+      <c r="D3" s="636"/>
+      <c r="E3" s="636"/>
+      <c r="F3" s="636"/>
+      <c r="G3" s="636"/>
+      <c r="H3" s="636"/>
+      <c r="I3" s="633"/>
+      <c r="J3" s="634"/>
     </row>
     <row r="4" spans="1:10" ht="13">
       <c r="A4" s="51"/>
-      <c r="B4" s="665"/>
-      <c r="C4" s="666"/>
-      <c r="D4" s="666"/>
-      <c r="E4" s="666"/>
-      <c r="F4" s="666"/>
-      <c r="G4" s="666"/>
+      <c r="B4" s="654"/>
+      <c r="C4" s="655"/>
+      <c r="D4" s="655"/>
+      <c r="E4" s="655"/>
+      <c r="F4" s="655"/>
+      <c r="G4" s="655"/>
       <c r="H4" s="401"/>
       <c r="I4" s="402"/>
       <c r="J4" s="403"/>
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="51"/>
-      <c r="B5" s="667" t="s">
+      <c r="B5" s="656" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="668"/>
-      <c r="D5" s="668"/>
-      <c r="E5" s="668"/>
-      <c r="F5" s="668"/>
-      <c r="G5" s="669"/>
+      <c r="C5" s="657"/>
+      <c r="D5" s="657"/>
+      <c r="E5" s="657"/>
+      <c r="F5" s="657"/>
+      <c r="G5" s="658"/>
       <c r="H5" s="404"/>
       <c r="I5" s="481" t="s">
         <v>16</v>
@@ -7537,29 +7539,29 @@
     </row>
     <row r="6" spans="1:10" ht="13.5" thickBot="1">
       <c r="A6" s="51"/>
-      <c r="B6" s="670"/>
-      <c r="C6" s="671"/>
-      <c r="D6" s="672"/>
+      <c r="B6" s="659"/>
+      <c r="C6" s="660"/>
+      <c r="D6" s="661"/>
       <c r="E6" s="52"/>
-      <c r="F6" s="663">
+      <c r="F6" s="652">
         <v>10.763999999999999</v>
       </c>
-      <c r="G6" s="664"/>
+      <c r="G6" s="653"/>
       <c r="H6" s="405"/>
-      <c r="I6" s="651">
+      <c r="I6" s="643">
         <v>10.763999999999999</v>
       </c>
-      <c r="J6" s="652"/>
+      <c r="J6" s="644"/>
     </row>
     <row r="7" spans="1:10" ht="26">
       <c r="A7" s="51"/>
       <c r="B7" s="482" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="673" t="s">
+      <c r="C7" s="662" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="674"/>
+      <c r="D7" s="663"/>
       <c r="E7" s="483"/>
       <c r="F7" s="483" t="s">
         <v>303</v>
@@ -7587,23 +7589,23 @@
       <c r="C8" s="486"/>
       <c r="D8" s="487"/>
       <c r="E8" s="488"/>
-      <c r="F8" s="597" t="s">
+      <c r="F8" s="590" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="631"/>
+      <c r="G8" s="591"/>
       <c r="H8" s="404"/>
-      <c r="I8" s="632" t="s">
+      <c r="I8" s="592" t="s">
         <v>67</v>
       </c>
-      <c r="J8" s="633"/>
+      <c r="J8" s="593"/>
     </row>
     <row r="9" spans="1:10" ht="13">
       <c r="A9" s="51"/>
-      <c r="B9" s="632" t="s">
+      <c r="B9" s="592" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="631"/>
-      <c r="D9" s="598"/>
+      <c r="C9" s="591"/>
+      <c r="D9" s="607"/>
       <c r="E9" s="489"/>
       <c r="F9" s="376" t="s">
         <v>75</v>
@@ -7624,21 +7626,21 @@
       <c r="B10" s="490">
         <v>1</v>
       </c>
-      <c r="C10" s="646" t="s">
+      <c r="C10" s="637" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="605"/>
+      <c r="D10" s="638"/>
       <c r="E10" s="491"/>
-      <c r="F10" s="657" t="s">
+      <c r="F10" s="649" t="s">
         <v>299</v>
       </c>
-      <c r="G10" s="658"/>
+      <c r="G10" s="650"/>
       <c r="H10" s="404"/>
-      <c r="I10" s="653" t="str">
+      <c r="I10" s="645" t="str">
         <f>+F10</f>
         <v>Chennai</v>
       </c>
-      <c r="J10" s="654"/>
+      <c r="J10" s="646"/>
     </row>
     <row r="11" spans="1:10" ht="28.5" customHeight="1">
       <c r="A11" s="51"/>
@@ -7646,19 +7648,19 @@
         <f>1+B10</f>
         <v>2</v>
       </c>
-      <c r="C11" s="647" t="s">
+      <c r="C11" s="639" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="648"/>
+      <c r="D11" s="640"/>
       <c r="E11" s="50"/>
-      <c r="F11" s="657"/>
-      <c r="G11" s="658"/>
+      <c r="F11" s="649"/>
+      <c r="G11" s="650"/>
       <c r="H11" s="404"/>
-      <c r="I11" s="655">
+      <c r="I11" s="647">
         <f>+F11</f>
         <v>0</v>
       </c>
-      <c r="J11" s="656"/>
+      <c r="J11" s="648"/>
     </row>
     <row r="12" spans="1:10" ht="27.75" customHeight="1">
       <c r="A12" s="51"/>
@@ -7666,19 +7668,19 @@
         <f>1+B11</f>
         <v>3</v>
       </c>
-      <c r="C12" s="591" t="s">
+      <c r="C12" s="600" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="590"/>
+      <c r="D12" s="601"/>
       <c r="E12" s="492"/>
-      <c r="F12" s="659"/>
-      <c r="G12" s="660"/>
+      <c r="F12" s="628"/>
+      <c r="G12" s="623"/>
       <c r="H12" s="404"/>
-      <c r="I12" s="675">
+      <c r="I12" s="624">
         <f>+F12</f>
         <v>0</v>
       </c>
-      <c r="J12" s="676"/>
+      <c r="J12" s="625"/>
     </row>
     <row r="13" spans="1:10" ht="15.9" customHeight="1">
       <c r="A13" s="51"/>
@@ -7686,16 +7688,16 @@
         <f t="shared" ref="B13:B30" si="0">1+B12</f>
         <v>4</v>
       </c>
-      <c r="C13" s="591" t="s">
+      <c r="C13" s="600" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="590"/>
+      <c r="D13" s="601"/>
       <c r="E13" s="50"/>
-      <c r="F13" s="662"/>
-      <c r="G13" s="660"/>
+      <c r="F13" s="622"/>
+      <c r="G13" s="623"/>
       <c r="H13" s="404"/>
-      <c r="I13" s="675"/>
-      <c r="J13" s="676"/>
+      <c r="I13" s="624"/>
+      <c r="J13" s="625"/>
     </row>
     <row r="14" spans="1:10" ht="48" customHeight="1">
       <c r="A14" s="51"/>
@@ -7703,21 +7705,21 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="649" t="s">
+      <c r="C14" s="641" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="650"/>
+      <c r="D14" s="642"/>
       <c r="E14" s="476"/>
-      <c r="F14" s="659" t="s">
+      <c r="F14" s="628" t="s">
         <v>300</v>
       </c>
-      <c r="G14" s="661"/>
+      <c r="G14" s="651"/>
       <c r="H14" s="404"/>
-      <c r="I14" s="675" t="str">
+      <c r="I14" s="624" t="str">
         <f>+F14</f>
         <v>6th floor</v>
       </c>
-      <c r="J14" s="676"/>
+      <c r="J14" s="625"/>
     </row>
     <row r="15" spans="1:10" ht="51.75" customHeight="1">
       <c r="A15" s="51"/>
@@ -7725,19 +7727,19 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="591" t="s">
+      <c r="C15" s="600" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="590"/>
+      <c r="D15" s="601"/>
       <c r="E15" s="58"/>
-      <c r="F15" s="597"/>
-      <c r="G15" s="631"/>
+      <c r="F15" s="590"/>
+      <c r="G15" s="591"/>
       <c r="H15" s="404"/>
-      <c r="I15" s="632">
+      <c r="I15" s="592">
         <f>+F15</f>
         <v>0</v>
       </c>
-      <c r="J15" s="633"/>
+      <c r="J15" s="593"/>
     </row>
     <row r="16" spans="1:10" ht="15.9" customHeight="1">
       <c r="A16" s="51"/>
@@ -7745,16 +7747,16 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="591" t="s">
+      <c r="C16" s="600" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="590"/>
+      <c r="D16" s="601"/>
       <c r="E16" s="58"/>
-      <c r="F16" s="662"/>
-      <c r="G16" s="660"/>
+      <c r="F16" s="622"/>
+      <c r="G16" s="623"/>
       <c r="H16" s="404"/>
-      <c r="I16" s="675"/>
-      <c r="J16" s="676"/>
+      <c r="I16" s="624"/>
+      <c r="J16" s="625"/>
     </row>
     <row r="17" spans="1:10" ht="15.9" customHeight="1">
       <c r="A17" s="51"/>
@@ -7762,21 +7764,21 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="591" t="s">
+      <c r="C17" s="600" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="590"/>
+      <c r="D17" s="601"/>
       <c r="E17" s="58"/>
-      <c r="F17" s="659" t="s">
+      <c r="F17" s="628" t="s">
         <v>85</v>
       </c>
-      <c r="G17" s="660"/>
+      <c r="G17" s="623"/>
       <c r="H17" s="404"/>
-      <c r="I17" s="675" t="str">
+      <c r="I17" s="624" t="str">
         <f>+F17</f>
         <v>Warm Shell</v>
       </c>
-      <c r="J17" s="676"/>
+      <c r="J17" s="625"/>
     </row>
     <row r="18" spans="1:10" ht="48" customHeight="1">
       <c r="A18" s="51"/>
@@ -7784,22 +7786,22 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="591" t="s">
+      <c r="C18" s="600" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="590"/>
+      <c r="D18" s="601"/>
       <c r="E18" s="163"/>
-      <c r="F18" s="597">
+      <c r="F18" s="590">
         <f>F15</f>
         <v>0</v>
       </c>
-      <c r="G18" s="631"/>
+      <c r="G18" s="591"/>
       <c r="H18" s="404"/>
-      <c r="I18" s="632">
+      <c r="I18" s="592">
         <f>+F18</f>
         <v>0</v>
       </c>
-      <c r="J18" s="633"/>
+      <c r="J18" s="593"/>
     </row>
     <row r="19" spans="1:10" ht="15.9" customHeight="1">
       <c r="A19" s="51"/>
@@ -7807,16 +7809,16 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="591" t="s">
+      <c r="C19" s="600" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="590"/>
+      <c r="D19" s="601"/>
       <c r="E19" s="163"/>
-      <c r="F19" s="662"/>
-      <c r="G19" s="660"/>
+      <c r="F19" s="622"/>
+      <c r="G19" s="623"/>
       <c r="H19" s="404"/>
-      <c r="I19" s="675"/>
-      <c r="J19" s="676"/>
+      <c r="I19" s="624"/>
+      <c r="J19" s="625"/>
     </row>
     <row r="20" spans="1:10" ht="15.9" customHeight="1">
       <c r="A20" s="51"/>
@@ -7824,10 +7826,10 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="589" t="s">
+      <c r="C20" s="594" t="s">
         <v>88</v>
       </c>
-      <c r="D20" s="590"/>
+      <c r="D20" s="601"/>
       <c r="E20" s="494"/>
       <c r="F20" s="56"/>
       <c r="G20" s="388"/>
@@ -7847,10 +7849,10 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="591" t="s">
+      <c r="C21" s="600" t="s">
         <v>89</v>
       </c>
-      <c r="D21" s="590"/>
+      <c r="D21" s="601"/>
       <c r="E21" s="494"/>
       <c r="F21" s="56">
         <f>Main!B3</f>
@@ -7876,10 +7878,10 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="589" t="s">
+      <c r="C22" s="594" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="590"/>
+      <c r="D22" s="601"/>
       <c r="E22" s="494"/>
       <c r="F22" s="56">
         <v>0</v>
@@ -7903,10 +7905,10 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="591" t="s">
+      <c r="C23" s="600" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="590"/>
+      <c r="D23" s="601"/>
       <c r="E23" s="494"/>
       <c r="F23" s="56">
         <f>+F21+F22</f>
@@ -7932,10 +7934,10 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="591" t="s">
+      <c r="C24" s="600" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="590"/>
+      <c r="D24" s="601"/>
       <c r="E24" s="59"/>
       <c r="F24" s="56"/>
       <c r="G24" s="388">
@@ -7958,10 +7960,10 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="591" t="s">
+      <c r="C25" s="600" t="s">
         <v>93</v>
       </c>
-      <c r="D25" s="590"/>
+      <c r="D25" s="601"/>
       <c r="E25" s="59"/>
       <c r="F25" s="56">
         <v>0</v>
@@ -7986,10 +7988,10 @@
         <f>1+B25</f>
         <v>17</v>
       </c>
-      <c r="C26" s="591" t="s">
+      <c r="C26" s="600" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="590"/>
+      <c r="D26" s="601"/>
       <c r="E26" s="60"/>
       <c r="F26" s="61">
         <f>F25/F23</f>
@@ -8015,10 +8017,10 @@
         <f>1+B26</f>
         <v>18</v>
       </c>
-      <c r="C27" s="589" t="s">
+      <c r="C27" s="594" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="590"/>
+      <c r="D27" s="601"/>
       <c r="E27" s="58"/>
       <c r="F27" s="293">
         <f>'CAPEX and PM'!E3</f>
@@ -8044,10 +8046,10 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="589" t="s">
+      <c r="C28" s="594" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="590"/>
+      <c r="D28" s="601"/>
       <c r="E28" s="64"/>
       <c r="F28" s="64">
         <f>Main!B12</f>
@@ -8073,10 +8075,10 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="589" t="s">
+      <c r="C29" s="594" t="s">
         <v>97</v>
       </c>
-      <c r="D29" s="590"/>
+      <c r="D29" s="601"/>
       <c r="E29" s="64"/>
       <c r="F29" s="60">
         <f>Main!B13</f>
@@ -8102,10 +8104,10 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="591" t="s">
+      <c r="C30" s="600" t="s">
         <v>98</v>
       </c>
-      <c r="D30" s="590"/>
+      <c r="D30" s="601"/>
       <c r="E30" s="58"/>
       <c r="F30" s="56">
         <v>0</v>
@@ -8126,11 +8128,11 @@
     </row>
     <row r="31" spans="1:10" ht="15.9" customHeight="1">
       <c r="A31" s="51"/>
-      <c r="B31" s="677" t="s">
+      <c r="B31" s="619" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="678"/>
-      <c r="D31" s="679"/>
+      <c r="C31" s="620"/>
+      <c r="D31" s="621"/>
       <c r="E31" s="497"/>
       <c r="F31" s="376" t="s">
         <v>75</v>
@@ -8151,10 +8153,10 @@
       <c r="B32" s="162">
         <v>1</v>
       </c>
-      <c r="C32" s="589" t="s">
+      <c r="C32" s="594" t="s">
         <v>100</v>
       </c>
-      <c r="D32" s="590"/>
+      <c r="D32" s="601"/>
       <c r="E32" s="59"/>
       <c r="F32" s="56">
         <f>Main!B9/(Main!B3*Main!B7)</f>
@@ -8180,10 +8182,10 @@
         <f>1+B32</f>
         <v>2</v>
       </c>
-      <c r="C33" s="589" t="s">
+      <c r="C33" s="594" t="s">
         <v>101</v>
       </c>
-      <c r="D33" s="590"/>
+      <c r="D33" s="601"/>
       <c r="E33" s="59"/>
       <c r="F33" s="56">
         <v>0</v>
@@ -8207,10 +8209,10 @@
         <f t="shared" ref="B34:B47" si="1">1+B33</f>
         <v>3</v>
       </c>
-      <c r="C34" s="589" t="s">
+      <c r="C34" s="594" t="s">
         <v>102</v>
       </c>
-      <c r="D34" s="590"/>
+      <c r="D34" s="601"/>
       <c r="E34" s="59"/>
       <c r="F34" s="56">
         <v>0</v>
@@ -8235,10 +8237,10 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="C35" s="591" t="s">
+      <c r="C35" s="600" t="s">
         <v>103</v>
       </c>
-      <c r="D35" s="590"/>
+      <c r="D35" s="601"/>
       <c r="E35" s="498"/>
       <c r="F35" s="68">
         <v>0</v>
@@ -8260,10 +8262,10 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="C36" s="589" t="s">
+      <c r="C36" s="594" t="s">
         <v>104</v>
       </c>
-      <c r="D36" s="590"/>
+      <c r="D36" s="601"/>
       <c r="E36" s="498"/>
       <c r="F36" s="70">
         <f>'Lease Rent'!H37</f>
@@ -8289,10 +8291,10 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="C37" s="589" t="s">
+      <c r="C37" s="594" t="s">
         <v>105</v>
       </c>
-      <c r="D37" s="590"/>
+      <c r="D37" s="601"/>
       <c r="E37" s="498"/>
       <c r="F37" s="70"/>
       <c r="G37" s="204">
@@ -8309,10 +8311,10 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="C38" s="589" t="s">
+      <c r="C38" s="594" t="s">
         <v>106</v>
       </c>
-      <c r="D38" s="590"/>
+      <c r="D38" s="601"/>
       <c r="E38" s="71"/>
       <c r="F38" s="70">
         <f>'Lease Rent'!J31</f>
@@ -8338,10 +8340,10 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="C39" s="589" t="s">
+      <c r="C39" s="594" t="s">
         <v>107</v>
       </c>
-      <c r="D39" s="590"/>
+      <c r="D39" s="601"/>
       <c r="E39" s="498"/>
       <c r="F39" s="70">
         <f>F36</f>
@@ -8367,10 +8369,10 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="C40" s="589" t="s">
+      <c r="C40" s="594" t="s">
         <v>108</v>
       </c>
-      <c r="D40" s="590"/>
+      <c r="D40" s="601"/>
       <c r="E40" s="498"/>
       <c r="F40" s="70">
         <v>0</v>
@@ -8395,10 +8397,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="C41" s="589" t="s">
+      <c r="C41" s="594" t="s">
         <v>109</v>
       </c>
-      <c r="D41" s="590"/>
+      <c r="D41" s="601"/>
       <c r="E41" s="58"/>
       <c r="F41" s="114">
         <f>F38</f>
@@ -8424,10 +8426,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="C42" s="591" t="s">
+      <c r="C42" s="600" t="s">
         <v>110</v>
       </c>
-      <c r="D42" s="590"/>
+      <c r="D42" s="601"/>
       <c r="E42" s="59"/>
       <c r="F42" s="109">
         <v>0</v>
@@ -8452,10 +8454,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="C43" s="591" t="s">
+      <c r="C43" s="600" t="s">
         <v>111</v>
       </c>
-      <c r="D43" s="590"/>
+      <c r="D43" s="601"/>
       <c r="E43" s="73"/>
       <c r="F43" s="68">
         <v>0</v>
@@ -8480,10 +8482,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="C44" s="591" t="s">
+      <c r="C44" s="600" t="s">
         <v>112</v>
       </c>
-      <c r="D44" s="590"/>
+      <c r="D44" s="601"/>
       <c r="E44" s="59"/>
       <c r="F44" s="56">
         <f>'Lease Rent'!C22</f>
@@ -8509,10 +8511,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="C45" s="589" t="s">
+      <c r="C45" s="594" t="s">
         <v>113</v>
       </c>
-      <c r="D45" s="590"/>
+      <c r="D45" s="601"/>
       <c r="E45" s="59"/>
       <c r="F45" s="109">
         <v>0</v>
@@ -8534,10 +8536,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="C46" s="591" t="s">
+      <c r="C46" s="600" t="s">
         <v>111</v>
       </c>
-      <c r="D46" s="590"/>
+      <c r="D46" s="601"/>
       <c r="E46" s="59"/>
       <c r="F46" s="56">
         <f>'Lease Rent'!D23</f>
@@ -8554,10 +8556,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="C47" s="591" t="s">
+      <c r="C47" s="600" t="s">
         <v>112</v>
       </c>
-      <c r="D47" s="590"/>
+      <c r="D47" s="601"/>
       <c r="E47" s="59"/>
       <c r="F47" s="56">
         <f>'Lease Rent'!C23</f>
@@ -8570,46 +8572,46 @@
     </row>
     <row r="48" spans="1:10" ht="28.5" customHeight="1">
       <c r="A48" s="51"/>
-      <c r="B48" s="636">
+      <c r="B48" s="666">
         <f>1+B47</f>
         <v>17</v>
       </c>
-      <c r="C48" s="589" t="s">
+      <c r="C48" s="594" t="s">
         <v>114</v>
       </c>
-      <c r="D48" s="590"/>
+      <c r="D48" s="601"/>
       <c r="E48" s="73"/>
-      <c r="F48" s="682" t="str">
+      <c r="F48" s="610" t="str">
         <f>Main!B14</f>
         <v>15% every 3 years</v>
       </c>
-      <c r="G48" s="683"/>
+      <c r="G48" s="611"/>
       <c r="H48" s="404"/>
-      <c r="I48" s="675" t="str">
+      <c r="I48" s="624" t="str">
         <f>+F48</f>
         <v>15% every 3 years</v>
       </c>
-      <c r="J48" s="676"/>
+      <c r="J48" s="625"/>
     </row>
     <row r="49" spans="1:18" ht="15.9" customHeight="1">
       <c r="A49" s="51"/>
-      <c r="B49" s="637"/>
-      <c r="C49" s="589" t="s">
+      <c r="B49" s="667"/>
+      <c r="C49" s="594" t="s">
         <v>115</v>
       </c>
-      <c r="D49" s="590"/>
+      <c r="D49" s="601"/>
       <c r="E49" s="73"/>
-      <c r="F49" s="682" t="str">
+      <c r="F49" s="610" t="str">
         <f>Main!B15</f>
         <v>5% every years</v>
       </c>
-      <c r="G49" s="683"/>
+      <c r="G49" s="611"/>
       <c r="H49" s="404"/>
-      <c r="I49" s="680" t="str">
+      <c r="I49" s="626" t="str">
         <f t="shared" ref="I49:I56" si="2">F49</f>
         <v>5% every years</v>
       </c>
-      <c r="J49" s="681"/>
+      <c r="J49" s="627"/>
     </row>
     <row r="50" spans="1:18" ht="15.9" customHeight="1">
       <c r="A50" s="51"/>
@@ -8617,22 +8619,22 @@
         <f>1+B48</f>
         <v>18</v>
       </c>
-      <c r="C50" s="591" t="s">
+      <c r="C50" s="600" t="s">
         <v>116</v>
       </c>
-      <c r="D50" s="590"/>
+      <c r="D50" s="601"/>
       <c r="E50" s="73"/>
-      <c r="F50" s="627">
+      <c r="F50" s="608">
         <f>'Lease Rent'!B31</f>
         <v>46023</v>
       </c>
-      <c r="G50" s="628"/>
+      <c r="G50" s="609"/>
       <c r="H50" s="404"/>
-      <c r="I50" s="629">
+      <c r="I50" s="617">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J50" s="630"/>
+      <c r="J50" s="618"/>
     </row>
     <row r="51" spans="1:18" ht="15.9" customHeight="1">
       <c r="A51" s="51"/>
@@ -8640,22 +8642,22 @@
         <f t="shared" ref="B51:B57" si="3">1+B50</f>
         <v>19</v>
       </c>
-      <c r="C51" s="589" t="s">
+      <c r="C51" s="594" t="s">
         <v>117</v>
       </c>
-      <c r="D51" s="590"/>
+      <c r="D51" s="601"/>
       <c r="E51" s="73"/>
-      <c r="F51" s="627">
+      <c r="F51" s="608">
         <f>'Lease Rent'!C102</f>
         <v>48213</v>
       </c>
-      <c r="G51" s="628"/>
+      <c r="G51" s="609"/>
       <c r="H51" s="404"/>
-      <c r="I51" s="629">
+      <c r="I51" s="617">
         <f>F51</f>
         <v>48213</v>
       </c>
-      <c r="J51" s="630"/>
+      <c r="J51" s="618"/>
     </row>
     <row r="52" spans="1:18" ht="15.9" customHeight="1">
       <c r="A52" s="51"/>
@@ -8663,22 +8665,22 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="C52" s="589" t="s">
+      <c r="C52" s="594" t="s">
         <v>118</v>
       </c>
-      <c r="D52" s="599"/>
+      <c r="D52" s="595"/>
       <c r="E52" s="73"/>
-      <c r="F52" s="627">
+      <c r="F52" s="608">
         <f>F50</f>
         <v>46023</v>
       </c>
-      <c r="G52" s="628"/>
+      <c r="G52" s="609"/>
       <c r="H52" s="404"/>
-      <c r="I52" s="629">
+      <c r="I52" s="617">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J52" s="630"/>
+      <c r="J52" s="618"/>
     </row>
     <row r="53" spans="1:18" ht="15.9" customHeight="1">
       <c r="A53" s="51"/>
@@ -8686,21 +8688,21 @@
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="C53" s="589" t="s">
+      <c r="C53" s="594" t="s">
         <v>119</v>
       </c>
-      <c r="D53" s="599"/>
+      <c r="D53" s="595"/>
       <c r="E53" s="73"/>
-      <c r="F53" s="597">
-        <v>0</v>
-      </c>
-      <c r="G53" s="631"/>
+      <c r="F53" s="590">
+        <v>0</v>
+      </c>
+      <c r="G53" s="591"/>
       <c r="H53" s="404"/>
-      <c r="I53" s="632">
+      <c r="I53" s="592">
         <f>+F53</f>
         <v>0</v>
       </c>
-      <c r="J53" s="633"/>
+      <c r="J53" s="593"/>
     </row>
     <row r="54" spans="1:18" ht="15.9" customHeight="1">
       <c r="A54" s="51"/>
@@ -8708,10 +8710,10 @@
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="C54" s="591" t="s">
+      <c r="C54" s="600" t="s">
         <v>120</v>
       </c>
-      <c r="D54" s="590"/>
+      <c r="D54" s="601"/>
       <c r="E54" s="58"/>
       <c r="F54" s="56">
         <f>(F51-F50)/365*12</f>
@@ -8738,10 +8740,10 @@
         <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="C55" s="591" t="s">
+      <c r="C55" s="600" t="s">
         <v>121</v>
       </c>
-      <c r="D55" s="590"/>
+      <c r="D55" s="601"/>
       <c r="E55" s="71"/>
       <c r="F55" s="56">
         <v>0</v>
@@ -8767,10 +8769,10 @@
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="C56" s="591" t="s">
+      <c r="C56" s="600" t="s">
         <v>122</v>
       </c>
-      <c r="D56" s="590"/>
+      <c r="D56" s="601"/>
       <c r="E56" s="71"/>
       <c r="F56" s="302" t="s">
         <v>68</v>
@@ -8796,10 +8798,10 @@
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="C57" s="591" t="s">
+      <c r="C57" s="600" t="s">
         <v>123</v>
       </c>
-      <c r="D57" s="590"/>
+      <c r="D57" s="601"/>
       <c r="E57" s="71"/>
       <c r="F57" s="56"/>
       <c r="G57" s="388"/>
@@ -8814,23 +8816,23 @@
       <c r="C58" s="74"/>
       <c r="D58" s="74"/>
       <c r="E58" s="58"/>
-      <c r="F58" s="597" t="s">
+      <c r="F58" s="590" t="s">
         <v>73</v>
       </c>
-      <c r="G58" s="631"/>
+      <c r="G58" s="591"/>
       <c r="H58" s="404"/>
-      <c r="I58" s="632" t="s">
+      <c r="I58" s="592" t="s">
         <v>67</v>
       </c>
-      <c r="J58" s="633"/>
+      <c r="J58" s="593"/>
     </row>
     <row r="59" spans="1:18" ht="15.9" customHeight="1">
       <c r="A59" s="51"/>
-      <c r="B59" s="634" t="s">
+      <c r="B59" s="664" t="s">
         <v>124</v>
       </c>
-      <c r="C59" s="635"/>
-      <c r="D59" s="635"/>
+      <c r="C59" s="665"/>
+      <c r="D59" s="665"/>
       <c r="E59" s="497"/>
       <c r="F59" s="376" t="s">
         <v>75</v>
@@ -8851,10 +8853,10 @@
       <c r="B60" s="162">
         <v>1</v>
       </c>
-      <c r="C60" s="589" t="s">
+      <c r="C60" s="594" t="s">
         <v>125</v>
       </c>
-      <c r="D60" s="590"/>
+      <c r="D60" s="601"/>
       <c r="E60" s="499"/>
       <c r="F60" s="70">
         <f>C220/F21/F54</f>
@@ -8880,10 +8882,10 @@
         <f>1+B60</f>
         <v>2</v>
       </c>
-      <c r="C61" s="589" t="s">
+      <c r="C61" s="594" t="s">
         <v>126</v>
       </c>
-      <c r="D61" s="590"/>
+      <c r="D61" s="601"/>
       <c r="E61" s="499"/>
       <c r="F61" s="70">
         <v>0</v>
@@ -8907,10 +8909,10 @@
         <f t="shared" ref="B62:B83" si="4">1+B61</f>
         <v>3</v>
       </c>
-      <c r="C62" s="592" t="s">
+      <c r="C62" s="596" t="s">
         <v>127</v>
       </c>
-      <c r="D62" s="593"/>
+      <c r="D62" s="597"/>
       <c r="E62" s="75"/>
       <c r="F62" s="76">
         <f>F60+F61</f>
@@ -8936,10 +8938,10 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="C63" s="589" t="s">
+      <c r="C63" s="594" t="s">
         <v>321</v>
       </c>
-      <c r="D63" s="590"/>
+      <c r="D63" s="601"/>
       <c r="E63" s="56"/>
       <c r="F63" s="54">
         <f>F62*F21</f>
@@ -8965,10 +8967,10 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="C64" s="589" t="s">
+      <c r="C64" s="594" t="s">
         <v>128</v>
       </c>
-      <c r="D64" s="590"/>
+      <c r="D64" s="601"/>
       <c r="E64" s="56"/>
       <c r="F64" s="70">
         <f>I220/F21/F54</f>
@@ -8994,10 +8996,10 @@
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="C65" s="591" t="s">
+      <c r="C65" s="600" t="s">
         <v>322</v>
       </c>
-      <c r="D65" s="590"/>
+      <c r="D65" s="601"/>
       <c r="E65" s="71"/>
       <c r="F65" s="54">
         <f>+F64*F21</f>
@@ -9023,10 +9025,10 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="C66" s="591" t="s">
+      <c r="C66" s="600" t="s">
         <v>323</v>
       </c>
-      <c r="D66" s="590"/>
+      <c r="D66" s="601"/>
       <c r="E66" s="59"/>
       <c r="F66" s="56">
         <f>(+G220/F54)</f>
@@ -9052,10 +9054,10 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="C67" s="591" t="s">
+      <c r="C67" s="600" t="s">
         <v>129</v>
       </c>
-      <c r="D67" s="590"/>
+      <c r="D67" s="601"/>
       <c r="E67" s="56"/>
       <c r="F67" s="56">
         <f>Main!B9</f>
@@ -9081,10 +9083,10 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="C68" s="591" t="s">
+      <c r="C68" s="600" t="s">
         <v>130</v>
       </c>
-      <c r="D68" s="590"/>
+      <c r="D68" s="601"/>
       <c r="E68" s="56"/>
       <c r="F68" s="56">
         <v>0</v>
@@ -9109,10 +9111,10 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="C69" s="589" t="s">
+      <c r="C69" s="594" t="s">
         <v>131</v>
       </c>
-      <c r="D69" s="590"/>
+      <c r="D69" s="601"/>
       <c r="E69" s="56"/>
       <c r="F69" s="56">
         <v>500000</v>
@@ -9137,10 +9139,10 @@
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="C70" s="591" t="s">
+      <c r="C70" s="600" t="s">
         <v>132</v>
       </c>
-      <c r="D70" s="590"/>
+      <c r="D70" s="601"/>
       <c r="E70" s="56"/>
       <c r="F70" s="54">
         <v>0</v>
@@ -9162,10 +9164,10 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="C71" s="591" t="s">
+      <c r="C71" s="600" t="s">
         <v>133</v>
       </c>
-      <c r="D71" s="590"/>
+      <c r="D71" s="601"/>
       <c r="E71" s="56"/>
       <c r="F71" s="54">
         <f>F38*F23*F33</f>
@@ -9191,10 +9193,10 @@
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="C72" s="591" t="s">
+      <c r="C72" s="600" t="s">
         <v>134</v>
       </c>
-      <c r="D72" s="590"/>
+      <c r="D72" s="601"/>
       <c r="E72" s="56"/>
       <c r="F72" s="56">
         <v>0</v>
@@ -9219,10 +9221,10 @@
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="C73" s="589" t="s">
+      <c r="C73" s="594" t="s">
         <v>135</v>
       </c>
-      <c r="D73" s="590"/>
+      <c r="D73" s="601"/>
       <c r="E73" s="498"/>
       <c r="F73" s="68">
         <f>+F35*F63</f>
@@ -9276,10 +9278,10 @@
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="C75" s="589" t="s">
+      <c r="C75" s="594" t="s">
         <v>137</v>
       </c>
-      <c r="D75" s="590"/>
+      <c r="D75" s="601"/>
       <c r="E75" s="59"/>
       <c r="F75" s="56">
         <f>+F77/F23</f>
@@ -9305,10 +9307,10 @@
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="C76" s="589" t="s">
+      <c r="C76" s="594" t="s">
         <v>138</v>
       </c>
-      <c r="D76" s="590"/>
+      <c r="D76" s="601"/>
       <c r="E76" s="71"/>
       <c r="F76" s="51"/>
       <c r="G76" s="493"/>
@@ -9328,10 +9330,10 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="C77" s="589" t="s">
+      <c r="C77" s="594" t="s">
         <v>139</v>
       </c>
-      <c r="D77" s="590"/>
+      <c r="D77" s="601"/>
       <c r="E77" s="71"/>
       <c r="F77" s="56">
         <f>'CAPEX and PM'!B6</f>
@@ -9357,10 +9359,10 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="C78" s="589" t="s">
+      <c r="C78" s="594" t="s">
         <v>140</v>
       </c>
-      <c r="D78" s="590"/>
+      <c r="D78" s="601"/>
       <c r="E78" s="71"/>
       <c r="F78" s="56">
         <f>'CAPEX and PM'!B37</f>
@@ -9386,10 +9388,10 @@
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="C79" s="589" t="s">
+      <c r="C79" s="594" t="s">
         <v>141</v>
       </c>
-      <c r="D79" s="590"/>
+      <c r="D79" s="601"/>
       <c r="E79" s="71"/>
       <c r="F79" s="56">
         <f>+'CAPEX and PM'!B95</f>
@@ -9415,10 +9417,10 @@
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="C80" s="589" t="s">
+      <c r="C80" s="594" t="s">
         <v>142</v>
       </c>
-      <c r="D80" s="590"/>
+      <c r="D80" s="601"/>
       <c r="E80" s="71"/>
       <c r="F80" s="56"/>
       <c r="G80" s="388"/>
@@ -9438,10 +9440,10 @@
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="C81" s="589" t="s">
+      <c r="C81" s="594" t="s">
         <v>143</v>
       </c>
-      <c r="D81" s="599"/>
+      <c r="D81" s="595"/>
       <c r="E81" s="71"/>
       <c r="F81" s="56"/>
       <c r="G81" s="388"/>
@@ -9461,10 +9463,10 @@
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="C82" s="589" t="s">
+      <c r="C82" s="594" t="s">
         <v>144</v>
       </c>
-      <c r="D82" s="590"/>
+      <c r="D82" s="601"/>
       <c r="E82" s="59"/>
       <c r="F82" s="56">
         <f>+G207</f>
@@ -9490,10 +9492,10 @@
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="C83" s="589" t="s">
+      <c r="C83" s="594" t="s">
         <v>324</v>
       </c>
-      <c r="D83" s="590"/>
+      <c r="D83" s="601"/>
       <c r="E83" s="498"/>
       <c r="F83" s="56">
         <f>+F30</f>
@@ -9526,11 +9528,11 @@
     </row>
     <row r="85" spans="1:24" ht="15.9" customHeight="1">
       <c r="A85" s="51"/>
-      <c r="B85" s="611" t="s">
+      <c r="B85" s="602" t="s">
         <v>145</v>
       </c>
-      <c r="C85" s="612"/>
-      <c r="D85" s="613"/>
+      <c r="C85" s="603"/>
+      <c r="D85" s="604"/>
       <c r="E85" s="389"/>
       <c r="F85" s="161" t="s">
         <v>75</v>
@@ -9551,10 +9553,10 @@
       <c r="B86" s="162">
         <v>1</v>
       </c>
-      <c r="C86" s="589" t="s">
+      <c r="C86" s="594" t="s">
         <v>146</v>
       </c>
-      <c r="D86" s="590"/>
+      <c r="D86" s="601"/>
       <c r="E86" s="71"/>
       <c r="F86" s="70">
         <f>+F62</f>
@@ -9583,10 +9585,10 @@
         <f>1+B86</f>
         <v>2</v>
       </c>
-      <c r="C87" s="591" t="s">
+      <c r="C87" s="600" t="s">
         <v>147</v>
       </c>
-      <c r="D87" s="590"/>
+      <c r="D87" s="601"/>
       <c r="E87" s="73"/>
       <c r="F87" s="56">
         <v>0</v>
@@ -9609,10 +9611,10 @@
         <f t="shared" ref="B88:B94" si="7">+B87+1</f>
         <v>3</v>
       </c>
-      <c r="C88" s="591" t="s">
+      <c r="C88" s="600" t="s">
         <v>148</v>
       </c>
-      <c r="D88" s="590"/>
+      <c r="D88" s="601"/>
       <c r="E88" s="73"/>
       <c r="F88" s="70">
         <f>(F66/F23)</f>
@@ -9640,10 +9642,10 @@
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="C89" s="591" t="s">
+      <c r="C89" s="600" t="s">
         <v>149</v>
       </c>
-      <c r="D89" s="590"/>
+      <c r="D89" s="601"/>
       <c r="E89" s="73"/>
       <c r="F89" s="66">
         <f>'Security Deposit'!C17</f>
@@ -9671,10 +9673,10 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="C90" s="591" t="s">
+      <c r="C90" s="600" t="s">
         <v>289</v>
       </c>
-      <c r="D90" s="590"/>
+      <c r="D90" s="601"/>
       <c r="E90" s="73"/>
       <c r="F90" s="202">
         <f>+F64</f>
@@ -9702,10 +9704,10 @@
         <f>+B89+1</f>
         <v>5</v>
       </c>
-      <c r="C91" s="591" t="s">
+      <c r="C91" s="600" t="s">
         <v>150</v>
       </c>
-      <c r="D91" s="590"/>
+      <c r="D91" s="601"/>
       <c r="E91" s="73"/>
       <c r="F91" s="66">
         <f>(+F83/F21/F54)</f>
@@ -9732,10 +9734,10 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="C92" s="591" t="s">
+      <c r="C92" s="600" t="s">
         <v>151</v>
       </c>
-      <c r="D92" s="590"/>
+      <c r="D92" s="601"/>
       <c r="E92" s="73"/>
       <c r="F92" s="66">
         <f>F82/F21/F54</f>
@@ -9763,10 +9765,10 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="C93" s="589" t="s">
+      <c r="C93" s="594" t="s">
         <v>152</v>
       </c>
-      <c r="D93" s="590"/>
+      <c r="D93" s="601"/>
       <c r="E93" s="71"/>
       <c r="F93" s="66">
         <f>+G93/F6</f>
@@ -9794,10 +9796,10 @@
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="C94" s="592" t="s">
+      <c r="C94" s="596" t="s">
         <v>69</v>
       </c>
-      <c r="D94" s="593"/>
+      <c r="D94" s="597"/>
       <c r="E94" s="78"/>
       <c r="F94" s="213">
         <f>SUM(F86:F93)</f>
@@ -9822,8 +9824,8 @@
     <row r="95" spans="1:24" ht="15.9" customHeight="1">
       <c r="A95" s="51"/>
       <c r="B95" s="381"/>
-      <c r="C95" s="631"/>
-      <c r="D95" s="631"/>
+      <c r="C95" s="591"/>
+      <c r="D95" s="591"/>
       <c r="E95" s="84"/>
       <c r="F95" s="85"/>
       <c r="G95" s="85"/>
@@ -9833,11 +9835,11 @@
     </row>
     <row r="96" spans="1:24" ht="15.9" customHeight="1">
       <c r="A96" s="51"/>
-      <c r="B96" s="594" t="s">
+      <c r="B96" s="598" t="s">
         <v>153</v>
       </c>
-      <c r="C96" s="595"/>
-      <c r="D96" s="595"/>
+      <c r="C96" s="599"/>
+      <c r="D96" s="599"/>
       <c r="E96" s="87"/>
       <c r="F96" s="161" t="s">
         <v>75</v>
@@ -9859,11 +9861,11 @@
       <c r="B97" s="162">
         <v>1</v>
       </c>
-      <c r="C97" s="591" t="str">
+      <c r="C97" s="600" t="str">
         <f>+C76</f>
         <v>Siemens Standard Fitout (Existing)</v>
       </c>
-      <c r="D97" s="590"/>
+      <c r="D97" s="601"/>
       <c r="E97" s="88"/>
       <c r="F97" s="66">
         <v>0</v>
@@ -9889,11 +9891,11 @@
         <f t="shared" ref="B98:B103" si="8">+B97+1</f>
         <v>2</v>
       </c>
-      <c r="C98" s="591" t="str">
+      <c r="C98" s="600" t="str">
         <f>+C77</f>
         <v>Siemens Standard Fitout (New)</v>
       </c>
-      <c r="D98" s="590"/>
+      <c r="D98" s="601"/>
       <c r="E98" s="71"/>
       <c r="F98" s="66">
         <f>'CAPEX and PM'!B29</f>
@@ -9921,11 +9923,11 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="C99" s="591" t="str">
+      <c r="C99" s="600" t="str">
         <f>+C78</f>
         <v>Capex over the period of lease period</v>
       </c>
-      <c r="D99" s="590"/>
+      <c r="D99" s="601"/>
       <c r="E99" s="71"/>
       <c r="F99" s="66">
         <f>'CAPEX and PM'!B89</f>
@@ -9953,11 +9955,11 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="C100" s="591" t="str">
+      <c r="C100" s="600" t="str">
         <f>+C79</f>
         <v>PM cost over the period of lease period</v>
       </c>
-      <c r="D100" s="590"/>
+      <c r="D100" s="601"/>
       <c r="E100" s="71"/>
       <c r="F100" s="66">
         <f>+'CAPEX and PM'!B96</f>
@@ -9985,11 +9987,11 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="C101" s="591" t="str">
+      <c r="C101" s="600" t="str">
         <f>+C80</f>
         <v>Asset Retirement Obligation ( Removal &amp; Restoration Obligation)</v>
       </c>
-      <c r="D101" s="590"/>
+      <c r="D101" s="601"/>
       <c r="E101" s="71"/>
       <c r="F101" s="66">
         <f>'Security Deposit'!D25</f>
@@ -10020,10 +10022,10 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="C102" s="589" t="s">
+      <c r="C102" s="594" t="s">
         <v>154</v>
       </c>
-      <c r="D102" s="590"/>
+      <c r="D102" s="601"/>
       <c r="E102" s="73"/>
       <c r="F102" s="66">
         <f>+F81/F21/F27</f>
@@ -10051,10 +10053,10 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="C103" s="592" t="s">
+      <c r="C103" s="596" t="s">
         <v>155</v>
       </c>
-      <c r="D103" s="593"/>
+      <c r="D103" s="597"/>
       <c r="E103" s="78"/>
       <c r="F103" s="54">
         <f>SUM(F97:F102)</f>
@@ -10091,7 +10093,7 @@
     </row>
     <row r="105" spans="1:26" ht="15.9" customHeight="1">
       <c r="A105" s="51"/>
-      <c r="B105" s="685" t="s">
+      <c r="B105" s="605" t="s">
         <v>156</v>
       </c>
       <c r="C105" s="606"/>
@@ -10116,10 +10118,10 @@
       <c r="B106" s="162">
         <v>1</v>
       </c>
-      <c r="C106" s="589" t="s">
+      <c r="C106" s="594" t="s">
         <v>69</v>
       </c>
-      <c r="D106" s="590"/>
+      <c r="D106" s="601"/>
       <c r="E106" s="71"/>
       <c r="F106" s="56">
         <f>+F94</f>
@@ -10147,10 +10149,10 @@
         <f>+B106+1</f>
         <v>2</v>
       </c>
-      <c r="C107" s="589" t="s">
+      <c r="C107" s="594" t="s">
         <v>155</v>
       </c>
-      <c r="D107" s="599"/>
+      <c r="D107" s="595"/>
       <c r="E107" s="71"/>
       <c r="F107" s="56">
         <f>+F103</f>
@@ -10178,10 +10180,10 @@
         <f>+B107+1</f>
         <v>3</v>
       </c>
-      <c r="C108" s="592" t="s">
+      <c r="C108" s="596" t="s">
         <v>157</v>
       </c>
-      <c r="D108" s="593"/>
+      <c r="D108" s="597"/>
       <c r="E108" s="78"/>
       <c r="F108" s="54">
         <f>SUM(F106:F107)</f>
@@ -10210,11 +10212,11 @@
     </row>
     <row r="109" spans="1:26" ht="15.9" customHeight="1">
       <c r="A109" s="51"/>
-      <c r="B109" s="594" t="s">
+      <c r="B109" s="598" t="s">
         <v>158</v>
       </c>
-      <c r="C109" s="595"/>
-      <c r="D109" s="595"/>
+      <c r="C109" s="599"/>
+      <c r="D109" s="599"/>
       <c r="E109" s="89"/>
       <c r="F109" s="161" t="s">
         <v>75</v>
@@ -10236,10 +10238,10 @@
       <c r="B110" s="249">
         <v>1</v>
       </c>
-      <c r="C110" s="589" t="s">
+      <c r="C110" s="594" t="s">
         <v>159</v>
       </c>
-      <c r="D110" s="599"/>
+      <c r="D110" s="595"/>
       <c r="E110" s="83"/>
       <c r="F110" s="376"/>
       <c r="G110" s="376"/>
@@ -10253,10 +10255,10 @@
         <f t="shared" ref="B111:B119" si="9">1+B110</f>
         <v>2</v>
       </c>
-      <c r="C111" s="589" t="s">
+      <c r="C111" s="594" t="s">
         <v>160</v>
       </c>
-      <c r="D111" s="599"/>
+      <c r="D111" s="595"/>
       <c r="E111" s="83"/>
       <c r="F111" s="376"/>
       <c r="G111" s="376"/>
@@ -10272,10 +10274,10 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="C112" s="589" t="s">
+      <c r="C112" s="594" t="s">
         <v>161</v>
       </c>
-      <c r="D112" s="599"/>
+      <c r="D112" s="595"/>
       <c r="E112" s="83"/>
       <c r="F112" s="388">
         <f>+F64*0</f>
@@ -10303,10 +10305,10 @@
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="C113" s="589" t="s">
+      <c r="C113" s="594" t="s">
         <v>162</v>
       </c>
-      <c r="D113" s="599"/>
+      <c r="D113" s="595"/>
       <c r="E113" s="83"/>
       <c r="F113" s="376"/>
       <c r="G113" s="376"/>
@@ -10320,10 +10322,10 @@
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="C114" s="589" t="s">
+      <c r="C114" s="594" t="s">
         <v>163</v>
       </c>
-      <c r="D114" s="599"/>
+      <c r="D114" s="595"/>
       <c r="E114" s="83"/>
       <c r="F114" s="376"/>
       <c r="G114" s="376"/>
@@ -10337,10 +10339,10 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="C115" s="589" t="s">
+      <c r="C115" s="594" t="s">
         <v>164</v>
       </c>
-      <c r="D115" s="599"/>
+      <c r="D115" s="595"/>
       <c r="E115" s="83"/>
       <c r="F115" s="376"/>
       <c r="G115" s="376"/>
@@ -10354,10 +10356,10 @@
         <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="C116" s="589" t="s">
+      <c r="C116" s="594" t="s">
         <v>165</v>
       </c>
-      <c r="D116" s="599"/>
+      <c r="D116" s="595"/>
       <c r="E116" s="83"/>
       <c r="F116" s="376"/>
       <c r="G116" s="376"/>
@@ -10371,10 +10373,10 @@
         <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="C117" s="589" t="s">
+      <c r="C117" s="594" t="s">
         <v>166</v>
       </c>
-      <c r="D117" s="590"/>
+      <c r="D117" s="601"/>
       <c r="E117" s="252"/>
       <c r="F117" s="360">
         <v>654</v>
@@ -10400,10 +10402,10 @@
         <f t="shared" si="9"/>
         <v>9</v>
       </c>
-      <c r="C118" s="589" t="s">
+      <c r="C118" s="594" t="s">
         <v>167</v>
       </c>
-      <c r="D118" s="599"/>
+      <c r="D118" s="595"/>
       <c r="E118" s="252"/>
       <c r="F118" s="90"/>
       <c r="G118" s="90">
@@ -10426,10 +10428,10 @@
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="C119" s="592" t="s">
+      <c r="C119" s="596" t="s">
         <v>168</v>
       </c>
-      <c r="D119" s="593"/>
+      <c r="D119" s="597"/>
       <c r="E119" s="253"/>
       <c r="F119" s="54">
         <f>SUM(F110:F118)</f>
@@ -10455,8 +10457,8 @@
     <row r="120" spans="1:26" ht="15.9" customHeight="1">
       <c r="A120" s="77"/>
       <c r="B120" s="162"/>
-      <c r="C120" s="597"/>
-      <c r="D120" s="598"/>
+      <c r="C120" s="590"/>
+      <c r="D120" s="607"/>
       <c r="E120" s="78"/>
       <c r="F120" s="54"/>
       <c r="G120" s="385"/>
@@ -10470,11 +10472,11 @@
     </row>
     <row r="121" spans="1:26" ht="15.9" customHeight="1">
       <c r="A121" s="77"/>
-      <c r="B121" s="594" t="s">
+      <c r="B121" s="598" t="s">
         <v>169</v>
       </c>
-      <c r="C121" s="595"/>
-      <c r="D121" s="595"/>
+      <c r="C121" s="599"/>
+      <c r="D121" s="599"/>
       <c r="E121" s="89"/>
       <c r="F121" s="161" t="s">
         <v>75</v>
@@ -10497,10 +10499,10 @@
       <c r="B122" s="251">
         <v>1</v>
       </c>
-      <c r="C122" s="589" t="s">
+      <c r="C122" s="594" t="s">
         <v>170</v>
       </c>
-      <c r="D122" s="599"/>
+      <c r="D122" s="595"/>
       <c r="E122" s="78"/>
       <c r="F122" s="54"/>
       <c r="G122" s="385"/>
@@ -10513,10 +10515,10 @@
       <c r="B123" s="162">
         <v>2</v>
       </c>
-      <c r="C123" s="592" t="s">
+      <c r="C123" s="596" t="s">
         <v>171</v>
       </c>
-      <c r="D123" s="593"/>
+      <c r="D123" s="597"/>
       <c r="E123" s="78"/>
       <c r="F123" s="54">
         <f>SUM(F122)</f>
@@ -10539,8 +10541,8 @@
     <row r="124" spans="1:26" ht="15.9" customHeight="1">
       <c r="A124" s="77"/>
       <c r="B124" s="162"/>
-      <c r="C124" s="597"/>
-      <c r="D124" s="598"/>
+      <c r="C124" s="590"/>
+      <c r="D124" s="607"/>
       <c r="E124" s="63"/>
       <c r="F124" s="54"/>
       <c r="G124" s="385"/>
@@ -10550,11 +10552,11 @@
     </row>
     <row r="125" spans="1:26" ht="15.9" customHeight="1">
       <c r="A125" s="77"/>
-      <c r="B125" s="594" t="s">
+      <c r="B125" s="598" t="s">
         <v>172</v>
       </c>
-      <c r="C125" s="595"/>
-      <c r="D125" s="595"/>
+      <c r="C125" s="599"/>
+      <c r="D125" s="599"/>
       <c r="E125" s="89"/>
       <c r="F125" s="161" t="s">
         <v>75</v>
@@ -10575,10 +10577,10 @@
       <c r="B126" s="249">
         <v>1</v>
       </c>
-      <c r="C126" s="589" t="s">
+      <c r="C126" s="594" t="s">
         <v>173</v>
       </c>
-      <c r="D126" s="599"/>
+      <c r="D126" s="595"/>
       <c r="E126" s="250"/>
       <c r="F126" s="385"/>
       <c r="G126" s="385"/>
@@ -10592,10 +10594,10 @@
         <f>1+B126</f>
         <v>2</v>
       </c>
-      <c r="C127" s="589" t="s">
+      <c r="C127" s="594" t="s">
         <v>174</v>
       </c>
-      <c r="D127" s="599"/>
+      <c r="D127" s="595"/>
       <c r="E127" s="250"/>
       <c r="F127" s="385"/>
       <c r="G127" s="385"/>
@@ -10609,10 +10611,10 @@
         <f>1+B127</f>
         <v>3</v>
       </c>
-      <c r="C128" s="589" t="s">
+      <c r="C128" s="594" t="s">
         <v>175</v>
       </c>
-      <c r="D128" s="599"/>
+      <c r="D128" s="595"/>
       <c r="E128" s="250"/>
       <c r="F128" s="385"/>
       <c r="G128" s="385"/>
@@ -10626,10 +10628,10 @@
         <f>1+B128</f>
         <v>4</v>
       </c>
-      <c r="C129" s="589" t="s">
+      <c r="C129" s="594" t="s">
         <v>176</v>
       </c>
-      <c r="D129" s="599"/>
+      <c r="D129" s="595"/>
       <c r="E129" s="250"/>
       <c r="F129" s="385"/>
       <c r="G129" s="385"/>
@@ -10643,10 +10645,10 @@
         <f>1+B129</f>
         <v>5</v>
       </c>
-      <c r="C130" s="589" t="s">
+      <c r="C130" s="594" t="s">
         <v>177</v>
       </c>
-      <c r="D130" s="599"/>
+      <c r="D130" s="595"/>
       <c r="E130" s="250"/>
       <c r="F130" s="385"/>
       <c r="G130" s="385"/>
@@ -10660,10 +10662,10 @@
         <f>1+B130</f>
         <v>6</v>
       </c>
-      <c r="C131" s="589" t="s">
+      <c r="C131" s="594" t="s">
         <v>178</v>
       </c>
-      <c r="D131" s="599"/>
+      <c r="D131" s="595"/>
       <c r="E131" s="250"/>
       <c r="F131" s="385"/>
       <c r="G131" s="385"/>
@@ -10676,10 +10678,10 @@
       <c r="B132" s="381">
         <v>7</v>
       </c>
-      <c r="C132" s="592" t="s">
+      <c r="C132" s="596" t="s">
         <v>179</v>
       </c>
-      <c r="D132" s="593"/>
+      <c r="D132" s="597"/>
       <c r="E132" s="250"/>
       <c r="F132" s="385">
         <f>SUM(F126:F131)</f>
@@ -10702,8 +10704,8 @@
     <row r="133" spans="1:20" ht="15.9" customHeight="1">
       <c r="A133" s="77"/>
       <c r="B133" s="162"/>
-      <c r="C133" s="631"/>
-      <c r="D133" s="598"/>
+      <c r="C133" s="591"/>
+      <c r="D133" s="607"/>
       <c r="E133" s="250"/>
       <c r="F133" s="385"/>
       <c r="G133" s="385"/>
@@ -10713,11 +10715,11 @@
     </row>
     <row r="134" spans="1:20" ht="15.9" customHeight="1">
       <c r="A134" s="51"/>
-      <c r="B134" s="594" t="s">
+      <c r="B134" s="598" t="s">
         <v>180</v>
       </c>
-      <c r="C134" s="595"/>
-      <c r="D134" s="595"/>
+      <c r="C134" s="599"/>
+      <c r="D134" s="599"/>
       <c r="E134" s="89"/>
       <c r="F134" s="161" t="s">
         <v>75</v>
@@ -10738,10 +10740,10 @@
       <c r="B135" s="162">
         <v>1</v>
       </c>
-      <c r="C135" s="592" t="s">
+      <c r="C135" s="596" t="s">
         <v>181</v>
       </c>
-      <c r="D135" s="593"/>
+      <c r="D135" s="597"/>
       <c r="E135" s="78"/>
       <c r="F135" s="54">
         <f>F119+F108+F123+F132</f>
@@ -10766,8 +10768,8 @@
     <row r="136" spans="1:20" ht="15.9" customHeight="1">
       <c r="A136" s="77"/>
       <c r="B136" s="162"/>
-      <c r="C136" s="597"/>
-      <c r="D136" s="598"/>
+      <c r="C136" s="590"/>
+      <c r="D136" s="607"/>
       <c r="E136" s="78"/>
       <c r="F136" s="54"/>
       <c r="G136" s="385"/>
@@ -10781,23 +10783,23 @@
       <c r="C137" s="380"/>
       <c r="D137" s="377"/>
       <c r="E137" s="167"/>
-      <c r="F137" s="597" t="s">
+      <c r="F137" s="590" t="s">
         <v>73</v>
       </c>
-      <c r="G137" s="631"/>
+      <c r="G137" s="591"/>
       <c r="H137" s="404"/>
-      <c r="I137" s="632" t="s">
+      <c r="I137" s="592" t="s">
         <v>67</v>
       </c>
-      <c r="J137" s="633"/>
+      <c r="J137" s="593"/>
     </row>
     <row r="138" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A138" s="51"/>
-      <c r="B138" s="594" t="s">
+      <c r="B138" s="598" t="s">
         <v>182</v>
       </c>
-      <c r="C138" s="595"/>
-      <c r="D138" s="596"/>
+      <c r="C138" s="599"/>
+      <c r="D138" s="614"/>
       <c r="E138" s="161"/>
       <c r="F138" s="161" t="s">
         <v>75</v>
@@ -10816,8 +10818,8 @@
     <row r="139" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A139" s="51"/>
       <c r="B139" s="91"/>
-      <c r="C139" s="600"/>
-      <c r="D139" s="601"/>
+      <c r="C139" s="615"/>
+      <c r="D139" s="616"/>
       <c r="E139" s="163"/>
       <c r="F139" s="54"/>
       <c r="G139" s="385"/>
@@ -10828,10 +10830,10 @@
     <row r="140" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A140" s="51"/>
       <c r="B140" s="91"/>
-      <c r="C140" s="589" t="s">
+      <c r="C140" s="594" t="s">
         <v>183</v>
       </c>
-      <c r="D140" s="590"/>
+      <c r="D140" s="601"/>
       <c r="E140" s="58"/>
       <c r="F140" s="243">
         <f>F21</f>
@@ -10854,10 +10856,10 @@
     <row r="141" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A141" s="51"/>
       <c r="B141" s="91"/>
-      <c r="C141" s="591" t="s">
+      <c r="C141" s="600" t="s">
         <v>184</v>
       </c>
-      <c r="D141" s="590"/>
+      <c r="D141" s="601"/>
       <c r="E141" s="59"/>
       <c r="F141" s="56">
         <f>F24</f>
@@ -10880,10 +10882,10 @@
     <row r="142" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A142" s="51"/>
       <c r="B142" s="91"/>
-      <c r="C142" s="591" t="s">
+      <c r="C142" s="600" t="s">
         <v>185</v>
       </c>
-      <c r="D142" s="590"/>
+      <c r="D142" s="601"/>
       <c r="E142" s="73"/>
       <c r="F142" s="56" t="e">
         <f>+#REF!</f>
@@ -10906,10 +10908,10 @@
     <row r="143" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A143" s="51"/>
       <c r="B143" s="91"/>
-      <c r="C143" s="589" t="s">
+      <c r="C143" s="594" t="s">
         <v>186</v>
       </c>
-      <c r="D143" s="590"/>
+      <c r="D143" s="601"/>
       <c r="E143" s="73"/>
       <c r="F143" s="56">
         <f>F108</f>
@@ -10932,10 +10934,10 @@
     <row r="144" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A144" s="51"/>
       <c r="B144" s="91"/>
-      <c r="C144" s="619" t="s">
+      <c r="C144" s="685" t="s">
         <v>187</v>
       </c>
-      <c r="D144" s="620"/>
+      <c r="D144" s="686"/>
       <c r="E144" s="92"/>
       <c r="F144" s="93">
         <f>F119</f>
@@ -10958,10 +10960,10 @@
     <row r="145" spans="1:10" ht="15.9" hidden="1" customHeight="1">
       <c r="A145" s="77"/>
       <c r="B145" s="162"/>
-      <c r="C145" s="592" t="s">
+      <c r="C145" s="596" t="s">
         <v>188</v>
       </c>
-      <c r="D145" s="593"/>
+      <c r="D145" s="597"/>
       <c r="E145" s="78"/>
       <c r="F145" s="245" t="e">
         <f>F135*#REF!</f>
@@ -10995,11 +10997,11 @@
     </row>
     <row r="147" spans="1:10" ht="15.9" customHeight="1">
       <c r="A147" s="77"/>
-      <c r="B147" s="594" t="s">
+      <c r="B147" s="598" t="s">
         <v>189</v>
       </c>
-      <c r="C147" s="595"/>
-      <c r="D147" s="596"/>
+      <c r="C147" s="599"/>
+      <c r="D147" s="614"/>
       <c r="E147" s="379"/>
       <c r="F147" s="379" t="s">
         <v>190</v>
@@ -11018,8 +11020,8 @@
     <row r="148" spans="1:10" ht="15.9" customHeight="1">
       <c r="A148" s="51"/>
       <c r="B148" s="99"/>
-      <c r="C148" s="600"/>
-      <c r="D148" s="601"/>
+      <c r="C148" s="615"/>
+      <c r="D148" s="616"/>
       <c r="E148" s="100"/>
       <c r="F148" s="101"/>
       <c r="G148" s="209"/>
@@ -11030,10 +11032,10 @@
     <row r="149" spans="1:10" ht="15.9" customHeight="1">
       <c r="A149" s="51"/>
       <c r="B149" s="99"/>
-      <c r="C149" s="591" t="s">
+      <c r="C149" s="600" t="s">
         <v>191</v>
       </c>
-      <c r="D149" s="590"/>
+      <c r="D149" s="601"/>
       <c r="E149" s="100"/>
       <c r="F149" s="101">
         <f>(+F63)*115%</f>
@@ -11056,10 +11058,10 @@
     <row r="150" spans="1:10" ht="15.9" customHeight="1">
       <c r="A150" s="51"/>
       <c r="B150" s="99"/>
-      <c r="C150" s="591" t="s">
+      <c r="C150" s="600" t="s">
         <v>192</v>
       </c>
-      <c r="D150" s="590"/>
+      <c r="D150" s="601"/>
       <c r="E150" s="100"/>
       <c r="F150" s="101">
         <v>0</v>
@@ -11078,10 +11080,10 @@
     <row r="151" spans="1:10" ht="15.9" customHeight="1">
       <c r="A151" s="51"/>
       <c r="B151" s="99"/>
-      <c r="C151" s="591" t="s">
+      <c r="C151" s="600" t="s">
         <v>193</v>
       </c>
-      <c r="D151" s="590"/>
+      <c r="D151" s="601"/>
       <c r="E151" s="100"/>
       <c r="F151" s="101">
         <f>(+F65)*115%</f>
@@ -11104,10 +11106,10 @@
     <row r="152" spans="1:10" ht="15.9" customHeight="1">
       <c r="A152" s="51"/>
       <c r="B152" s="99"/>
-      <c r="C152" s="591" t="s">
+      <c r="C152" s="600" t="s">
         <v>194</v>
       </c>
-      <c r="D152" s="590"/>
+      <c r="D152" s="601"/>
       <c r="E152" s="100"/>
       <c r="F152" s="101">
         <f>(+F66)*115%</f>
@@ -11130,10 +11132,10 @@
     <row r="153" spans="1:10" ht="15.9" customHeight="1">
       <c r="A153" s="51"/>
       <c r="B153" s="99"/>
-      <c r="C153" s="589" t="s">
+      <c r="C153" s="594" t="s">
         <v>195</v>
       </c>
-      <c r="D153" s="590"/>
+      <c r="D153" s="601"/>
       <c r="E153" s="103"/>
       <c r="F153" s="104">
         <f>SUM(F149:F152)</f>
@@ -11156,10 +11158,10 @@
     <row r="154" spans="1:10" ht="15.9" customHeight="1">
       <c r="A154" s="51"/>
       <c r="B154" s="99"/>
-      <c r="C154" s="589" t="s">
+      <c r="C154" s="594" t="s">
         <v>196</v>
       </c>
-      <c r="D154" s="590"/>
+      <c r="D154" s="601"/>
       <c r="E154" s="105"/>
       <c r="F154" s="101">
         <f>+F153*12</f>
@@ -11182,8 +11184,8 @@
     <row r="155" spans="1:10" ht="15.9" customHeight="1">
       <c r="A155" s="51"/>
       <c r="B155" s="99"/>
-      <c r="C155" s="600"/>
-      <c r="D155" s="601"/>
+      <c r="C155" s="615"/>
+      <c r="D155" s="616"/>
       <c r="E155" s="105"/>
       <c r="F155" s="101"/>
       <c r="G155" s="209"/>
@@ -11193,11 +11195,11 @@
     </row>
     <row r="156" spans="1:10" ht="15.9" customHeight="1">
       <c r="A156" s="51"/>
-      <c r="B156" s="594" t="s">
+      <c r="B156" s="598" t="s">
         <v>197</v>
       </c>
-      <c r="C156" s="595"/>
-      <c r="D156" s="596"/>
+      <c r="C156" s="599"/>
+      <c r="D156" s="614"/>
       <c r="E156" s="375"/>
       <c r="F156" s="379" t="s">
         <v>190</v>
@@ -11216,8 +11218,8 @@
     <row r="157" spans="1:10" ht="15.9" customHeight="1">
       <c r="A157" s="51"/>
       <c r="B157" s="99"/>
-      <c r="C157" s="600"/>
-      <c r="D157" s="601"/>
+      <c r="C157" s="615"/>
+      <c r="D157" s="616"/>
       <c r="E157" s="105"/>
       <c r="F157" s="101"/>
       <c r="G157" s="209"/>
@@ -11228,10 +11230,10 @@
     <row r="158" spans="1:10" ht="15.9" customHeight="1">
       <c r="A158" s="51"/>
       <c r="B158" s="99"/>
-      <c r="C158" s="617" t="s">
+      <c r="C158" s="683" t="s">
         <v>198</v>
       </c>
-      <c r="D158" s="618"/>
+      <c r="D158" s="684"/>
       <c r="E158" s="105"/>
       <c r="F158" s="101">
         <f t="shared" ref="F158:G160" si="10">+F77</f>
@@ -11254,10 +11256,10 @@
     <row r="159" spans="1:10" ht="15.9" customHeight="1">
       <c r="A159" s="51"/>
       <c r="B159" s="99"/>
-      <c r="C159" s="589" t="s">
+      <c r="C159" s="594" t="s">
         <v>199</v>
       </c>
-      <c r="D159" s="599"/>
+      <c r="D159" s="595"/>
       <c r="E159" s="105"/>
       <c r="F159" s="101">
         <f t="shared" si="10"/>
@@ -11280,10 +11282,10 @@
     <row r="160" spans="1:10" ht="15.9" customHeight="1">
       <c r="A160" s="51"/>
       <c r="B160" s="99"/>
-      <c r="C160" s="589" t="s">
+      <c r="C160" s="594" t="s">
         <v>200</v>
       </c>
-      <c r="D160" s="599"/>
+      <c r="D160" s="595"/>
       <c r="E160" s="105"/>
       <c r="F160" s="101">
         <f t="shared" si="10"/>
@@ -11306,10 +11308,10 @@
     <row r="161" spans="1:22" ht="15.9" customHeight="1">
       <c r="A161" s="51"/>
       <c r="B161" s="99"/>
-      <c r="C161" s="592" t="s">
+      <c r="C161" s="596" t="s">
         <v>29</v>
       </c>
-      <c r="D161" s="593"/>
+      <c r="D161" s="597"/>
       <c r="E161" s="105"/>
       <c r="F161" s="237">
         <f>SUM(F158:F160)</f>
@@ -11332,8 +11334,8 @@
     <row r="162" spans="1:22" ht="15.9" customHeight="1">
       <c r="A162" s="51"/>
       <c r="B162" s="99"/>
-      <c r="C162" s="600"/>
-      <c r="D162" s="601"/>
+      <c r="C162" s="615"/>
+      <c r="D162" s="616"/>
       <c r="E162" s="105"/>
       <c r="F162" s="101"/>
       <c r="G162" s="209"/>
@@ -11343,12 +11345,12 @@
     </row>
     <row r="163" spans="1:22" ht="15.9" customHeight="1">
       <c r="A163" s="106"/>
-      <c r="B163" s="611" t="s">
+      <c r="B163" s="602" t="s">
         <v>201</v>
       </c>
-      <c r="C163" s="612"/>
-      <c r="D163" s="613"/>
-      <c r="E163" s="684"/>
+      <c r="C163" s="603"/>
+      <c r="D163" s="604"/>
+      <c r="E163" s="612"/>
       <c r="F163" s="161" t="s">
         <v>75</v>
       </c>
@@ -11365,10 +11367,10 @@
     </row>
     <row r="164" spans="1:22" ht="15.9" customHeight="1">
       <c r="A164" s="106"/>
-      <c r="B164" s="614"/>
-      <c r="C164" s="615"/>
-      <c r="D164" s="616"/>
-      <c r="E164" s="604"/>
+      <c r="B164" s="680"/>
+      <c r="C164" s="681"/>
+      <c r="D164" s="682"/>
+      <c r="E164" s="613"/>
       <c r="F164" s="161" t="s">
         <v>73</v>
       </c>
@@ -11386,8 +11388,8 @@
     <row r="165" spans="1:22" ht="15.9" customHeight="1">
       <c r="A165" s="107"/>
       <c r="B165" s="99"/>
-      <c r="C165" s="600"/>
-      <c r="D165" s="601"/>
+      <c r="C165" s="615"/>
+      <c r="D165" s="616"/>
       <c r="E165" s="59"/>
       <c r="F165" s="56"/>
       <c r="G165" s="388"/>
@@ -11398,11 +11400,11 @@
     <row r="166" spans="1:22" ht="15.9" customHeight="1">
       <c r="A166" s="107"/>
       <c r="B166" s="99"/>
-      <c r="C166" s="602" t="str">
+      <c r="C166" s="678" t="str">
         <f>+C106</f>
         <v>Net Rent I</v>
       </c>
-      <c r="D166" s="603"/>
+      <c r="D166" s="679"/>
       <c r="E166" s="59"/>
       <c r="F166" s="56">
         <f>+F106</f>
@@ -11426,11 +11428,11 @@
     <row r="167" spans="1:22" ht="15.9" customHeight="1">
       <c r="A167" s="107"/>
       <c r="B167" s="99"/>
-      <c r="C167" s="602" t="str">
+      <c r="C167" s="678" t="str">
         <f>+C107</f>
         <v>Net Rent II</v>
       </c>
-      <c r="D167" s="603"/>
+      <c r="D167" s="679"/>
       <c r="E167" s="59"/>
       <c r="F167" s="56">
         <f>+F107</f>
@@ -11454,10 +11456,10 @@
     <row r="168" spans="1:22" ht="15.9" customHeight="1">
       <c r="A168" s="107"/>
       <c r="B168" s="147"/>
-      <c r="C168" s="607" t="s">
+      <c r="C168" s="674" t="s">
         <v>202</v>
       </c>
-      <c r="D168" s="608"/>
+      <c r="D168" s="675"/>
       <c r="E168" s="148"/>
       <c r="F168" s="149">
         <f>SUM(F166:F167)</f>
@@ -11482,8 +11484,8 @@
     <row r="169" spans="1:22" ht="15.9" customHeight="1">
       <c r="A169" s="107"/>
       <c r="B169" s="162"/>
-      <c r="C169" s="609"/>
-      <c r="D169" s="610"/>
+      <c r="C169" s="676"/>
+      <c r="D169" s="677"/>
       <c r="E169" s="75"/>
       <c r="F169" s="54"/>
       <c r="G169" s="385"/>
@@ -11496,11 +11498,11 @@
     <row r="170" spans="1:22" ht="15.9" customHeight="1">
       <c r="A170" s="107"/>
       <c r="B170" s="99"/>
-      <c r="C170" s="602" t="str">
+      <c r="C170" s="678" t="str">
         <f>+C119</f>
         <v xml:space="preserve">OpEx I </v>
       </c>
-      <c r="D170" s="603"/>
+      <c r="D170" s="679"/>
       <c r="E170" s="59"/>
       <c r="F170" s="56">
         <f>+F119</f>
@@ -11524,11 +11526,11 @@
     <row r="171" spans="1:22" ht="15.9" customHeight="1">
       <c r="A171" s="107"/>
       <c r="B171" s="99"/>
-      <c r="C171" s="602" t="str">
+      <c r="C171" s="678" t="str">
         <f>+C123</f>
         <v xml:space="preserve">OpEx II </v>
       </c>
-      <c r="D171" s="603"/>
+      <c r="D171" s="679"/>
       <c r="E171" s="59"/>
       <c r="F171" s="56">
         <f>+F123</f>
@@ -11551,10 +11553,10 @@
     <row r="172" spans="1:22" ht="15.9" customHeight="1">
       <c r="A172" s="107"/>
       <c r="B172" s="150"/>
-      <c r="C172" s="607" t="s">
+      <c r="C172" s="674" t="s">
         <v>203</v>
       </c>
-      <c r="D172" s="608"/>
+      <c r="D172" s="675"/>
       <c r="E172" s="151"/>
       <c r="F172" s="152">
         <f>SUM(F170:F171)</f>
@@ -11589,11 +11591,11 @@
     <row r="174" spans="1:22" ht="15.9" customHeight="1">
       <c r="A174" s="107"/>
       <c r="B174" s="99"/>
-      <c r="C174" s="602" t="str">
+      <c r="C174" s="678" t="str">
         <f>+C132</f>
         <v xml:space="preserve">Services </v>
       </c>
-      <c r="D174" s="603"/>
+      <c r="D174" s="679"/>
       <c r="E174" s="59"/>
       <c r="F174" s="56">
         <f>+F132</f>
@@ -11616,10 +11618,10 @@
     <row r="175" spans="1:22" ht="15.9" customHeight="1">
       <c r="A175" s="107"/>
       <c r="B175" s="150"/>
-      <c r="C175" s="607" t="s">
+      <c r="C175" s="674" t="s">
         <v>204</v>
       </c>
-      <c r="D175" s="608"/>
+      <c r="D175" s="675"/>
       <c r="E175" s="151"/>
       <c r="F175" s="152">
         <f>SUM(F174)</f>
@@ -11642,8 +11644,8 @@
     <row r="176" spans="1:22" ht="15.9" customHeight="1">
       <c r="A176" s="107"/>
       <c r="B176" s="99"/>
-      <c r="C176" s="600"/>
-      <c r="D176" s="601"/>
+      <c r="C176" s="615"/>
+      <c r="D176" s="616"/>
       <c r="E176" s="59"/>
       <c r="F176" s="56"/>
       <c r="G176" s="388"/>
@@ -11654,10 +11656,10 @@
     <row r="177" spans="1:19" ht="15.9" customHeight="1">
       <c r="A177" s="107"/>
       <c r="B177" s="150"/>
-      <c r="C177" s="607" t="s">
+      <c r="C177" s="674" t="s">
         <v>205</v>
       </c>
-      <c r="D177" s="608"/>
+      <c r="D177" s="675"/>
       <c r="E177" s="154"/>
       <c r="F177" s="149">
         <f>+F168+F172+F175</f>
@@ -11692,11 +11694,11 @@
     </row>
     <row r="179" spans="1:19" ht="15.9" customHeight="1">
       <c r="A179" s="107"/>
-      <c r="B179" s="594" t="s">
+      <c r="B179" s="598" t="s">
         <v>206</v>
       </c>
-      <c r="C179" s="595"/>
-      <c r="D179" s="596"/>
+      <c r="C179" s="599"/>
+      <c r="D179" s="614"/>
       <c r="E179" s="379"/>
       <c r="F179" s="379" t="s">
         <v>190</v>
@@ -11715,8 +11717,8 @@
     <row r="180" spans="1:19" ht="15.9" customHeight="1">
       <c r="A180" s="107"/>
       <c r="B180" s="99"/>
-      <c r="C180" s="600"/>
-      <c r="D180" s="601"/>
+      <c r="C180" s="615"/>
+      <c r="D180" s="616"/>
       <c r="E180" s="59"/>
       <c r="F180" s="56"/>
       <c r="G180" s="388"/>
@@ -11727,10 +11729,10 @@
     <row r="181" spans="1:19" ht="15.9" customHeight="1">
       <c r="A181" s="107"/>
       <c r="B181" s="99"/>
-      <c r="C181" s="591" t="s">
+      <c r="C181" s="600" t="s">
         <v>207</v>
       </c>
-      <c r="D181" s="590"/>
+      <c r="D181" s="601"/>
       <c r="E181" s="100"/>
       <c r="F181" s="101"/>
       <c r="G181" s="209">
@@ -11747,10 +11749,10 @@
     <row r="182" spans="1:19" ht="15.9" customHeight="1">
       <c r="A182" s="107"/>
       <c r="B182" s="99"/>
-      <c r="C182" s="589" t="s">
+      <c r="C182" s="594" t="s">
         <v>208</v>
       </c>
-      <c r="D182" s="590"/>
+      <c r="D182" s="601"/>
       <c r="E182" s="100"/>
       <c r="F182" s="101"/>
       <c r="G182" s="209">
@@ -11767,10 +11769,10 @@
     <row r="183" spans="1:19" ht="15.9" customHeight="1">
       <c r="A183" s="107"/>
       <c r="B183" s="99"/>
-      <c r="C183" s="589" t="s">
+      <c r="C183" s="594" t="s">
         <v>209</v>
       </c>
-      <c r="D183" s="599"/>
+      <c r="D183" s="595"/>
       <c r="E183" s="100"/>
       <c r="F183" s="101"/>
       <c r="G183" s="209">
@@ -11784,10 +11786,10 @@
     <row r="184" spans="1:19" ht="15.9" customHeight="1">
       <c r="A184" s="107"/>
       <c r="B184" s="99"/>
-      <c r="C184" s="589" t="s">
+      <c r="C184" s="594" t="s">
         <v>210</v>
       </c>
-      <c r="D184" s="590"/>
+      <c r="D184" s="601"/>
       <c r="E184" s="100"/>
       <c r="F184" s="101"/>
       <c r="G184" s="209">
@@ -11804,10 +11806,10 @@
     <row r="185" spans="1:19" ht="15.9" customHeight="1">
       <c r="A185" s="107"/>
       <c r="B185" s="99"/>
-      <c r="C185" s="589" t="s">
+      <c r="C185" s="594" t="s">
         <v>211</v>
       </c>
-      <c r="D185" s="590"/>
+      <c r="D185" s="601"/>
       <c r="E185" s="100"/>
       <c r="F185" s="101"/>
       <c r="G185" s="209">
@@ -11835,25 +11837,25 @@
     </row>
     <row r="187" spans="1:19" ht="15.9" customHeight="1" thickBot="1">
       <c r="A187" s="107"/>
-      <c r="B187" s="624" t="s">
+      <c r="B187" s="671" t="s">
         <v>212</v>
       </c>
-      <c r="C187" s="625"/>
-      <c r="D187" s="625"/>
-      <c r="E187" s="625"/>
-      <c r="F187" s="625"/>
-      <c r="G187" s="625"/>
-      <c r="H187" s="625"/>
-      <c r="I187" s="625"/>
-      <c r="J187" s="626"/>
+      <c r="C187" s="672"/>
+      <c r="D187" s="672"/>
+      <c r="E187" s="672"/>
+      <c r="F187" s="672"/>
+      <c r="G187" s="672"/>
+      <c r="H187" s="672"/>
+      <c r="I187" s="672"/>
+      <c r="J187" s="673"/>
     </row>
     <row r="188" spans="1:19" ht="15.9" customHeight="1">
       <c r="A188" s="51"/>
       <c r="B188" s="164"/>
-      <c r="C188" s="604" t="s">
+      <c r="C188" s="613" t="s">
         <v>213</v>
       </c>
-      <c r="D188" s="604"/>
+      <c r="D188" s="613"/>
       <c r="E188" s="378"/>
       <c r="F188" s="378" t="s">
         <v>190</v>
@@ -11861,7 +11863,7 @@
       <c r="G188" s="168" t="s">
         <v>190</v>
       </c>
-      <c r="H188" s="621"/>
+      <c r="H188" s="668"/>
       <c r="I188" s="229" t="s">
         <v>67</v>
       </c>
@@ -11872,17 +11874,17 @@
     <row r="189" spans="1:19" ht="15.9" customHeight="1">
       <c r="A189" s="51"/>
       <c r="B189" s="162"/>
-      <c r="C189" s="591" t="s">
+      <c r="C189" s="600" t="s">
         <v>214</v>
       </c>
-      <c r="D189" s="590"/>
+      <c r="D189" s="601"/>
       <c r="E189" s="163"/>
       <c r="F189" s="163"/>
       <c r="G189" s="102">
         <f>+G20</f>
         <v>0</v>
       </c>
-      <c r="H189" s="622"/>
+      <c r="H189" s="669"/>
       <c r="I189" s="162"/>
       <c r="J189" s="102">
         <f>+G189/J5</f>
@@ -11892,17 +11894,17 @@
     <row r="190" spans="1:19" ht="15.9" customHeight="1">
       <c r="A190" s="51"/>
       <c r="B190" s="162"/>
-      <c r="C190" s="591" t="s">
+      <c r="C190" s="600" t="s">
         <v>215</v>
       </c>
-      <c r="D190" s="590"/>
+      <c r="D190" s="601"/>
       <c r="E190" s="163"/>
       <c r="F190" s="163"/>
       <c r="G190" s="102">
         <f>+G189*G23</f>
         <v>0</v>
       </c>
-      <c r="H190" s="622"/>
+      <c r="H190" s="669"/>
       <c r="I190" s="162"/>
       <c r="J190" s="102">
         <f>+J189*J23</f>
@@ -11912,17 +11914,17 @@
     <row r="191" spans="1:19" ht="15.9" customHeight="1">
       <c r="A191" s="51"/>
       <c r="B191" s="162"/>
-      <c r="C191" s="605" t="s">
+      <c r="C191" s="638" t="s">
         <v>216</v>
       </c>
-      <c r="D191" s="605"/>
+      <c r="D191" s="638"/>
       <c r="E191" s="163"/>
       <c r="F191" s="163"/>
       <c r="G191" s="102">
         <f>+G190*25%</f>
         <v>0</v>
       </c>
-      <c r="H191" s="622"/>
+      <c r="H191" s="669"/>
       <c r="I191" s="162"/>
       <c r="J191" s="102">
         <f>+J190*25%</f>
@@ -11932,17 +11934,17 @@
     <row r="192" spans="1:19" ht="15.9" customHeight="1">
       <c r="A192" s="51"/>
       <c r="B192" s="162"/>
-      <c r="C192" s="589" t="s">
+      <c r="C192" s="594" t="s">
         <v>217</v>
       </c>
-      <c r="D192" s="590"/>
+      <c r="D192" s="601"/>
       <c r="E192" s="163"/>
       <c r="F192" s="163"/>
       <c r="G192" s="102">
         <f>+G191*1%</f>
         <v>0</v>
       </c>
-      <c r="H192" s="622"/>
+      <c r="H192" s="669"/>
       <c r="I192" s="162"/>
       <c r="J192" s="102">
         <f>G192/J5</f>
@@ -11952,17 +11954,17 @@
     <row r="193" spans="1:20" ht="15.9" customHeight="1">
       <c r="A193" s="51"/>
       <c r="B193" s="162"/>
-      <c r="C193" s="589" t="s">
+      <c r="C193" s="594" t="s">
         <v>218</v>
       </c>
-      <c r="D193" s="590"/>
+      <c r="D193" s="601"/>
       <c r="E193" s="163"/>
       <c r="F193" s="163"/>
       <c r="G193" s="102">
         <f>G192*0.5</f>
         <v>0</v>
       </c>
-      <c r="H193" s="622"/>
+      <c r="H193" s="669"/>
       <c r="I193" s="162"/>
       <c r="J193" s="102">
         <f>G193/J5</f>
@@ -11972,17 +11974,17 @@
     <row r="194" spans="1:20" ht="15.9" customHeight="1" thickBot="1">
       <c r="A194" s="51"/>
       <c r="B194" s="162"/>
-      <c r="C194" s="605" t="s">
+      <c r="C194" s="638" t="s">
         <v>219</v>
       </c>
-      <c r="D194" s="605"/>
+      <c r="D194" s="638"/>
       <c r="E194" s="163"/>
       <c r="F194" s="163"/>
       <c r="G194" s="110">
         <f>G82</f>
         <v>565315.30184775486</v>
       </c>
-      <c r="H194" s="622"/>
+      <c r="H194" s="669"/>
       <c r="I194" s="162"/>
       <c r="J194" s="110">
         <f>+J192+J193</f>
@@ -12001,7 +12003,7 @@
       <c r="G195" s="53" t="s">
         <v>190</v>
       </c>
-      <c r="H195" s="622"/>
+      <c r="H195" s="669"/>
       <c r="I195" s="229" t="s">
         <v>67</v>
       </c>
@@ -12012,17 +12014,17 @@
     <row r="196" spans="1:20" ht="15.9" customHeight="1">
       <c r="A196" s="74"/>
       <c r="B196" s="99"/>
-      <c r="C196" s="591" t="s">
+      <c r="C196" s="600" t="s">
         <v>220</v>
       </c>
-      <c r="D196" s="590"/>
+      <c r="D196" s="601"/>
       <c r="E196" s="58"/>
       <c r="F196" s="50"/>
       <c r="G196" s="102">
         <f>+G54</f>
         <v>72</v>
       </c>
-      <c r="H196" s="622"/>
+      <c r="H196" s="669"/>
       <c r="I196" s="91"/>
       <c r="J196" s="102">
         <f>+J54</f>
@@ -12032,17 +12034,17 @@
     <row r="197" spans="1:20" ht="15.9" customHeight="1">
       <c r="A197" s="74"/>
       <c r="B197" s="99"/>
-      <c r="C197" s="591" t="s">
+      <c r="C197" s="600" t="s">
         <v>221</v>
       </c>
-      <c r="D197" s="590"/>
+      <c r="D197" s="601"/>
       <c r="E197" s="58"/>
       <c r="F197" s="50"/>
       <c r="G197" s="102">
         <f>F140</f>
         <v>9515</v>
       </c>
-      <c r="H197" s="622"/>
+      <c r="H197" s="669"/>
       <c r="I197" s="91"/>
       <c r="J197" s="102">
         <f>I140</f>
@@ -12052,17 +12054,17 @@
     <row r="198" spans="1:20" ht="15.9" customHeight="1">
       <c r="A198" s="120"/>
       <c r="B198" s="99"/>
-      <c r="C198" s="591" t="s">
+      <c r="C198" s="600" t="s">
         <v>222</v>
       </c>
-      <c r="D198" s="590"/>
+      <c r="D198" s="601"/>
       <c r="E198" s="58"/>
       <c r="F198" s="50"/>
       <c r="G198" s="111">
         <f>+F60</f>
         <v>129</v>
       </c>
-      <c r="H198" s="622"/>
+      <c r="H198" s="669"/>
       <c r="I198" s="91"/>
       <c r="J198" s="111">
         <f>+I60</f>
@@ -12072,17 +12074,17 @@
     <row r="199" spans="1:20" ht="15.9" customHeight="1">
       <c r="A199" s="74"/>
       <c r="B199" s="99"/>
-      <c r="C199" s="591" t="s">
+      <c r="C199" s="600" t="s">
         <v>222</v>
       </c>
-      <c r="D199" s="590"/>
+      <c r="D199" s="601"/>
       <c r="E199" s="58"/>
       <c r="F199" s="50"/>
       <c r="G199" s="102">
         <f>(G197*G198*G196)</f>
         <v>88375320</v>
       </c>
-      <c r="H199" s="622"/>
+      <c r="H199" s="669"/>
       <c r="I199" s="91"/>
       <c r="J199" s="102">
         <f>+G199/$J$5</f>
@@ -12092,17 +12094,17 @@
     <row r="200" spans="1:20" ht="15.9" customHeight="1">
       <c r="A200" s="74"/>
       <c r="B200" s="99"/>
-      <c r="C200" s="591" t="s">
+      <c r="C200" s="600" t="s">
         <v>223</v>
       </c>
-      <c r="D200" s="590"/>
+      <c r="D200" s="601"/>
       <c r="E200" s="58"/>
       <c r="F200" s="50"/>
       <c r="G200" s="102">
         <f>G199/G196*12</f>
         <v>14729220</v>
       </c>
-      <c r="H200" s="622"/>
+      <c r="H200" s="669"/>
       <c r="I200" s="91"/>
       <c r="J200" s="102">
         <f>+G200/$J$5</f>
@@ -12112,17 +12114,17 @@
     <row r="201" spans="1:20" ht="15.9" customHeight="1">
       <c r="A201" s="74"/>
       <c r="B201" s="99"/>
-      <c r="C201" s="591" t="s">
+      <c r="C201" s="600" t="s">
         <v>224</v>
       </c>
-      <c r="D201" s="590"/>
+      <c r="D201" s="601"/>
       <c r="E201" s="58"/>
       <c r="F201" s="50"/>
       <c r="G201" s="102">
         <f>(+G220*115%)/5</f>
         <v>3026339.9999999995</v>
       </c>
-      <c r="H201" s="622"/>
+      <c r="H201" s="669"/>
       <c r="I201" s="91"/>
       <c r="J201" s="102">
         <f>+G201/$J$5</f>
@@ -12132,17 +12134,17 @@
     <row r="202" spans="1:20" ht="15.9" customHeight="1">
       <c r="A202" s="74"/>
       <c r="B202" s="99"/>
-      <c r="C202" s="591" t="s">
+      <c r="C202" s="600" t="s">
         <v>225</v>
       </c>
-      <c r="D202" s="590"/>
+      <c r="D202" s="601"/>
       <c r="E202" s="58"/>
       <c r="F202" s="50"/>
       <c r="G202" s="102">
         <f>(+I220*115%)/5</f>
         <v>2765157.6185172233</v>
       </c>
-      <c r="H202" s="622"/>
+      <c r="H202" s="669"/>
       <c r="I202" s="91"/>
       <c r="J202" s="102">
         <f>+G202/$J$5</f>
@@ -12152,17 +12154,17 @@
     <row r="203" spans="1:20" ht="15.9" customHeight="1">
       <c r="A203" s="74"/>
       <c r="B203" s="99"/>
-      <c r="C203" s="591" t="s">
+      <c r="C203" s="600" t="s">
         <v>36</v>
       </c>
-      <c r="D203" s="590"/>
+      <c r="D203" s="601"/>
       <c r="E203" s="58"/>
       <c r="F203" s="50"/>
       <c r="G203" s="102">
         <f>+G67</f>
         <v>11418000</v>
       </c>
-      <c r="H203" s="622"/>
+      <c r="H203" s="669"/>
       <c r="I203" s="91"/>
       <c r="J203" s="102">
         <f>+G203/$J$5</f>
@@ -12172,17 +12174,17 @@
     <row r="204" spans="1:20" ht="15.9" customHeight="1">
       <c r="A204" s="74"/>
       <c r="B204" s="99"/>
-      <c r="C204" s="589" t="s">
+      <c r="C204" s="594" t="s">
         <v>226</v>
       </c>
-      <c r="D204" s="590"/>
+      <c r="D204" s="601"/>
       <c r="E204" s="58"/>
       <c r="F204" s="50"/>
       <c r="G204" s="102">
         <f>(G200+G201+G202+G203)*1.18</f>
         <v>37687686.789850324</v>
       </c>
-      <c r="H204" s="622"/>
+      <c r="H204" s="669"/>
       <c r="I204" s="91"/>
       <c r="J204" s="102">
         <f>+J200+J201+J202+J203</f>
@@ -12192,17 +12194,17 @@
     <row r="205" spans="1:20" ht="15.9" customHeight="1">
       <c r="A205" s="74"/>
       <c r="B205" s="99"/>
-      <c r="C205" s="589" t="s">
+      <c r="C205" s="594" t="s">
         <v>227</v>
       </c>
-      <c r="D205" s="590"/>
+      <c r="D205" s="601"/>
       <c r="E205" s="58"/>
       <c r="F205" s="50"/>
       <c r="G205" s="102">
         <f>G204*1%</f>
         <v>376876.86789850326</v>
       </c>
-      <c r="H205" s="622"/>
+      <c r="H205" s="669"/>
       <c r="I205" s="91"/>
       <c r="J205" s="102">
         <f>J204*1%</f>
@@ -12212,17 +12214,17 @@
     <row r="206" spans="1:20" ht="15.9" customHeight="1">
       <c r="A206" s="74"/>
       <c r="B206" s="99"/>
-      <c r="C206" s="591" t="s">
+      <c r="C206" s="600" t="s">
         <v>228</v>
       </c>
-      <c r="D206" s="590"/>
+      <c r="D206" s="601"/>
       <c r="E206" s="58"/>
       <c r="F206" s="50"/>
       <c r="G206" s="102">
         <f>G204*0.5%</f>
         <v>188438.43394925163</v>
       </c>
-      <c r="H206" s="622"/>
+      <c r="H206" s="669"/>
       <c r="I206" s="91"/>
       <c r="J206" s="102">
         <f>J204*0.5%</f>
@@ -12232,17 +12234,17 @@
     <row r="207" spans="1:20" ht="15.9" customHeight="1">
       <c r="A207" s="74"/>
       <c r="B207" s="99"/>
-      <c r="C207" s="592" t="s">
+      <c r="C207" s="596" t="s">
         <v>219</v>
       </c>
-      <c r="D207" s="593"/>
+      <c r="D207" s="597"/>
       <c r="E207" s="58"/>
       <c r="F207" s="50"/>
       <c r="G207" s="102">
         <f>G205+G206</f>
         <v>565315.30184775486</v>
       </c>
-      <c r="H207" s="622"/>
+      <c r="H207" s="669"/>
       <c r="I207" s="91"/>
       <c r="J207" s="102">
         <v>0</v>
@@ -12257,7 +12259,7 @@
       <c r="E208" s="80"/>
       <c r="F208" s="51"/>
       <c r="G208" s="337"/>
-      <c r="H208" s="622"/>
+      <c r="H208" s="669"/>
       <c r="I208" s="94"/>
       <c r="J208" s="81"/>
     </row>
@@ -12279,7 +12281,7 @@
       <c r="G209" s="161" t="s">
         <v>233</v>
       </c>
-      <c r="H209" s="622"/>
+      <c r="H209" s="669"/>
       <c r="I209" s="379" t="s">
         <v>234</v>
       </c>
@@ -12305,7 +12307,7 @@
         <f>'Lease Rent'!P39</f>
         <v>1360000</v>
       </c>
-      <c r="H210" s="622"/>
+      <c r="H210" s="669"/>
       <c r="I210" s="101">
         <f>'Lease Rent'!O39</f>
         <v>1178337.5999999999</v>
@@ -12335,7 +12337,7 @@
         <f>'Lease Rent'!P51</f>
         <v>2040000</v>
       </c>
-      <c r="H211" s="622"/>
+      <c r="H211" s="669"/>
       <c r="I211" s="101">
         <f>'Lease Rent'!O51</f>
         <v>1826423.2800000005</v>
@@ -12364,7 +12366,7 @@
         <f>'Lease Rent'!P63</f>
         <v>2040000</v>
       </c>
-      <c r="H212" s="622"/>
+      <c r="H212" s="669"/>
       <c r="I212" s="101">
         <f>'Lease Rent'!O63</f>
         <v>1917744.4440000001</v>
@@ -12393,7 +12395,7 @@
         <f>'Lease Rent'!P75</f>
         <v>2244000</v>
       </c>
-      <c r="H213" s="622"/>
+      <c r="H213" s="669"/>
       <c r="I213" s="101">
         <f>'Lease Rent'!O75</f>
         <v>2013631.6662000006</v>
@@ -12422,7 +12424,7 @@
         <f>'Lease Rent'!P87</f>
         <v>2345999.9999999995</v>
       </c>
-      <c r="H214" s="622"/>
+      <c r="H214" s="669"/>
       <c r="I214" s="101">
         <f>'Lease Rent'!O87</f>
         <v>2114313.2495100005</v>
@@ -12451,7 +12453,7 @@
         <f>'Lease Rent'!P99</f>
         <v>2345999.9999999995</v>
       </c>
-      <c r="H215" s="622"/>
+      <c r="H215" s="669"/>
       <c r="I215" s="101">
         <f>'Lease Rent'!O99</f>
         <v>2220028.9119855007</v>
@@ -12479,7 +12481,7 @@
         <f>'Lease Rent'!P103</f>
         <v>781999.99999999988</v>
       </c>
-      <c r="H216" s="622"/>
+      <c r="H216" s="669"/>
       <c r="I216" s="101">
         <f>'Lease Rent'!O103</f>
         <v>751945.27664025011</v>
@@ -12502,7 +12504,7 @@
         <f>'Lease Rent'!R10</f>
         <v>0</v>
       </c>
-      <c r="H217" s="622"/>
+      <c r="H217" s="669"/>
       <c r="I217" s="301"/>
       <c r="J217" s="111"/>
     </row>
@@ -12519,7 +12521,7 @@
         <v>0</v>
       </c>
       <c r="G218" s="118"/>
-      <c r="H218" s="622"/>
+      <c r="H218" s="669"/>
       <c r="I218" s="101"/>
       <c r="J218" s="111"/>
     </row>
@@ -12533,7 +12535,7 @@
       <c r="E219" s="117"/>
       <c r="F219" s="232"/>
       <c r="G219" s="118"/>
-      <c r="H219" s="622"/>
+      <c r="H219" s="669"/>
       <c r="I219" s="101"/>
       <c r="J219" s="111"/>
     </row>
@@ -12556,7 +12558,7 @@
         <f>SUM(G210:G219)</f>
         <v>13158000</v>
       </c>
-      <c r="H220" s="623"/>
+      <c r="H220" s="670"/>
       <c r="I220" s="283">
         <f>SUM(I210:I219)</f>
         <v>12022424.428335754</v>
@@ -12626,35 +12628,190 @@
     </row>
   </sheetData>
   <mergeCells count="237">
-    <mergeCell ref="F137:G137"/>
-    <mergeCell ref="I137:J137"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C131:D131"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="B134:D134"/>
-    <mergeCell ref="C106:D106"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="B105:D105"/>
-    <mergeCell ref="C124:D124"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="C204:D204"/>
+    <mergeCell ref="C203:D203"/>
+    <mergeCell ref="C161:D161"/>
+    <mergeCell ref="B138:D138"/>
+    <mergeCell ref="C141:D141"/>
+    <mergeCell ref="C120:D120"/>
+    <mergeCell ref="C192:D192"/>
+    <mergeCell ref="C193:D193"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="C189:D189"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C160:D160"/>
+    <mergeCell ref="C190:D190"/>
+    <mergeCell ref="B179:D179"/>
+    <mergeCell ref="C162:D162"/>
+    <mergeCell ref="C165:D165"/>
+    <mergeCell ref="C205:D205"/>
+    <mergeCell ref="C206:D206"/>
+    <mergeCell ref="C207:D207"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C174:D174"/>
+    <mergeCell ref="C197:D197"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="C199:D199"/>
+    <mergeCell ref="C200:D200"/>
+    <mergeCell ref="C201:D201"/>
+    <mergeCell ref="C202:D202"/>
+    <mergeCell ref="C188:D188"/>
+    <mergeCell ref="C191:D191"/>
+    <mergeCell ref="C194:D194"/>
+    <mergeCell ref="C195:D195"/>
+    <mergeCell ref="C196:D196"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C181:D181"/>
+    <mergeCell ref="C185:D185"/>
+    <mergeCell ref="C168:D168"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="C169:D169"/>
+    <mergeCell ref="C183:D183"/>
+    <mergeCell ref="C170:D170"/>
+    <mergeCell ref="C140:D140"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="C122:D122"/>
+    <mergeCell ref="C171:D171"/>
+    <mergeCell ref="C167:D167"/>
+    <mergeCell ref="B147:D147"/>
+    <mergeCell ref="B163:D164"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="C144:D144"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="C166:D166"/>
+    <mergeCell ref="C182:D182"/>
+    <mergeCell ref="H188:H220"/>
+    <mergeCell ref="C159:D159"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B187:J187"/>
+    <mergeCell ref="C172:D172"/>
+    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="C177:D177"/>
+    <mergeCell ref="C180:D180"/>
+    <mergeCell ref="C157:D157"/>
+    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="C175:D175"/>
+    <mergeCell ref="C149:D149"/>
+    <mergeCell ref="C150:D150"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="C143:D143"/>
+    <mergeCell ref="C184:D184"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B1:J3"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C48:D48"/>
     <mergeCell ref="F52:G52"/>
     <mergeCell ref="F48:G48"/>
     <mergeCell ref="F49:G49"/>
@@ -12679,190 +12836,35 @@
     <mergeCell ref="C135:D135"/>
     <mergeCell ref="C136:D136"/>
     <mergeCell ref="C133:D133"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B1:J3"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="H188:H220"/>
-    <mergeCell ref="C159:D159"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B187:J187"/>
-    <mergeCell ref="C172:D172"/>
-    <mergeCell ref="C176:D176"/>
-    <mergeCell ref="C177:D177"/>
-    <mergeCell ref="C180:D180"/>
-    <mergeCell ref="C157:D157"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="C175:D175"/>
-    <mergeCell ref="C149:D149"/>
-    <mergeCell ref="C150:D150"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="I58:J58"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="C143:D143"/>
-    <mergeCell ref="C184:D184"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C181:D181"/>
-    <mergeCell ref="C185:D185"/>
-    <mergeCell ref="C168:D168"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="C169:D169"/>
-    <mergeCell ref="C183:D183"/>
-    <mergeCell ref="C170:D170"/>
-    <mergeCell ref="C140:D140"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="C122:D122"/>
-    <mergeCell ref="C171:D171"/>
-    <mergeCell ref="C167:D167"/>
-    <mergeCell ref="B147:D147"/>
-    <mergeCell ref="B163:D164"/>
-    <mergeCell ref="B125:D125"/>
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="C144:D144"/>
-    <mergeCell ref="C139:D139"/>
-    <mergeCell ref="C166:D166"/>
-    <mergeCell ref="C182:D182"/>
-    <mergeCell ref="C205:D205"/>
-    <mergeCell ref="C206:D206"/>
-    <mergeCell ref="C207:D207"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C174:D174"/>
-    <mergeCell ref="C197:D197"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="C199:D199"/>
-    <mergeCell ref="C200:D200"/>
-    <mergeCell ref="C201:D201"/>
-    <mergeCell ref="C202:D202"/>
-    <mergeCell ref="C188:D188"/>
-    <mergeCell ref="C191:D191"/>
-    <mergeCell ref="C194:D194"/>
-    <mergeCell ref="C195:D195"/>
-    <mergeCell ref="C196:D196"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C204:D204"/>
-    <mergeCell ref="C203:D203"/>
-    <mergeCell ref="C161:D161"/>
-    <mergeCell ref="B138:D138"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="C120:D120"/>
-    <mergeCell ref="C192:D192"/>
-    <mergeCell ref="C193:D193"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="C189:D189"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C160:D160"/>
-    <mergeCell ref="C190:D190"/>
-    <mergeCell ref="B179:D179"/>
-    <mergeCell ref="C162:D162"/>
-    <mergeCell ref="C165:D165"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="B134:D134"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="B105:D105"/>
+    <mergeCell ref="C124:D124"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="F137:G137"/>
+    <mergeCell ref="I137:J137"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C107:D107"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.25" top="0.75" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="58" orientation="portrait" r:id="rId1"/>
@@ -12935,215 +12937,215 @@
       <c r="S1" s="1"/>
     </row>
     <row r="2" spans="1:27" ht="11.25" customHeight="1">
-      <c r="A2" s="665"/>
-      <c r="B2" s="666"/>
-      <c r="C2" s="666"/>
-      <c r="D2" s="666"/>
-      <c r="E2" s="666"/>
-      <c r="F2" s="666"/>
-      <c r="G2" s="666"/>
-      <c r="H2" s="666"/>
-      <c r="I2" s="666"/>
-      <c r="J2" s="666"/>
-      <c r="K2" s="666"/>
-      <c r="L2" s="666"/>
-      <c r="M2" s="666"/>
-      <c r="N2" s="666"/>
-      <c r="O2" s="666"/>
-      <c r="P2" s="666"/>
-      <c r="Q2" s="666"/>
-      <c r="R2" s="666"/>
-      <c r="S2" s="666"/>
-      <c r="T2" s="666"/>
-      <c r="U2" s="666"/>
-      <c r="V2" s="666"/>
-      <c r="W2" s="666"/>
-      <c r="X2" s="666"/>
-      <c r="Y2" s="666"/>
-      <c r="Z2" s="666"/>
-      <c r="AA2" s="690"/>
+      <c r="A2" s="654"/>
+      <c r="B2" s="655"/>
+      <c r="C2" s="655"/>
+      <c r="D2" s="655"/>
+      <c r="E2" s="655"/>
+      <c r="F2" s="655"/>
+      <c r="G2" s="655"/>
+      <c r="H2" s="655"/>
+      <c r="I2" s="655"/>
+      <c r="J2" s="655"/>
+      <c r="K2" s="655"/>
+      <c r="L2" s="655"/>
+      <c r="M2" s="655"/>
+      <c r="N2" s="655"/>
+      <c r="O2" s="655"/>
+      <c r="P2" s="655"/>
+      <c r="Q2" s="655"/>
+      <c r="R2" s="655"/>
+      <c r="S2" s="655"/>
+      <c r="T2" s="655"/>
+      <c r="U2" s="655"/>
+      <c r="V2" s="655"/>
+      <c r="W2" s="655"/>
+      <c r="X2" s="655"/>
+      <c r="Y2" s="655"/>
+      <c r="Z2" s="655"/>
+      <c r="AA2" s="691"/>
     </row>
     <row r="3" spans="1:27" ht="11.25" customHeight="1">
-      <c r="A3" s="691"/>
-      <c r="B3" s="692"/>
-      <c r="C3" s="692"/>
-      <c r="D3" s="692"/>
-      <c r="E3" s="692"/>
-      <c r="F3" s="692"/>
-      <c r="G3" s="692"/>
-      <c r="H3" s="692"/>
-      <c r="I3" s="692"/>
-      <c r="J3" s="692"/>
-      <c r="K3" s="692"/>
-      <c r="L3" s="692"/>
-      <c r="M3" s="692"/>
-      <c r="N3" s="692"/>
-      <c r="O3" s="692"/>
-      <c r="P3" s="692"/>
-      <c r="Q3" s="692"/>
-      <c r="R3" s="692"/>
-      <c r="S3" s="692"/>
-      <c r="T3" s="692"/>
-      <c r="U3" s="692"/>
-      <c r="V3" s="692"/>
-      <c r="W3" s="692"/>
-      <c r="X3" s="692"/>
-      <c r="Y3" s="692"/>
-      <c r="Z3" s="692"/>
-      <c r="AA3" s="693"/>
+      <c r="A3" s="692"/>
+      <c r="B3" s="693"/>
+      <c r="C3" s="693"/>
+      <c r="D3" s="693"/>
+      <c r="E3" s="693"/>
+      <c r="F3" s="693"/>
+      <c r="G3" s="693"/>
+      <c r="H3" s="693"/>
+      <c r="I3" s="693"/>
+      <c r="J3" s="693"/>
+      <c r="K3" s="693"/>
+      <c r="L3" s="693"/>
+      <c r="M3" s="693"/>
+      <c r="N3" s="693"/>
+      <c r="O3" s="693"/>
+      <c r="P3" s="693"/>
+      <c r="Q3" s="693"/>
+      <c r="R3" s="693"/>
+      <c r="S3" s="693"/>
+      <c r="T3" s="693"/>
+      <c r="U3" s="693"/>
+      <c r="V3" s="693"/>
+      <c r="W3" s="693"/>
+      <c r="X3" s="693"/>
+      <c r="Y3" s="693"/>
+      <c r="Z3" s="693"/>
+      <c r="AA3" s="694"/>
     </row>
     <row r="4" spans="1:27" ht="12" customHeight="1" thickBot="1">
-      <c r="A4" s="694"/>
-      <c r="B4" s="695"/>
-      <c r="C4" s="695"/>
-      <c r="D4" s="695"/>
-      <c r="E4" s="695"/>
-      <c r="F4" s="695"/>
-      <c r="G4" s="695"/>
-      <c r="H4" s="695"/>
-      <c r="I4" s="695"/>
-      <c r="J4" s="695"/>
-      <c r="K4" s="695"/>
-      <c r="L4" s="695"/>
-      <c r="M4" s="695"/>
-      <c r="N4" s="695"/>
-      <c r="O4" s="695"/>
-      <c r="P4" s="695"/>
-      <c r="Q4" s="695"/>
-      <c r="R4" s="695"/>
-      <c r="S4" s="695"/>
-      <c r="T4" s="695"/>
-      <c r="U4" s="695"/>
-      <c r="V4" s="695"/>
-      <c r="W4" s="695"/>
-      <c r="X4" s="695"/>
-      <c r="Y4" s="695"/>
-      <c r="Z4" s="695"/>
-      <c r="AA4" s="696"/>
+      <c r="A4" s="695"/>
+      <c r="B4" s="696"/>
+      <c r="C4" s="696"/>
+      <c r="D4" s="696"/>
+      <c r="E4" s="696"/>
+      <c r="F4" s="696"/>
+      <c r="G4" s="696"/>
+      <c r="H4" s="696"/>
+      <c r="I4" s="696"/>
+      <c r="J4" s="696"/>
+      <c r="K4" s="696"/>
+      <c r="L4" s="696"/>
+      <c r="M4" s="696"/>
+      <c r="N4" s="696"/>
+      <c r="O4" s="696"/>
+      <c r="P4" s="696"/>
+      <c r="Q4" s="696"/>
+      <c r="R4" s="696"/>
+      <c r="S4" s="696"/>
+      <c r="T4" s="696"/>
+      <c r="U4" s="696"/>
+      <c r="V4" s="696"/>
+      <c r="W4" s="696"/>
+      <c r="X4" s="696"/>
+      <c r="Y4" s="696"/>
+      <c r="Z4" s="696"/>
+      <c r="AA4" s="697"/>
     </row>
     <row r="5" spans="1:27" ht="12.75" customHeight="1">
-      <c r="A5" s="665" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="666"/>
-      <c r="C5" s="666"/>
-      <c r="D5" s="666"/>
-      <c r="E5" s="666"/>
-      <c r="F5" s="666"/>
-      <c r="G5" s="666"/>
-      <c r="H5" s="666"/>
-      <c r="I5" s="666"/>
-      <c r="J5" s="666"/>
-      <c r="K5" s="666"/>
-      <c r="L5" s="666"/>
-      <c r="M5" s="666"/>
-      <c r="N5" s="666"/>
-      <c r="O5" s="666"/>
-      <c r="P5" s="666"/>
-      <c r="Q5" s="666"/>
-      <c r="R5" s="666"/>
-      <c r="S5" s="666"/>
-      <c r="T5" s="666"/>
-      <c r="U5" s="666"/>
-      <c r="V5" s="666"/>
-      <c r="W5" s="666"/>
-      <c r="X5" s="666"/>
-      <c r="Y5" s="666"/>
-      <c r="Z5" s="666"/>
-      <c r="AA5" s="690"/>
+      <c r="A5" s="654" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="655"/>
+      <c r="C5" s="655"/>
+      <c r="D5" s="655"/>
+      <c r="E5" s="655"/>
+      <c r="F5" s="655"/>
+      <c r="G5" s="655"/>
+      <c r="H5" s="655"/>
+      <c r="I5" s="655"/>
+      <c r="J5" s="655"/>
+      <c r="K5" s="655"/>
+      <c r="L5" s="655"/>
+      <c r="M5" s="655"/>
+      <c r="N5" s="655"/>
+      <c r="O5" s="655"/>
+      <c r="P5" s="655"/>
+      <c r="Q5" s="655"/>
+      <c r="R5" s="655"/>
+      <c r="S5" s="655"/>
+      <c r="T5" s="655"/>
+      <c r="U5" s="655"/>
+      <c r="V5" s="655"/>
+      <c r="W5" s="655"/>
+      <c r="X5" s="655"/>
+      <c r="Y5" s="655"/>
+      <c r="Z5" s="655"/>
+      <c r="AA5" s="691"/>
     </row>
     <row r="6" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A6" s="697"/>
-      <c r="B6" s="698"/>
-      <c r="C6" s="698"/>
-      <c r="D6" s="698"/>
-      <c r="E6" s="698"/>
-      <c r="F6" s="698"/>
-      <c r="G6" s="698"/>
-      <c r="H6" s="698"/>
-      <c r="I6" s="698"/>
-      <c r="J6" s="698"/>
-      <c r="K6" s="698"/>
-      <c r="L6" s="698"/>
-      <c r="M6" s="698"/>
-      <c r="N6" s="698"/>
-      <c r="O6" s="698"/>
-      <c r="P6" s="698"/>
-      <c r="Q6" s="698"/>
-      <c r="R6" s="698"/>
-      <c r="S6" s="698"/>
-      <c r="T6" s="698"/>
-      <c r="U6" s="698"/>
-      <c r="V6" s="698"/>
-      <c r="W6" s="698"/>
-      <c r="X6" s="698"/>
-      <c r="Y6" s="698"/>
-      <c r="Z6" s="698"/>
-      <c r="AA6" s="699"/>
+      <c r="A6" s="698"/>
+      <c r="B6" s="699"/>
+      <c r="C6" s="699"/>
+      <c r="D6" s="699"/>
+      <c r="E6" s="699"/>
+      <c r="F6" s="699"/>
+      <c r="G6" s="699"/>
+      <c r="H6" s="699"/>
+      <c r="I6" s="699"/>
+      <c r="J6" s="699"/>
+      <c r="K6" s="699"/>
+      <c r="L6" s="699"/>
+      <c r="M6" s="699"/>
+      <c r="N6" s="699"/>
+      <c r="O6" s="699"/>
+      <c r="P6" s="699"/>
+      <c r="Q6" s="699"/>
+      <c r="R6" s="699"/>
+      <c r="S6" s="699"/>
+      <c r="T6" s="699"/>
+      <c r="U6" s="699"/>
+      <c r="V6" s="699"/>
+      <c r="W6" s="699"/>
+      <c r="X6" s="699"/>
+      <c r="Y6" s="699"/>
+      <c r="Z6" s="699"/>
+      <c r="AA6" s="700"/>
     </row>
     <row r="7" spans="1:27" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A7" s="700" t="s">
+      <c r="A7" s="701" t="s">
         <v>296</v>
       </c>
-      <c r="B7" s="701"/>
-      <c r="C7" s="701"/>
-      <c r="D7" s="701"/>
-      <c r="E7" s="701"/>
-      <c r="F7" s="701"/>
-      <c r="G7" s="701"/>
-      <c r="H7" s="701"/>
-      <c r="I7" s="701"/>
-      <c r="J7" s="701"/>
-      <c r="K7" s="701"/>
-      <c r="L7" s="701"/>
-      <c r="M7" s="701"/>
-      <c r="N7" s="701"/>
-      <c r="O7" s="701"/>
-      <c r="P7" s="702"/>
-      <c r="Q7" s="702"/>
-      <c r="R7" s="702"/>
-      <c r="S7" s="702"/>
-      <c r="T7" s="702"/>
-      <c r="U7" s="702"/>
-      <c r="V7" s="702"/>
-      <c r="W7" s="702"/>
-      <c r="X7" s="702"/>
-      <c r="Y7" s="702"/>
-      <c r="Z7" s="702"/>
-      <c r="AA7" s="703"/>
+      <c r="B7" s="702"/>
+      <c r="C7" s="702"/>
+      <c r="D7" s="702"/>
+      <c r="E7" s="702"/>
+      <c r="F7" s="702"/>
+      <c r="G7" s="702"/>
+      <c r="H7" s="702"/>
+      <c r="I7" s="702"/>
+      <c r="J7" s="702"/>
+      <c r="K7" s="702"/>
+      <c r="L7" s="702"/>
+      <c r="M7" s="702"/>
+      <c r="N7" s="702"/>
+      <c r="O7" s="702"/>
+      <c r="P7" s="703"/>
+      <c r="Q7" s="703"/>
+      <c r="R7" s="703"/>
+      <c r="S7" s="703"/>
+      <c r="T7" s="703"/>
+      <c r="U7" s="703"/>
+      <c r="V7" s="703"/>
+      <c r="W7" s="703"/>
+      <c r="X7" s="703"/>
+      <c r="Y7" s="703"/>
+      <c r="Z7" s="703"/>
+      <c r="AA7" s="704"/>
     </row>
     <row r="8" spans="1:27" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A8" s="704" t="s">
+      <c r="A8" s="705" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="705"/>
-      <c r="C8" s="705"/>
-      <c r="D8" s="705"/>
-      <c r="E8" s="705"/>
-      <c r="F8" s="705"/>
-      <c r="G8" s="705"/>
-      <c r="H8" s="705"/>
-      <c r="I8" s="705"/>
-      <c r="J8" s="705"/>
-      <c r="K8" s="705"/>
-      <c r="L8" s="705"/>
-      <c r="M8" s="705"/>
-      <c r="N8" s="706"/>
+      <c r="B8" s="706"/>
+      <c r="C8" s="706"/>
+      <c r="D8" s="706"/>
+      <c r="E8" s="706"/>
+      <c r="F8" s="706"/>
+      <c r="G8" s="706"/>
+      <c r="H8" s="706"/>
+      <c r="I8" s="706"/>
+      <c r="J8" s="706"/>
+      <c r="K8" s="706"/>
+      <c r="L8" s="706"/>
+      <c r="M8" s="706"/>
+      <c r="N8" s="707"/>
       <c r="O8" s="6"/>
-      <c r="P8" s="704" t="s">
+      <c r="P8" s="705" t="s">
         <v>2</v>
       </c>
-      <c r="Q8" s="705"/>
-      <c r="R8" s="705"/>
-      <c r="S8" s="705"/>
-      <c r="T8" s="705"/>
-      <c r="U8" s="705"/>
-      <c r="V8" s="705"/>
-      <c r="W8" s="705"/>
-      <c r="X8" s="705"/>
-      <c r="Y8" s="705"/>
-      <c r="Z8" s="705"/>
-      <c r="AA8" s="707"/>
+      <c r="Q8" s="706"/>
+      <c r="R8" s="706"/>
+      <c r="S8" s="706"/>
+      <c r="T8" s="706"/>
+      <c r="U8" s="706"/>
+      <c r="V8" s="706"/>
+      <c r="W8" s="706"/>
+      <c r="X8" s="706"/>
+      <c r="Y8" s="706"/>
+      <c r="Z8" s="706"/>
+      <c r="AA8" s="708"/>
     </row>
     <row r="9" spans="1:27" s="215" customFormat="1" ht="45.75" customHeight="1">
       <c r="A9" s="216">
@@ -14689,7 +14691,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
-      <c r="H32" s="157">
+      <c r="H32" s="716">
         <f>+H31/1000000</f>
         <v>1.8436589195408826</v>
       </c>
@@ -14698,7 +14700,7 @@
       <c r="K32" s="157"/>
       <c r="L32" s="157"/>
       <c r="M32" s="36"/>
-      <c r="N32" s="157">
+      <c r="N32" s="716">
         <f>+N31/1000000</f>
         <v>1.4601854336242732</v>
       </c>
@@ -14709,11 +14711,11 @@
       <c r="R32" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="T32" s="687" t="s">
+      <c r="T32" s="688" t="s">
         <v>53</v>
       </c>
-      <c r="U32" s="688"/>
-      <c r="V32" s="689"/>
+      <c r="U32" s="689"/>
+      <c r="V32" s="690"/>
     </row>
     <row r="33" spans="1:27" ht="10.5">
       <c r="A33" s="37"/>
@@ -14811,7 +14813,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
-      <c r="H36" s="160">
+      <c r="H36" s="717">
         <f>+H32+H34</f>
         <v>1.8436589195408826</v>
       </c>
@@ -14820,12 +14822,12 @@
       <c r="K36" s="160"/>
       <c r="L36" s="160"/>
       <c r="M36" s="3"/>
-      <c r="N36" s="160">
+      <c r="N36" s="717">
         <f>+N32+N34</f>
         <v>1.4601854336242732</v>
       </c>
-      <c r="P36" s="686"/>
-      <c r="Q36" s="686"/>
+      <c r="P36" s="687"/>
+      <c r="Q36" s="687"/>
       <c r="T36" s="31" t="s">
         <v>59</v>
       </c>
@@ -16142,10 +16144,10 @@
       </c>
     </row>
     <row r="11" spans="2:21" s="362" customFormat="1" ht="13" hidden="1">
-      <c r="B11" s="708" t="s">
+      <c r="B11" s="709" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="708"/>
+      <c r="C11" s="709"/>
       <c r="D11" s="391">
         <v>42</v>
       </c>
@@ -20609,22 +20611,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="16" thickBot="1">
-      <c r="A1" s="709" t="s">
+      <c r="A1" s="710" t="s">
         <v>256</v>
       </c>
-      <c r="B1" s="710"/>
-      <c r="C1" s="710"/>
-      <c r="D1" s="710"/>
-      <c r="E1" s="710"/>
-      <c r="F1" s="710"/>
-      <c r="G1" s="710"/>
-      <c r="H1" s="710"/>
-      <c r="I1" s="710"/>
-      <c r="J1" s="710"/>
-      <c r="K1" s="710"/>
-      <c r="L1" s="710"/>
-      <c r="M1" s="710"/>
-      <c r="N1" s="711"/>
+      <c r="B1" s="711"/>
+      <c r="C1" s="711"/>
+      <c r="D1" s="711"/>
+      <c r="E1" s="711"/>
+      <c r="F1" s="711"/>
+      <c r="G1" s="711"/>
+      <c r="H1" s="711"/>
+      <c r="I1" s="711"/>
+      <c r="J1" s="711"/>
+      <c r="K1" s="711"/>
+      <c r="L1" s="711"/>
+      <c r="M1" s="711"/>
+      <c r="N1" s="712"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="178" t="s">
@@ -21650,21 +21652,21 @@
       <c r="I34" s="358"/>
     </row>
     <row r="35" spans="1:15" ht="16" outlineLevel="1" thickBot="1">
-      <c r="A35" s="709"/>
-      <c r="B35" s="710"/>
-      <c r="C35" s="710"/>
-      <c r="D35" s="710"/>
-      <c r="E35" s="710"/>
-      <c r="F35" s="710"/>
-      <c r="G35" s="710"/>
-      <c r="H35" s="710"/>
-      <c r="I35" s="710"/>
-      <c r="J35" s="710"/>
-      <c r="K35" s="710"/>
-      <c r="L35" s="710"/>
-      <c r="M35" s="710"/>
-      <c r="N35" s="710"/>
-      <c r="O35" s="711"/>
+      <c r="A35" s="710"/>
+      <c r="B35" s="711"/>
+      <c r="C35" s="711"/>
+      <c r="D35" s="711"/>
+      <c r="E35" s="711"/>
+      <c r="F35" s="711"/>
+      <c r="G35" s="711"/>
+      <c r="H35" s="711"/>
+      <c r="I35" s="711"/>
+      <c r="J35" s="711"/>
+      <c r="K35" s="711"/>
+      <c r="L35" s="711"/>
+      <c r="M35" s="711"/>
+      <c r="N35" s="711"/>
+      <c r="O35" s="712"/>
     </row>
     <row r="36" spans="1:15" outlineLevel="1">
       <c r="A36" s="306" t="s">
@@ -23454,21 +23456,21 @@
       <c r="I91" s="186"/>
     </row>
     <row r="92" spans="1:15" ht="16" thickBot="1">
-      <c r="A92" s="712"/>
-      <c r="B92" s="713"/>
-      <c r="C92" s="713"/>
-      <c r="D92" s="713"/>
-      <c r="E92" s="713"/>
-      <c r="F92" s="713"/>
-      <c r="G92" s="713"/>
-      <c r="H92" s="713"/>
-      <c r="I92" s="713"/>
-      <c r="J92" s="713"/>
-      <c r="K92" s="713"/>
-      <c r="L92" s="713"/>
-      <c r="M92" s="713"/>
-      <c r="N92" s="713"/>
-      <c r="O92" s="714"/>
+      <c r="A92" s="713"/>
+      <c r="B92" s="714"/>
+      <c r="C92" s="714"/>
+      <c r="D92" s="714"/>
+      <c r="E92" s="714"/>
+      <c r="F92" s="714"/>
+      <c r="G92" s="714"/>
+      <c r="H92" s="714"/>
+      <c r="I92" s="714"/>
+      <c r="J92" s="714"/>
+      <c r="K92" s="714"/>
+      <c r="L92" s="714"/>
+      <c r="M92" s="714"/>
+      <c r="N92" s="714"/>
+      <c r="O92" s="715"/>
     </row>
     <row r="93" spans="1:15">
       <c r="A93" s="178"/>
@@ -23792,7 +23794,7 @@
       <c r="A16" s="197" t="s">
         <v>286</v>
       </c>
-      <c r="B16" s="715">
+      <c r="B16" s="589">
         <f>'Rent Calculation'!F54</f>
         <v>72</v>
       </c>
@@ -23899,27 +23901,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" xsi:nil="true"/>
-    <Status xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100907921E7373C1341A3C877D189CE8922" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2036b66ca2b7955135caa708c7901a86">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xmlns:ns3="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fed2217af4f675ffeab875e34aa73a78" ns2:_="" ns3:_="">
     <xsd:import namespace="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
@@ -24162,26 +24143,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC57694E-BA35-486E-AC74-B7B624F1FDE0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" xsi:nil="true"/>
+    <Status xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12D5BE44-B07C-4182-BC7A-71E5962390BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
-    <ds:schemaRef ds:uri="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB719E29-C329-4AB1-8ED0-5CC29C0FF757}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24200,6 +24183,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12D5BE44-B07C-4182-BC7A-71E5962390BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
+    <ds:schemaRef ds:uri="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC57694E-BA35-486E-AC74-B7B624F1FDE0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{a59b6cd5-d141-4a33-8bf1-0ca04484304f}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" removed="0"/>

--- a/artifacts/Rental Specimen.xlsx
+++ b/artifacts/Rental Specimen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z0050s8t\Documents\rental-automation\artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF91041-4CA4-40B4-B6D4-80B5A323F3D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD07F51-7080-4834-9EC6-0D26BC88ED92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="764" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="764" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="26" r:id="rId1"/>
@@ -5544,9 +5544,206 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="14" fillId="0" borderId="8" xfId="190" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="25" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="26" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="4" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="54" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="6" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="55" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="50" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5556,351 +5753,156 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="33" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="29" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="33" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="29" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="25" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="26" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="4" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="54" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="6" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="55" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="50" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="192" fontId="52" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5922,8 +5924,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1012">
     <cellStyle name="??" xfId="303" xr:uid="{91225FB4-C7AB-4245-B40E-51FA489A4ADF}"/>
@@ -7473,62 +7473,62 @@
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1">
       <c r="A1" s="51"/>
-      <c r="B1" s="629"/>
-      <c r="C1" s="630"/>
-      <c r="D1" s="630"/>
-      <c r="E1" s="630"/>
-      <c r="F1" s="630"/>
-      <c r="G1" s="630"/>
-      <c r="H1" s="630"/>
-      <c r="I1" s="630"/>
-      <c r="J1" s="631"/>
+      <c r="B1" s="665"/>
+      <c r="C1" s="666"/>
+      <c r="D1" s="666"/>
+      <c r="E1" s="666"/>
+      <c r="F1" s="666"/>
+      <c r="G1" s="666"/>
+      <c r="H1" s="666"/>
+      <c r="I1" s="666"/>
+      <c r="J1" s="667"/>
     </row>
     <row r="2" spans="1:10" ht="14.25" customHeight="1">
       <c r="A2" s="51"/>
-      <c r="B2" s="632"/>
-      <c r="C2" s="633"/>
-      <c r="D2" s="633"/>
-      <c r="E2" s="633"/>
-      <c r="F2" s="633"/>
-      <c r="G2" s="633"/>
-      <c r="H2" s="633"/>
-      <c r="I2" s="633"/>
-      <c r="J2" s="634"/>
+      <c r="B2" s="668"/>
+      <c r="C2" s="669"/>
+      <c r="D2" s="669"/>
+      <c r="E2" s="669"/>
+      <c r="F2" s="669"/>
+      <c r="G2" s="669"/>
+      <c r="H2" s="669"/>
+      <c r="I2" s="669"/>
+      <c r="J2" s="670"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A3" s="51"/>
-      <c r="B3" s="635"/>
-      <c r="C3" s="636"/>
-      <c r="D3" s="636"/>
-      <c r="E3" s="636"/>
-      <c r="F3" s="636"/>
-      <c r="G3" s="636"/>
-      <c r="H3" s="636"/>
-      <c r="I3" s="633"/>
-      <c r="J3" s="634"/>
+      <c r="B3" s="671"/>
+      <c r="C3" s="672"/>
+      <c r="D3" s="672"/>
+      <c r="E3" s="672"/>
+      <c r="F3" s="672"/>
+      <c r="G3" s="672"/>
+      <c r="H3" s="672"/>
+      <c r="I3" s="669"/>
+      <c r="J3" s="670"/>
     </row>
     <row r="4" spans="1:10" ht="13">
       <c r="A4" s="51"/>
-      <c r="B4" s="654"/>
-      <c r="C4" s="655"/>
-      <c r="D4" s="655"/>
-      <c r="E4" s="655"/>
-      <c r="F4" s="655"/>
-      <c r="G4" s="655"/>
+      <c r="B4" s="596"/>
+      <c r="C4" s="597"/>
+      <c r="D4" s="597"/>
+      <c r="E4" s="597"/>
+      <c r="F4" s="597"/>
+      <c r="G4" s="597"/>
       <c r="H4" s="401"/>
       <c r="I4" s="402"/>
       <c r="J4" s="403"/>
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="51"/>
-      <c r="B5" s="656" t="s">
+      <c r="B5" s="692" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="657"/>
-      <c r="D5" s="657"/>
-      <c r="E5" s="657"/>
-      <c r="F5" s="657"/>
-      <c r="G5" s="658"/>
+      <c r="C5" s="693"/>
+      <c r="D5" s="693"/>
+      <c r="E5" s="693"/>
+      <c r="F5" s="693"/>
+      <c r="G5" s="694"/>
       <c r="H5" s="404"/>
       <c r="I5" s="481" t="s">
         <v>16</v>
@@ -7539,29 +7539,29 @@
     </row>
     <row r="6" spans="1:10" ht="13.5" thickBot="1">
       <c r="A6" s="51"/>
-      <c r="B6" s="659"/>
-      <c r="C6" s="660"/>
-      <c r="D6" s="661"/>
+      <c r="B6" s="695"/>
+      <c r="C6" s="696"/>
+      <c r="D6" s="697"/>
       <c r="E6" s="52"/>
-      <c r="F6" s="652">
+      <c r="F6" s="690">
         <v>10.763999999999999</v>
       </c>
-      <c r="G6" s="653"/>
+      <c r="G6" s="691"/>
       <c r="H6" s="405"/>
-      <c r="I6" s="643">
+      <c r="I6" s="678">
         <v>10.763999999999999</v>
       </c>
-      <c r="J6" s="644"/>
+      <c r="J6" s="679"/>
     </row>
     <row r="7" spans="1:10" ht="26">
       <c r="A7" s="51"/>
       <c r="B7" s="482" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="662" t="s">
+      <c r="C7" s="698" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="663"/>
+      <c r="D7" s="699"/>
       <c r="E7" s="483"/>
       <c r="F7" s="483" t="s">
         <v>303</v>
@@ -7589,23 +7589,23 @@
       <c r="C8" s="486"/>
       <c r="D8" s="487"/>
       <c r="E8" s="488"/>
-      <c r="F8" s="590" t="s">
+      <c r="F8" s="624" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="591"/>
+      <c r="G8" s="658"/>
       <c r="H8" s="404"/>
-      <c r="I8" s="592" t="s">
+      <c r="I8" s="659" t="s">
         <v>67</v>
       </c>
-      <c r="J8" s="593"/>
+      <c r="J8" s="660"/>
     </row>
     <row r="9" spans="1:10" ht="13">
       <c r="A9" s="51"/>
-      <c r="B9" s="592" t="s">
+      <c r="B9" s="659" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="591"/>
-      <c r="D9" s="607"/>
+      <c r="C9" s="658"/>
+      <c r="D9" s="625"/>
       <c r="E9" s="489"/>
       <c r="F9" s="376" t="s">
         <v>75</v>
@@ -7626,21 +7626,21 @@
       <c r="B10" s="490">
         <v>1</v>
       </c>
-      <c r="C10" s="637" t="s">
+      <c r="C10" s="673" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="638"/>
+      <c r="D10" s="632"/>
       <c r="E10" s="491"/>
-      <c r="F10" s="649" t="s">
+      <c r="F10" s="684" t="s">
         <v>299</v>
       </c>
-      <c r="G10" s="650"/>
+      <c r="G10" s="685"/>
       <c r="H10" s="404"/>
-      <c r="I10" s="645" t="str">
+      <c r="I10" s="680" t="str">
         <f>+F10</f>
         <v>Chennai</v>
       </c>
-      <c r="J10" s="646"/>
+      <c r="J10" s="681"/>
     </row>
     <row r="11" spans="1:10" ht="28.5" customHeight="1">
       <c r="A11" s="51"/>
@@ -7648,19 +7648,19 @@
         <f>1+B10</f>
         <v>2</v>
       </c>
-      <c r="C11" s="639" t="s">
+      <c r="C11" s="674" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="640"/>
+      <c r="D11" s="675"/>
       <c r="E11" s="50"/>
-      <c r="F11" s="649"/>
-      <c r="G11" s="650"/>
+      <c r="F11" s="684"/>
+      <c r="G11" s="685"/>
       <c r="H11" s="404"/>
-      <c r="I11" s="647">
+      <c r="I11" s="682">
         <f>+F11</f>
         <v>0</v>
       </c>
-      <c r="J11" s="648"/>
+      <c r="J11" s="683"/>
     </row>
     <row r="12" spans="1:10" ht="27.75" customHeight="1">
       <c r="A12" s="51"/>
@@ -7668,19 +7668,19 @@
         <f>1+B11</f>
         <v>3</v>
       </c>
-      <c r="C12" s="600" t="s">
+      <c r="C12" s="618" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="601"/>
+      <c r="D12" s="617"/>
       <c r="E12" s="492"/>
-      <c r="F12" s="628"/>
-      <c r="G12" s="623"/>
+      <c r="F12" s="686"/>
+      <c r="G12" s="687"/>
       <c r="H12" s="404"/>
-      <c r="I12" s="624">
+      <c r="I12" s="700">
         <f>+F12</f>
         <v>0</v>
       </c>
-      <c r="J12" s="625"/>
+      <c r="J12" s="701"/>
     </row>
     <row r="13" spans="1:10" ht="15.9" customHeight="1">
       <c r="A13" s="51"/>
@@ -7688,16 +7688,16 @@
         <f t="shared" ref="B13:B30" si="0">1+B12</f>
         <v>4</v>
       </c>
-      <c r="C13" s="600" t="s">
+      <c r="C13" s="618" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="601"/>
+      <c r="D13" s="617"/>
       <c r="E13" s="50"/>
-      <c r="F13" s="622"/>
-      <c r="G13" s="623"/>
+      <c r="F13" s="689"/>
+      <c r="G13" s="687"/>
       <c r="H13" s="404"/>
-      <c r="I13" s="624"/>
-      <c r="J13" s="625"/>
+      <c r="I13" s="700"/>
+      <c r="J13" s="701"/>
     </row>
     <row r="14" spans="1:10" ht="48" customHeight="1">
       <c r="A14" s="51"/>
@@ -7705,21 +7705,21 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="641" t="s">
+      <c r="C14" s="676" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="642"/>
+      <c r="D14" s="677"/>
       <c r="E14" s="476"/>
-      <c r="F14" s="628" t="s">
+      <c r="F14" s="686" t="s">
         <v>300</v>
       </c>
-      <c r="G14" s="651"/>
+      <c r="G14" s="688"/>
       <c r="H14" s="404"/>
-      <c r="I14" s="624" t="str">
+      <c r="I14" s="700" t="str">
         <f>+F14</f>
         <v>6th floor</v>
       </c>
-      <c r="J14" s="625"/>
+      <c r="J14" s="701"/>
     </row>
     <row r="15" spans="1:10" ht="51.75" customHeight="1">
       <c r="A15" s="51"/>
@@ -7727,19 +7727,19 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="600" t="s">
+      <c r="C15" s="618" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="601"/>
+      <c r="D15" s="617"/>
       <c r="E15" s="58"/>
-      <c r="F15" s="590"/>
-      <c r="G15" s="591"/>
+      <c r="F15" s="624"/>
+      <c r="G15" s="658"/>
       <c r="H15" s="404"/>
-      <c r="I15" s="592">
+      <c r="I15" s="659">
         <f>+F15</f>
         <v>0</v>
       </c>
-      <c r="J15" s="593"/>
+      <c r="J15" s="660"/>
     </row>
     <row r="16" spans="1:10" ht="15.9" customHeight="1">
       <c r="A16" s="51"/>
@@ -7747,16 +7747,16 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="600" t="s">
+      <c r="C16" s="618" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="601"/>
+      <c r="D16" s="617"/>
       <c r="E16" s="58"/>
-      <c r="F16" s="622"/>
-      <c r="G16" s="623"/>
+      <c r="F16" s="689"/>
+      <c r="G16" s="687"/>
       <c r="H16" s="404"/>
-      <c r="I16" s="624"/>
-      <c r="J16" s="625"/>
+      <c r="I16" s="700"/>
+      <c r="J16" s="701"/>
     </row>
     <row r="17" spans="1:10" ht="15.9" customHeight="1">
       <c r="A17" s="51"/>
@@ -7764,21 +7764,21 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="600" t="s">
+      <c r="C17" s="618" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="601"/>
+      <c r="D17" s="617"/>
       <c r="E17" s="58"/>
-      <c r="F17" s="628" t="s">
+      <c r="F17" s="686" t="s">
         <v>85</v>
       </c>
-      <c r="G17" s="623"/>
+      <c r="G17" s="687"/>
       <c r="H17" s="404"/>
-      <c r="I17" s="624" t="str">
+      <c r="I17" s="700" t="str">
         <f>+F17</f>
         <v>Warm Shell</v>
       </c>
-      <c r="J17" s="625"/>
+      <c r="J17" s="701"/>
     </row>
     <row r="18" spans="1:10" ht="48" customHeight="1">
       <c r="A18" s="51"/>
@@ -7786,22 +7786,22 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="600" t="s">
+      <c r="C18" s="618" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="601"/>
+      <c r="D18" s="617"/>
       <c r="E18" s="163"/>
-      <c r="F18" s="590">
+      <c r="F18" s="624">
         <f>F15</f>
         <v>0</v>
       </c>
-      <c r="G18" s="591"/>
+      <c r="G18" s="658"/>
       <c r="H18" s="404"/>
-      <c r="I18" s="592">
+      <c r="I18" s="659">
         <f>+F18</f>
         <v>0</v>
       </c>
-      <c r="J18" s="593"/>
+      <c r="J18" s="660"/>
     </row>
     <row r="19" spans="1:10" ht="15.9" customHeight="1">
       <c r="A19" s="51"/>
@@ -7809,16 +7809,16 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="600" t="s">
+      <c r="C19" s="618" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="601"/>
+      <c r="D19" s="617"/>
       <c r="E19" s="163"/>
-      <c r="F19" s="622"/>
-      <c r="G19" s="623"/>
+      <c r="F19" s="689"/>
+      <c r="G19" s="687"/>
       <c r="H19" s="404"/>
-      <c r="I19" s="624"/>
-      <c r="J19" s="625"/>
+      <c r="I19" s="700"/>
+      <c r="J19" s="701"/>
     </row>
     <row r="20" spans="1:10" ht="15.9" customHeight="1">
       <c r="A20" s="51"/>
@@ -7826,10 +7826,10 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="594" t="s">
+      <c r="C20" s="616" t="s">
         <v>88</v>
       </c>
-      <c r="D20" s="601"/>
+      <c r="D20" s="617"/>
       <c r="E20" s="494"/>
       <c r="F20" s="56"/>
       <c r="G20" s="388"/>
@@ -7849,10 +7849,10 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="600" t="s">
+      <c r="C21" s="618" t="s">
         <v>89</v>
       </c>
-      <c r="D21" s="601"/>
+      <c r="D21" s="617"/>
       <c r="E21" s="494"/>
       <c r="F21" s="56">
         <f>Main!B3</f>
@@ -7878,10 +7878,10 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="594" t="s">
+      <c r="C22" s="616" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="601"/>
+      <c r="D22" s="617"/>
       <c r="E22" s="494"/>
       <c r="F22" s="56">
         <v>0</v>
@@ -7905,10 +7905,10 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="600" t="s">
+      <c r="C23" s="618" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="601"/>
+      <c r="D23" s="617"/>
       <c r="E23" s="494"/>
       <c r="F23" s="56">
         <f>+F21+F22</f>
@@ -7934,10 +7934,10 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="600" t="s">
+      <c r="C24" s="618" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="601"/>
+      <c r="D24" s="617"/>
       <c r="E24" s="59"/>
       <c r="F24" s="56"/>
       <c r="G24" s="388">
@@ -7960,10 +7960,10 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="600" t="s">
+      <c r="C25" s="618" t="s">
         <v>93</v>
       </c>
-      <c r="D25" s="601"/>
+      <c r="D25" s="617"/>
       <c r="E25" s="59"/>
       <c r="F25" s="56">
         <v>0</v>
@@ -7988,10 +7988,10 @@
         <f>1+B25</f>
         <v>17</v>
       </c>
-      <c r="C26" s="600" t="s">
+      <c r="C26" s="618" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="601"/>
+      <c r="D26" s="617"/>
       <c r="E26" s="60"/>
       <c r="F26" s="61">
         <f>F25/F23</f>
@@ -8017,10 +8017,10 @@
         <f>1+B26</f>
         <v>18</v>
       </c>
-      <c r="C27" s="594" t="s">
+      <c r="C27" s="616" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="601"/>
+      <c r="D27" s="617"/>
       <c r="E27" s="58"/>
       <c r="F27" s="293">
         <f>'CAPEX and PM'!E3</f>
@@ -8046,10 +8046,10 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="594" t="s">
+      <c r="C28" s="616" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="601"/>
+      <c r="D28" s="617"/>
       <c r="E28" s="64"/>
       <c r="F28" s="64">
         <f>Main!B12</f>
@@ -8075,10 +8075,10 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="594" t="s">
+      <c r="C29" s="616" t="s">
         <v>97</v>
       </c>
-      <c r="D29" s="601"/>
+      <c r="D29" s="617"/>
       <c r="E29" s="64"/>
       <c r="F29" s="60">
         <f>Main!B13</f>
@@ -8104,10 +8104,10 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="600" t="s">
+      <c r="C30" s="618" t="s">
         <v>98</v>
       </c>
-      <c r="D30" s="601"/>
+      <c r="D30" s="617"/>
       <c r="E30" s="58"/>
       <c r="F30" s="56">
         <v>0</v>
@@ -8128,11 +8128,11 @@
     </row>
     <row r="31" spans="1:10" ht="15.9" customHeight="1">
       <c r="A31" s="51"/>
-      <c r="B31" s="619" t="s">
+      <c r="B31" s="702" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="620"/>
-      <c r="D31" s="621"/>
+      <c r="C31" s="703"/>
+      <c r="D31" s="704"/>
       <c r="E31" s="497"/>
       <c r="F31" s="376" t="s">
         <v>75</v>
@@ -8153,10 +8153,10 @@
       <c r="B32" s="162">
         <v>1</v>
       </c>
-      <c r="C32" s="594" t="s">
+      <c r="C32" s="616" t="s">
         <v>100</v>
       </c>
-      <c r="D32" s="601"/>
+      <c r="D32" s="617"/>
       <c r="E32" s="59"/>
       <c r="F32" s="56">
         <f>Main!B9/(Main!B3*Main!B7)</f>
@@ -8182,10 +8182,10 @@
         <f>1+B32</f>
         <v>2</v>
       </c>
-      <c r="C33" s="594" t="s">
+      <c r="C33" s="616" t="s">
         <v>101</v>
       </c>
-      <c r="D33" s="601"/>
+      <c r="D33" s="617"/>
       <c r="E33" s="59"/>
       <c r="F33" s="56">
         <v>0</v>
@@ -8209,10 +8209,10 @@
         <f t="shared" ref="B34:B47" si="1">1+B33</f>
         <v>3</v>
       </c>
-      <c r="C34" s="594" t="s">
+      <c r="C34" s="616" t="s">
         <v>102</v>
       </c>
-      <c r="D34" s="601"/>
+      <c r="D34" s="617"/>
       <c r="E34" s="59"/>
       <c r="F34" s="56">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="C35" s="600" t="s">
+      <c r="C35" s="618" t="s">
         <v>103</v>
       </c>
-      <c r="D35" s="601"/>
+      <c r="D35" s="617"/>
       <c r="E35" s="498"/>
       <c r="F35" s="68">
         <v>0</v>
@@ -8262,10 +8262,10 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="C36" s="594" t="s">
+      <c r="C36" s="616" t="s">
         <v>104</v>
       </c>
-      <c r="D36" s="601"/>
+      <c r="D36" s="617"/>
       <c r="E36" s="498"/>
       <c r="F36" s="70">
         <f>'Lease Rent'!H37</f>
@@ -8291,10 +8291,10 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="C37" s="594" t="s">
+      <c r="C37" s="616" t="s">
         <v>105</v>
       </c>
-      <c r="D37" s="601"/>
+      <c r="D37" s="617"/>
       <c r="E37" s="498"/>
       <c r="F37" s="70"/>
       <c r="G37" s="204">
@@ -8311,10 +8311,10 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="C38" s="594" t="s">
+      <c r="C38" s="616" t="s">
         <v>106</v>
       </c>
-      <c r="D38" s="601"/>
+      <c r="D38" s="617"/>
       <c r="E38" s="71"/>
       <c r="F38" s="70">
         <f>'Lease Rent'!J31</f>
@@ -8340,10 +8340,10 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="C39" s="594" t="s">
+      <c r="C39" s="616" t="s">
         <v>107</v>
       </c>
-      <c r="D39" s="601"/>
+      <c r="D39" s="617"/>
       <c r="E39" s="498"/>
       <c r="F39" s="70">
         <f>F36</f>
@@ -8369,10 +8369,10 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="C40" s="594" t="s">
+      <c r="C40" s="616" t="s">
         <v>108</v>
       </c>
-      <c r="D40" s="601"/>
+      <c r="D40" s="617"/>
       <c r="E40" s="498"/>
       <c r="F40" s="70">
         <v>0</v>
@@ -8397,10 +8397,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="C41" s="594" t="s">
+      <c r="C41" s="616" t="s">
         <v>109</v>
       </c>
-      <c r="D41" s="601"/>
+      <c r="D41" s="617"/>
       <c r="E41" s="58"/>
       <c r="F41" s="114">
         <f>F38</f>
@@ -8426,10 +8426,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="C42" s="600" t="s">
+      <c r="C42" s="618" t="s">
         <v>110</v>
       </c>
-      <c r="D42" s="601"/>
+      <c r="D42" s="617"/>
       <c r="E42" s="59"/>
       <c r="F42" s="109">
         <v>0</v>
@@ -8454,10 +8454,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="C43" s="600" t="s">
+      <c r="C43" s="618" t="s">
         <v>111</v>
       </c>
-      <c r="D43" s="601"/>
+      <c r="D43" s="617"/>
       <c r="E43" s="73"/>
       <c r="F43" s="68">
         <v>0</v>
@@ -8482,10 +8482,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="C44" s="600" t="s">
+      <c r="C44" s="618" t="s">
         <v>112</v>
       </c>
-      <c r="D44" s="601"/>
+      <c r="D44" s="617"/>
       <c r="E44" s="59"/>
       <c r="F44" s="56">
         <f>'Lease Rent'!C22</f>
@@ -8511,10 +8511,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="C45" s="594" t="s">
+      <c r="C45" s="616" t="s">
         <v>113</v>
       </c>
-      <c r="D45" s="601"/>
+      <c r="D45" s="617"/>
       <c r="E45" s="59"/>
       <c r="F45" s="109">
         <v>0</v>
@@ -8536,10 +8536,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="C46" s="600" t="s">
+      <c r="C46" s="618" t="s">
         <v>111</v>
       </c>
-      <c r="D46" s="601"/>
+      <c r="D46" s="617"/>
       <c r="E46" s="59"/>
       <c r="F46" s="56">
         <f>'Lease Rent'!D23</f>
@@ -8556,10 +8556,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="C47" s="600" t="s">
+      <c r="C47" s="618" t="s">
         <v>112</v>
       </c>
-      <c r="D47" s="601"/>
+      <c r="D47" s="617"/>
       <c r="E47" s="59"/>
       <c r="F47" s="56">
         <f>'Lease Rent'!C23</f>
@@ -8572,46 +8572,46 @@
     </row>
     <row r="48" spans="1:10" ht="28.5" customHeight="1">
       <c r="A48" s="51"/>
-      <c r="B48" s="666">
+      <c r="B48" s="663">
         <f>1+B47</f>
         <v>17</v>
       </c>
-      <c r="C48" s="594" t="s">
+      <c r="C48" s="616" t="s">
         <v>114</v>
       </c>
-      <c r="D48" s="601"/>
+      <c r="D48" s="617"/>
       <c r="E48" s="73"/>
-      <c r="F48" s="610" t="str">
+      <c r="F48" s="707" t="str">
         <f>Main!B14</f>
         <v>15% every 3 years</v>
       </c>
-      <c r="G48" s="611"/>
+      <c r="G48" s="708"/>
       <c r="H48" s="404"/>
-      <c r="I48" s="624" t="str">
+      <c r="I48" s="700" t="str">
         <f>+F48</f>
         <v>15% every 3 years</v>
       </c>
-      <c r="J48" s="625"/>
+      <c r="J48" s="701"/>
     </row>
     <row r="49" spans="1:18" ht="15.9" customHeight="1">
       <c r="A49" s="51"/>
-      <c r="B49" s="667"/>
-      <c r="C49" s="594" t="s">
+      <c r="B49" s="664"/>
+      <c r="C49" s="616" t="s">
         <v>115</v>
       </c>
-      <c r="D49" s="601"/>
+      <c r="D49" s="617"/>
       <c r="E49" s="73"/>
-      <c r="F49" s="610" t="str">
+      <c r="F49" s="707" t="str">
         <f>Main!B15</f>
         <v>5% every years</v>
       </c>
-      <c r="G49" s="611"/>
+      <c r="G49" s="708"/>
       <c r="H49" s="404"/>
-      <c r="I49" s="626" t="str">
+      <c r="I49" s="705" t="str">
         <f t="shared" ref="I49:I56" si="2">F49</f>
         <v>5% every years</v>
       </c>
-      <c r="J49" s="627"/>
+      <c r="J49" s="706"/>
     </row>
     <row r="50" spans="1:18" ht="15.9" customHeight="1">
       <c r="A50" s="51"/>
@@ -8619,22 +8619,22 @@
         <f>1+B48</f>
         <v>18</v>
       </c>
-      <c r="C50" s="600" t="s">
+      <c r="C50" s="618" t="s">
         <v>116</v>
       </c>
-      <c r="D50" s="601"/>
+      <c r="D50" s="617"/>
       <c r="E50" s="73"/>
-      <c r="F50" s="608">
+      <c r="F50" s="654">
         <f>'Lease Rent'!B31</f>
         <v>46023</v>
       </c>
-      <c r="G50" s="609"/>
+      <c r="G50" s="655"/>
       <c r="H50" s="404"/>
-      <c r="I50" s="617">
+      <c r="I50" s="656">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J50" s="618"/>
+      <c r="J50" s="657"/>
     </row>
     <row r="51" spans="1:18" ht="15.9" customHeight="1">
       <c r="A51" s="51"/>
@@ -8642,22 +8642,22 @@
         <f t="shared" ref="B51:B57" si="3">1+B50</f>
         <v>19</v>
       </c>
-      <c r="C51" s="594" t="s">
+      <c r="C51" s="616" t="s">
         <v>117</v>
       </c>
-      <c r="D51" s="601"/>
+      <c r="D51" s="617"/>
       <c r="E51" s="73"/>
-      <c r="F51" s="608">
+      <c r="F51" s="654">
         <f>'Lease Rent'!C102</f>
         <v>48213</v>
       </c>
-      <c r="G51" s="609"/>
+      <c r="G51" s="655"/>
       <c r="H51" s="404"/>
-      <c r="I51" s="617">
+      <c r="I51" s="656">
         <f>F51</f>
         <v>48213</v>
       </c>
-      <c r="J51" s="618"/>
+      <c r="J51" s="657"/>
     </row>
     <row r="52" spans="1:18" ht="15.9" customHeight="1">
       <c r="A52" s="51"/>
@@ -8665,22 +8665,22 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="C52" s="594" t="s">
+      <c r="C52" s="616" t="s">
         <v>118</v>
       </c>
-      <c r="D52" s="595"/>
+      <c r="D52" s="626"/>
       <c r="E52" s="73"/>
-      <c r="F52" s="608">
+      <c r="F52" s="654">
         <f>F50</f>
         <v>46023</v>
       </c>
-      <c r="G52" s="609"/>
+      <c r="G52" s="655"/>
       <c r="H52" s="404"/>
-      <c r="I52" s="617">
+      <c r="I52" s="656">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J52" s="618"/>
+      <c r="J52" s="657"/>
     </row>
     <row r="53" spans="1:18" ht="15.9" customHeight="1">
       <c r="A53" s="51"/>
@@ -8688,21 +8688,21 @@
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="C53" s="594" t="s">
+      <c r="C53" s="616" t="s">
         <v>119</v>
       </c>
-      <c r="D53" s="595"/>
+      <c r="D53" s="626"/>
       <c r="E53" s="73"/>
-      <c r="F53" s="590">
-        <v>0</v>
-      </c>
-      <c r="G53" s="591"/>
+      <c r="F53" s="624">
+        <v>0</v>
+      </c>
+      <c r="G53" s="658"/>
       <c r="H53" s="404"/>
-      <c r="I53" s="592">
+      <c r="I53" s="659">
         <f>+F53</f>
         <v>0</v>
       </c>
-      <c r="J53" s="593"/>
+      <c r="J53" s="660"/>
     </row>
     <row r="54" spans="1:18" ht="15.9" customHeight="1">
       <c r="A54" s="51"/>
@@ -8710,10 +8710,10 @@
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="C54" s="600" t="s">
+      <c r="C54" s="618" t="s">
         <v>120</v>
       </c>
-      <c r="D54" s="601"/>
+      <c r="D54" s="617"/>
       <c r="E54" s="58"/>
       <c r="F54" s="56">
         <f>(F51-F50)/365*12</f>
@@ -8740,10 +8740,10 @@
         <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="C55" s="600" t="s">
+      <c r="C55" s="618" t="s">
         <v>121</v>
       </c>
-      <c r="D55" s="601"/>
+      <c r="D55" s="617"/>
       <c r="E55" s="71"/>
       <c r="F55" s="56">
         <v>0</v>
@@ -8769,10 +8769,10 @@
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="C56" s="600" t="s">
+      <c r="C56" s="618" t="s">
         <v>122</v>
       </c>
-      <c r="D56" s="601"/>
+      <c r="D56" s="617"/>
       <c r="E56" s="71"/>
       <c r="F56" s="302" t="s">
         <v>68</v>
@@ -8798,10 +8798,10 @@
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="C57" s="600" t="s">
+      <c r="C57" s="618" t="s">
         <v>123</v>
       </c>
-      <c r="D57" s="601"/>
+      <c r="D57" s="617"/>
       <c r="E57" s="71"/>
       <c r="F57" s="56"/>
       <c r="G57" s="388"/>
@@ -8816,23 +8816,23 @@
       <c r="C58" s="74"/>
       <c r="D58" s="74"/>
       <c r="E58" s="58"/>
-      <c r="F58" s="590" t="s">
+      <c r="F58" s="624" t="s">
         <v>73</v>
       </c>
-      <c r="G58" s="591"/>
+      <c r="G58" s="658"/>
       <c r="H58" s="404"/>
-      <c r="I58" s="592" t="s">
+      <c r="I58" s="659" t="s">
         <v>67</v>
       </c>
-      <c r="J58" s="593"/>
+      <c r="J58" s="660"/>
     </row>
     <row r="59" spans="1:18" ht="15.9" customHeight="1">
       <c r="A59" s="51"/>
-      <c r="B59" s="664" t="s">
+      <c r="B59" s="661" t="s">
         <v>124</v>
       </c>
-      <c r="C59" s="665"/>
-      <c r="D59" s="665"/>
+      <c r="C59" s="662"/>
+      <c r="D59" s="662"/>
       <c r="E59" s="497"/>
       <c r="F59" s="376" t="s">
         <v>75</v>
@@ -8853,10 +8853,10 @@
       <c r="B60" s="162">
         <v>1</v>
       </c>
-      <c r="C60" s="594" t="s">
+      <c r="C60" s="616" t="s">
         <v>125</v>
       </c>
-      <c r="D60" s="601"/>
+      <c r="D60" s="617"/>
       <c r="E60" s="499"/>
       <c r="F60" s="70">
         <f>C220/F21/F54</f>
@@ -8882,10 +8882,10 @@
         <f>1+B60</f>
         <v>2</v>
       </c>
-      <c r="C61" s="594" t="s">
+      <c r="C61" s="616" t="s">
         <v>126</v>
       </c>
-      <c r="D61" s="601"/>
+      <c r="D61" s="617"/>
       <c r="E61" s="499"/>
       <c r="F61" s="70">
         <v>0</v>
@@ -8909,10 +8909,10 @@
         <f t="shared" ref="B62:B83" si="4">1+B61</f>
         <v>3</v>
       </c>
-      <c r="C62" s="596" t="s">
+      <c r="C62" s="619" t="s">
         <v>127</v>
       </c>
-      <c r="D62" s="597"/>
+      <c r="D62" s="620"/>
       <c r="E62" s="75"/>
       <c r="F62" s="76">
         <f>F60+F61</f>
@@ -8938,10 +8938,10 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="C63" s="594" t="s">
+      <c r="C63" s="616" t="s">
         <v>321</v>
       </c>
-      <c r="D63" s="601"/>
+      <c r="D63" s="617"/>
       <c r="E63" s="56"/>
       <c r="F63" s="54">
         <f>F62*F21</f>
@@ -8967,10 +8967,10 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="C64" s="594" t="s">
+      <c r="C64" s="616" t="s">
         <v>128</v>
       </c>
-      <c r="D64" s="601"/>
+      <c r="D64" s="617"/>
       <c r="E64" s="56"/>
       <c r="F64" s="70">
         <f>I220/F21/F54</f>
@@ -8996,10 +8996,10 @@
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="C65" s="600" t="s">
+      <c r="C65" s="618" t="s">
         <v>322</v>
       </c>
-      <c r="D65" s="601"/>
+      <c r="D65" s="617"/>
       <c r="E65" s="71"/>
       <c r="F65" s="54">
         <f>+F64*F21</f>
@@ -9025,10 +9025,10 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="C66" s="600" t="s">
+      <c r="C66" s="618" t="s">
         <v>323</v>
       </c>
-      <c r="D66" s="601"/>
+      <c r="D66" s="617"/>
       <c r="E66" s="59"/>
       <c r="F66" s="56">
         <f>(+G220/F54)</f>
@@ -9054,10 +9054,10 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="C67" s="600" t="s">
+      <c r="C67" s="618" t="s">
         <v>129</v>
       </c>
-      <c r="D67" s="601"/>
+      <c r="D67" s="617"/>
       <c r="E67" s="56"/>
       <c r="F67" s="56">
         <f>Main!B9</f>
@@ -9083,10 +9083,10 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="C68" s="600" t="s">
+      <c r="C68" s="618" t="s">
         <v>130</v>
       </c>
-      <c r="D68" s="601"/>
+      <c r="D68" s="617"/>
       <c r="E68" s="56"/>
       <c r="F68" s="56">
         <v>0</v>
@@ -9111,10 +9111,10 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="C69" s="594" t="s">
+      <c r="C69" s="616" t="s">
         <v>131</v>
       </c>
-      <c r="D69" s="601"/>
+      <c r="D69" s="617"/>
       <c r="E69" s="56"/>
       <c r="F69" s="56">
         <v>500000</v>
@@ -9139,10 +9139,10 @@
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="C70" s="600" t="s">
+      <c r="C70" s="618" t="s">
         <v>132</v>
       </c>
-      <c r="D70" s="601"/>
+      <c r="D70" s="617"/>
       <c r="E70" s="56"/>
       <c r="F70" s="54">
         <v>0</v>
@@ -9164,10 +9164,10 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="C71" s="600" t="s">
+      <c r="C71" s="618" t="s">
         <v>133</v>
       </c>
-      <c r="D71" s="601"/>
+      <c r="D71" s="617"/>
       <c r="E71" s="56"/>
       <c r="F71" s="54">
         <f>F38*F23*F33</f>
@@ -9193,10 +9193,10 @@
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="C72" s="600" t="s">
+      <c r="C72" s="618" t="s">
         <v>134</v>
       </c>
-      <c r="D72" s="601"/>
+      <c r="D72" s="617"/>
       <c r="E72" s="56"/>
       <c r="F72" s="56">
         <v>0</v>
@@ -9221,10 +9221,10 @@
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="C73" s="594" t="s">
+      <c r="C73" s="616" t="s">
         <v>135</v>
       </c>
-      <c r="D73" s="601"/>
+      <c r="D73" s="617"/>
       <c r="E73" s="498"/>
       <c r="F73" s="68">
         <f>+F35*F63</f>
@@ -9278,10 +9278,10 @@
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="C75" s="594" t="s">
+      <c r="C75" s="616" t="s">
         <v>137</v>
       </c>
-      <c r="D75" s="601"/>
+      <c r="D75" s="617"/>
       <c r="E75" s="59"/>
       <c r="F75" s="56">
         <f>+F77/F23</f>
@@ -9307,10 +9307,10 @@
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="C76" s="594" t="s">
+      <c r="C76" s="616" t="s">
         <v>138</v>
       </c>
-      <c r="D76" s="601"/>
+      <c r="D76" s="617"/>
       <c r="E76" s="71"/>
       <c r="F76" s="51"/>
       <c r="G76" s="493"/>
@@ -9330,10 +9330,10 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="C77" s="594" t="s">
+      <c r="C77" s="616" t="s">
         <v>139</v>
       </c>
-      <c r="D77" s="601"/>
+      <c r="D77" s="617"/>
       <c r="E77" s="71"/>
       <c r="F77" s="56">
         <f>'CAPEX and PM'!B6</f>
@@ -9359,10 +9359,10 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="C78" s="594" t="s">
+      <c r="C78" s="616" t="s">
         <v>140</v>
       </c>
-      <c r="D78" s="601"/>
+      <c r="D78" s="617"/>
       <c r="E78" s="71"/>
       <c r="F78" s="56">
         <f>'CAPEX and PM'!B37</f>
@@ -9388,10 +9388,10 @@
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="C79" s="594" t="s">
+      <c r="C79" s="616" t="s">
         <v>141</v>
       </c>
-      <c r="D79" s="601"/>
+      <c r="D79" s="617"/>
       <c r="E79" s="71"/>
       <c r="F79" s="56">
         <f>+'CAPEX and PM'!B95</f>
@@ -9417,10 +9417,10 @@
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="C80" s="594" t="s">
+      <c r="C80" s="616" t="s">
         <v>142</v>
       </c>
-      <c r="D80" s="601"/>
+      <c r="D80" s="617"/>
       <c r="E80" s="71"/>
       <c r="F80" s="56"/>
       <c r="G80" s="388"/>
@@ -9440,10 +9440,10 @@
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="C81" s="594" t="s">
+      <c r="C81" s="616" t="s">
         <v>143</v>
       </c>
-      <c r="D81" s="595"/>
+      <c r="D81" s="626"/>
       <c r="E81" s="71"/>
       <c r="F81" s="56"/>
       <c r="G81" s="388"/>
@@ -9463,10 +9463,10 @@
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="C82" s="594" t="s">
+      <c r="C82" s="616" t="s">
         <v>144</v>
       </c>
-      <c r="D82" s="601"/>
+      <c r="D82" s="617"/>
       <c r="E82" s="59"/>
       <c r="F82" s="56">
         <f>+G207</f>
@@ -9492,10 +9492,10 @@
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="C83" s="594" t="s">
+      <c r="C83" s="616" t="s">
         <v>324</v>
       </c>
-      <c r="D83" s="601"/>
+      <c r="D83" s="617"/>
       <c r="E83" s="498"/>
       <c r="F83" s="56">
         <f>+F30</f>
@@ -9528,11 +9528,11 @@
     </row>
     <row r="85" spans="1:24" ht="15.9" customHeight="1">
       <c r="A85" s="51"/>
-      <c r="B85" s="602" t="s">
+      <c r="B85" s="638" t="s">
         <v>145</v>
       </c>
-      <c r="C85" s="603"/>
-      <c r="D85" s="604"/>
+      <c r="C85" s="639"/>
+      <c r="D85" s="640"/>
       <c r="E85" s="389"/>
       <c r="F85" s="161" t="s">
         <v>75</v>
@@ -9553,10 +9553,10 @@
       <c r="B86" s="162">
         <v>1</v>
       </c>
-      <c r="C86" s="594" t="s">
+      <c r="C86" s="616" t="s">
         <v>146</v>
       </c>
-      <c r="D86" s="601"/>
+      <c r="D86" s="617"/>
       <c r="E86" s="71"/>
       <c r="F86" s="70">
         <f>+F62</f>
@@ -9585,10 +9585,10 @@
         <f>1+B86</f>
         <v>2</v>
       </c>
-      <c r="C87" s="600" t="s">
+      <c r="C87" s="618" t="s">
         <v>147</v>
       </c>
-      <c r="D87" s="601"/>
+      <c r="D87" s="617"/>
       <c r="E87" s="73"/>
       <c r="F87" s="56">
         <v>0</v>
@@ -9611,10 +9611,10 @@
         <f t="shared" ref="B88:B94" si="7">+B87+1</f>
         <v>3</v>
       </c>
-      <c r="C88" s="600" t="s">
+      <c r="C88" s="618" t="s">
         <v>148</v>
       </c>
-      <c r="D88" s="601"/>
+      <c r="D88" s="617"/>
       <c r="E88" s="73"/>
       <c r="F88" s="70">
         <f>(F66/F23)</f>
@@ -9642,10 +9642,10 @@
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="C89" s="600" t="s">
+      <c r="C89" s="618" t="s">
         <v>149</v>
       </c>
-      <c r="D89" s="601"/>
+      <c r="D89" s="617"/>
       <c r="E89" s="73"/>
       <c r="F89" s="66">
         <f>'Security Deposit'!C17</f>
@@ -9673,10 +9673,10 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="C90" s="600" t="s">
+      <c r="C90" s="618" t="s">
         <v>289</v>
       </c>
-      <c r="D90" s="601"/>
+      <c r="D90" s="617"/>
       <c r="E90" s="73"/>
       <c r="F90" s="202">
         <f>+F64</f>
@@ -9704,10 +9704,10 @@
         <f>+B89+1</f>
         <v>5</v>
       </c>
-      <c r="C91" s="600" t="s">
+      <c r="C91" s="618" t="s">
         <v>150</v>
       </c>
-      <c r="D91" s="601"/>
+      <c r="D91" s="617"/>
       <c r="E91" s="73"/>
       <c r="F91" s="66">
         <f>(+F83/F21/F54)</f>
@@ -9734,10 +9734,10 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="C92" s="600" t="s">
+      <c r="C92" s="618" t="s">
         <v>151</v>
       </c>
-      <c r="D92" s="601"/>
+      <c r="D92" s="617"/>
       <c r="E92" s="73"/>
       <c r="F92" s="66">
         <f>F82/F21/F54</f>
@@ -9765,10 +9765,10 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="C93" s="594" t="s">
+      <c r="C93" s="616" t="s">
         <v>152</v>
       </c>
-      <c r="D93" s="601"/>
+      <c r="D93" s="617"/>
       <c r="E93" s="71"/>
       <c r="F93" s="66">
         <f>+G93/F6</f>
@@ -9796,10 +9796,10 @@
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="C94" s="596" t="s">
+      <c r="C94" s="619" t="s">
         <v>69</v>
       </c>
-      <c r="D94" s="597"/>
+      <c r="D94" s="620"/>
       <c r="E94" s="78"/>
       <c r="F94" s="213">
         <f>SUM(F86:F93)</f>
@@ -9824,8 +9824,8 @@
     <row r="95" spans="1:24" ht="15.9" customHeight="1">
       <c r="A95" s="51"/>
       <c r="B95" s="381"/>
-      <c r="C95" s="591"/>
-      <c r="D95" s="591"/>
+      <c r="C95" s="658"/>
+      <c r="D95" s="658"/>
       <c r="E95" s="84"/>
       <c r="F95" s="85"/>
       <c r="G95" s="85"/>
@@ -9835,11 +9835,11 @@
     </row>
     <row r="96" spans="1:24" ht="15.9" customHeight="1">
       <c r="A96" s="51"/>
-      <c r="B96" s="598" t="s">
+      <c r="B96" s="621" t="s">
         <v>153</v>
       </c>
-      <c r="C96" s="599"/>
-      <c r="D96" s="599"/>
+      <c r="C96" s="622"/>
+      <c r="D96" s="622"/>
       <c r="E96" s="87"/>
       <c r="F96" s="161" t="s">
         <v>75</v>
@@ -9861,11 +9861,11 @@
       <c r="B97" s="162">
         <v>1</v>
       </c>
-      <c r="C97" s="600" t="str">
+      <c r="C97" s="618" t="str">
         <f>+C76</f>
         <v>Siemens Standard Fitout (Existing)</v>
       </c>
-      <c r="D97" s="601"/>
+      <c r="D97" s="617"/>
       <c r="E97" s="88"/>
       <c r="F97" s="66">
         <v>0</v>
@@ -9891,11 +9891,11 @@
         <f t="shared" ref="B98:B103" si="8">+B97+1</f>
         <v>2</v>
       </c>
-      <c r="C98" s="600" t="str">
+      <c r="C98" s="618" t="str">
         <f>+C77</f>
         <v>Siemens Standard Fitout (New)</v>
       </c>
-      <c r="D98" s="601"/>
+      <c r="D98" s="617"/>
       <c r="E98" s="71"/>
       <c r="F98" s="66">
         <f>'CAPEX and PM'!B29</f>
@@ -9923,11 +9923,11 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="C99" s="600" t="str">
+      <c r="C99" s="618" t="str">
         <f>+C78</f>
         <v>Capex over the period of lease period</v>
       </c>
-      <c r="D99" s="601"/>
+      <c r="D99" s="617"/>
       <c r="E99" s="71"/>
       <c r="F99" s="66">
         <f>'CAPEX and PM'!B89</f>
@@ -9955,11 +9955,11 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="C100" s="600" t="str">
+      <c r="C100" s="618" t="str">
         <f>+C79</f>
         <v>PM cost over the period of lease period</v>
       </c>
-      <c r="D100" s="601"/>
+      <c r="D100" s="617"/>
       <c r="E100" s="71"/>
       <c r="F100" s="66">
         <f>+'CAPEX and PM'!B96</f>
@@ -9987,11 +9987,11 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="C101" s="600" t="str">
+      <c r="C101" s="618" t="str">
         <f>+C80</f>
         <v>Asset Retirement Obligation ( Removal &amp; Restoration Obligation)</v>
       </c>
-      <c r="D101" s="601"/>
+      <c r="D101" s="617"/>
       <c r="E101" s="71"/>
       <c r="F101" s="66">
         <f>'Security Deposit'!D25</f>
@@ -10022,10 +10022,10 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="C102" s="594" t="s">
+      <c r="C102" s="616" t="s">
         <v>154</v>
       </c>
-      <c r="D102" s="601"/>
+      <c r="D102" s="617"/>
       <c r="E102" s="73"/>
       <c r="F102" s="66">
         <f>+F81/F21/F27</f>
@@ -10053,10 +10053,10 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="C103" s="596" t="s">
+      <c r="C103" s="619" t="s">
         <v>155</v>
       </c>
-      <c r="D103" s="597"/>
+      <c r="D103" s="620"/>
       <c r="E103" s="78"/>
       <c r="F103" s="54">
         <f>SUM(F97:F102)</f>
@@ -10093,11 +10093,11 @@
     </row>
     <row r="105" spans="1:26" ht="15.9" customHeight="1">
       <c r="A105" s="51"/>
-      <c r="B105" s="605" t="s">
+      <c r="B105" s="710" t="s">
         <v>156</v>
       </c>
-      <c r="C105" s="606"/>
-      <c r="D105" s="606"/>
+      <c r="C105" s="633"/>
+      <c r="D105" s="633"/>
       <c r="E105" s="87"/>
       <c r="F105" s="161" t="s">
         <v>75</v>
@@ -10118,10 +10118,10 @@
       <c r="B106" s="162">
         <v>1</v>
       </c>
-      <c r="C106" s="594" t="s">
+      <c r="C106" s="616" t="s">
         <v>69</v>
       </c>
-      <c r="D106" s="601"/>
+      <c r="D106" s="617"/>
       <c r="E106" s="71"/>
       <c r="F106" s="56">
         <f>+F94</f>
@@ -10149,10 +10149,10 @@
         <f>+B106+1</f>
         <v>2</v>
       </c>
-      <c r="C107" s="594" t="s">
+      <c r="C107" s="616" t="s">
         <v>155</v>
       </c>
-      <c r="D107" s="595"/>
+      <c r="D107" s="626"/>
       <c r="E107" s="71"/>
       <c r="F107" s="56">
         <f>+F103</f>
@@ -10180,10 +10180,10 @@
         <f>+B107+1</f>
         <v>3</v>
       </c>
-      <c r="C108" s="596" t="s">
+      <c r="C108" s="619" t="s">
         <v>157</v>
       </c>
-      <c r="D108" s="597"/>
+      <c r="D108" s="620"/>
       <c r="E108" s="78"/>
       <c r="F108" s="54">
         <f>SUM(F106:F107)</f>
@@ -10212,11 +10212,11 @@
     </row>
     <row r="109" spans="1:26" ht="15.9" customHeight="1">
       <c r="A109" s="51"/>
-      <c r="B109" s="598" t="s">
+      <c r="B109" s="621" t="s">
         <v>158</v>
       </c>
-      <c r="C109" s="599"/>
-      <c r="D109" s="599"/>
+      <c r="C109" s="622"/>
+      <c r="D109" s="622"/>
       <c r="E109" s="89"/>
       <c r="F109" s="161" t="s">
         <v>75</v>
@@ -10238,10 +10238,10 @@
       <c r="B110" s="249">
         <v>1</v>
       </c>
-      <c r="C110" s="594" t="s">
+      <c r="C110" s="616" t="s">
         <v>159</v>
       </c>
-      <c r="D110" s="595"/>
+      <c r="D110" s="626"/>
       <c r="E110" s="83"/>
       <c r="F110" s="376"/>
       <c r="G110" s="376"/>
@@ -10255,10 +10255,10 @@
         <f t="shared" ref="B111:B119" si="9">1+B110</f>
         <v>2</v>
       </c>
-      <c r="C111" s="594" t="s">
+      <c r="C111" s="616" t="s">
         <v>160</v>
       </c>
-      <c r="D111" s="595"/>
+      <c r="D111" s="626"/>
       <c r="E111" s="83"/>
       <c r="F111" s="376"/>
       <c r="G111" s="376"/>
@@ -10274,10 +10274,10 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="C112" s="594" t="s">
+      <c r="C112" s="616" t="s">
         <v>161</v>
       </c>
-      <c r="D112" s="595"/>
+      <c r="D112" s="626"/>
       <c r="E112" s="83"/>
       <c r="F112" s="388">
         <f>+F64*0</f>
@@ -10305,10 +10305,10 @@
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="C113" s="594" t="s">
+      <c r="C113" s="616" t="s">
         <v>162</v>
       </c>
-      <c r="D113" s="595"/>
+      <c r="D113" s="626"/>
       <c r="E113" s="83"/>
       <c r="F113" s="376"/>
       <c r="G113" s="376"/>
@@ -10322,10 +10322,10 @@
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="C114" s="594" t="s">
+      <c r="C114" s="616" t="s">
         <v>163</v>
       </c>
-      <c r="D114" s="595"/>
+      <c r="D114" s="626"/>
       <c r="E114" s="83"/>
       <c r="F114" s="376"/>
       <c r="G114" s="376"/>
@@ -10339,10 +10339,10 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="C115" s="594" t="s">
+      <c r="C115" s="616" t="s">
         <v>164</v>
       </c>
-      <c r="D115" s="595"/>
+      <c r="D115" s="626"/>
       <c r="E115" s="83"/>
       <c r="F115" s="376"/>
       <c r="G115" s="376"/>
@@ -10356,10 +10356,10 @@
         <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="C116" s="594" t="s">
+      <c r="C116" s="616" t="s">
         <v>165</v>
       </c>
-      <c r="D116" s="595"/>
+      <c r="D116" s="626"/>
       <c r="E116" s="83"/>
       <c r="F116" s="376"/>
       <c r="G116" s="376"/>
@@ -10373,10 +10373,10 @@
         <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="C117" s="594" t="s">
+      <c r="C117" s="616" t="s">
         <v>166</v>
       </c>
-      <c r="D117" s="601"/>
+      <c r="D117" s="617"/>
       <c r="E117" s="252"/>
       <c r="F117" s="360">
         <v>654</v>
@@ -10402,10 +10402,10 @@
         <f t="shared" si="9"/>
         <v>9</v>
       </c>
-      <c r="C118" s="594" t="s">
+      <c r="C118" s="616" t="s">
         <v>167</v>
       </c>
-      <c r="D118" s="595"/>
+      <c r="D118" s="626"/>
       <c r="E118" s="252"/>
       <c r="F118" s="90"/>
       <c r="G118" s="90">
@@ -10428,10 +10428,10 @@
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="C119" s="596" t="s">
+      <c r="C119" s="619" t="s">
         <v>168</v>
       </c>
-      <c r="D119" s="597"/>
+      <c r="D119" s="620"/>
       <c r="E119" s="253"/>
       <c r="F119" s="54">
         <f>SUM(F110:F118)</f>
@@ -10457,8 +10457,8 @@
     <row r="120" spans="1:26" ht="15.9" customHeight="1">
       <c r="A120" s="77"/>
       <c r="B120" s="162"/>
-      <c r="C120" s="590"/>
-      <c r="D120" s="607"/>
+      <c r="C120" s="624"/>
+      <c r="D120" s="625"/>
       <c r="E120" s="78"/>
       <c r="F120" s="54"/>
       <c r="G120" s="385"/>
@@ -10472,11 +10472,11 @@
     </row>
     <row r="121" spans="1:26" ht="15.9" customHeight="1">
       <c r="A121" s="77"/>
-      <c r="B121" s="598" t="s">
+      <c r="B121" s="621" t="s">
         <v>169</v>
       </c>
-      <c r="C121" s="599"/>
-      <c r="D121" s="599"/>
+      <c r="C121" s="622"/>
+      <c r="D121" s="622"/>
       <c r="E121" s="89"/>
       <c r="F121" s="161" t="s">
         <v>75</v>
@@ -10499,10 +10499,10 @@
       <c r="B122" s="251">
         <v>1</v>
       </c>
-      <c r="C122" s="594" t="s">
+      <c r="C122" s="616" t="s">
         <v>170</v>
       </c>
-      <c r="D122" s="595"/>
+      <c r="D122" s="626"/>
       <c r="E122" s="78"/>
       <c r="F122" s="54"/>
       <c r="G122" s="385"/>
@@ -10515,10 +10515,10 @@
       <c r="B123" s="162">
         <v>2</v>
       </c>
-      <c r="C123" s="596" t="s">
+      <c r="C123" s="619" t="s">
         <v>171</v>
       </c>
-      <c r="D123" s="597"/>
+      <c r="D123" s="620"/>
       <c r="E123" s="78"/>
       <c r="F123" s="54">
         <f>SUM(F122)</f>
@@ -10541,8 +10541,8 @@
     <row r="124" spans="1:26" ht="15.9" customHeight="1">
       <c r="A124" s="77"/>
       <c r="B124" s="162"/>
-      <c r="C124" s="590"/>
-      <c r="D124" s="607"/>
+      <c r="C124" s="624"/>
+      <c r="D124" s="625"/>
       <c r="E124" s="63"/>
       <c r="F124" s="54"/>
       <c r="G124" s="385"/>
@@ -10552,11 +10552,11 @@
     </row>
     <row r="125" spans="1:26" ht="15.9" customHeight="1">
       <c r="A125" s="77"/>
-      <c r="B125" s="598" t="s">
+      <c r="B125" s="621" t="s">
         <v>172</v>
       </c>
-      <c r="C125" s="599"/>
-      <c r="D125" s="599"/>
+      <c r="C125" s="622"/>
+      <c r="D125" s="622"/>
       <c r="E125" s="89"/>
       <c r="F125" s="161" t="s">
         <v>75</v>
@@ -10577,10 +10577,10 @@
       <c r="B126" s="249">
         <v>1</v>
       </c>
-      <c r="C126" s="594" t="s">
+      <c r="C126" s="616" t="s">
         <v>173</v>
       </c>
-      <c r="D126" s="595"/>
+      <c r="D126" s="626"/>
       <c r="E126" s="250"/>
       <c r="F126" s="385"/>
       <c r="G126" s="385"/>
@@ -10594,10 +10594,10 @@
         <f>1+B126</f>
         <v>2</v>
       </c>
-      <c r="C127" s="594" t="s">
+      <c r="C127" s="616" t="s">
         <v>174</v>
       </c>
-      <c r="D127" s="595"/>
+      <c r="D127" s="626"/>
       <c r="E127" s="250"/>
       <c r="F127" s="385"/>
       <c r="G127" s="385"/>
@@ -10611,10 +10611,10 @@
         <f>1+B127</f>
         <v>3</v>
       </c>
-      <c r="C128" s="594" t="s">
+      <c r="C128" s="616" t="s">
         <v>175</v>
       </c>
-      <c r="D128" s="595"/>
+      <c r="D128" s="626"/>
       <c r="E128" s="250"/>
       <c r="F128" s="385"/>
       <c r="G128" s="385"/>
@@ -10628,10 +10628,10 @@
         <f>1+B128</f>
         <v>4</v>
       </c>
-      <c r="C129" s="594" t="s">
+      <c r="C129" s="616" t="s">
         <v>176</v>
       </c>
-      <c r="D129" s="595"/>
+      <c r="D129" s="626"/>
       <c r="E129" s="250"/>
       <c r="F129" s="385"/>
       <c r="G129" s="385"/>
@@ -10645,10 +10645,10 @@
         <f>1+B129</f>
         <v>5</v>
       </c>
-      <c r="C130" s="594" t="s">
+      <c r="C130" s="616" t="s">
         <v>177</v>
       </c>
-      <c r="D130" s="595"/>
+      <c r="D130" s="626"/>
       <c r="E130" s="250"/>
       <c r="F130" s="385"/>
       <c r="G130" s="385"/>
@@ -10662,10 +10662,10 @@
         <f>1+B130</f>
         <v>6</v>
       </c>
-      <c r="C131" s="594" t="s">
+      <c r="C131" s="616" t="s">
         <v>178</v>
       </c>
-      <c r="D131" s="595"/>
+      <c r="D131" s="626"/>
       <c r="E131" s="250"/>
       <c r="F131" s="385"/>
       <c r="G131" s="385"/>
@@ -10678,10 +10678,10 @@
       <c r="B132" s="381">
         <v>7</v>
       </c>
-      <c r="C132" s="596" t="s">
+      <c r="C132" s="619" t="s">
         <v>179</v>
       </c>
-      <c r="D132" s="597"/>
+      <c r="D132" s="620"/>
       <c r="E132" s="250"/>
       <c r="F132" s="385">
         <f>SUM(F126:F131)</f>
@@ -10704,8 +10704,8 @@
     <row r="133" spans="1:20" ht="15.9" customHeight="1">
       <c r="A133" s="77"/>
       <c r="B133" s="162"/>
-      <c r="C133" s="591"/>
-      <c r="D133" s="607"/>
+      <c r="C133" s="658"/>
+      <c r="D133" s="625"/>
       <c r="E133" s="250"/>
       <c r="F133" s="385"/>
       <c r="G133" s="385"/>
@@ -10715,11 +10715,11 @@
     </row>
     <row r="134" spans="1:20" ht="15.9" customHeight="1">
       <c r="A134" s="51"/>
-      <c r="B134" s="598" t="s">
+      <c r="B134" s="621" t="s">
         <v>180</v>
       </c>
-      <c r="C134" s="599"/>
-      <c r="D134" s="599"/>
+      <c r="C134" s="622"/>
+      <c r="D134" s="622"/>
       <c r="E134" s="89"/>
       <c r="F134" s="161" t="s">
         <v>75</v>
@@ -10740,10 +10740,10 @@
       <c r="B135" s="162">
         <v>1</v>
       </c>
-      <c r="C135" s="596" t="s">
+      <c r="C135" s="619" t="s">
         <v>181</v>
       </c>
-      <c r="D135" s="597"/>
+      <c r="D135" s="620"/>
       <c r="E135" s="78"/>
       <c r="F135" s="54">
         <f>F119+F108+F123+F132</f>
@@ -10768,8 +10768,8 @@
     <row r="136" spans="1:20" ht="15.9" customHeight="1">
       <c r="A136" s="77"/>
       <c r="B136" s="162"/>
-      <c r="C136" s="590"/>
-      <c r="D136" s="607"/>
+      <c r="C136" s="624"/>
+      <c r="D136" s="625"/>
       <c r="E136" s="78"/>
       <c r="F136" s="54"/>
       <c r="G136" s="385"/>
@@ -10783,23 +10783,23 @@
       <c r="C137" s="380"/>
       <c r="D137" s="377"/>
       <c r="E137" s="167"/>
-      <c r="F137" s="590" t="s">
+      <c r="F137" s="624" t="s">
         <v>73</v>
       </c>
-      <c r="G137" s="591"/>
+      <c r="G137" s="658"/>
       <c r="H137" s="404"/>
-      <c r="I137" s="592" t="s">
+      <c r="I137" s="659" t="s">
         <v>67</v>
       </c>
-      <c r="J137" s="593"/>
+      <c r="J137" s="660"/>
     </row>
     <row r="138" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A138" s="51"/>
-      <c r="B138" s="598" t="s">
+      <c r="B138" s="621" t="s">
         <v>182</v>
       </c>
-      <c r="C138" s="599"/>
-      <c r="D138" s="614"/>
+      <c r="C138" s="622"/>
+      <c r="D138" s="623"/>
       <c r="E138" s="161"/>
       <c r="F138" s="161" t="s">
         <v>75</v>
@@ -10818,8 +10818,8 @@
     <row r="139" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A139" s="51"/>
       <c r="B139" s="91"/>
-      <c r="C139" s="615"/>
-      <c r="D139" s="616"/>
+      <c r="C139" s="627"/>
+      <c r="D139" s="628"/>
       <c r="E139" s="163"/>
       <c r="F139" s="54"/>
       <c r="G139" s="385"/>
@@ -10830,10 +10830,10 @@
     <row r="140" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A140" s="51"/>
       <c r="B140" s="91"/>
-      <c r="C140" s="594" t="s">
+      <c r="C140" s="616" t="s">
         <v>183</v>
       </c>
-      <c r="D140" s="601"/>
+      <c r="D140" s="617"/>
       <c r="E140" s="58"/>
       <c r="F140" s="243">
         <f>F21</f>
@@ -10856,10 +10856,10 @@
     <row r="141" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A141" s="51"/>
       <c r="B141" s="91"/>
-      <c r="C141" s="600" t="s">
+      <c r="C141" s="618" t="s">
         <v>184</v>
       </c>
-      <c r="D141" s="601"/>
+      <c r="D141" s="617"/>
       <c r="E141" s="59"/>
       <c r="F141" s="56">
         <f>F24</f>
@@ -10882,10 +10882,10 @@
     <row r="142" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A142" s="51"/>
       <c r="B142" s="91"/>
-      <c r="C142" s="600" t="s">
+      <c r="C142" s="618" t="s">
         <v>185</v>
       </c>
-      <c r="D142" s="601"/>
+      <c r="D142" s="617"/>
       <c r="E142" s="73"/>
       <c r="F142" s="56" t="e">
         <f>+#REF!</f>
@@ -10908,10 +10908,10 @@
     <row r="143" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A143" s="51"/>
       <c r="B143" s="91"/>
-      <c r="C143" s="594" t="s">
+      <c r="C143" s="616" t="s">
         <v>186</v>
       </c>
-      <c r="D143" s="601"/>
+      <c r="D143" s="617"/>
       <c r="E143" s="73"/>
       <c r="F143" s="56">
         <f>F108</f>
@@ -10934,10 +10934,10 @@
     <row r="144" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A144" s="51"/>
       <c r="B144" s="91"/>
-      <c r="C144" s="685" t="s">
+      <c r="C144" s="646" t="s">
         <v>187</v>
       </c>
-      <c r="D144" s="686"/>
+      <c r="D144" s="647"/>
       <c r="E144" s="92"/>
       <c r="F144" s="93">
         <f>F119</f>
@@ -10960,10 +10960,10 @@
     <row r="145" spans="1:10" ht="15.9" hidden="1" customHeight="1">
       <c r="A145" s="77"/>
       <c r="B145" s="162"/>
-      <c r="C145" s="596" t="s">
+      <c r="C145" s="619" t="s">
         <v>188</v>
       </c>
-      <c r="D145" s="597"/>
+      <c r="D145" s="620"/>
       <c r="E145" s="78"/>
       <c r="F145" s="245" t="e">
         <f>F135*#REF!</f>
@@ -10997,11 +10997,11 @@
     </row>
     <row r="147" spans="1:10" ht="15.9" customHeight="1">
       <c r="A147" s="77"/>
-      <c r="B147" s="598" t="s">
+      <c r="B147" s="621" t="s">
         <v>189</v>
       </c>
-      <c r="C147" s="599"/>
-      <c r="D147" s="614"/>
+      <c r="C147" s="622"/>
+      <c r="D147" s="623"/>
       <c r="E147" s="379"/>
       <c r="F147" s="379" t="s">
         <v>190</v>
@@ -11020,8 +11020,8 @@
     <row r="148" spans="1:10" ht="15.9" customHeight="1">
       <c r="A148" s="51"/>
       <c r="B148" s="99"/>
-      <c r="C148" s="615"/>
-      <c r="D148" s="616"/>
+      <c r="C148" s="627"/>
+      <c r="D148" s="628"/>
       <c r="E148" s="100"/>
       <c r="F148" s="101"/>
       <c r="G148" s="209"/>
@@ -11032,10 +11032,10 @@
     <row r="149" spans="1:10" ht="15.9" customHeight="1">
       <c r="A149" s="51"/>
       <c r="B149" s="99"/>
-      <c r="C149" s="600" t="s">
+      <c r="C149" s="618" t="s">
         <v>191</v>
       </c>
-      <c r="D149" s="601"/>
+      <c r="D149" s="617"/>
       <c r="E149" s="100"/>
       <c r="F149" s="101">
         <f>(+F63)*115%</f>
@@ -11058,10 +11058,10 @@
     <row r="150" spans="1:10" ht="15.9" customHeight="1">
       <c r="A150" s="51"/>
       <c r="B150" s="99"/>
-      <c r="C150" s="600" t="s">
+      <c r="C150" s="618" t="s">
         <v>192</v>
       </c>
-      <c r="D150" s="601"/>
+      <c r="D150" s="617"/>
       <c r="E150" s="100"/>
       <c r="F150" s="101">
         <v>0</v>
@@ -11080,10 +11080,10 @@
     <row r="151" spans="1:10" ht="15.9" customHeight="1">
       <c r="A151" s="51"/>
       <c r="B151" s="99"/>
-      <c r="C151" s="600" t="s">
+      <c r="C151" s="618" t="s">
         <v>193</v>
       </c>
-      <c r="D151" s="601"/>
+      <c r="D151" s="617"/>
       <c r="E151" s="100"/>
       <c r="F151" s="101">
         <f>(+F65)*115%</f>
@@ -11106,10 +11106,10 @@
     <row r="152" spans="1:10" ht="15.9" customHeight="1">
       <c r="A152" s="51"/>
       <c r="B152" s="99"/>
-      <c r="C152" s="600" t="s">
+      <c r="C152" s="618" t="s">
         <v>194</v>
       </c>
-      <c r="D152" s="601"/>
+      <c r="D152" s="617"/>
       <c r="E152" s="100"/>
       <c r="F152" s="101">
         <f>(+F66)*115%</f>
@@ -11132,10 +11132,10 @@
     <row r="153" spans="1:10" ht="15.9" customHeight="1">
       <c r="A153" s="51"/>
       <c r="B153" s="99"/>
-      <c r="C153" s="594" t="s">
+      <c r="C153" s="616" t="s">
         <v>195</v>
       </c>
-      <c r="D153" s="601"/>
+      <c r="D153" s="617"/>
       <c r="E153" s="103"/>
       <c r="F153" s="104">
         <f>SUM(F149:F152)</f>
@@ -11158,10 +11158,10 @@
     <row r="154" spans="1:10" ht="15.9" customHeight="1">
       <c r="A154" s="51"/>
       <c r="B154" s="99"/>
-      <c r="C154" s="594" t="s">
+      <c r="C154" s="616" t="s">
         <v>196</v>
       </c>
-      <c r="D154" s="601"/>
+      <c r="D154" s="617"/>
       <c r="E154" s="105"/>
       <c r="F154" s="101">
         <f>+F153*12</f>
@@ -11184,8 +11184,8 @@
     <row r="155" spans="1:10" ht="15.9" customHeight="1">
       <c r="A155" s="51"/>
       <c r="B155" s="99"/>
-      <c r="C155" s="615"/>
-      <c r="D155" s="616"/>
+      <c r="C155" s="627"/>
+      <c r="D155" s="628"/>
       <c r="E155" s="105"/>
       <c r="F155" s="101"/>
       <c r="G155" s="209"/>
@@ -11195,11 +11195,11 @@
     </row>
     <row r="156" spans="1:10" ht="15.9" customHeight="1">
       <c r="A156" s="51"/>
-      <c r="B156" s="598" t="s">
+      <c r="B156" s="621" t="s">
         <v>197</v>
       </c>
-      <c r="C156" s="599"/>
-      <c r="D156" s="614"/>
+      <c r="C156" s="622"/>
+      <c r="D156" s="623"/>
       <c r="E156" s="375"/>
       <c r="F156" s="379" t="s">
         <v>190</v>
@@ -11218,8 +11218,8 @@
     <row r="157" spans="1:10" ht="15.9" customHeight="1">
       <c r="A157" s="51"/>
       <c r="B157" s="99"/>
-      <c r="C157" s="615"/>
-      <c r="D157" s="616"/>
+      <c r="C157" s="627"/>
+      <c r="D157" s="628"/>
       <c r="E157" s="105"/>
       <c r="F157" s="101"/>
       <c r="G157" s="209"/>
@@ -11230,10 +11230,10 @@
     <row r="158" spans="1:10" ht="15.9" customHeight="1">
       <c r="A158" s="51"/>
       <c r="B158" s="99"/>
-      <c r="C158" s="683" t="s">
+      <c r="C158" s="644" t="s">
         <v>198</v>
       </c>
-      <c r="D158" s="684"/>
+      <c r="D158" s="645"/>
       <c r="E158" s="105"/>
       <c r="F158" s="101">
         <f t="shared" ref="F158:G160" si="10">+F77</f>
@@ -11256,10 +11256,10 @@
     <row r="159" spans="1:10" ht="15.9" customHeight="1">
       <c r="A159" s="51"/>
       <c r="B159" s="99"/>
-      <c r="C159" s="594" t="s">
+      <c r="C159" s="616" t="s">
         <v>199</v>
       </c>
-      <c r="D159" s="595"/>
+      <c r="D159" s="626"/>
       <c r="E159" s="105"/>
       <c r="F159" s="101">
         <f t="shared" si="10"/>
@@ -11282,10 +11282,10 @@
     <row r="160" spans="1:10" ht="15.9" customHeight="1">
       <c r="A160" s="51"/>
       <c r="B160" s="99"/>
-      <c r="C160" s="594" t="s">
+      <c r="C160" s="616" t="s">
         <v>200</v>
       </c>
-      <c r="D160" s="595"/>
+      <c r="D160" s="626"/>
       <c r="E160" s="105"/>
       <c r="F160" s="101">
         <f t="shared" si="10"/>
@@ -11308,10 +11308,10 @@
     <row r="161" spans="1:22" ht="15.9" customHeight="1">
       <c r="A161" s="51"/>
       <c r="B161" s="99"/>
-      <c r="C161" s="596" t="s">
+      <c r="C161" s="619" t="s">
         <v>29</v>
       </c>
-      <c r="D161" s="597"/>
+      <c r="D161" s="620"/>
       <c r="E161" s="105"/>
       <c r="F161" s="237">
         <f>SUM(F158:F160)</f>
@@ -11334,8 +11334,8 @@
     <row r="162" spans="1:22" ht="15.9" customHeight="1">
       <c r="A162" s="51"/>
       <c r="B162" s="99"/>
-      <c r="C162" s="615"/>
-      <c r="D162" s="616"/>
+      <c r="C162" s="627"/>
+      <c r="D162" s="628"/>
       <c r="E162" s="105"/>
       <c r="F162" s="101"/>
       <c r="G162" s="209"/>
@@ -11345,12 +11345,12 @@
     </row>
     <row r="163" spans="1:22" ht="15.9" customHeight="1">
       <c r="A163" s="106"/>
-      <c r="B163" s="602" t="s">
+      <c r="B163" s="638" t="s">
         <v>201</v>
       </c>
-      <c r="C163" s="603"/>
-      <c r="D163" s="604"/>
-      <c r="E163" s="612"/>
+      <c r="C163" s="639"/>
+      <c r="D163" s="640"/>
+      <c r="E163" s="709"/>
       <c r="F163" s="161" t="s">
         <v>75</v>
       </c>
@@ -11367,10 +11367,10 @@
     </row>
     <row r="164" spans="1:22" ht="15.9" customHeight="1">
       <c r="A164" s="106"/>
-      <c r="B164" s="680"/>
-      <c r="C164" s="681"/>
-      <c r="D164" s="682"/>
-      <c r="E164" s="613"/>
+      <c r="B164" s="641"/>
+      <c r="C164" s="642"/>
+      <c r="D164" s="643"/>
+      <c r="E164" s="631"/>
       <c r="F164" s="161" t="s">
         <v>73</v>
       </c>
@@ -11388,8 +11388,8 @@
     <row r="165" spans="1:22" ht="15.9" customHeight="1">
       <c r="A165" s="107"/>
       <c r="B165" s="99"/>
-      <c r="C165" s="615"/>
-      <c r="D165" s="616"/>
+      <c r="C165" s="627"/>
+      <c r="D165" s="628"/>
       <c r="E165" s="59"/>
       <c r="F165" s="56"/>
       <c r="G165" s="388"/>
@@ -11400,11 +11400,11 @@
     <row r="166" spans="1:22" ht="15.9" customHeight="1">
       <c r="A166" s="107"/>
       <c r="B166" s="99"/>
-      <c r="C166" s="678" t="str">
+      <c r="C166" s="629" t="str">
         <f>+C106</f>
         <v>Net Rent I</v>
       </c>
-      <c r="D166" s="679"/>
+      <c r="D166" s="630"/>
       <c r="E166" s="59"/>
       <c r="F166" s="56">
         <f>+F106</f>
@@ -11428,11 +11428,11 @@
     <row r="167" spans="1:22" ht="15.9" customHeight="1">
       <c r="A167" s="107"/>
       <c r="B167" s="99"/>
-      <c r="C167" s="678" t="str">
+      <c r="C167" s="629" t="str">
         <f>+C107</f>
         <v>Net Rent II</v>
       </c>
-      <c r="D167" s="679"/>
+      <c r="D167" s="630"/>
       <c r="E167" s="59"/>
       <c r="F167" s="56">
         <f>+F107</f>
@@ -11456,10 +11456,10 @@
     <row r="168" spans="1:22" ht="15.9" customHeight="1">
       <c r="A168" s="107"/>
       <c r="B168" s="147"/>
-      <c r="C168" s="674" t="s">
+      <c r="C168" s="634" t="s">
         <v>202</v>
       </c>
-      <c r="D168" s="675"/>
+      <c r="D168" s="635"/>
       <c r="E168" s="148"/>
       <c r="F168" s="149">
         <f>SUM(F166:F167)</f>
@@ -11484,8 +11484,8 @@
     <row r="169" spans="1:22" ht="15.9" customHeight="1">
       <c r="A169" s="107"/>
       <c r="B169" s="162"/>
-      <c r="C169" s="676"/>
-      <c r="D169" s="677"/>
+      <c r="C169" s="636"/>
+      <c r="D169" s="637"/>
       <c r="E169" s="75"/>
       <c r="F169" s="54"/>
       <c r="G169" s="385"/>
@@ -11498,11 +11498,11 @@
     <row r="170" spans="1:22" ht="15.9" customHeight="1">
       <c r="A170" s="107"/>
       <c r="B170" s="99"/>
-      <c r="C170" s="678" t="str">
+      <c r="C170" s="629" t="str">
         <f>+C119</f>
         <v xml:space="preserve">OpEx I </v>
       </c>
-      <c r="D170" s="679"/>
+      <c r="D170" s="630"/>
       <c r="E170" s="59"/>
       <c r="F170" s="56">
         <f>+F119</f>
@@ -11526,11 +11526,11 @@
     <row r="171" spans="1:22" ht="15.9" customHeight="1">
       <c r="A171" s="107"/>
       <c r="B171" s="99"/>
-      <c r="C171" s="678" t="str">
+      <c r="C171" s="629" t="str">
         <f>+C123</f>
         <v xml:space="preserve">OpEx II </v>
       </c>
-      <c r="D171" s="679"/>
+      <c r="D171" s="630"/>
       <c r="E171" s="59"/>
       <c r="F171" s="56">
         <f>+F123</f>
@@ -11553,10 +11553,10 @@
     <row r="172" spans="1:22" ht="15.9" customHeight="1">
       <c r="A172" s="107"/>
       <c r="B172" s="150"/>
-      <c r="C172" s="674" t="s">
+      <c r="C172" s="634" t="s">
         <v>203</v>
       </c>
-      <c r="D172" s="675"/>
+      <c r="D172" s="635"/>
       <c r="E172" s="151"/>
       <c r="F172" s="152">
         <f>SUM(F170:F171)</f>
@@ -11591,11 +11591,11 @@
     <row r="174" spans="1:22" ht="15.9" customHeight="1">
       <c r="A174" s="107"/>
       <c r="B174" s="99"/>
-      <c r="C174" s="678" t="str">
+      <c r="C174" s="629" t="str">
         <f>+C132</f>
         <v xml:space="preserve">Services </v>
       </c>
-      <c r="D174" s="679"/>
+      <c r="D174" s="630"/>
       <c r="E174" s="59"/>
       <c r="F174" s="56">
         <f>+F132</f>
@@ -11618,10 +11618,10 @@
     <row r="175" spans="1:22" ht="15.9" customHeight="1">
       <c r="A175" s="107"/>
       <c r="B175" s="150"/>
-      <c r="C175" s="674" t="s">
+      <c r="C175" s="634" t="s">
         <v>204</v>
       </c>
-      <c r="D175" s="675"/>
+      <c r="D175" s="635"/>
       <c r="E175" s="151"/>
       <c r="F175" s="152">
         <f>SUM(F174)</f>
@@ -11644,8 +11644,8 @@
     <row r="176" spans="1:22" ht="15.9" customHeight="1">
       <c r="A176" s="107"/>
       <c r="B176" s="99"/>
-      <c r="C176" s="615"/>
-      <c r="D176" s="616"/>
+      <c r="C176" s="627"/>
+      <c r="D176" s="628"/>
       <c r="E176" s="59"/>
       <c r="F176" s="56"/>
       <c r="G176" s="388"/>
@@ -11656,10 +11656,10 @@
     <row r="177" spans="1:19" ht="15.9" customHeight="1">
       <c r="A177" s="107"/>
       <c r="B177" s="150"/>
-      <c r="C177" s="674" t="s">
+      <c r="C177" s="634" t="s">
         <v>205</v>
       </c>
-      <c r="D177" s="675"/>
+      <c r="D177" s="635"/>
       <c r="E177" s="154"/>
       <c r="F177" s="149">
         <f>+F168+F172+F175</f>
@@ -11694,11 +11694,11 @@
     </row>
     <row r="179" spans="1:19" ht="15.9" customHeight="1">
       <c r="A179" s="107"/>
-      <c r="B179" s="598" t="s">
+      <c r="B179" s="621" t="s">
         <v>206</v>
       </c>
-      <c r="C179" s="599"/>
-      <c r="D179" s="614"/>
+      <c r="C179" s="622"/>
+      <c r="D179" s="623"/>
       <c r="E179" s="379"/>
       <c r="F179" s="379" t="s">
         <v>190</v>
@@ -11717,8 +11717,8 @@
     <row r="180" spans="1:19" ht="15.9" customHeight="1">
       <c r="A180" s="107"/>
       <c r="B180" s="99"/>
-      <c r="C180" s="615"/>
-      <c r="D180" s="616"/>
+      <c r="C180" s="627"/>
+      <c r="D180" s="628"/>
       <c r="E180" s="59"/>
       <c r="F180" s="56"/>
       <c r="G180" s="388"/>
@@ -11729,10 +11729,10 @@
     <row r="181" spans="1:19" ht="15.9" customHeight="1">
       <c r="A181" s="107"/>
       <c r="B181" s="99"/>
-      <c r="C181" s="600" t="s">
+      <c r="C181" s="618" t="s">
         <v>207</v>
       </c>
-      <c r="D181" s="601"/>
+      <c r="D181" s="617"/>
       <c r="E181" s="100"/>
       <c r="F181" s="101"/>
       <c r="G181" s="209">
@@ -11749,10 +11749,10 @@
     <row r="182" spans="1:19" ht="15.9" customHeight="1">
       <c r="A182" s="107"/>
       <c r="B182" s="99"/>
-      <c r="C182" s="594" t="s">
+      <c r="C182" s="616" t="s">
         <v>208</v>
       </c>
-      <c r="D182" s="601"/>
+      <c r="D182" s="617"/>
       <c r="E182" s="100"/>
       <c r="F182" s="101"/>
       <c r="G182" s="209">
@@ -11769,10 +11769,10 @@
     <row r="183" spans="1:19" ht="15.9" customHeight="1">
       <c r="A183" s="107"/>
       <c r="B183" s="99"/>
-      <c r="C183" s="594" t="s">
+      <c r="C183" s="616" t="s">
         <v>209</v>
       </c>
-      <c r="D183" s="595"/>
+      <c r="D183" s="626"/>
       <c r="E183" s="100"/>
       <c r="F183" s="101"/>
       <c r="G183" s="209">
@@ -11786,10 +11786,10 @@
     <row r="184" spans="1:19" ht="15.9" customHeight="1">
       <c r="A184" s="107"/>
       <c r="B184" s="99"/>
-      <c r="C184" s="594" t="s">
+      <c r="C184" s="616" t="s">
         <v>210</v>
       </c>
-      <c r="D184" s="601"/>
+      <c r="D184" s="617"/>
       <c r="E184" s="100"/>
       <c r="F184" s="101"/>
       <c r="G184" s="209">
@@ -11806,10 +11806,10 @@
     <row r="185" spans="1:19" ht="15.9" customHeight="1">
       <c r="A185" s="107"/>
       <c r="B185" s="99"/>
-      <c r="C185" s="594" t="s">
+      <c r="C185" s="616" t="s">
         <v>211</v>
       </c>
-      <c r="D185" s="601"/>
+      <c r="D185" s="617"/>
       <c r="E185" s="100"/>
       <c r="F185" s="101"/>
       <c r="G185" s="209">
@@ -11837,25 +11837,25 @@
     </row>
     <row r="187" spans="1:19" ht="15.9" customHeight="1" thickBot="1">
       <c r="A187" s="107"/>
-      <c r="B187" s="671" t="s">
+      <c r="B187" s="651" t="s">
         <v>212</v>
       </c>
-      <c r="C187" s="672"/>
-      <c r="D187" s="672"/>
-      <c r="E187" s="672"/>
-      <c r="F187" s="672"/>
-      <c r="G187" s="672"/>
-      <c r="H187" s="672"/>
-      <c r="I187" s="672"/>
-      <c r="J187" s="673"/>
+      <c r="C187" s="652"/>
+      <c r="D187" s="652"/>
+      <c r="E187" s="652"/>
+      <c r="F187" s="652"/>
+      <c r="G187" s="652"/>
+      <c r="H187" s="652"/>
+      <c r="I187" s="652"/>
+      <c r="J187" s="653"/>
     </row>
     <row r="188" spans="1:19" ht="15.9" customHeight="1">
       <c r="A188" s="51"/>
       <c r="B188" s="164"/>
-      <c r="C188" s="613" t="s">
+      <c r="C188" s="631" t="s">
         <v>213</v>
       </c>
-      <c r="D188" s="613"/>
+      <c r="D188" s="631"/>
       <c r="E188" s="378"/>
       <c r="F188" s="378" t="s">
         <v>190</v>
@@ -11863,7 +11863,7 @@
       <c r="G188" s="168" t="s">
         <v>190</v>
       </c>
-      <c r="H188" s="668"/>
+      <c r="H188" s="648"/>
       <c r="I188" s="229" t="s">
         <v>67</v>
       </c>
@@ -11874,17 +11874,17 @@
     <row r="189" spans="1:19" ht="15.9" customHeight="1">
       <c r="A189" s="51"/>
       <c r="B189" s="162"/>
-      <c r="C189" s="600" t="s">
+      <c r="C189" s="618" t="s">
         <v>214</v>
       </c>
-      <c r="D189" s="601"/>
+      <c r="D189" s="617"/>
       <c r="E189" s="163"/>
       <c r="F189" s="163"/>
       <c r="G189" s="102">
         <f>+G20</f>
         <v>0</v>
       </c>
-      <c r="H189" s="669"/>
+      <c r="H189" s="649"/>
       <c r="I189" s="162"/>
       <c r="J189" s="102">
         <f>+G189/J5</f>
@@ -11894,17 +11894,17 @@
     <row r="190" spans="1:19" ht="15.9" customHeight="1">
       <c r="A190" s="51"/>
       <c r="B190" s="162"/>
-      <c r="C190" s="600" t="s">
+      <c r="C190" s="618" t="s">
         <v>215</v>
       </c>
-      <c r="D190" s="601"/>
+      <c r="D190" s="617"/>
       <c r="E190" s="163"/>
       <c r="F190" s="163"/>
       <c r="G190" s="102">
         <f>+G189*G23</f>
         <v>0</v>
       </c>
-      <c r="H190" s="669"/>
+      <c r="H190" s="649"/>
       <c r="I190" s="162"/>
       <c r="J190" s="102">
         <f>+J189*J23</f>
@@ -11914,17 +11914,17 @@
     <row r="191" spans="1:19" ht="15.9" customHeight="1">
       <c r="A191" s="51"/>
       <c r="B191" s="162"/>
-      <c r="C191" s="638" t="s">
+      <c r="C191" s="632" t="s">
         <v>216</v>
       </c>
-      <c r="D191" s="638"/>
+      <c r="D191" s="632"/>
       <c r="E191" s="163"/>
       <c r="F191" s="163"/>
       <c r="G191" s="102">
         <f>+G190*25%</f>
         <v>0</v>
       </c>
-      <c r="H191" s="669"/>
+      <c r="H191" s="649"/>
       <c r="I191" s="162"/>
       <c r="J191" s="102">
         <f>+J190*25%</f>
@@ -11934,17 +11934,17 @@
     <row r="192" spans="1:19" ht="15.9" customHeight="1">
       <c r="A192" s="51"/>
       <c r="B192" s="162"/>
-      <c r="C192" s="594" t="s">
+      <c r="C192" s="616" t="s">
         <v>217</v>
       </c>
-      <c r="D192" s="601"/>
+      <c r="D192" s="617"/>
       <c r="E192" s="163"/>
       <c r="F192" s="163"/>
       <c r="G192" s="102">
         <f>+G191*1%</f>
         <v>0</v>
       </c>
-      <c r="H192" s="669"/>
+      <c r="H192" s="649"/>
       <c r="I192" s="162"/>
       <c r="J192" s="102">
         <f>G192/J5</f>
@@ -11954,17 +11954,17 @@
     <row r="193" spans="1:20" ht="15.9" customHeight="1">
       <c r="A193" s="51"/>
       <c r="B193" s="162"/>
-      <c r="C193" s="594" t="s">
+      <c r="C193" s="616" t="s">
         <v>218</v>
       </c>
-      <c r="D193" s="601"/>
+      <c r="D193" s="617"/>
       <c r="E193" s="163"/>
       <c r="F193" s="163"/>
       <c r="G193" s="102">
         <f>G192*0.5</f>
         <v>0</v>
       </c>
-      <c r="H193" s="669"/>
+      <c r="H193" s="649"/>
       <c r="I193" s="162"/>
       <c r="J193" s="102">
         <f>G193/J5</f>
@@ -11974,17 +11974,17 @@
     <row r="194" spans="1:20" ht="15.9" customHeight="1" thickBot="1">
       <c r="A194" s="51"/>
       <c r="B194" s="162"/>
-      <c r="C194" s="638" t="s">
+      <c r="C194" s="632" t="s">
         <v>219</v>
       </c>
-      <c r="D194" s="638"/>
+      <c r="D194" s="632"/>
       <c r="E194" s="163"/>
       <c r="F194" s="163"/>
       <c r="G194" s="110">
         <f>G82</f>
         <v>565315.30184775486</v>
       </c>
-      <c r="H194" s="669"/>
+      <c r="H194" s="649"/>
       <c r="I194" s="162"/>
       <c r="J194" s="110">
         <f>+J192+J193</f>
@@ -11994,8 +11994,8 @@
     <row r="195" spans="1:20" ht="15.9" customHeight="1">
       <c r="A195" s="166"/>
       <c r="B195" s="382"/>
-      <c r="C195" s="606"/>
-      <c r="D195" s="606"/>
+      <c r="C195" s="633"/>
+      <c r="D195" s="633"/>
       <c r="E195" s="379"/>
       <c r="F195" s="379" t="s">
         <v>190</v>
@@ -12003,7 +12003,7 @@
       <c r="G195" s="53" t="s">
         <v>190</v>
       </c>
-      <c r="H195" s="669"/>
+      <c r="H195" s="649"/>
       <c r="I195" s="229" t="s">
         <v>67</v>
       </c>
@@ -12014,17 +12014,17 @@
     <row r="196" spans="1:20" ht="15.9" customHeight="1">
       <c r="A196" s="74"/>
       <c r="B196" s="99"/>
-      <c r="C196" s="600" t="s">
+      <c r="C196" s="618" t="s">
         <v>220</v>
       </c>
-      <c r="D196" s="601"/>
+      <c r="D196" s="617"/>
       <c r="E196" s="58"/>
       <c r="F196" s="50"/>
       <c r="G196" s="102">
         <f>+G54</f>
         <v>72</v>
       </c>
-      <c r="H196" s="669"/>
+      <c r="H196" s="649"/>
       <c r="I196" s="91"/>
       <c r="J196" s="102">
         <f>+J54</f>
@@ -12034,17 +12034,17 @@
     <row r="197" spans="1:20" ht="15.9" customHeight="1">
       <c r="A197" s="74"/>
       <c r="B197" s="99"/>
-      <c r="C197" s="600" t="s">
+      <c r="C197" s="618" t="s">
         <v>221</v>
       </c>
-      <c r="D197" s="601"/>
+      <c r="D197" s="617"/>
       <c r="E197" s="58"/>
       <c r="F197" s="50"/>
       <c r="G197" s="102">
         <f>F140</f>
         <v>9515</v>
       </c>
-      <c r="H197" s="669"/>
+      <c r="H197" s="649"/>
       <c r="I197" s="91"/>
       <c r="J197" s="102">
         <f>I140</f>
@@ -12054,17 +12054,17 @@
     <row r="198" spans="1:20" ht="15.9" customHeight="1">
       <c r="A198" s="120"/>
       <c r="B198" s="99"/>
-      <c r="C198" s="600" t="s">
+      <c r="C198" s="618" t="s">
         <v>222</v>
       </c>
-      <c r="D198" s="601"/>
+      <c r="D198" s="617"/>
       <c r="E198" s="58"/>
       <c r="F198" s="50"/>
       <c r="G198" s="111">
         <f>+F60</f>
         <v>129</v>
       </c>
-      <c r="H198" s="669"/>
+      <c r="H198" s="649"/>
       <c r="I198" s="91"/>
       <c r="J198" s="111">
         <f>+I60</f>
@@ -12074,17 +12074,17 @@
     <row r="199" spans="1:20" ht="15.9" customHeight="1">
       <c r="A199" s="74"/>
       <c r="B199" s="99"/>
-      <c r="C199" s="600" t="s">
+      <c r="C199" s="618" t="s">
         <v>222</v>
       </c>
-      <c r="D199" s="601"/>
+      <c r="D199" s="617"/>
       <c r="E199" s="58"/>
       <c r="F199" s="50"/>
       <c r="G199" s="102">
         <f>(G197*G198*G196)</f>
         <v>88375320</v>
       </c>
-      <c r="H199" s="669"/>
+      <c r="H199" s="649"/>
       <c r="I199" s="91"/>
       <c r="J199" s="102">
         <f>+G199/$J$5</f>
@@ -12094,17 +12094,17 @@
     <row r="200" spans="1:20" ht="15.9" customHeight="1">
       <c r="A200" s="74"/>
       <c r="B200" s="99"/>
-      <c r="C200" s="600" t="s">
+      <c r="C200" s="618" t="s">
         <v>223</v>
       </c>
-      <c r="D200" s="601"/>
+      <c r="D200" s="617"/>
       <c r="E200" s="58"/>
       <c r="F200" s="50"/>
       <c r="G200" s="102">
         <f>G199/G196*12</f>
         <v>14729220</v>
       </c>
-      <c r="H200" s="669"/>
+      <c r="H200" s="649"/>
       <c r="I200" s="91"/>
       <c r="J200" s="102">
         <f>+G200/$J$5</f>
@@ -12114,17 +12114,17 @@
     <row r="201" spans="1:20" ht="15.9" customHeight="1">
       <c r="A201" s="74"/>
       <c r="B201" s="99"/>
-      <c r="C201" s="600" t="s">
+      <c r="C201" s="618" t="s">
         <v>224</v>
       </c>
-      <c r="D201" s="601"/>
+      <c r="D201" s="617"/>
       <c r="E201" s="58"/>
       <c r="F201" s="50"/>
       <c r="G201" s="102">
         <f>(+G220*115%)/5</f>
         <v>3026339.9999999995</v>
       </c>
-      <c r="H201" s="669"/>
+      <c r="H201" s="649"/>
       <c r="I201" s="91"/>
       <c r="J201" s="102">
         <f>+G201/$J$5</f>
@@ -12134,17 +12134,17 @@
     <row r="202" spans="1:20" ht="15.9" customHeight="1">
       <c r="A202" s="74"/>
       <c r="B202" s="99"/>
-      <c r="C202" s="600" t="s">
+      <c r="C202" s="618" t="s">
         <v>225</v>
       </c>
-      <c r="D202" s="601"/>
+      <c r="D202" s="617"/>
       <c r="E202" s="58"/>
       <c r="F202" s="50"/>
       <c r="G202" s="102">
         <f>(+I220*115%)/5</f>
         <v>2765157.6185172233</v>
       </c>
-      <c r="H202" s="669"/>
+      <c r="H202" s="649"/>
       <c r="I202" s="91"/>
       <c r="J202" s="102">
         <f>+G202/$J$5</f>
@@ -12154,17 +12154,17 @@
     <row r="203" spans="1:20" ht="15.9" customHeight="1">
       <c r="A203" s="74"/>
       <c r="B203" s="99"/>
-      <c r="C203" s="600" t="s">
+      <c r="C203" s="618" t="s">
         <v>36</v>
       </c>
-      <c r="D203" s="601"/>
+      <c r="D203" s="617"/>
       <c r="E203" s="58"/>
       <c r="F203" s="50"/>
       <c r="G203" s="102">
         <f>+G67</f>
         <v>11418000</v>
       </c>
-      <c r="H203" s="669"/>
+      <c r="H203" s="649"/>
       <c r="I203" s="91"/>
       <c r="J203" s="102">
         <f>+G203/$J$5</f>
@@ -12174,17 +12174,17 @@
     <row r="204" spans="1:20" ht="15.9" customHeight="1">
       <c r="A204" s="74"/>
       <c r="B204" s="99"/>
-      <c r="C204" s="594" t="s">
+      <c r="C204" s="616" t="s">
         <v>226</v>
       </c>
-      <c r="D204" s="601"/>
+      <c r="D204" s="617"/>
       <c r="E204" s="58"/>
       <c r="F204" s="50"/>
       <c r="G204" s="102">
         <f>(G200+G201+G202+G203)*1.18</f>
         <v>37687686.789850324</v>
       </c>
-      <c r="H204" s="669"/>
+      <c r="H204" s="649"/>
       <c r="I204" s="91"/>
       <c r="J204" s="102">
         <f>+J200+J201+J202+J203</f>
@@ -12194,17 +12194,17 @@
     <row r="205" spans="1:20" ht="15.9" customHeight="1">
       <c r="A205" s="74"/>
       <c r="B205" s="99"/>
-      <c r="C205" s="594" t="s">
+      <c r="C205" s="616" t="s">
         <v>227</v>
       </c>
-      <c r="D205" s="601"/>
+      <c r="D205" s="617"/>
       <c r="E205" s="58"/>
       <c r="F205" s="50"/>
       <c r="G205" s="102">
         <f>G204*1%</f>
         <v>376876.86789850326</v>
       </c>
-      <c r="H205" s="669"/>
+      <c r="H205" s="649"/>
       <c r="I205" s="91"/>
       <c r="J205" s="102">
         <f>J204*1%</f>
@@ -12214,17 +12214,17 @@
     <row r="206" spans="1:20" ht="15.9" customHeight="1">
       <c r="A206" s="74"/>
       <c r="B206" s="99"/>
-      <c r="C206" s="600" t="s">
+      <c r="C206" s="618" t="s">
         <v>228</v>
       </c>
-      <c r="D206" s="601"/>
+      <c r="D206" s="617"/>
       <c r="E206" s="58"/>
       <c r="F206" s="50"/>
       <c r="G206" s="102">
         <f>G204*0.5%</f>
         <v>188438.43394925163</v>
       </c>
-      <c r="H206" s="669"/>
+      <c r="H206" s="649"/>
       <c r="I206" s="91"/>
       <c r="J206" s="102">
         <f>J204*0.5%</f>
@@ -12234,17 +12234,17 @@
     <row r="207" spans="1:20" ht="15.9" customHeight="1">
       <c r="A207" s="74"/>
       <c r="B207" s="99"/>
-      <c r="C207" s="596" t="s">
+      <c r="C207" s="619" t="s">
         <v>219</v>
       </c>
-      <c r="D207" s="597"/>
+      <c r="D207" s="620"/>
       <c r="E207" s="58"/>
       <c r="F207" s="50"/>
       <c r="G207" s="102">
         <f>G205+G206</f>
         <v>565315.30184775486</v>
       </c>
-      <c r="H207" s="669"/>
+      <c r="H207" s="649"/>
       <c r="I207" s="91"/>
       <c r="J207" s="102">
         <v>0</v>
@@ -12259,7 +12259,7 @@
       <c r="E208" s="80"/>
       <c r="F208" s="51"/>
       <c r="G208" s="337"/>
-      <c r="H208" s="669"/>
+      <c r="H208" s="649"/>
       <c r="I208" s="94"/>
       <c r="J208" s="81"/>
     </row>
@@ -12281,7 +12281,7 @@
       <c r="G209" s="161" t="s">
         <v>233</v>
       </c>
-      <c r="H209" s="669"/>
+      <c r="H209" s="649"/>
       <c r="I209" s="379" t="s">
         <v>234</v>
       </c>
@@ -12307,7 +12307,7 @@
         <f>'Lease Rent'!P39</f>
         <v>1360000</v>
       </c>
-      <c r="H210" s="669"/>
+      <c r="H210" s="649"/>
       <c r="I210" s="101">
         <f>'Lease Rent'!O39</f>
         <v>1178337.5999999999</v>
@@ -12337,7 +12337,7 @@
         <f>'Lease Rent'!P51</f>
         <v>2040000</v>
       </c>
-      <c r="H211" s="669"/>
+      <c r="H211" s="649"/>
       <c r="I211" s="101">
         <f>'Lease Rent'!O51</f>
         <v>1826423.2800000005</v>
@@ -12366,7 +12366,7 @@
         <f>'Lease Rent'!P63</f>
         <v>2040000</v>
       </c>
-      <c r="H212" s="669"/>
+      <c r="H212" s="649"/>
       <c r="I212" s="101">
         <f>'Lease Rent'!O63</f>
         <v>1917744.4440000001</v>
@@ -12395,7 +12395,7 @@
         <f>'Lease Rent'!P75</f>
         <v>2244000</v>
       </c>
-      <c r="H213" s="669"/>
+      <c r="H213" s="649"/>
       <c r="I213" s="101">
         <f>'Lease Rent'!O75</f>
         <v>2013631.6662000006</v>
@@ -12424,7 +12424,7 @@
         <f>'Lease Rent'!P87</f>
         <v>2345999.9999999995</v>
       </c>
-      <c r="H214" s="669"/>
+      <c r="H214" s="649"/>
       <c r="I214" s="101">
         <f>'Lease Rent'!O87</f>
         <v>2114313.2495100005</v>
@@ -12453,7 +12453,7 @@
         <f>'Lease Rent'!P99</f>
         <v>2345999.9999999995</v>
       </c>
-      <c r="H215" s="669"/>
+      <c r="H215" s="649"/>
       <c r="I215" s="101">
         <f>'Lease Rent'!O99</f>
         <v>2220028.9119855007</v>
@@ -12481,7 +12481,7 @@
         <f>'Lease Rent'!P103</f>
         <v>781999.99999999988</v>
       </c>
-      <c r="H216" s="669"/>
+      <c r="H216" s="649"/>
       <c r="I216" s="101">
         <f>'Lease Rent'!O103</f>
         <v>751945.27664025011</v>
@@ -12504,7 +12504,7 @@
         <f>'Lease Rent'!R10</f>
         <v>0</v>
       </c>
-      <c r="H217" s="669"/>
+      <c r="H217" s="649"/>
       <c r="I217" s="301"/>
       <c r="J217" s="111"/>
     </row>
@@ -12521,7 +12521,7 @@
         <v>0</v>
       </c>
       <c r="G218" s="118"/>
-      <c r="H218" s="669"/>
+      <c r="H218" s="649"/>
       <c r="I218" s="101"/>
       <c r="J218" s="111"/>
     </row>
@@ -12535,7 +12535,7 @@
       <c r="E219" s="117"/>
       <c r="F219" s="232"/>
       <c r="G219" s="118"/>
-      <c r="H219" s="669"/>
+      <c r="H219" s="649"/>
       <c r="I219" s="101"/>
       <c r="J219" s="111"/>
     </row>
@@ -12558,7 +12558,7 @@
         <f>SUM(G210:G219)</f>
         <v>13158000</v>
       </c>
-      <c r="H220" s="670"/>
+      <c r="H220" s="650"/>
       <c r="I220" s="283">
         <f>SUM(I210:I219)</f>
         <v>12022424.428335754</v>
@@ -12628,6 +12628,219 @@
     </row>
   </sheetData>
   <mergeCells count="237">
+    <mergeCell ref="F137:G137"/>
+    <mergeCell ref="I137:J137"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="B134:D134"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="B105:D105"/>
+    <mergeCell ref="C124:D124"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="E163:E164"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="C123:D123"/>
+    <mergeCell ref="C118:D118"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="B156:D156"/>
+    <mergeCell ref="C151:D151"/>
+    <mergeCell ref="C152:D152"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="C145:D145"/>
+    <mergeCell ref="C148:D148"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B1:J3"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="H188:H220"/>
+    <mergeCell ref="C159:D159"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B187:J187"/>
+    <mergeCell ref="C172:D172"/>
+    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="C177:D177"/>
+    <mergeCell ref="C180:D180"/>
+    <mergeCell ref="C157:D157"/>
+    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="C175:D175"/>
+    <mergeCell ref="C149:D149"/>
+    <mergeCell ref="C150:D150"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="C143:D143"/>
+    <mergeCell ref="C184:D184"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C181:D181"/>
+    <mergeCell ref="C185:D185"/>
+    <mergeCell ref="C168:D168"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="C169:D169"/>
+    <mergeCell ref="C183:D183"/>
+    <mergeCell ref="C170:D170"/>
+    <mergeCell ref="C140:D140"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="C122:D122"/>
+    <mergeCell ref="C171:D171"/>
+    <mergeCell ref="C167:D167"/>
+    <mergeCell ref="B147:D147"/>
+    <mergeCell ref="B163:D164"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="C144:D144"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="C166:D166"/>
+    <mergeCell ref="C182:D182"/>
+    <mergeCell ref="C205:D205"/>
+    <mergeCell ref="C206:D206"/>
+    <mergeCell ref="C207:D207"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C174:D174"/>
+    <mergeCell ref="C197:D197"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="C199:D199"/>
+    <mergeCell ref="C200:D200"/>
+    <mergeCell ref="C201:D201"/>
+    <mergeCell ref="C202:D202"/>
+    <mergeCell ref="C188:D188"/>
+    <mergeCell ref="C191:D191"/>
+    <mergeCell ref="C194:D194"/>
+    <mergeCell ref="C195:D195"/>
+    <mergeCell ref="C196:D196"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
     <mergeCell ref="C204:D204"/>
     <mergeCell ref="C203:D203"/>
     <mergeCell ref="C161:D161"/>
@@ -12652,219 +12865,6 @@
     <mergeCell ref="B179:D179"/>
     <mergeCell ref="C162:D162"/>
     <mergeCell ref="C165:D165"/>
-    <mergeCell ref="C205:D205"/>
-    <mergeCell ref="C206:D206"/>
-    <mergeCell ref="C207:D207"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C174:D174"/>
-    <mergeCell ref="C197:D197"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="C199:D199"/>
-    <mergeCell ref="C200:D200"/>
-    <mergeCell ref="C201:D201"/>
-    <mergeCell ref="C202:D202"/>
-    <mergeCell ref="C188:D188"/>
-    <mergeCell ref="C191:D191"/>
-    <mergeCell ref="C194:D194"/>
-    <mergeCell ref="C195:D195"/>
-    <mergeCell ref="C196:D196"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C181:D181"/>
-    <mergeCell ref="C185:D185"/>
-    <mergeCell ref="C168:D168"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="C169:D169"/>
-    <mergeCell ref="C183:D183"/>
-    <mergeCell ref="C170:D170"/>
-    <mergeCell ref="C140:D140"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="C122:D122"/>
-    <mergeCell ref="C171:D171"/>
-    <mergeCell ref="C167:D167"/>
-    <mergeCell ref="B147:D147"/>
-    <mergeCell ref="B163:D164"/>
-    <mergeCell ref="B125:D125"/>
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="C144:D144"/>
-    <mergeCell ref="C139:D139"/>
-    <mergeCell ref="C166:D166"/>
-    <mergeCell ref="C182:D182"/>
-    <mergeCell ref="H188:H220"/>
-    <mergeCell ref="C159:D159"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B187:J187"/>
-    <mergeCell ref="C172:D172"/>
-    <mergeCell ref="C176:D176"/>
-    <mergeCell ref="C177:D177"/>
-    <mergeCell ref="C180:D180"/>
-    <mergeCell ref="C157:D157"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="C175:D175"/>
-    <mergeCell ref="C149:D149"/>
-    <mergeCell ref="C150:D150"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="I58:J58"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="C143:D143"/>
-    <mergeCell ref="C184:D184"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B1:J3"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="E163:E164"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="C123:D123"/>
-    <mergeCell ref="C118:D118"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="B156:D156"/>
-    <mergeCell ref="C151:D151"/>
-    <mergeCell ref="C152:D152"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="C145:D145"/>
-    <mergeCell ref="C148:D148"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="C136:D136"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="B134:D134"/>
-    <mergeCell ref="C106:D106"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="B105:D105"/>
-    <mergeCell ref="C124:D124"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="F137:G137"/>
-    <mergeCell ref="I137:J137"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C131:D131"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="C107:D107"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.25" top="0.75" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="58" orientation="portrait" r:id="rId1"/>
@@ -12937,215 +12937,215 @@
       <c r="S1" s="1"/>
     </row>
     <row r="2" spans="1:27" ht="11.25" customHeight="1">
-      <c r="A2" s="654"/>
-      <c r="B2" s="655"/>
-      <c r="C2" s="655"/>
-      <c r="D2" s="655"/>
-      <c r="E2" s="655"/>
-      <c r="F2" s="655"/>
-      <c r="G2" s="655"/>
-      <c r="H2" s="655"/>
-      <c r="I2" s="655"/>
-      <c r="J2" s="655"/>
-      <c r="K2" s="655"/>
-      <c r="L2" s="655"/>
-      <c r="M2" s="655"/>
-      <c r="N2" s="655"/>
-      <c r="O2" s="655"/>
-      <c r="P2" s="655"/>
-      <c r="Q2" s="655"/>
-      <c r="R2" s="655"/>
-      <c r="S2" s="655"/>
-      <c r="T2" s="655"/>
-      <c r="U2" s="655"/>
-      <c r="V2" s="655"/>
-      <c r="W2" s="655"/>
-      <c r="X2" s="655"/>
-      <c r="Y2" s="655"/>
-      <c r="Z2" s="655"/>
-      <c r="AA2" s="691"/>
+      <c r="A2" s="596"/>
+      <c r="B2" s="597"/>
+      <c r="C2" s="597"/>
+      <c r="D2" s="597"/>
+      <c r="E2" s="597"/>
+      <c r="F2" s="597"/>
+      <c r="G2" s="597"/>
+      <c r="H2" s="597"/>
+      <c r="I2" s="597"/>
+      <c r="J2" s="597"/>
+      <c r="K2" s="597"/>
+      <c r="L2" s="597"/>
+      <c r="M2" s="597"/>
+      <c r="N2" s="597"/>
+      <c r="O2" s="597"/>
+      <c r="P2" s="597"/>
+      <c r="Q2" s="597"/>
+      <c r="R2" s="597"/>
+      <c r="S2" s="597"/>
+      <c r="T2" s="597"/>
+      <c r="U2" s="597"/>
+      <c r="V2" s="597"/>
+      <c r="W2" s="597"/>
+      <c r="X2" s="597"/>
+      <c r="Y2" s="597"/>
+      <c r="Z2" s="597"/>
+      <c r="AA2" s="598"/>
     </row>
     <row r="3" spans="1:27" ht="11.25" customHeight="1">
-      <c r="A3" s="692"/>
-      <c r="B3" s="693"/>
-      <c r="C3" s="693"/>
-      <c r="D3" s="693"/>
-      <c r="E3" s="693"/>
-      <c r="F3" s="693"/>
-      <c r="G3" s="693"/>
-      <c r="H3" s="693"/>
-      <c r="I3" s="693"/>
-      <c r="J3" s="693"/>
-      <c r="K3" s="693"/>
-      <c r="L3" s="693"/>
-      <c r="M3" s="693"/>
-      <c r="N3" s="693"/>
-      <c r="O3" s="693"/>
-      <c r="P3" s="693"/>
-      <c r="Q3" s="693"/>
-      <c r="R3" s="693"/>
-      <c r="S3" s="693"/>
-      <c r="T3" s="693"/>
-      <c r="U3" s="693"/>
-      <c r="V3" s="693"/>
-      <c r="W3" s="693"/>
-      <c r="X3" s="693"/>
-      <c r="Y3" s="693"/>
-      <c r="Z3" s="693"/>
-      <c r="AA3" s="694"/>
+      <c r="A3" s="599"/>
+      <c r="B3" s="600"/>
+      <c r="C3" s="600"/>
+      <c r="D3" s="600"/>
+      <c r="E3" s="600"/>
+      <c r="F3" s="600"/>
+      <c r="G3" s="600"/>
+      <c r="H3" s="600"/>
+      <c r="I3" s="600"/>
+      <c r="J3" s="600"/>
+      <c r="K3" s="600"/>
+      <c r="L3" s="600"/>
+      <c r="M3" s="600"/>
+      <c r="N3" s="600"/>
+      <c r="O3" s="600"/>
+      <c r="P3" s="600"/>
+      <c r="Q3" s="600"/>
+      <c r="R3" s="600"/>
+      <c r="S3" s="600"/>
+      <c r="T3" s="600"/>
+      <c r="U3" s="600"/>
+      <c r="V3" s="600"/>
+      <c r="W3" s="600"/>
+      <c r="X3" s="600"/>
+      <c r="Y3" s="600"/>
+      <c r="Z3" s="600"/>
+      <c r="AA3" s="601"/>
     </row>
     <row r="4" spans="1:27" ht="12" customHeight="1" thickBot="1">
-      <c r="A4" s="695"/>
-      <c r="B4" s="696"/>
-      <c r="C4" s="696"/>
-      <c r="D4" s="696"/>
-      <c r="E4" s="696"/>
-      <c r="F4" s="696"/>
-      <c r="G4" s="696"/>
-      <c r="H4" s="696"/>
-      <c r="I4" s="696"/>
-      <c r="J4" s="696"/>
-      <c r="K4" s="696"/>
-      <c r="L4" s="696"/>
-      <c r="M4" s="696"/>
-      <c r="N4" s="696"/>
-      <c r="O4" s="696"/>
-      <c r="P4" s="696"/>
-      <c r="Q4" s="696"/>
-      <c r="R4" s="696"/>
-      <c r="S4" s="696"/>
-      <c r="T4" s="696"/>
-      <c r="U4" s="696"/>
-      <c r="V4" s="696"/>
-      <c r="W4" s="696"/>
-      <c r="X4" s="696"/>
-      <c r="Y4" s="696"/>
-      <c r="Z4" s="696"/>
-      <c r="AA4" s="697"/>
+      <c r="A4" s="602"/>
+      <c r="B4" s="603"/>
+      <c r="C4" s="603"/>
+      <c r="D4" s="603"/>
+      <c r="E4" s="603"/>
+      <c r="F4" s="603"/>
+      <c r="G4" s="603"/>
+      <c r="H4" s="603"/>
+      <c r="I4" s="603"/>
+      <c r="J4" s="603"/>
+      <c r="K4" s="603"/>
+      <c r="L4" s="603"/>
+      <c r="M4" s="603"/>
+      <c r="N4" s="603"/>
+      <c r="O4" s="603"/>
+      <c r="P4" s="603"/>
+      <c r="Q4" s="603"/>
+      <c r="R4" s="603"/>
+      <c r="S4" s="603"/>
+      <c r="T4" s="603"/>
+      <c r="U4" s="603"/>
+      <c r="V4" s="603"/>
+      <c r="W4" s="603"/>
+      <c r="X4" s="603"/>
+      <c r="Y4" s="603"/>
+      <c r="Z4" s="603"/>
+      <c r="AA4" s="604"/>
     </row>
     <row r="5" spans="1:27" ht="12.75" customHeight="1">
-      <c r="A5" s="654" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="655"/>
-      <c r="C5" s="655"/>
-      <c r="D5" s="655"/>
-      <c r="E5" s="655"/>
-      <c r="F5" s="655"/>
-      <c r="G5" s="655"/>
-      <c r="H5" s="655"/>
-      <c r="I5" s="655"/>
-      <c r="J5" s="655"/>
-      <c r="K5" s="655"/>
-      <c r="L5" s="655"/>
-      <c r="M5" s="655"/>
-      <c r="N5" s="655"/>
-      <c r="O5" s="655"/>
-      <c r="P5" s="655"/>
-      <c r="Q5" s="655"/>
-      <c r="R5" s="655"/>
-      <c r="S5" s="655"/>
-      <c r="T5" s="655"/>
-      <c r="U5" s="655"/>
-      <c r="V5" s="655"/>
-      <c r="W5" s="655"/>
-      <c r="X5" s="655"/>
-      <c r="Y5" s="655"/>
-      <c r="Z5" s="655"/>
-      <c r="AA5" s="691"/>
+      <c r="A5" s="596" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="597"/>
+      <c r="C5" s="597"/>
+      <c r="D5" s="597"/>
+      <c r="E5" s="597"/>
+      <c r="F5" s="597"/>
+      <c r="G5" s="597"/>
+      <c r="H5" s="597"/>
+      <c r="I5" s="597"/>
+      <c r="J5" s="597"/>
+      <c r="K5" s="597"/>
+      <c r="L5" s="597"/>
+      <c r="M5" s="597"/>
+      <c r="N5" s="597"/>
+      <c r="O5" s="597"/>
+      <c r="P5" s="597"/>
+      <c r="Q5" s="597"/>
+      <c r="R5" s="597"/>
+      <c r="S5" s="597"/>
+      <c r="T5" s="597"/>
+      <c r="U5" s="597"/>
+      <c r="V5" s="597"/>
+      <c r="W5" s="597"/>
+      <c r="X5" s="597"/>
+      <c r="Y5" s="597"/>
+      <c r="Z5" s="597"/>
+      <c r="AA5" s="598"/>
     </row>
     <row r="6" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A6" s="698"/>
-      <c r="B6" s="699"/>
-      <c r="C6" s="699"/>
-      <c r="D6" s="699"/>
-      <c r="E6" s="699"/>
-      <c r="F6" s="699"/>
-      <c r="G6" s="699"/>
-      <c r="H6" s="699"/>
-      <c r="I6" s="699"/>
-      <c r="J6" s="699"/>
-      <c r="K6" s="699"/>
-      <c r="L6" s="699"/>
-      <c r="M6" s="699"/>
-      <c r="N6" s="699"/>
-      <c r="O6" s="699"/>
-      <c r="P6" s="699"/>
-      <c r="Q6" s="699"/>
-      <c r="R6" s="699"/>
-      <c r="S6" s="699"/>
-      <c r="T6" s="699"/>
-      <c r="U6" s="699"/>
-      <c r="V6" s="699"/>
-      <c r="W6" s="699"/>
-      <c r="X6" s="699"/>
-      <c r="Y6" s="699"/>
-      <c r="Z6" s="699"/>
-      <c r="AA6" s="700"/>
+      <c r="A6" s="605"/>
+      <c r="B6" s="606"/>
+      <c r="C6" s="606"/>
+      <c r="D6" s="606"/>
+      <c r="E6" s="606"/>
+      <c r="F6" s="606"/>
+      <c r="G6" s="606"/>
+      <c r="H6" s="606"/>
+      <c r="I6" s="606"/>
+      <c r="J6" s="606"/>
+      <c r="K6" s="606"/>
+      <c r="L6" s="606"/>
+      <c r="M6" s="606"/>
+      <c r="N6" s="606"/>
+      <c r="O6" s="606"/>
+      <c r="P6" s="606"/>
+      <c r="Q6" s="606"/>
+      <c r="R6" s="606"/>
+      <c r="S6" s="606"/>
+      <c r="T6" s="606"/>
+      <c r="U6" s="606"/>
+      <c r="V6" s="606"/>
+      <c r="W6" s="606"/>
+      <c r="X6" s="606"/>
+      <c r="Y6" s="606"/>
+      <c r="Z6" s="606"/>
+      <c r="AA6" s="607"/>
     </row>
     <row r="7" spans="1:27" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A7" s="701" t="s">
+      <c r="A7" s="608" t="s">
         <v>296</v>
       </c>
-      <c r="B7" s="702"/>
-      <c r="C7" s="702"/>
-      <c r="D7" s="702"/>
-      <c r="E7" s="702"/>
-      <c r="F7" s="702"/>
-      <c r="G7" s="702"/>
-      <c r="H7" s="702"/>
-      <c r="I7" s="702"/>
-      <c r="J7" s="702"/>
-      <c r="K7" s="702"/>
-      <c r="L7" s="702"/>
-      <c r="M7" s="702"/>
-      <c r="N7" s="702"/>
-      <c r="O7" s="702"/>
-      <c r="P7" s="703"/>
-      <c r="Q7" s="703"/>
-      <c r="R7" s="703"/>
-      <c r="S7" s="703"/>
-      <c r="T7" s="703"/>
-      <c r="U7" s="703"/>
-      <c r="V7" s="703"/>
-      <c r="W7" s="703"/>
-      <c r="X7" s="703"/>
-      <c r="Y7" s="703"/>
-      <c r="Z7" s="703"/>
-      <c r="AA7" s="704"/>
+      <c r="B7" s="609"/>
+      <c r="C7" s="609"/>
+      <c r="D7" s="609"/>
+      <c r="E7" s="609"/>
+      <c r="F7" s="609"/>
+      <c r="G7" s="609"/>
+      <c r="H7" s="609"/>
+      <c r="I7" s="609"/>
+      <c r="J7" s="609"/>
+      <c r="K7" s="609"/>
+      <c r="L7" s="609"/>
+      <c r="M7" s="609"/>
+      <c r="N7" s="609"/>
+      <c r="O7" s="609"/>
+      <c r="P7" s="610"/>
+      <c r="Q7" s="610"/>
+      <c r="R7" s="610"/>
+      <c r="S7" s="610"/>
+      <c r="T7" s="610"/>
+      <c r="U7" s="610"/>
+      <c r="V7" s="610"/>
+      <c r="W7" s="610"/>
+      <c r="X7" s="610"/>
+      <c r="Y7" s="610"/>
+      <c r="Z7" s="610"/>
+      <c r="AA7" s="611"/>
     </row>
     <row r="8" spans="1:27" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A8" s="705" t="s">
+      <c r="A8" s="612" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="706"/>
-      <c r="C8" s="706"/>
-      <c r="D8" s="706"/>
-      <c r="E8" s="706"/>
-      <c r="F8" s="706"/>
-      <c r="G8" s="706"/>
-      <c r="H8" s="706"/>
-      <c r="I8" s="706"/>
-      <c r="J8" s="706"/>
-      <c r="K8" s="706"/>
-      <c r="L8" s="706"/>
-      <c r="M8" s="706"/>
-      <c r="N8" s="707"/>
+      <c r="B8" s="613"/>
+      <c r="C8" s="613"/>
+      <c r="D8" s="613"/>
+      <c r="E8" s="613"/>
+      <c r="F8" s="613"/>
+      <c r="G8" s="613"/>
+      <c r="H8" s="613"/>
+      <c r="I8" s="613"/>
+      <c r="J8" s="613"/>
+      <c r="K8" s="613"/>
+      <c r="L8" s="613"/>
+      <c r="M8" s="613"/>
+      <c r="N8" s="614"/>
       <c r="O8" s="6"/>
-      <c r="P8" s="705" t="s">
+      <c r="P8" s="612" t="s">
         <v>2</v>
       </c>
-      <c r="Q8" s="706"/>
-      <c r="R8" s="706"/>
-      <c r="S8" s="706"/>
-      <c r="T8" s="706"/>
-      <c r="U8" s="706"/>
-      <c r="V8" s="706"/>
-      <c r="W8" s="706"/>
-      <c r="X8" s="706"/>
-      <c r="Y8" s="706"/>
-      <c r="Z8" s="706"/>
-      <c r="AA8" s="708"/>
+      <c r="Q8" s="613"/>
+      <c r="R8" s="613"/>
+      <c r="S8" s="613"/>
+      <c r="T8" s="613"/>
+      <c r="U8" s="613"/>
+      <c r="V8" s="613"/>
+      <c r="W8" s="613"/>
+      <c r="X8" s="613"/>
+      <c r="Y8" s="613"/>
+      <c r="Z8" s="613"/>
+      <c r="AA8" s="615"/>
     </row>
     <row r="9" spans="1:27" s="215" customFormat="1" ht="45.75" customHeight="1">
       <c r="A9" s="216">
@@ -14243,10 +14243,7 @@
       <c r="I24" s="10"/>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
-      <c r="L24" s="10">
-        <f>L23-H23</f>
-        <v>433250.80936964368</v>
-      </c>
+      <c r="L24" s="10"/>
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
       <c r="P24" s="10"/>
@@ -14691,7 +14688,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
-      <c r="H32" s="716">
+      <c r="H32" s="590">
         <f>+H31/1000000</f>
         <v>1.8436589195408826</v>
       </c>
@@ -14700,7 +14697,7 @@
       <c r="K32" s="157"/>
       <c r="L32" s="157"/>
       <c r="M32" s="36"/>
-      <c r="N32" s="716">
+      <c r="N32" s="590">
         <f>+N31/1000000</f>
         <v>1.4601854336242732</v>
       </c>
@@ -14711,11 +14708,11 @@
       <c r="R32" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="T32" s="688" t="s">
+      <c r="T32" s="593" t="s">
         <v>53</v>
       </c>
-      <c r="U32" s="689"/>
-      <c r="V32" s="690"/>
+      <c r="U32" s="594"/>
+      <c r="V32" s="595"/>
     </row>
     <row r="33" spans="1:27" ht="10.5">
       <c r="A33" s="37"/>
@@ -14813,7 +14810,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
-      <c r="H36" s="717">
+      <c r="H36" s="591">
         <f>+H32+H34</f>
         <v>1.8436589195408826</v>
       </c>
@@ -14822,12 +14819,12 @@
       <c r="K36" s="160"/>
       <c r="L36" s="160"/>
       <c r="M36" s="3"/>
-      <c r="N36" s="717">
+      <c r="N36" s="591">
         <f>+N32+N34</f>
         <v>1.4601854336242732</v>
       </c>
-      <c r="P36" s="687"/>
-      <c r="Q36" s="687"/>
+      <c r="P36" s="592"/>
+      <c r="Q36" s="592"/>
       <c r="T36" s="31" t="s">
         <v>59</v>
       </c>
@@ -16144,10 +16141,10 @@
       </c>
     </row>
     <row r="11" spans="2:21" s="362" customFormat="1" ht="13" hidden="1">
-      <c r="B11" s="709" t="s">
+      <c r="B11" s="711" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="709"/>
+      <c r="C11" s="711"/>
       <c r="D11" s="391">
         <v>42</v>
       </c>
@@ -20611,22 +20608,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="16" thickBot="1">
-      <c r="A1" s="710" t="s">
+      <c r="A1" s="712" t="s">
         <v>256</v>
       </c>
-      <c r="B1" s="711"/>
-      <c r="C1" s="711"/>
-      <c r="D1" s="711"/>
-      <c r="E1" s="711"/>
-      <c r="F1" s="711"/>
-      <c r="G1" s="711"/>
-      <c r="H1" s="711"/>
-      <c r="I1" s="711"/>
-      <c r="J1" s="711"/>
-      <c r="K1" s="711"/>
-      <c r="L1" s="711"/>
-      <c r="M1" s="711"/>
-      <c r="N1" s="712"/>
+      <c r="B1" s="713"/>
+      <c r="C1" s="713"/>
+      <c r="D1" s="713"/>
+      <c r="E1" s="713"/>
+      <c r="F1" s="713"/>
+      <c r="G1" s="713"/>
+      <c r="H1" s="713"/>
+      <c r="I1" s="713"/>
+      <c r="J1" s="713"/>
+      <c r="K1" s="713"/>
+      <c r="L1" s="713"/>
+      <c r="M1" s="713"/>
+      <c r="N1" s="714"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="178" t="s">
@@ -21652,21 +21649,21 @@
       <c r="I34" s="358"/>
     </row>
     <row r="35" spans="1:15" ht="16" outlineLevel="1" thickBot="1">
-      <c r="A35" s="710"/>
-      <c r="B35" s="711"/>
-      <c r="C35" s="711"/>
-      <c r="D35" s="711"/>
-      <c r="E35" s="711"/>
-      <c r="F35" s="711"/>
-      <c r="G35" s="711"/>
-      <c r="H35" s="711"/>
-      <c r="I35" s="711"/>
-      <c r="J35" s="711"/>
-      <c r="K35" s="711"/>
-      <c r="L35" s="711"/>
-      <c r="M35" s="711"/>
-      <c r="N35" s="711"/>
-      <c r="O35" s="712"/>
+      <c r="A35" s="712"/>
+      <c r="B35" s="713"/>
+      <c r="C35" s="713"/>
+      <c r="D35" s="713"/>
+      <c r="E35" s="713"/>
+      <c r="F35" s="713"/>
+      <c r="G35" s="713"/>
+      <c r="H35" s="713"/>
+      <c r="I35" s="713"/>
+      <c r="J35" s="713"/>
+      <c r="K35" s="713"/>
+      <c r="L35" s="713"/>
+      <c r="M35" s="713"/>
+      <c r="N35" s="713"/>
+      <c r="O35" s="714"/>
     </row>
     <row r="36" spans="1:15" outlineLevel="1">
       <c r="A36" s="306" t="s">
@@ -23456,21 +23453,21 @@
       <c r="I91" s="186"/>
     </row>
     <row r="92" spans="1:15" ht="16" thickBot="1">
-      <c r="A92" s="713"/>
-      <c r="B92" s="714"/>
-      <c r="C92" s="714"/>
-      <c r="D92" s="714"/>
-      <c r="E92" s="714"/>
-      <c r="F92" s="714"/>
-      <c r="G92" s="714"/>
-      <c r="H92" s="714"/>
-      <c r="I92" s="714"/>
-      <c r="J92" s="714"/>
-      <c r="K92" s="714"/>
-      <c r="L92" s="714"/>
-      <c r="M92" s="714"/>
-      <c r="N92" s="714"/>
-      <c r="O92" s="715"/>
+      <c r="A92" s="715"/>
+      <c r="B92" s="716"/>
+      <c r="C92" s="716"/>
+      <c r="D92" s="716"/>
+      <c r="E92" s="716"/>
+      <c r="F92" s="716"/>
+      <c r="G92" s="716"/>
+      <c r="H92" s="716"/>
+      <c r="I92" s="716"/>
+      <c r="J92" s="716"/>
+      <c r="K92" s="716"/>
+      <c r="L92" s="716"/>
+      <c r="M92" s="716"/>
+      <c r="N92" s="716"/>
+      <c r="O92" s="717"/>
     </row>
     <row r="93" spans="1:15">
       <c r="A93" s="178"/>
@@ -23901,6 +23898,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" xsi:nil="true"/>
+    <Status xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100907921E7373C1341A3C877D189CE8922" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2036b66ca2b7955135caa708c7901a86">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xmlns:ns3="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fed2217af4f675ffeab875e34aa73a78" ns2:_="" ns3:_="">
     <xsd:import namespace="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
@@ -24143,28 +24161,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" xsi:nil="true"/>
-    <Status xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC57694E-BA35-486E-AC74-B7B624F1FDE0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12D5BE44-B07C-4182-BC7A-71E5962390BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
+    <ds:schemaRef ds:uri="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB719E29-C329-4AB1-8ED0-5CC29C0FF757}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24183,25 +24199,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12D5BE44-B07C-4182-BC7A-71E5962390BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
-    <ds:schemaRef ds:uri="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC57694E-BA35-486E-AC74-B7B624F1FDE0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{a59b6cd5-d141-4a33-8bf1-0ca04484304f}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" removed="0"/>

--- a/artifacts/Rental Specimen.xlsx
+++ b/artifacts/Rental Specimen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z0050s8t\Documents\rental-automation\artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD07F51-7080-4834-9EC6-0D26BC88ED92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28BE0EA-D0ED-4868-B8A0-9801CEFF7438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="764" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="764" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="26" r:id="rId1"/>
@@ -5618,81 +5618,270 @@
     <xf numFmtId="167" fontId="6" fillId="0" borderId="50" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="33" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="29" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5713,195 +5902,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="33" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="29" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="192" fontId="52" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7473,39 +7473,39 @@
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1">
       <c r="A1" s="51"/>
-      <c r="B1" s="665"/>
-      <c r="C1" s="666"/>
-      <c r="D1" s="666"/>
-      <c r="E1" s="666"/>
-      <c r="F1" s="666"/>
-      <c r="G1" s="666"/>
-      <c r="H1" s="666"/>
-      <c r="I1" s="666"/>
-      <c r="J1" s="667"/>
+      <c r="B1" s="655"/>
+      <c r="C1" s="656"/>
+      <c r="D1" s="656"/>
+      <c r="E1" s="656"/>
+      <c r="F1" s="656"/>
+      <c r="G1" s="656"/>
+      <c r="H1" s="656"/>
+      <c r="I1" s="656"/>
+      <c r="J1" s="657"/>
     </row>
     <row r="2" spans="1:10" ht="14.25" customHeight="1">
       <c r="A2" s="51"/>
-      <c r="B2" s="668"/>
-      <c r="C2" s="669"/>
-      <c r="D2" s="669"/>
-      <c r="E2" s="669"/>
-      <c r="F2" s="669"/>
-      <c r="G2" s="669"/>
-      <c r="H2" s="669"/>
-      <c r="I2" s="669"/>
-      <c r="J2" s="670"/>
+      <c r="B2" s="658"/>
+      <c r="C2" s="659"/>
+      <c r="D2" s="659"/>
+      <c r="E2" s="659"/>
+      <c r="F2" s="659"/>
+      <c r="G2" s="659"/>
+      <c r="H2" s="659"/>
+      <c r="I2" s="659"/>
+      <c r="J2" s="660"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A3" s="51"/>
-      <c r="B3" s="671"/>
-      <c r="C3" s="672"/>
-      <c r="D3" s="672"/>
-      <c r="E3" s="672"/>
-      <c r="F3" s="672"/>
-      <c r="G3" s="672"/>
-      <c r="H3" s="672"/>
-      <c r="I3" s="669"/>
-      <c r="J3" s="670"/>
+      <c r="B3" s="661"/>
+      <c r="C3" s="662"/>
+      <c r="D3" s="662"/>
+      <c r="E3" s="662"/>
+      <c r="F3" s="662"/>
+      <c r="G3" s="662"/>
+      <c r="H3" s="662"/>
+      <c r="I3" s="659"/>
+      <c r="J3" s="660"/>
     </row>
     <row r="4" spans="1:10" ht="13">
       <c r="A4" s="51"/>
@@ -7521,14 +7521,14 @@
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="51"/>
-      <c r="B5" s="692" t="s">
+      <c r="B5" s="680" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="693"/>
-      <c r="D5" s="693"/>
-      <c r="E5" s="693"/>
-      <c r="F5" s="693"/>
-      <c r="G5" s="694"/>
+      <c r="C5" s="681"/>
+      <c r="D5" s="681"/>
+      <c r="E5" s="681"/>
+      <c r="F5" s="681"/>
+      <c r="G5" s="682"/>
       <c r="H5" s="404"/>
       <c r="I5" s="481" t="s">
         <v>16</v>
@@ -7539,29 +7539,29 @@
     </row>
     <row r="6" spans="1:10" ht="13.5" thickBot="1">
       <c r="A6" s="51"/>
-      <c r="B6" s="695"/>
-      <c r="C6" s="696"/>
-      <c r="D6" s="697"/>
+      <c r="B6" s="683"/>
+      <c r="C6" s="684"/>
+      <c r="D6" s="685"/>
       <c r="E6" s="52"/>
-      <c r="F6" s="690">
+      <c r="F6" s="678">
         <v>10.763999999999999</v>
       </c>
-      <c r="G6" s="691"/>
+      <c r="G6" s="679"/>
       <c r="H6" s="405"/>
-      <c r="I6" s="678">
+      <c r="I6" s="669">
         <v>10.763999999999999</v>
       </c>
-      <c r="J6" s="679"/>
+      <c r="J6" s="670"/>
     </row>
     <row r="7" spans="1:10" ht="26">
       <c r="A7" s="51"/>
       <c r="B7" s="482" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="698" t="s">
+      <c r="C7" s="686" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="699"/>
+      <c r="D7" s="687"/>
       <c r="E7" s="483"/>
       <c r="F7" s="483" t="s">
         <v>303</v>
@@ -7589,23 +7589,23 @@
       <c r="C8" s="486"/>
       <c r="D8" s="487"/>
       <c r="E8" s="488"/>
-      <c r="F8" s="624" t="s">
+      <c r="F8" s="616" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="658"/>
+      <c r="G8" s="617"/>
       <c r="H8" s="404"/>
-      <c r="I8" s="659" t="s">
+      <c r="I8" s="618" t="s">
         <v>67</v>
       </c>
-      <c r="J8" s="660"/>
+      <c r="J8" s="619"/>
     </row>
     <row r="9" spans="1:10" ht="13">
       <c r="A9" s="51"/>
-      <c r="B9" s="659" t="s">
+      <c r="B9" s="618" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="658"/>
-      <c r="D9" s="625"/>
+      <c r="C9" s="617"/>
+      <c r="D9" s="633"/>
       <c r="E9" s="489"/>
       <c r="F9" s="376" t="s">
         <v>75</v>
@@ -7626,21 +7626,21 @@
       <c r="B10" s="490">
         <v>1</v>
       </c>
-      <c r="C10" s="673" t="s">
+      <c r="C10" s="663" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="632"/>
+      <c r="D10" s="664"/>
       <c r="E10" s="491"/>
-      <c r="F10" s="684" t="s">
+      <c r="F10" s="675" t="s">
         <v>299</v>
       </c>
-      <c r="G10" s="685"/>
+      <c r="G10" s="676"/>
       <c r="H10" s="404"/>
-      <c r="I10" s="680" t="str">
+      <c r="I10" s="671" t="str">
         <f>+F10</f>
         <v>Chennai</v>
       </c>
-      <c r="J10" s="681"/>
+      <c r="J10" s="672"/>
     </row>
     <row r="11" spans="1:10" ht="28.5" customHeight="1">
       <c r="A11" s="51"/>
@@ -7648,19 +7648,19 @@
         <f>1+B10</f>
         <v>2</v>
       </c>
-      <c r="C11" s="674" t="s">
+      <c r="C11" s="665" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="675"/>
+      <c r="D11" s="666"/>
       <c r="E11" s="50"/>
-      <c r="F11" s="684"/>
-      <c r="G11" s="685"/>
+      <c r="F11" s="675"/>
+      <c r="G11" s="676"/>
       <c r="H11" s="404"/>
-      <c r="I11" s="682">
+      <c r="I11" s="673">
         <f>+F11</f>
         <v>0</v>
       </c>
-      <c r="J11" s="683"/>
+      <c r="J11" s="674"/>
     </row>
     <row r="12" spans="1:10" ht="27.75" customHeight="1">
       <c r="A12" s="51"/>
@@ -7668,19 +7668,19 @@
         <f>1+B11</f>
         <v>3</v>
       </c>
-      <c r="C12" s="618" t="s">
+      <c r="C12" s="626" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="617"/>
+      <c r="D12" s="627"/>
       <c r="E12" s="492"/>
-      <c r="F12" s="686"/>
-      <c r="G12" s="687"/>
+      <c r="F12" s="654"/>
+      <c r="G12" s="649"/>
       <c r="H12" s="404"/>
-      <c r="I12" s="700">
+      <c r="I12" s="650">
         <f>+F12</f>
         <v>0</v>
       </c>
-      <c r="J12" s="701"/>
+      <c r="J12" s="651"/>
     </row>
     <row r="13" spans="1:10" ht="15.9" customHeight="1">
       <c r="A13" s="51"/>
@@ -7688,16 +7688,16 @@
         <f t="shared" ref="B13:B30" si="0">1+B12</f>
         <v>4</v>
       </c>
-      <c r="C13" s="618" t="s">
+      <c r="C13" s="626" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="617"/>
+      <c r="D13" s="627"/>
       <c r="E13" s="50"/>
-      <c r="F13" s="689"/>
-      <c r="G13" s="687"/>
+      <c r="F13" s="648"/>
+      <c r="G13" s="649"/>
       <c r="H13" s="404"/>
-      <c r="I13" s="700"/>
-      <c r="J13" s="701"/>
+      <c r="I13" s="650"/>
+      <c r="J13" s="651"/>
     </row>
     <row r="14" spans="1:10" ht="48" customHeight="1">
       <c r="A14" s="51"/>
@@ -7705,21 +7705,21 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="676" t="s">
+      <c r="C14" s="667" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="677"/>
+      <c r="D14" s="668"/>
       <c r="E14" s="476"/>
-      <c r="F14" s="686" t="s">
+      <c r="F14" s="654" t="s">
         <v>300</v>
       </c>
-      <c r="G14" s="688"/>
+      <c r="G14" s="677"/>
       <c r="H14" s="404"/>
-      <c r="I14" s="700" t="str">
+      <c r="I14" s="650" t="str">
         <f>+F14</f>
         <v>6th floor</v>
       </c>
-      <c r="J14" s="701"/>
+      <c r="J14" s="651"/>
     </row>
     <row r="15" spans="1:10" ht="51.75" customHeight="1">
       <c r="A15" s="51"/>
@@ -7727,19 +7727,19 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="618" t="s">
+      <c r="C15" s="626" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="617"/>
+      <c r="D15" s="627"/>
       <c r="E15" s="58"/>
-      <c r="F15" s="624"/>
-      <c r="G15" s="658"/>
+      <c r="F15" s="616"/>
+      <c r="G15" s="617"/>
       <c r="H15" s="404"/>
-      <c r="I15" s="659">
+      <c r="I15" s="618">
         <f>+F15</f>
         <v>0</v>
       </c>
-      <c r="J15" s="660"/>
+      <c r="J15" s="619"/>
     </row>
     <row r="16" spans="1:10" ht="15.9" customHeight="1">
       <c r="A16" s="51"/>
@@ -7747,16 +7747,16 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="618" t="s">
+      <c r="C16" s="626" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="617"/>
+      <c r="D16" s="627"/>
       <c r="E16" s="58"/>
-      <c r="F16" s="689"/>
-      <c r="G16" s="687"/>
+      <c r="F16" s="648"/>
+      <c r="G16" s="649"/>
       <c r="H16" s="404"/>
-      <c r="I16" s="700"/>
-      <c r="J16" s="701"/>
+      <c r="I16" s="650"/>
+      <c r="J16" s="651"/>
     </row>
     <row r="17" spans="1:10" ht="15.9" customHeight="1">
       <c r="A17" s="51"/>
@@ -7764,21 +7764,21 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="618" t="s">
+      <c r="C17" s="626" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="617"/>
+      <c r="D17" s="627"/>
       <c r="E17" s="58"/>
-      <c r="F17" s="686" t="s">
+      <c r="F17" s="654" t="s">
         <v>85</v>
       </c>
-      <c r="G17" s="687"/>
+      <c r="G17" s="649"/>
       <c r="H17" s="404"/>
-      <c r="I17" s="700" t="str">
+      <c r="I17" s="650" t="str">
         <f>+F17</f>
         <v>Warm Shell</v>
       </c>
-      <c r="J17" s="701"/>
+      <c r="J17" s="651"/>
     </row>
     <row r="18" spans="1:10" ht="48" customHeight="1">
       <c r="A18" s="51"/>
@@ -7786,22 +7786,22 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="618" t="s">
+      <c r="C18" s="626" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="617"/>
+      <c r="D18" s="627"/>
       <c r="E18" s="163"/>
-      <c r="F18" s="624">
+      <c r="F18" s="616">
         <f>F15</f>
         <v>0</v>
       </c>
-      <c r="G18" s="658"/>
+      <c r="G18" s="617"/>
       <c r="H18" s="404"/>
-      <c r="I18" s="659">
+      <c r="I18" s="618">
         <f>+F18</f>
         <v>0</v>
       </c>
-      <c r="J18" s="660"/>
+      <c r="J18" s="619"/>
     </row>
     <row r="19" spans="1:10" ht="15.9" customHeight="1">
       <c r="A19" s="51"/>
@@ -7809,16 +7809,16 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="618" t="s">
+      <c r="C19" s="626" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="617"/>
+      <c r="D19" s="627"/>
       <c r="E19" s="163"/>
-      <c r="F19" s="689"/>
-      <c r="G19" s="687"/>
+      <c r="F19" s="648"/>
+      <c r="G19" s="649"/>
       <c r="H19" s="404"/>
-      <c r="I19" s="700"/>
-      <c r="J19" s="701"/>
+      <c r="I19" s="650"/>
+      <c r="J19" s="651"/>
     </row>
     <row r="20" spans="1:10" ht="15.9" customHeight="1">
       <c r="A20" s="51"/>
@@ -7826,10 +7826,10 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="616" t="s">
+      <c r="C20" s="620" t="s">
         <v>88</v>
       </c>
-      <c r="D20" s="617"/>
+      <c r="D20" s="627"/>
       <c r="E20" s="494"/>
       <c r="F20" s="56"/>
       <c r="G20" s="388"/>
@@ -7849,10 +7849,10 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="618" t="s">
+      <c r="C21" s="626" t="s">
         <v>89</v>
       </c>
-      <c r="D21" s="617"/>
+      <c r="D21" s="627"/>
       <c r="E21" s="494"/>
       <c r="F21" s="56">
         <f>Main!B3</f>
@@ -7878,10 +7878,10 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="616" t="s">
+      <c r="C22" s="620" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="617"/>
+      <c r="D22" s="627"/>
       <c r="E22" s="494"/>
       <c r="F22" s="56">
         <v>0</v>
@@ -7905,10 +7905,10 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="618" t="s">
+      <c r="C23" s="626" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="617"/>
+      <c r="D23" s="627"/>
       <c r="E23" s="494"/>
       <c r="F23" s="56">
         <f>+F21+F22</f>
@@ -7934,10 +7934,10 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="618" t="s">
+      <c r="C24" s="626" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="617"/>
+      <c r="D24" s="627"/>
       <c r="E24" s="59"/>
       <c r="F24" s="56"/>
       <c r="G24" s="388">
@@ -7960,10 +7960,10 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="618" t="s">
+      <c r="C25" s="626" t="s">
         <v>93</v>
       </c>
-      <c r="D25" s="617"/>
+      <c r="D25" s="627"/>
       <c r="E25" s="59"/>
       <c r="F25" s="56">
         <v>0</v>
@@ -7988,10 +7988,10 @@
         <f>1+B25</f>
         <v>17</v>
       </c>
-      <c r="C26" s="618" t="s">
+      <c r="C26" s="626" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="617"/>
+      <c r="D26" s="627"/>
       <c r="E26" s="60"/>
       <c r="F26" s="61">
         <f>F25/F23</f>
@@ -8017,10 +8017,10 @@
         <f>1+B26</f>
         <v>18</v>
       </c>
-      <c r="C27" s="616" t="s">
+      <c r="C27" s="620" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="617"/>
+      <c r="D27" s="627"/>
       <c r="E27" s="58"/>
       <c r="F27" s="293">
         <f>'CAPEX and PM'!E3</f>
@@ -8046,10 +8046,10 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="616" t="s">
+      <c r="C28" s="620" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="617"/>
+      <c r="D28" s="627"/>
       <c r="E28" s="64"/>
       <c r="F28" s="64">
         <f>Main!B12</f>
@@ -8075,10 +8075,10 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="616" t="s">
+      <c r="C29" s="620" t="s">
         <v>97</v>
       </c>
-      <c r="D29" s="617"/>
+      <c r="D29" s="627"/>
       <c r="E29" s="64"/>
       <c r="F29" s="60">
         <f>Main!B13</f>
@@ -8104,10 +8104,10 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="618" t="s">
+      <c r="C30" s="626" t="s">
         <v>98</v>
       </c>
-      <c r="D30" s="617"/>
+      <c r="D30" s="627"/>
       <c r="E30" s="58"/>
       <c r="F30" s="56">
         <v>0</v>
@@ -8128,11 +8128,11 @@
     </row>
     <row r="31" spans="1:10" ht="15.9" customHeight="1">
       <c r="A31" s="51"/>
-      <c r="B31" s="702" t="s">
+      <c r="B31" s="645" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="703"/>
-      <c r="D31" s="704"/>
+      <c r="C31" s="646"/>
+      <c r="D31" s="647"/>
       <c r="E31" s="497"/>
       <c r="F31" s="376" t="s">
         <v>75</v>
@@ -8153,10 +8153,10 @@
       <c r="B32" s="162">
         <v>1</v>
       </c>
-      <c r="C32" s="616" t="s">
+      <c r="C32" s="620" t="s">
         <v>100</v>
       </c>
-      <c r="D32" s="617"/>
+      <c r="D32" s="627"/>
       <c r="E32" s="59"/>
       <c r="F32" s="56">
         <f>Main!B9/(Main!B3*Main!B7)</f>
@@ -8182,10 +8182,10 @@
         <f>1+B32</f>
         <v>2</v>
       </c>
-      <c r="C33" s="616" t="s">
+      <c r="C33" s="620" t="s">
         <v>101</v>
       </c>
-      <c r="D33" s="617"/>
+      <c r="D33" s="627"/>
       <c r="E33" s="59"/>
       <c r="F33" s="56">
         <v>0</v>
@@ -8209,10 +8209,10 @@
         <f t="shared" ref="B34:B47" si="1">1+B33</f>
         <v>3</v>
       </c>
-      <c r="C34" s="616" t="s">
+      <c r="C34" s="620" t="s">
         <v>102</v>
       </c>
-      <c r="D34" s="617"/>
+      <c r="D34" s="627"/>
       <c r="E34" s="59"/>
       <c r="F34" s="56">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="C35" s="618" t="s">
+      <c r="C35" s="626" t="s">
         <v>103</v>
       </c>
-      <c r="D35" s="617"/>
+      <c r="D35" s="627"/>
       <c r="E35" s="498"/>
       <c r="F35" s="68">
         <v>0</v>
@@ -8262,10 +8262,10 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="C36" s="616" t="s">
+      <c r="C36" s="620" t="s">
         <v>104</v>
       </c>
-      <c r="D36" s="617"/>
+      <c r="D36" s="627"/>
       <c r="E36" s="498"/>
       <c r="F36" s="70">
         <f>'Lease Rent'!H37</f>
@@ -8291,10 +8291,10 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="C37" s="616" t="s">
+      <c r="C37" s="620" t="s">
         <v>105</v>
       </c>
-      <c r="D37" s="617"/>
+      <c r="D37" s="627"/>
       <c r="E37" s="498"/>
       <c r="F37" s="70"/>
       <c r="G37" s="204">
@@ -8311,10 +8311,10 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="C38" s="616" t="s">
+      <c r="C38" s="620" t="s">
         <v>106</v>
       </c>
-      <c r="D38" s="617"/>
+      <c r="D38" s="627"/>
       <c r="E38" s="71"/>
       <c r="F38" s="70">
         <f>'Lease Rent'!J31</f>
@@ -8340,10 +8340,10 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="C39" s="616" t="s">
+      <c r="C39" s="620" t="s">
         <v>107</v>
       </c>
-      <c r="D39" s="617"/>
+      <c r="D39" s="627"/>
       <c r="E39" s="498"/>
       <c r="F39" s="70">
         <f>F36</f>
@@ -8369,10 +8369,10 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="C40" s="616" t="s">
+      <c r="C40" s="620" t="s">
         <v>108</v>
       </c>
-      <c r="D40" s="617"/>
+      <c r="D40" s="627"/>
       <c r="E40" s="498"/>
       <c r="F40" s="70">
         <v>0</v>
@@ -8397,10 +8397,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="C41" s="616" t="s">
+      <c r="C41" s="620" t="s">
         <v>109</v>
       </c>
-      <c r="D41" s="617"/>
+      <c r="D41" s="627"/>
       <c r="E41" s="58"/>
       <c r="F41" s="114">
         <f>F38</f>
@@ -8426,10 +8426,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="C42" s="618" t="s">
+      <c r="C42" s="626" t="s">
         <v>110</v>
       </c>
-      <c r="D42" s="617"/>
+      <c r="D42" s="627"/>
       <c r="E42" s="59"/>
       <c r="F42" s="109">
         <v>0</v>
@@ -8454,10 +8454,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="C43" s="618" t="s">
+      <c r="C43" s="626" t="s">
         <v>111</v>
       </c>
-      <c r="D43" s="617"/>
+      <c r="D43" s="627"/>
       <c r="E43" s="73"/>
       <c r="F43" s="68">
         <v>0</v>
@@ -8482,10 +8482,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="C44" s="618" t="s">
+      <c r="C44" s="626" t="s">
         <v>112</v>
       </c>
-      <c r="D44" s="617"/>
+      <c r="D44" s="627"/>
       <c r="E44" s="59"/>
       <c r="F44" s="56">
         <f>'Lease Rent'!C22</f>
@@ -8511,10 +8511,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="C45" s="616" t="s">
+      <c r="C45" s="620" t="s">
         <v>113</v>
       </c>
-      <c r="D45" s="617"/>
+      <c r="D45" s="627"/>
       <c r="E45" s="59"/>
       <c r="F45" s="109">
         <v>0</v>
@@ -8536,10 +8536,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="C46" s="618" t="s">
+      <c r="C46" s="626" t="s">
         <v>111</v>
       </c>
-      <c r="D46" s="617"/>
+      <c r="D46" s="627"/>
       <c r="E46" s="59"/>
       <c r="F46" s="56">
         <f>'Lease Rent'!D23</f>
@@ -8556,10 +8556,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="C47" s="618" t="s">
+      <c r="C47" s="626" t="s">
         <v>112</v>
       </c>
-      <c r="D47" s="617"/>
+      <c r="D47" s="627"/>
       <c r="E47" s="59"/>
       <c r="F47" s="56">
         <f>'Lease Rent'!C23</f>
@@ -8572,46 +8572,46 @@
     </row>
     <row r="48" spans="1:10" ht="28.5" customHeight="1">
       <c r="A48" s="51"/>
-      <c r="B48" s="663">
+      <c r="B48" s="690">
         <f>1+B47</f>
         <v>17</v>
       </c>
-      <c r="C48" s="616" t="s">
+      <c r="C48" s="620" t="s">
         <v>114</v>
       </c>
-      <c r="D48" s="617"/>
+      <c r="D48" s="627"/>
       <c r="E48" s="73"/>
-      <c r="F48" s="707" t="str">
+      <c r="F48" s="636" t="str">
         <f>Main!B14</f>
         <v>15% every 3 years</v>
       </c>
-      <c r="G48" s="708"/>
+      <c r="G48" s="637"/>
       <c r="H48" s="404"/>
-      <c r="I48" s="700" t="str">
+      <c r="I48" s="650" t="str">
         <f>+F48</f>
         <v>15% every 3 years</v>
       </c>
-      <c r="J48" s="701"/>
+      <c r="J48" s="651"/>
     </row>
     <row r="49" spans="1:18" ht="15.9" customHeight="1">
       <c r="A49" s="51"/>
-      <c r="B49" s="664"/>
-      <c r="C49" s="616" t="s">
+      <c r="B49" s="691"/>
+      <c r="C49" s="620" t="s">
         <v>115</v>
       </c>
-      <c r="D49" s="617"/>
+      <c r="D49" s="627"/>
       <c r="E49" s="73"/>
-      <c r="F49" s="707" t="str">
+      <c r="F49" s="636" t="str">
         <f>Main!B15</f>
         <v>5% every years</v>
       </c>
-      <c r="G49" s="708"/>
+      <c r="G49" s="637"/>
       <c r="H49" s="404"/>
-      <c r="I49" s="705" t="str">
+      <c r="I49" s="652" t="str">
         <f t="shared" ref="I49:I56" si="2">F49</f>
         <v>5% every years</v>
       </c>
-      <c r="J49" s="706"/>
+      <c r="J49" s="653"/>
     </row>
     <row r="50" spans="1:18" ht="15.9" customHeight="1">
       <c r="A50" s="51"/>
@@ -8619,22 +8619,22 @@
         <f>1+B48</f>
         <v>18</v>
       </c>
-      <c r="C50" s="618" t="s">
+      <c r="C50" s="626" t="s">
         <v>116</v>
       </c>
-      <c r="D50" s="617"/>
+      <c r="D50" s="627"/>
       <c r="E50" s="73"/>
-      <c r="F50" s="654">
+      <c r="F50" s="634">
         <f>'Lease Rent'!B31</f>
         <v>46023</v>
       </c>
-      <c r="G50" s="655"/>
+      <c r="G50" s="635"/>
       <c r="H50" s="404"/>
-      <c r="I50" s="656">
+      <c r="I50" s="643">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J50" s="657"/>
+      <c r="J50" s="644"/>
     </row>
     <row r="51" spans="1:18" ht="15.9" customHeight="1">
       <c r="A51" s="51"/>
@@ -8642,22 +8642,22 @@
         <f t="shared" ref="B51:B57" si="3">1+B50</f>
         <v>19</v>
       </c>
-      <c r="C51" s="616" t="s">
+      <c r="C51" s="620" t="s">
         <v>117</v>
       </c>
-      <c r="D51" s="617"/>
+      <c r="D51" s="627"/>
       <c r="E51" s="73"/>
-      <c r="F51" s="654">
+      <c r="F51" s="634">
         <f>'Lease Rent'!C102</f>
         <v>48213</v>
       </c>
-      <c r="G51" s="655"/>
+      <c r="G51" s="635"/>
       <c r="H51" s="404"/>
-      <c r="I51" s="656">
+      <c r="I51" s="643">
         <f>F51</f>
         <v>48213</v>
       </c>
-      <c r="J51" s="657"/>
+      <c r="J51" s="644"/>
     </row>
     <row r="52" spans="1:18" ht="15.9" customHeight="1">
       <c r="A52" s="51"/>
@@ -8665,22 +8665,22 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="C52" s="616" t="s">
+      <c r="C52" s="620" t="s">
         <v>118</v>
       </c>
-      <c r="D52" s="626"/>
+      <c r="D52" s="621"/>
       <c r="E52" s="73"/>
-      <c r="F52" s="654">
+      <c r="F52" s="634">
         <f>F50</f>
         <v>46023</v>
       </c>
-      <c r="G52" s="655"/>
+      <c r="G52" s="635"/>
       <c r="H52" s="404"/>
-      <c r="I52" s="656">
+      <c r="I52" s="643">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J52" s="657"/>
+      <c r="J52" s="644"/>
     </row>
     <row r="53" spans="1:18" ht="15.9" customHeight="1">
       <c r="A53" s="51"/>
@@ -8688,21 +8688,21 @@
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="C53" s="616" t="s">
+      <c r="C53" s="620" t="s">
         <v>119</v>
       </c>
-      <c r="D53" s="626"/>
+      <c r="D53" s="621"/>
       <c r="E53" s="73"/>
-      <c r="F53" s="624">
-        <v>0</v>
-      </c>
-      <c r="G53" s="658"/>
+      <c r="F53" s="616">
+        <v>0</v>
+      </c>
+      <c r="G53" s="617"/>
       <c r="H53" s="404"/>
-      <c r="I53" s="659">
+      <c r="I53" s="618">
         <f>+F53</f>
         <v>0</v>
       </c>
-      <c r="J53" s="660"/>
+      <c r="J53" s="619"/>
     </row>
     <row r="54" spans="1:18" ht="15.9" customHeight="1">
       <c r="A54" s="51"/>
@@ -8710,10 +8710,10 @@
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="C54" s="618" t="s">
+      <c r="C54" s="626" t="s">
         <v>120</v>
       </c>
-      <c r="D54" s="617"/>
+      <c r="D54" s="627"/>
       <c r="E54" s="58"/>
       <c r="F54" s="56">
         <f>(F51-F50)/365*12</f>
@@ -8740,10 +8740,10 @@
         <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="C55" s="618" t="s">
+      <c r="C55" s="626" t="s">
         <v>121</v>
       </c>
-      <c r="D55" s="617"/>
+      <c r="D55" s="627"/>
       <c r="E55" s="71"/>
       <c r="F55" s="56">
         <v>0</v>
@@ -8769,10 +8769,10 @@
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="C56" s="618" t="s">
+      <c r="C56" s="626" t="s">
         <v>122</v>
       </c>
-      <c r="D56" s="617"/>
+      <c r="D56" s="627"/>
       <c r="E56" s="71"/>
       <c r="F56" s="302" t="s">
         <v>68</v>
@@ -8798,10 +8798,10 @@
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="C57" s="618" t="s">
+      <c r="C57" s="626" t="s">
         <v>123</v>
       </c>
-      <c r="D57" s="617"/>
+      <c r="D57" s="627"/>
       <c r="E57" s="71"/>
       <c r="F57" s="56"/>
       <c r="G57" s="388"/>
@@ -8816,23 +8816,23 @@
       <c r="C58" s="74"/>
       <c r="D58" s="74"/>
       <c r="E58" s="58"/>
-      <c r="F58" s="624" t="s">
+      <c r="F58" s="616" t="s">
         <v>73</v>
       </c>
-      <c r="G58" s="658"/>
+      <c r="G58" s="617"/>
       <c r="H58" s="404"/>
-      <c r="I58" s="659" t="s">
+      <c r="I58" s="618" t="s">
         <v>67</v>
       </c>
-      <c r="J58" s="660"/>
+      <c r="J58" s="619"/>
     </row>
     <row r="59" spans="1:18" ht="15.9" customHeight="1">
       <c r="A59" s="51"/>
-      <c r="B59" s="661" t="s">
+      <c r="B59" s="688" t="s">
         <v>124</v>
       </c>
-      <c r="C59" s="662"/>
-      <c r="D59" s="662"/>
+      <c r="C59" s="689"/>
+      <c r="D59" s="689"/>
       <c r="E59" s="497"/>
       <c r="F59" s="376" t="s">
         <v>75</v>
@@ -8853,10 +8853,10 @@
       <c r="B60" s="162">
         <v>1</v>
       </c>
-      <c r="C60" s="616" t="s">
+      <c r="C60" s="620" t="s">
         <v>125</v>
       </c>
-      <c r="D60" s="617"/>
+      <c r="D60" s="627"/>
       <c r="E60" s="499"/>
       <c r="F60" s="70">
         <f>C220/F21/F54</f>
@@ -8882,10 +8882,10 @@
         <f>1+B60</f>
         <v>2</v>
       </c>
-      <c r="C61" s="616" t="s">
+      <c r="C61" s="620" t="s">
         <v>126</v>
       </c>
-      <c r="D61" s="617"/>
+      <c r="D61" s="627"/>
       <c r="E61" s="499"/>
       <c r="F61" s="70">
         <v>0</v>
@@ -8909,10 +8909,10 @@
         <f t="shared" ref="B62:B83" si="4">1+B61</f>
         <v>3</v>
       </c>
-      <c r="C62" s="619" t="s">
+      <c r="C62" s="622" t="s">
         <v>127</v>
       </c>
-      <c r="D62" s="620"/>
+      <c r="D62" s="623"/>
       <c r="E62" s="75"/>
       <c r="F62" s="76">
         <f>F60+F61</f>
@@ -8938,10 +8938,10 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="C63" s="616" t="s">
+      <c r="C63" s="620" t="s">
         <v>321</v>
       </c>
-      <c r="D63" s="617"/>
+      <c r="D63" s="627"/>
       <c r="E63" s="56"/>
       <c r="F63" s="54">
         <f>F62*F21</f>
@@ -8967,10 +8967,10 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="C64" s="616" t="s">
+      <c r="C64" s="620" t="s">
         <v>128</v>
       </c>
-      <c r="D64" s="617"/>
+      <c r="D64" s="627"/>
       <c r="E64" s="56"/>
       <c r="F64" s="70">
         <f>I220/F21/F54</f>
@@ -8996,10 +8996,10 @@
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="C65" s="618" t="s">
+      <c r="C65" s="626" t="s">
         <v>322</v>
       </c>
-      <c r="D65" s="617"/>
+      <c r="D65" s="627"/>
       <c r="E65" s="71"/>
       <c r="F65" s="54">
         <f>+F64*F21</f>
@@ -9025,10 +9025,10 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="C66" s="618" t="s">
+      <c r="C66" s="626" t="s">
         <v>323</v>
       </c>
-      <c r="D66" s="617"/>
+      <c r="D66" s="627"/>
       <c r="E66" s="59"/>
       <c r="F66" s="56">
         <f>(+G220/F54)</f>
@@ -9054,10 +9054,10 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="C67" s="618" t="s">
+      <c r="C67" s="626" t="s">
         <v>129</v>
       </c>
-      <c r="D67" s="617"/>
+      <c r="D67" s="627"/>
       <c r="E67" s="56"/>
       <c r="F67" s="56">
         <f>Main!B9</f>
@@ -9083,10 +9083,10 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="C68" s="618" t="s">
+      <c r="C68" s="626" t="s">
         <v>130</v>
       </c>
-      <c r="D68" s="617"/>
+      <c r="D68" s="627"/>
       <c r="E68" s="56"/>
       <c r="F68" s="56">
         <v>0</v>
@@ -9111,10 +9111,10 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="C69" s="616" t="s">
+      <c r="C69" s="620" t="s">
         <v>131</v>
       </c>
-      <c r="D69" s="617"/>
+      <c r="D69" s="627"/>
       <c r="E69" s="56"/>
       <c r="F69" s="56">
         <v>500000</v>
@@ -9139,10 +9139,10 @@
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="C70" s="618" t="s">
+      <c r="C70" s="626" t="s">
         <v>132</v>
       </c>
-      <c r="D70" s="617"/>
+      <c r="D70" s="627"/>
       <c r="E70" s="56"/>
       <c r="F70" s="54">
         <v>0</v>
@@ -9164,10 +9164,10 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="C71" s="618" t="s">
+      <c r="C71" s="626" t="s">
         <v>133</v>
       </c>
-      <c r="D71" s="617"/>
+      <c r="D71" s="627"/>
       <c r="E71" s="56"/>
       <c r="F71" s="54">
         <f>F38*F23*F33</f>
@@ -9193,10 +9193,10 @@
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="C72" s="618" t="s">
+      <c r="C72" s="626" t="s">
         <v>134</v>
       </c>
-      <c r="D72" s="617"/>
+      <c r="D72" s="627"/>
       <c r="E72" s="56"/>
       <c r="F72" s="56">
         <v>0</v>
@@ -9221,10 +9221,10 @@
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="C73" s="616" t="s">
+      <c r="C73" s="620" t="s">
         <v>135</v>
       </c>
-      <c r="D73" s="617"/>
+      <c r="D73" s="627"/>
       <c r="E73" s="498"/>
       <c r="F73" s="68">
         <f>+F35*F63</f>
@@ -9257,7 +9257,7 @@
       <c r="E74" s="498"/>
       <c r="F74" s="356">
         <f>F119</f>
-        <v>654</v>
+        <v>699.78</v>
       </c>
       <c r="G74" s="460">
         <v>0</v>
@@ -9265,11 +9265,11 @@
       <c r="H74" s="404"/>
       <c r="I74" s="138">
         <f>+F74/J5</f>
-        <v>6.227385259950486</v>
+        <v>6.6633022281470193</v>
       </c>
       <c r="J74" s="57">
         <f t="shared" si="6"/>
-        <v>67.031574938107028</v>
+        <v>71.72378518377451</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="15.9" customHeight="1">
@@ -9278,10 +9278,10 @@
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="C75" s="616" t="s">
+      <c r="C75" s="620" t="s">
         <v>137</v>
       </c>
-      <c r="D75" s="617"/>
+      <c r="D75" s="627"/>
       <c r="E75" s="59"/>
       <c r="F75" s="56">
         <f>+F77/F23</f>
@@ -9307,10 +9307,10 @@
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="C76" s="616" t="s">
+      <c r="C76" s="620" t="s">
         <v>138</v>
       </c>
-      <c r="D76" s="617"/>
+      <c r="D76" s="627"/>
       <c r="E76" s="71"/>
       <c r="F76" s="51"/>
       <c r="G76" s="493"/>
@@ -9330,10 +9330,10 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="C77" s="616" t="s">
+      <c r="C77" s="620" t="s">
         <v>139</v>
       </c>
-      <c r="D77" s="617"/>
+      <c r="D77" s="627"/>
       <c r="E77" s="71"/>
       <c r="F77" s="56">
         <f>'CAPEX and PM'!B6</f>
@@ -9359,10 +9359,10 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="C78" s="616" t="s">
+      <c r="C78" s="620" t="s">
         <v>140</v>
       </c>
-      <c r="D78" s="617"/>
+      <c r="D78" s="627"/>
       <c r="E78" s="71"/>
       <c r="F78" s="56">
         <f>'CAPEX and PM'!B37</f>
@@ -9388,10 +9388,10 @@
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="C79" s="616" t="s">
+      <c r="C79" s="620" t="s">
         <v>141</v>
       </c>
-      <c r="D79" s="617"/>
+      <c r="D79" s="627"/>
       <c r="E79" s="71"/>
       <c r="F79" s="56">
         <f>+'CAPEX and PM'!B95</f>
@@ -9417,10 +9417,10 @@
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="C80" s="616" t="s">
+      <c r="C80" s="620" t="s">
         <v>142</v>
       </c>
-      <c r="D80" s="617"/>
+      <c r="D80" s="627"/>
       <c r="E80" s="71"/>
       <c r="F80" s="56"/>
       <c r="G80" s="388"/>
@@ -9440,10 +9440,10 @@
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="C81" s="616" t="s">
+      <c r="C81" s="620" t="s">
         <v>143</v>
       </c>
-      <c r="D81" s="626"/>
+      <c r="D81" s="621"/>
       <c r="E81" s="71"/>
       <c r="F81" s="56"/>
       <c r="G81" s="388"/>
@@ -9463,10 +9463,10 @@
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="C82" s="616" t="s">
+      <c r="C82" s="620" t="s">
         <v>144</v>
       </c>
-      <c r="D82" s="617"/>
+      <c r="D82" s="627"/>
       <c r="E82" s="59"/>
       <c r="F82" s="56">
         <f>+G207</f>
@@ -9492,10 +9492,10 @@
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="C83" s="616" t="s">
+      <c r="C83" s="620" t="s">
         <v>324</v>
       </c>
-      <c r="D83" s="617"/>
+      <c r="D83" s="627"/>
       <c r="E83" s="498"/>
       <c r="F83" s="56">
         <f>+F30</f>
@@ -9528,11 +9528,11 @@
     </row>
     <row r="85" spans="1:24" ht="15.9" customHeight="1">
       <c r="A85" s="51"/>
-      <c r="B85" s="638" t="s">
+      <c r="B85" s="628" t="s">
         <v>145</v>
       </c>
-      <c r="C85" s="639"/>
-      <c r="D85" s="640"/>
+      <c r="C85" s="629"/>
+      <c r="D85" s="630"/>
       <c r="E85" s="389"/>
       <c r="F85" s="161" t="s">
         <v>75</v>
@@ -9553,10 +9553,10 @@
       <c r="B86" s="162">
         <v>1</v>
       </c>
-      <c r="C86" s="616" t="s">
+      <c r="C86" s="620" t="s">
         <v>146</v>
       </c>
-      <c r="D86" s="617"/>
+      <c r="D86" s="627"/>
       <c r="E86" s="71"/>
       <c r="F86" s="70">
         <f>+F62</f>
@@ -9585,10 +9585,10 @@
         <f>1+B86</f>
         <v>2</v>
       </c>
-      <c r="C87" s="618" t="s">
+      <c r="C87" s="626" t="s">
         <v>147</v>
       </c>
-      <c r="D87" s="617"/>
+      <c r="D87" s="627"/>
       <c r="E87" s="73"/>
       <c r="F87" s="56">
         <v>0</v>
@@ -9611,10 +9611,10 @@
         <f t="shared" ref="B88:B94" si="7">+B87+1</f>
         <v>3</v>
       </c>
-      <c r="C88" s="618" t="s">
+      <c r="C88" s="626" t="s">
         <v>148</v>
       </c>
-      <c r="D88" s="617"/>
+      <c r="D88" s="627"/>
       <c r="E88" s="73"/>
       <c r="F88" s="70">
         <f>(F66/F23)</f>
@@ -9642,10 +9642,10 @@
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="C89" s="618" t="s">
+      <c r="C89" s="626" t="s">
         <v>149</v>
       </c>
-      <c r="D89" s="617"/>
+      <c r="D89" s="627"/>
       <c r="E89" s="73"/>
       <c r="F89" s="66">
         <f>'Security Deposit'!C17</f>
@@ -9673,10 +9673,10 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="C90" s="618" t="s">
+      <c r="C90" s="626" t="s">
         <v>289</v>
       </c>
-      <c r="D90" s="617"/>
+      <c r="D90" s="627"/>
       <c r="E90" s="73"/>
       <c r="F90" s="202">
         <f>+F64</f>
@@ -9704,10 +9704,10 @@
         <f>+B89+1</f>
         <v>5</v>
       </c>
-      <c r="C91" s="618" t="s">
+      <c r="C91" s="626" t="s">
         <v>150</v>
       </c>
-      <c r="D91" s="617"/>
+      <c r="D91" s="627"/>
       <c r="E91" s="73"/>
       <c r="F91" s="66">
         <f>(+F83/F21/F54)</f>
@@ -9734,10 +9734,10 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="C92" s="618" t="s">
+      <c r="C92" s="626" t="s">
         <v>151</v>
       </c>
-      <c r="D92" s="617"/>
+      <c r="D92" s="627"/>
       <c r="E92" s="73"/>
       <c r="F92" s="66">
         <f>F82/F21/F54</f>
@@ -9765,10 +9765,10 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="C93" s="616" t="s">
+      <c r="C93" s="620" t="s">
         <v>152</v>
       </c>
-      <c r="D93" s="617"/>
+      <c r="D93" s="627"/>
       <c r="E93" s="71"/>
       <c r="F93" s="66">
         <f>+G93/F6</f>
@@ -9796,10 +9796,10 @@
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="C94" s="619" t="s">
+      <c r="C94" s="622" t="s">
         <v>69</v>
       </c>
-      <c r="D94" s="620"/>
+      <c r="D94" s="623"/>
       <c r="E94" s="78"/>
       <c r="F94" s="213">
         <f>SUM(F86:F93)</f>
@@ -9824,8 +9824,8 @@
     <row r="95" spans="1:24" ht="15.9" customHeight="1">
       <c r="A95" s="51"/>
       <c r="B95" s="381"/>
-      <c r="C95" s="658"/>
-      <c r="D95" s="658"/>
+      <c r="C95" s="617"/>
+      <c r="D95" s="617"/>
       <c r="E95" s="84"/>
       <c r="F95" s="85"/>
       <c r="G95" s="85"/>
@@ -9835,11 +9835,11 @@
     </row>
     <row r="96" spans="1:24" ht="15.9" customHeight="1">
       <c r="A96" s="51"/>
-      <c r="B96" s="621" t="s">
+      <c r="B96" s="624" t="s">
         <v>153</v>
       </c>
-      <c r="C96" s="622"/>
-      <c r="D96" s="622"/>
+      <c r="C96" s="625"/>
+      <c r="D96" s="625"/>
       <c r="E96" s="87"/>
       <c r="F96" s="161" t="s">
         <v>75</v>
@@ -9861,11 +9861,11 @@
       <c r="B97" s="162">
         <v>1</v>
       </c>
-      <c r="C97" s="618" t="str">
+      <c r="C97" s="626" t="str">
         <f>+C76</f>
         <v>Siemens Standard Fitout (Existing)</v>
       </c>
-      <c r="D97" s="617"/>
+      <c r="D97" s="627"/>
       <c r="E97" s="88"/>
       <c r="F97" s="66">
         <v>0</v>
@@ -9891,11 +9891,11 @@
         <f t="shared" ref="B98:B103" si="8">+B97+1</f>
         <v>2</v>
       </c>
-      <c r="C98" s="618" t="str">
+      <c r="C98" s="626" t="str">
         <f>+C77</f>
         <v>Siemens Standard Fitout (New)</v>
       </c>
-      <c r="D98" s="617"/>
+      <c r="D98" s="627"/>
       <c r="E98" s="71"/>
       <c r="F98" s="66">
         <f>'CAPEX and PM'!B29</f>
@@ -9923,11 +9923,11 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="C99" s="618" t="str">
+      <c r="C99" s="626" t="str">
         <f>+C78</f>
         <v>Capex over the period of lease period</v>
       </c>
-      <c r="D99" s="617"/>
+      <c r="D99" s="627"/>
       <c r="E99" s="71"/>
       <c r="F99" s="66">
         <f>'CAPEX and PM'!B89</f>
@@ -9955,11 +9955,11 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="C100" s="618" t="str">
+      <c r="C100" s="626" t="str">
         <f>+C79</f>
         <v>PM cost over the period of lease period</v>
       </c>
-      <c r="D100" s="617"/>
+      <c r="D100" s="627"/>
       <c r="E100" s="71"/>
       <c r="F100" s="66">
         <f>+'CAPEX and PM'!B96</f>
@@ -9987,11 +9987,11 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="C101" s="618" t="str">
+      <c r="C101" s="626" t="str">
         <f>+C80</f>
         <v>Asset Retirement Obligation ( Removal &amp; Restoration Obligation)</v>
       </c>
-      <c r="D101" s="617"/>
+      <c r="D101" s="627"/>
       <c r="E101" s="71"/>
       <c r="F101" s="66">
         <f>'Security Deposit'!D25</f>
@@ -10022,10 +10022,10 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="C102" s="616" t="s">
+      <c r="C102" s="620" t="s">
         <v>154</v>
       </c>
-      <c r="D102" s="617"/>
+      <c r="D102" s="627"/>
       <c r="E102" s="73"/>
       <c r="F102" s="66">
         <f>+F81/F21/F27</f>
@@ -10053,10 +10053,10 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="C103" s="619" t="s">
+      <c r="C103" s="622" t="s">
         <v>155</v>
       </c>
-      <c r="D103" s="620"/>
+      <c r="D103" s="623"/>
       <c r="E103" s="78"/>
       <c r="F103" s="54">
         <f>SUM(F97:F102)</f>
@@ -10093,11 +10093,11 @@
     </row>
     <row r="105" spans="1:26" ht="15.9" customHeight="1">
       <c r="A105" s="51"/>
-      <c r="B105" s="710" t="s">
+      <c r="B105" s="631" t="s">
         <v>156</v>
       </c>
-      <c r="C105" s="633"/>
-      <c r="D105" s="633"/>
+      <c r="C105" s="632"/>
+      <c r="D105" s="632"/>
       <c r="E105" s="87"/>
       <c r="F105" s="161" t="s">
         <v>75</v>
@@ -10118,10 +10118,10 @@
       <c r="B106" s="162">
         <v>1</v>
       </c>
-      <c r="C106" s="616" t="s">
+      <c r="C106" s="620" t="s">
         <v>69</v>
       </c>
-      <c r="D106" s="617"/>
+      <c r="D106" s="627"/>
       <c r="E106" s="71"/>
       <c r="F106" s="56">
         <f>+F94</f>
@@ -10149,10 +10149,10 @@
         <f>+B106+1</f>
         <v>2</v>
       </c>
-      <c r="C107" s="616" t="s">
+      <c r="C107" s="620" t="s">
         <v>155</v>
       </c>
-      <c r="D107" s="626"/>
+      <c r="D107" s="621"/>
       <c r="E107" s="71"/>
       <c r="F107" s="56">
         <f>+F103</f>
@@ -10180,10 +10180,10 @@
         <f>+B107+1</f>
         <v>3</v>
       </c>
-      <c r="C108" s="619" t="s">
+      <c r="C108" s="622" t="s">
         <v>157</v>
       </c>
-      <c r="D108" s="620"/>
+      <c r="D108" s="623"/>
       <c r="E108" s="78"/>
       <c r="F108" s="54">
         <f>SUM(F106:F107)</f>
@@ -10212,11 +10212,11 @@
     </row>
     <row r="109" spans="1:26" ht="15.9" customHeight="1">
       <c r="A109" s="51"/>
-      <c r="B109" s="621" t="s">
+      <c r="B109" s="624" t="s">
         <v>158</v>
       </c>
-      <c r="C109" s="622"/>
-      <c r="D109" s="622"/>
+      <c r="C109" s="625"/>
+      <c r="D109" s="625"/>
       <c r="E109" s="89"/>
       <c r="F109" s="161" t="s">
         <v>75</v>
@@ -10238,10 +10238,10 @@
       <c r="B110" s="249">
         <v>1</v>
       </c>
-      <c r="C110" s="616" t="s">
+      <c r="C110" s="620" t="s">
         <v>159</v>
       </c>
-      <c r="D110" s="626"/>
+      <c r="D110" s="621"/>
       <c r="E110" s="83"/>
       <c r="F110" s="376"/>
       <c r="G110" s="376"/>
@@ -10255,10 +10255,10 @@
         <f t="shared" ref="B111:B119" si="9">1+B110</f>
         <v>2</v>
       </c>
-      <c r="C111" s="616" t="s">
+      <c r="C111" s="620" t="s">
         <v>160</v>
       </c>
-      <c r="D111" s="626"/>
+      <c r="D111" s="621"/>
       <c r="E111" s="83"/>
       <c r="F111" s="376"/>
       <c r="G111" s="376"/>
@@ -10274,10 +10274,10 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="C112" s="616" t="s">
+      <c r="C112" s="620" t="s">
         <v>161</v>
       </c>
-      <c r="D112" s="626"/>
+      <c r="D112" s="621"/>
       <c r="E112" s="83"/>
       <c r="F112" s="388">
         <f>+F64*0</f>
@@ -10305,10 +10305,10 @@
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="C113" s="616" t="s">
+      <c r="C113" s="620" t="s">
         <v>162</v>
       </c>
-      <c r="D113" s="626"/>
+      <c r="D113" s="621"/>
       <c r="E113" s="83"/>
       <c r="F113" s="376"/>
       <c r="G113" s="376"/>
@@ -10322,10 +10322,10 @@
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="C114" s="616" t="s">
+      <c r="C114" s="620" t="s">
         <v>163</v>
       </c>
-      <c r="D114" s="626"/>
+      <c r="D114" s="621"/>
       <c r="E114" s="83"/>
       <c r="F114" s="376"/>
       <c r="G114" s="376"/>
@@ -10339,10 +10339,10 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="C115" s="616" t="s">
+      <c r="C115" s="620" t="s">
         <v>164</v>
       </c>
-      <c r="D115" s="626"/>
+      <c r="D115" s="621"/>
       <c r="E115" s="83"/>
       <c r="F115" s="376"/>
       <c r="G115" s="376"/>
@@ -10356,10 +10356,10 @@
         <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="C116" s="616" t="s">
+      <c r="C116" s="620" t="s">
         <v>165</v>
       </c>
-      <c r="D116" s="626"/>
+      <c r="D116" s="621"/>
       <c r="E116" s="83"/>
       <c r="F116" s="376"/>
       <c r="G116" s="376"/>
@@ -10373,17 +10373,17 @@
         <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="C117" s="616" t="s">
+      <c r="C117" s="620" t="s">
         <v>166</v>
       </c>
-      <c r="D117" s="617"/>
+      <c r="D117" s="627"/>
       <c r="E117" s="252"/>
       <c r="F117" s="360">
         <v>654</v>
       </c>
       <c r="G117" s="207">
-        <f>F117</f>
-        <v>654</v>
+        <f>F117*I6</f>
+        <v>7039.6559999999999</v>
       </c>
       <c r="H117" s="404"/>
       <c r="I117" s="156">
@@ -10402,24 +10402,27 @@
         <f t="shared" si="9"/>
         <v>9</v>
       </c>
-      <c r="C118" s="616" t="s">
+      <c r="C118" s="620" t="s">
         <v>167</v>
       </c>
-      <c r="D118" s="626"/>
+      <c r="D118" s="621"/>
       <c r="E118" s="252"/>
-      <c r="F118" s="90"/>
+      <c r="F118" s="90">
+        <f>F117*7%</f>
+        <v>45.78</v>
+      </c>
       <c r="G118" s="90">
         <f>G117*7%</f>
-        <v>45.78</v>
+        <v>492.77592000000004</v>
       </c>
       <c r="H118" s="404"/>
       <c r="I118" s="156">
         <f>+F118/$J$5</f>
-        <v>0</v>
+        <v>0.43591696819653403</v>
       </c>
       <c r="J118" s="131">
         <f>+I118*I6</f>
-        <v>0</v>
+        <v>4.6922102456674919</v>
       </c>
     </row>
     <row r="119" spans="1:26" ht="15.9" customHeight="1">
@@ -10428,27 +10431,27 @@
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="C119" s="619" t="s">
+      <c r="C119" s="622" t="s">
         <v>168</v>
       </c>
-      <c r="D119" s="620"/>
+      <c r="D119" s="623"/>
       <c r="E119" s="253"/>
       <c r="F119" s="54">
         <f>SUM(F110:F118)</f>
-        <v>654</v>
+        <v>699.78</v>
       </c>
       <c r="G119" s="385">
         <f>SUM(G110:G118)</f>
-        <v>699.78</v>
+        <v>7532.43192</v>
       </c>
       <c r="H119" s="404"/>
       <c r="I119" s="191">
         <f>SUM(I110:I118)</f>
-        <v>6.227385259950486</v>
+        <v>6.6633022281470202</v>
       </c>
       <c r="J119" s="82">
         <f>G119/$J$5</f>
-        <v>6.6633022281470193</v>
+        <v>71.723785183774524</v>
       </c>
       <c r="S119" s="400"/>
       <c r="T119" s="400"/>
@@ -10457,8 +10460,8 @@
     <row r="120" spans="1:26" ht="15.9" customHeight="1">
       <c r="A120" s="77"/>
       <c r="B120" s="162"/>
-      <c r="C120" s="624"/>
-      <c r="D120" s="625"/>
+      <c r="C120" s="616"/>
+      <c r="D120" s="633"/>
       <c r="E120" s="78"/>
       <c r="F120" s="54"/>
       <c r="G120" s="385"/>
@@ -10472,11 +10475,11 @@
     </row>
     <row r="121" spans="1:26" ht="15.9" customHeight="1">
       <c r="A121" s="77"/>
-      <c r="B121" s="621" t="s">
+      <c r="B121" s="624" t="s">
         <v>169</v>
       </c>
-      <c r="C121" s="622"/>
-      <c r="D121" s="622"/>
+      <c r="C121" s="625"/>
+      <c r="D121" s="625"/>
       <c r="E121" s="89"/>
       <c r="F121" s="161" t="s">
         <v>75</v>
@@ -10499,10 +10502,10 @@
       <c r="B122" s="251">
         <v>1</v>
       </c>
-      <c r="C122" s="616" t="s">
+      <c r="C122" s="620" t="s">
         <v>170</v>
       </c>
-      <c r="D122" s="626"/>
+      <c r="D122" s="621"/>
       <c r="E122" s="78"/>
       <c r="F122" s="54"/>
       <c r="G122" s="385"/>
@@ -10515,10 +10518,10 @@
       <c r="B123" s="162">
         <v>2</v>
       </c>
-      <c r="C123" s="619" t="s">
+      <c r="C123" s="622" t="s">
         <v>171</v>
       </c>
-      <c r="D123" s="620"/>
+      <c r="D123" s="623"/>
       <c r="E123" s="78"/>
       <c r="F123" s="54">
         <f>SUM(F122)</f>
@@ -10541,8 +10544,8 @@
     <row r="124" spans="1:26" ht="15.9" customHeight="1">
       <c r="A124" s="77"/>
       <c r="B124" s="162"/>
-      <c r="C124" s="624"/>
-      <c r="D124" s="625"/>
+      <c r="C124" s="616"/>
+      <c r="D124" s="633"/>
       <c r="E124" s="63"/>
       <c r="F124" s="54"/>
       <c r="G124" s="385"/>
@@ -10552,11 +10555,11 @@
     </row>
     <row r="125" spans="1:26" ht="15.9" customHeight="1">
       <c r="A125" s="77"/>
-      <c r="B125" s="621" t="s">
+      <c r="B125" s="624" t="s">
         <v>172</v>
       </c>
-      <c r="C125" s="622"/>
-      <c r="D125" s="622"/>
+      <c r="C125" s="625"/>
+      <c r="D125" s="625"/>
       <c r="E125" s="89"/>
       <c r="F125" s="161" t="s">
         <v>75</v>
@@ -10577,10 +10580,10 @@
       <c r="B126" s="249">
         <v>1</v>
       </c>
-      <c r="C126" s="616" t="s">
+      <c r="C126" s="620" t="s">
         <v>173</v>
       </c>
-      <c r="D126" s="626"/>
+      <c r="D126" s="621"/>
       <c r="E126" s="250"/>
       <c r="F126" s="385"/>
       <c r="G126" s="385"/>
@@ -10594,10 +10597,10 @@
         <f>1+B126</f>
         <v>2</v>
       </c>
-      <c r="C127" s="616" t="s">
+      <c r="C127" s="620" t="s">
         <v>174</v>
       </c>
-      <c r="D127" s="626"/>
+      <c r="D127" s="621"/>
       <c r="E127" s="250"/>
       <c r="F127" s="385"/>
       <c r="G127" s="385"/>
@@ -10611,10 +10614,10 @@
         <f>1+B127</f>
         <v>3</v>
       </c>
-      <c r="C128" s="616" t="s">
+      <c r="C128" s="620" t="s">
         <v>175</v>
       </c>
-      <c r="D128" s="626"/>
+      <c r="D128" s="621"/>
       <c r="E128" s="250"/>
       <c r="F128" s="385"/>
       <c r="G128" s="385"/>
@@ -10628,10 +10631,10 @@
         <f>1+B128</f>
         <v>4</v>
       </c>
-      <c r="C129" s="616" t="s">
+      <c r="C129" s="620" t="s">
         <v>176</v>
       </c>
-      <c r="D129" s="626"/>
+      <c r="D129" s="621"/>
       <c r="E129" s="250"/>
       <c r="F129" s="385"/>
       <c r="G129" s="385"/>
@@ -10645,10 +10648,10 @@
         <f>1+B129</f>
         <v>5</v>
       </c>
-      <c r="C130" s="616" t="s">
+      <c r="C130" s="620" t="s">
         <v>177</v>
       </c>
-      <c r="D130" s="626"/>
+      <c r="D130" s="621"/>
       <c r="E130" s="250"/>
       <c r="F130" s="385"/>
       <c r="G130" s="385"/>
@@ -10662,10 +10665,10 @@
         <f>1+B130</f>
         <v>6</v>
       </c>
-      <c r="C131" s="616" t="s">
+      <c r="C131" s="620" t="s">
         <v>178</v>
       </c>
-      <c r="D131" s="626"/>
+      <c r="D131" s="621"/>
       <c r="E131" s="250"/>
       <c r="F131" s="385"/>
       <c r="G131" s="385"/>
@@ -10678,10 +10681,10 @@
       <c r="B132" s="381">
         <v>7</v>
       </c>
-      <c r="C132" s="619" t="s">
+      <c r="C132" s="622" t="s">
         <v>179</v>
       </c>
-      <c r="D132" s="620"/>
+      <c r="D132" s="623"/>
       <c r="E132" s="250"/>
       <c r="F132" s="385">
         <f>SUM(F126:F131)</f>
@@ -10704,8 +10707,8 @@
     <row r="133" spans="1:20" ht="15.9" customHeight="1">
       <c r="A133" s="77"/>
       <c r="B133" s="162"/>
-      <c r="C133" s="658"/>
-      <c r="D133" s="625"/>
+      <c r="C133" s="617"/>
+      <c r="D133" s="633"/>
       <c r="E133" s="250"/>
       <c r="F133" s="385"/>
       <c r="G133" s="385"/>
@@ -10715,11 +10718,11 @@
     </row>
     <row r="134" spans="1:20" ht="15.9" customHeight="1">
       <c r="A134" s="51"/>
-      <c r="B134" s="621" t="s">
+      <c r="B134" s="624" t="s">
         <v>180</v>
       </c>
-      <c r="C134" s="622"/>
-      <c r="D134" s="622"/>
+      <c r="C134" s="625"/>
+      <c r="D134" s="625"/>
       <c r="E134" s="89"/>
       <c r="F134" s="161" t="s">
         <v>75</v>
@@ -10740,27 +10743,27 @@
       <c r="B135" s="162">
         <v>1</v>
       </c>
-      <c r="C135" s="619" t="s">
+      <c r="C135" s="622" t="s">
         <v>181</v>
       </c>
-      <c r="D135" s="620"/>
+      <c r="D135" s="623"/>
       <c r="E135" s="78"/>
       <c r="F135" s="54">
         <f>F119+F108+F123+F132</f>
-        <v>989.63622191271531</v>
+        <v>1035.4162219127152</v>
       </c>
       <c r="G135" s="385">
         <f>G119+G108+G123+G132</f>
-        <v>4312.5682926684685</v>
+        <v>11145.220212668468</v>
       </c>
       <c r="H135" s="404"/>
       <c r="I135" s="191">
         <f>I119+I108+I123+I132</f>
-        <v>9.4233119587956153</v>
+        <v>9.8592289269921487</v>
       </c>
       <c r="J135" s="192">
         <f>J119+J108+J123+J132</f>
-        <v>41.064257214515976</v>
+        <v>106.12474017014348</v>
       </c>
       <c r="S135" s="408"/>
       <c r="T135" s="406"/>
@@ -10768,8 +10771,8 @@
     <row r="136" spans="1:20" ht="15.9" customHeight="1">
       <c r="A136" s="77"/>
       <c r="B136" s="162"/>
-      <c r="C136" s="624"/>
-      <c r="D136" s="625"/>
+      <c r="C136" s="616"/>
+      <c r="D136" s="633"/>
       <c r="E136" s="78"/>
       <c r="F136" s="54"/>
       <c r="G136" s="385"/>
@@ -10783,23 +10786,23 @@
       <c r="C137" s="380"/>
       <c r="D137" s="377"/>
       <c r="E137" s="167"/>
-      <c r="F137" s="624" t="s">
+      <c r="F137" s="616" t="s">
         <v>73</v>
       </c>
-      <c r="G137" s="658"/>
+      <c r="G137" s="617"/>
       <c r="H137" s="404"/>
-      <c r="I137" s="659" t="s">
+      <c r="I137" s="618" t="s">
         <v>67</v>
       </c>
-      <c r="J137" s="660"/>
+      <c r="J137" s="619"/>
     </row>
     <row r="138" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A138" s="51"/>
-      <c r="B138" s="621" t="s">
+      <c r="B138" s="624" t="s">
         <v>182</v>
       </c>
-      <c r="C138" s="622"/>
-      <c r="D138" s="623"/>
+      <c r="C138" s="625"/>
+      <c r="D138" s="640"/>
       <c r="E138" s="161"/>
       <c r="F138" s="161" t="s">
         <v>75</v>
@@ -10818,8 +10821,8 @@
     <row r="139" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A139" s="51"/>
       <c r="B139" s="91"/>
-      <c r="C139" s="627"/>
-      <c r="D139" s="628"/>
+      <c r="C139" s="641"/>
+      <c r="D139" s="642"/>
       <c r="E139" s="163"/>
       <c r="F139" s="54"/>
       <c r="G139" s="385"/>
@@ -10830,10 +10833,10 @@
     <row r="140" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A140" s="51"/>
       <c r="B140" s="91"/>
-      <c r="C140" s="616" t="s">
+      <c r="C140" s="620" t="s">
         <v>183</v>
       </c>
-      <c r="D140" s="617"/>
+      <c r="D140" s="627"/>
       <c r="E140" s="58"/>
       <c r="F140" s="243">
         <f>F21</f>
@@ -10856,10 +10859,10 @@
     <row r="141" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A141" s="51"/>
       <c r="B141" s="91"/>
-      <c r="C141" s="618" t="s">
+      <c r="C141" s="626" t="s">
         <v>184</v>
       </c>
-      <c r="D141" s="617"/>
+      <c r="D141" s="627"/>
       <c r="E141" s="59"/>
       <c r="F141" s="56">
         <f>F24</f>
@@ -10882,10 +10885,10 @@
     <row r="142" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A142" s="51"/>
       <c r="B142" s="91"/>
-      <c r="C142" s="618" t="s">
+      <c r="C142" s="626" t="s">
         <v>185</v>
       </c>
-      <c r="D142" s="617"/>
+      <c r="D142" s="627"/>
       <c r="E142" s="73"/>
       <c r="F142" s="56" t="e">
         <f>+#REF!</f>
@@ -10908,10 +10911,10 @@
     <row r="143" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A143" s="51"/>
       <c r="B143" s="91"/>
-      <c r="C143" s="616" t="s">
+      <c r="C143" s="620" t="s">
         <v>186</v>
       </c>
-      <c r="D143" s="617"/>
+      <c r="D143" s="627"/>
       <c r="E143" s="73"/>
       <c r="F143" s="56">
         <f>F108</f>
@@ -10934,36 +10937,36 @@
     <row r="144" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A144" s="51"/>
       <c r="B144" s="91"/>
-      <c r="C144" s="646" t="s">
+      <c r="C144" s="709" t="s">
         <v>187</v>
       </c>
-      <c r="D144" s="647"/>
+      <c r="D144" s="710"/>
       <c r="E144" s="92"/>
       <c r="F144" s="93">
         <f>F119</f>
-        <v>654</v>
+        <v>699.78</v>
       </c>
       <c r="G144" s="208">
         <f>G119</f>
-        <v>699.78</v>
+        <v>7532.43192</v>
       </c>
       <c r="H144" s="404"/>
       <c r="I144" s="141">
         <f>I119</f>
-        <v>6.227385259950486</v>
+        <v>6.6633022281470202</v>
       </c>
       <c r="J144" s="130">
         <f>J119</f>
-        <v>6.6633022281470193</v>
+        <v>71.723785183774524</v>
       </c>
     </row>
     <row r="145" spans="1:10" ht="15.9" hidden="1" customHeight="1">
       <c r="A145" s="77"/>
       <c r="B145" s="162"/>
-      <c r="C145" s="619" t="s">
+      <c r="C145" s="622" t="s">
         <v>188</v>
       </c>
-      <c r="D145" s="620"/>
+      <c r="D145" s="623"/>
       <c r="E145" s="78"/>
       <c r="F145" s="245" t="e">
         <f>F135*#REF!</f>
@@ -10997,11 +11000,11 @@
     </row>
     <row r="147" spans="1:10" ht="15.9" customHeight="1">
       <c r="A147" s="77"/>
-      <c r="B147" s="621" t="s">
+      <c r="B147" s="624" t="s">
         <v>189</v>
       </c>
-      <c r="C147" s="622"/>
-      <c r="D147" s="623"/>
+      <c r="C147" s="625"/>
+      <c r="D147" s="640"/>
       <c r="E147" s="379"/>
       <c r="F147" s="379" t="s">
         <v>190</v>
@@ -11020,8 +11023,8 @@
     <row r="148" spans="1:10" ht="15.9" customHeight="1">
       <c r="A148" s="51"/>
       <c r="B148" s="99"/>
-      <c r="C148" s="627"/>
-      <c r="D148" s="628"/>
+      <c r="C148" s="641"/>
+      <c r="D148" s="642"/>
       <c r="E148" s="100"/>
       <c r="F148" s="101"/>
       <c r="G148" s="209"/>
@@ -11032,10 +11035,10 @@
     <row r="149" spans="1:10" ht="15.9" customHeight="1">
       <c r="A149" s="51"/>
       <c r="B149" s="99"/>
-      <c r="C149" s="618" t="s">
+      <c r="C149" s="626" t="s">
         <v>191</v>
       </c>
-      <c r="D149" s="617"/>
+      <c r="D149" s="627"/>
       <c r="E149" s="100"/>
       <c r="F149" s="101">
         <f>(+F63)*115%</f>
@@ -11058,10 +11061,10 @@
     <row r="150" spans="1:10" ht="15.9" customHeight="1">
       <c r="A150" s="51"/>
       <c r="B150" s="99"/>
-      <c r="C150" s="618" t="s">
+      <c r="C150" s="626" t="s">
         <v>192</v>
       </c>
-      <c r="D150" s="617"/>
+      <c r="D150" s="627"/>
       <c r="E150" s="100"/>
       <c r="F150" s="101">
         <v>0</v>
@@ -11080,10 +11083,10 @@
     <row r="151" spans="1:10" ht="15.9" customHeight="1">
       <c r="A151" s="51"/>
       <c r="B151" s="99"/>
-      <c r="C151" s="618" t="s">
+      <c r="C151" s="626" t="s">
         <v>193</v>
       </c>
-      <c r="D151" s="617"/>
+      <c r="D151" s="627"/>
       <c r="E151" s="100"/>
       <c r="F151" s="101">
         <f>(+F65)*115%</f>
@@ -11106,10 +11109,10 @@
     <row r="152" spans="1:10" ht="15.9" customHeight="1">
       <c r="A152" s="51"/>
       <c r="B152" s="99"/>
-      <c r="C152" s="618" t="s">
+      <c r="C152" s="626" t="s">
         <v>194</v>
       </c>
-      <c r="D152" s="617"/>
+      <c r="D152" s="627"/>
       <c r="E152" s="100"/>
       <c r="F152" s="101">
         <f>(+F66)*115%</f>
@@ -11132,10 +11135,10 @@
     <row r="153" spans="1:10" ht="15.9" customHeight="1">
       <c r="A153" s="51"/>
       <c r="B153" s="99"/>
-      <c r="C153" s="616" t="s">
+      <c r="C153" s="620" t="s">
         <v>195</v>
       </c>
-      <c r="D153" s="617"/>
+      <c r="D153" s="627"/>
       <c r="E153" s="103"/>
       <c r="F153" s="104">
         <f>SUM(F149:F152)</f>
@@ -11158,10 +11161,10 @@
     <row r="154" spans="1:10" ht="15.9" customHeight="1">
       <c r="A154" s="51"/>
       <c r="B154" s="99"/>
-      <c r="C154" s="616" t="s">
+      <c r="C154" s="620" t="s">
         <v>196</v>
       </c>
-      <c r="D154" s="617"/>
+      <c r="D154" s="627"/>
       <c r="E154" s="105"/>
       <c r="F154" s="101">
         <f>+F153*12</f>
@@ -11184,8 +11187,8 @@
     <row r="155" spans="1:10" ht="15.9" customHeight="1">
       <c r="A155" s="51"/>
       <c r="B155" s="99"/>
-      <c r="C155" s="627"/>
-      <c r="D155" s="628"/>
+      <c r="C155" s="641"/>
+      <c r="D155" s="642"/>
       <c r="E155" s="105"/>
       <c r="F155" s="101"/>
       <c r="G155" s="209"/>
@@ -11195,11 +11198,11 @@
     </row>
     <row r="156" spans="1:10" ht="15.9" customHeight="1">
       <c r="A156" s="51"/>
-      <c r="B156" s="621" t="s">
+      <c r="B156" s="624" t="s">
         <v>197</v>
       </c>
-      <c r="C156" s="622"/>
-      <c r="D156" s="623"/>
+      <c r="C156" s="625"/>
+      <c r="D156" s="640"/>
       <c r="E156" s="375"/>
       <c r="F156" s="379" t="s">
         <v>190</v>
@@ -11218,8 +11221,8 @@
     <row r="157" spans="1:10" ht="15.9" customHeight="1">
       <c r="A157" s="51"/>
       <c r="B157" s="99"/>
-      <c r="C157" s="627"/>
-      <c r="D157" s="628"/>
+      <c r="C157" s="641"/>
+      <c r="D157" s="642"/>
       <c r="E157" s="105"/>
       <c r="F157" s="101"/>
       <c r="G157" s="209"/>
@@ -11230,10 +11233,10 @@
     <row r="158" spans="1:10" ht="15.9" customHeight="1">
       <c r="A158" s="51"/>
       <c r="B158" s="99"/>
-      <c r="C158" s="644" t="s">
+      <c r="C158" s="707" t="s">
         <v>198</v>
       </c>
-      <c r="D158" s="645"/>
+      <c r="D158" s="708"/>
       <c r="E158" s="105"/>
       <c r="F158" s="101">
         <f t="shared" ref="F158:G160" si="10">+F77</f>
@@ -11256,10 +11259,10 @@
     <row r="159" spans="1:10" ht="15.9" customHeight="1">
       <c r="A159" s="51"/>
       <c r="B159" s="99"/>
-      <c r="C159" s="616" t="s">
+      <c r="C159" s="620" t="s">
         <v>199</v>
       </c>
-      <c r="D159" s="626"/>
+      <c r="D159" s="621"/>
       <c r="E159" s="105"/>
       <c r="F159" s="101">
         <f t="shared" si="10"/>
@@ -11282,10 +11285,10 @@
     <row r="160" spans="1:10" ht="15.9" customHeight="1">
       <c r="A160" s="51"/>
       <c r="B160" s="99"/>
-      <c r="C160" s="616" t="s">
+      <c r="C160" s="620" t="s">
         <v>200</v>
       </c>
-      <c r="D160" s="626"/>
+      <c r="D160" s="621"/>
       <c r="E160" s="105"/>
       <c r="F160" s="101">
         <f t="shared" si="10"/>
@@ -11308,10 +11311,10 @@
     <row r="161" spans="1:22" ht="15.9" customHeight="1">
       <c r="A161" s="51"/>
       <c r="B161" s="99"/>
-      <c r="C161" s="619" t="s">
+      <c r="C161" s="622" t="s">
         <v>29</v>
       </c>
-      <c r="D161" s="620"/>
+      <c r="D161" s="623"/>
       <c r="E161" s="105"/>
       <c r="F161" s="237">
         <f>SUM(F158:F160)</f>
@@ -11334,8 +11337,8 @@
     <row r="162" spans="1:22" ht="15.9" customHeight="1">
       <c r="A162" s="51"/>
       <c r="B162" s="99"/>
-      <c r="C162" s="627"/>
-      <c r="D162" s="628"/>
+      <c r="C162" s="641"/>
+      <c r="D162" s="642"/>
       <c r="E162" s="105"/>
       <c r="F162" s="101"/>
       <c r="G162" s="209"/>
@@ -11345,12 +11348,12 @@
     </row>
     <row r="163" spans="1:22" ht="15.9" customHeight="1">
       <c r="A163" s="106"/>
-      <c r="B163" s="638" t="s">
+      <c r="B163" s="628" t="s">
         <v>201</v>
       </c>
-      <c r="C163" s="639"/>
-      <c r="D163" s="640"/>
-      <c r="E163" s="709"/>
+      <c r="C163" s="629"/>
+      <c r="D163" s="630"/>
+      <c r="E163" s="638"/>
       <c r="F163" s="161" t="s">
         <v>75</v>
       </c>
@@ -11367,10 +11370,10 @@
     </row>
     <row r="164" spans="1:22" ht="15.9" customHeight="1">
       <c r="A164" s="106"/>
-      <c r="B164" s="641"/>
-      <c r="C164" s="642"/>
-      <c r="D164" s="643"/>
-      <c r="E164" s="631"/>
+      <c r="B164" s="704"/>
+      <c r="C164" s="705"/>
+      <c r="D164" s="706"/>
+      <c r="E164" s="639"/>
       <c r="F164" s="161" t="s">
         <v>73</v>
       </c>
@@ -11388,8 +11391,8 @@
     <row r="165" spans="1:22" ht="15.9" customHeight="1">
       <c r="A165" s="107"/>
       <c r="B165" s="99"/>
-      <c r="C165" s="627"/>
-      <c r="D165" s="628"/>
+      <c r="C165" s="641"/>
+      <c r="D165" s="642"/>
       <c r="E165" s="59"/>
       <c r="F165" s="56"/>
       <c r="G165" s="388"/>
@@ -11400,11 +11403,11 @@
     <row r="166" spans="1:22" ht="15.9" customHeight="1">
       <c r="A166" s="107"/>
       <c r="B166" s="99"/>
-      <c r="C166" s="629" t="str">
+      <c r="C166" s="702" t="str">
         <f>+C106</f>
         <v>Net Rent I</v>
       </c>
-      <c r="D166" s="630"/>
+      <c r="D166" s="703"/>
       <c r="E166" s="59"/>
       <c r="F166" s="56">
         <f>+F106</f>
@@ -11428,11 +11431,11 @@
     <row r="167" spans="1:22" ht="15.9" customHeight="1">
       <c r="A167" s="107"/>
       <c r="B167" s="99"/>
-      <c r="C167" s="629" t="str">
+      <c r="C167" s="702" t="str">
         <f>+C107</f>
         <v>Net Rent II</v>
       </c>
-      <c r="D167" s="630"/>
+      <c r="D167" s="703"/>
       <c r="E167" s="59"/>
       <c r="F167" s="56">
         <f>+F107</f>
@@ -11456,10 +11459,10 @@
     <row r="168" spans="1:22" ht="15.9" customHeight="1">
       <c r="A168" s="107"/>
       <c r="B168" s="147"/>
-      <c r="C168" s="634" t="s">
+      <c r="C168" s="698" t="s">
         <v>202</v>
       </c>
-      <c r="D168" s="635"/>
+      <c r="D168" s="699"/>
       <c r="E168" s="148"/>
       <c r="F168" s="149">
         <f>SUM(F166:F167)</f>
@@ -11484,8 +11487,8 @@
     <row r="169" spans="1:22" ht="15.9" customHeight="1">
       <c r="A169" s="107"/>
       <c r="B169" s="162"/>
-      <c r="C169" s="636"/>
-      <c r="D169" s="637"/>
+      <c r="C169" s="700"/>
+      <c r="D169" s="701"/>
       <c r="E169" s="75"/>
       <c r="F169" s="54"/>
       <c r="G169" s="385"/>
@@ -11498,39 +11501,39 @@
     <row r="170" spans="1:22" ht="15.9" customHeight="1">
       <c r="A170" s="107"/>
       <c r="B170" s="99"/>
-      <c r="C170" s="629" t="str">
+      <c r="C170" s="702" t="str">
         <f>+C119</f>
         <v xml:space="preserve">OpEx I </v>
       </c>
-      <c r="D170" s="630"/>
+      <c r="D170" s="703"/>
       <c r="E170" s="59"/>
       <c r="F170" s="56">
         <f>+F119</f>
-        <v>654</v>
+        <v>699.78</v>
       </c>
       <c r="G170" s="56">
         <f>+G119</f>
-        <v>699.78</v>
+        <v>7532.43192</v>
       </c>
       <c r="H170" s="404"/>
       <c r="I170" s="136">
         <f>F170/J5</f>
-        <v>6.227385259950486</v>
+        <v>6.6633022281470193</v>
       </c>
       <c r="J170" s="67">
         <f>G170/J5</f>
-        <v>6.6633022281470193</v>
+        <v>71.723785183774524</v>
       </c>
       <c r="T170" s="409"/>
     </row>
     <row r="171" spans="1:22" ht="15.9" customHeight="1">
       <c r="A171" s="107"/>
       <c r="B171" s="99"/>
-      <c r="C171" s="629" t="str">
+      <c r="C171" s="702" t="str">
         <f>+C123</f>
         <v xml:space="preserve">OpEx II </v>
       </c>
-      <c r="D171" s="630"/>
+      <c r="D171" s="703"/>
       <c r="E171" s="59"/>
       <c r="F171" s="56">
         <f>+F123</f>
@@ -11553,27 +11556,27 @@
     <row r="172" spans="1:22" ht="15.9" customHeight="1">
       <c r="A172" s="107"/>
       <c r="B172" s="150"/>
-      <c r="C172" s="634" t="s">
+      <c r="C172" s="698" t="s">
         <v>203</v>
       </c>
-      <c r="D172" s="635"/>
+      <c r="D172" s="699"/>
       <c r="E172" s="151"/>
       <c r="F172" s="152">
         <f>SUM(F170:F171)</f>
-        <v>654</v>
+        <v>699.78</v>
       </c>
       <c r="G172" s="278">
         <f>SUM(G170:G171)</f>
-        <v>699.78</v>
+        <v>7532.43192</v>
       </c>
       <c r="H172" s="413"/>
       <c r="I172" s="153">
         <f>SUM(I170:I171)</f>
-        <v>6.227385259950486</v>
+        <v>6.6633022281470193</v>
       </c>
       <c r="J172" s="247">
         <f>SUM(J170:J171)</f>
-        <v>6.6633022281470193</v>
+        <v>71.723785183774524</v>
       </c>
     </row>
     <row r="173" spans="1:22" ht="15.9" customHeight="1">
@@ -11591,11 +11594,11 @@
     <row r="174" spans="1:22" ht="15.9" customHeight="1">
       <c r="A174" s="107"/>
       <c r="B174" s="99"/>
-      <c r="C174" s="629" t="str">
+      <c r="C174" s="702" t="str">
         <f>+C132</f>
         <v xml:space="preserve">Services </v>
       </c>
-      <c r="D174" s="630"/>
+      <c r="D174" s="703"/>
       <c r="E174" s="59"/>
       <c r="F174" s="56">
         <f>+F132</f>
@@ -11618,10 +11621,10 @@
     <row r="175" spans="1:22" ht="15.9" customHeight="1">
       <c r="A175" s="107"/>
       <c r="B175" s="150"/>
-      <c r="C175" s="634" t="s">
+      <c r="C175" s="698" t="s">
         <v>204</v>
       </c>
-      <c r="D175" s="635"/>
+      <c r="D175" s="699"/>
       <c r="E175" s="151"/>
       <c r="F175" s="152">
         <f>SUM(F174)</f>
@@ -11644,8 +11647,8 @@
     <row r="176" spans="1:22" ht="15.9" customHeight="1">
       <c r="A176" s="107"/>
       <c r="B176" s="99"/>
-      <c r="C176" s="627"/>
-      <c r="D176" s="628"/>
+      <c r="C176" s="641"/>
+      <c r="D176" s="642"/>
       <c r="E176" s="59"/>
       <c r="F176" s="56"/>
       <c r="G176" s="388"/>
@@ -11656,27 +11659,27 @@
     <row r="177" spans="1:19" ht="15.9" customHeight="1">
       <c r="A177" s="107"/>
       <c r="B177" s="150"/>
-      <c r="C177" s="634" t="s">
+      <c r="C177" s="698" t="s">
         <v>205</v>
       </c>
-      <c r="D177" s="635"/>
+      <c r="D177" s="699"/>
       <c r="E177" s="154"/>
       <c r="F177" s="149">
         <f>+F168+F172+F175</f>
-        <v>989.63622191271531</v>
+        <v>1035.4162219127152</v>
       </c>
       <c r="G177" s="211">
         <f>+G168+G172+G175</f>
-        <v>4312.5682926684685</v>
+        <v>11145.220212668468</v>
       </c>
       <c r="H177" s="415"/>
       <c r="I177" s="234">
         <f>+I168+I172+I175</f>
-        <v>9.4233119587956153</v>
+        <v>9.8592289269921487</v>
       </c>
       <c r="J177" s="214">
         <f>+J168+J172+J175</f>
-        <v>41.064257214515976</v>
+        <v>106.12474017014348</v>
       </c>
       <c r="S177" s="408"/>
     </row>
@@ -11694,11 +11697,11 @@
     </row>
     <row r="179" spans="1:19" ht="15.9" customHeight="1">
       <c r="A179" s="107"/>
-      <c r="B179" s="621" t="s">
+      <c r="B179" s="624" t="s">
         <v>206</v>
       </c>
-      <c r="C179" s="622"/>
-      <c r="D179" s="623"/>
+      <c r="C179" s="625"/>
+      <c r="D179" s="640"/>
       <c r="E179" s="379"/>
       <c r="F179" s="379" t="s">
         <v>190</v>
@@ -11717,8 +11720,8 @@
     <row r="180" spans="1:19" ht="15.9" customHeight="1">
       <c r="A180" s="107"/>
       <c r="B180" s="99"/>
-      <c r="C180" s="627"/>
-      <c r="D180" s="628"/>
+      <c r="C180" s="641"/>
+      <c r="D180" s="642"/>
       <c r="E180" s="59"/>
       <c r="F180" s="56"/>
       <c r="G180" s="388"/>
@@ -11729,10 +11732,10 @@
     <row r="181" spans="1:19" ht="15.9" customHeight="1">
       <c r="A181" s="107"/>
       <c r="B181" s="99"/>
-      <c r="C181" s="618" t="s">
+      <c r="C181" s="626" t="s">
         <v>207</v>
       </c>
-      <c r="D181" s="617"/>
+      <c r="D181" s="627"/>
       <c r="E181" s="100"/>
       <c r="F181" s="101"/>
       <c r="G181" s="209">
@@ -11749,30 +11752,30 @@
     <row r="182" spans="1:19" ht="15.9" customHeight="1">
       <c r="A182" s="107"/>
       <c r="B182" s="99"/>
-      <c r="C182" s="616" t="s">
+      <c r="C182" s="620" t="s">
         <v>208</v>
       </c>
-      <c r="D182" s="617"/>
+      <c r="D182" s="627"/>
       <c r="E182" s="100"/>
       <c r="F182" s="101"/>
       <c r="G182" s="209">
         <f>+G172*G21</f>
-        <v>618581.07580824976</v>
+        <v>6658406.7000000002</v>
       </c>
       <c r="H182" s="404"/>
       <c r="I182" s="143"/>
       <c r="J182" s="102">
         <f>+G182/$J$5</f>
-        <v>5890.1264121905333</v>
+        <v>63401.320700818898</v>
       </c>
     </row>
     <row r="183" spans="1:19" ht="15.9" customHeight="1">
       <c r="A183" s="107"/>
       <c r="B183" s="99"/>
-      <c r="C183" s="616" t="s">
+      <c r="C183" s="620" t="s">
         <v>209</v>
       </c>
-      <c r="D183" s="626"/>
+      <c r="D183" s="621"/>
       <c r="E183" s="100"/>
       <c r="F183" s="101"/>
       <c r="G183" s="209">
@@ -11786,41 +11789,41 @@
     <row r="184" spans="1:19" ht="15.9" customHeight="1">
       <c r="A184" s="107"/>
       <c r="B184" s="99"/>
-      <c r="C184" s="616" t="s">
+      <c r="C184" s="620" t="s">
         <v>210</v>
       </c>
-      <c r="D184" s="617"/>
+      <c r="D184" s="627"/>
       <c r="E184" s="100"/>
       <c r="F184" s="101"/>
       <c r="G184" s="209">
         <f>SUM(G181:G183)</f>
-        <v>3812159.7273077369</v>
+        <v>9851985.3514994867</v>
       </c>
       <c r="H184" s="404"/>
       <c r="I184" s="143"/>
       <c r="J184" s="102">
         <f>SUM(J181:J183)</f>
-        <v>36299.368951701937</v>
+        <v>93810.563240330303</v>
       </c>
     </row>
     <row r="185" spans="1:19" ht="15.9" customHeight="1">
       <c r="A185" s="107"/>
       <c r="B185" s="99"/>
-      <c r="C185" s="616" t="s">
+      <c r="C185" s="620" t="s">
         <v>211</v>
       </c>
-      <c r="D185" s="617"/>
+      <c r="D185" s="627"/>
       <c r="E185" s="100"/>
       <c r="F185" s="101"/>
       <c r="G185" s="209">
         <f>+G184*12</f>
-        <v>45745916.727692842</v>
+        <v>118223824.21799384</v>
       </c>
       <c r="H185" s="404"/>
       <c r="I185" s="143"/>
       <c r="J185" s="102">
         <f>+J184*12</f>
-        <v>435592.42742042325</v>
+        <v>1125726.7588839636</v>
       </c>
     </row>
     <row r="186" spans="1:19" ht="15.9" customHeight="1" thickBot="1">
@@ -11837,25 +11840,25 @@
     </row>
     <row r="187" spans="1:19" ht="15.9" customHeight="1" thickBot="1">
       <c r="A187" s="107"/>
-      <c r="B187" s="651" t="s">
+      <c r="B187" s="695" t="s">
         <v>212</v>
       </c>
-      <c r="C187" s="652"/>
-      <c r="D187" s="652"/>
-      <c r="E187" s="652"/>
-      <c r="F187" s="652"/>
-      <c r="G187" s="652"/>
-      <c r="H187" s="652"/>
-      <c r="I187" s="652"/>
-      <c r="J187" s="653"/>
+      <c r="C187" s="696"/>
+      <c r="D187" s="696"/>
+      <c r="E187" s="696"/>
+      <c r="F187" s="696"/>
+      <c r="G187" s="696"/>
+      <c r="H187" s="696"/>
+      <c r="I187" s="696"/>
+      <c r="J187" s="697"/>
     </row>
     <row r="188" spans="1:19" ht="15.9" customHeight="1">
       <c r="A188" s="51"/>
       <c r="B188" s="164"/>
-      <c r="C188" s="631" t="s">
+      <c r="C188" s="639" t="s">
         <v>213</v>
       </c>
-      <c r="D188" s="631"/>
+      <c r="D188" s="639"/>
       <c r="E188" s="378"/>
       <c r="F188" s="378" t="s">
         <v>190</v>
@@ -11863,7 +11866,7 @@
       <c r="G188" s="168" t="s">
         <v>190</v>
       </c>
-      <c r="H188" s="648"/>
+      <c r="H188" s="692"/>
       <c r="I188" s="229" t="s">
         <v>67</v>
       </c>
@@ -11874,17 +11877,17 @@
     <row r="189" spans="1:19" ht="15.9" customHeight="1">
       <c r="A189" s="51"/>
       <c r="B189" s="162"/>
-      <c r="C189" s="618" t="s">
+      <c r="C189" s="626" t="s">
         <v>214</v>
       </c>
-      <c r="D189" s="617"/>
+      <c r="D189" s="627"/>
       <c r="E189" s="163"/>
       <c r="F189" s="163"/>
       <c r="G189" s="102">
         <f>+G20</f>
         <v>0</v>
       </c>
-      <c r="H189" s="649"/>
+      <c r="H189" s="693"/>
       <c r="I189" s="162"/>
       <c r="J189" s="102">
         <f>+G189/J5</f>
@@ -11894,17 +11897,17 @@
     <row r="190" spans="1:19" ht="15.9" customHeight="1">
       <c r="A190" s="51"/>
       <c r="B190" s="162"/>
-      <c r="C190" s="618" t="s">
+      <c r="C190" s="626" t="s">
         <v>215</v>
       </c>
-      <c r="D190" s="617"/>
+      <c r="D190" s="627"/>
       <c r="E190" s="163"/>
       <c r="F190" s="163"/>
       <c r="G190" s="102">
         <f>+G189*G23</f>
         <v>0</v>
       </c>
-      <c r="H190" s="649"/>
+      <c r="H190" s="693"/>
       <c r="I190" s="162"/>
       <c r="J190" s="102">
         <f>+J189*J23</f>
@@ -11914,17 +11917,17 @@
     <row r="191" spans="1:19" ht="15.9" customHeight="1">
       <c r="A191" s="51"/>
       <c r="B191" s="162"/>
-      <c r="C191" s="632" t="s">
+      <c r="C191" s="664" t="s">
         <v>216</v>
       </c>
-      <c r="D191" s="632"/>
+      <c r="D191" s="664"/>
       <c r="E191" s="163"/>
       <c r="F191" s="163"/>
       <c r="G191" s="102">
         <f>+G190*25%</f>
         <v>0</v>
       </c>
-      <c r="H191" s="649"/>
+      <c r="H191" s="693"/>
       <c r="I191" s="162"/>
       <c r="J191" s="102">
         <f>+J190*25%</f>
@@ -11934,17 +11937,17 @@
     <row r="192" spans="1:19" ht="15.9" customHeight="1">
       <c r="A192" s="51"/>
       <c r="B192" s="162"/>
-      <c r="C192" s="616" t="s">
+      <c r="C192" s="620" t="s">
         <v>217</v>
       </c>
-      <c r="D192" s="617"/>
+      <c r="D192" s="627"/>
       <c r="E192" s="163"/>
       <c r="F192" s="163"/>
       <c r="G192" s="102">
         <f>+G191*1%</f>
         <v>0</v>
       </c>
-      <c r="H192" s="649"/>
+      <c r="H192" s="693"/>
       <c r="I192" s="162"/>
       <c r="J192" s="102">
         <f>G192/J5</f>
@@ -11954,17 +11957,17 @@
     <row r="193" spans="1:20" ht="15.9" customHeight="1">
       <c r="A193" s="51"/>
       <c r="B193" s="162"/>
-      <c r="C193" s="616" t="s">
+      <c r="C193" s="620" t="s">
         <v>218</v>
       </c>
-      <c r="D193" s="617"/>
+      <c r="D193" s="627"/>
       <c r="E193" s="163"/>
       <c r="F193" s="163"/>
       <c r="G193" s="102">
         <f>G192*0.5</f>
         <v>0</v>
       </c>
-      <c r="H193" s="649"/>
+      <c r="H193" s="693"/>
       <c r="I193" s="162"/>
       <c r="J193" s="102">
         <f>G193/J5</f>
@@ -11974,17 +11977,17 @@
     <row r="194" spans="1:20" ht="15.9" customHeight="1" thickBot="1">
       <c r="A194" s="51"/>
       <c r="B194" s="162"/>
-      <c r="C194" s="632" t="s">
+      <c r="C194" s="664" t="s">
         <v>219</v>
       </c>
-      <c r="D194" s="632"/>
+      <c r="D194" s="664"/>
       <c r="E194" s="163"/>
       <c r="F194" s="163"/>
       <c r="G194" s="110">
         <f>G82</f>
         <v>565315.30184775486</v>
       </c>
-      <c r="H194" s="649"/>
+      <c r="H194" s="693"/>
       <c r="I194" s="162"/>
       <c r="J194" s="110">
         <f>+J192+J193</f>
@@ -11994,8 +11997,8 @@
     <row r="195" spans="1:20" ht="15.9" customHeight="1">
       <c r="A195" s="166"/>
       <c r="B195" s="382"/>
-      <c r="C195" s="633"/>
-      <c r="D195" s="633"/>
+      <c r="C195" s="632"/>
+      <c r="D195" s="632"/>
       <c r="E195" s="379"/>
       <c r="F195" s="379" t="s">
         <v>190</v>
@@ -12003,7 +12006,7 @@
       <c r="G195" s="53" t="s">
         <v>190</v>
       </c>
-      <c r="H195" s="649"/>
+      <c r="H195" s="693"/>
       <c r="I195" s="229" t="s">
         <v>67</v>
       </c>
@@ -12014,17 +12017,17 @@
     <row r="196" spans="1:20" ht="15.9" customHeight="1">
       <c r="A196" s="74"/>
       <c r="B196" s="99"/>
-      <c r="C196" s="618" t="s">
+      <c r="C196" s="626" t="s">
         <v>220</v>
       </c>
-      <c r="D196" s="617"/>
+      <c r="D196" s="627"/>
       <c r="E196" s="58"/>
       <c r="F196" s="50"/>
       <c r="G196" s="102">
         <f>+G54</f>
         <v>72</v>
       </c>
-      <c r="H196" s="649"/>
+      <c r="H196" s="693"/>
       <c r="I196" s="91"/>
       <c r="J196" s="102">
         <f>+J54</f>
@@ -12034,17 +12037,17 @@
     <row r="197" spans="1:20" ht="15.9" customHeight="1">
       <c r="A197" s="74"/>
       <c r="B197" s="99"/>
-      <c r="C197" s="618" t="s">
+      <c r="C197" s="626" t="s">
         <v>221</v>
       </c>
-      <c r="D197" s="617"/>
+      <c r="D197" s="627"/>
       <c r="E197" s="58"/>
       <c r="F197" s="50"/>
       <c r="G197" s="102">
         <f>F140</f>
         <v>9515</v>
       </c>
-      <c r="H197" s="649"/>
+      <c r="H197" s="693"/>
       <c r="I197" s="91"/>
       <c r="J197" s="102">
         <f>I140</f>
@@ -12054,17 +12057,17 @@
     <row r="198" spans="1:20" ht="15.9" customHeight="1">
       <c r="A198" s="120"/>
       <c r="B198" s="99"/>
-      <c r="C198" s="618" t="s">
+      <c r="C198" s="626" t="s">
         <v>222</v>
       </c>
-      <c r="D198" s="617"/>
+      <c r="D198" s="627"/>
       <c r="E198" s="58"/>
       <c r="F198" s="50"/>
       <c r="G198" s="111">
         <f>+F60</f>
         <v>129</v>
       </c>
-      <c r="H198" s="649"/>
+      <c r="H198" s="693"/>
       <c r="I198" s="91"/>
       <c r="J198" s="111">
         <f>+I60</f>
@@ -12074,17 +12077,17 @@
     <row r="199" spans="1:20" ht="15.9" customHeight="1">
       <c r="A199" s="74"/>
       <c r="B199" s="99"/>
-      <c r="C199" s="618" t="s">
+      <c r="C199" s="626" t="s">
         <v>222</v>
       </c>
-      <c r="D199" s="617"/>
+      <c r="D199" s="627"/>
       <c r="E199" s="58"/>
       <c r="F199" s="50"/>
       <c r="G199" s="102">
         <f>(G197*G198*G196)</f>
         <v>88375320</v>
       </c>
-      <c r="H199" s="649"/>
+      <c r="H199" s="693"/>
       <c r="I199" s="91"/>
       <c r="J199" s="102">
         <f>+G199/$J$5</f>
@@ -12094,17 +12097,17 @@
     <row r="200" spans="1:20" ht="15.9" customHeight="1">
       <c r="A200" s="74"/>
       <c r="B200" s="99"/>
-      <c r="C200" s="618" t="s">
+      <c r="C200" s="626" t="s">
         <v>223</v>
       </c>
-      <c r="D200" s="617"/>
+      <c r="D200" s="627"/>
       <c r="E200" s="58"/>
       <c r="F200" s="50"/>
       <c r="G200" s="102">
         <f>G199/G196*12</f>
         <v>14729220</v>
       </c>
-      <c r="H200" s="649"/>
+      <c r="H200" s="693"/>
       <c r="I200" s="91"/>
       <c r="J200" s="102">
         <f>+G200/$J$5</f>
@@ -12114,17 +12117,17 @@
     <row r="201" spans="1:20" ht="15.9" customHeight="1">
       <c r="A201" s="74"/>
       <c r="B201" s="99"/>
-      <c r="C201" s="618" t="s">
+      <c r="C201" s="626" t="s">
         <v>224</v>
       </c>
-      <c r="D201" s="617"/>
+      <c r="D201" s="627"/>
       <c r="E201" s="58"/>
       <c r="F201" s="50"/>
       <c r="G201" s="102">
         <f>(+G220*115%)/5</f>
         <v>3026339.9999999995</v>
       </c>
-      <c r="H201" s="649"/>
+      <c r="H201" s="693"/>
       <c r="I201" s="91"/>
       <c r="J201" s="102">
         <f>+G201/$J$5</f>
@@ -12134,17 +12137,17 @@
     <row r="202" spans="1:20" ht="15.9" customHeight="1">
       <c r="A202" s="74"/>
       <c r="B202" s="99"/>
-      <c r="C202" s="618" t="s">
+      <c r="C202" s="626" t="s">
         <v>225</v>
       </c>
-      <c r="D202" s="617"/>
+      <c r="D202" s="627"/>
       <c r="E202" s="58"/>
       <c r="F202" s="50"/>
       <c r="G202" s="102">
         <f>(+I220*115%)/5</f>
         <v>2765157.6185172233</v>
       </c>
-      <c r="H202" s="649"/>
+      <c r="H202" s="693"/>
       <c r="I202" s="91"/>
       <c r="J202" s="102">
         <f>+G202/$J$5</f>
@@ -12154,17 +12157,17 @@
     <row r="203" spans="1:20" ht="15.9" customHeight="1">
       <c r="A203" s="74"/>
       <c r="B203" s="99"/>
-      <c r="C203" s="618" t="s">
+      <c r="C203" s="626" t="s">
         <v>36</v>
       </c>
-      <c r="D203" s="617"/>
+      <c r="D203" s="627"/>
       <c r="E203" s="58"/>
       <c r="F203" s="50"/>
       <c r="G203" s="102">
         <f>+G67</f>
         <v>11418000</v>
       </c>
-      <c r="H203" s="649"/>
+      <c r="H203" s="693"/>
       <c r="I203" s="91"/>
       <c r="J203" s="102">
         <f>+G203/$J$5</f>
@@ -12174,17 +12177,17 @@
     <row r="204" spans="1:20" ht="15.9" customHeight="1">
       <c r="A204" s="74"/>
       <c r="B204" s="99"/>
-      <c r="C204" s="616" t="s">
+      <c r="C204" s="620" t="s">
         <v>226</v>
       </c>
-      <c r="D204" s="617"/>
+      <c r="D204" s="627"/>
       <c r="E204" s="58"/>
       <c r="F204" s="50"/>
       <c r="G204" s="102">
         <f>(G200+G201+G202+G203)*1.18</f>
         <v>37687686.789850324</v>
       </c>
-      <c r="H204" s="649"/>
+      <c r="H204" s="693"/>
       <c r="I204" s="91"/>
       <c r="J204" s="102">
         <f>+J200+J201+J202+J203</f>
@@ -12194,17 +12197,17 @@
     <row r="205" spans="1:20" ht="15.9" customHeight="1">
       <c r="A205" s="74"/>
       <c r="B205" s="99"/>
-      <c r="C205" s="616" t="s">
+      <c r="C205" s="620" t="s">
         <v>227</v>
       </c>
-      <c r="D205" s="617"/>
+      <c r="D205" s="627"/>
       <c r="E205" s="58"/>
       <c r="F205" s="50"/>
       <c r="G205" s="102">
         <f>G204*1%</f>
         <v>376876.86789850326</v>
       </c>
-      <c r="H205" s="649"/>
+      <c r="H205" s="693"/>
       <c r="I205" s="91"/>
       <c r="J205" s="102">
         <f>J204*1%</f>
@@ -12214,17 +12217,17 @@
     <row r="206" spans="1:20" ht="15.9" customHeight="1">
       <c r="A206" s="74"/>
       <c r="B206" s="99"/>
-      <c r="C206" s="618" t="s">
+      <c r="C206" s="626" t="s">
         <v>228</v>
       </c>
-      <c r="D206" s="617"/>
+      <c r="D206" s="627"/>
       <c r="E206" s="58"/>
       <c r="F206" s="50"/>
       <c r="G206" s="102">
         <f>G204*0.5%</f>
         <v>188438.43394925163</v>
       </c>
-      <c r="H206" s="649"/>
+      <c r="H206" s="693"/>
       <c r="I206" s="91"/>
       <c r="J206" s="102">
         <f>J204*0.5%</f>
@@ -12234,17 +12237,17 @@
     <row r="207" spans="1:20" ht="15.9" customHeight="1">
       <c r="A207" s="74"/>
       <c r="B207" s="99"/>
-      <c r="C207" s="619" t="s">
+      <c r="C207" s="622" t="s">
         <v>219</v>
       </c>
-      <c r="D207" s="620"/>
+      <c r="D207" s="623"/>
       <c r="E207" s="58"/>
       <c r="F207" s="50"/>
       <c r="G207" s="102">
         <f>G205+G206</f>
         <v>565315.30184775486</v>
       </c>
-      <c r="H207" s="649"/>
+      <c r="H207" s="693"/>
       <c r="I207" s="91"/>
       <c r="J207" s="102">
         <v>0</v>
@@ -12259,7 +12262,7 @@
       <c r="E208" s="80"/>
       <c r="F208" s="51"/>
       <c r="G208" s="337"/>
-      <c r="H208" s="649"/>
+      <c r="H208" s="693"/>
       <c r="I208" s="94"/>
       <c r="J208" s="81"/>
     </row>
@@ -12281,7 +12284,7 @@
       <c r="G209" s="161" t="s">
         <v>233</v>
       </c>
-      <c r="H209" s="649"/>
+      <c r="H209" s="693"/>
       <c r="I209" s="379" t="s">
         <v>234</v>
       </c>
@@ -12307,7 +12310,7 @@
         <f>'Lease Rent'!P39</f>
         <v>1360000</v>
       </c>
-      <c r="H210" s="649"/>
+      <c r="H210" s="693"/>
       <c r="I210" s="101">
         <f>'Lease Rent'!O39</f>
         <v>1178337.5999999999</v>
@@ -12337,7 +12340,7 @@
         <f>'Lease Rent'!P51</f>
         <v>2040000</v>
       </c>
-      <c r="H211" s="649"/>
+      <c r="H211" s="693"/>
       <c r="I211" s="101">
         <f>'Lease Rent'!O51</f>
         <v>1826423.2800000005</v>
@@ -12366,7 +12369,7 @@
         <f>'Lease Rent'!P63</f>
         <v>2040000</v>
       </c>
-      <c r="H212" s="649"/>
+      <c r="H212" s="693"/>
       <c r="I212" s="101">
         <f>'Lease Rent'!O63</f>
         <v>1917744.4440000001</v>
@@ -12395,7 +12398,7 @@
         <f>'Lease Rent'!P75</f>
         <v>2244000</v>
       </c>
-      <c r="H213" s="649"/>
+      <c r="H213" s="693"/>
       <c r="I213" s="101">
         <f>'Lease Rent'!O75</f>
         <v>2013631.6662000006</v>
@@ -12424,7 +12427,7 @@
         <f>'Lease Rent'!P87</f>
         <v>2345999.9999999995</v>
       </c>
-      <c r="H214" s="649"/>
+      <c r="H214" s="693"/>
       <c r="I214" s="101">
         <f>'Lease Rent'!O87</f>
         <v>2114313.2495100005</v>
@@ -12453,7 +12456,7 @@
         <f>'Lease Rent'!P99</f>
         <v>2345999.9999999995</v>
       </c>
-      <c r="H215" s="649"/>
+      <c r="H215" s="693"/>
       <c r="I215" s="101">
         <f>'Lease Rent'!O99</f>
         <v>2220028.9119855007</v>
@@ -12481,7 +12484,7 @@
         <f>'Lease Rent'!P103</f>
         <v>781999.99999999988</v>
       </c>
-      <c r="H216" s="649"/>
+      <c r="H216" s="693"/>
       <c r="I216" s="101">
         <f>'Lease Rent'!O103</f>
         <v>751945.27664025011</v>
@@ -12504,7 +12507,7 @@
         <f>'Lease Rent'!R10</f>
         <v>0</v>
       </c>
-      <c r="H217" s="649"/>
+      <c r="H217" s="693"/>
       <c r="I217" s="301"/>
       <c r="J217" s="111"/>
     </row>
@@ -12521,7 +12524,7 @@
         <v>0</v>
       </c>
       <c r="G218" s="118"/>
-      <c r="H218" s="649"/>
+      <c r="H218" s="693"/>
       <c r="I218" s="101"/>
       <c r="J218" s="111"/>
     </row>
@@ -12535,7 +12538,7 @@
       <c r="E219" s="117"/>
       <c r="F219" s="232"/>
       <c r="G219" s="118"/>
-      <c r="H219" s="649"/>
+      <c r="H219" s="693"/>
       <c r="I219" s="101"/>
       <c r="J219" s="111"/>
     </row>
@@ -12558,7 +12561,7 @@
         <f>SUM(G210:G219)</f>
         <v>13158000</v>
       </c>
-      <c r="H220" s="650"/>
+      <c r="H220" s="694"/>
       <c r="I220" s="283">
         <f>SUM(I210:I219)</f>
         <v>12022424.428335754</v>
@@ -12628,35 +12631,190 @@
     </row>
   </sheetData>
   <mergeCells count="237">
-    <mergeCell ref="F137:G137"/>
-    <mergeCell ref="I137:J137"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C131:D131"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="B134:D134"/>
-    <mergeCell ref="C106:D106"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="B105:D105"/>
-    <mergeCell ref="C124:D124"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="C204:D204"/>
+    <mergeCell ref="C203:D203"/>
+    <mergeCell ref="C161:D161"/>
+    <mergeCell ref="B138:D138"/>
+    <mergeCell ref="C141:D141"/>
+    <mergeCell ref="C120:D120"/>
+    <mergeCell ref="C192:D192"/>
+    <mergeCell ref="C193:D193"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="C189:D189"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C160:D160"/>
+    <mergeCell ref="C190:D190"/>
+    <mergeCell ref="B179:D179"/>
+    <mergeCell ref="C162:D162"/>
+    <mergeCell ref="C165:D165"/>
+    <mergeCell ref="C205:D205"/>
+    <mergeCell ref="C206:D206"/>
+    <mergeCell ref="C207:D207"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C174:D174"/>
+    <mergeCell ref="C197:D197"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="C199:D199"/>
+    <mergeCell ref="C200:D200"/>
+    <mergeCell ref="C201:D201"/>
+    <mergeCell ref="C202:D202"/>
+    <mergeCell ref="C188:D188"/>
+    <mergeCell ref="C191:D191"/>
+    <mergeCell ref="C194:D194"/>
+    <mergeCell ref="C195:D195"/>
+    <mergeCell ref="C196:D196"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C181:D181"/>
+    <mergeCell ref="C185:D185"/>
+    <mergeCell ref="C168:D168"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="C169:D169"/>
+    <mergeCell ref="C183:D183"/>
+    <mergeCell ref="C170:D170"/>
+    <mergeCell ref="C140:D140"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="C122:D122"/>
+    <mergeCell ref="C171:D171"/>
+    <mergeCell ref="C167:D167"/>
+    <mergeCell ref="B147:D147"/>
+    <mergeCell ref="B163:D164"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="C144:D144"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="C166:D166"/>
+    <mergeCell ref="C182:D182"/>
+    <mergeCell ref="H188:H220"/>
+    <mergeCell ref="C159:D159"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B187:J187"/>
+    <mergeCell ref="C172:D172"/>
+    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="C177:D177"/>
+    <mergeCell ref="C180:D180"/>
+    <mergeCell ref="C157:D157"/>
+    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="C175:D175"/>
+    <mergeCell ref="C149:D149"/>
+    <mergeCell ref="C150:D150"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="C143:D143"/>
+    <mergeCell ref="C184:D184"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B1:J3"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C48:D48"/>
     <mergeCell ref="F52:G52"/>
     <mergeCell ref="F48:G48"/>
     <mergeCell ref="F49:G49"/>
@@ -12681,190 +12839,35 @@
     <mergeCell ref="C135:D135"/>
     <mergeCell ref="C136:D136"/>
     <mergeCell ref="C133:D133"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B1:J3"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="H188:H220"/>
-    <mergeCell ref="C159:D159"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B187:J187"/>
-    <mergeCell ref="C172:D172"/>
-    <mergeCell ref="C176:D176"/>
-    <mergeCell ref="C177:D177"/>
-    <mergeCell ref="C180:D180"/>
-    <mergeCell ref="C157:D157"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="C175:D175"/>
-    <mergeCell ref="C149:D149"/>
-    <mergeCell ref="C150:D150"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="I58:J58"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="C143:D143"/>
-    <mergeCell ref="C184:D184"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C181:D181"/>
-    <mergeCell ref="C185:D185"/>
-    <mergeCell ref="C168:D168"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="C169:D169"/>
-    <mergeCell ref="C183:D183"/>
-    <mergeCell ref="C170:D170"/>
-    <mergeCell ref="C140:D140"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="C122:D122"/>
-    <mergeCell ref="C171:D171"/>
-    <mergeCell ref="C167:D167"/>
-    <mergeCell ref="B147:D147"/>
-    <mergeCell ref="B163:D164"/>
-    <mergeCell ref="B125:D125"/>
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="C144:D144"/>
-    <mergeCell ref="C139:D139"/>
-    <mergeCell ref="C166:D166"/>
-    <mergeCell ref="C182:D182"/>
-    <mergeCell ref="C205:D205"/>
-    <mergeCell ref="C206:D206"/>
-    <mergeCell ref="C207:D207"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C174:D174"/>
-    <mergeCell ref="C197:D197"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="C199:D199"/>
-    <mergeCell ref="C200:D200"/>
-    <mergeCell ref="C201:D201"/>
-    <mergeCell ref="C202:D202"/>
-    <mergeCell ref="C188:D188"/>
-    <mergeCell ref="C191:D191"/>
-    <mergeCell ref="C194:D194"/>
-    <mergeCell ref="C195:D195"/>
-    <mergeCell ref="C196:D196"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C204:D204"/>
-    <mergeCell ref="C203:D203"/>
-    <mergeCell ref="C161:D161"/>
-    <mergeCell ref="B138:D138"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="C120:D120"/>
-    <mergeCell ref="C192:D192"/>
-    <mergeCell ref="C193:D193"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="C189:D189"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C160:D160"/>
-    <mergeCell ref="C190:D190"/>
-    <mergeCell ref="B179:D179"/>
-    <mergeCell ref="C162:D162"/>
-    <mergeCell ref="C165:D165"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="B134:D134"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="B105:D105"/>
+    <mergeCell ref="C124:D124"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="F137:G137"/>
+    <mergeCell ref="I137:J137"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C107:D107"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.25" top="0.75" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="58" orientation="portrait" r:id="rId1"/>
@@ -23898,27 +23901,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" xsi:nil="true"/>
-    <Status xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100907921E7373C1341A3C877D189CE8922" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2036b66ca2b7955135caa708c7901a86">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xmlns:ns3="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fed2217af4f675ffeab875e34aa73a78" ns2:_="" ns3:_="">
     <xsd:import namespace="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
@@ -24161,26 +24143,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC57694E-BA35-486E-AC74-B7B624F1FDE0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" xsi:nil="true"/>
+    <Status xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12D5BE44-B07C-4182-BC7A-71E5962390BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
-    <ds:schemaRef ds:uri="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB719E29-C329-4AB1-8ED0-5CC29C0FF757}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24199,6 +24183,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12D5BE44-B07C-4182-BC7A-71E5962390BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
+    <ds:schemaRef ds:uri="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC57694E-BA35-486E-AC74-B7B624F1FDE0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{a59b6cd5-d141-4a33-8bf1-0ca04484304f}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" removed="0"/>

--- a/artifacts/Rental Specimen.xlsx
+++ b/artifacts/Rental Specimen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z0050s8t\Documents\rental-automation\artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28BE0EA-D0ED-4868-B8A0-9801CEFF7438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A123D19-52D3-4436-B578-CA13EBFCA27B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="764" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="764" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="26" r:id="rId1"/>
@@ -5546,6 +5546,297 @@
     <xf numFmtId="1" fontId="14" fillId="0" borderId="8" xfId="190" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="8" xfId="21" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="33" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="29" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5558,12 +5849,6 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5617,291 +5902,6 @@
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="50" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="33" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="29" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="192" fontId="52" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7473,62 +7473,62 @@
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1">
       <c r="A1" s="51"/>
-      <c r="B1" s="655"/>
-      <c r="C1" s="656"/>
-      <c r="D1" s="656"/>
-      <c r="E1" s="656"/>
-      <c r="F1" s="656"/>
-      <c r="G1" s="656"/>
-      <c r="H1" s="656"/>
-      <c r="I1" s="656"/>
-      <c r="J1" s="657"/>
+      <c r="B1" s="641"/>
+      <c r="C1" s="642"/>
+      <c r="D1" s="642"/>
+      <c r="E1" s="642"/>
+      <c r="F1" s="642"/>
+      <c r="G1" s="642"/>
+      <c r="H1" s="642"/>
+      <c r="I1" s="642"/>
+      <c r="J1" s="643"/>
     </row>
     <row r="2" spans="1:10" ht="14.25" customHeight="1">
       <c r="A2" s="51"/>
-      <c r="B2" s="658"/>
-      <c r="C2" s="659"/>
-      <c r="D2" s="659"/>
-      <c r="E2" s="659"/>
-      <c r="F2" s="659"/>
-      <c r="G2" s="659"/>
-      <c r="H2" s="659"/>
-      <c r="I2" s="659"/>
-      <c r="J2" s="660"/>
+      <c r="B2" s="644"/>
+      <c r="C2" s="645"/>
+      <c r="D2" s="645"/>
+      <c r="E2" s="645"/>
+      <c r="F2" s="645"/>
+      <c r="G2" s="645"/>
+      <c r="H2" s="645"/>
+      <c r="I2" s="645"/>
+      <c r="J2" s="646"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A3" s="51"/>
-      <c r="B3" s="661"/>
-      <c r="C3" s="662"/>
-      <c r="D3" s="662"/>
-      <c r="E3" s="662"/>
-      <c r="F3" s="662"/>
-      <c r="G3" s="662"/>
-      <c r="H3" s="662"/>
-      <c r="I3" s="659"/>
-      <c r="J3" s="660"/>
+      <c r="B3" s="647"/>
+      <c r="C3" s="648"/>
+      <c r="D3" s="648"/>
+      <c r="E3" s="648"/>
+      <c r="F3" s="648"/>
+      <c r="G3" s="648"/>
+      <c r="H3" s="648"/>
+      <c r="I3" s="645"/>
+      <c r="J3" s="646"/>
     </row>
     <row r="4" spans="1:10" ht="13">
       <c r="A4" s="51"/>
-      <c r="B4" s="596"/>
-      <c r="C4" s="597"/>
-      <c r="D4" s="597"/>
-      <c r="E4" s="597"/>
-      <c r="F4" s="597"/>
-      <c r="G4" s="597"/>
+      <c r="B4" s="668"/>
+      <c r="C4" s="669"/>
+      <c r="D4" s="669"/>
+      <c r="E4" s="669"/>
+      <c r="F4" s="669"/>
+      <c r="G4" s="669"/>
       <c r="H4" s="401"/>
       <c r="I4" s="402"/>
       <c r="J4" s="403"/>
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="51"/>
-      <c r="B5" s="680" t="s">
+      <c r="B5" s="670" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="681"/>
-      <c r="D5" s="681"/>
-      <c r="E5" s="681"/>
-      <c r="F5" s="681"/>
-      <c r="G5" s="682"/>
+      <c r="C5" s="671"/>
+      <c r="D5" s="671"/>
+      <c r="E5" s="671"/>
+      <c r="F5" s="671"/>
+      <c r="G5" s="672"/>
       <c r="H5" s="404"/>
       <c r="I5" s="481" t="s">
         <v>16</v>
@@ -7539,29 +7539,29 @@
     </row>
     <row r="6" spans="1:10" ht="13.5" thickBot="1">
       <c r="A6" s="51"/>
-      <c r="B6" s="683"/>
-      <c r="C6" s="684"/>
-      <c r="D6" s="685"/>
+      <c r="B6" s="673"/>
+      <c r="C6" s="674"/>
+      <c r="D6" s="675"/>
       <c r="E6" s="52"/>
-      <c r="F6" s="678">
+      <c r="F6" s="666">
         <v>10.763999999999999</v>
       </c>
-      <c r="G6" s="679"/>
+      <c r="G6" s="667"/>
       <c r="H6" s="405"/>
-      <c r="I6" s="669">
+      <c r="I6" s="654">
         <v>10.763999999999999</v>
       </c>
-      <c r="J6" s="670"/>
+      <c r="J6" s="655"/>
     </row>
     <row r="7" spans="1:10" ht="26">
       <c r="A7" s="51"/>
       <c r="B7" s="482" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="686" t="s">
+      <c r="C7" s="676" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="687"/>
+      <c r="D7" s="677"/>
       <c r="E7" s="483"/>
       <c r="F7" s="483" t="s">
         <v>303</v>
@@ -7589,23 +7589,23 @@
       <c r="C8" s="486"/>
       <c r="D8" s="487"/>
       <c r="E8" s="488"/>
-      <c r="F8" s="616" t="s">
+      <c r="F8" s="600" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="617"/>
+      <c r="G8" s="634"/>
       <c r="H8" s="404"/>
-      <c r="I8" s="618" t="s">
+      <c r="I8" s="635" t="s">
         <v>67</v>
       </c>
-      <c r="J8" s="619"/>
+      <c r="J8" s="636"/>
     </row>
     <row r="9" spans="1:10" ht="13">
       <c r="A9" s="51"/>
-      <c r="B9" s="618" t="s">
+      <c r="B9" s="635" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="617"/>
-      <c r="D9" s="633"/>
+      <c r="C9" s="634"/>
+      <c r="D9" s="601"/>
       <c r="E9" s="489"/>
       <c r="F9" s="376" t="s">
         <v>75</v>
@@ -7626,21 +7626,21 @@
       <c r="B10" s="490">
         <v>1</v>
       </c>
-      <c r="C10" s="663" t="s">
+      <c r="C10" s="649" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="664"/>
+      <c r="D10" s="608"/>
       <c r="E10" s="491"/>
-      <c r="F10" s="675" t="s">
+      <c r="F10" s="660" t="s">
         <v>299</v>
       </c>
-      <c r="G10" s="676"/>
+      <c r="G10" s="661"/>
       <c r="H10" s="404"/>
-      <c r="I10" s="671" t="str">
+      <c r="I10" s="656" t="str">
         <f>+F10</f>
         <v>Chennai</v>
       </c>
-      <c r="J10" s="672"/>
+      <c r="J10" s="657"/>
     </row>
     <row r="11" spans="1:10" ht="28.5" customHeight="1">
       <c r="A11" s="51"/>
@@ -7648,19 +7648,19 @@
         <f>1+B10</f>
         <v>2</v>
       </c>
-      <c r="C11" s="665" t="s">
+      <c r="C11" s="650" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="666"/>
+      <c r="D11" s="651"/>
       <c r="E11" s="50"/>
-      <c r="F11" s="675"/>
-      <c r="G11" s="676"/>
+      <c r="F11" s="660"/>
+      <c r="G11" s="661"/>
       <c r="H11" s="404"/>
-      <c r="I11" s="673">
+      <c r="I11" s="658">
         <f>+F11</f>
         <v>0</v>
       </c>
-      <c r="J11" s="674"/>
+      <c r="J11" s="659"/>
     </row>
     <row r="12" spans="1:10" ht="27.75" customHeight="1">
       <c r="A12" s="51"/>
@@ -7668,19 +7668,19 @@
         <f>1+B11</f>
         <v>3</v>
       </c>
-      <c r="C12" s="626" t="s">
+      <c r="C12" s="594" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="627"/>
+      <c r="D12" s="593"/>
       <c r="E12" s="492"/>
-      <c r="F12" s="654"/>
-      <c r="G12" s="649"/>
+      <c r="F12" s="662"/>
+      <c r="G12" s="663"/>
       <c r="H12" s="404"/>
-      <c r="I12" s="650">
+      <c r="I12" s="678">
         <f>+F12</f>
         <v>0</v>
       </c>
-      <c r="J12" s="651"/>
+      <c r="J12" s="679"/>
     </row>
     <row r="13" spans="1:10" ht="15.9" customHeight="1">
       <c r="A13" s="51"/>
@@ -7688,16 +7688,16 @@
         <f t="shared" ref="B13:B30" si="0">1+B12</f>
         <v>4</v>
       </c>
-      <c r="C13" s="626" t="s">
+      <c r="C13" s="594" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="627"/>
+      <c r="D13" s="593"/>
       <c r="E13" s="50"/>
-      <c r="F13" s="648"/>
-      <c r="G13" s="649"/>
+      <c r="F13" s="665"/>
+      <c r="G13" s="663"/>
       <c r="H13" s="404"/>
-      <c r="I13" s="650"/>
-      <c r="J13" s="651"/>
+      <c r="I13" s="678"/>
+      <c r="J13" s="679"/>
     </row>
     <row r="14" spans="1:10" ht="48" customHeight="1">
       <c r="A14" s="51"/>
@@ -7705,21 +7705,21 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="667" t="s">
+      <c r="C14" s="652" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="668"/>
+      <c r="D14" s="653"/>
       <c r="E14" s="476"/>
-      <c r="F14" s="654" t="s">
+      <c r="F14" s="662" t="s">
         <v>300</v>
       </c>
-      <c r="G14" s="677"/>
+      <c r="G14" s="664"/>
       <c r="H14" s="404"/>
-      <c r="I14" s="650" t="str">
+      <c r="I14" s="678" t="str">
         <f>+F14</f>
         <v>6th floor</v>
       </c>
-      <c r="J14" s="651"/>
+      <c r="J14" s="679"/>
     </row>
     <row r="15" spans="1:10" ht="51.75" customHeight="1">
       <c r="A15" s="51"/>
@@ -7727,19 +7727,19 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="626" t="s">
+      <c r="C15" s="594" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="627"/>
+      <c r="D15" s="593"/>
       <c r="E15" s="58"/>
-      <c r="F15" s="616"/>
-      <c r="G15" s="617"/>
+      <c r="F15" s="600"/>
+      <c r="G15" s="634"/>
       <c r="H15" s="404"/>
-      <c r="I15" s="618">
+      <c r="I15" s="635">
         <f>+F15</f>
         <v>0</v>
       </c>
-      <c r="J15" s="619"/>
+      <c r="J15" s="636"/>
     </row>
     <row r="16" spans="1:10" ht="15.9" customHeight="1">
       <c r="A16" s="51"/>
@@ -7747,16 +7747,16 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="626" t="s">
+      <c r="C16" s="594" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="627"/>
+      <c r="D16" s="593"/>
       <c r="E16" s="58"/>
-      <c r="F16" s="648"/>
-      <c r="G16" s="649"/>
+      <c r="F16" s="665"/>
+      <c r="G16" s="663"/>
       <c r="H16" s="404"/>
-      <c r="I16" s="650"/>
-      <c r="J16" s="651"/>
+      <c r="I16" s="678"/>
+      <c r="J16" s="679"/>
     </row>
     <row r="17" spans="1:10" ht="15.9" customHeight="1">
       <c r="A17" s="51"/>
@@ -7764,21 +7764,21 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="626" t="s">
+      <c r="C17" s="594" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="627"/>
+      <c r="D17" s="593"/>
       <c r="E17" s="58"/>
-      <c r="F17" s="654" t="s">
+      <c r="F17" s="662" t="s">
         <v>85</v>
       </c>
-      <c r="G17" s="649"/>
+      <c r="G17" s="663"/>
       <c r="H17" s="404"/>
-      <c r="I17" s="650" t="str">
+      <c r="I17" s="678" t="str">
         <f>+F17</f>
         <v>Warm Shell</v>
       </c>
-      <c r="J17" s="651"/>
+      <c r="J17" s="679"/>
     </row>
     <row r="18" spans="1:10" ht="48" customHeight="1">
       <c r="A18" s="51"/>
@@ -7786,22 +7786,22 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="626" t="s">
+      <c r="C18" s="594" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="627"/>
+      <c r="D18" s="593"/>
       <c r="E18" s="163"/>
-      <c r="F18" s="616">
+      <c r="F18" s="600">
         <f>F15</f>
         <v>0</v>
       </c>
-      <c r="G18" s="617"/>
+      <c r="G18" s="634"/>
       <c r="H18" s="404"/>
-      <c r="I18" s="618">
+      <c r="I18" s="635">
         <f>+F18</f>
         <v>0</v>
       </c>
-      <c r="J18" s="619"/>
+      <c r="J18" s="636"/>
     </row>
     <row r="19" spans="1:10" ht="15.9" customHeight="1">
       <c r="A19" s="51"/>
@@ -7809,16 +7809,16 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="626" t="s">
+      <c r="C19" s="594" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="627"/>
+      <c r="D19" s="593"/>
       <c r="E19" s="163"/>
-      <c r="F19" s="648"/>
-      <c r="G19" s="649"/>
+      <c r="F19" s="665"/>
+      <c r="G19" s="663"/>
       <c r="H19" s="404"/>
-      <c r="I19" s="650"/>
-      <c r="J19" s="651"/>
+      <c r="I19" s="678"/>
+      <c r="J19" s="679"/>
     </row>
     <row r="20" spans="1:10" ht="15.9" customHeight="1">
       <c r="A20" s="51"/>
@@ -7826,10 +7826,10 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="620" t="s">
+      <c r="C20" s="592" t="s">
         <v>88</v>
       </c>
-      <c r="D20" s="627"/>
+      <c r="D20" s="593"/>
       <c r="E20" s="494"/>
       <c r="F20" s="56"/>
       <c r="G20" s="388"/>
@@ -7849,10 +7849,10 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="626" t="s">
+      <c r="C21" s="594" t="s">
         <v>89</v>
       </c>
-      <c r="D21" s="627"/>
+      <c r="D21" s="593"/>
       <c r="E21" s="494"/>
       <c r="F21" s="56">
         <f>Main!B3</f>
@@ -7878,10 +7878,10 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="620" t="s">
+      <c r="C22" s="592" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="627"/>
+      <c r="D22" s="593"/>
       <c r="E22" s="494"/>
       <c r="F22" s="56">
         <v>0</v>
@@ -7905,10 +7905,10 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="626" t="s">
+      <c r="C23" s="594" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="627"/>
+      <c r="D23" s="593"/>
       <c r="E23" s="494"/>
       <c r="F23" s="56">
         <f>+F21+F22</f>
@@ -7934,10 +7934,10 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="626" t="s">
+      <c r="C24" s="594" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="627"/>
+      <c r="D24" s="593"/>
       <c r="E24" s="59"/>
       <c r="F24" s="56"/>
       <c r="G24" s="388">
@@ -7960,10 +7960,10 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="626" t="s">
+      <c r="C25" s="594" t="s">
         <v>93</v>
       </c>
-      <c r="D25" s="627"/>
+      <c r="D25" s="593"/>
       <c r="E25" s="59"/>
       <c r="F25" s="56">
         <v>0</v>
@@ -7988,10 +7988,10 @@
         <f>1+B25</f>
         <v>17</v>
       </c>
-      <c r="C26" s="626" t="s">
+      <c r="C26" s="594" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="627"/>
+      <c r="D26" s="593"/>
       <c r="E26" s="60"/>
       <c r="F26" s="61">
         <f>F25/F23</f>
@@ -8017,10 +8017,10 @@
         <f>1+B26</f>
         <v>18</v>
       </c>
-      <c r="C27" s="620" t="s">
+      <c r="C27" s="592" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="627"/>
+      <c r="D27" s="593"/>
       <c r="E27" s="58"/>
       <c r="F27" s="293">
         <f>'CAPEX and PM'!E3</f>
@@ -8046,10 +8046,10 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="620" t="s">
+      <c r="C28" s="592" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="627"/>
+      <c r="D28" s="593"/>
       <c r="E28" s="64"/>
       <c r="F28" s="64">
         <f>Main!B12</f>
@@ -8075,10 +8075,10 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="620" t="s">
+      <c r="C29" s="592" t="s">
         <v>97</v>
       </c>
-      <c r="D29" s="627"/>
+      <c r="D29" s="593"/>
       <c r="E29" s="64"/>
       <c r="F29" s="60">
         <f>Main!B13</f>
@@ -8104,10 +8104,10 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="626" t="s">
+      <c r="C30" s="594" t="s">
         <v>98</v>
       </c>
-      <c r="D30" s="627"/>
+      <c r="D30" s="593"/>
       <c r="E30" s="58"/>
       <c r="F30" s="56">
         <v>0</v>
@@ -8128,11 +8128,11 @@
     </row>
     <row r="31" spans="1:10" ht="15.9" customHeight="1">
       <c r="A31" s="51"/>
-      <c r="B31" s="645" t="s">
+      <c r="B31" s="680" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="646"/>
-      <c r="D31" s="647"/>
+      <c r="C31" s="681"/>
+      <c r="D31" s="682"/>
       <c r="E31" s="497"/>
       <c r="F31" s="376" t="s">
         <v>75</v>
@@ -8153,10 +8153,10 @@
       <c r="B32" s="162">
         <v>1</v>
       </c>
-      <c r="C32" s="620" t="s">
+      <c r="C32" s="592" t="s">
         <v>100</v>
       </c>
-      <c r="D32" s="627"/>
+      <c r="D32" s="593"/>
       <c r="E32" s="59"/>
       <c r="F32" s="56">
         <f>Main!B9/(Main!B3*Main!B7)</f>
@@ -8182,10 +8182,10 @@
         <f>1+B32</f>
         <v>2</v>
       </c>
-      <c r="C33" s="620" t="s">
+      <c r="C33" s="592" t="s">
         <v>101</v>
       </c>
-      <c r="D33" s="627"/>
+      <c r="D33" s="593"/>
       <c r="E33" s="59"/>
       <c r="F33" s="56">
         <v>0</v>
@@ -8209,10 +8209,10 @@
         <f t="shared" ref="B34:B47" si="1">1+B33</f>
         <v>3</v>
       </c>
-      <c r="C34" s="620" t="s">
+      <c r="C34" s="592" t="s">
         <v>102</v>
       </c>
-      <c r="D34" s="627"/>
+      <c r="D34" s="593"/>
       <c r="E34" s="59"/>
       <c r="F34" s="56">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="C35" s="626" t="s">
+      <c r="C35" s="594" t="s">
         <v>103</v>
       </c>
-      <c r="D35" s="627"/>
+      <c r="D35" s="593"/>
       <c r="E35" s="498"/>
       <c r="F35" s="68">
         <v>0</v>
@@ -8262,10 +8262,10 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="C36" s="620" t="s">
+      <c r="C36" s="592" t="s">
         <v>104</v>
       </c>
-      <c r="D36" s="627"/>
+      <c r="D36" s="593"/>
       <c r="E36" s="498"/>
       <c r="F36" s="70">
         <f>'Lease Rent'!H37</f>
@@ -8291,10 +8291,10 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="C37" s="620" t="s">
+      <c r="C37" s="592" t="s">
         <v>105</v>
       </c>
-      <c r="D37" s="627"/>
+      <c r="D37" s="593"/>
       <c r="E37" s="498"/>
       <c r="F37" s="70"/>
       <c r="G37" s="204">
@@ -8311,10 +8311,10 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="C38" s="620" t="s">
+      <c r="C38" s="592" t="s">
         <v>106</v>
       </c>
-      <c r="D38" s="627"/>
+      <c r="D38" s="593"/>
       <c r="E38" s="71"/>
       <c r="F38" s="70">
         <f>'Lease Rent'!J31</f>
@@ -8340,10 +8340,10 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="C39" s="620" t="s">
+      <c r="C39" s="592" t="s">
         <v>107</v>
       </c>
-      <c r="D39" s="627"/>
+      <c r="D39" s="593"/>
       <c r="E39" s="498"/>
       <c r="F39" s="70">
         <f>F36</f>
@@ -8369,10 +8369,10 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="C40" s="620" t="s">
+      <c r="C40" s="592" t="s">
         <v>108</v>
       </c>
-      <c r="D40" s="627"/>
+      <c r="D40" s="593"/>
       <c r="E40" s="498"/>
       <c r="F40" s="70">
         <v>0</v>
@@ -8397,10 +8397,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="C41" s="620" t="s">
+      <c r="C41" s="592" t="s">
         <v>109</v>
       </c>
-      <c r="D41" s="627"/>
+      <c r="D41" s="593"/>
       <c r="E41" s="58"/>
       <c r="F41" s="114">
         <f>F38</f>
@@ -8426,10 +8426,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="C42" s="626" t="s">
+      <c r="C42" s="594" t="s">
         <v>110</v>
       </c>
-      <c r="D42" s="627"/>
+      <c r="D42" s="593"/>
       <c r="E42" s="59"/>
       <c r="F42" s="109">
         <v>0</v>
@@ -8454,10 +8454,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="C43" s="626" t="s">
+      <c r="C43" s="594" t="s">
         <v>111</v>
       </c>
-      <c r="D43" s="627"/>
+      <c r="D43" s="593"/>
       <c r="E43" s="73"/>
       <c r="F43" s="68">
         <v>0</v>
@@ -8482,10 +8482,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="C44" s="626" t="s">
+      <c r="C44" s="594" t="s">
         <v>112</v>
       </c>
-      <c r="D44" s="627"/>
+      <c r="D44" s="593"/>
       <c r="E44" s="59"/>
       <c r="F44" s="56">
         <f>'Lease Rent'!C22</f>
@@ -8511,10 +8511,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="C45" s="620" t="s">
+      <c r="C45" s="592" t="s">
         <v>113</v>
       </c>
-      <c r="D45" s="627"/>
+      <c r="D45" s="593"/>
       <c r="E45" s="59"/>
       <c r="F45" s="109">
         <v>0</v>
@@ -8536,10 +8536,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="C46" s="626" t="s">
+      <c r="C46" s="594" t="s">
         <v>111</v>
       </c>
-      <c r="D46" s="627"/>
+      <c r="D46" s="593"/>
       <c r="E46" s="59"/>
       <c r="F46" s="56">
         <f>'Lease Rent'!D23</f>
@@ -8556,10 +8556,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="C47" s="626" t="s">
+      <c r="C47" s="594" t="s">
         <v>112</v>
       </c>
-      <c r="D47" s="627"/>
+      <c r="D47" s="593"/>
       <c r="E47" s="59"/>
       <c r="F47" s="56">
         <f>'Lease Rent'!C23</f>
@@ -8572,46 +8572,46 @@
     </row>
     <row r="48" spans="1:10" ht="28.5" customHeight="1">
       <c r="A48" s="51"/>
-      <c r="B48" s="690">
+      <c r="B48" s="639">
         <f>1+B47</f>
         <v>17</v>
       </c>
-      <c r="C48" s="620" t="s">
+      <c r="C48" s="592" t="s">
         <v>114</v>
       </c>
-      <c r="D48" s="627"/>
+      <c r="D48" s="593"/>
       <c r="E48" s="73"/>
-      <c r="F48" s="636" t="str">
+      <c r="F48" s="685" t="str">
         <f>Main!B14</f>
         <v>15% every 3 years</v>
       </c>
-      <c r="G48" s="637"/>
+      <c r="G48" s="686"/>
       <c r="H48" s="404"/>
-      <c r="I48" s="650" t="str">
+      <c r="I48" s="678" t="str">
         <f>+F48</f>
         <v>15% every 3 years</v>
       </c>
-      <c r="J48" s="651"/>
+      <c r="J48" s="679"/>
     </row>
     <row r="49" spans="1:18" ht="15.9" customHeight="1">
       <c r="A49" s="51"/>
-      <c r="B49" s="691"/>
-      <c r="C49" s="620" t="s">
+      <c r="B49" s="640"/>
+      <c r="C49" s="592" t="s">
         <v>115</v>
       </c>
-      <c r="D49" s="627"/>
+      <c r="D49" s="593"/>
       <c r="E49" s="73"/>
-      <c r="F49" s="636" t="str">
+      <c r="F49" s="685" t="str">
         <f>Main!B15</f>
         <v>5% every years</v>
       </c>
-      <c r="G49" s="637"/>
+      <c r="G49" s="686"/>
       <c r="H49" s="404"/>
-      <c r="I49" s="652" t="str">
+      <c r="I49" s="683" t="str">
         <f t="shared" ref="I49:I56" si="2">F49</f>
         <v>5% every years</v>
       </c>
-      <c r="J49" s="653"/>
+      <c r="J49" s="684"/>
     </row>
     <row r="50" spans="1:18" ht="15.9" customHeight="1">
       <c r="A50" s="51"/>
@@ -8619,22 +8619,22 @@
         <f>1+B48</f>
         <v>18</v>
       </c>
-      <c r="C50" s="626" t="s">
+      <c r="C50" s="594" t="s">
         <v>116</v>
       </c>
-      <c r="D50" s="627"/>
+      <c r="D50" s="593"/>
       <c r="E50" s="73"/>
-      <c r="F50" s="634">
+      <c r="F50" s="630">
         <f>'Lease Rent'!B31</f>
         <v>46023</v>
       </c>
-      <c r="G50" s="635"/>
+      <c r="G50" s="631"/>
       <c r="H50" s="404"/>
-      <c r="I50" s="643">
+      <c r="I50" s="632">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J50" s="644"/>
+      <c r="J50" s="633"/>
     </row>
     <row r="51" spans="1:18" ht="15.9" customHeight="1">
       <c r="A51" s="51"/>
@@ -8642,22 +8642,22 @@
         <f t="shared" ref="B51:B57" si="3">1+B50</f>
         <v>19</v>
       </c>
-      <c r="C51" s="620" t="s">
+      <c r="C51" s="592" t="s">
         <v>117</v>
       </c>
-      <c r="D51" s="627"/>
+      <c r="D51" s="593"/>
       <c r="E51" s="73"/>
-      <c r="F51" s="634">
+      <c r="F51" s="630">
         <f>'Lease Rent'!C102</f>
         <v>48213</v>
       </c>
-      <c r="G51" s="635"/>
+      <c r="G51" s="631"/>
       <c r="H51" s="404"/>
-      <c r="I51" s="643">
+      <c r="I51" s="632">
         <f>F51</f>
         <v>48213</v>
       </c>
-      <c r="J51" s="644"/>
+      <c r="J51" s="633"/>
     </row>
     <row r="52" spans="1:18" ht="15.9" customHeight="1">
       <c r="A52" s="51"/>
@@ -8665,22 +8665,22 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="C52" s="620" t="s">
+      <c r="C52" s="592" t="s">
         <v>118</v>
       </c>
-      <c r="D52" s="621"/>
+      <c r="D52" s="602"/>
       <c r="E52" s="73"/>
-      <c r="F52" s="634">
+      <c r="F52" s="630">
         <f>F50</f>
         <v>46023</v>
       </c>
-      <c r="G52" s="635"/>
+      <c r="G52" s="631"/>
       <c r="H52" s="404"/>
-      <c r="I52" s="643">
+      <c r="I52" s="632">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J52" s="644"/>
+      <c r="J52" s="633"/>
     </row>
     <row r="53" spans="1:18" ht="15.9" customHeight="1">
       <c r="A53" s="51"/>
@@ -8688,21 +8688,21 @@
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="C53" s="620" t="s">
+      <c r="C53" s="592" t="s">
         <v>119</v>
       </c>
-      <c r="D53" s="621"/>
+      <c r="D53" s="602"/>
       <c r="E53" s="73"/>
-      <c r="F53" s="616">
-        <v>0</v>
-      </c>
-      <c r="G53" s="617"/>
+      <c r="F53" s="600">
+        <v>0</v>
+      </c>
+      <c r="G53" s="634"/>
       <c r="H53" s="404"/>
-      <c r="I53" s="618">
+      <c r="I53" s="635">
         <f>+F53</f>
         <v>0</v>
       </c>
-      <c r="J53" s="619"/>
+      <c r="J53" s="636"/>
     </row>
     <row r="54" spans="1:18" ht="15.9" customHeight="1">
       <c r="A54" s="51"/>
@@ -8710,10 +8710,10 @@
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="C54" s="626" t="s">
+      <c r="C54" s="594" t="s">
         <v>120</v>
       </c>
-      <c r="D54" s="627"/>
+      <c r="D54" s="593"/>
       <c r="E54" s="58"/>
       <c r="F54" s="56">
         <f>(F51-F50)/365*12</f>
@@ -8740,10 +8740,10 @@
         <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="C55" s="626" t="s">
+      <c r="C55" s="594" t="s">
         <v>121</v>
       </c>
-      <c r="D55" s="627"/>
+      <c r="D55" s="593"/>
       <c r="E55" s="71"/>
       <c r="F55" s="56">
         <v>0</v>
@@ -8769,10 +8769,10 @@
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="C56" s="626" t="s">
+      <c r="C56" s="594" t="s">
         <v>122</v>
       </c>
-      <c r="D56" s="627"/>
+      <c r="D56" s="593"/>
       <c r="E56" s="71"/>
       <c r="F56" s="302" t="s">
         <v>68</v>
@@ -8798,10 +8798,10 @@
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="C57" s="626" t="s">
+      <c r="C57" s="594" t="s">
         <v>123</v>
       </c>
-      <c r="D57" s="627"/>
+      <c r="D57" s="593"/>
       <c r="E57" s="71"/>
       <c r="F57" s="56"/>
       <c r="G57" s="388"/>
@@ -8816,23 +8816,23 @@
       <c r="C58" s="74"/>
       <c r="D58" s="74"/>
       <c r="E58" s="58"/>
-      <c r="F58" s="616" t="s">
+      <c r="F58" s="600" t="s">
         <v>73</v>
       </c>
-      <c r="G58" s="617"/>
+      <c r="G58" s="634"/>
       <c r="H58" s="404"/>
-      <c r="I58" s="618" t="s">
+      <c r="I58" s="635" t="s">
         <v>67</v>
       </c>
-      <c r="J58" s="619"/>
+      <c r="J58" s="636"/>
     </row>
     <row r="59" spans="1:18" ht="15.9" customHeight="1">
       <c r="A59" s="51"/>
-      <c r="B59" s="688" t="s">
+      <c r="B59" s="637" t="s">
         <v>124</v>
       </c>
-      <c r="C59" s="689"/>
-      <c r="D59" s="689"/>
+      <c r="C59" s="638"/>
+      <c r="D59" s="638"/>
       <c r="E59" s="497"/>
       <c r="F59" s="376" t="s">
         <v>75</v>
@@ -8853,10 +8853,10 @@
       <c r="B60" s="162">
         <v>1</v>
       </c>
-      <c r="C60" s="620" t="s">
+      <c r="C60" s="592" t="s">
         <v>125</v>
       </c>
-      <c r="D60" s="627"/>
+      <c r="D60" s="593"/>
       <c r="E60" s="499"/>
       <c r="F60" s="70">
         <f>C220/F21/F54</f>
@@ -8882,10 +8882,10 @@
         <f>1+B60</f>
         <v>2</v>
       </c>
-      <c r="C61" s="620" t="s">
+      <c r="C61" s="592" t="s">
         <v>126</v>
       </c>
-      <c r="D61" s="627"/>
+      <c r="D61" s="593"/>
       <c r="E61" s="499"/>
       <c r="F61" s="70">
         <v>0</v>
@@ -8909,10 +8909,10 @@
         <f t="shared" ref="B62:B83" si="4">1+B61</f>
         <v>3</v>
       </c>
-      <c r="C62" s="622" t="s">
+      <c r="C62" s="595" t="s">
         <v>127</v>
       </c>
-      <c r="D62" s="623"/>
+      <c r="D62" s="596"/>
       <c r="E62" s="75"/>
       <c r="F62" s="76">
         <f>F60+F61</f>
@@ -8938,10 +8938,10 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="C63" s="620" t="s">
+      <c r="C63" s="592" t="s">
         <v>321</v>
       </c>
-      <c r="D63" s="627"/>
+      <c r="D63" s="593"/>
       <c r="E63" s="56"/>
       <c r="F63" s="54">
         <f>F62*F21</f>
@@ -8967,10 +8967,10 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="C64" s="620" t="s">
+      <c r="C64" s="592" t="s">
         <v>128</v>
       </c>
-      <c r="D64" s="627"/>
+      <c r="D64" s="593"/>
       <c r="E64" s="56"/>
       <c r="F64" s="70">
         <f>I220/F21/F54</f>
@@ -8996,10 +8996,10 @@
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="C65" s="626" t="s">
+      <c r="C65" s="594" t="s">
         <v>322</v>
       </c>
-      <c r="D65" s="627"/>
+      <c r="D65" s="593"/>
       <c r="E65" s="71"/>
       <c r="F65" s="54">
         <f>+F64*F21</f>
@@ -9025,10 +9025,10 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="C66" s="626" t="s">
+      <c r="C66" s="594" t="s">
         <v>323</v>
       </c>
-      <c r="D66" s="627"/>
+      <c r="D66" s="593"/>
       <c r="E66" s="59"/>
       <c r="F66" s="56">
         <f>(+G220/F54)</f>
@@ -9054,10 +9054,10 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="C67" s="626" t="s">
+      <c r="C67" s="594" t="s">
         <v>129</v>
       </c>
-      <c r="D67" s="627"/>
+      <c r="D67" s="593"/>
       <c r="E67" s="56"/>
       <c r="F67" s="56">
         <f>Main!B9</f>
@@ -9083,10 +9083,10 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="C68" s="626" t="s">
+      <c r="C68" s="594" t="s">
         <v>130</v>
       </c>
-      <c r="D68" s="627"/>
+      <c r="D68" s="593"/>
       <c r="E68" s="56"/>
       <c r="F68" s="56">
         <v>0</v>
@@ -9111,10 +9111,10 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="C69" s="620" t="s">
+      <c r="C69" s="592" t="s">
         <v>131</v>
       </c>
-      <c r="D69" s="627"/>
+      <c r="D69" s="593"/>
       <c r="E69" s="56"/>
       <c r="F69" s="56">
         <v>500000</v>
@@ -9139,10 +9139,10 @@
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="C70" s="626" t="s">
+      <c r="C70" s="594" t="s">
         <v>132</v>
       </c>
-      <c r="D70" s="627"/>
+      <c r="D70" s="593"/>
       <c r="E70" s="56"/>
       <c r="F70" s="54">
         <v>0</v>
@@ -9164,10 +9164,10 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="C71" s="626" t="s">
+      <c r="C71" s="594" t="s">
         <v>133</v>
       </c>
-      <c r="D71" s="627"/>
+      <c r="D71" s="593"/>
       <c r="E71" s="56"/>
       <c r="F71" s="54">
         <f>F38*F23*F33</f>
@@ -9193,10 +9193,10 @@
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="C72" s="626" t="s">
+      <c r="C72" s="594" t="s">
         <v>134</v>
       </c>
-      <c r="D72" s="627"/>
+      <c r="D72" s="593"/>
       <c r="E72" s="56"/>
       <c r="F72" s="56">
         <v>0</v>
@@ -9221,10 +9221,10 @@
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="C73" s="620" t="s">
+      <c r="C73" s="592" t="s">
         <v>135</v>
       </c>
-      <c r="D73" s="627"/>
+      <c r="D73" s="593"/>
       <c r="E73" s="498"/>
       <c r="F73" s="68">
         <f>+F35*F63</f>
@@ -9278,10 +9278,10 @@
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="C75" s="620" t="s">
+      <c r="C75" s="592" t="s">
         <v>137</v>
       </c>
-      <c r="D75" s="627"/>
+      <c r="D75" s="593"/>
       <c r="E75" s="59"/>
       <c r="F75" s="56">
         <f>+F77/F23</f>
@@ -9307,10 +9307,10 @@
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="C76" s="620" t="s">
+      <c r="C76" s="592" t="s">
         <v>138</v>
       </c>
-      <c r="D76" s="627"/>
+      <c r="D76" s="593"/>
       <c r="E76" s="71"/>
       <c r="F76" s="51"/>
       <c r="G76" s="493"/>
@@ -9330,10 +9330,10 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="C77" s="620" t="s">
+      <c r="C77" s="592" t="s">
         <v>139</v>
       </c>
-      <c r="D77" s="627"/>
+      <c r="D77" s="593"/>
       <c r="E77" s="71"/>
       <c r="F77" s="56">
         <f>'CAPEX and PM'!B6</f>
@@ -9359,10 +9359,10 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="C78" s="620" t="s">
+      <c r="C78" s="592" t="s">
         <v>140</v>
       </c>
-      <c r="D78" s="627"/>
+      <c r="D78" s="593"/>
       <c r="E78" s="71"/>
       <c r="F78" s="56">
         <f>'CAPEX and PM'!B37</f>
@@ -9388,10 +9388,10 @@
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="C79" s="620" t="s">
+      <c r="C79" s="592" t="s">
         <v>141</v>
       </c>
-      <c r="D79" s="627"/>
+      <c r="D79" s="593"/>
       <c r="E79" s="71"/>
       <c r="F79" s="56">
         <f>+'CAPEX and PM'!B95</f>
@@ -9417,10 +9417,10 @@
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="C80" s="620" t="s">
+      <c r="C80" s="592" t="s">
         <v>142</v>
       </c>
-      <c r="D80" s="627"/>
+      <c r="D80" s="593"/>
       <c r="E80" s="71"/>
       <c r="F80" s="56"/>
       <c r="G80" s="388"/>
@@ -9440,10 +9440,10 @@
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="C81" s="620" t="s">
+      <c r="C81" s="592" t="s">
         <v>143</v>
       </c>
-      <c r="D81" s="621"/>
+      <c r="D81" s="602"/>
       <c r="E81" s="71"/>
       <c r="F81" s="56"/>
       <c r="G81" s="388"/>
@@ -9463,10 +9463,10 @@
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="C82" s="620" t="s">
+      <c r="C82" s="592" t="s">
         <v>144</v>
       </c>
-      <c r="D82" s="627"/>
+      <c r="D82" s="593"/>
       <c r="E82" s="59"/>
       <c r="F82" s="56">
         <f>+G207</f>
@@ -9492,10 +9492,10 @@
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="C83" s="620" t="s">
+      <c r="C83" s="592" t="s">
         <v>324</v>
       </c>
-      <c r="D83" s="627"/>
+      <c r="D83" s="593"/>
       <c r="E83" s="498"/>
       <c r="F83" s="56">
         <f>+F30</f>
@@ -9528,11 +9528,11 @@
     </row>
     <row r="85" spans="1:24" ht="15.9" customHeight="1">
       <c r="A85" s="51"/>
-      <c r="B85" s="628" t="s">
+      <c r="B85" s="614" t="s">
         <v>145</v>
       </c>
-      <c r="C85" s="629"/>
-      <c r="D85" s="630"/>
+      <c r="C85" s="615"/>
+      <c r="D85" s="616"/>
       <c r="E85" s="389"/>
       <c r="F85" s="161" t="s">
         <v>75</v>
@@ -9553,10 +9553,10 @@
       <c r="B86" s="162">
         <v>1</v>
       </c>
-      <c r="C86" s="620" t="s">
+      <c r="C86" s="592" t="s">
         <v>146</v>
       </c>
-      <c r="D86" s="627"/>
+      <c r="D86" s="593"/>
       <c r="E86" s="71"/>
       <c r="F86" s="70">
         <f>+F62</f>
@@ -9585,10 +9585,10 @@
         <f>1+B86</f>
         <v>2</v>
       </c>
-      <c r="C87" s="626" t="s">
+      <c r="C87" s="594" t="s">
         <v>147</v>
       </c>
-      <c r="D87" s="627"/>
+      <c r="D87" s="593"/>
       <c r="E87" s="73"/>
       <c r="F87" s="56">
         <v>0</v>
@@ -9611,10 +9611,10 @@
         <f t="shared" ref="B88:B94" si="7">+B87+1</f>
         <v>3</v>
       </c>
-      <c r="C88" s="626" t="s">
+      <c r="C88" s="594" t="s">
         <v>148</v>
       </c>
-      <c r="D88" s="627"/>
+      <c r="D88" s="593"/>
       <c r="E88" s="73"/>
       <c r="F88" s="70">
         <f>(F66/F23)</f>
@@ -9642,10 +9642,10 @@
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="C89" s="626" t="s">
+      <c r="C89" s="594" t="s">
         <v>149</v>
       </c>
-      <c r="D89" s="627"/>
+      <c r="D89" s="593"/>
       <c r="E89" s="73"/>
       <c r="F89" s="66">
         <f>'Security Deposit'!C17</f>
@@ -9673,10 +9673,10 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="C90" s="626" t="s">
+      <c r="C90" s="594" t="s">
         <v>289</v>
       </c>
-      <c r="D90" s="627"/>
+      <c r="D90" s="593"/>
       <c r="E90" s="73"/>
       <c r="F90" s="202">
         <f>+F64</f>
@@ -9704,10 +9704,10 @@
         <f>+B89+1</f>
         <v>5</v>
       </c>
-      <c r="C91" s="626" t="s">
+      <c r="C91" s="594" t="s">
         <v>150</v>
       </c>
-      <c r="D91" s="627"/>
+      <c r="D91" s="593"/>
       <c r="E91" s="73"/>
       <c r="F91" s="66">
         <f>(+F83/F21/F54)</f>
@@ -9734,10 +9734,10 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="C92" s="626" t="s">
+      <c r="C92" s="594" t="s">
         <v>151</v>
       </c>
-      <c r="D92" s="627"/>
+      <c r="D92" s="593"/>
       <c r="E92" s="73"/>
       <c r="F92" s="66">
         <f>F82/F21/F54</f>
@@ -9765,10 +9765,10 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="C93" s="620" t="s">
+      <c r="C93" s="592" t="s">
         <v>152</v>
       </c>
-      <c r="D93" s="627"/>
+      <c r="D93" s="593"/>
       <c r="E93" s="71"/>
       <c r="F93" s="66">
         <f>+G93/F6</f>
@@ -9796,10 +9796,10 @@
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="C94" s="622" t="s">
+      <c r="C94" s="595" t="s">
         <v>69</v>
       </c>
-      <c r="D94" s="623"/>
+      <c r="D94" s="596"/>
       <c r="E94" s="78"/>
       <c r="F94" s="213">
         <f>SUM(F86:F93)</f>
@@ -9824,8 +9824,8 @@
     <row r="95" spans="1:24" ht="15.9" customHeight="1">
       <c r="A95" s="51"/>
       <c r="B95" s="381"/>
-      <c r="C95" s="617"/>
-      <c r="D95" s="617"/>
+      <c r="C95" s="634"/>
+      <c r="D95" s="634"/>
       <c r="E95" s="84"/>
       <c r="F95" s="85"/>
       <c r="G95" s="85"/>
@@ -9835,11 +9835,11 @@
     </row>
     <row r="96" spans="1:24" ht="15.9" customHeight="1">
       <c r="A96" s="51"/>
-      <c r="B96" s="624" t="s">
+      <c r="B96" s="597" t="s">
         <v>153</v>
       </c>
-      <c r="C96" s="625"/>
-      <c r="D96" s="625"/>
+      <c r="C96" s="598"/>
+      <c r="D96" s="598"/>
       <c r="E96" s="87"/>
       <c r="F96" s="161" t="s">
         <v>75</v>
@@ -9861,11 +9861,11 @@
       <c r="B97" s="162">
         <v>1</v>
       </c>
-      <c r="C97" s="626" t="str">
+      <c r="C97" s="594" t="str">
         <f>+C76</f>
         <v>Siemens Standard Fitout (Existing)</v>
       </c>
-      <c r="D97" s="627"/>
+      <c r="D97" s="593"/>
       <c r="E97" s="88"/>
       <c r="F97" s="66">
         <v>0</v>
@@ -9891,11 +9891,11 @@
         <f t="shared" ref="B98:B103" si="8">+B97+1</f>
         <v>2</v>
       </c>
-      <c r="C98" s="626" t="str">
+      <c r="C98" s="594" t="str">
         <f>+C77</f>
         <v>Siemens Standard Fitout (New)</v>
       </c>
-      <c r="D98" s="627"/>
+      <c r="D98" s="593"/>
       <c r="E98" s="71"/>
       <c r="F98" s="66">
         <f>'CAPEX and PM'!B29</f>
@@ -9923,11 +9923,11 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="C99" s="626" t="str">
+      <c r="C99" s="594" t="str">
         <f>+C78</f>
         <v>Capex over the period of lease period</v>
       </c>
-      <c r="D99" s="627"/>
+      <c r="D99" s="593"/>
       <c r="E99" s="71"/>
       <c r="F99" s="66">
         <f>'CAPEX and PM'!B89</f>
@@ -9955,11 +9955,11 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="C100" s="626" t="str">
+      <c r="C100" s="594" t="str">
         <f>+C79</f>
         <v>PM cost over the period of lease period</v>
       </c>
-      <c r="D100" s="627"/>
+      <c r="D100" s="593"/>
       <c r="E100" s="71"/>
       <c r="F100" s="66">
         <f>+'CAPEX and PM'!B96</f>
@@ -9987,11 +9987,11 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="C101" s="626" t="str">
+      <c r="C101" s="594" t="str">
         <f>+C80</f>
         <v>Asset Retirement Obligation ( Removal &amp; Restoration Obligation)</v>
       </c>
-      <c r="D101" s="627"/>
+      <c r="D101" s="593"/>
       <c r="E101" s="71"/>
       <c r="F101" s="66">
         <f>'Security Deposit'!D25</f>
@@ -10022,10 +10022,10 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="C102" s="620" t="s">
+      <c r="C102" s="592" t="s">
         <v>154</v>
       </c>
-      <c r="D102" s="627"/>
+      <c r="D102" s="593"/>
       <c r="E102" s="73"/>
       <c r="F102" s="66">
         <f>+F81/F21/F27</f>
@@ -10053,10 +10053,10 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="C103" s="622" t="s">
+      <c r="C103" s="595" t="s">
         <v>155</v>
       </c>
-      <c r="D103" s="623"/>
+      <c r="D103" s="596"/>
       <c r="E103" s="78"/>
       <c r="F103" s="54">
         <f>SUM(F97:F102)</f>
@@ -10093,11 +10093,11 @@
     </row>
     <row r="105" spans="1:26" ht="15.9" customHeight="1">
       <c r="A105" s="51"/>
-      <c r="B105" s="631" t="s">
+      <c r="B105" s="688" t="s">
         <v>156</v>
       </c>
-      <c r="C105" s="632"/>
-      <c r="D105" s="632"/>
+      <c r="C105" s="609"/>
+      <c r="D105" s="609"/>
       <c r="E105" s="87"/>
       <c r="F105" s="161" t="s">
         <v>75</v>
@@ -10118,10 +10118,10 @@
       <c r="B106" s="162">
         <v>1</v>
       </c>
-      <c r="C106" s="620" t="s">
+      <c r="C106" s="592" t="s">
         <v>69</v>
       </c>
-      <c r="D106" s="627"/>
+      <c r="D106" s="593"/>
       <c r="E106" s="71"/>
       <c r="F106" s="56">
         <f>+F94</f>
@@ -10149,10 +10149,10 @@
         <f>+B106+1</f>
         <v>2</v>
       </c>
-      <c r="C107" s="620" t="s">
+      <c r="C107" s="592" t="s">
         <v>155</v>
       </c>
-      <c r="D107" s="621"/>
+      <c r="D107" s="602"/>
       <c r="E107" s="71"/>
       <c r="F107" s="56">
         <f>+F103</f>
@@ -10180,10 +10180,10 @@
         <f>+B107+1</f>
         <v>3</v>
       </c>
-      <c r="C108" s="622" t="s">
+      <c r="C108" s="595" t="s">
         <v>157</v>
       </c>
-      <c r="D108" s="623"/>
+      <c r="D108" s="596"/>
       <c r="E108" s="78"/>
       <c r="F108" s="54">
         <f>SUM(F106:F107)</f>
@@ -10212,11 +10212,11 @@
     </row>
     <row r="109" spans="1:26" ht="15.9" customHeight="1">
       <c r="A109" s="51"/>
-      <c r="B109" s="624" t="s">
+      <c r="B109" s="597" t="s">
         <v>158</v>
       </c>
-      <c r="C109" s="625"/>
-      <c r="D109" s="625"/>
+      <c r="C109" s="598"/>
+      <c r="D109" s="598"/>
       <c r="E109" s="89"/>
       <c r="F109" s="161" t="s">
         <v>75</v>
@@ -10238,10 +10238,10 @@
       <c r="B110" s="249">
         <v>1</v>
       </c>
-      <c r="C110" s="620" t="s">
+      <c r="C110" s="592" t="s">
         <v>159</v>
       </c>
-      <c r="D110" s="621"/>
+      <c r="D110" s="602"/>
       <c r="E110" s="83"/>
       <c r="F110" s="376"/>
       <c r="G110" s="376"/>
@@ -10255,10 +10255,10 @@
         <f t="shared" ref="B111:B119" si="9">1+B110</f>
         <v>2</v>
       </c>
-      <c r="C111" s="620" t="s">
+      <c r="C111" s="592" t="s">
         <v>160</v>
       </c>
-      <c r="D111" s="621"/>
+      <c r="D111" s="602"/>
       <c r="E111" s="83"/>
       <c r="F111" s="376"/>
       <c r="G111" s="376"/>
@@ -10274,10 +10274,10 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="C112" s="620" t="s">
+      <c r="C112" s="592" t="s">
         <v>161</v>
       </c>
-      <c r="D112" s="621"/>
+      <c r="D112" s="602"/>
       <c r="E112" s="83"/>
       <c r="F112" s="388">
         <f>+F64*0</f>
@@ -10305,10 +10305,10 @@
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="C113" s="620" t="s">
+      <c r="C113" s="592" t="s">
         <v>162</v>
       </c>
-      <c r="D113" s="621"/>
+      <c r="D113" s="602"/>
       <c r="E113" s="83"/>
       <c r="F113" s="376"/>
       <c r="G113" s="376"/>
@@ -10322,10 +10322,10 @@
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="C114" s="620" t="s">
+      <c r="C114" s="592" t="s">
         <v>163</v>
       </c>
-      <c r="D114" s="621"/>
+      <c r="D114" s="602"/>
       <c r="E114" s="83"/>
       <c r="F114" s="376"/>
       <c r="G114" s="376"/>
@@ -10339,10 +10339,10 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="C115" s="620" t="s">
+      <c r="C115" s="592" t="s">
         <v>164</v>
       </c>
-      <c r="D115" s="621"/>
+      <c r="D115" s="602"/>
       <c r="E115" s="83"/>
       <c r="F115" s="376"/>
       <c r="G115" s="376"/>
@@ -10356,10 +10356,10 @@
         <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="C116" s="620" t="s">
+      <c r="C116" s="592" t="s">
         <v>165</v>
       </c>
-      <c r="D116" s="621"/>
+      <c r="D116" s="602"/>
       <c r="E116" s="83"/>
       <c r="F116" s="376"/>
       <c r="G116" s="376"/>
@@ -10373,10 +10373,10 @@
         <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="C117" s="620" t="s">
+      <c r="C117" s="592" t="s">
         <v>166</v>
       </c>
-      <c r="D117" s="627"/>
+      <c r="D117" s="593"/>
       <c r="E117" s="252"/>
       <c r="F117" s="360">
         <v>654</v>
@@ -10402,10 +10402,10 @@
         <f t="shared" si="9"/>
         <v>9</v>
       </c>
-      <c r="C118" s="620" t="s">
+      <c r="C118" s="592" t="s">
         <v>167</v>
       </c>
-      <c r="D118" s="621"/>
+      <c r="D118" s="602"/>
       <c r="E118" s="252"/>
       <c r="F118" s="90">
         <f>F117*7%</f>
@@ -10431,10 +10431,10 @@
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="C119" s="622" t="s">
+      <c r="C119" s="595" t="s">
         <v>168</v>
       </c>
-      <c r="D119" s="623"/>
+      <c r="D119" s="596"/>
       <c r="E119" s="253"/>
       <c r="F119" s="54">
         <f>SUM(F110:F118)</f>
@@ -10460,8 +10460,8 @@
     <row r="120" spans="1:26" ht="15.9" customHeight="1">
       <c r="A120" s="77"/>
       <c r="B120" s="162"/>
-      <c r="C120" s="616"/>
-      <c r="D120" s="633"/>
+      <c r="C120" s="600"/>
+      <c r="D120" s="601"/>
       <c r="E120" s="78"/>
       <c r="F120" s="54"/>
       <c r="G120" s="385"/>
@@ -10475,11 +10475,11 @@
     </row>
     <row r="121" spans="1:26" ht="15.9" customHeight="1">
       <c r="A121" s="77"/>
-      <c r="B121" s="624" t="s">
+      <c r="B121" s="597" t="s">
         <v>169</v>
       </c>
-      <c r="C121" s="625"/>
-      <c r="D121" s="625"/>
+      <c r="C121" s="598"/>
+      <c r="D121" s="598"/>
       <c r="E121" s="89"/>
       <c r="F121" s="161" t="s">
         <v>75</v>
@@ -10502,10 +10502,10 @@
       <c r="B122" s="251">
         <v>1</v>
       </c>
-      <c r="C122" s="620" t="s">
+      <c r="C122" s="592" t="s">
         <v>170</v>
       </c>
-      <c r="D122" s="621"/>
+      <c r="D122" s="602"/>
       <c r="E122" s="78"/>
       <c r="F122" s="54"/>
       <c r="G122" s="385"/>
@@ -10518,10 +10518,10 @@
       <c r="B123" s="162">
         <v>2</v>
       </c>
-      <c r="C123" s="622" t="s">
+      <c r="C123" s="595" t="s">
         <v>171</v>
       </c>
-      <c r="D123" s="623"/>
+      <c r="D123" s="596"/>
       <c r="E123" s="78"/>
       <c r="F123" s="54">
         <f>SUM(F122)</f>
@@ -10544,8 +10544,8 @@
     <row r="124" spans="1:26" ht="15.9" customHeight="1">
       <c r="A124" s="77"/>
       <c r="B124" s="162"/>
-      <c r="C124" s="616"/>
-      <c r="D124" s="633"/>
+      <c r="C124" s="600"/>
+      <c r="D124" s="601"/>
       <c r="E124" s="63"/>
       <c r="F124" s="54"/>
       <c r="G124" s="385"/>
@@ -10555,11 +10555,11 @@
     </row>
     <row r="125" spans="1:26" ht="15.9" customHeight="1">
       <c r="A125" s="77"/>
-      <c r="B125" s="624" t="s">
+      <c r="B125" s="597" t="s">
         <v>172</v>
       </c>
-      <c r="C125" s="625"/>
-      <c r="D125" s="625"/>
+      <c r="C125" s="598"/>
+      <c r="D125" s="598"/>
       <c r="E125" s="89"/>
       <c r="F125" s="161" t="s">
         <v>75</v>
@@ -10580,10 +10580,10 @@
       <c r="B126" s="249">
         <v>1</v>
       </c>
-      <c r="C126" s="620" t="s">
+      <c r="C126" s="592" t="s">
         <v>173</v>
       </c>
-      <c r="D126" s="621"/>
+      <c r="D126" s="602"/>
       <c r="E126" s="250"/>
       <c r="F126" s="385"/>
       <c r="G126" s="385"/>
@@ -10597,10 +10597,10 @@
         <f>1+B126</f>
         <v>2</v>
       </c>
-      <c r="C127" s="620" t="s">
+      <c r="C127" s="592" t="s">
         <v>174</v>
       </c>
-      <c r="D127" s="621"/>
+      <c r="D127" s="602"/>
       <c r="E127" s="250"/>
       <c r="F127" s="385"/>
       <c r="G127" s="385"/>
@@ -10614,10 +10614,10 @@
         <f>1+B127</f>
         <v>3</v>
       </c>
-      <c r="C128" s="620" t="s">
+      <c r="C128" s="592" t="s">
         <v>175</v>
       </c>
-      <c r="D128" s="621"/>
+      <c r="D128" s="602"/>
       <c r="E128" s="250"/>
       <c r="F128" s="385"/>
       <c r="G128" s="385"/>
@@ -10631,10 +10631,10 @@
         <f>1+B128</f>
         <v>4</v>
       </c>
-      <c r="C129" s="620" t="s">
+      <c r="C129" s="592" t="s">
         <v>176</v>
       </c>
-      <c r="D129" s="621"/>
+      <c r="D129" s="602"/>
       <c r="E129" s="250"/>
       <c r="F129" s="385"/>
       <c r="G129" s="385"/>
@@ -10648,10 +10648,10 @@
         <f>1+B129</f>
         <v>5</v>
       </c>
-      <c r="C130" s="620" t="s">
+      <c r="C130" s="592" t="s">
         <v>177</v>
       </c>
-      <c r="D130" s="621"/>
+      <c r="D130" s="602"/>
       <c r="E130" s="250"/>
       <c r="F130" s="385"/>
       <c r="G130" s="385"/>
@@ -10665,10 +10665,10 @@
         <f>1+B130</f>
         <v>6</v>
       </c>
-      <c r="C131" s="620" t="s">
+      <c r="C131" s="592" t="s">
         <v>178</v>
       </c>
-      <c r="D131" s="621"/>
+      <c r="D131" s="602"/>
       <c r="E131" s="250"/>
       <c r="F131" s="385"/>
       <c r="G131" s="385"/>
@@ -10681,10 +10681,10 @@
       <c r="B132" s="381">
         <v>7</v>
       </c>
-      <c r="C132" s="622" t="s">
+      <c r="C132" s="595" t="s">
         <v>179</v>
       </c>
-      <c r="D132" s="623"/>
+      <c r="D132" s="596"/>
       <c r="E132" s="250"/>
       <c r="F132" s="385">
         <f>SUM(F126:F131)</f>
@@ -10707,8 +10707,8 @@
     <row r="133" spans="1:20" ht="15.9" customHeight="1">
       <c r="A133" s="77"/>
       <c r="B133" s="162"/>
-      <c r="C133" s="617"/>
-      <c r="D133" s="633"/>
+      <c r="C133" s="634"/>
+      <c r="D133" s="601"/>
       <c r="E133" s="250"/>
       <c r="F133" s="385"/>
       <c r="G133" s="385"/>
@@ -10718,11 +10718,11 @@
     </row>
     <row r="134" spans="1:20" ht="15.9" customHeight="1">
       <c r="A134" s="51"/>
-      <c r="B134" s="624" t="s">
+      <c r="B134" s="597" t="s">
         <v>180</v>
       </c>
-      <c r="C134" s="625"/>
-      <c r="D134" s="625"/>
+      <c r="C134" s="598"/>
+      <c r="D134" s="598"/>
       <c r="E134" s="89"/>
       <c r="F134" s="161" t="s">
         <v>75</v>
@@ -10743,10 +10743,10 @@
       <c r="B135" s="162">
         <v>1</v>
       </c>
-      <c r="C135" s="622" t="s">
+      <c r="C135" s="595" t="s">
         <v>181</v>
       </c>
-      <c r="D135" s="623"/>
+      <c r="D135" s="596"/>
       <c r="E135" s="78"/>
       <c r="F135" s="54">
         <f>F119+F108+F123+F132</f>
@@ -10771,8 +10771,8 @@
     <row r="136" spans="1:20" ht="15.9" customHeight="1">
       <c r="A136" s="77"/>
       <c r="B136" s="162"/>
-      <c r="C136" s="616"/>
-      <c r="D136" s="633"/>
+      <c r="C136" s="600"/>
+      <c r="D136" s="601"/>
       <c r="E136" s="78"/>
       <c r="F136" s="54"/>
       <c r="G136" s="385"/>
@@ -10786,23 +10786,23 @@
       <c r="C137" s="380"/>
       <c r="D137" s="377"/>
       <c r="E137" s="167"/>
-      <c r="F137" s="616" t="s">
+      <c r="F137" s="600" t="s">
         <v>73</v>
       </c>
-      <c r="G137" s="617"/>
+      <c r="G137" s="634"/>
       <c r="H137" s="404"/>
-      <c r="I137" s="618" t="s">
+      <c r="I137" s="635" t="s">
         <v>67</v>
       </c>
-      <c r="J137" s="619"/>
+      <c r="J137" s="636"/>
     </row>
     <row r="138" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A138" s="51"/>
-      <c r="B138" s="624" t="s">
+      <c r="B138" s="597" t="s">
         <v>182</v>
       </c>
-      <c r="C138" s="625"/>
-      <c r="D138" s="640"/>
+      <c r="C138" s="598"/>
+      <c r="D138" s="599"/>
       <c r="E138" s="161"/>
       <c r="F138" s="161" t="s">
         <v>75</v>
@@ -10821,8 +10821,8 @@
     <row r="139" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A139" s="51"/>
       <c r="B139" s="91"/>
-      <c r="C139" s="641"/>
-      <c r="D139" s="642"/>
+      <c r="C139" s="603"/>
+      <c r="D139" s="604"/>
       <c r="E139" s="163"/>
       <c r="F139" s="54"/>
       <c r="G139" s="385"/>
@@ -10833,10 +10833,10 @@
     <row r="140" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A140" s="51"/>
       <c r="B140" s="91"/>
-      <c r="C140" s="620" t="s">
+      <c r="C140" s="592" t="s">
         <v>183</v>
       </c>
-      <c r="D140" s="627"/>
+      <c r="D140" s="593"/>
       <c r="E140" s="58"/>
       <c r="F140" s="243">
         <f>F21</f>
@@ -10859,10 +10859,10 @@
     <row r="141" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A141" s="51"/>
       <c r="B141" s="91"/>
-      <c r="C141" s="626" t="s">
+      <c r="C141" s="594" t="s">
         <v>184</v>
       </c>
-      <c r="D141" s="627"/>
+      <c r="D141" s="593"/>
       <c r="E141" s="59"/>
       <c r="F141" s="56">
         <f>F24</f>
@@ -10885,10 +10885,10 @@
     <row r="142" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A142" s="51"/>
       <c r="B142" s="91"/>
-      <c r="C142" s="626" t="s">
+      <c r="C142" s="594" t="s">
         <v>185</v>
       </c>
-      <c r="D142" s="627"/>
+      <c r="D142" s="593"/>
       <c r="E142" s="73"/>
       <c r="F142" s="56" t="e">
         <f>+#REF!</f>
@@ -10911,10 +10911,10 @@
     <row r="143" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A143" s="51"/>
       <c r="B143" s="91"/>
-      <c r="C143" s="620" t="s">
+      <c r="C143" s="592" t="s">
         <v>186</v>
       </c>
-      <c r="D143" s="627"/>
+      <c r="D143" s="593"/>
       <c r="E143" s="73"/>
       <c r="F143" s="56">
         <f>F108</f>
@@ -10937,10 +10937,10 @@
     <row r="144" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A144" s="51"/>
       <c r="B144" s="91"/>
-      <c r="C144" s="709" t="s">
+      <c r="C144" s="622" t="s">
         <v>187</v>
       </c>
-      <c r="D144" s="710"/>
+      <c r="D144" s="623"/>
       <c r="E144" s="92"/>
       <c r="F144" s="93">
         <f>F119</f>
@@ -10963,10 +10963,10 @@
     <row r="145" spans="1:10" ht="15.9" hidden="1" customHeight="1">
       <c r="A145" s="77"/>
       <c r="B145" s="162"/>
-      <c r="C145" s="622" t="s">
+      <c r="C145" s="595" t="s">
         <v>188</v>
       </c>
-      <c r="D145" s="623"/>
+      <c r="D145" s="596"/>
       <c r="E145" s="78"/>
       <c r="F145" s="245" t="e">
         <f>F135*#REF!</f>
@@ -11000,11 +11000,11 @@
     </row>
     <row r="147" spans="1:10" ht="15.9" customHeight="1">
       <c r="A147" s="77"/>
-      <c r="B147" s="624" t="s">
+      <c r="B147" s="597" t="s">
         <v>189</v>
       </c>
-      <c r="C147" s="625"/>
-      <c r="D147" s="640"/>
+      <c r="C147" s="598"/>
+      <c r="D147" s="599"/>
       <c r="E147" s="379"/>
       <c r="F147" s="379" t="s">
         <v>190</v>
@@ -11023,8 +11023,8 @@
     <row r="148" spans="1:10" ht="15.9" customHeight="1">
       <c r="A148" s="51"/>
       <c r="B148" s="99"/>
-      <c r="C148" s="641"/>
-      <c r="D148" s="642"/>
+      <c r="C148" s="603"/>
+      <c r="D148" s="604"/>
       <c r="E148" s="100"/>
       <c r="F148" s="101"/>
       <c r="G148" s="209"/>
@@ -11035,10 +11035,10 @@
     <row r="149" spans="1:10" ht="15.9" customHeight="1">
       <c r="A149" s="51"/>
       <c r="B149" s="99"/>
-      <c r="C149" s="626" t="s">
+      <c r="C149" s="594" t="s">
         <v>191</v>
       </c>
-      <c r="D149" s="627"/>
+      <c r="D149" s="593"/>
       <c r="E149" s="100"/>
       <c r="F149" s="101">
         <f>(+F63)*115%</f>
@@ -11061,10 +11061,10 @@
     <row r="150" spans="1:10" ht="15.9" customHeight="1">
       <c r="A150" s="51"/>
       <c r="B150" s="99"/>
-      <c r="C150" s="626" t="s">
+      <c r="C150" s="594" t="s">
         <v>192</v>
       </c>
-      <c r="D150" s="627"/>
+      <c r="D150" s="593"/>
       <c r="E150" s="100"/>
       <c r="F150" s="101">
         <v>0</v>
@@ -11083,10 +11083,10 @@
     <row r="151" spans="1:10" ht="15.9" customHeight="1">
       <c r="A151" s="51"/>
       <c r="B151" s="99"/>
-      <c r="C151" s="626" t="s">
+      <c r="C151" s="594" t="s">
         <v>193</v>
       </c>
-      <c r="D151" s="627"/>
+      <c r="D151" s="593"/>
       <c r="E151" s="100"/>
       <c r="F151" s="101">
         <f>(+F65)*115%</f>
@@ -11109,10 +11109,10 @@
     <row r="152" spans="1:10" ht="15.9" customHeight="1">
       <c r="A152" s="51"/>
       <c r="B152" s="99"/>
-      <c r="C152" s="626" t="s">
+      <c r="C152" s="594" t="s">
         <v>194</v>
       </c>
-      <c r="D152" s="627"/>
+      <c r="D152" s="593"/>
       <c r="E152" s="100"/>
       <c r="F152" s="101">
         <f>(+F66)*115%</f>
@@ -11135,10 +11135,10 @@
     <row r="153" spans="1:10" ht="15.9" customHeight="1">
       <c r="A153" s="51"/>
       <c r="B153" s="99"/>
-      <c r="C153" s="620" t="s">
+      <c r="C153" s="592" t="s">
         <v>195</v>
       </c>
-      <c r="D153" s="627"/>
+      <c r="D153" s="593"/>
       <c r="E153" s="103"/>
       <c r="F153" s="104">
         <f>SUM(F149:F152)</f>
@@ -11161,10 +11161,10 @@
     <row r="154" spans="1:10" ht="15.9" customHeight="1">
       <c r="A154" s="51"/>
       <c r="B154" s="99"/>
-      <c r="C154" s="620" t="s">
+      <c r="C154" s="592" t="s">
         <v>196</v>
       </c>
-      <c r="D154" s="627"/>
+      <c r="D154" s="593"/>
       <c r="E154" s="105"/>
       <c r="F154" s="101">
         <f>+F153*12</f>
@@ -11187,8 +11187,8 @@
     <row r="155" spans="1:10" ht="15.9" customHeight="1">
       <c r="A155" s="51"/>
       <c r="B155" s="99"/>
-      <c r="C155" s="641"/>
-      <c r="D155" s="642"/>
+      <c r="C155" s="603"/>
+      <c r="D155" s="604"/>
       <c r="E155" s="105"/>
       <c r="F155" s="101"/>
       <c r="G155" s="209"/>
@@ -11198,11 +11198,11 @@
     </row>
     <row r="156" spans="1:10" ht="15.9" customHeight="1">
       <c r="A156" s="51"/>
-      <c r="B156" s="624" t="s">
+      <c r="B156" s="597" t="s">
         <v>197</v>
       </c>
-      <c r="C156" s="625"/>
-      <c r="D156" s="640"/>
+      <c r="C156" s="598"/>
+      <c r="D156" s="599"/>
       <c r="E156" s="375"/>
       <c r="F156" s="379" t="s">
         <v>190</v>
@@ -11221,8 +11221,8 @@
     <row r="157" spans="1:10" ht="15.9" customHeight="1">
       <c r="A157" s="51"/>
       <c r="B157" s="99"/>
-      <c r="C157" s="641"/>
-      <c r="D157" s="642"/>
+      <c r="C157" s="603"/>
+      <c r="D157" s="604"/>
       <c r="E157" s="105"/>
       <c r="F157" s="101"/>
       <c r="G157" s="209"/>
@@ -11233,10 +11233,10 @@
     <row r="158" spans="1:10" ht="15.9" customHeight="1">
       <c r="A158" s="51"/>
       <c r="B158" s="99"/>
-      <c r="C158" s="707" t="s">
+      <c r="C158" s="620" t="s">
         <v>198</v>
       </c>
-      <c r="D158" s="708"/>
+      <c r="D158" s="621"/>
       <c r="E158" s="105"/>
       <c r="F158" s="101">
         <f t="shared" ref="F158:G160" si="10">+F77</f>
@@ -11259,10 +11259,10 @@
     <row r="159" spans="1:10" ht="15.9" customHeight="1">
       <c r="A159" s="51"/>
       <c r="B159" s="99"/>
-      <c r="C159" s="620" t="s">
+      <c r="C159" s="592" t="s">
         <v>199</v>
       </c>
-      <c r="D159" s="621"/>
+      <c r="D159" s="602"/>
       <c r="E159" s="105"/>
       <c r="F159" s="101">
         <f t="shared" si="10"/>
@@ -11285,10 +11285,10 @@
     <row r="160" spans="1:10" ht="15.9" customHeight="1">
       <c r="A160" s="51"/>
       <c r="B160" s="99"/>
-      <c r="C160" s="620" t="s">
+      <c r="C160" s="592" t="s">
         <v>200</v>
       </c>
-      <c r="D160" s="621"/>
+      <c r="D160" s="602"/>
       <c r="E160" s="105"/>
       <c r="F160" s="101">
         <f t="shared" si="10"/>
@@ -11311,10 +11311,10 @@
     <row r="161" spans="1:22" ht="15.9" customHeight="1">
       <c r="A161" s="51"/>
       <c r="B161" s="99"/>
-      <c r="C161" s="622" t="s">
+      <c r="C161" s="595" t="s">
         <v>29</v>
       </c>
-      <c r="D161" s="623"/>
+      <c r="D161" s="596"/>
       <c r="E161" s="105"/>
       <c r="F161" s="237">
         <f>SUM(F158:F160)</f>
@@ -11337,8 +11337,8 @@
     <row r="162" spans="1:22" ht="15.9" customHeight="1">
       <c r="A162" s="51"/>
       <c r="B162" s="99"/>
-      <c r="C162" s="641"/>
-      <c r="D162" s="642"/>
+      <c r="C162" s="603"/>
+      <c r="D162" s="604"/>
       <c r="E162" s="105"/>
       <c r="F162" s="101"/>
       <c r="G162" s="209"/>
@@ -11348,12 +11348,12 @@
     </row>
     <row r="163" spans="1:22" ht="15.9" customHeight="1">
       <c r="A163" s="106"/>
-      <c r="B163" s="628" t="s">
+      <c r="B163" s="614" t="s">
         <v>201</v>
       </c>
-      <c r="C163" s="629"/>
-      <c r="D163" s="630"/>
-      <c r="E163" s="638"/>
+      <c r="C163" s="615"/>
+      <c r="D163" s="616"/>
+      <c r="E163" s="687"/>
       <c r="F163" s="161" t="s">
         <v>75</v>
       </c>
@@ -11370,10 +11370,10 @@
     </row>
     <row r="164" spans="1:22" ht="15.9" customHeight="1">
       <c r="A164" s="106"/>
-      <c r="B164" s="704"/>
-      <c r="C164" s="705"/>
-      <c r="D164" s="706"/>
-      <c r="E164" s="639"/>
+      <c r="B164" s="617"/>
+      <c r="C164" s="618"/>
+      <c r="D164" s="619"/>
+      <c r="E164" s="607"/>
       <c r="F164" s="161" t="s">
         <v>73</v>
       </c>
@@ -11391,8 +11391,8 @@
     <row r="165" spans="1:22" ht="15.9" customHeight="1">
       <c r="A165" s="107"/>
       <c r="B165" s="99"/>
-      <c r="C165" s="641"/>
-      <c r="D165" s="642"/>
+      <c r="C165" s="603"/>
+      <c r="D165" s="604"/>
       <c r="E165" s="59"/>
       <c r="F165" s="56"/>
       <c r="G165" s="388"/>
@@ -11403,11 +11403,11 @@
     <row r="166" spans="1:22" ht="15.9" customHeight="1">
       <c r="A166" s="107"/>
       <c r="B166" s="99"/>
-      <c r="C166" s="702" t="str">
+      <c r="C166" s="605" t="str">
         <f>+C106</f>
         <v>Net Rent I</v>
       </c>
-      <c r="D166" s="703"/>
+      <c r="D166" s="606"/>
       <c r="E166" s="59"/>
       <c r="F166" s="56">
         <f>+F106</f>
@@ -11431,11 +11431,11 @@
     <row r="167" spans="1:22" ht="15.9" customHeight="1">
       <c r="A167" s="107"/>
       <c r="B167" s="99"/>
-      <c r="C167" s="702" t="str">
+      <c r="C167" s="605" t="str">
         <f>+C107</f>
         <v>Net Rent II</v>
       </c>
-      <c r="D167" s="703"/>
+      <c r="D167" s="606"/>
       <c r="E167" s="59"/>
       <c r="F167" s="56">
         <f>+F107</f>
@@ -11459,10 +11459,10 @@
     <row r="168" spans="1:22" ht="15.9" customHeight="1">
       <c r="A168" s="107"/>
       <c r="B168" s="147"/>
-      <c r="C168" s="698" t="s">
+      <c r="C168" s="610" t="s">
         <v>202</v>
       </c>
-      <c r="D168" s="699"/>
+      <c r="D168" s="611"/>
       <c r="E168" s="148"/>
       <c r="F168" s="149">
         <f>SUM(F166:F167)</f>
@@ -11487,8 +11487,8 @@
     <row r="169" spans="1:22" ht="15.9" customHeight="1">
       <c r="A169" s="107"/>
       <c r="B169" s="162"/>
-      <c r="C169" s="700"/>
-      <c r="D169" s="701"/>
+      <c r="C169" s="612"/>
+      <c r="D169" s="613"/>
       <c r="E169" s="75"/>
       <c r="F169" s="54"/>
       <c r="G169" s="385"/>
@@ -11501,11 +11501,11 @@
     <row r="170" spans="1:22" ht="15.9" customHeight="1">
       <c r="A170" s="107"/>
       <c r="B170" s="99"/>
-      <c r="C170" s="702" t="str">
+      <c r="C170" s="605" t="str">
         <f>+C119</f>
         <v xml:space="preserve">OpEx I </v>
       </c>
-      <c r="D170" s="703"/>
+      <c r="D170" s="606"/>
       <c r="E170" s="59"/>
       <c r="F170" s="56">
         <f>+F119</f>
@@ -11529,11 +11529,11 @@
     <row r="171" spans="1:22" ht="15.9" customHeight="1">
       <c r="A171" s="107"/>
       <c r="B171" s="99"/>
-      <c r="C171" s="702" t="str">
+      <c r="C171" s="605" t="str">
         <f>+C123</f>
         <v xml:space="preserve">OpEx II </v>
       </c>
-      <c r="D171" s="703"/>
+      <c r="D171" s="606"/>
       <c r="E171" s="59"/>
       <c r="F171" s="56">
         <f>+F123</f>
@@ -11556,10 +11556,10 @@
     <row r="172" spans="1:22" ht="15.9" customHeight="1">
       <c r="A172" s="107"/>
       <c r="B172" s="150"/>
-      <c r="C172" s="698" t="s">
+      <c r="C172" s="610" t="s">
         <v>203</v>
       </c>
-      <c r="D172" s="699"/>
+      <c r="D172" s="611"/>
       <c r="E172" s="151"/>
       <c r="F172" s="152">
         <f>SUM(F170:F171)</f>
@@ -11594,11 +11594,11 @@
     <row r="174" spans="1:22" ht="15.9" customHeight="1">
       <c r="A174" s="107"/>
       <c r="B174" s="99"/>
-      <c r="C174" s="702" t="str">
+      <c r="C174" s="605" t="str">
         <f>+C132</f>
         <v xml:space="preserve">Services </v>
       </c>
-      <c r="D174" s="703"/>
+      <c r="D174" s="606"/>
       <c r="E174" s="59"/>
       <c r="F174" s="56">
         <f>+F132</f>
@@ -11621,10 +11621,10 @@
     <row r="175" spans="1:22" ht="15.9" customHeight="1">
       <c r="A175" s="107"/>
       <c r="B175" s="150"/>
-      <c r="C175" s="698" t="s">
+      <c r="C175" s="610" t="s">
         <v>204</v>
       </c>
-      <c r="D175" s="699"/>
+      <c r="D175" s="611"/>
       <c r="E175" s="151"/>
       <c r="F175" s="152">
         <f>SUM(F174)</f>
@@ -11647,8 +11647,8 @@
     <row r="176" spans="1:22" ht="15.9" customHeight="1">
       <c r="A176" s="107"/>
       <c r="B176" s="99"/>
-      <c r="C176" s="641"/>
-      <c r="D176" s="642"/>
+      <c r="C176" s="603"/>
+      <c r="D176" s="604"/>
       <c r="E176" s="59"/>
       <c r="F176" s="56"/>
       <c r="G176" s="388"/>
@@ -11659,10 +11659,10 @@
     <row r="177" spans="1:19" ht="15.9" customHeight="1">
       <c r="A177" s="107"/>
       <c r="B177" s="150"/>
-      <c r="C177" s="698" t="s">
+      <c r="C177" s="610" t="s">
         <v>205</v>
       </c>
-      <c r="D177" s="699"/>
+      <c r="D177" s="611"/>
       <c r="E177" s="154"/>
       <c r="F177" s="149">
         <f>+F168+F172+F175</f>
@@ -11697,11 +11697,11 @@
     </row>
     <row r="179" spans="1:19" ht="15.9" customHeight="1">
       <c r="A179" s="107"/>
-      <c r="B179" s="624" t="s">
+      <c r="B179" s="597" t="s">
         <v>206</v>
       </c>
-      <c r="C179" s="625"/>
-      <c r="D179" s="640"/>
+      <c r="C179" s="598"/>
+      <c r="D179" s="599"/>
       <c r="E179" s="379"/>
       <c r="F179" s="379" t="s">
         <v>190</v>
@@ -11720,8 +11720,8 @@
     <row r="180" spans="1:19" ht="15.9" customHeight="1">
       <c r="A180" s="107"/>
       <c r="B180" s="99"/>
-      <c r="C180" s="641"/>
-      <c r="D180" s="642"/>
+      <c r="C180" s="603"/>
+      <c r="D180" s="604"/>
       <c r="E180" s="59"/>
       <c r="F180" s="56"/>
       <c r="G180" s="388"/>
@@ -11732,10 +11732,10 @@
     <row r="181" spans="1:19" ht="15.9" customHeight="1">
       <c r="A181" s="107"/>
       <c r="B181" s="99"/>
-      <c r="C181" s="626" t="s">
+      <c r="C181" s="594" t="s">
         <v>207</v>
       </c>
-      <c r="D181" s="627"/>
+      <c r="D181" s="593"/>
       <c r="E181" s="100"/>
       <c r="F181" s="101"/>
       <c r="G181" s="209">
@@ -11752,10 +11752,10 @@
     <row r="182" spans="1:19" ht="15.9" customHeight="1">
       <c r="A182" s="107"/>
       <c r="B182" s="99"/>
-      <c r="C182" s="620" t="s">
+      <c r="C182" s="592" t="s">
         <v>208</v>
       </c>
-      <c r="D182" s="627"/>
+      <c r="D182" s="593"/>
       <c r="E182" s="100"/>
       <c r="F182" s="101"/>
       <c r="G182" s="209">
@@ -11772,10 +11772,10 @@
     <row r="183" spans="1:19" ht="15.9" customHeight="1">
       <c r="A183" s="107"/>
       <c r="B183" s="99"/>
-      <c r="C183" s="620" t="s">
+      <c r="C183" s="592" t="s">
         <v>209</v>
       </c>
-      <c r="D183" s="621"/>
+      <c r="D183" s="602"/>
       <c r="E183" s="100"/>
       <c r="F183" s="101"/>
       <c r="G183" s="209">
@@ -11789,10 +11789,10 @@
     <row r="184" spans="1:19" ht="15.9" customHeight="1">
       <c r="A184" s="107"/>
       <c r="B184" s="99"/>
-      <c r="C184" s="620" t="s">
+      <c r="C184" s="592" t="s">
         <v>210</v>
       </c>
-      <c r="D184" s="627"/>
+      <c r="D184" s="593"/>
       <c r="E184" s="100"/>
       <c r="F184" s="101"/>
       <c r="G184" s="209">
@@ -11809,10 +11809,10 @@
     <row r="185" spans="1:19" ht="15.9" customHeight="1">
       <c r="A185" s="107"/>
       <c r="B185" s="99"/>
-      <c r="C185" s="620" t="s">
+      <c r="C185" s="592" t="s">
         <v>211</v>
       </c>
-      <c r="D185" s="627"/>
+      <c r="D185" s="593"/>
       <c r="E185" s="100"/>
       <c r="F185" s="101"/>
       <c r="G185" s="209">
@@ -11840,25 +11840,25 @@
     </row>
     <row r="187" spans="1:19" ht="15.9" customHeight="1" thickBot="1">
       <c r="A187" s="107"/>
-      <c r="B187" s="695" t="s">
+      <c r="B187" s="627" t="s">
         <v>212</v>
       </c>
-      <c r="C187" s="696"/>
-      <c r="D187" s="696"/>
-      <c r="E187" s="696"/>
-      <c r="F187" s="696"/>
-      <c r="G187" s="696"/>
-      <c r="H187" s="696"/>
-      <c r="I187" s="696"/>
-      <c r="J187" s="697"/>
+      <c r="C187" s="628"/>
+      <c r="D187" s="628"/>
+      <c r="E187" s="628"/>
+      <c r="F187" s="628"/>
+      <c r="G187" s="628"/>
+      <c r="H187" s="628"/>
+      <c r="I187" s="628"/>
+      <c r="J187" s="629"/>
     </row>
     <row r="188" spans="1:19" ht="15.9" customHeight="1">
       <c r="A188" s="51"/>
       <c r="B188" s="164"/>
-      <c r="C188" s="639" t="s">
+      <c r="C188" s="607" t="s">
         <v>213</v>
       </c>
-      <c r="D188" s="639"/>
+      <c r="D188" s="607"/>
       <c r="E188" s="378"/>
       <c r="F188" s="378" t="s">
         <v>190</v>
@@ -11866,7 +11866,7 @@
       <c r="G188" s="168" t="s">
         <v>190</v>
       </c>
-      <c r="H188" s="692"/>
+      <c r="H188" s="624"/>
       <c r="I188" s="229" t="s">
         <v>67</v>
       </c>
@@ -11877,17 +11877,17 @@
     <row r="189" spans="1:19" ht="15.9" customHeight="1">
       <c r="A189" s="51"/>
       <c r="B189" s="162"/>
-      <c r="C189" s="626" t="s">
+      <c r="C189" s="594" t="s">
         <v>214</v>
       </c>
-      <c r="D189" s="627"/>
+      <c r="D189" s="593"/>
       <c r="E189" s="163"/>
       <c r="F189" s="163"/>
       <c r="G189" s="102">
         <f>+G20</f>
         <v>0</v>
       </c>
-      <c r="H189" s="693"/>
+      <c r="H189" s="625"/>
       <c r="I189" s="162"/>
       <c r="J189" s="102">
         <f>+G189/J5</f>
@@ -11897,17 +11897,17 @@
     <row r="190" spans="1:19" ht="15.9" customHeight="1">
       <c r="A190" s="51"/>
       <c r="B190" s="162"/>
-      <c r="C190" s="626" t="s">
+      <c r="C190" s="594" t="s">
         <v>215</v>
       </c>
-      <c r="D190" s="627"/>
+      <c r="D190" s="593"/>
       <c r="E190" s="163"/>
       <c r="F190" s="163"/>
       <c r="G190" s="102">
         <f>+G189*G23</f>
         <v>0</v>
       </c>
-      <c r="H190" s="693"/>
+      <c r="H190" s="625"/>
       <c r="I190" s="162"/>
       <c r="J190" s="102">
         <f>+J189*J23</f>
@@ -11917,17 +11917,17 @@
     <row r="191" spans="1:19" ht="15.9" customHeight="1">
       <c r="A191" s="51"/>
       <c r="B191" s="162"/>
-      <c r="C191" s="664" t="s">
+      <c r="C191" s="608" t="s">
         <v>216</v>
       </c>
-      <c r="D191" s="664"/>
+      <c r="D191" s="608"/>
       <c r="E191" s="163"/>
       <c r="F191" s="163"/>
       <c r="G191" s="102">
         <f>+G190*25%</f>
         <v>0</v>
       </c>
-      <c r="H191" s="693"/>
+      <c r="H191" s="625"/>
       <c r="I191" s="162"/>
       <c r="J191" s="102">
         <f>+J190*25%</f>
@@ -11937,17 +11937,17 @@
     <row r="192" spans="1:19" ht="15.9" customHeight="1">
       <c r="A192" s="51"/>
       <c r="B192" s="162"/>
-      <c r="C192" s="620" t="s">
+      <c r="C192" s="592" t="s">
         <v>217</v>
       </c>
-      <c r="D192" s="627"/>
+      <c r="D192" s="593"/>
       <c r="E192" s="163"/>
       <c r="F192" s="163"/>
       <c r="G192" s="102">
         <f>+G191*1%</f>
         <v>0</v>
       </c>
-      <c r="H192" s="693"/>
+      <c r="H192" s="625"/>
       <c r="I192" s="162"/>
       <c r="J192" s="102">
         <f>G192/J5</f>
@@ -11957,17 +11957,17 @@
     <row r="193" spans="1:20" ht="15.9" customHeight="1">
       <c r="A193" s="51"/>
       <c r="B193" s="162"/>
-      <c r="C193" s="620" t="s">
+      <c r="C193" s="592" t="s">
         <v>218</v>
       </c>
-      <c r="D193" s="627"/>
+      <c r="D193" s="593"/>
       <c r="E193" s="163"/>
       <c r="F193" s="163"/>
       <c r="G193" s="102">
         <f>G192*0.5</f>
         <v>0</v>
       </c>
-      <c r="H193" s="693"/>
+      <c r="H193" s="625"/>
       <c r="I193" s="162"/>
       <c r="J193" s="102">
         <f>G193/J5</f>
@@ -11977,17 +11977,17 @@
     <row r="194" spans="1:20" ht="15.9" customHeight="1" thickBot="1">
       <c r="A194" s="51"/>
       <c r="B194" s="162"/>
-      <c r="C194" s="664" t="s">
+      <c r="C194" s="608" t="s">
         <v>219</v>
       </c>
-      <c r="D194" s="664"/>
+      <c r="D194" s="608"/>
       <c r="E194" s="163"/>
       <c r="F194" s="163"/>
       <c r="G194" s="110">
         <f>G82</f>
         <v>565315.30184775486</v>
       </c>
-      <c r="H194" s="693"/>
+      <c r="H194" s="625"/>
       <c r="I194" s="162"/>
       <c r="J194" s="110">
         <f>+J192+J193</f>
@@ -11997,8 +11997,8 @@
     <row r="195" spans="1:20" ht="15.9" customHeight="1">
       <c r="A195" s="166"/>
       <c r="B195" s="382"/>
-      <c r="C195" s="632"/>
-      <c r="D195" s="632"/>
+      <c r="C195" s="609"/>
+      <c r="D195" s="609"/>
       <c r="E195" s="379"/>
       <c r="F195" s="379" t="s">
         <v>190</v>
@@ -12006,7 +12006,7 @@
       <c r="G195" s="53" t="s">
         <v>190</v>
       </c>
-      <c r="H195" s="693"/>
+      <c r="H195" s="625"/>
       <c r="I195" s="229" t="s">
         <v>67</v>
       </c>
@@ -12017,17 +12017,17 @@
     <row r="196" spans="1:20" ht="15.9" customHeight="1">
       <c r="A196" s="74"/>
       <c r="B196" s="99"/>
-      <c r="C196" s="626" t="s">
+      <c r="C196" s="594" t="s">
         <v>220</v>
       </c>
-      <c r="D196" s="627"/>
+      <c r="D196" s="593"/>
       <c r="E196" s="58"/>
       <c r="F196" s="50"/>
       <c r="G196" s="102">
         <f>+G54</f>
         <v>72</v>
       </c>
-      <c r="H196" s="693"/>
+      <c r="H196" s="625"/>
       <c r="I196" s="91"/>
       <c r="J196" s="102">
         <f>+J54</f>
@@ -12037,17 +12037,17 @@
     <row r="197" spans="1:20" ht="15.9" customHeight="1">
       <c r="A197" s="74"/>
       <c r="B197" s="99"/>
-      <c r="C197" s="626" t="s">
+      <c r="C197" s="594" t="s">
         <v>221</v>
       </c>
-      <c r="D197" s="627"/>
+      <c r="D197" s="593"/>
       <c r="E197" s="58"/>
       <c r="F197" s="50"/>
       <c r="G197" s="102">
         <f>F140</f>
         <v>9515</v>
       </c>
-      <c r="H197" s="693"/>
+      <c r="H197" s="625"/>
       <c r="I197" s="91"/>
       <c r="J197" s="102">
         <f>I140</f>
@@ -12057,17 +12057,17 @@
     <row r="198" spans="1:20" ht="15.9" customHeight="1">
       <c r="A198" s="120"/>
       <c r="B198" s="99"/>
-      <c r="C198" s="626" t="s">
+      <c r="C198" s="594" t="s">
         <v>222</v>
       </c>
-      <c r="D198" s="627"/>
+      <c r="D198" s="593"/>
       <c r="E198" s="58"/>
       <c r="F198" s="50"/>
       <c r="G198" s="111">
         <f>+F60</f>
         <v>129</v>
       </c>
-      <c r="H198" s="693"/>
+      <c r="H198" s="625"/>
       <c r="I198" s="91"/>
       <c r="J198" s="111">
         <f>+I60</f>
@@ -12077,17 +12077,17 @@
     <row r="199" spans="1:20" ht="15.9" customHeight="1">
       <c r="A199" s="74"/>
       <c r="B199" s="99"/>
-      <c r="C199" s="626" t="s">
+      <c r="C199" s="594" t="s">
         <v>222</v>
       </c>
-      <c r="D199" s="627"/>
+      <c r="D199" s="593"/>
       <c r="E199" s="58"/>
       <c r="F199" s="50"/>
       <c r="G199" s="102">
         <f>(G197*G198*G196)</f>
         <v>88375320</v>
       </c>
-      <c r="H199" s="693"/>
+      <c r="H199" s="625"/>
       <c r="I199" s="91"/>
       <c r="J199" s="102">
         <f>+G199/$J$5</f>
@@ -12097,17 +12097,17 @@
     <row r="200" spans="1:20" ht="15.9" customHeight="1">
       <c r="A200" s="74"/>
       <c r="B200" s="99"/>
-      <c r="C200" s="626" t="s">
+      <c r="C200" s="594" t="s">
         <v>223</v>
       </c>
-      <c r="D200" s="627"/>
+      <c r="D200" s="593"/>
       <c r="E200" s="58"/>
       <c r="F200" s="50"/>
       <c r="G200" s="102">
         <f>G199/G196*12</f>
         <v>14729220</v>
       </c>
-      <c r="H200" s="693"/>
+      <c r="H200" s="625"/>
       <c r="I200" s="91"/>
       <c r="J200" s="102">
         <f>+G200/$J$5</f>
@@ -12117,17 +12117,17 @@
     <row r="201" spans="1:20" ht="15.9" customHeight="1">
       <c r="A201" s="74"/>
       <c r="B201" s="99"/>
-      <c r="C201" s="626" t="s">
+      <c r="C201" s="594" t="s">
         <v>224</v>
       </c>
-      <c r="D201" s="627"/>
+      <c r="D201" s="593"/>
       <c r="E201" s="58"/>
       <c r="F201" s="50"/>
       <c r="G201" s="102">
         <f>(+G220*115%)/5</f>
         <v>3026339.9999999995</v>
       </c>
-      <c r="H201" s="693"/>
+      <c r="H201" s="625"/>
       <c r="I201" s="91"/>
       <c r="J201" s="102">
         <f>+G201/$J$5</f>
@@ -12137,17 +12137,17 @@
     <row r="202" spans="1:20" ht="15.9" customHeight="1">
       <c r="A202" s="74"/>
       <c r="B202" s="99"/>
-      <c r="C202" s="626" t="s">
+      <c r="C202" s="594" t="s">
         <v>225</v>
       </c>
-      <c r="D202" s="627"/>
+      <c r="D202" s="593"/>
       <c r="E202" s="58"/>
       <c r="F202" s="50"/>
       <c r="G202" s="102">
         <f>(+I220*115%)/5</f>
         <v>2765157.6185172233</v>
       </c>
-      <c r="H202" s="693"/>
+      <c r="H202" s="625"/>
       <c r="I202" s="91"/>
       <c r="J202" s="102">
         <f>+G202/$J$5</f>
@@ -12157,17 +12157,17 @@
     <row r="203" spans="1:20" ht="15.9" customHeight="1">
       <c r="A203" s="74"/>
       <c r="B203" s="99"/>
-      <c r="C203" s="626" t="s">
+      <c r="C203" s="594" t="s">
         <v>36</v>
       </c>
-      <c r="D203" s="627"/>
+      <c r="D203" s="593"/>
       <c r="E203" s="58"/>
       <c r="F203" s="50"/>
       <c r="G203" s="102">
         <f>+G67</f>
         <v>11418000</v>
       </c>
-      <c r="H203" s="693"/>
+      <c r="H203" s="625"/>
       <c r="I203" s="91"/>
       <c r="J203" s="102">
         <f>+G203/$J$5</f>
@@ -12177,17 +12177,17 @@
     <row r="204" spans="1:20" ht="15.9" customHeight="1">
       <c r="A204" s="74"/>
       <c r="B204" s="99"/>
-      <c r="C204" s="620" t="s">
+      <c r="C204" s="592" t="s">
         <v>226</v>
       </c>
-      <c r="D204" s="627"/>
+      <c r="D204" s="593"/>
       <c r="E204" s="58"/>
       <c r="F204" s="50"/>
       <c r="G204" s="102">
         <f>(G200+G201+G202+G203)*1.18</f>
         <v>37687686.789850324</v>
       </c>
-      <c r="H204" s="693"/>
+      <c r="H204" s="625"/>
       <c r="I204" s="91"/>
       <c r="J204" s="102">
         <f>+J200+J201+J202+J203</f>
@@ -12197,17 +12197,17 @@
     <row r="205" spans="1:20" ht="15.9" customHeight="1">
       <c r="A205" s="74"/>
       <c r="B205" s="99"/>
-      <c r="C205" s="620" t="s">
+      <c r="C205" s="592" t="s">
         <v>227</v>
       </c>
-      <c r="D205" s="627"/>
+      <c r="D205" s="593"/>
       <c r="E205" s="58"/>
       <c r="F205" s="50"/>
       <c r="G205" s="102">
         <f>G204*1%</f>
         <v>376876.86789850326</v>
       </c>
-      <c r="H205" s="693"/>
+      <c r="H205" s="625"/>
       <c r="I205" s="91"/>
       <c r="J205" s="102">
         <f>J204*1%</f>
@@ -12217,17 +12217,17 @@
     <row r="206" spans="1:20" ht="15.9" customHeight="1">
       <c r="A206" s="74"/>
       <c r="B206" s="99"/>
-      <c r="C206" s="626" t="s">
+      <c r="C206" s="594" t="s">
         <v>228</v>
       </c>
-      <c r="D206" s="627"/>
+      <c r="D206" s="593"/>
       <c r="E206" s="58"/>
       <c r="F206" s="50"/>
       <c r="G206" s="102">
         <f>G204*0.5%</f>
         <v>188438.43394925163</v>
       </c>
-      <c r="H206" s="693"/>
+      <c r="H206" s="625"/>
       <c r="I206" s="91"/>
       <c r="J206" s="102">
         <f>J204*0.5%</f>
@@ -12237,17 +12237,17 @@
     <row r="207" spans="1:20" ht="15.9" customHeight="1">
       <c r="A207" s="74"/>
       <c r="B207" s="99"/>
-      <c r="C207" s="622" t="s">
+      <c r="C207" s="595" t="s">
         <v>219</v>
       </c>
-      <c r="D207" s="623"/>
+      <c r="D207" s="596"/>
       <c r="E207" s="58"/>
       <c r="F207" s="50"/>
       <c r="G207" s="102">
         <f>G205+G206</f>
         <v>565315.30184775486</v>
       </c>
-      <c r="H207" s="693"/>
+      <c r="H207" s="625"/>
       <c r="I207" s="91"/>
       <c r="J207" s="102">
         <v>0</v>
@@ -12262,7 +12262,7 @@
       <c r="E208" s="80"/>
       <c r="F208" s="51"/>
       <c r="G208" s="337"/>
-      <c r="H208" s="693"/>
+      <c r="H208" s="625"/>
       <c r="I208" s="94"/>
       <c r="J208" s="81"/>
     </row>
@@ -12284,7 +12284,7 @@
       <c r="G209" s="161" t="s">
         <v>233</v>
       </c>
-      <c r="H209" s="693"/>
+      <c r="H209" s="625"/>
       <c r="I209" s="379" t="s">
         <v>234</v>
       </c>
@@ -12310,7 +12310,7 @@
         <f>'Lease Rent'!P39</f>
         <v>1360000</v>
       </c>
-      <c r="H210" s="693"/>
+      <c r="H210" s="625"/>
       <c r="I210" s="101">
         <f>'Lease Rent'!O39</f>
         <v>1178337.5999999999</v>
@@ -12340,7 +12340,7 @@
         <f>'Lease Rent'!P51</f>
         <v>2040000</v>
       </c>
-      <c r="H211" s="693"/>
+      <c r="H211" s="625"/>
       <c r="I211" s="101">
         <f>'Lease Rent'!O51</f>
         <v>1826423.2800000005</v>
@@ -12369,7 +12369,7 @@
         <f>'Lease Rent'!P63</f>
         <v>2040000</v>
       </c>
-      <c r="H212" s="693"/>
+      <c r="H212" s="625"/>
       <c r="I212" s="101">
         <f>'Lease Rent'!O63</f>
         <v>1917744.4440000001</v>
@@ -12398,7 +12398,7 @@
         <f>'Lease Rent'!P75</f>
         <v>2244000</v>
       </c>
-      <c r="H213" s="693"/>
+      <c r="H213" s="625"/>
       <c r="I213" s="101">
         <f>'Lease Rent'!O75</f>
         <v>2013631.6662000006</v>
@@ -12427,7 +12427,7 @@
         <f>'Lease Rent'!P87</f>
         <v>2345999.9999999995</v>
       </c>
-      <c r="H214" s="693"/>
+      <c r="H214" s="625"/>
       <c r="I214" s="101">
         <f>'Lease Rent'!O87</f>
         <v>2114313.2495100005</v>
@@ -12456,7 +12456,7 @@
         <f>'Lease Rent'!P99</f>
         <v>2345999.9999999995</v>
       </c>
-      <c r="H215" s="693"/>
+      <c r="H215" s="625"/>
       <c r="I215" s="101">
         <f>'Lease Rent'!O99</f>
         <v>2220028.9119855007</v>
@@ -12484,7 +12484,7 @@
         <f>'Lease Rent'!P103</f>
         <v>781999.99999999988</v>
       </c>
-      <c r="H216" s="693"/>
+      <c r="H216" s="625"/>
       <c r="I216" s="101">
         <f>'Lease Rent'!O103</f>
         <v>751945.27664025011</v>
@@ -12507,7 +12507,7 @@
         <f>'Lease Rent'!R10</f>
         <v>0</v>
       </c>
-      <c r="H217" s="693"/>
+      <c r="H217" s="625"/>
       <c r="I217" s="301"/>
       <c r="J217" s="111"/>
     </row>
@@ -12524,7 +12524,7 @@
         <v>0</v>
       </c>
       <c r="G218" s="118"/>
-      <c r="H218" s="693"/>
+      <c r="H218" s="625"/>
       <c r="I218" s="101"/>
       <c r="J218" s="111"/>
     </row>
@@ -12538,7 +12538,7 @@
       <c r="E219" s="117"/>
       <c r="F219" s="232"/>
       <c r="G219" s="118"/>
-      <c r="H219" s="693"/>
+      <c r="H219" s="625"/>
       <c r="I219" s="101"/>
       <c r="J219" s="111"/>
     </row>
@@ -12561,7 +12561,7 @@
         <f>SUM(G210:G219)</f>
         <v>13158000</v>
       </c>
-      <c r="H220" s="694"/>
+      <c r="H220" s="626"/>
       <c r="I220" s="283">
         <f>SUM(I210:I219)</f>
         <v>12022424.428335754</v>
@@ -12631,6 +12631,219 @@
     </row>
   </sheetData>
   <mergeCells count="237">
+    <mergeCell ref="F137:G137"/>
+    <mergeCell ref="I137:J137"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="B134:D134"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="B105:D105"/>
+    <mergeCell ref="C124:D124"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="E163:E164"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="C123:D123"/>
+    <mergeCell ref="C118:D118"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="B156:D156"/>
+    <mergeCell ref="C151:D151"/>
+    <mergeCell ref="C152:D152"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="C145:D145"/>
+    <mergeCell ref="C148:D148"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B1:J3"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="H188:H220"/>
+    <mergeCell ref="C159:D159"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B187:J187"/>
+    <mergeCell ref="C172:D172"/>
+    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="C177:D177"/>
+    <mergeCell ref="C180:D180"/>
+    <mergeCell ref="C157:D157"/>
+    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="C175:D175"/>
+    <mergeCell ref="C149:D149"/>
+    <mergeCell ref="C150:D150"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="C143:D143"/>
+    <mergeCell ref="C184:D184"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C181:D181"/>
+    <mergeCell ref="C185:D185"/>
+    <mergeCell ref="C168:D168"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="C169:D169"/>
+    <mergeCell ref="C183:D183"/>
+    <mergeCell ref="C170:D170"/>
+    <mergeCell ref="C140:D140"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="C122:D122"/>
+    <mergeCell ref="C171:D171"/>
+    <mergeCell ref="C167:D167"/>
+    <mergeCell ref="B147:D147"/>
+    <mergeCell ref="B163:D164"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="C144:D144"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="C166:D166"/>
+    <mergeCell ref="C182:D182"/>
+    <mergeCell ref="C205:D205"/>
+    <mergeCell ref="C206:D206"/>
+    <mergeCell ref="C207:D207"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C174:D174"/>
+    <mergeCell ref="C197:D197"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="C199:D199"/>
+    <mergeCell ref="C200:D200"/>
+    <mergeCell ref="C201:D201"/>
+    <mergeCell ref="C202:D202"/>
+    <mergeCell ref="C188:D188"/>
+    <mergeCell ref="C191:D191"/>
+    <mergeCell ref="C194:D194"/>
+    <mergeCell ref="C195:D195"/>
+    <mergeCell ref="C196:D196"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
     <mergeCell ref="C204:D204"/>
     <mergeCell ref="C203:D203"/>
     <mergeCell ref="C161:D161"/>
@@ -12655,219 +12868,6 @@
     <mergeCell ref="B179:D179"/>
     <mergeCell ref="C162:D162"/>
     <mergeCell ref="C165:D165"/>
-    <mergeCell ref="C205:D205"/>
-    <mergeCell ref="C206:D206"/>
-    <mergeCell ref="C207:D207"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C174:D174"/>
-    <mergeCell ref="C197:D197"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="C199:D199"/>
-    <mergeCell ref="C200:D200"/>
-    <mergeCell ref="C201:D201"/>
-    <mergeCell ref="C202:D202"/>
-    <mergeCell ref="C188:D188"/>
-    <mergeCell ref="C191:D191"/>
-    <mergeCell ref="C194:D194"/>
-    <mergeCell ref="C195:D195"/>
-    <mergeCell ref="C196:D196"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C181:D181"/>
-    <mergeCell ref="C185:D185"/>
-    <mergeCell ref="C168:D168"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="C169:D169"/>
-    <mergeCell ref="C183:D183"/>
-    <mergeCell ref="C170:D170"/>
-    <mergeCell ref="C140:D140"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="C122:D122"/>
-    <mergeCell ref="C171:D171"/>
-    <mergeCell ref="C167:D167"/>
-    <mergeCell ref="B147:D147"/>
-    <mergeCell ref="B163:D164"/>
-    <mergeCell ref="B125:D125"/>
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="C144:D144"/>
-    <mergeCell ref="C139:D139"/>
-    <mergeCell ref="C166:D166"/>
-    <mergeCell ref="C182:D182"/>
-    <mergeCell ref="H188:H220"/>
-    <mergeCell ref="C159:D159"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B187:J187"/>
-    <mergeCell ref="C172:D172"/>
-    <mergeCell ref="C176:D176"/>
-    <mergeCell ref="C177:D177"/>
-    <mergeCell ref="C180:D180"/>
-    <mergeCell ref="C157:D157"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="C175:D175"/>
-    <mergeCell ref="C149:D149"/>
-    <mergeCell ref="C150:D150"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="I58:J58"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="C143:D143"/>
-    <mergeCell ref="C184:D184"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B1:J3"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="E163:E164"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="C123:D123"/>
-    <mergeCell ref="C118:D118"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="B156:D156"/>
-    <mergeCell ref="C151:D151"/>
-    <mergeCell ref="C152:D152"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="C145:D145"/>
-    <mergeCell ref="C148:D148"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="C136:D136"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="B134:D134"/>
-    <mergeCell ref="C106:D106"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="B105:D105"/>
-    <mergeCell ref="C124:D124"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="F137:G137"/>
-    <mergeCell ref="I137:J137"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C131:D131"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="C107:D107"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.25" top="0.75" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="58" orientation="portrait" r:id="rId1"/>
@@ -12940,215 +12940,215 @@
       <c r="S1" s="1"/>
     </row>
     <row r="2" spans="1:27" ht="11.25" customHeight="1">
-      <c r="A2" s="596"/>
-      <c r="B2" s="597"/>
-      <c r="C2" s="597"/>
-      <c r="D2" s="597"/>
-      <c r="E2" s="597"/>
-      <c r="F2" s="597"/>
-      <c r="G2" s="597"/>
-      <c r="H2" s="597"/>
-      <c r="I2" s="597"/>
-      <c r="J2" s="597"/>
-      <c r="K2" s="597"/>
-      <c r="L2" s="597"/>
-      <c r="M2" s="597"/>
-      <c r="N2" s="597"/>
-      <c r="O2" s="597"/>
-      <c r="P2" s="597"/>
-      <c r="Q2" s="597"/>
-      <c r="R2" s="597"/>
-      <c r="S2" s="597"/>
-      <c r="T2" s="597"/>
-      <c r="U2" s="597"/>
-      <c r="V2" s="597"/>
-      <c r="W2" s="597"/>
-      <c r="X2" s="597"/>
-      <c r="Y2" s="597"/>
-      <c r="Z2" s="597"/>
-      <c r="AA2" s="598"/>
+      <c r="A2" s="668"/>
+      <c r="B2" s="669"/>
+      <c r="C2" s="669"/>
+      <c r="D2" s="669"/>
+      <c r="E2" s="669"/>
+      <c r="F2" s="669"/>
+      <c r="G2" s="669"/>
+      <c r="H2" s="669"/>
+      <c r="I2" s="669"/>
+      <c r="J2" s="669"/>
+      <c r="K2" s="669"/>
+      <c r="L2" s="669"/>
+      <c r="M2" s="669"/>
+      <c r="N2" s="669"/>
+      <c r="O2" s="669"/>
+      <c r="P2" s="669"/>
+      <c r="Q2" s="669"/>
+      <c r="R2" s="669"/>
+      <c r="S2" s="669"/>
+      <c r="T2" s="669"/>
+      <c r="U2" s="669"/>
+      <c r="V2" s="669"/>
+      <c r="W2" s="669"/>
+      <c r="X2" s="669"/>
+      <c r="Y2" s="669"/>
+      <c r="Z2" s="669"/>
+      <c r="AA2" s="693"/>
     </row>
     <row r="3" spans="1:27" ht="11.25" customHeight="1">
-      <c r="A3" s="599"/>
-      <c r="B3" s="600"/>
-      <c r="C3" s="600"/>
-      <c r="D3" s="600"/>
-      <c r="E3" s="600"/>
-      <c r="F3" s="600"/>
-      <c r="G3" s="600"/>
-      <c r="H3" s="600"/>
-      <c r="I3" s="600"/>
-      <c r="J3" s="600"/>
-      <c r="K3" s="600"/>
-      <c r="L3" s="600"/>
-      <c r="M3" s="600"/>
-      <c r="N3" s="600"/>
-      <c r="O3" s="600"/>
-      <c r="P3" s="600"/>
-      <c r="Q3" s="600"/>
-      <c r="R3" s="600"/>
-      <c r="S3" s="600"/>
-      <c r="T3" s="600"/>
-      <c r="U3" s="600"/>
-      <c r="V3" s="600"/>
-      <c r="W3" s="600"/>
-      <c r="X3" s="600"/>
-      <c r="Y3" s="600"/>
-      <c r="Z3" s="600"/>
-      <c r="AA3" s="601"/>
+      <c r="A3" s="694"/>
+      <c r="B3" s="695"/>
+      <c r="C3" s="695"/>
+      <c r="D3" s="695"/>
+      <c r="E3" s="695"/>
+      <c r="F3" s="695"/>
+      <c r="G3" s="695"/>
+      <c r="H3" s="695"/>
+      <c r="I3" s="695"/>
+      <c r="J3" s="695"/>
+      <c r="K3" s="695"/>
+      <c r="L3" s="695"/>
+      <c r="M3" s="695"/>
+      <c r="N3" s="695"/>
+      <c r="O3" s="695"/>
+      <c r="P3" s="695"/>
+      <c r="Q3" s="695"/>
+      <c r="R3" s="695"/>
+      <c r="S3" s="695"/>
+      <c r="T3" s="695"/>
+      <c r="U3" s="695"/>
+      <c r="V3" s="695"/>
+      <c r="W3" s="695"/>
+      <c r="X3" s="695"/>
+      <c r="Y3" s="695"/>
+      <c r="Z3" s="695"/>
+      <c r="AA3" s="696"/>
     </row>
     <row r="4" spans="1:27" ht="12" customHeight="1" thickBot="1">
-      <c r="A4" s="602"/>
-      <c r="B4" s="603"/>
-      <c r="C4" s="603"/>
-      <c r="D4" s="603"/>
-      <c r="E4" s="603"/>
-      <c r="F4" s="603"/>
-      <c r="G4" s="603"/>
-      <c r="H4" s="603"/>
-      <c r="I4" s="603"/>
-      <c r="J4" s="603"/>
-      <c r="K4" s="603"/>
-      <c r="L4" s="603"/>
-      <c r="M4" s="603"/>
-      <c r="N4" s="603"/>
-      <c r="O4" s="603"/>
-      <c r="P4" s="603"/>
-      <c r="Q4" s="603"/>
-      <c r="R4" s="603"/>
-      <c r="S4" s="603"/>
-      <c r="T4" s="603"/>
-      <c r="U4" s="603"/>
-      <c r="V4" s="603"/>
-      <c r="W4" s="603"/>
-      <c r="X4" s="603"/>
-      <c r="Y4" s="603"/>
-      <c r="Z4" s="603"/>
-      <c r="AA4" s="604"/>
+      <c r="A4" s="697"/>
+      <c r="B4" s="698"/>
+      <c r="C4" s="698"/>
+      <c r="D4" s="698"/>
+      <c r="E4" s="698"/>
+      <c r="F4" s="698"/>
+      <c r="G4" s="698"/>
+      <c r="H4" s="698"/>
+      <c r="I4" s="698"/>
+      <c r="J4" s="698"/>
+      <c r="K4" s="698"/>
+      <c r="L4" s="698"/>
+      <c r="M4" s="698"/>
+      <c r="N4" s="698"/>
+      <c r="O4" s="698"/>
+      <c r="P4" s="698"/>
+      <c r="Q4" s="698"/>
+      <c r="R4" s="698"/>
+      <c r="S4" s="698"/>
+      <c r="T4" s="698"/>
+      <c r="U4" s="698"/>
+      <c r="V4" s="698"/>
+      <c r="W4" s="698"/>
+      <c r="X4" s="698"/>
+      <c r="Y4" s="698"/>
+      <c r="Z4" s="698"/>
+      <c r="AA4" s="699"/>
     </row>
     <row r="5" spans="1:27" ht="12.75" customHeight="1">
-      <c r="A5" s="596" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="597"/>
-      <c r="C5" s="597"/>
-      <c r="D5" s="597"/>
-      <c r="E5" s="597"/>
-      <c r="F5" s="597"/>
-      <c r="G5" s="597"/>
-      <c r="H5" s="597"/>
-      <c r="I5" s="597"/>
-      <c r="J5" s="597"/>
-      <c r="K5" s="597"/>
-      <c r="L5" s="597"/>
-      <c r="M5" s="597"/>
-      <c r="N5" s="597"/>
-      <c r="O5" s="597"/>
-      <c r="P5" s="597"/>
-      <c r="Q5" s="597"/>
-      <c r="R5" s="597"/>
-      <c r="S5" s="597"/>
-      <c r="T5" s="597"/>
-      <c r="U5" s="597"/>
-      <c r="V5" s="597"/>
-      <c r="W5" s="597"/>
-      <c r="X5" s="597"/>
-      <c r="Y5" s="597"/>
-      <c r="Z5" s="597"/>
-      <c r="AA5" s="598"/>
+      <c r="A5" s="668" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="669"/>
+      <c r="C5" s="669"/>
+      <c r="D5" s="669"/>
+      <c r="E5" s="669"/>
+      <c r="F5" s="669"/>
+      <c r="G5" s="669"/>
+      <c r="H5" s="669"/>
+      <c r="I5" s="669"/>
+      <c r="J5" s="669"/>
+      <c r="K5" s="669"/>
+      <c r="L5" s="669"/>
+      <c r="M5" s="669"/>
+      <c r="N5" s="669"/>
+      <c r="O5" s="669"/>
+      <c r="P5" s="669"/>
+      <c r="Q5" s="669"/>
+      <c r="R5" s="669"/>
+      <c r="S5" s="669"/>
+      <c r="T5" s="669"/>
+      <c r="U5" s="669"/>
+      <c r="V5" s="669"/>
+      <c r="W5" s="669"/>
+      <c r="X5" s="669"/>
+      <c r="Y5" s="669"/>
+      <c r="Z5" s="669"/>
+      <c r="AA5" s="693"/>
     </row>
     <row r="6" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A6" s="605"/>
-      <c r="B6" s="606"/>
-      <c r="C6" s="606"/>
-      <c r="D6" s="606"/>
-      <c r="E6" s="606"/>
-      <c r="F6" s="606"/>
-      <c r="G6" s="606"/>
-      <c r="H6" s="606"/>
-      <c r="I6" s="606"/>
-      <c r="J6" s="606"/>
-      <c r="K6" s="606"/>
-      <c r="L6" s="606"/>
-      <c r="M6" s="606"/>
-      <c r="N6" s="606"/>
-      <c r="O6" s="606"/>
-      <c r="P6" s="606"/>
-      <c r="Q6" s="606"/>
-      <c r="R6" s="606"/>
-      <c r="S6" s="606"/>
-      <c r="T6" s="606"/>
-      <c r="U6" s="606"/>
-      <c r="V6" s="606"/>
-      <c r="W6" s="606"/>
-      <c r="X6" s="606"/>
-      <c r="Y6" s="606"/>
-      <c r="Z6" s="606"/>
-      <c r="AA6" s="607"/>
+      <c r="A6" s="700"/>
+      <c r="B6" s="701"/>
+      <c r="C6" s="701"/>
+      <c r="D6" s="701"/>
+      <c r="E6" s="701"/>
+      <c r="F6" s="701"/>
+      <c r="G6" s="701"/>
+      <c r="H6" s="701"/>
+      <c r="I6" s="701"/>
+      <c r="J6" s="701"/>
+      <c r="K6" s="701"/>
+      <c r="L6" s="701"/>
+      <c r="M6" s="701"/>
+      <c r="N6" s="701"/>
+      <c r="O6" s="701"/>
+      <c r="P6" s="701"/>
+      <c r="Q6" s="701"/>
+      <c r="R6" s="701"/>
+      <c r="S6" s="701"/>
+      <c r="T6" s="701"/>
+      <c r="U6" s="701"/>
+      <c r="V6" s="701"/>
+      <c r="W6" s="701"/>
+      <c r="X6" s="701"/>
+      <c r="Y6" s="701"/>
+      <c r="Z6" s="701"/>
+      <c r="AA6" s="702"/>
     </row>
     <row r="7" spans="1:27" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A7" s="608" t="s">
+      <c r="A7" s="703" t="s">
         <v>296</v>
       </c>
-      <c r="B7" s="609"/>
-      <c r="C7" s="609"/>
-      <c r="D7" s="609"/>
-      <c r="E7" s="609"/>
-      <c r="F7" s="609"/>
-      <c r="G7" s="609"/>
-      <c r="H7" s="609"/>
-      <c r="I7" s="609"/>
-      <c r="J7" s="609"/>
-      <c r="K7" s="609"/>
-      <c r="L7" s="609"/>
-      <c r="M7" s="609"/>
-      <c r="N7" s="609"/>
-      <c r="O7" s="609"/>
-      <c r="P7" s="610"/>
-      <c r="Q7" s="610"/>
-      <c r="R7" s="610"/>
-      <c r="S7" s="610"/>
-      <c r="T7" s="610"/>
-      <c r="U7" s="610"/>
-      <c r="V7" s="610"/>
-      <c r="W7" s="610"/>
-      <c r="X7" s="610"/>
-      <c r="Y7" s="610"/>
-      <c r="Z7" s="610"/>
-      <c r="AA7" s="611"/>
+      <c r="B7" s="704"/>
+      <c r="C7" s="704"/>
+      <c r="D7" s="704"/>
+      <c r="E7" s="704"/>
+      <c r="F7" s="704"/>
+      <c r="G7" s="704"/>
+      <c r="H7" s="704"/>
+      <c r="I7" s="704"/>
+      <c r="J7" s="704"/>
+      <c r="K7" s="704"/>
+      <c r="L7" s="704"/>
+      <c r="M7" s="704"/>
+      <c r="N7" s="704"/>
+      <c r="O7" s="704"/>
+      <c r="P7" s="705"/>
+      <c r="Q7" s="705"/>
+      <c r="R7" s="705"/>
+      <c r="S7" s="705"/>
+      <c r="T7" s="705"/>
+      <c r="U7" s="705"/>
+      <c r="V7" s="705"/>
+      <c r="W7" s="705"/>
+      <c r="X7" s="705"/>
+      <c r="Y7" s="705"/>
+      <c r="Z7" s="705"/>
+      <c r="AA7" s="706"/>
     </row>
     <row r="8" spans="1:27" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A8" s="612" t="s">
+      <c r="A8" s="707" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="613"/>
-      <c r="C8" s="613"/>
-      <c r="D8" s="613"/>
-      <c r="E8" s="613"/>
-      <c r="F8" s="613"/>
-      <c r="G8" s="613"/>
-      <c r="H8" s="613"/>
-      <c r="I8" s="613"/>
-      <c r="J8" s="613"/>
-      <c r="K8" s="613"/>
-      <c r="L8" s="613"/>
-      <c r="M8" s="613"/>
-      <c r="N8" s="614"/>
+      <c r="B8" s="708"/>
+      <c r="C8" s="708"/>
+      <c r="D8" s="708"/>
+      <c r="E8" s="708"/>
+      <c r="F8" s="708"/>
+      <c r="G8" s="708"/>
+      <c r="H8" s="708"/>
+      <c r="I8" s="708"/>
+      <c r="J8" s="708"/>
+      <c r="K8" s="708"/>
+      <c r="L8" s="708"/>
+      <c r="M8" s="708"/>
+      <c r="N8" s="709"/>
       <c r="O8" s="6"/>
-      <c r="P8" s="612" t="s">
+      <c r="P8" s="707" t="s">
         <v>2</v>
       </c>
-      <c r="Q8" s="613"/>
-      <c r="R8" s="613"/>
-      <c r="S8" s="613"/>
-      <c r="T8" s="613"/>
-      <c r="U8" s="613"/>
-      <c r="V8" s="613"/>
-      <c r="W8" s="613"/>
-      <c r="X8" s="613"/>
-      <c r="Y8" s="613"/>
-      <c r="Z8" s="613"/>
-      <c r="AA8" s="615"/>
+      <c r="Q8" s="708"/>
+      <c r="R8" s="708"/>
+      <c r="S8" s="708"/>
+      <c r="T8" s="708"/>
+      <c r="U8" s="708"/>
+      <c r="V8" s="708"/>
+      <c r="W8" s="708"/>
+      <c r="X8" s="708"/>
+      <c r="Y8" s="708"/>
+      <c r="Z8" s="708"/>
+      <c r="AA8" s="710"/>
     </row>
     <row r="9" spans="1:27" s="215" customFormat="1" ht="45.75" customHeight="1">
       <c r="A9" s="216">
@@ -14375,14 +14375,11 @@
         <f>G26/$T$9</f>
         <v>323747.85755094269</v>
       </c>
-      <c r="I26" s="10">
-        <f>'CAPEX and PM'!B12+'CAPEX and PM'!B18</f>
-        <v>20000000</v>
-      </c>
+      <c r="I26" s="10"/>
       <c r="J26" s="10"/>
       <c r="K26" s="5">
         <f>+G26+I26+J26</f>
-        <v>54000000</v>
+        <v>34000000</v>
       </c>
       <c r="L26" s="10"/>
       <c r="M26" s="10"/>
@@ -14494,12 +14491,12 @@
       </c>
       <c r="I28" s="20">
         <f>SUM(I25:I27)</f>
-        <v>20000000</v>
+        <v>0</v>
       </c>
       <c r="J28" s="20"/>
       <c r="K28" s="20">
         <f>SUM(K25:K27)</f>
-        <v>54565315.301847756</v>
+        <v>34565315.301847756</v>
       </c>
       <c r="L28" s="20"/>
       <c r="M28" s="20">
@@ -14711,11 +14708,11 @@
       <c r="R32" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="T32" s="593" t="s">
+      <c r="T32" s="690" t="s">
         <v>53</v>
       </c>
-      <c r="U32" s="594"/>
-      <c r="V32" s="595"/>
+      <c r="U32" s="691"/>
+      <c r="V32" s="692"/>
     </row>
     <row r="33" spans="1:27" ht="10.5">
       <c r="A33" s="37"/>
@@ -14826,8 +14823,8 @@
         <f>+N32+N34</f>
         <v>1.4601854336242732</v>
       </c>
-      <c r="P36" s="592"/>
-      <c r="Q36" s="592"/>
+      <c r="P36" s="689"/>
+      <c r="Q36" s="689"/>
       <c r="T36" s="31" t="s">
         <v>59</v>
       </c>
@@ -23901,6 +23898,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" xsi:nil="true"/>
+    <Status xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100907921E7373C1341A3C877D189CE8922" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2036b66ca2b7955135caa708c7901a86">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xmlns:ns3="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fed2217af4f675ffeab875e34aa73a78" ns2:_="" ns3:_="">
     <xsd:import namespace="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
@@ -24143,28 +24161,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" xsi:nil="true"/>
-    <Status xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC57694E-BA35-486E-AC74-B7B624F1FDE0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12D5BE44-B07C-4182-BC7A-71E5962390BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
+    <ds:schemaRef ds:uri="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB719E29-C329-4AB1-8ED0-5CC29C0FF757}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24183,25 +24199,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12D5BE44-B07C-4182-BC7A-71E5962390BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
-    <ds:schemaRef ds:uri="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC57694E-BA35-486E-AC74-B7B624F1FDE0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{a59b6cd5-d141-4a33-8bf1-0ca04484304f}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" removed="0"/>

--- a/artifacts/Rental Specimen.xlsx
+++ b/artifacts/Rental Specimen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z0050s8t\Documents\rental-automation\artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE078CAC-E1F0-426B-AB05-917A2DC16468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C41BAEE-2128-46AE-ABAD-7D42AA97368E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="764" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="764" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="26" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="333">
   <si>
     <t>RENTAL CALCULATION FOR NEW LEASE</t>
   </si>
@@ -1121,6 +1121,12 @@
   </si>
   <si>
     <t>Rate per 2 wheeler</t>
+  </si>
+  <si>
+    <t>No. of  dedicated bike parks - chargeable</t>
+  </si>
+  <si>
+    <t>Bikepark - charges per bike including Service tax</t>
   </si>
 </sst>
 </file>
@@ -5556,6 +5562,366 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="184" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="184" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="184" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="33" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="29" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="25" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="26" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="4" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="54" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="6" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="55" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="50" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="192" fontId="52" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="54" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5572,366 +5938,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="33" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="29" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="25" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="26" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="4" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="54" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="6" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="55" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="50" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="192" fontId="52" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -7483,62 +7489,62 @@
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1">
       <c r="A1" s="43"/>
-      <c r="B1" s="639"/>
-      <c r="C1" s="640"/>
-      <c r="D1" s="640"/>
-      <c r="E1" s="640"/>
-      <c r="F1" s="640"/>
-      <c r="G1" s="640"/>
-      <c r="H1" s="640"/>
-      <c r="I1" s="640"/>
-      <c r="J1" s="641"/>
+      <c r="B1" s="643"/>
+      <c r="C1" s="644"/>
+      <c r="D1" s="644"/>
+      <c r="E1" s="644"/>
+      <c r="F1" s="644"/>
+      <c r="G1" s="644"/>
+      <c r="H1" s="644"/>
+      <c r="I1" s="644"/>
+      <c r="J1" s="645"/>
     </row>
     <row r="2" spans="1:10" ht="14.25" customHeight="1">
       <c r="A2" s="43"/>
-      <c r="B2" s="642"/>
-      <c r="C2" s="643"/>
-      <c r="D2" s="643"/>
-      <c r="E2" s="643"/>
-      <c r="F2" s="643"/>
-      <c r="G2" s="643"/>
-      <c r="H2" s="643"/>
-      <c r="I2" s="643"/>
-      <c r="J2" s="644"/>
+      <c r="B2" s="646"/>
+      <c r="C2" s="647"/>
+      <c r="D2" s="647"/>
+      <c r="E2" s="647"/>
+      <c r="F2" s="647"/>
+      <c r="G2" s="647"/>
+      <c r="H2" s="647"/>
+      <c r="I2" s="647"/>
+      <c r="J2" s="648"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A3" s="43"/>
-      <c r="B3" s="645"/>
-      <c r="C3" s="646"/>
-      <c r="D3" s="646"/>
-      <c r="E3" s="646"/>
-      <c r="F3" s="646"/>
-      <c r="G3" s="646"/>
-      <c r="H3" s="646"/>
-      <c r="I3" s="643"/>
-      <c r="J3" s="644"/>
+      <c r="B3" s="649"/>
+      <c r="C3" s="650"/>
+      <c r="D3" s="650"/>
+      <c r="E3" s="650"/>
+      <c r="F3" s="650"/>
+      <c r="G3" s="650"/>
+      <c r="H3" s="650"/>
+      <c r="I3" s="647"/>
+      <c r="J3" s="648"/>
     </row>
     <row r="4" spans="1:10" ht="13">
       <c r="A4" s="43"/>
-      <c r="B4" s="664"/>
-      <c r="C4" s="665"/>
-      <c r="D4" s="665"/>
-      <c r="E4" s="665"/>
-      <c r="F4" s="665"/>
-      <c r="G4" s="665"/>
+      <c r="B4" s="670"/>
+      <c r="C4" s="671"/>
+      <c r="D4" s="671"/>
+      <c r="E4" s="671"/>
+      <c r="F4" s="671"/>
+      <c r="G4" s="671"/>
       <c r="H4" s="389"/>
       <c r="I4" s="390"/>
       <c r="J4" s="391"/>
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="43"/>
-      <c r="B5" s="666" t="s">
+      <c r="B5" s="672" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="667"/>
-      <c r="D5" s="667"/>
-      <c r="E5" s="667"/>
-      <c r="F5" s="667"/>
-      <c r="G5" s="668"/>
+      <c r="C5" s="673"/>
+      <c r="D5" s="673"/>
+      <c r="E5" s="673"/>
+      <c r="F5" s="673"/>
+      <c r="G5" s="674"/>
       <c r="H5" s="392"/>
       <c r="I5" s="469" t="s">
         <v>16</v>
@@ -7549,29 +7555,29 @@
     </row>
     <row r="6" spans="1:10" ht="13.5" thickBot="1">
       <c r="A6" s="43"/>
-      <c r="B6" s="669"/>
-      <c r="C6" s="670"/>
-      <c r="D6" s="671"/>
+      <c r="B6" s="675"/>
+      <c r="C6" s="676"/>
+      <c r="D6" s="677"/>
       <c r="E6" s="44"/>
-      <c r="F6" s="662">
+      <c r="F6" s="668">
         <v>10.763999999999999</v>
       </c>
-      <c r="G6" s="663"/>
+      <c r="G6" s="669"/>
       <c r="H6" s="393"/>
-      <c r="I6" s="653">
+      <c r="I6" s="656">
         <v>10.763999999999999</v>
       </c>
-      <c r="J6" s="654"/>
+      <c r="J6" s="657"/>
     </row>
     <row r="7" spans="1:10" ht="26">
       <c r="A7" s="43"/>
       <c r="B7" s="470" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="672" t="s">
+      <c r="C7" s="678" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="673"/>
+      <c r="D7" s="679"/>
       <c r="E7" s="471"/>
       <c r="F7" s="471" t="s">
         <v>299</v>
@@ -7599,23 +7605,23 @@
       <c r="C8" s="474"/>
       <c r="D8" s="475"/>
       <c r="E8" s="476"/>
-      <c r="F8" s="600" t="s">
+      <c r="F8" s="602" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="601"/>
+      <c r="G8" s="636"/>
       <c r="H8" s="392"/>
-      <c r="I8" s="602" t="s">
+      <c r="I8" s="637" t="s">
         <v>63</v>
       </c>
-      <c r="J8" s="603"/>
+      <c r="J8" s="638"/>
     </row>
     <row r="9" spans="1:10" ht="13">
       <c r="A9" s="43"/>
-      <c r="B9" s="602" t="s">
+      <c r="B9" s="637" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="601"/>
-      <c r="D9" s="617"/>
+      <c r="C9" s="636"/>
+      <c r="D9" s="603"/>
       <c r="E9" s="477"/>
       <c r="F9" s="364" t="s">
         <v>71</v>
@@ -7636,21 +7642,21 @@
       <c r="B10" s="478">
         <v>1</v>
       </c>
-      <c r="C10" s="647" t="s">
+      <c r="C10" s="651" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="648"/>
+      <c r="D10" s="610"/>
       <c r="E10" s="479"/>
-      <c r="F10" s="659" t="s">
+      <c r="F10" s="662" t="s">
         <v>295</v>
       </c>
-      <c r="G10" s="660"/>
+      <c r="G10" s="663"/>
       <c r="H10" s="392"/>
-      <c r="I10" s="655" t="str">
+      <c r="I10" s="658" t="str">
         <f>+F10</f>
         <v>Chennai</v>
       </c>
-      <c r="J10" s="656"/>
+      <c r="J10" s="659"/>
     </row>
     <row r="11" spans="1:10" ht="28.5" customHeight="1">
       <c r="A11" s="43"/>
@@ -7658,19 +7664,19 @@
         <f>1+B10</f>
         <v>2</v>
       </c>
-      <c r="C11" s="649" t="s">
+      <c r="C11" s="652" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="650"/>
+      <c r="D11" s="653"/>
       <c r="E11" s="42"/>
-      <c r="F11" s="659"/>
-      <c r="G11" s="660"/>
+      <c r="F11" s="662"/>
+      <c r="G11" s="663"/>
       <c r="H11" s="392"/>
-      <c r="I11" s="657">
+      <c r="I11" s="660">
         <f>+F11</f>
         <v>0</v>
       </c>
-      <c r="J11" s="658"/>
+      <c r="J11" s="661"/>
     </row>
     <row r="12" spans="1:10" ht="27.75" customHeight="1">
       <c r="A12" s="43"/>
@@ -7678,19 +7684,19 @@
         <f>1+B11</f>
         <v>3</v>
       </c>
-      <c r="C12" s="610" t="s">
+      <c r="C12" s="596" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="611"/>
+      <c r="D12" s="595"/>
       <c r="E12" s="480"/>
-      <c r="F12" s="638"/>
-      <c r="G12" s="633"/>
+      <c r="F12" s="664"/>
+      <c r="G12" s="665"/>
       <c r="H12" s="392"/>
-      <c r="I12" s="634">
+      <c r="I12" s="680">
         <f>+F12</f>
         <v>0</v>
       </c>
-      <c r="J12" s="635"/>
+      <c r="J12" s="681"/>
     </row>
     <row r="13" spans="1:10" ht="15.9" customHeight="1">
       <c r="A13" s="43"/>
@@ -7698,16 +7704,16 @@
         <f t="shared" ref="B13:B30" si="0">1+B12</f>
         <v>4</v>
       </c>
-      <c r="C13" s="610" t="s">
+      <c r="C13" s="596" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="611"/>
+      <c r="D13" s="595"/>
       <c r="E13" s="42"/>
-      <c r="F13" s="632"/>
-      <c r="G13" s="633"/>
+      <c r="F13" s="667"/>
+      <c r="G13" s="665"/>
       <c r="H13" s="392"/>
-      <c r="I13" s="634"/>
-      <c r="J13" s="635"/>
+      <c r="I13" s="680"/>
+      <c r="J13" s="681"/>
     </row>
     <row r="14" spans="1:10" ht="48" customHeight="1">
       <c r="A14" s="43"/>
@@ -7715,21 +7721,21 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="651" t="s">
+      <c r="C14" s="654" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="652"/>
+      <c r="D14" s="655"/>
       <c r="E14" s="464"/>
-      <c r="F14" s="638" t="s">
+      <c r="F14" s="664" t="s">
         <v>296</v>
       </c>
-      <c r="G14" s="661"/>
+      <c r="G14" s="666"/>
       <c r="H14" s="392"/>
-      <c r="I14" s="634" t="str">
+      <c r="I14" s="680" t="str">
         <f>+F14</f>
         <v>6th floor</v>
       </c>
-      <c r="J14" s="635"/>
+      <c r="J14" s="681"/>
     </row>
     <row r="15" spans="1:10" ht="51.75" customHeight="1">
       <c r="A15" s="43"/>
@@ -7737,19 +7743,19 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="610" t="s">
+      <c r="C15" s="596" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="611"/>
+      <c r="D15" s="595"/>
       <c r="E15" s="50"/>
-      <c r="F15" s="600"/>
-      <c r="G15" s="601"/>
+      <c r="F15" s="602"/>
+      <c r="G15" s="636"/>
       <c r="H15" s="392"/>
-      <c r="I15" s="602">
+      <c r="I15" s="637">
         <f>+F15</f>
         <v>0</v>
       </c>
-      <c r="J15" s="603"/>
+      <c r="J15" s="638"/>
     </row>
     <row r="16" spans="1:10" ht="15.9" customHeight="1">
       <c r="A16" s="43"/>
@@ -7757,16 +7763,16 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="610" t="s">
+      <c r="C16" s="596" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="611"/>
+      <c r="D16" s="595"/>
       <c r="E16" s="50"/>
-      <c r="F16" s="632"/>
-      <c r="G16" s="633"/>
+      <c r="F16" s="667"/>
+      <c r="G16" s="665"/>
       <c r="H16" s="392"/>
-      <c r="I16" s="634"/>
-      <c r="J16" s="635"/>
+      <c r="I16" s="680"/>
+      <c r="J16" s="681"/>
     </row>
     <row r="17" spans="1:10" ht="15.9" customHeight="1">
       <c r="A17" s="43"/>
@@ -7774,21 +7780,21 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="610" t="s">
+      <c r="C17" s="596" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="611"/>
+      <c r="D17" s="595"/>
       <c r="E17" s="50"/>
-      <c r="F17" s="638" t="s">
+      <c r="F17" s="664" t="s">
         <v>81</v>
       </c>
-      <c r="G17" s="633"/>
+      <c r="G17" s="665"/>
       <c r="H17" s="392"/>
-      <c r="I17" s="634" t="str">
+      <c r="I17" s="680" t="str">
         <f>+F17</f>
         <v>Warm Shell</v>
       </c>
-      <c r="J17" s="635"/>
+      <c r="J17" s="681"/>
     </row>
     <row r="18" spans="1:10" ht="48" customHeight="1">
       <c r="A18" s="43"/>
@@ -7796,22 +7802,22 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="610" t="s">
+      <c r="C18" s="596" t="s">
         <v>82</v>
       </c>
-      <c r="D18" s="611"/>
+      <c r="D18" s="595"/>
       <c r="E18" s="155"/>
-      <c r="F18" s="600">
+      <c r="F18" s="602">
         <f>F15</f>
         <v>0</v>
       </c>
-      <c r="G18" s="601"/>
+      <c r="G18" s="636"/>
       <c r="H18" s="392"/>
-      <c r="I18" s="602">
+      <c r="I18" s="637">
         <f>+F18</f>
         <v>0</v>
       </c>
-      <c r="J18" s="603"/>
+      <c r="J18" s="638"/>
     </row>
     <row r="19" spans="1:10" ht="15.9" customHeight="1">
       <c r="A19" s="43"/>
@@ -7819,16 +7825,16 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="610" t="s">
+      <c r="C19" s="596" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="611"/>
+      <c r="D19" s="595"/>
       <c r="E19" s="155"/>
-      <c r="F19" s="632"/>
-      <c r="G19" s="633"/>
+      <c r="F19" s="667"/>
+      <c r="G19" s="665"/>
       <c r="H19" s="392"/>
-      <c r="I19" s="634"/>
-      <c r="J19" s="635"/>
+      <c r="I19" s="680"/>
+      <c r="J19" s="681"/>
     </row>
     <row r="20" spans="1:10" ht="15.9" customHeight="1">
       <c r="A20" s="43"/>
@@ -7836,10 +7842,10 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="604" t="s">
+      <c r="C20" s="594" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="611"/>
+      <c r="D20" s="595"/>
       <c r="E20" s="482"/>
       <c r="F20" s="48"/>
       <c r="G20" s="376"/>
@@ -7859,10 +7865,10 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="610" t="s">
+      <c r="C21" s="596" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="611"/>
+      <c r="D21" s="595"/>
       <c r="E21" s="482"/>
       <c r="F21" s="48">
         <f>Main!B3</f>
@@ -7888,10 +7894,10 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="604" t="s">
+      <c r="C22" s="594" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="611"/>
+      <c r="D22" s="595"/>
       <c r="E22" s="482"/>
       <c r="F22" s="48">
         <v>0</v>
@@ -7915,10 +7921,10 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="610" t="s">
+      <c r="C23" s="596" t="s">
         <v>87</v>
       </c>
-      <c r="D23" s="611"/>
+      <c r="D23" s="595"/>
       <c r="E23" s="482"/>
       <c r="F23" s="48">
         <f>+F21+F22</f>
@@ -7944,10 +7950,10 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="610" t="s">
+      <c r="C24" s="596" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="611"/>
+      <c r="D24" s="595"/>
       <c r="E24" s="51"/>
       <c r="F24" s="48"/>
       <c r="G24" s="376">
@@ -7970,10 +7976,10 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="610" t="s">
+      <c r="C25" s="596" t="s">
         <v>89</v>
       </c>
-      <c r="D25" s="611"/>
+      <c r="D25" s="595"/>
       <c r="E25" s="51"/>
       <c r="F25" s="48">
         <v>0</v>
@@ -7998,10 +8004,10 @@
         <f>1+B25</f>
         <v>17</v>
       </c>
-      <c r="C26" s="610" t="s">
+      <c r="C26" s="596" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="611"/>
+      <c r="D26" s="595"/>
       <c r="E26" s="52"/>
       <c r="F26" s="53">
         <f>F25/F23</f>
@@ -8027,10 +8033,10 @@
         <f>1+B26</f>
         <v>18</v>
       </c>
-      <c r="C27" s="604" t="s">
+      <c r="C27" s="594" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="611"/>
+      <c r="D27" s="595"/>
       <c r="E27" s="50"/>
       <c r="F27" s="281">
         <f>'CAPEX and PM'!E3</f>
@@ -8056,10 +8062,10 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="604" t="s">
+      <c r="C28" s="594" t="s">
         <v>92</v>
       </c>
-      <c r="D28" s="611"/>
+      <c r="D28" s="595"/>
       <c r="E28" s="56"/>
       <c r="F28" s="56">
         <f>Main!B12</f>
@@ -8085,10 +8091,10 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="604" t="s">
+      <c r="C29" s="594" t="s">
         <v>93</v>
       </c>
-      <c r="D29" s="611"/>
+      <c r="D29" s="595"/>
       <c r="E29" s="56"/>
       <c r="F29" s="52">
         <f>Main!B13</f>
@@ -8114,10 +8120,10 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="610" t="s">
+      <c r="C30" s="596" t="s">
         <v>94</v>
       </c>
-      <c r="D30" s="611"/>
+      <c r="D30" s="595"/>
       <c r="E30" s="50"/>
       <c r="F30" s="48">
         <v>0</v>
@@ -8138,11 +8144,11 @@
     </row>
     <row r="31" spans="1:10" ht="15.9" customHeight="1">
       <c r="A31" s="43"/>
-      <c r="B31" s="629" t="s">
+      <c r="B31" s="682" t="s">
         <v>95</v>
       </c>
-      <c r="C31" s="630"/>
-      <c r="D31" s="631"/>
+      <c r="C31" s="683"/>
+      <c r="D31" s="684"/>
       <c r="E31" s="485"/>
       <c r="F31" s="364" t="s">
         <v>71</v>
@@ -8163,10 +8169,10 @@
       <c r="B32" s="154">
         <v>1</v>
       </c>
-      <c r="C32" s="604" t="s">
+      <c r="C32" s="594" t="s">
         <v>96</v>
       </c>
-      <c r="D32" s="611"/>
+      <c r="D32" s="595"/>
       <c r="E32" s="51"/>
       <c r="F32" s="48">
         <f>Main!B9/(Main!B3*Main!B7)</f>
@@ -8192,10 +8198,10 @@
         <f>1+B32</f>
         <v>2</v>
       </c>
-      <c r="C33" s="604" t="s">
+      <c r="C33" s="594" t="s">
         <v>97</v>
       </c>
-      <c r="D33" s="611"/>
+      <c r="D33" s="595"/>
       <c r="E33" s="51"/>
       <c r="F33" s="48">
         <v>0</v>
@@ -8219,10 +8225,10 @@
         <f t="shared" ref="B34:B47" si="1">1+B33</f>
         <v>3</v>
       </c>
-      <c r="C34" s="604" t="s">
+      <c r="C34" s="594" t="s">
         <v>98</v>
       </c>
-      <c r="D34" s="611"/>
+      <c r="D34" s="595"/>
       <c r="E34" s="51"/>
       <c r="F34" s="48">
         <v>0</v>
@@ -8247,10 +8253,10 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="C35" s="610" t="s">
+      <c r="C35" s="596" t="s">
         <v>99</v>
       </c>
-      <c r="D35" s="611"/>
+      <c r="D35" s="595"/>
       <c r="E35" s="486"/>
       <c r="F35" s="60">
         <v>0</v>
@@ -8272,10 +8278,10 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="C36" s="604" t="s">
+      <c r="C36" s="594" t="s">
         <v>100</v>
       </c>
-      <c r="D36" s="611"/>
+      <c r="D36" s="595"/>
       <c r="E36" s="486"/>
       <c r="F36" s="62">
         <f>'Lease Rent'!H37</f>
@@ -8301,10 +8307,10 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="C37" s="604" t="s">
+      <c r="C37" s="594" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="611"/>
+      <c r="D37" s="595"/>
       <c r="E37" s="486"/>
       <c r="F37" s="62"/>
       <c r="G37" s="192">
@@ -8321,10 +8327,10 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="C38" s="604" t="s">
+      <c r="C38" s="594" t="s">
         <v>102</v>
       </c>
-      <c r="D38" s="611"/>
+      <c r="D38" s="595"/>
       <c r="E38" s="63"/>
       <c r="F38" s="62">
         <f>'Lease Rent'!J31</f>
@@ -8350,10 +8356,10 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="C39" s="604" t="s">
+      <c r="C39" s="594" t="s">
         <v>103</v>
       </c>
-      <c r="D39" s="611"/>
+      <c r="D39" s="595"/>
       <c r="E39" s="486"/>
       <c r="F39" s="62">
         <f>F36</f>
@@ -8379,10 +8385,10 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="C40" s="604" t="s">
+      <c r="C40" s="594" t="s">
         <v>104</v>
       </c>
-      <c r="D40" s="611"/>
+      <c r="D40" s="595"/>
       <c r="E40" s="486"/>
       <c r="F40" s="62">
         <v>0</v>
@@ -8407,10 +8413,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="C41" s="604" t="s">
+      <c r="C41" s="594" t="s">
         <v>105</v>
       </c>
-      <c r="D41" s="611"/>
+      <c r="D41" s="595"/>
       <c r="E41" s="50"/>
       <c r="F41" s="106">
         <f>F38</f>
@@ -8436,10 +8442,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="C42" s="610" t="s">
+      <c r="C42" s="596" t="s">
         <v>106</v>
       </c>
-      <c r="D42" s="611"/>
+      <c r="D42" s="595"/>
       <c r="E42" s="51"/>
       <c r="F42" s="101">
         <v>0</v>
@@ -8464,26 +8470,27 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="C43" s="610" t="s">
+      <c r="C43" s="596" t="s">
         <v>107</v>
       </c>
-      <c r="D43" s="611"/>
+      <c r="D43" s="595"/>
       <c r="E43" s="65"/>
       <c r="F43" s="60">
-        <v>0</v>
+        <f>'Lease Rent'!D22</f>
+        <v>80</v>
       </c>
       <c r="G43" s="191">
         <f>F43</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H43" s="392"/>
       <c r="I43" s="129">
         <f>+F43</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J43" s="61">
         <f>I43</f>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15.9" customHeight="1">
@@ -8492,10 +8499,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="C44" s="610" t="s">
+      <c r="C44" s="596" t="s">
         <v>108</v>
       </c>
-      <c r="D44" s="611"/>
+      <c r="D44" s="595"/>
       <c r="E44" s="51"/>
       <c r="F44" s="48">
         <f>'Lease Rent'!C22</f>
@@ -8521,10 +8528,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="C45" s="604" t="s">
+      <c r="C45" s="594" t="s">
         <v>109</v>
       </c>
-      <c r="D45" s="611"/>
+      <c r="D45" s="595"/>
       <c r="E45" s="51"/>
       <c r="F45" s="101">
         <v>0</v>
@@ -8546,10 +8553,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="C46" s="610" t="s">
-        <v>107</v>
-      </c>
-      <c r="D46" s="611"/>
+      <c r="C46" s="596" t="s">
+        <v>331</v>
+      </c>
+      <c r="D46" s="595"/>
       <c r="E46" s="51"/>
       <c r="F46" s="48">
         <f>'Lease Rent'!D23</f>
@@ -8566,10 +8573,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="C47" s="610" t="s">
-        <v>108</v>
-      </c>
-      <c r="D47" s="611"/>
+      <c r="C47" s="596" t="s">
+        <v>332</v>
+      </c>
+      <c r="D47" s="595"/>
       <c r="E47" s="51"/>
       <c r="F47" s="48">
         <f>'Lease Rent'!C23</f>
@@ -8582,46 +8589,46 @@
     </row>
     <row r="48" spans="1:10" ht="28.5" customHeight="1">
       <c r="A48" s="43"/>
-      <c r="B48" s="676">
+      <c r="B48" s="641">
         <f>1+B47</f>
         <v>17</v>
       </c>
-      <c r="C48" s="604" t="s">
+      <c r="C48" s="594" t="s">
         <v>110</v>
       </c>
-      <c r="D48" s="611"/>
+      <c r="D48" s="595"/>
       <c r="E48" s="65"/>
-      <c r="F48" s="620" t="str">
+      <c r="F48" s="687" t="str">
         <f>Main!B14</f>
         <v>15% every 3 years</v>
       </c>
-      <c r="G48" s="621"/>
+      <c r="G48" s="688"/>
       <c r="H48" s="392"/>
-      <c r="I48" s="634" t="str">
+      <c r="I48" s="680" t="str">
         <f>+F48</f>
         <v>15% every 3 years</v>
       </c>
-      <c r="J48" s="635"/>
+      <c r="J48" s="681"/>
     </row>
     <row r="49" spans="1:18" ht="15.9" customHeight="1">
       <c r="A49" s="43"/>
-      <c r="B49" s="677"/>
-      <c r="C49" s="604" t="s">
+      <c r="B49" s="642"/>
+      <c r="C49" s="594" t="s">
         <v>111</v>
       </c>
-      <c r="D49" s="611"/>
+      <c r="D49" s="595"/>
       <c r="E49" s="65"/>
-      <c r="F49" s="620" t="str">
+      <c r="F49" s="687" t="str">
         <f>Main!B15</f>
         <v>5% every years</v>
       </c>
-      <c r="G49" s="621"/>
+      <c r="G49" s="688"/>
       <c r="H49" s="392"/>
-      <c r="I49" s="636" t="str">
+      <c r="I49" s="685" t="str">
         <f t="shared" ref="I49:I56" si="2">F49</f>
         <v>5% every years</v>
       </c>
-      <c r="J49" s="637"/>
+      <c r="J49" s="686"/>
     </row>
     <row r="50" spans="1:18" ht="15.9" customHeight="1">
       <c r="A50" s="43"/>
@@ -8629,22 +8636,22 @@
         <f>1+B48</f>
         <v>18</v>
       </c>
-      <c r="C50" s="610" t="s">
+      <c r="C50" s="596" t="s">
         <v>112</v>
       </c>
-      <c r="D50" s="611"/>
+      <c r="D50" s="595"/>
       <c r="E50" s="65"/>
-      <c r="F50" s="618">
+      <c r="F50" s="632">
         <f>'Lease Rent'!B31</f>
         <v>46023</v>
       </c>
-      <c r="G50" s="619"/>
+      <c r="G50" s="633"/>
       <c r="H50" s="392"/>
-      <c r="I50" s="627">
+      <c r="I50" s="634">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J50" s="628"/>
+      <c r="J50" s="635"/>
     </row>
     <row r="51" spans="1:18" ht="15.9" customHeight="1">
       <c r="A51" s="43"/>
@@ -8652,22 +8659,22 @@
         <f t="shared" ref="B51:B57" si="3">1+B50</f>
         <v>19</v>
       </c>
-      <c r="C51" s="604" t="s">
+      <c r="C51" s="594" t="s">
         <v>113</v>
       </c>
-      <c r="D51" s="611"/>
+      <c r="D51" s="595"/>
       <c r="E51" s="65"/>
-      <c r="F51" s="618">
+      <c r="F51" s="632">
         <f>'Lease Rent'!C102</f>
         <v>48213</v>
       </c>
-      <c r="G51" s="619"/>
+      <c r="G51" s="633"/>
       <c r="H51" s="392"/>
-      <c r="I51" s="627">
+      <c r="I51" s="634">
         <f>F51</f>
         <v>48213</v>
       </c>
-      <c r="J51" s="628"/>
+      <c r="J51" s="635"/>
     </row>
     <row r="52" spans="1:18" ht="15.9" customHeight="1">
       <c r="A52" s="43"/>
@@ -8675,22 +8682,22 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="C52" s="604" t="s">
+      <c r="C52" s="594" t="s">
         <v>114</v>
       </c>
-      <c r="D52" s="605"/>
+      <c r="D52" s="604"/>
       <c r="E52" s="65"/>
-      <c r="F52" s="618">
+      <c r="F52" s="632">
         <f>F50</f>
         <v>46023</v>
       </c>
-      <c r="G52" s="619"/>
+      <c r="G52" s="633"/>
       <c r="H52" s="392"/>
-      <c r="I52" s="627">
+      <c r="I52" s="634">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J52" s="628"/>
+      <c r="J52" s="635"/>
     </row>
     <row r="53" spans="1:18" ht="15.9" customHeight="1">
       <c r="A53" s="43"/>
@@ -8698,21 +8705,21 @@
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="C53" s="604" t="s">
+      <c r="C53" s="594" t="s">
         <v>115</v>
       </c>
-      <c r="D53" s="605"/>
+      <c r="D53" s="604"/>
       <c r="E53" s="65"/>
-      <c r="F53" s="600">
-        <v>0</v>
-      </c>
-      <c r="G53" s="601"/>
+      <c r="F53" s="602">
+        <v>0</v>
+      </c>
+      <c r="G53" s="636"/>
       <c r="H53" s="392"/>
-      <c r="I53" s="602">
+      <c r="I53" s="637">
         <f>+F53</f>
         <v>0</v>
       </c>
-      <c r="J53" s="603"/>
+      <c r="J53" s="638"/>
     </row>
     <row r="54" spans="1:18" ht="15.9" customHeight="1">
       <c r="A54" s="43"/>
@@ -8720,10 +8727,10 @@
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="C54" s="610" t="s">
+      <c r="C54" s="596" t="s">
         <v>116</v>
       </c>
-      <c r="D54" s="611"/>
+      <c r="D54" s="595"/>
       <c r="E54" s="50"/>
       <c r="F54" s="48">
         <f>(F51-F50)/365*12</f>
@@ -8750,10 +8757,10 @@
         <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="C55" s="610" t="s">
+      <c r="C55" s="596" t="s">
         <v>117</v>
       </c>
-      <c r="D55" s="611"/>
+      <c r="D55" s="595"/>
       <c r="E55" s="63"/>
       <c r="F55" s="48">
         <v>0</v>
@@ -8779,10 +8786,10 @@
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="C56" s="610" t="s">
+      <c r="C56" s="596" t="s">
         <v>118</v>
       </c>
-      <c r="D56" s="611"/>
+      <c r="D56" s="595"/>
       <c r="E56" s="63"/>
       <c r="F56" s="290" t="s">
         <v>64</v>
@@ -8808,10 +8815,10 @@
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="C57" s="610" t="s">
+      <c r="C57" s="596" t="s">
         <v>119</v>
       </c>
-      <c r="D57" s="611"/>
+      <c r="D57" s="595"/>
       <c r="E57" s="63"/>
       <c r="F57" s="48"/>
       <c r="G57" s="376"/>
@@ -8826,23 +8833,23 @@
       <c r="C58" s="66"/>
       <c r="D58" s="66"/>
       <c r="E58" s="50"/>
-      <c r="F58" s="600" t="s">
+      <c r="F58" s="602" t="s">
         <v>69</v>
       </c>
-      <c r="G58" s="601"/>
+      <c r="G58" s="636"/>
       <c r="H58" s="392"/>
-      <c r="I58" s="602" t="s">
+      <c r="I58" s="637" t="s">
         <v>63</v>
       </c>
-      <c r="J58" s="603"/>
+      <c r="J58" s="638"/>
     </row>
     <row r="59" spans="1:18" ht="15.9" customHeight="1">
       <c r="A59" s="43"/>
-      <c r="B59" s="674" t="s">
+      <c r="B59" s="639" t="s">
         <v>120</v>
       </c>
-      <c r="C59" s="675"/>
-      <c r="D59" s="675"/>
+      <c r="C59" s="640"/>
+      <c r="D59" s="640"/>
       <c r="E59" s="485"/>
       <c r="F59" s="364" t="s">
         <v>71</v>
@@ -8863,10 +8870,10 @@
       <c r="B60" s="154">
         <v>1</v>
       </c>
-      <c r="C60" s="604" t="s">
+      <c r="C60" s="594" t="s">
         <v>121</v>
       </c>
-      <c r="D60" s="611"/>
+      <c r="D60" s="595"/>
       <c r="E60" s="487"/>
       <c r="F60" s="62">
         <f>C220/F21/F54</f>
@@ -8892,10 +8899,10 @@
         <f>1+B60</f>
         <v>2</v>
       </c>
-      <c r="C61" s="604" t="s">
+      <c r="C61" s="594" t="s">
         <v>122</v>
       </c>
-      <c r="D61" s="611"/>
+      <c r="D61" s="595"/>
       <c r="E61" s="487"/>
       <c r="F61" s="62">
         <v>0</v>
@@ -8919,10 +8926,10 @@
         <f t="shared" ref="B62:B83" si="4">1+B61</f>
         <v>3</v>
       </c>
-      <c r="C62" s="606" t="s">
+      <c r="C62" s="597" t="s">
         <v>123</v>
       </c>
-      <c r="D62" s="607"/>
+      <c r="D62" s="598"/>
       <c r="E62" s="67"/>
       <c r="F62" s="68">
         <f>F60+F61</f>
@@ -8948,10 +8955,10 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="C63" s="604" t="s">
+      <c r="C63" s="594" t="s">
         <v>317</v>
       </c>
-      <c r="D63" s="611"/>
+      <c r="D63" s="595"/>
       <c r="E63" s="48"/>
       <c r="F63" s="46">
         <f>F62*F21</f>
@@ -8977,10 +8984,10 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="C64" s="604" t="s">
+      <c r="C64" s="594" t="s">
         <v>124</v>
       </c>
-      <c r="D64" s="611"/>
+      <c r="D64" s="595"/>
       <c r="E64" s="48"/>
       <c r="F64" s="62">
         <f>I220/F21/F54</f>
@@ -9006,10 +9013,10 @@
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="C65" s="610" t="s">
+      <c r="C65" s="596" t="s">
         <v>318</v>
       </c>
-      <c r="D65" s="611"/>
+      <c r="D65" s="595"/>
       <c r="E65" s="63"/>
       <c r="F65" s="46">
         <f>+F64*F21</f>
@@ -9035,10 +9042,10 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="C66" s="610" t="s">
+      <c r="C66" s="596" t="s">
         <v>319</v>
       </c>
-      <c r="D66" s="611"/>
+      <c r="D66" s="595"/>
       <c r="E66" s="51"/>
       <c r="F66" s="48">
         <f>(+G220/F54)</f>
@@ -9064,10 +9071,10 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="C67" s="610" t="s">
+      <c r="C67" s="596" t="s">
         <v>125</v>
       </c>
-      <c r="D67" s="611"/>
+      <c r="D67" s="595"/>
       <c r="E67" s="48"/>
       <c r="F67" s="48">
         <f>Main!B9</f>
@@ -9093,10 +9100,10 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="C68" s="610" t="s">
+      <c r="C68" s="596" t="s">
         <v>126</v>
       </c>
-      <c r="D68" s="611"/>
+      <c r="D68" s="595"/>
       <c r="E68" s="48"/>
       <c r="F68" s="48">
         <v>0</v>
@@ -9121,10 +9128,10 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="C69" s="604" t="s">
+      <c r="C69" s="594" t="s">
         <v>127</v>
       </c>
-      <c r="D69" s="611"/>
+      <c r="D69" s="595"/>
       <c r="E69" s="48"/>
       <c r="F69" s="48">
         <v>500000</v>
@@ -9149,10 +9156,10 @@
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="C70" s="610" t="s">
+      <c r="C70" s="596" t="s">
         <v>128</v>
       </c>
-      <c r="D70" s="611"/>
+      <c r="D70" s="595"/>
       <c r="E70" s="48"/>
       <c r="F70" s="46">
         <v>0</v>
@@ -9174,10 +9181,10 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="C71" s="610" t="s">
+      <c r="C71" s="596" t="s">
         <v>129</v>
       </c>
-      <c r="D71" s="611"/>
+      <c r="D71" s="595"/>
       <c r="E71" s="48"/>
       <c r="F71" s="46">
         <f>F38*F23*F33</f>
@@ -9203,10 +9210,10 @@
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="C72" s="610" t="s">
+      <c r="C72" s="596" t="s">
         <v>130</v>
       </c>
-      <c r="D72" s="611"/>
+      <c r="D72" s="595"/>
       <c r="E72" s="48"/>
       <c r="F72" s="48">
         <v>0</v>
@@ -9231,10 +9238,10 @@
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="C73" s="604" t="s">
+      <c r="C73" s="594" t="s">
         <v>131</v>
       </c>
-      <c r="D73" s="611"/>
+      <c r="D73" s="595"/>
       <c r="E73" s="486"/>
       <c r="F73" s="60">
         <f>+F35*F63</f>
@@ -9288,10 +9295,10 @@
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="C75" s="604" t="s">
+      <c r="C75" s="594" t="s">
         <v>133</v>
       </c>
-      <c r="D75" s="611"/>
+      <c r="D75" s="595"/>
       <c r="E75" s="51"/>
       <c r="F75" s="48">
         <f>+F77/F23</f>
@@ -9317,10 +9324,10 @@
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="C76" s="604" t="s">
+      <c r="C76" s="594" t="s">
         <v>134</v>
       </c>
-      <c r="D76" s="611"/>
+      <c r="D76" s="595"/>
       <c r="E76" s="63"/>
       <c r="F76" s="43"/>
       <c r="G76" s="481"/>
@@ -9340,10 +9347,10 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="C77" s="604" t="s">
+      <c r="C77" s="594" t="s">
         <v>135</v>
       </c>
-      <c r="D77" s="611"/>
+      <c r="D77" s="595"/>
       <c r="E77" s="63"/>
       <c r="F77" s="48">
         <f>'CAPEX and PM'!B6</f>
@@ -9369,10 +9376,10 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="C78" s="604" t="s">
+      <c r="C78" s="594" t="s">
         <v>136</v>
       </c>
-      <c r="D78" s="611"/>
+      <c r="D78" s="595"/>
       <c r="E78" s="63"/>
       <c r="F78" s="48">
         <f>'CAPEX and PM'!B37</f>
@@ -9398,10 +9405,10 @@
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="C79" s="604" t="s">
+      <c r="C79" s="594" t="s">
         <v>137</v>
       </c>
-      <c r="D79" s="611"/>
+      <c r="D79" s="595"/>
       <c r="E79" s="63"/>
       <c r="F79" s="48">
         <f>+'CAPEX and PM'!B104</f>
@@ -9427,10 +9434,10 @@
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="C80" s="604" t="s">
+      <c r="C80" s="594" t="s">
         <v>138</v>
       </c>
-      <c r="D80" s="611"/>
+      <c r="D80" s="595"/>
       <c r="E80" s="63"/>
       <c r="F80" s="48"/>
       <c r="G80" s="376"/>
@@ -9450,10 +9457,10 @@
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="C81" s="604" t="s">
+      <c r="C81" s="594" t="s">
         <v>139</v>
       </c>
-      <c r="D81" s="605"/>
+      <c r="D81" s="604"/>
       <c r="E81" s="63"/>
       <c r="F81" s="48"/>
       <c r="G81" s="376"/>
@@ -9473,10 +9480,10 @@
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="C82" s="604" t="s">
+      <c r="C82" s="594" t="s">
         <v>140</v>
       </c>
-      <c r="D82" s="611"/>
+      <c r="D82" s="595"/>
       <c r="E82" s="51"/>
       <c r="F82" s="48">
         <f>+G207</f>
@@ -9502,10 +9509,10 @@
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="C83" s="604" t="s">
+      <c r="C83" s="594" t="s">
         <v>320</v>
       </c>
-      <c r="D83" s="611"/>
+      <c r="D83" s="595"/>
       <c r="E83" s="486"/>
       <c r="F83" s="48">
         <f>+F30</f>
@@ -9538,11 +9545,11 @@
     </row>
     <row r="85" spans="1:24" ht="15.9" customHeight="1">
       <c r="A85" s="43"/>
-      <c r="B85" s="612" t="s">
+      <c r="B85" s="616" t="s">
         <v>141</v>
       </c>
-      <c r="C85" s="613"/>
-      <c r="D85" s="614"/>
+      <c r="C85" s="617"/>
+      <c r="D85" s="618"/>
       <c r="E85" s="377"/>
       <c r="F85" s="153" t="s">
         <v>71</v>
@@ -9563,10 +9570,10 @@
       <c r="B86" s="154">
         <v>1</v>
       </c>
-      <c r="C86" s="604" t="s">
+      <c r="C86" s="594" t="s">
         <v>142</v>
       </c>
-      <c r="D86" s="611"/>
+      <c r="D86" s="595"/>
       <c r="E86" s="63"/>
       <c r="F86" s="62">
         <f>+F62</f>
@@ -9595,10 +9602,10 @@
         <f>1+B86</f>
         <v>2</v>
       </c>
-      <c r="C87" s="610" t="s">
+      <c r="C87" s="596" t="s">
         <v>143</v>
       </c>
-      <c r="D87" s="611"/>
+      <c r="D87" s="595"/>
       <c r="E87" s="65"/>
       <c r="F87" s="48">
         <v>0</v>
@@ -9621,10 +9628,10 @@
         <f t="shared" ref="B88:B94" si="7">+B87+1</f>
         <v>3</v>
       </c>
-      <c r="C88" s="610" t="s">
+      <c r="C88" s="596" t="s">
         <v>144</v>
       </c>
-      <c r="D88" s="611"/>
+      <c r="D88" s="595"/>
       <c r="E88" s="65"/>
       <c r="F88" s="62">
         <f>(F66/F23)</f>
@@ -9652,10 +9659,10 @@
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="C89" s="610" t="s">
+      <c r="C89" s="596" t="s">
         <v>145</v>
       </c>
-      <c r="D89" s="611"/>
+      <c r="D89" s="595"/>
       <c r="E89" s="65"/>
       <c r="F89" s="58">
         <f>'Security Deposit'!C17</f>
@@ -9683,10 +9690,10 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="C90" s="610" t="s">
+      <c r="C90" s="596" t="s">
         <v>285</v>
       </c>
-      <c r="D90" s="611"/>
+      <c r="D90" s="595"/>
       <c r="E90" s="65"/>
       <c r="F90" s="190">
         <f>+F64</f>
@@ -9714,10 +9721,10 @@
         <f>+B89+1</f>
         <v>5</v>
       </c>
-      <c r="C91" s="610" t="s">
+      <c r="C91" s="596" t="s">
         <v>146</v>
       </c>
-      <c r="D91" s="611"/>
+      <c r="D91" s="595"/>
       <c r="E91" s="65"/>
       <c r="F91" s="58">
         <f>(+F83/F21/F54)</f>
@@ -9744,10 +9751,10 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="C92" s="610" t="s">
+      <c r="C92" s="596" t="s">
         <v>147</v>
       </c>
-      <c r="D92" s="611"/>
+      <c r="D92" s="595"/>
       <c r="E92" s="65"/>
       <c r="F92" s="58">
         <f>F82/F21/F54</f>
@@ -9775,10 +9782,10 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="C93" s="604" t="s">
+      <c r="C93" s="594" t="s">
         <v>148</v>
       </c>
-      <c r="D93" s="611"/>
+      <c r="D93" s="595"/>
       <c r="E93" s="63"/>
       <c r="F93" s="58">
         <f>+G93/F6</f>
@@ -9806,10 +9813,10 @@
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="C94" s="606" t="s">
+      <c r="C94" s="597" t="s">
         <v>65</v>
       </c>
-      <c r="D94" s="607"/>
+      <c r="D94" s="598"/>
       <c r="E94" s="70"/>
       <c r="F94" s="201">
         <f>SUM(F86:F93)</f>
@@ -9834,8 +9841,8 @@
     <row r="95" spans="1:24" ht="15.9" customHeight="1">
       <c r="A95" s="43"/>
       <c r="B95" s="369"/>
-      <c r="C95" s="601"/>
-      <c r="D95" s="601"/>
+      <c r="C95" s="636"/>
+      <c r="D95" s="636"/>
       <c r="E95" s="76"/>
       <c r="F95" s="77"/>
       <c r="G95" s="77"/>
@@ -9845,11 +9852,11 @@
     </row>
     <row r="96" spans="1:24" ht="15.9" customHeight="1">
       <c r="A96" s="43"/>
-      <c r="B96" s="608" t="s">
+      <c r="B96" s="599" t="s">
         <v>149</v>
       </c>
-      <c r="C96" s="609"/>
-      <c r="D96" s="609"/>
+      <c r="C96" s="600"/>
+      <c r="D96" s="600"/>
       <c r="E96" s="79"/>
       <c r="F96" s="153" t="s">
         <v>71</v>
@@ -9871,11 +9878,11 @@
       <c r="B97" s="154">
         <v>1</v>
       </c>
-      <c r="C97" s="610" t="str">
+      <c r="C97" s="596" t="str">
         <f>+C76</f>
         <v>Siemens Standard Fitout (Existing)</v>
       </c>
-      <c r="D97" s="611"/>
+      <c r="D97" s="595"/>
       <c r="E97" s="80"/>
       <c r="F97" s="58">
         <v>0</v>
@@ -9901,11 +9908,11 @@
         <f t="shared" ref="B98:B103" si="8">+B97+1</f>
         <v>2</v>
       </c>
-      <c r="C98" s="610" t="str">
+      <c r="C98" s="596" t="str">
         <f>+C77</f>
         <v>Siemens Standard Fitout (New)</v>
       </c>
-      <c r="D98" s="611"/>
+      <c r="D98" s="595"/>
       <c r="E98" s="63"/>
       <c r="F98" s="58">
         <f>'CAPEX and PM'!B29</f>
@@ -9933,11 +9940,11 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="C99" s="610" t="str">
+      <c r="C99" s="596" t="str">
         <f>+C78</f>
         <v>Capex over the period of lease period</v>
       </c>
-      <c r="D99" s="611"/>
+      <c r="D99" s="595"/>
       <c r="E99" s="63"/>
       <c r="F99" s="58">
         <f>'CAPEX and PM'!B98</f>
@@ -9965,11 +9972,11 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="C100" s="610" t="str">
+      <c r="C100" s="596" t="str">
         <f>+C79</f>
         <v>PM cost over the period of lease period</v>
       </c>
-      <c r="D100" s="611"/>
+      <c r="D100" s="595"/>
       <c r="E100" s="63"/>
       <c r="F100" s="58">
         <f>+'CAPEX and PM'!B105</f>
@@ -9997,11 +10004,11 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="C101" s="610" t="str">
+      <c r="C101" s="596" t="str">
         <f>+C80</f>
         <v>Asset Retirement Obligation ( Removal &amp; Restoration Obligation)</v>
       </c>
-      <c r="D101" s="611"/>
+      <c r="D101" s="595"/>
       <c r="E101" s="63"/>
       <c r="F101" s="58">
         <f>'Security Deposit'!D25</f>
@@ -10032,10 +10039,10 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="C102" s="604" t="s">
+      <c r="C102" s="594" t="s">
         <v>150</v>
       </c>
-      <c r="D102" s="611"/>
+      <c r="D102" s="595"/>
       <c r="E102" s="65"/>
       <c r="F102" s="58">
         <f>+F81/F21/F27</f>
@@ -10063,10 +10070,10 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="C103" s="606" t="s">
+      <c r="C103" s="597" t="s">
         <v>151</v>
       </c>
-      <c r="D103" s="607"/>
+      <c r="D103" s="598"/>
       <c r="E103" s="70"/>
       <c r="F103" s="46">
         <f>SUM(F97:F102)</f>
@@ -10103,11 +10110,11 @@
     </row>
     <row r="105" spans="1:26" ht="15.9" customHeight="1">
       <c r="A105" s="43"/>
-      <c r="B105" s="615" t="s">
+      <c r="B105" s="690" t="s">
         <v>152</v>
       </c>
-      <c r="C105" s="616"/>
-      <c r="D105" s="616"/>
+      <c r="C105" s="611"/>
+      <c r="D105" s="611"/>
       <c r="E105" s="79"/>
       <c r="F105" s="153" t="s">
         <v>71</v>
@@ -10128,10 +10135,10 @@
       <c r="B106" s="154">
         <v>1</v>
       </c>
-      <c r="C106" s="604" t="s">
+      <c r="C106" s="594" t="s">
         <v>65</v>
       </c>
-      <c r="D106" s="611"/>
+      <c r="D106" s="595"/>
       <c r="E106" s="63"/>
       <c r="F106" s="48">
         <f>+F94</f>
@@ -10159,10 +10166,10 @@
         <f>+B106+1</f>
         <v>2</v>
       </c>
-      <c r="C107" s="604" t="s">
+      <c r="C107" s="594" t="s">
         <v>151</v>
       </c>
-      <c r="D107" s="605"/>
+      <c r="D107" s="604"/>
       <c r="E107" s="63"/>
       <c r="F107" s="48">
         <f>+F103</f>
@@ -10190,10 +10197,10 @@
         <f>+B107+1</f>
         <v>3</v>
       </c>
-      <c r="C108" s="606" t="s">
+      <c r="C108" s="597" t="s">
         <v>153</v>
       </c>
-      <c r="D108" s="607"/>
+      <c r="D108" s="598"/>
       <c r="E108" s="70"/>
       <c r="F108" s="46">
         <f>SUM(F106:F107)</f>
@@ -10222,11 +10229,11 @@
     </row>
     <row r="109" spans="1:26" ht="15.9" customHeight="1">
       <c r="A109" s="43"/>
-      <c r="B109" s="608" t="s">
+      <c r="B109" s="599" t="s">
         <v>154</v>
       </c>
-      <c r="C109" s="609"/>
-      <c r="D109" s="609"/>
+      <c r="C109" s="600"/>
+      <c r="D109" s="600"/>
       <c r="E109" s="81"/>
       <c r="F109" s="153" t="s">
         <v>71</v>
@@ -10248,10 +10255,10 @@
       <c r="B110" s="237">
         <v>1</v>
       </c>
-      <c r="C110" s="604" t="s">
+      <c r="C110" s="594" t="s">
         <v>155</v>
       </c>
-      <c r="D110" s="605"/>
+      <c r="D110" s="604"/>
       <c r="E110" s="75"/>
       <c r="F110" s="364"/>
       <c r="G110" s="364"/>
@@ -10265,10 +10272,10 @@
         <f t="shared" ref="B111:B119" si="9">1+B110</f>
         <v>2</v>
       </c>
-      <c r="C111" s="604" t="s">
+      <c r="C111" s="594" t="s">
         <v>156</v>
       </c>
-      <c r="D111" s="605"/>
+      <c r="D111" s="604"/>
       <c r="E111" s="75"/>
       <c r="F111" s="364"/>
       <c r="G111" s="364"/>
@@ -10284,10 +10291,10 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="C112" s="604" t="s">
+      <c r="C112" s="594" t="s">
         <v>157</v>
       </c>
-      <c r="D112" s="605"/>
+      <c r="D112" s="604"/>
       <c r="E112" s="75"/>
       <c r="F112" s="376">
         <f>+F64*0</f>
@@ -10315,10 +10322,10 @@
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="C113" s="604" t="s">
+      <c r="C113" s="594" t="s">
         <v>158</v>
       </c>
-      <c r="D113" s="605"/>
+      <c r="D113" s="604"/>
       <c r="E113" s="75"/>
       <c r="F113" s="364"/>
       <c r="G113" s="364"/>
@@ -10332,10 +10339,10 @@
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="C114" s="604" t="s">
+      <c r="C114" s="594" t="s">
         <v>159</v>
       </c>
-      <c r="D114" s="605"/>
+      <c r="D114" s="604"/>
       <c r="E114" s="75"/>
       <c r="F114" s="364"/>
       <c r="G114" s="364"/>
@@ -10349,10 +10356,10 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="C115" s="604" t="s">
+      <c r="C115" s="594" t="s">
         <v>160</v>
       </c>
-      <c r="D115" s="605"/>
+      <c r="D115" s="604"/>
       <c r="E115" s="75"/>
       <c r="F115" s="364"/>
       <c r="G115" s="364"/>
@@ -10366,10 +10373,10 @@
         <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="C116" s="604" t="s">
+      <c r="C116" s="594" t="s">
         <v>161</v>
       </c>
-      <c r="D116" s="605"/>
+      <c r="D116" s="604"/>
       <c r="E116" s="75"/>
       <c r="F116" s="364"/>
       <c r="G116" s="364"/>
@@ -10383,10 +10390,10 @@
         <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="C117" s="604" t="s">
+      <c r="C117" s="594" t="s">
         <v>162</v>
       </c>
-      <c r="D117" s="611"/>
+      <c r="D117" s="595"/>
       <c r="E117" s="240"/>
       <c r="F117" s="348">
         <v>654</v>
@@ -10412,10 +10419,10 @@
         <f t="shared" si="9"/>
         <v>9</v>
       </c>
-      <c r="C118" s="604" t="s">
+      <c r="C118" s="594" t="s">
         <v>163</v>
       </c>
-      <c r="D118" s="605"/>
+      <c r="D118" s="604"/>
       <c r="E118" s="240"/>
       <c r="F118" s="82">
         <f>F117*7%</f>
@@ -10441,10 +10448,10 @@
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="C119" s="606" t="s">
+      <c r="C119" s="597" t="s">
         <v>164</v>
       </c>
-      <c r="D119" s="607"/>
+      <c r="D119" s="598"/>
       <c r="E119" s="241"/>
       <c r="F119" s="46">
         <f>SUM(F110:F118)</f>
@@ -10470,8 +10477,8 @@
     <row r="120" spans="1:26" ht="15.9" customHeight="1">
       <c r="A120" s="69"/>
       <c r="B120" s="154"/>
-      <c r="C120" s="600"/>
-      <c r="D120" s="617"/>
+      <c r="C120" s="602"/>
+      <c r="D120" s="603"/>
       <c r="E120" s="70"/>
       <c r="F120" s="46"/>
       <c r="G120" s="373"/>
@@ -10485,11 +10492,11 @@
     </row>
     <row r="121" spans="1:26" ht="15.9" customHeight="1">
       <c r="A121" s="69"/>
-      <c r="B121" s="608" t="s">
+      <c r="B121" s="599" t="s">
         <v>165</v>
       </c>
-      <c r="C121" s="609"/>
-      <c r="D121" s="609"/>
+      <c r="C121" s="600"/>
+      <c r="D121" s="600"/>
       <c r="E121" s="81"/>
       <c r="F121" s="153" t="s">
         <v>71</v>
@@ -10512,10 +10519,10 @@
       <c r="B122" s="239">
         <v>1</v>
       </c>
-      <c r="C122" s="604" t="s">
+      <c r="C122" s="594" t="s">
         <v>166</v>
       </c>
-      <c r="D122" s="605"/>
+      <c r="D122" s="604"/>
       <c r="E122" s="70"/>
       <c r="F122" s="46"/>
       <c r="G122" s="373"/>
@@ -10528,10 +10535,10 @@
       <c r="B123" s="154">
         <v>2</v>
       </c>
-      <c r="C123" s="606" t="s">
+      <c r="C123" s="597" t="s">
         <v>167</v>
       </c>
-      <c r="D123" s="607"/>
+      <c r="D123" s="598"/>
       <c r="E123" s="70"/>
       <c r="F123" s="46">
         <f>SUM(F122)</f>
@@ -10554,8 +10561,8 @@
     <row r="124" spans="1:26" ht="15.9" customHeight="1">
       <c r="A124" s="69"/>
       <c r="B124" s="154"/>
-      <c r="C124" s="600"/>
-      <c r="D124" s="617"/>
+      <c r="C124" s="602"/>
+      <c r="D124" s="603"/>
       <c r="E124" s="55"/>
       <c r="F124" s="46"/>
       <c r="G124" s="373"/>
@@ -10565,11 +10572,11 @@
     </row>
     <row r="125" spans="1:26" ht="15.9" customHeight="1">
       <c r="A125" s="69"/>
-      <c r="B125" s="608" t="s">
+      <c r="B125" s="599" t="s">
         <v>168</v>
       </c>
-      <c r="C125" s="609"/>
-      <c r="D125" s="609"/>
+      <c r="C125" s="600"/>
+      <c r="D125" s="600"/>
       <c r="E125" s="81"/>
       <c r="F125" s="153" t="s">
         <v>71</v>
@@ -10590,10 +10597,10 @@
       <c r="B126" s="237">
         <v>1</v>
       </c>
-      <c r="C126" s="604" t="s">
+      <c r="C126" s="594" t="s">
         <v>169</v>
       </c>
-      <c r="D126" s="605"/>
+      <c r="D126" s="604"/>
       <c r="E126" s="238"/>
       <c r="F126" s="373"/>
       <c r="G126" s="373"/>
@@ -10607,10 +10614,10 @@
         <f>1+B126</f>
         <v>2</v>
       </c>
-      <c r="C127" s="604" t="s">
+      <c r="C127" s="594" t="s">
         <v>170</v>
       </c>
-      <c r="D127" s="605"/>
+      <c r="D127" s="604"/>
       <c r="E127" s="238"/>
       <c r="F127" s="373"/>
       <c r="G127" s="373"/>
@@ -10624,10 +10631,10 @@
         <f>1+B127</f>
         <v>3</v>
       </c>
-      <c r="C128" s="604" t="s">
+      <c r="C128" s="594" t="s">
         <v>171</v>
       </c>
-      <c r="D128" s="605"/>
+      <c r="D128" s="604"/>
       <c r="E128" s="238"/>
       <c r="F128" s="373"/>
       <c r="G128" s="373"/>
@@ -10641,10 +10648,10 @@
         <f>1+B128</f>
         <v>4</v>
       </c>
-      <c r="C129" s="604" t="s">
+      <c r="C129" s="594" t="s">
         <v>172</v>
       </c>
-      <c r="D129" s="605"/>
+      <c r="D129" s="604"/>
       <c r="E129" s="238"/>
       <c r="F129" s="373"/>
       <c r="G129" s="373"/>
@@ -10658,10 +10665,10 @@
         <f>1+B129</f>
         <v>5</v>
       </c>
-      <c r="C130" s="604" t="s">
+      <c r="C130" s="594" t="s">
         <v>173</v>
       </c>
-      <c r="D130" s="605"/>
+      <c r="D130" s="604"/>
       <c r="E130" s="238"/>
       <c r="F130" s="373"/>
       <c r="G130" s="373"/>
@@ -10675,10 +10682,10 @@
         <f>1+B130</f>
         <v>6</v>
       </c>
-      <c r="C131" s="604" t="s">
+      <c r="C131" s="594" t="s">
         <v>174</v>
       </c>
-      <c r="D131" s="605"/>
+      <c r="D131" s="604"/>
       <c r="E131" s="238"/>
       <c r="F131" s="373"/>
       <c r="G131" s="373"/>
@@ -10691,10 +10698,10 @@
       <c r="B132" s="369">
         <v>7</v>
       </c>
-      <c r="C132" s="606" t="s">
+      <c r="C132" s="597" t="s">
         <v>175</v>
       </c>
-      <c r="D132" s="607"/>
+      <c r="D132" s="598"/>
       <c r="E132" s="238"/>
       <c r="F132" s="373">
         <f>SUM(F126:F131)</f>
@@ -10717,8 +10724,8 @@
     <row r="133" spans="1:20" ht="15.9" customHeight="1">
       <c r="A133" s="69"/>
       <c r="B133" s="154"/>
-      <c r="C133" s="601"/>
-      <c r="D133" s="617"/>
+      <c r="C133" s="636"/>
+      <c r="D133" s="603"/>
       <c r="E133" s="238"/>
       <c r="F133" s="373"/>
       <c r="G133" s="373"/>
@@ -10728,11 +10735,11 @@
     </row>
     <row r="134" spans="1:20" ht="15.9" customHeight="1">
       <c r="A134" s="43"/>
-      <c r="B134" s="608" t="s">
+      <c r="B134" s="599" t="s">
         <v>176</v>
       </c>
-      <c r="C134" s="609"/>
-      <c r="D134" s="609"/>
+      <c r="C134" s="600"/>
+      <c r="D134" s="600"/>
       <c r="E134" s="81"/>
       <c r="F134" s="153" t="s">
         <v>71</v>
@@ -10753,10 +10760,10 @@
       <c r="B135" s="154">
         <v>1</v>
       </c>
-      <c r="C135" s="606" t="s">
+      <c r="C135" s="597" t="s">
         <v>177</v>
       </c>
-      <c r="D135" s="607"/>
+      <c r="D135" s="598"/>
       <c r="E135" s="70"/>
       <c r="F135" s="46">
         <f>F119+F108+F123+F132</f>
@@ -10781,8 +10788,8 @@
     <row r="136" spans="1:20" ht="15.9" customHeight="1">
       <c r="A136" s="69"/>
       <c r="B136" s="154"/>
-      <c r="C136" s="600"/>
-      <c r="D136" s="617"/>
+      <c r="C136" s="602"/>
+      <c r="D136" s="603"/>
       <c r="E136" s="70"/>
       <c r="F136" s="46"/>
       <c r="G136" s="373"/>
@@ -10796,23 +10803,23 @@
       <c r="C137" s="368"/>
       <c r="D137" s="365"/>
       <c r="E137" s="159"/>
-      <c r="F137" s="600" t="s">
+      <c r="F137" s="602" t="s">
         <v>69</v>
       </c>
-      <c r="G137" s="601"/>
+      <c r="G137" s="636"/>
       <c r="H137" s="392"/>
-      <c r="I137" s="602" t="s">
+      <c r="I137" s="637" t="s">
         <v>63</v>
       </c>
-      <c r="J137" s="603"/>
+      <c r="J137" s="638"/>
     </row>
     <row r="138" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A138" s="43"/>
-      <c r="B138" s="608" t="s">
+      <c r="B138" s="599" t="s">
         <v>178</v>
       </c>
-      <c r="C138" s="609"/>
-      <c r="D138" s="624"/>
+      <c r="C138" s="600"/>
+      <c r="D138" s="601"/>
       <c r="E138" s="153"/>
       <c r="F138" s="153" t="s">
         <v>71</v>
@@ -10831,8 +10838,8 @@
     <row r="139" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A139" s="43"/>
       <c r="B139" s="83"/>
-      <c r="C139" s="625"/>
-      <c r="D139" s="626"/>
+      <c r="C139" s="605"/>
+      <c r="D139" s="606"/>
       <c r="E139" s="155"/>
       <c r="F139" s="46"/>
       <c r="G139" s="373"/>
@@ -10843,10 +10850,10 @@
     <row r="140" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A140" s="43"/>
       <c r="B140" s="83"/>
-      <c r="C140" s="604" t="s">
+      <c r="C140" s="594" t="s">
         <v>179</v>
       </c>
-      <c r="D140" s="611"/>
+      <c r="D140" s="595"/>
       <c r="E140" s="50"/>
       <c r="F140" s="231">
         <f>F21</f>
@@ -10869,10 +10876,10 @@
     <row r="141" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A141" s="43"/>
       <c r="B141" s="83"/>
-      <c r="C141" s="610" t="s">
+      <c r="C141" s="596" t="s">
         <v>180</v>
       </c>
-      <c r="D141" s="611"/>
+      <c r="D141" s="595"/>
       <c r="E141" s="51"/>
       <c r="F141" s="48">
         <f>F24</f>
@@ -10895,10 +10902,10 @@
     <row r="142" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A142" s="43"/>
       <c r="B142" s="83"/>
-      <c r="C142" s="610" t="s">
+      <c r="C142" s="596" t="s">
         <v>181</v>
       </c>
-      <c r="D142" s="611"/>
+      <c r="D142" s="595"/>
       <c r="E142" s="65"/>
       <c r="F142" s="48" t="e">
         <f>+#REF!</f>
@@ -10921,10 +10928,10 @@
     <row r="143" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A143" s="43"/>
       <c r="B143" s="83"/>
-      <c r="C143" s="604" t="s">
+      <c r="C143" s="594" t="s">
         <v>182</v>
       </c>
-      <c r="D143" s="611"/>
+      <c r="D143" s="595"/>
       <c r="E143" s="65"/>
       <c r="F143" s="48">
         <f>F108</f>
@@ -10947,10 +10954,10 @@
     <row r="144" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A144" s="43"/>
       <c r="B144" s="83"/>
-      <c r="C144" s="695" t="s">
+      <c r="C144" s="624" t="s">
         <v>183</v>
       </c>
-      <c r="D144" s="696"/>
+      <c r="D144" s="625"/>
       <c r="E144" s="84"/>
       <c r="F144" s="85">
         <f>F119</f>
@@ -10973,10 +10980,10 @@
     <row r="145" spans="1:10" ht="15.9" hidden="1" customHeight="1">
       <c r="A145" s="69"/>
       <c r="B145" s="154"/>
-      <c r="C145" s="606" t="s">
+      <c r="C145" s="597" t="s">
         <v>184</v>
       </c>
-      <c r="D145" s="607"/>
+      <c r="D145" s="598"/>
       <c r="E145" s="70"/>
       <c r="F145" s="233" t="e">
         <f>F135*#REF!</f>
@@ -11010,11 +11017,11 @@
     </row>
     <row r="147" spans="1:10" ht="15.9" customHeight="1">
       <c r="A147" s="69"/>
-      <c r="B147" s="608" t="s">
+      <c r="B147" s="599" t="s">
         <v>185</v>
       </c>
-      <c r="C147" s="609"/>
-      <c r="D147" s="624"/>
+      <c r="C147" s="600"/>
+      <c r="D147" s="601"/>
       <c r="E147" s="367"/>
       <c r="F147" s="367" t="s">
         <v>186</v>
@@ -11033,8 +11040,8 @@
     <row r="148" spans="1:10" ht="15.9" customHeight="1">
       <c r="A148" s="43"/>
       <c r="B148" s="91"/>
-      <c r="C148" s="625"/>
-      <c r="D148" s="626"/>
+      <c r="C148" s="605"/>
+      <c r="D148" s="606"/>
       <c r="E148" s="92"/>
       <c r="F148" s="93"/>
       <c r="G148" s="197"/>
@@ -11045,10 +11052,10 @@
     <row r="149" spans="1:10" ht="15.9" customHeight="1">
       <c r="A149" s="43"/>
       <c r="B149" s="91"/>
-      <c r="C149" s="610" t="s">
+      <c r="C149" s="596" t="s">
         <v>187</v>
       </c>
-      <c r="D149" s="611"/>
+      <c r="D149" s="595"/>
       <c r="E149" s="92"/>
       <c r="F149" s="93">
         <f>(+F63)*115%</f>
@@ -11071,10 +11078,10 @@
     <row r="150" spans="1:10" ht="15.9" customHeight="1">
       <c r="A150" s="43"/>
       <c r="B150" s="91"/>
-      <c r="C150" s="610" t="s">
+      <c r="C150" s="596" t="s">
         <v>188</v>
       </c>
-      <c r="D150" s="611"/>
+      <c r="D150" s="595"/>
       <c r="E150" s="92"/>
       <c r="F150" s="93">
         <v>0</v>
@@ -11093,10 +11100,10 @@
     <row r="151" spans="1:10" ht="15.9" customHeight="1">
       <c r="A151" s="43"/>
       <c r="B151" s="91"/>
-      <c r="C151" s="610" t="s">
+      <c r="C151" s="596" t="s">
         <v>189</v>
       </c>
-      <c r="D151" s="611"/>
+      <c r="D151" s="595"/>
       <c r="E151" s="92"/>
       <c r="F151" s="93">
         <f>(+F65)*115%</f>
@@ -11119,10 +11126,10 @@
     <row r="152" spans="1:10" ht="15.9" customHeight="1">
       <c r="A152" s="43"/>
       <c r="B152" s="91"/>
-      <c r="C152" s="610" t="s">
+      <c r="C152" s="596" t="s">
         <v>190</v>
       </c>
-      <c r="D152" s="611"/>
+      <c r="D152" s="595"/>
       <c r="E152" s="92"/>
       <c r="F152" s="93">
         <f>(+F66)*115%</f>
@@ -11145,10 +11152,10 @@
     <row r="153" spans="1:10" ht="15.9" customHeight="1">
       <c r="A153" s="43"/>
       <c r="B153" s="91"/>
-      <c r="C153" s="604" t="s">
+      <c r="C153" s="594" t="s">
         <v>191</v>
       </c>
-      <c r="D153" s="611"/>
+      <c r="D153" s="595"/>
       <c r="E153" s="95"/>
       <c r="F153" s="96">
         <f>SUM(F149:F152)</f>
@@ -11171,10 +11178,10 @@
     <row r="154" spans="1:10" ht="15.9" customHeight="1">
       <c r="A154" s="43"/>
       <c r="B154" s="91"/>
-      <c r="C154" s="604" t="s">
+      <c r="C154" s="594" t="s">
         <v>192</v>
       </c>
-      <c r="D154" s="611"/>
+      <c r="D154" s="595"/>
       <c r="E154" s="97"/>
       <c r="F154" s="93">
         <f>+F153*12</f>
@@ -11197,8 +11204,8 @@
     <row r="155" spans="1:10" ht="15.9" customHeight="1">
       <c r="A155" s="43"/>
       <c r="B155" s="91"/>
-      <c r="C155" s="625"/>
-      <c r="D155" s="626"/>
+      <c r="C155" s="605"/>
+      <c r="D155" s="606"/>
       <c r="E155" s="97"/>
       <c r="F155" s="93"/>
       <c r="G155" s="197"/>
@@ -11208,11 +11215,11 @@
     </row>
     <row r="156" spans="1:10" ht="15.9" customHeight="1">
       <c r="A156" s="43"/>
-      <c r="B156" s="608" t="s">
+      <c r="B156" s="599" t="s">
         <v>193</v>
       </c>
-      <c r="C156" s="609"/>
-      <c r="D156" s="624"/>
+      <c r="C156" s="600"/>
+      <c r="D156" s="601"/>
       <c r="E156" s="363"/>
       <c r="F156" s="367" t="s">
         <v>186</v>
@@ -11231,8 +11238,8 @@
     <row r="157" spans="1:10" ht="15.9" customHeight="1">
       <c r="A157" s="43"/>
       <c r="B157" s="91"/>
-      <c r="C157" s="625"/>
-      <c r="D157" s="626"/>
+      <c r="C157" s="605"/>
+      <c r="D157" s="606"/>
       <c r="E157" s="97"/>
       <c r="F157" s="93"/>
       <c r="G157" s="197"/>
@@ -11243,10 +11250,10 @@
     <row r="158" spans="1:10" ht="15.9" customHeight="1">
       <c r="A158" s="43"/>
       <c r="B158" s="91"/>
-      <c r="C158" s="693" t="s">
+      <c r="C158" s="622" t="s">
         <v>194</v>
       </c>
-      <c r="D158" s="694"/>
+      <c r="D158" s="623"/>
       <c r="E158" s="97"/>
       <c r="F158" s="93">
         <f t="shared" ref="F158:G160" si="10">+F77</f>
@@ -11269,10 +11276,10 @@
     <row r="159" spans="1:10" ht="15.9" customHeight="1">
       <c r="A159" s="43"/>
       <c r="B159" s="91"/>
-      <c r="C159" s="604" t="s">
+      <c r="C159" s="594" t="s">
         <v>195</v>
       </c>
-      <c r="D159" s="605"/>
+      <c r="D159" s="604"/>
       <c r="E159" s="97"/>
       <c r="F159" s="93">
         <f t="shared" si="10"/>
@@ -11295,10 +11302,10 @@
     <row r="160" spans="1:10" ht="15.9" customHeight="1">
       <c r="A160" s="43"/>
       <c r="B160" s="91"/>
-      <c r="C160" s="604" t="s">
+      <c r="C160" s="594" t="s">
         <v>196</v>
       </c>
-      <c r="D160" s="605"/>
+      <c r="D160" s="604"/>
       <c r="E160" s="97"/>
       <c r="F160" s="93">
         <f t="shared" si="10"/>
@@ -11321,10 +11328,10 @@
     <row r="161" spans="1:22" ht="15.9" customHeight="1">
       <c r="A161" s="43"/>
       <c r="B161" s="91"/>
-      <c r="C161" s="606" t="s">
+      <c r="C161" s="597" t="s">
         <v>29</v>
       </c>
-      <c r="D161" s="607"/>
+      <c r="D161" s="598"/>
       <c r="E161" s="97"/>
       <c r="F161" s="225">
         <f>SUM(F158:F160)</f>
@@ -11347,8 +11354,8 @@
     <row r="162" spans="1:22" ht="15.9" customHeight="1">
       <c r="A162" s="43"/>
       <c r="B162" s="91"/>
-      <c r="C162" s="625"/>
-      <c r="D162" s="626"/>
+      <c r="C162" s="605"/>
+      <c r="D162" s="606"/>
       <c r="E162" s="97"/>
       <c r="F162" s="93"/>
       <c r="G162" s="197"/>
@@ -11358,12 +11365,12 @@
     </row>
     <row r="163" spans="1:22" ht="15.9" customHeight="1">
       <c r="A163" s="98"/>
-      <c r="B163" s="612" t="s">
+      <c r="B163" s="616" t="s">
         <v>197</v>
       </c>
-      <c r="C163" s="613"/>
-      <c r="D163" s="614"/>
-      <c r="E163" s="622"/>
+      <c r="C163" s="617"/>
+      <c r="D163" s="618"/>
+      <c r="E163" s="689"/>
       <c r="F163" s="153" t="s">
         <v>71</v>
       </c>
@@ -11380,10 +11387,10 @@
     </row>
     <row r="164" spans="1:22" ht="15.9" customHeight="1">
       <c r="A164" s="98"/>
-      <c r="B164" s="690"/>
-      <c r="C164" s="691"/>
-      <c r="D164" s="692"/>
-      <c r="E164" s="623"/>
+      <c r="B164" s="619"/>
+      <c r="C164" s="620"/>
+      <c r="D164" s="621"/>
+      <c r="E164" s="609"/>
       <c r="F164" s="153" t="s">
         <v>69</v>
       </c>
@@ -11401,8 +11408,8 @@
     <row r="165" spans="1:22" ht="15.9" customHeight="1">
       <c r="A165" s="99"/>
       <c r="B165" s="91"/>
-      <c r="C165" s="625"/>
-      <c r="D165" s="626"/>
+      <c r="C165" s="605"/>
+      <c r="D165" s="606"/>
       <c r="E165" s="51"/>
       <c r="F165" s="48"/>
       <c r="G165" s="376"/>
@@ -11413,11 +11420,11 @@
     <row r="166" spans="1:22" ht="15.9" customHeight="1">
       <c r="A166" s="99"/>
       <c r="B166" s="91"/>
-      <c r="C166" s="688" t="str">
+      <c r="C166" s="607" t="str">
         <f>+C106</f>
         <v>Net Rent I</v>
       </c>
-      <c r="D166" s="689"/>
+      <c r="D166" s="608"/>
       <c r="E166" s="51"/>
       <c r="F166" s="48">
         <f>+F106</f>
@@ -11441,11 +11448,11 @@
     <row r="167" spans="1:22" ht="15.9" customHeight="1">
       <c r="A167" s="99"/>
       <c r="B167" s="91"/>
-      <c r="C167" s="688" t="str">
+      <c r="C167" s="607" t="str">
         <f>+C107</f>
         <v>Net Rent II</v>
       </c>
-      <c r="D167" s="689"/>
+      <c r="D167" s="608"/>
       <c r="E167" s="51"/>
       <c r="F167" s="48">
         <f>+F107</f>
@@ -11469,10 +11476,10 @@
     <row r="168" spans="1:22" ht="15.9" customHeight="1">
       <c r="A168" s="99"/>
       <c r="B168" s="139"/>
-      <c r="C168" s="684" t="s">
+      <c r="C168" s="612" t="s">
         <v>198</v>
       </c>
-      <c r="D168" s="685"/>
+      <c r="D168" s="613"/>
       <c r="E168" s="140"/>
       <c r="F168" s="141">
         <f>SUM(F166:F167)</f>
@@ -11497,8 +11504,8 @@
     <row r="169" spans="1:22" ht="15.9" customHeight="1">
       <c r="A169" s="99"/>
       <c r="B169" s="154"/>
-      <c r="C169" s="686"/>
-      <c r="D169" s="687"/>
+      <c r="C169" s="614"/>
+      <c r="D169" s="615"/>
       <c r="E169" s="67"/>
       <c r="F169" s="46"/>
       <c r="G169" s="373"/>
@@ -11511,11 +11518,11 @@
     <row r="170" spans="1:22" ht="15.9" customHeight="1">
       <c r="A170" s="99"/>
       <c r="B170" s="91"/>
-      <c r="C170" s="688" t="str">
+      <c r="C170" s="607" t="str">
         <f>+C119</f>
         <v xml:space="preserve">OpEx I </v>
       </c>
-      <c r="D170" s="689"/>
+      <c r="D170" s="608"/>
       <c r="E170" s="51"/>
       <c r="F170" s="48">
         <f>+F119</f>
@@ -11539,11 +11546,11 @@
     <row r="171" spans="1:22" ht="15.9" customHeight="1">
       <c r="A171" s="99"/>
       <c r="B171" s="91"/>
-      <c r="C171" s="688" t="str">
+      <c r="C171" s="607" t="str">
         <f>+C123</f>
         <v xml:space="preserve">OpEx II </v>
       </c>
-      <c r="D171" s="689"/>
+      <c r="D171" s="608"/>
       <c r="E171" s="51"/>
       <c r="F171" s="48">
         <f>+F123</f>
@@ -11566,10 +11573,10 @@
     <row r="172" spans="1:22" ht="15.9" customHeight="1">
       <c r="A172" s="99"/>
       <c r="B172" s="142"/>
-      <c r="C172" s="684" t="s">
+      <c r="C172" s="612" t="s">
         <v>199</v>
       </c>
-      <c r="D172" s="685"/>
+      <c r="D172" s="613"/>
       <c r="E172" s="143"/>
       <c r="F172" s="144">
         <f>SUM(F170:F171)</f>
@@ -11604,11 +11611,11 @@
     <row r="174" spans="1:22" ht="15.9" customHeight="1">
       <c r="A174" s="99"/>
       <c r="B174" s="91"/>
-      <c r="C174" s="688" t="str">
+      <c r="C174" s="607" t="str">
         <f>+C132</f>
         <v xml:space="preserve">Services </v>
       </c>
-      <c r="D174" s="689"/>
+      <c r="D174" s="608"/>
       <c r="E174" s="51"/>
       <c r="F174" s="48">
         <f>+F132</f>
@@ -11631,10 +11638,10 @@
     <row r="175" spans="1:22" ht="15.9" customHeight="1">
       <c r="A175" s="99"/>
       <c r="B175" s="142"/>
-      <c r="C175" s="684" t="s">
+      <c r="C175" s="612" t="s">
         <v>200</v>
       </c>
-      <c r="D175" s="685"/>
+      <c r="D175" s="613"/>
       <c r="E175" s="143"/>
       <c r="F175" s="144">
         <f>SUM(F174)</f>
@@ -11657,8 +11664,8 @@
     <row r="176" spans="1:22" ht="15.9" customHeight="1">
       <c r="A176" s="99"/>
       <c r="B176" s="91"/>
-      <c r="C176" s="625"/>
-      <c r="D176" s="626"/>
+      <c r="C176" s="605"/>
+      <c r="D176" s="606"/>
       <c r="E176" s="51"/>
       <c r="F176" s="48"/>
       <c r="G176" s="376"/>
@@ -11669,10 +11676,10 @@
     <row r="177" spans="1:19" ht="15.9" customHeight="1">
       <c r="A177" s="99"/>
       <c r="B177" s="142"/>
-      <c r="C177" s="684" t="s">
+      <c r="C177" s="612" t="s">
         <v>201</v>
       </c>
-      <c r="D177" s="685"/>
+      <c r="D177" s="613"/>
       <c r="E177" s="146"/>
       <c r="F177" s="141">
         <f>+F168+F172+F175</f>
@@ -11707,11 +11714,11 @@
     </row>
     <row r="179" spans="1:19" ht="15.9" customHeight="1">
       <c r="A179" s="99"/>
-      <c r="B179" s="608" t="s">
+      <c r="B179" s="599" t="s">
         <v>202</v>
       </c>
-      <c r="C179" s="609"/>
-      <c r="D179" s="624"/>
+      <c r="C179" s="600"/>
+      <c r="D179" s="601"/>
       <c r="E179" s="367"/>
       <c r="F179" s="367" t="s">
         <v>186</v>
@@ -11730,8 +11737,8 @@
     <row r="180" spans="1:19" ht="15.9" customHeight="1">
       <c r="A180" s="99"/>
       <c r="B180" s="91"/>
-      <c r="C180" s="625"/>
-      <c r="D180" s="626"/>
+      <c r="C180" s="605"/>
+      <c r="D180" s="606"/>
       <c r="E180" s="51"/>
       <c r="F180" s="48"/>
       <c r="G180" s="376"/>
@@ -11742,10 +11749,10 @@
     <row r="181" spans="1:19" ht="15.9" customHeight="1">
       <c r="A181" s="99"/>
       <c r="B181" s="91"/>
-      <c r="C181" s="610" t="s">
+      <c r="C181" s="596" t="s">
         <v>203</v>
       </c>
-      <c r="D181" s="611"/>
+      <c r="D181" s="595"/>
       <c r="E181" s="92"/>
       <c r="F181" s="93"/>
       <c r="G181" s="197">
@@ -11762,10 +11769,10 @@
     <row r="182" spans="1:19" ht="15.9" customHeight="1">
       <c r="A182" s="99"/>
       <c r="B182" s="91"/>
-      <c r="C182" s="604" t="s">
+      <c r="C182" s="594" t="s">
         <v>204</v>
       </c>
-      <c r="D182" s="611"/>
+      <c r="D182" s="595"/>
       <c r="E182" s="92"/>
       <c r="F182" s="93"/>
       <c r="G182" s="197">
@@ -11782,10 +11789,10 @@
     <row r="183" spans="1:19" ht="15.9" customHeight="1">
       <c r="A183" s="99"/>
       <c r="B183" s="91"/>
-      <c r="C183" s="604" t="s">
+      <c r="C183" s="594" t="s">
         <v>205</v>
       </c>
-      <c r="D183" s="605"/>
+      <c r="D183" s="604"/>
       <c r="E183" s="92"/>
       <c r="F183" s="93"/>
       <c r="G183" s="197">
@@ -11799,10 +11806,10 @@
     <row r="184" spans="1:19" ht="15.9" customHeight="1">
       <c r="A184" s="99"/>
       <c r="B184" s="91"/>
-      <c r="C184" s="604" t="s">
+      <c r="C184" s="594" t="s">
         <v>206</v>
       </c>
-      <c r="D184" s="611"/>
+      <c r="D184" s="595"/>
       <c r="E184" s="92"/>
       <c r="F184" s="93"/>
       <c r="G184" s="197">
@@ -11819,10 +11826,10 @@
     <row r="185" spans="1:19" ht="15.9" customHeight="1">
       <c r="A185" s="99"/>
       <c r="B185" s="91"/>
-      <c r="C185" s="604" t="s">
+      <c r="C185" s="594" t="s">
         <v>207</v>
       </c>
-      <c r="D185" s="611"/>
+      <c r="D185" s="595"/>
       <c r="E185" s="92"/>
       <c r="F185" s="93"/>
       <c r="G185" s="197">
@@ -11850,25 +11857,25 @@
     </row>
     <row r="187" spans="1:19" ht="15.9" customHeight="1" thickBot="1">
       <c r="A187" s="99"/>
-      <c r="B187" s="681" t="s">
+      <c r="B187" s="629" t="s">
         <v>208</v>
       </c>
-      <c r="C187" s="682"/>
-      <c r="D187" s="682"/>
-      <c r="E187" s="682"/>
-      <c r="F187" s="682"/>
-      <c r="G187" s="682"/>
-      <c r="H187" s="682"/>
-      <c r="I187" s="682"/>
-      <c r="J187" s="683"/>
+      <c r="C187" s="630"/>
+      <c r="D187" s="630"/>
+      <c r="E187" s="630"/>
+      <c r="F187" s="630"/>
+      <c r="G187" s="630"/>
+      <c r="H187" s="630"/>
+      <c r="I187" s="630"/>
+      <c r="J187" s="631"/>
     </row>
     <row r="188" spans="1:19" ht="15.9" customHeight="1">
       <c r="A188" s="43"/>
       <c r="B188" s="156"/>
-      <c r="C188" s="623" t="s">
+      <c r="C188" s="609" t="s">
         <v>209</v>
       </c>
-      <c r="D188" s="623"/>
+      <c r="D188" s="609"/>
       <c r="E188" s="366"/>
       <c r="F188" s="366" t="s">
         <v>186</v>
@@ -11876,7 +11883,7 @@
       <c r="G188" s="160" t="s">
         <v>186</v>
       </c>
-      <c r="H188" s="678"/>
+      <c r="H188" s="626"/>
       <c r="I188" s="217" t="s">
         <v>63</v>
       </c>
@@ -11887,17 +11894,17 @@
     <row r="189" spans="1:19" ht="15.9" customHeight="1">
       <c r="A189" s="43"/>
       <c r="B189" s="154"/>
-      <c r="C189" s="610" t="s">
+      <c r="C189" s="596" t="s">
         <v>210</v>
       </c>
-      <c r="D189" s="611"/>
+      <c r="D189" s="595"/>
       <c r="E189" s="155"/>
       <c r="F189" s="155"/>
       <c r="G189" s="94">
         <f>+G20</f>
         <v>0</v>
       </c>
-      <c r="H189" s="679"/>
+      <c r="H189" s="627"/>
       <c r="I189" s="154"/>
       <c r="J189" s="94">
         <f>+G189/J5</f>
@@ -11907,17 +11914,17 @@
     <row r="190" spans="1:19" ht="15.9" customHeight="1">
       <c r="A190" s="43"/>
       <c r="B190" s="154"/>
-      <c r="C190" s="610" t="s">
+      <c r="C190" s="596" t="s">
         <v>211</v>
       </c>
-      <c r="D190" s="611"/>
+      <c r="D190" s="595"/>
       <c r="E190" s="155"/>
       <c r="F190" s="155"/>
       <c r="G190" s="94">
         <f>+G189*G23</f>
         <v>0</v>
       </c>
-      <c r="H190" s="679"/>
+      <c r="H190" s="627"/>
       <c r="I190" s="154"/>
       <c r="J190" s="94">
         <f>+J189*J23</f>
@@ -11927,17 +11934,17 @@
     <row r="191" spans="1:19" ht="15.9" customHeight="1">
       <c r="A191" s="43"/>
       <c r="B191" s="154"/>
-      <c r="C191" s="648" t="s">
+      <c r="C191" s="610" t="s">
         <v>212</v>
       </c>
-      <c r="D191" s="648"/>
+      <c r="D191" s="610"/>
       <c r="E191" s="155"/>
       <c r="F191" s="155"/>
       <c r="G191" s="94">
         <f>+G190*25%</f>
         <v>0</v>
       </c>
-      <c r="H191" s="679"/>
+      <c r="H191" s="627"/>
       <c r="I191" s="154"/>
       <c r="J191" s="94">
         <f>+J190*25%</f>
@@ -11947,17 +11954,17 @@
     <row r="192" spans="1:19" ht="15.9" customHeight="1">
       <c r="A192" s="43"/>
       <c r="B192" s="154"/>
-      <c r="C192" s="604" t="s">
+      <c r="C192" s="594" t="s">
         <v>213</v>
       </c>
-      <c r="D192" s="611"/>
+      <c r="D192" s="595"/>
       <c r="E192" s="155"/>
       <c r="F192" s="155"/>
       <c r="G192" s="94">
         <f>+G191*1%</f>
         <v>0</v>
       </c>
-      <c r="H192" s="679"/>
+      <c r="H192" s="627"/>
       <c r="I192" s="154"/>
       <c r="J192" s="94">
         <f>G192/J5</f>
@@ -11967,17 +11974,17 @@
     <row r="193" spans="1:20" ht="15.9" customHeight="1">
       <c r="A193" s="43"/>
       <c r="B193" s="154"/>
-      <c r="C193" s="604" t="s">
+      <c r="C193" s="594" t="s">
         <v>214</v>
       </c>
-      <c r="D193" s="611"/>
+      <c r="D193" s="595"/>
       <c r="E193" s="155"/>
       <c r="F193" s="155"/>
       <c r="G193" s="94">
         <f>G192*0.5</f>
         <v>0</v>
       </c>
-      <c r="H193" s="679"/>
+      <c r="H193" s="627"/>
       <c r="I193" s="154"/>
       <c r="J193" s="94">
         <f>G193/J5</f>
@@ -11987,17 +11994,17 @@
     <row r="194" spans="1:20" ht="15.9" customHeight="1" thickBot="1">
       <c r="A194" s="43"/>
       <c r="B194" s="154"/>
-      <c r="C194" s="648" t="s">
+      <c r="C194" s="610" t="s">
         <v>215</v>
       </c>
-      <c r="D194" s="648"/>
+      <c r="D194" s="610"/>
       <c r="E194" s="155"/>
       <c r="F194" s="155"/>
       <c r="G194" s="102">
         <f>G82</f>
         <v>565315.30184775486</v>
       </c>
-      <c r="H194" s="679"/>
+      <c r="H194" s="627"/>
       <c r="I194" s="154"/>
       <c r="J194" s="102">
         <f>+J192+J193</f>
@@ -12007,8 +12014,8 @@
     <row r="195" spans="1:20" ht="15.9" customHeight="1">
       <c r="A195" s="158"/>
       <c r="B195" s="370"/>
-      <c r="C195" s="616"/>
-      <c r="D195" s="616"/>
+      <c r="C195" s="611"/>
+      <c r="D195" s="611"/>
       <c r="E195" s="367"/>
       <c r="F195" s="367" t="s">
         <v>186</v>
@@ -12016,7 +12023,7 @@
       <c r="G195" s="45" t="s">
         <v>186</v>
       </c>
-      <c r="H195" s="679"/>
+      <c r="H195" s="627"/>
       <c r="I195" s="217" t="s">
         <v>63</v>
       </c>
@@ -12027,17 +12034,17 @@
     <row r="196" spans="1:20" ht="15.9" customHeight="1">
       <c r="A196" s="66"/>
       <c r="B196" s="91"/>
-      <c r="C196" s="610" t="s">
+      <c r="C196" s="596" t="s">
         <v>216</v>
       </c>
-      <c r="D196" s="611"/>
+      <c r="D196" s="595"/>
       <c r="E196" s="50"/>
       <c r="F196" s="42"/>
       <c r="G196" s="94">
         <f>+G54</f>
         <v>72</v>
       </c>
-      <c r="H196" s="679"/>
+      <c r="H196" s="627"/>
       <c r="I196" s="83"/>
       <c r="J196" s="94">
         <f>+J54</f>
@@ -12047,17 +12054,17 @@
     <row r="197" spans="1:20" ht="15.9" customHeight="1">
       <c r="A197" s="66"/>
       <c r="B197" s="91"/>
-      <c r="C197" s="610" t="s">
+      <c r="C197" s="596" t="s">
         <v>217</v>
       </c>
-      <c r="D197" s="611"/>
+      <c r="D197" s="595"/>
       <c r="E197" s="50"/>
       <c r="F197" s="42"/>
       <c r="G197" s="94">
         <f>F140</f>
         <v>9515</v>
       </c>
-      <c r="H197" s="679"/>
+      <c r="H197" s="627"/>
       <c r="I197" s="83"/>
       <c r="J197" s="94">
         <f>I140</f>
@@ -12067,17 +12074,17 @@
     <row r="198" spans="1:20" ht="15.9" customHeight="1">
       <c r="A198" s="112"/>
       <c r="B198" s="91"/>
-      <c r="C198" s="610" t="s">
+      <c r="C198" s="596" t="s">
         <v>218</v>
       </c>
-      <c r="D198" s="611"/>
+      <c r="D198" s="595"/>
       <c r="E198" s="50"/>
       <c r="F198" s="42"/>
       <c r="G198" s="103">
         <f>+F60</f>
         <v>129</v>
       </c>
-      <c r="H198" s="679"/>
+      <c r="H198" s="627"/>
       <c r="I198" s="83"/>
       <c r="J198" s="103">
         <f>+I60</f>
@@ -12087,17 +12094,17 @@
     <row r="199" spans="1:20" ht="15.9" customHeight="1">
       <c r="A199" s="66"/>
       <c r="B199" s="91"/>
-      <c r="C199" s="610" t="s">
+      <c r="C199" s="596" t="s">
         <v>218</v>
       </c>
-      <c r="D199" s="611"/>
+      <c r="D199" s="595"/>
       <c r="E199" s="50"/>
       <c r="F199" s="42"/>
       <c r="G199" s="94">
         <f>(G197*G198*G196)</f>
         <v>88375320</v>
       </c>
-      <c r="H199" s="679"/>
+      <c r="H199" s="627"/>
       <c r="I199" s="83"/>
       <c r="J199" s="94">
         <f>+G199/$J$5</f>
@@ -12107,17 +12114,17 @@
     <row r="200" spans="1:20" ht="15.9" customHeight="1">
       <c r="A200" s="66"/>
       <c r="B200" s="91"/>
-      <c r="C200" s="610" t="s">
+      <c r="C200" s="596" t="s">
         <v>219</v>
       </c>
-      <c r="D200" s="611"/>
+      <c r="D200" s="595"/>
       <c r="E200" s="50"/>
       <c r="F200" s="42"/>
       <c r="G200" s="94">
         <f>G199/G196*12</f>
         <v>14729220</v>
       </c>
-      <c r="H200" s="679"/>
+      <c r="H200" s="627"/>
       <c r="I200" s="83"/>
       <c r="J200" s="94">
         <f>+G200/$J$5</f>
@@ -12127,17 +12134,17 @@
     <row r="201" spans="1:20" ht="15.9" customHeight="1">
       <c r="A201" s="66"/>
       <c r="B201" s="91"/>
-      <c r="C201" s="610" t="s">
+      <c r="C201" s="596" t="s">
         <v>220</v>
       </c>
-      <c r="D201" s="611"/>
+      <c r="D201" s="595"/>
       <c r="E201" s="50"/>
       <c r="F201" s="42"/>
       <c r="G201" s="94">
         <f>(+G220*115%)/5</f>
         <v>3026339.9999999995</v>
       </c>
-      <c r="H201" s="679"/>
+      <c r="H201" s="627"/>
       <c r="I201" s="83"/>
       <c r="J201" s="94">
         <f>+G201/$J$5</f>
@@ -12147,17 +12154,17 @@
     <row r="202" spans="1:20" ht="15.9" customHeight="1">
       <c r="A202" s="66"/>
       <c r="B202" s="91"/>
-      <c r="C202" s="610" t="s">
+      <c r="C202" s="596" t="s">
         <v>221</v>
       </c>
-      <c r="D202" s="611"/>
+      <c r="D202" s="595"/>
       <c r="E202" s="50"/>
       <c r="F202" s="42"/>
       <c r="G202" s="94">
         <f>(+I220*115%)/5</f>
         <v>2765157.6185172233</v>
       </c>
-      <c r="H202" s="679"/>
+      <c r="H202" s="627"/>
       <c r="I202" s="83"/>
       <c r="J202" s="94">
         <f>+G202/$J$5</f>
@@ -12167,17 +12174,17 @@
     <row r="203" spans="1:20" ht="15.9" customHeight="1">
       <c r="A203" s="66"/>
       <c r="B203" s="91"/>
-      <c r="C203" s="610" t="s">
+      <c r="C203" s="596" t="s">
         <v>36</v>
       </c>
-      <c r="D203" s="611"/>
+      <c r="D203" s="595"/>
       <c r="E203" s="50"/>
       <c r="F203" s="42"/>
       <c r="G203" s="94">
         <f>+G67</f>
         <v>11418000</v>
       </c>
-      <c r="H203" s="679"/>
+      <c r="H203" s="627"/>
       <c r="I203" s="83"/>
       <c r="J203" s="94">
         <f>+G203/$J$5</f>
@@ -12187,17 +12194,17 @@
     <row r="204" spans="1:20" ht="15.9" customHeight="1">
       <c r="A204" s="66"/>
       <c r="B204" s="91"/>
-      <c r="C204" s="604" t="s">
+      <c r="C204" s="594" t="s">
         <v>222</v>
       </c>
-      <c r="D204" s="611"/>
+      <c r="D204" s="595"/>
       <c r="E204" s="50"/>
       <c r="F204" s="42"/>
       <c r="G204" s="94">
         <f>(G200+G201+G202+G203)*1.18</f>
         <v>37687686.789850324</v>
       </c>
-      <c r="H204" s="679"/>
+      <c r="H204" s="627"/>
       <c r="I204" s="83"/>
       <c r="J204" s="94">
         <f>+J200+J201+J202+J203</f>
@@ -12207,17 +12214,17 @@
     <row r="205" spans="1:20" ht="15.9" customHeight="1">
       <c r="A205" s="66"/>
       <c r="B205" s="91"/>
-      <c r="C205" s="604" t="s">
+      <c r="C205" s="594" t="s">
         <v>223</v>
       </c>
-      <c r="D205" s="611"/>
+      <c r="D205" s="595"/>
       <c r="E205" s="50"/>
       <c r="F205" s="42"/>
       <c r="G205" s="94">
         <f>G204*1%</f>
         <v>376876.86789850326</v>
       </c>
-      <c r="H205" s="679"/>
+      <c r="H205" s="627"/>
       <c r="I205" s="83"/>
       <c r="J205" s="94">
         <f>J204*1%</f>
@@ -12227,17 +12234,17 @@
     <row r="206" spans="1:20" ht="15.9" customHeight="1">
       <c r="A206" s="66"/>
       <c r="B206" s="91"/>
-      <c r="C206" s="610" t="s">
+      <c r="C206" s="596" t="s">
         <v>224</v>
       </c>
-      <c r="D206" s="611"/>
+      <c r="D206" s="595"/>
       <c r="E206" s="50"/>
       <c r="F206" s="42"/>
       <c r="G206" s="94">
         <f>G204*0.5%</f>
         <v>188438.43394925163</v>
       </c>
-      <c r="H206" s="679"/>
+      <c r="H206" s="627"/>
       <c r="I206" s="83"/>
       <c r="J206" s="94">
         <f>J204*0.5%</f>
@@ -12247,17 +12254,17 @@
     <row r="207" spans="1:20" ht="15.9" customHeight="1">
       <c r="A207" s="66"/>
       <c r="B207" s="91"/>
-      <c r="C207" s="606" t="s">
+      <c r="C207" s="597" t="s">
         <v>215</v>
       </c>
-      <c r="D207" s="607"/>
+      <c r="D207" s="598"/>
       <c r="E207" s="50"/>
       <c r="F207" s="42"/>
       <c r="G207" s="94">
         <f>G205+G206</f>
         <v>565315.30184775486</v>
       </c>
-      <c r="H207" s="679"/>
+      <c r="H207" s="627"/>
       <c r="I207" s="83"/>
       <c r="J207" s="94">
         <v>0</v>
@@ -12272,7 +12279,7 @@
       <c r="E208" s="72"/>
       <c r="F208" s="43"/>
       <c r="G208" s="325"/>
-      <c r="H208" s="679"/>
+      <c r="H208" s="627"/>
       <c r="I208" s="86"/>
       <c r="J208" s="73"/>
     </row>
@@ -12294,7 +12301,7 @@
       <c r="G209" s="153" t="s">
         <v>229</v>
       </c>
-      <c r="H209" s="679"/>
+      <c r="H209" s="627"/>
       <c r="I209" s="367" t="s">
         <v>230</v>
       </c>
@@ -12320,7 +12327,7 @@
         <f>'Lease Rent'!P39</f>
         <v>1360000</v>
       </c>
-      <c r="H210" s="679"/>
+      <c r="H210" s="627"/>
       <c r="I210" s="93">
         <f>'Lease Rent'!O39</f>
         <v>1178337.5999999999</v>
@@ -12350,7 +12357,7 @@
         <f>'Lease Rent'!P51</f>
         <v>2040000</v>
       </c>
-      <c r="H211" s="679"/>
+      <c r="H211" s="627"/>
       <c r="I211" s="93">
         <f>'Lease Rent'!O51</f>
         <v>1826423.2800000005</v>
@@ -12379,7 +12386,7 @@
         <f>'Lease Rent'!P63</f>
         <v>2040000</v>
       </c>
-      <c r="H212" s="679"/>
+      <c r="H212" s="627"/>
       <c r="I212" s="93">
         <f>'Lease Rent'!O63</f>
         <v>1917744.4440000001</v>
@@ -12408,7 +12415,7 @@
         <f>'Lease Rent'!P75</f>
         <v>2244000</v>
       </c>
-      <c r="H213" s="679"/>
+      <c r="H213" s="627"/>
       <c r="I213" s="93">
         <f>'Lease Rent'!O75</f>
         <v>2013631.6662000006</v>
@@ -12437,7 +12444,7 @@
         <f>'Lease Rent'!P87</f>
         <v>2345999.9999999995</v>
       </c>
-      <c r="H214" s="679"/>
+      <c r="H214" s="627"/>
       <c r="I214" s="93">
         <f>'Lease Rent'!O87</f>
         <v>2114313.2495100005</v>
@@ -12466,7 +12473,7 @@
         <f>'Lease Rent'!P99</f>
         <v>2345999.9999999995</v>
       </c>
-      <c r="H215" s="679"/>
+      <c r="H215" s="627"/>
       <c r="I215" s="93">
         <f>'Lease Rent'!O99</f>
         <v>2220028.9119855007</v>
@@ -12494,7 +12501,7 @@
         <f>'Lease Rent'!P103</f>
         <v>781999.99999999988</v>
       </c>
-      <c r="H216" s="679"/>
+      <c r="H216" s="627"/>
       <c r="I216" s="93">
         <f>'Lease Rent'!O103</f>
         <v>751945.27664025011</v>
@@ -12517,7 +12524,7 @@
         <f>'Lease Rent'!R10</f>
         <v>0</v>
       </c>
-      <c r="H217" s="679"/>
+      <c r="H217" s="627"/>
       <c r="I217" s="289"/>
       <c r="J217" s="103"/>
     </row>
@@ -12534,7 +12541,7 @@
         <v>0</v>
       </c>
       <c r="G218" s="110"/>
-      <c r="H218" s="679"/>
+      <c r="H218" s="627"/>
       <c r="I218" s="93"/>
       <c r="J218" s="103"/>
     </row>
@@ -12548,7 +12555,7 @@
       <c r="E219" s="109"/>
       <c r="F219" s="220"/>
       <c r="G219" s="110"/>
-      <c r="H219" s="679"/>
+      <c r="H219" s="627"/>
       <c r="I219" s="93"/>
       <c r="J219" s="103"/>
     </row>
@@ -12571,7 +12578,7 @@
         <f>SUM(G210:G219)</f>
         <v>13158000</v>
       </c>
-      <c r="H220" s="680"/>
+      <c r="H220" s="628"/>
       <c r="I220" s="271">
         <f>SUM(I210:I219)</f>
         <v>12022424.428335754</v>
@@ -12641,6 +12648,219 @@
     </row>
   </sheetData>
   <mergeCells count="237">
+    <mergeCell ref="F137:G137"/>
+    <mergeCell ref="I137:J137"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="B134:D134"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="B105:D105"/>
+    <mergeCell ref="C124:D124"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="E163:E164"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="C123:D123"/>
+    <mergeCell ref="C118:D118"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="B156:D156"/>
+    <mergeCell ref="C151:D151"/>
+    <mergeCell ref="C152:D152"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="C145:D145"/>
+    <mergeCell ref="C148:D148"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B1:J3"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="H188:H220"/>
+    <mergeCell ref="C159:D159"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B187:J187"/>
+    <mergeCell ref="C172:D172"/>
+    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="C177:D177"/>
+    <mergeCell ref="C180:D180"/>
+    <mergeCell ref="C157:D157"/>
+    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="C175:D175"/>
+    <mergeCell ref="C149:D149"/>
+    <mergeCell ref="C150:D150"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="C143:D143"/>
+    <mergeCell ref="C184:D184"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C181:D181"/>
+    <mergeCell ref="C185:D185"/>
+    <mergeCell ref="C168:D168"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="C169:D169"/>
+    <mergeCell ref="C183:D183"/>
+    <mergeCell ref="C170:D170"/>
+    <mergeCell ref="C140:D140"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="C122:D122"/>
+    <mergeCell ref="C171:D171"/>
+    <mergeCell ref="C167:D167"/>
+    <mergeCell ref="B147:D147"/>
+    <mergeCell ref="B163:D164"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="C144:D144"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="C166:D166"/>
+    <mergeCell ref="C182:D182"/>
+    <mergeCell ref="C205:D205"/>
+    <mergeCell ref="C206:D206"/>
+    <mergeCell ref="C207:D207"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C174:D174"/>
+    <mergeCell ref="C197:D197"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="C199:D199"/>
+    <mergeCell ref="C200:D200"/>
+    <mergeCell ref="C201:D201"/>
+    <mergeCell ref="C202:D202"/>
+    <mergeCell ref="C188:D188"/>
+    <mergeCell ref="C191:D191"/>
+    <mergeCell ref="C194:D194"/>
+    <mergeCell ref="C195:D195"/>
+    <mergeCell ref="C196:D196"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
     <mergeCell ref="C204:D204"/>
     <mergeCell ref="C203:D203"/>
     <mergeCell ref="C161:D161"/>
@@ -12665,219 +12885,6 @@
     <mergeCell ref="B179:D179"/>
     <mergeCell ref="C162:D162"/>
     <mergeCell ref="C165:D165"/>
-    <mergeCell ref="C205:D205"/>
-    <mergeCell ref="C206:D206"/>
-    <mergeCell ref="C207:D207"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C174:D174"/>
-    <mergeCell ref="C197:D197"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="C199:D199"/>
-    <mergeCell ref="C200:D200"/>
-    <mergeCell ref="C201:D201"/>
-    <mergeCell ref="C202:D202"/>
-    <mergeCell ref="C188:D188"/>
-    <mergeCell ref="C191:D191"/>
-    <mergeCell ref="C194:D194"/>
-    <mergeCell ref="C195:D195"/>
-    <mergeCell ref="C196:D196"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C181:D181"/>
-    <mergeCell ref="C185:D185"/>
-    <mergeCell ref="C168:D168"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="C169:D169"/>
-    <mergeCell ref="C183:D183"/>
-    <mergeCell ref="C170:D170"/>
-    <mergeCell ref="C140:D140"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="C122:D122"/>
-    <mergeCell ref="C171:D171"/>
-    <mergeCell ref="C167:D167"/>
-    <mergeCell ref="B147:D147"/>
-    <mergeCell ref="B163:D164"/>
-    <mergeCell ref="B125:D125"/>
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="C144:D144"/>
-    <mergeCell ref="C139:D139"/>
-    <mergeCell ref="C166:D166"/>
-    <mergeCell ref="C182:D182"/>
-    <mergeCell ref="H188:H220"/>
-    <mergeCell ref="C159:D159"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B187:J187"/>
-    <mergeCell ref="C172:D172"/>
-    <mergeCell ref="C176:D176"/>
-    <mergeCell ref="C177:D177"/>
-    <mergeCell ref="C180:D180"/>
-    <mergeCell ref="C157:D157"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="C175:D175"/>
-    <mergeCell ref="C149:D149"/>
-    <mergeCell ref="C150:D150"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="I58:J58"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="C143:D143"/>
-    <mergeCell ref="C184:D184"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B1:J3"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="E163:E164"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="C123:D123"/>
-    <mergeCell ref="C118:D118"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="B156:D156"/>
-    <mergeCell ref="C151:D151"/>
-    <mergeCell ref="C152:D152"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="C145:D145"/>
-    <mergeCell ref="C148:D148"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="C136:D136"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="B134:D134"/>
-    <mergeCell ref="C106:D106"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="B105:D105"/>
-    <mergeCell ref="C124:D124"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="F137:G137"/>
-    <mergeCell ref="I137:J137"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C131:D131"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="C107:D107"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.25" top="0.75" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="58" orientation="portrait" r:id="rId1"/>
@@ -12950,215 +12957,215 @@
       <c r="S1" s="1"/>
     </row>
     <row r="2" spans="1:27" ht="11.25" customHeight="1">
-      <c r="A2" s="664"/>
-      <c r="B2" s="665"/>
-      <c r="C2" s="665"/>
-      <c r="D2" s="665"/>
-      <c r="E2" s="665"/>
-      <c r="F2" s="665"/>
-      <c r="G2" s="665"/>
-      <c r="H2" s="665"/>
-      <c r="I2" s="665"/>
-      <c r="J2" s="665"/>
-      <c r="K2" s="665"/>
-      <c r="L2" s="665"/>
-      <c r="M2" s="665"/>
-      <c r="N2" s="665"/>
-      <c r="O2" s="665"/>
-      <c r="P2" s="665"/>
-      <c r="Q2" s="665"/>
-      <c r="R2" s="665"/>
-      <c r="S2" s="665"/>
-      <c r="T2" s="665"/>
-      <c r="U2" s="665"/>
-      <c r="V2" s="665"/>
-      <c r="W2" s="665"/>
-      <c r="X2" s="665"/>
-      <c r="Y2" s="665"/>
-      <c r="Z2" s="665"/>
-      <c r="AA2" s="701"/>
+      <c r="A2" s="670"/>
+      <c r="B2" s="671"/>
+      <c r="C2" s="671"/>
+      <c r="D2" s="671"/>
+      <c r="E2" s="671"/>
+      <c r="F2" s="671"/>
+      <c r="G2" s="671"/>
+      <c r="H2" s="671"/>
+      <c r="I2" s="671"/>
+      <c r="J2" s="671"/>
+      <c r="K2" s="671"/>
+      <c r="L2" s="671"/>
+      <c r="M2" s="671"/>
+      <c r="N2" s="671"/>
+      <c r="O2" s="671"/>
+      <c r="P2" s="671"/>
+      <c r="Q2" s="671"/>
+      <c r="R2" s="671"/>
+      <c r="S2" s="671"/>
+      <c r="T2" s="671"/>
+      <c r="U2" s="671"/>
+      <c r="V2" s="671"/>
+      <c r="W2" s="671"/>
+      <c r="X2" s="671"/>
+      <c r="Y2" s="671"/>
+      <c r="Z2" s="671"/>
+      <c r="AA2" s="695"/>
     </row>
     <row r="3" spans="1:27" ht="11.25" customHeight="1">
-      <c r="A3" s="702"/>
-      <c r="B3" s="703"/>
-      <c r="C3" s="703"/>
-      <c r="D3" s="703"/>
-      <c r="E3" s="703"/>
-      <c r="F3" s="703"/>
-      <c r="G3" s="703"/>
-      <c r="H3" s="703"/>
-      <c r="I3" s="703"/>
-      <c r="J3" s="703"/>
-      <c r="K3" s="703"/>
-      <c r="L3" s="703"/>
-      <c r="M3" s="703"/>
-      <c r="N3" s="703"/>
-      <c r="O3" s="703"/>
-      <c r="P3" s="703"/>
-      <c r="Q3" s="703"/>
-      <c r="R3" s="703"/>
-      <c r="S3" s="703"/>
-      <c r="T3" s="703"/>
-      <c r="U3" s="703"/>
-      <c r="V3" s="703"/>
-      <c r="W3" s="703"/>
-      <c r="X3" s="703"/>
-      <c r="Y3" s="703"/>
-      <c r="Z3" s="703"/>
-      <c r="AA3" s="704"/>
+      <c r="A3" s="696"/>
+      <c r="B3" s="697"/>
+      <c r="C3" s="697"/>
+      <c r="D3" s="697"/>
+      <c r="E3" s="697"/>
+      <c r="F3" s="697"/>
+      <c r="G3" s="697"/>
+      <c r="H3" s="697"/>
+      <c r="I3" s="697"/>
+      <c r="J3" s="697"/>
+      <c r="K3" s="697"/>
+      <c r="L3" s="697"/>
+      <c r="M3" s="697"/>
+      <c r="N3" s="697"/>
+      <c r="O3" s="697"/>
+      <c r="P3" s="697"/>
+      <c r="Q3" s="697"/>
+      <c r="R3" s="697"/>
+      <c r="S3" s="697"/>
+      <c r="T3" s="697"/>
+      <c r="U3" s="697"/>
+      <c r="V3" s="697"/>
+      <c r="W3" s="697"/>
+      <c r="X3" s="697"/>
+      <c r="Y3" s="697"/>
+      <c r="Z3" s="697"/>
+      <c r="AA3" s="698"/>
     </row>
     <row r="4" spans="1:27" ht="12" customHeight="1" thickBot="1">
-      <c r="A4" s="705"/>
-      <c r="B4" s="706"/>
-      <c r="C4" s="706"/>
-      <c r="D4" s="706"/>
-      <c r="E4" s="706"/>
-      <c r="F4" s="706"/>
-      <c r="G4" s="706"/>
-      <c r="H4" s="706"/>
-      <c r="I4" s="706"/>
-      <c r="J4" s="706"/>
-      <c r="K4" s="706"/>
-      <c r="L4" s="706"/>
-      <c r="M4" s="706"/>
-      <c r="N4" s="706"/>
-      <c r="O4" s="706"/>
-      <c r="P4" s="706"/>
-      <c r="Q4" s="706"/>
-      <c r="R4" s="706"/>
-      <c r="S4" s="706"/>
-      <c r="T4" s="706"/>
-      <c r="U4" s="706"/>
-      <c r="V4" s="706"/>
-      <c r="W4" s="706"/>
-      <c r="X4" s="706"/>
-      <c r="Y4" s="706"/>
-      <c r="Z4" s="706"/>
-      <c r="AA4" s="707"/>
+      <c r="A4" s="699"/>
+      <c r="B4" s="700"/>
+      <c r="C4" s="700"/>
+      <c r="D4" s="700"/>
+      <c r="E4" s="700"/>
+      <c r="F4" s="700"/>
+      <c r="G4" s="700"/>
+      <c r="H4" s="700"/>
+      <c r="I4" s="700"/>
+      <c r="J4" s="700"/>
+      <c r="K4" s="700"/>
+      <c r="L4" s="700"/>
+      <c r="M4" s="700"/>
+      <c r="N4" s="700"/>
+      <c r="O4" s="700"/>
+      <c r="P4" s="700"/>
+      <c r="Q4" s="700"/>
+      <c r="R4" s="700"/>
+      <c r="S4" s="700"/>
+      <c r="T4" s="700"/>
+      <c r="U4" s="700"/>
+      <c r="V4" s="700"/>
+      <c r="W4" s="700"/>
+      <c r="X4" s="700"/>
+      <c r="Y4" s="700"/>
+      <c r="Z4" s="700"/>
+      <c r="AA4" s="701"/>
     </row>
     <row r="5" spans="1:27" ht="12.75" customHeight="1">
-      <c r="A5" s="664" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="665"/>
-      <c r="C5" s="665"/>
-      <c r="D5" s="665"/>
-      <c r="E5" s="665"/>
-      <c r="F5" s="665"/>
-      <c r="G5" s="665"/>
-      <c r="H5" s="665"/>
-      <c r="I5" s="665"/>
-      <c r="J5" s="665"/>
-      <c r="K5" s="665"/>
-      <c r="L5" s="665"/>
-      <c r="M5" s="665"/>
-      <c r="N5" s="665"/>
-      <c r="O5" s="665"/>
-      <c r="P5" s="665"/>
-      <c r="Q5" s="665"/>
-      <c r="R5" s="665"/>
-      <c r="S5" s="665"/>
-      <c r="T5" s="665"/>
-      <c r="U5" s="665"/>
-      <c r="V5" s="665"/>
-      <c r="W5" s="665"/>
-      <c r="X5" s="665"/>
-      <c r="Y5" s="665"/>
-      <c r="Z5" s="665"/>
-      <c r="AA5" s="701"/>
+      <c r="A5" s="670" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="671"/>
+      <c r="C5" s="671"/>
+      <c r="D5" s="671"/>
+      <c r="E5" s="671"/>
+      <c r="F5" s="671"/>
+      <c r="G5" s="671"/>
+      <c r="H5" s="671"/>
+      <c r="I5" s="671"/>
+      <c r="J5" s="671"/>
+      <c r="K5" s="671"/>
+      <c r="L5" s="671"/>
+      <c r="M5" s="671"/>
+      <c r="N5" s="671"/>
+      <c r="O5" s="671"/>
+      <c r="P5" s="671"/>
+      <c r="Q5" s="671"/>
+      <c r="R5" s="671"/>
+      <c r="S5" s="671"/>
+      <c r="T5" s="671"/>
+      <c r="U5" s="671"/>
+      <c r="V5" s="671"/>
+      <c r="W5" s="671"/>
+      <c r="X5" s="671"/>
+      <c r="Y5" s="671"/>
+      <c r="Z5" s="671"/>
+      <c r="AA5" s="695"/>
     </row>
     <row r="6" spans="1:27" ht="13.5" customHeight="1">
-      <c r="A6" s="708"/>
-      <c r="B6" s="709"/>
-      <c r="C6" s="709"/>
-      <c r="D6" s="709"/>
-      <c r="E6" s="709"/>
-      <c r="F6" s="709"/>
-      <c r="G6" s="709"/>
-      <c r="H6" s="709"/>
-      <c r="I6" s="709"/>
-      <c r="J6" s="709"/>
-      <c r="K6" s="709"/>
-      <c r="L6" s="709"/>
-      <c r="M6" s="709"/>
-      <c r="N6" s="709"/>
-      <c r="O6" s="709"/>
-      <c r="P6" s="709"/>
-      <c r="Q6" s="709"/>
-      <c r="R6" s="709"/>
-      <c r="S6" s="709"/>
-      <c r="T6" s="709"/>
-      <c r="U6" s="709"/>
-      <c r="V6" s="709"/>
-      <c r="W6" s="709"/>
-      <c r="X6" s="709"/>
-      <c r="Y6" s="709"/>
-      <c r="Z6" s="709"/>
-      <c r="AA6" s="710"/>
+      <c r="A6" s="702"/>
+      <c r="B6" s="703"/>
+      <c r="C6" s="703"/>
+      <c r="D6" s="703"/>
+      <c r="E6" s="703"/>
+      <c r="F6" s="703"/>
+      <c r="G6" s="703"/>
+      <c r="H6" s="703"/>
+      <c r="I6" s="703"/>
+      <c r="J6" s="703"/>
+      <c r="K6" s="703"/>
+      <c r="L6" s="703"/>
+      <c r="M6" s="703"/>
+      <c r="N6" s="703"/>
+      <c r="O6" s="703"/>
+      <c r="P6" s="703"/>
+      <c r="Q6" s="703"/>
+      <c r="R6" s="703"/>
+      <c r="S6" s="703"/>
+      <c r="T6" s="703"/>
+      <c r="U6" s="703"/>
+      <c r="V6" s="703"/>
+      <c r="W6" s="703"/>
+      <c r="X6" s="703"/>
+      <c r="Y6" s="703"/>
+      <c r="Z6" s="703"/>
+      <c r="AA6" s="704"/>
     </row>
     <row r="7" spans="1:27" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A7" s="711" t="s">
+      <c r="A7" s="705" t="s">
         <v>292</v>
       </c>
-      <c r="B7" s="712"/>
-      <c r="C7" s="712"/>
-      <c r="D7" s="712"/>
-      <c r="E7" s="712"/>
-      <c r="F7" s="712"/>
-      <c r="G7" s="712"/>
-      <c r="H7" s="712"/>
-      <c r="I7" s="712"/>
-      <c r="J7" s="712"/>
-      <c r="K7" s="712"/>
-      <c r="L7" s="712"/>
-      <c r="M7" s="712"/>
-      <c r="N7" s="712"/>
-      <c r="O7" s="712"/>
-      <c r="P7" s="713"/>
-      <c r="Q7" s="713"/>
-      <c r="R7" s="713"/>
-      <c r="S7" s="713"/>
-      <c r="T7" s="713"/>
-      <c r="U7" s="713"/>
-      <c r="V7" s="713"/>
-      <c r="W7" s="713"/>
-      <c r="X7" s="713"/>
-      <c r="Y7" s="713"/>
-      <c r="Z7" s="713"/>
-      <c r="AA7" s="714"/>
+      <c r="B7" s="706"/>
+      <c r="C7" s="706"/>
+      <c r="D7" s="706"/>
+      <c r="E7" s="706"/>
+      <c r="F7" s="706"/>
+      <c r="G7" s="706"/>
+      <c r="H7" s="706"/>
+      <c r="I7" s="706"/>
+      <c r="J7" s="706"/>
+      <c r="K7" s="706"/>
+      <c r="L7" s="706"/>
+      <c r="M7" s="706"/>
+      <c r="N7" s="706"/>
+      <c r="O7" s="706"/>
+      <c r="P7" s="707"/>
+      <c r="Q7" s="707"/>
+      <c r="R7" s="707"/>
+      <c r="S7" s="707"/>
+      <c r="T7" s="707"/>
+      <c r="U7" s="707"/>
+      <c r="V7" s="707"/>
+      <c r="W7" s="707"/>
+      <c r="X7" s="707"/>
+      <c r="Y7" s="707"/>
+      <c r="Z7" s="707"/>
+      <c r="AA7" s="708"/>
     </row>
     <row r="8" spans="1:27" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A8" s="715" t="s">
+      <c r="A8" s="709" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="716"/>
-      <c r="C8" s="716"/>
-      <c r="D8" s="716"/>
-      <c r="E8" s="716"/>
-      <c r="F8" s="716"/>
-      <c r="G8" s="716"/>
-      <c r="H8" s="716"/>
-      <c r="I8" s="716"/>
-      <c r="J8" s="716"/>
-      <c r="K8" s="716"/>
-      <c r="L8" s="716"/>
-      <c r="M8" s="716"/>
-      <c r="N8" s="717"/>
+      <c r="B8" s="710"/>
+      <c r="C8" s="710"/>
+      <c r="D8" s="710"/>
+      <c r="E8" s="710"/>
+      <c r="F8" s="710"/>
+      <c r="G8" s="710"/>
+      <c r="H8" s="710"/>
+      <c r="I8" s="710"/>
+      <c r="J8" s="710"/>
+      <c r="K8" s="710"/>
+      <c r="L8" s="710"/>
+      <c r="M8" s="710"/>
+      <c r="N8" s="711"/>
       <c r="O8" s="6"/>
-      <c r="P8" s="715" t="s">
+      <c r="P8" s="709" t="s">
         <v>2</v>
       </c>
-      <c r="Q8" s="716"/>
-      <c r="R8" s="716"/>
-      <c r="S8" s="716"/>
-      <c r="T8" s="716"/>
-      <c r="U8" s="716"/>
-      <c r="V8" s="716"/>
-      <c r="W8" s="716"/>
-      <c r="X8" s="716"/>
-      <c r="Y8" s="716"/>
-      <c r="Z8" s="716"/>
-      <c r="AA8" s="718"/>
+      <c r="Q8" s="710"/>
+      <c r="R8" s="710"/>
+      <c r="S8" s="710"/>
+      <c r="T8" s="710"/>
+      <c r="U8" s="710"/>
+      <c r="V8" s="710"/>
+      <c r="W8" s="710"/>
+      <c r="X8" s="710"/>
+      <c r="Y8" s="710"/>
+      <c r="Z8" s="710"/>
+      <c r="AA8" s="712"/>
     </row>
     <row r="9" spans="1:27" s="203" customFormat="1" ht="45.75" customHeight="1">
       <c r="A9" s="204">
@@ -13243,7 +13250,7 @@
       </c>
       <c r="E10" s="8">
         <f>+((+'Rent Calculation'!F43*'Rent Calculation'!F44)/'Rent Calculation'!F23)</f>
-        <v>0</v>
+        <v>12.611665790856541</v>
       </c>
       <c r="F10" s="8">
         <f>+'Rent Calculation'!F41</f>
@@ -13251,7 +13258,7 @@
       </c>
       <c r="G10" s="8">
         <f t="shared" ref="G10:G15" si="0">SUM(B10:F10)</f>
-        <v>135.47999999999999</v>
+        <v>148.09166579085652</v>
       </c>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
@@ -13287,7 +13294,7 @@
       </c>
       <c r="E11" s="9">
         <f>+E10*'Rent Calculation'!F21</f>
-        <v>0</v>
+        <v>119999.99999999999</v>
       </c>
       <c r="F11" s="9">
         <f>F10*'Rent Calculation'!F21</f>
@@ -13295,7 +13302,7 @@
       </c>
       <c r="G11" s="9">
         <f t="shared" si="0"/>
-        <v>1289092.2</v>
+        <v>1409092.2</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
@@ -14720,11 +14727,11 @@
       <c r="R32" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="T32" s="698" t="s">
+      <c r="T32" s="692" t="s">
         <v>53</v>
       </c>
-      <c r="U32" s="699"/>
-      <c r="V32" s="700"/>
+      <c r="U32" s="693"/>
+      <c r="V32" s="694"/>
     </row>
     <row r="33" spans="1:27" ht="10.5">
       <c r="A33" s="36"/>
@@ -14835,8 +14842,8 @@
         <f>+N32+N34</f>
         <v>1.4582436408706672</v>
       </c>
-      <c r="P36" s="697"/>
-      <c r="Q36" s="697"/>
+      <c r="P36" s="691"/>
+      <c r="Q36" s="691"/>
       <c r="T36" s="30" t="s">
         <v>59</v>
       </c>
@@ -16128,10 +16135,10 @@
       </c>
     </row>
     <row r="11" spans="2:21" s="350" customFormat="1" ht="13" hidden="1">
-      <c r="B11" s="719" t="s">
+      <c r="B11" s="713" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="719"/>
+      <c r="C11" s="713"/>
       <c r="D11" s="379">
         <v>42</v>
       </c>
@@ -20595,22 +20602,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="16" thickBot="1">
-      <c r="A1" s="594" t="s">
+      <c r="A1" s="714" t="s">
         <v>252</v>
       </c>
-      <c r="B1" s="595"/>
-      <c r="C1" s="595"/>
-      <c r="D1" s="595"/>
-      <c r="E1" s="595"/>
-      <c r="F1" s="595"/>
-      <c r="G1" s="595"/>
-      <c r="H1" s="595"/>
-      <c r="I1" s="595"/>
-      <c r="J1" s="595"/>
-      <c r="K1" s="595"/>
-      <c r="L1" s="595"/>
-      <c r="M1" s="595"/>
-      <c r="N1" s="595"/>
+      <c r="B1" s="715"/>
+      <c r="C1" s="715"/>
+      <c r="D1" s="715"/>
+      <c r="E1" s="715"/>
+      <c r="F1" s="715"/>
+      <c r="G1" s="715"/>
+      <c r="H1" s="715"/>
+      <c r="I1" s="715"/>
+      <c r="J1" s="715"/>
+      <c r="K1" s="715"/>
+      <c r="L1" s="715"/>
+      <c r="M1" s="715"/>
+      <c r="N1" s="715"/>
       <c r="O1" s="590"/>
     </row>
     <row r="2" spans="1:15">
@@ -21708,21 +21715,21 @@
       <c r="I34" s="346"/>
     </row>
     <row r="35" spans="1:15" ht="16" outlineLevel="1" thickBot="1">
-      <c r="A35" s="594"/>
-      <c r="B35" s="595"/>
-      <c r="C35" s="595"/>
-      <c r="D35" s="595"/>
-      <c r="E35" s="595"/>
-      <c r="F35" s="595"/>
-      <c r="G35" s="595"/>
-      <c r="H35" s="595"/>
-      <c r="I35" s="595"/>
-      <c r="J35" s="595"/>
-      <c r="K35" s="595"/>
-      <c r="L35" s="595"/>
-      <c r="M35" s="595"/>
-      <c r="N35" s="595"/>
-      <c r="O35" s="596"/>
+      <c r="A35" s="714"/>
+      <c r="B35" s="715"/>
+      <c r="C35" s="715"/>
+      <c r="D35" s="715"/>
+      <c r="E35" s="715"/>
+      <c r="F35" s="715"/>
+      <c r="G35" s="715"/>
+      <c r="H35" s="715"/>
+      <c r="I35" s="715"/>
+      <c r="J35" s="715"/>
+      <c r="K35" s="715"/>
+      <c r="L35" s="715"/>
+      <c r="M35" s="715"/>
+      <c r="N35" s="715"/>
+      <c r="O35" s="716"/>
     </row>
     <row r="36" spans="1:15" outlineLevel="1">
       <c r="A36" s="294" t="s">
@@ -23749,21 +23756,21 @@
       <c r="I100" s="175"/>
     </row>
     <row r="101" spans="1:15" ht="16" thickBot="1">
-      <c r="A101" s="597"/>
-      <c r="B101" s="598"/>
-      <c r="C101" s="598"/>
-      <c r="D101" s="598"/>
-      <c r="E101" s="598"/>
-      <c r="F101" s="598"/>
-      <c r="G101" s="598"/>
-      <c r="H101" s="598"/>
-      <c r="I101" s="598"/>
-      <c r="J101" s="598"/>
-      <c r="K101" s="598"/>
-      <c r="L101" s="598"/>
-      <c r="M101" s="598"/>
-      <c r="N101" s="598"/>
-      <c r="O101" s="599"/>
+      <c r="A101" s="717"/>
+      <c r="B101" s="718"/>
+      <c r="C101" s="718"/>
+      <c r="D101" s="718"/>
+      <c r="E101" s="718"/>
+      <c r="F101" s="718"/>
+      <c r="G101" s="718"/>
+      <c r="H101" s="718"/>
+      <c r="I101" s="718"/>
+      <c r="J101" s="718"/>
+      <c r="K101" s="718"/>
+      <c r="L101" s="718"/>
+      <c r="M101" s="718"/>
+      <c r="N101" s="718"/>
+      <c r="O101" s="719"/>
     </row>
     <row r="102" spans="1:15">
       <c r="A102" s="167"/>
@@ -24194,6 +24201,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" xsi:nil="true"/>
+    <Status xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100907921E7373C1341A3C877D189CE8922" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2036b66ca2b7955135caa708c7901a86">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xmlns:ns3="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fed2217af4f675ffeab875e34aa73a78" ns2:_="" ns3:_="">
     <xsd:import namespace="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
@@ -24436,28 +24464,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" xsi:nil="true"/>
-    <Status xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC57694E-BA35-486E-AC74-B7B624F1FDE0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12D5BE44-B07C-4182-BC7A-71E5962390BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
+    <ds:schemaRef ds:uri="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB719E29-C329-4AB1-8ED0-5CC29C0FF757}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24476,25 +24502,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12D5BE44-B07C-4182-BC7A-71E5962390BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
-    <ds:schemaRef ds:uri="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC57694E-BA35-486E-AC74-B7B624F1FDE0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{a59b6cd5-d141-4a33-8bf1-0ca04484304f}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" removed="0"/>

--- a/artifacts/Rental Specimen.xlsx
+++ b/artifacts/Rental Specimen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z0050s8t\Documents\rental-automation\artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C41BAEE-2128-46AE-ABAD-7D42AA97368E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1051DB5E-6430-4095-987A-803B467179E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="764" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5562,81 +5562,276 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="184" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="184" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="184" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="33" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="29" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5657,201 +5852,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="33" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="29" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7489,62 +7489,62 @@
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1">
       <c r="A1" s="43"/>
-      <c r="B1" s="643"/>
-      <c r="C1" s="644"/>
-      <c r="D1" s="644"/>
-      <c r="E1" s="644"/>
-      <c r="F1" s="644"/>
-      <c r="G1" s="644"/>
-      <c r="H1" s="644"/>
-      <c r="I1" s="644"/>
-      <c r="J1" s="645"/>
+      <c r="B1" s="633"/>
+      <c r="C1" s="634"/>
+      <c r="D1" s="634"/>
+      <c r="E1" s="634"/>
+      <c r="F1" s="634"/>
+      <c r="G1" s="634"/>
+      <c r="H1" s="634"/>
+      <c r="I1" s="634"/>
+      <c r="J1" s="635"/>
     </row>
     <row r="2" spans="1:10" ht="14.25" customHeight="1">
       <c r="A2" s="43"/>
-      <c r="B2" s="646"/>
-      <c r="C2" s="647"/>
-      <c r="D2" s="647"/>
-      <c r="E2" s="647"/>
-      <c r="F2" s="647"/>
-      <c r="G2" s="647"/>
-      <c r="H2" s="647"/>
-      <c r="I2" s="647"/>
-      <c r="J2" s="648"/>
+      <c r="B2" s="636"/>
+      <c r="C2" s="637"/>
+      <c r="D2" s="637"/>
+      <c r="E2" s="637"/>
+      <c r="F2" s="637"/>
+      <c r="G2" s="637"/>
+      <c r="H2" s="637"/>
+      <c r="I2" s="637"/>
+      <c r="J2" s="638"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A3" s="43"/>
-      <c r="B3" s="649"/>
-      <c r="C3" s="650"/>
-      <c r="D3" s="650"/>
-      <c r="E3" s="650"/>
-      <c r="F3" s="650"/>
-      <c r="G3" s="650"/>
-      <c r="H3" s="650"/>
-      <c r="I3" s="647"/>
-      <c r="J3" s="648"/>
+      <c r="B3" s="639"/>
+      <c r="C3" s="640"/>
+      <c r="D3" s="640"/>
+      <c r="E3" s="640"/>
+      <c r="F3" s="640"/>
+      <c r="G3" s="640"/>
+      <c r="H3" s="640"/>
+      <c r="I3" s="637"/>
+      <c r="J3" s="638"/>
     </row>
     <row r="4" spans="1:10" ht="13">
       <c r="A4" s="43"/>
-      <c r="B4" s="670"/>
-      <c r="C4" s="671"/>
-      <c r="D4" s="671"/>
-      <c r="E4" s="671"/>
-      <c r="F4" s="671"/>
-      <c r="G4" s="671"/>
+      <c r="B4" s="658"/>
+      <c r="C4" s="659"/>
+      <c r="D4" s="659"/>
+      <c r="E4" s="659"/>
+      <c r="F4" s="659"/>
+      <c r="G4" s="659"/>
       <c r="H4" s="389"/>
       <c r="I4" s="390"/>
       <c r="J4" s="391"/>
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="43"/>
-      <c r="B5" s="672" t="s">
+      <c r="B5" s="660" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="673"/>
-      <c r="D5" s="673"/>
-      <c r="E5" s="673"/>
-      <c r="F5" s="673"/>
-      <c r="G5" s="674"/>
+      <c r="C5" s="661"/>
+      <c r="D5" s="661"/>
+      <c r="E5" s="661"/>
+      <c r="F5" s="661"/>
+      <c r="G5" s="662"/>
       <c r="H5" s="392"/>
       <c r="I5" s="469" t="s">
         <v>16</v>
@@ -7555,29 +7555,29 @@
     </row>
     <row r="6" spans="1:10" ht="13.5" thickBot="1">
       <c r="A6" s="43"/>
-      <c r="B6" s="675"/>
-      <c r="C6" s="676"/>
-      <c r="D6" s="677"/>
+      <c r="B6" s="663"/>
+      <c r="C6" s="664"/>
+      <c r="D6" s="665"/>
       <c r="E6" s="44"/>
-      <c r="F6" s="668">
+      <c r="F6" s="656">
         <v>10.763999999999999</v>
       </c>
-      <c r="G6" s="669"/>
+      <c r="G6" s="657"/>
       <c r="H6" s="393"/>
-      <c r="I6" s="656">
+      <c r="I6" s="647">
         <v>10.763999999999999</v>
       </c>
-      <c r="J6" s="657"/>
+      <c r="J6" s="648"/>
     </row>
     <row r="7" spans="1:10" ht="26">
       <c r="A7" s="43"/>
       <c r="B7" s="470" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="678" t="s">
+      <c r="C7" s="666" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="679"/>
+      <c r="D7" s="667"/>
       <c r="E7" s="471"/>
       <c r="F7" s="471" t="s">
         <v>299</v>
@@ -7605,23 +7605,23 @@
       <c r="C8" s="474"/>
       <c r="D8" s="475"/>
       <c r="E8" s="476"/>
-      <c r="F8" s="602" t="s">
+      <c r="F8" s="594" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="636"/>
+      <c r="G8" s="595"/>
       <c r="H8" s="392"/>
-      <c r="I8" s="637" t="s">
+      <c r="I8" s="596" t="s">
         <v>63</v>
       </c>
-      <c r="J8" s="638"/>
+      <c r="J8" s="597"/>
     </row>
     <row r="9" spans="1:10" ht="13">
       <c r="A9" s="43"/>
-      <c r="B9" s="637" t="s">
+      <c r="B9" s="596" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="636"/>
-      <c r="D9" s="603"/>
+      <c r="C9" s="595"/>
+      <c r="D9" s="611"/>
       <c r="E9" s="477"/>
       <c r="F9" s="364" t="s">
         <v>71</v>
@@ -7642,21 +7642,21 @@
       <c r="B10" s="478">
         <v>1</v>
       </c>
-      <c r="C10" s="651" t="s">
+      <c r="C10" s="641" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="610"/>
+      <c r="D10" s="642"/>
       <c r="E10" s="479"/>
-      <c r="F10" s="662" t="s">
+      <c r="F10" s="653" t="s">
         <v>295</v>
       </c>
-      <c r="G10" s="663"/>
+      <c r="G10" s="654"/>
       <c r="H10" s="392"/>
-      <c r="I10" s="658" t="str">
+      <c r="I10" s="649" t="str">
         <f>+F10</f>
         <v>Chennai</v>
       </c>
-      <c r="J10" s="659"/>
+      <c r="J10" s="650"/>
     </row>
     <row r="11" spans="1:10" ht="28.5" customHeight="1">
       <c r="A11" s="43"/>
@@ -7664,19 +7664,19 @@
         <f>1+B10</f>
         <v>2</v>
       </c>
-      <c r="C11" s="652" t="s">
+      <c r="C11" s="643" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="653"/>
+      <c r="D11" s="644"/>
       <c r="E11" s="42"/>
-      <c r="F11" s="662"/>
-      <c r="G11" s="663"/>
+      <c r="F11" s="653"/>
+      <c r="G11" s="654"/>
       <c r="H11" s="392"/>
-      <c r="I11" s="660">
+      <c r="I11" s="651">
         <f>+F11</f>
         <v>0</v>
       </c>
-      <c r="J11" s="661"/>
+      <c r="J11" s="652"/>
     </row>
     <row r="12" spans="1:10" ht="27.75" customHeight="1">
       <c r="A12" s="43"/>
@@ -7684,19 +7684,19 @@
         <f>1+B11</f>
         <v>3</v>
       </c>
-      <c r="C12" s="596" t="s">
+      <c r="C12" s="604" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="595"/>
+      <c r="D12" s="605"/>
       <c r="E12" s="480"/>
-      <c r="F12" s="664"/>
-      <c r="G12" s="665"/>
+      <c r="F12" s="632"/>
+      <c r="G12" s="627"/>
       <c r="H12" s="392"/>
-      <c r="I12" s="680">
+      <c r="I12" s="628">
         <f>+F12</f>
         <v>0</v>
       </c>
-      <c r="J12" s="681"/>
+      <c r="J12" s="629"/>
     </row>
     <row r="13" spans="1:10" ht="15.9" customHeight="1">
       <c r="A13" s="43"/>
@@ -7704,16 +7704,16 @@
         <f t="shared" ref="B13:B30" si="0">1+B12</f>
         <v>4</v>
       </c>
-      <c r="C13" s="596" t="s">
+      <c r="C13" s="604" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="595"/>
+      <c r="D13" s="605"/>
       <c r="E13" s="42"/>
-      <c r="F13" s="667"/>
-      <c r="G13" s="665"/>
+      <c r="F13" s="626"/>
+      <c r="G13" s="627"/>
       <c r="H13" s="392"/>
-      <c r="I13" s="680"/>
-      <c r="J13" s="681"/>
+      <c r="I13" s="628"/>
+      <c r="J13" s="629"/>
     </row>
     <row r="14" spans="1:10" ht="48" customHeight="1">
       <c r="A14" s="43"/>
@@ -7721,21 +7721,21 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="654" t="s">
+      <c r="C14" s="645" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="655"/>
+      <c r="D14" s="646"/>
       <c r="E14" s="464"/>
-      <c r="F14" s="664" t="s">
+      <c r="F14" s="632" t="s">
         <v>296</v>
       </c>
-      <c r="G14" s="666"/>
+      <c r="G14" s="655"/>
       <c r="H14" s="392"/>
-      <c r="I14" s="680" t="str">
+      <c r="I14" s="628" t="str">
         <f>+F14</f>
         <v>6th floor</v>
       </c>
-      <c r="J14" s="681"/>
+      <c r="J14" s="629"/>
     </row>
     <row r="15" spans="1:10" ht="51.75" customHeight="1">
       <c r="A15" s="43"/>
@@ -7743,19 +7743,19 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="596" t="s">
+      <c r="C15" s="604" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="595"/>
+      <c r="D15" s="605"/>
       <c r="E15" s="50"/>
-      <c r="F15" s="602"/>
-      <c r="G15" s="636"/>
+      <c r="F15" s="594"/>
+      <c r="G15" s="595"/>
       <c r="H15" s="392"/>
-      <c r="I15" s="637">
+      <c r="I15" s="596">
         <f>+F15</f>
         <v>0</v>
       </c>
-      <c r="J15" s="638"/>
+      <c r="J15" s="597"/>
     </row>
     <row r="16" spans="1:10" ht="15.9" customHeight="1">
       <c r="A16" s="43"/>
@@ -7763,16 +7763,16 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="596" t="s">
+      <c r="C16" s="604" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="595"/>
+      <c r="D16" s="605"/>
       <c r="E16" s="50"/>
-      <c r="F16" s="667"/>
-      <c r="G16" s="665"/>
+      <c r="F16" s="626"/>
+      <c r="G16" s="627"/>
       <c r="H16" s="392"/>
-      <c r="I16" s="680"/>
-      <c r="J16" s="681"/>
+      <c r="I16" s="628"/>
+      <c r="J16" s="629"/>
     </row>
     <row r="17" spans="1:10" ht="15.9" customHeight="1">
       <c r="A17" s="43"/>
@@ -7780,21 +7780,21 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="596" t="s">
+      <c r="C17" s="604" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="595"/>
+      <c r="D17" s="605"/>
       <c r="E17" s="50"/>
-      <c r="F17" s="664" t="s">
+      <c r="F17" s="632" t="s">
         <v>81</v>
       </c>
-      <c r="G17" s="665"/>
+      <c r="G17" s="627"/>
       <c r="H17" s="392"/>
-      <c r="I17" s="680" t="str">
+      <c r="I17" s="628" t="str">
         <f>+F17</f>
         <v>Warm Shell</v>
       </c>
-      <c r="J17" s="681"/>
+      <c r="J17" s="629"/>
     </row>
     <row r="18" spans="1:10" ht="48" customHeight="1">
       <c r="A18" s="43"/>
@@ -7802,22 +7802,22 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="596" t="s">
+      <c r="C18" s="604" t="s">
         <v>82</v>
       </c>
-      <c r="D18" s="595"/>
+      <c r="D18" s="605"/>
       <c r="E18" s="155"/>
-      <c r="F18" s="602">
+      <c r="F18" s="594">
         <f>F15</f>
         <v>0</v>
       </c>
-      <c r="G18" s="636"/>
+      <c r="G18" s="595"/>
       <c r="H18" s="392"/>
-      <c r="I18" s="637">
+      <c r="I18" s="596">
         <f>+F18</f>
         <v>0</v>
       </c>
-      <c r="J18" s="638"/>
+      <c r="J18" s="597"/>
     </row>
     <row r="19" spans="1:10" ht="15.9" customHeight="1">
       <c r="A19" s="43"/>
@@ -7825,16 +7825,16 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="596" t="s">
+      <c r="C19" s="604" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="595"/>
+      <c r="D19" s="605"/>
       <c r="E19" s="155"/>
-      <c r="F19" s="667"/>
-      <c r="G19" s="665"/>
+      <c r="F19" s="626"/>
+      <c r="G19" s="627"/>
       <c r="H19" s="392"/>
-      <c r="I19" s="680"/>
-      <c r="J19" s="681"/>
+      <c r="I19" s="628"/>
+      <c r="J19" s="629"/>
     </row>
     <row r="20" spans="1:10" ht="15.9" customHeight="1">
       <c r="A20" s="43"/>
@@ -7842,10 +7842,10 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="594" t="s">
+      <c r="C20" s="598" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="595"/>
+      <c r="D20" s="605"/>
       <c r="E20" s="482"/>
       <c r="F20" s="48"/>
       <c r="G20" s="376"/>
@@ -7865,10 +7865,10 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="596" t="s">
+      <c r="C21" s="604" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="595"/>
+      <c r="D21" s="605"/>
       <c r="E21" s="482"/>
       <c r="F21" s="48">
         <f>Main!B3</f>
@@ -7894,10 +7894,10 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="594" t="s">
+      <c r="C22" s="598" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="595"/>
+      <c r="D22" s="605"/>
       <c r="E22" s="482"/>
       <c r="F22" s="48">
         <v>0</v>
@@ -7921,10 +7921,10 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="596" t="s">
+      <c r="C23" s="604" t="s">
         <v>87</v>
       </c>
-      <c r="D23" s="595"/>
+      <c r="D23" s="605"/>
       <c r="E23" s="482"/>
       <c r="F23" s="48">
         <f>+F21+F22</f>
@@ -7950,10 +7950,10 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="596" t="s">
+      <c r="C24" s="604" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="595"/>
+      <c r="D24" s="605"/>
       <c r="E24" s="51"/>
       <c r="F24" s="48"/>
       <c r="G24" s="376">
@@ -7976,10 +7976,10 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="596" t="s">
+      <c r="C25" s="604" t="s">
         <v>89</v>
       </c>
-      <c r="D25" s="595"/>
+      <c r="D25" s="605"/>
       <c r="E25" s="51"/>
       <c r="F25" s="48">
         <v>0</v>
@@ -8004,10 +8004,10 @@
         <f>1+B25</f>
         <v>17</v>
       </c>
-      <c r="C26" s="596" t="s">
+      <c r="C26" s="604" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="595"/>
+      <c r="D26" s="605"/>
       <c r="E26" s="52"/>
       <c r="F26" s="53">
         <f>F25/F23</f>
@@ -8033,10 +8033,10 @@
         <f>1+B26</f>
         <v>18</v>
       </c>
-      <c r="C27" s="594" t="s">
+      <c r="C27" s="598" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="595"/>
+      <c r="D27" s="605"/>
       <c r="E27" s="50"/>
       <c r="F27" s="281">
         <f>'CAPEX and PM'!E3</f>
@@ -8062,10 +8062,10 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="594" t="s">
+      <c r="C28" s="598" t="s">
         <v>92</v>
       </c>
-      <c r="D28" s="595"/>
+      <c r="D28" s="605"/>
       <c r="E28" s="56"/>
       <c r="F28" s="56">
         <f>Main!B12</f>
@@ -8091,10 +8091,10 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="594" t="s">
+      <c r="C29" s="598" t="s">
         <v>93</v>
       </c>
-      <c r="D29" s="595"/>
+      <c r="D29" s="605"/>
       <c r="E29" s="56"/>
       <c r="F29" s="52">
         <f>Main!B13</f>
@@ -8120,10 +8120,10 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="596" t="s">
+      <c r="C30" s="604" t="s">
         <v>94</v>
       </c>
-      <c r="D30" s="595"/>
+      <c r="D30" s="605"/>
       <c r="E30" s="50"/>
       <c r="F30" s="48">
         <v>0</v>
@@ -8144,11 +8144,11 @@
     </row>
     <row r="31" spans="1:10" ht="15.9" customHeight="1">
       <c r="A31" s="43"/>
-      <c r="B31" s="682" t="s">
+      <c r="B31" s="623" t="s">
         <v>95</v>
       </c>
-      <c r="C31" s="683"/>
-      <c r="D31" s="684"/>
+      <c r="C31" s="624"/>
+      <c r="D31" s="625"/>
       <c r="E31" s="485"/>
       <c r="F31" s="364" t="s">
         <v>71</v>
@@ -8169,10 +8169,10 @@
       <c r="B32" s="154">
         <v>1</v>
       </c>
-      <c r="C32" s="594" t="s">
+      <c r="C32" s="598" t="s">
         <v>96</v>
       </c>
-      <c r="D32" s="595"/>
+      <c r="D32" s="605"/>
       <c r="E32" s="51"/>
       <c r="F32" s="48">
         <f>Main!B9/(Main!B3*Main!B7)</f>
@@ -8198,10 +8198,10 @@
         <f>1+B32</f>
         <v>2</v>
       </c>
-      <c r="C33" s="594" t="s">
+      <c r="C33" s="598" t="s">
         <v>97</v>
       </c>
-      <c r="D33" s="595"/>
+      <c r="D33" s="605"/>
       <c r="E33" s="51"/>
       <c r="F33" s="48">
         <v>0</v>
@@ -8225,10 +8225,10 @@
         <f t="shared" ref="B34:B47" si="1">1+B33</f>
         <v>3</v>
       </c>
-      <c r="C34" s="594" t="s">
+      <c r="C34" s="598" t="s">
         <v>98</v>
       </c>
-      <c r="D34" s="595"/>
+      <c r="D34" s="605"/>
       <c r="E34" s="51"/>
       <c r="F34" s="48">
         <v>0</v>
@@ -8253,10 +8253,10 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="C35" s="596" t="s">
+      <c r="C35" s="604" t="s">
         <v>99</v>
       </c>
-      <c r="D35" s="595"/>
+      <c r="D35" s="605"/>
       <c r="E35" s="486"/>
       <c r="F35" s="60">
         <v>0</v>
@@ -8278,10 +8278,10 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="C36" s="594" t="s">
+      <c r="C36" s="598" t="s">
         <v>100</v>
       </c>
-      <c r="D36" s="595"/>
+      <c r="D36" s="605"/>
       <c r="E36" s="486"/>
       <c r="F36" s="62">
         <f>'Lease Rent'!H37</f>
@@ -8307,10 +8307,10 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="C37" s="594" t="s">
+      <c r="C37" s="598" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="595"/>
+      <c r="D37" s="605"/>
       <c r="E37" s="486"/>
       <c r="F37" s="62"/>
       <c r="G37" s="192">
@@ -8327,10 +8327,10 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="C38" s="594" t="s">
+      <c r="C38" s="598" t="s">
         <v>102</v>
       </c>
-      <c r="D38" s="595"/>
+      <c r="D38" s="605"/>
       <c r="E38" s="63"/>
       <c r="F38" s="62">
         <f>'Lease Rent'!J31</f>
@@ -8356,10 +8356,10 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="C39" s="594" t="s">
+      <c r="C39" s="598" t="s">
         <v>103</v>
       </c>
-      <c r="D39" s="595"/>
+      <c r="D39" s="605"/>
       <c r="E39" s="486"/>
       <c r="F39" s="62">
         <f>F36</f>
@@ -8385,10 +8385,10 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="C40" s="594" t="s">
+      <c r="C40" s="598" t="s">
         <v>104</v>
       </c>
-      <c r="D40" s="595"/>
+      <c r="D40" s="605"/>
       <c r="E40" s="486"/>
       <c r="F40" s="62">
         <v>0</v>
@@ -8413,10 +8413,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="C41" s="594" t="s">
+      <c r="C41" s="598" t="s">
         <v>105</v>
       </c>
-      <c r="D41" s="595"/>
+      <c r="D41" s="605"/>
       <c r="E41" s="50"/>
       <c r="F41" s="106">
         <f>F38</f>
@@ -8442,10 +8442,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="C42" s="596" t="s">
+      <c r="C42" s="604" t="s">
         <v>106</v>
       </c>
-      <c r="D42" s="595"/>
+      <c r="D42" s="605"/>
       <c r="E42" s="51"/>
       <c r="F42" s="101">
         <v>0</v>
@@ -8470,10 +8470,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="C43" s="596" t="s">
+      <c r="C43" s="604" t="s">
         <v>107</v>
       </c>
-      <c r="D43" s="595"/>
+      <c r="D43" s="605"/>
       <c r="E43" s="65"/>
       <c r="F43" s="60">
         <f>'Lease Rent'!D22</f>
@@ -8499,10 +8499,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="C44" s="596" t="s">
+      <c r="C44" s="604" t="s">
         <v>108</v>
       </c>
-      <c r="D44" s="595"/>
+      <c r="D44" s="605"/>
       <c r="E44" s="51"/>
       <c r="F44" s="48">
         <f>'Lease Rent'!C22</f>
@@ -8528,10 +8528,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="C45" s="594" t="s">
+      <c r="C45" s="598" t="s">
         <v>109</v>
       </c>
-      <c r="D45" s="595"/>
+      <c r="D45" s="605"/>
       <c r="E45" s="51"/>
       <c r="F45" s="101">
         <v>0</v>
@@ -8553,10 +8553,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="C46" s="596" t="s">
+      <c r="C46" s="604" t="s">
         <v>331</v>
       </c>
-      <c r="D46" s="595"/>
+      <c r="D46" s="605"/>
       <c r="E46" s="51"/>
       <c r="F46" s="48">
         <f>'Lease Rent'!D23</f>
@@ -8573,10 +8573,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="C47" s="596" t="s">
+      <c r="C47" s="604" t="s">
         <v>332</v>
       </c>
-      <c r="D47" s="595"/>
+      <c r="D47" s="605"/>
       <c r="E47" s="51"/>
       <c r="F47" s="48">
         <f>'Lease Rent'!C23</f>
@@ -8589,46 +8589,46 @@
     </row>
     <row r="48" spans="1:10" ht="28.5" customHeight="1">
       <c r="A48" s="43"/>
-      <c r="B48" s="641">
+      <c r="B48" s="670">
         <f>1+B47</f>
         <v>17</v>
       </c>
-      <c r="C48" s="594" t="s">
+      <c r="C48" s="598" t="s">
         <v>110</v>
       </c>
-      <c r="D48" s="595"/>
+      <c r="D48" s="605"/>
       <c r="E48" s="65"/>
-      <c r="F48" s="687" t="str">
+      <c r="F48" s="614" t="str">
         <f>Main!B14</f>
         <v>15% every 3 years</v>
       </c>
-      <c r="G48" s="688"/>
+      <c r="G48" s="615"/>
       <c r="H48" s="392"/>
-      <c r="I48" s="680" t="str">
+      <c r="I48" s="628" t="str">
         <f>+F48</f>
         <v>15% every 3 years</v>
       </c>
-      <c r="J48" s="681"/>
+      <c r="J48" s="629"/>
     </row>
     <row r="49" spans="1:18" ht="15.9" customHeight="1">
       <c r="A49" s="43"/>
-      <c r="B49" s="642"/>
-      <c r="C49" s="594" t="s">
+      <c r="B49" s="671"/>
+      <c r="C49" s="598" t="s">
         <v>111</v>
       </c>
-      <c r="D49" s="595"/>
+      <c r="D49" s="605"/>
       <c r="E49" s="65"/>
-      <c r="F49" s="687" t="str">
+      <c r="F49" s="614" t="str">
         <f>Main!B15</f>
         <v>5% every years</v>
       </c>
-      <c r="G49" s="688"/>
+      <c r="G49" s="615"/>
       <c r="H49" s="392"/>
-      <c r="I49" s="685" t="str">
+      <c r="I49" s="630" t="str">
         <f t="shared" ref="I49:I56" si="2">F49</f>
         <v>5% every years</v>
       </c>
-      <c r="J49" s="686"/>
+      <c r="J49" s="631"/>
     </row>
     <row r="50" spans="1:18" ht="15.9" customHeight="1">
       <c r="A50" s="43"/>
@@ -8636,22 +8636,22 @@
         <f>1+B48</f>
         <v>18</v>
       </c>
-      <c r="C50" s="596" t="s">
+      <c r="C50" s="604" t="s">
         <v>112</v>
       </c>
-      <c r="D50" s="595"/>
+      <c r="D50" s="605"/>
       <c r="E50" s="65"/>
-      <c r="F50" s="632">
+      <c r="F50" s="612">
         <f>'Lease Rent'!B31</f>
         <v>46023</v>
       </c>
-      <c r="G50" s="633"/>
+      <c r="G50" s="613"/>
       <c r="H50" s="392"/>
-      <c r="I50" s="634">
+      <c r="I50" s="621">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J50" s="635"/>
+      <c r="J50" s="622"/>
     </row>
     <row r="51" spans="1:18" ht="15.9" customHeight="1">
       <c r="A51" s="43"/>
@@ -8659,22 +8659,22 @@
         <f t="shared" ref="B51:B57" si="3">1+B50</f>
         <v>19</v>
       </c>
-      <c r="C51" s="594" t="s">
+      <c r="C51" s="598" t="s">
         <v>113</v>
       </c>
-      <c r="D51" s="595"/>
+      <c r="D51" s="605"/>
       <c r="E51" s="65"/>
-      <c r="F51" s="632">
+      <c r="F51" s="612">
         <f>'Lease Rent'!C102</f>
         <v>48213</v>
       </c>
-      <c r="G51" s="633"/>
+      <c r="G51" s="613"/>
       <c r="H51" s="392"/>
-      <c r="I51" s="634">
+      <c r="I51" s="621">
         <f>F51</f>
         <v>48213</v>
       </c>
-      <c r="J51" s="635"/>
+      <c r="J51" s="622"/>
     </row>
     <row r="52" spans="1:18" ht="15.9" customHeight="1">
       <c r="A52" s="43"/>
@@ -8682,22 +8682,22 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="C52" s="594" t="s">
+      <c r="C52" s="598" t="s">
         <v>114</v>
       </c>
-      <c r="D52" s="604"/>
+      <c r="D52" s="599"/>
       <c r="E52" s="65"/>
-      <c r="F52" s="632">
+      <c r="F52" s="612">
         <f>F50</f>
         <v>46023</v>
       </c>
-      <c r="G52" s="633"/>
+      <c r="G52" s="613"/>
       <c r="H52" s="392"/>
-      <c r="I52" s="634">
+      <c r="I52" s="621">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J52" s="635"/>
+      <c r="J52" s="622"/>
     </row>
     <row r="53" spans="1:18" ht="15.9" customHeight="1">
       <c r="A53" s="43"/>
@@ -8705,21 +8705,21 @@
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="C53" s="594" t="s">
+      <c r="C53" s="598" t="s">
         <v>115</v>
       </c>
-      <c r="D53" s="604"/>
+      <c r="D53" s="599"/>
       <c r="E53" s="65"/>
-      <c r="F53" s="602">
-        <v>0</v>
-      </c>
-      <c r="G53" s="636"/>
+      <c r="F53" s="594">
+        <v>0</v>
+      </c>
+      <c r="G53" s="595"/>
       <c r="H53" s="392"/>
-      <c r="I53" s="637">
+      <c r="I53" s="596">
         <f>+F53</f>
         <v>0</v>
       </c>
-      <c r="J53" s="638"/>
+      <c r="J53" s="597"/>
     </row>
     <row r="54" spans="1:18" ht="15.9" customHeight="1">
       <c r="A54" s="43"/>
@@ -8727,10 +8727,10 @@
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="C54" s="596" t="s">
+      <c r="C54" s="604" t="s">
         <v>116</v>
       </c>
-      <c r="D54" s="595"/>
+      <c r="D54" s="605"/>
       <c r="E54" s="50"/>
       <c r="F54" s="48">
         <f>(F51-F50)/365*12</f>
@@ -8757,10 +8757,10 @@
         <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="C55" s="596" t="s">
+      <c r="C55" s="604" t="s">
         <v>117</v>
       </c>
-      <c r="D55" s="595"/>
+      <c r="D55" s="605"/>
       <c r="E55" s="63"/>
       <c r="F55" s="48">
         <v>0</v>
@@ -8786,10 +8786,10 @@
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="C56" s="596" t="s">
+      <c r="C56" s="604" t="s">
         <v>118</v>
       </c>
-      <c r="D56" s="595"/>
+      <c r="D56" s="605"/>
       <c r="E56" s="63"/>
       <c r="F56" s="290" t="s">
         <v>64</v>
@@ -8815,10 +8815,10 @@
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="C57" s="596" t="s">
+      <c r="C57" s="604" t="s">
         <v>119</v>
       </c>
-      <c r="D57" s="595"/>
+      <c r="D57" s="605"/>
       <c r="E57" s="63"/>
       <c r="F57" s="48"/>
       <c r="G57" s="376"/>
@@ -8833,23 +8833,23 @@
       <c r="C58" s="66"/>
       <c r="D58" s="66"/>
       <c r="E58" s="50"/>
-      <c r="F58" s="602" t="s">
+      <c r="F58" s="594" t="s">
         <v>69</v>
       </c>
-      <c r="G58" s="636"/>
+      <c r="G58" s="595"/>
       <c r="H58" s="392"/>
-      <c r="I58" s="637" t="s">
+      <c r="I58" s="596" t="s">
         <v>63</v>
       </c>
-      <c r="J58" s="638"/>
+      <c r="J58" s="597"/>
     </row>
     <row r="59" spans="1:18" ht="15.9" customHeight="1">
       <c r="A59" s="43"/>
-      <c r="B59" s="639" t="s">
+      <c r="B59" s="668" t="s">
         <v>120</v>
       </c>
-      <c r="C59" s="640"/>
-      <c r="D59" s="640"/>
+      <c r="C59" s="669"/>
+      <c r="D59" s="669"/>
       <c r="E59" s="485"/>
       <c r="F59" s="364" t="s">
         <v>71</v>
@@ -8870,10 +8870,10 @@
       <c r="B60" s="154">
         <v>1</v>
       </c>
-      <c r="C60" s="594" t="s">
+      <c r="C60" s="598" t="s">
         <v>121</v>
       </c>
-      <c r="D60" s="595"/>
+      <c r="D60" s="605"/>
       <c r="E60" s="487"/>
       <c r="F60" s="62">
         <f>C220/F21/F54</f>
@@ -8899,10 +8899,10 @@
         <f>1+B60</f>
         <v>2</v>
       </c>
-      <c r="C61" s="594" t="s">
+      <c r="C61" s="598" t="s">
         <v>122</v>
       </c>
-      <c r="D61" s="595"/>
+      <c r="D61" s="605"/>
       <c r="E61" s="487"/>
       <c r="F61" s="62">
         <v>0</v>
@@ -8926,10 +8926,10 @@
         <f t="shared" ref="B62:B83" si="4">1+B61</f>
         <v>3</v>
       </c>
-      <c r="C62" s="597" t="s">
+      <c r="C62" s="600" t="s">
         <v>123</v>
       </c>
-      <c r="D62" s="598"/>
+      <c r="D62" s="601"/>
       <c r="E62" s="67"/>
       <c r="F62" s="68">
         <f>F60+F61</f>
@@ -8955,10 +8955,10 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="C63" s="594" t="s">
+      <c r="C63" s="598" t="s">
         <v>317</v>
       </c>
-      <c r="D63" s="595"/>
+      <c r="D63" s="605"/>
       <c r="E63" s="48"/>
       <c r="F63" s="46">
         <f>F62*F21</f>
@@ -8984,10 +8984,10 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="C64" s="594" t="s">
+      <c r="C64" s="598" t="s">
         <v>124</v>
       </c>
-      <c r="D64" s="595"/>
+      <c r="D64" s="605"/>
       <c r="E64" s="48"/>
       <c r="F64" s="62">
         <f>I220/F21/F54</f>
@@ -9013,10 +9013,10 @@
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="C65" s="596" t="s">
+      <c r="C65" s="604" t="s">
         <v>318</v>
       </c>
-      <c r="D65" s="595"/>
+      <c r="D65" s="605"/>
       <c r="E65" s="63"/>
       <c r="F65" s="46">
         <f>+F64*F21</f>
@@ -9042,10 +9042,10 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="C66" s="596" t="s">
+      <c r="C66" s="604" t="s">
         <v>319</v>
       </c>
-      <c r="D66" s="595"/>
+      <c r="D66" s="605"/>
       <c r="E66" s="51"/>
       <c r="F66" s="48">
         <f>(+G220/F54)</f>
@@ -9071,10 +9071,10 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="C67" s="596" t="s">
+      <c r="C67" s="604" t="s">
         <v>125</v>
       </c>
-      <c r="D67" s="595"/>
+      <c r="D67" s="605"/>
       <c r="E67" s="48"/>
       <c r="F67" s="48">
         <f>Main!B9</f>
@@ -9100,10 +9100,10 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="C68" s="596" t="s">
+      <c r="C68" s="604" t="s">
         <v>126</v>
       </c>
-      <c r="D68" s="595"/>
+      <c r="D68" s="605"/>
       <c r="E68" s="48"/>
       <c r="F68" s="48">
         <v>0</v>
@@ -9128,10 +9128,10 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="C69" s="594" t="s">
+      <c r="C69" s="598" t="s">
         <v>127</v>
       </c>
-      <c r="D69" s="595"/>
+      <c r="D69" s="605"/>
       <c r="E69" s="48"/>
       <c r="F69" s="48">
         <v>500000</v>
@@ -9156,10 +9156,10 @@
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="C70" s="596" t="s">
+      <c r="C70" s="604" t="s">
         <v>128</v>
       </c>
-      <c r="D70" s="595"/>
+      <c r="D70" s="605"/>
       <c r="E70" s="48"/>
       <c r="F70" s="46">
         <v>0</v>
@@ -9181,10 +9181,10 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="C71" s="596" t="s">
+      <c r="C71" s="604" t="s">
         <v>129</v>
       </c>
-      <c r="D71" s="595"/>
+      <c r="D71" s="605"/>
       <c r="E71" s="48"/>
       <c r="F71" s="46">
         <f>F38*F23*F33</f>
@@ -9210,10 +9210,10 @@
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="C72" s="596" t="s">
+      <c r="C72" s="604" t="s">
         <v>130</v>
       </c>
-      <c r="D72" s="595"/>
+      <c r="D72" s="605"/>
       <c r="E72" s="48"/>
       <c r="F72" s="48">
         <v>0</v>
@@ -9238,10 +9238,10 @@
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="C73" s="594" t="s">
+      <c r="C73" s="598" t="s">
         <v>131</v>
       </c>
-      <c r="D73" s="595"/>
+      <c r="D73" s="605"/>
       <c r="E73" s="486"/>
       <c r="F73" s="60">
         <f>+F35*F63</f>
@@ -9295,10 +9295,10 @@
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="C75" s="594" t="s">
+      <c r="C75" s="598" t="s">
         <v>133</v>
       </c>
-      <c r="D75" s="595"/>
+      <c r="D75" s="605"/>
       <c r="E75" s="51"/>
       <c r="F75" s="48">
         <f>+F77/F23</f>
@@ -9324,10 +9324,10 @@
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="C76" s="594" t="s">
+      <c r="C76" s="598" t="s">
         <v>134</v>
       </c>
-      <c r="D76" s="595"/>
+      <c r="D76" s="605"/>
       <c r="E76" s="63"/>
       <c r="F76" s="43"/>
       <c r="G76" s="481"/>
@@ -9347,10 +9347,10 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="C77" s="594" t="s">
+      <c r="C77" s="598" t="s">
         <v>135</v>
       </c>
-      <c r="D77" s="595"/>
+      <c r="D77" s="605"/>
       <c r="E77" s="63"/>
       <c r="F77" s="48">
         <f>'CAPEX and PM'!B6</f>
@@ -9376,10 +9376,10 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="C78" s="594" t="s">
+      <c r="C78" s="598" t="s">
         <v>136</v>
       </c>
-      <c r="D78" s="595"/>
+      <c r="D78" s="605"/>
       <c r="E78" s="63"/>
       <c r="F78" s="48">
         <f>'CAPEX and PM'!B37</f>
@@ -9405,10 +9405,10 @@
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="C79" s="594" t="s">
+      <c r="C79" s="598" t="s">
         <v>137</v>
       </c>
-      <c r="D79" s="595"/>
+      <c r="D79" s="605"/>
       <c r="E79" s="63"/>
       <c r="F79" s="48">
         <f>+'CAPEX and PM'!B104</f>
@@ -9434,10 +9434,10 @@
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="C80" s="594" t="s">
+      <c r="C80" s="598" t="s">
         <v>138</v>
       </c>
-      <c r="D80" s="595"/>
+      <c r="D80" s="605"/>
       <c r="E80" s="63"/>
       <c r="F80" s="48"/>
       <c r="G80" s="376"/>
@@ -9457,10 +9457,10 @@
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="C81" s="594" t="s">
+      <c r="C81" s="598" t="s">
         <v>139</v>
       </c>
-      <c r="D81" s="604"/>
+      <c r="D81" s="599"/>
       <c r="E81" s="63"/>
       <c r="F81" s="48"/>
       <c r="G81" s="376"/>
@@ -9480,10 +9480,10 @@
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="C82" s="594" t="s">
+      <c r="C82" s="598" t="s">
         <v>140</v>
       </c>
-      <c r="D82" s="595"/>
+      <c r="D82" s="605"/>
       <c r="E82" s="51"/>
       <c r="F82" s="48">
         <f>+G207</f>
@@ -9509,10 +9509,10 @@
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="C83" s="594" t="s">
+      <c r="C83" s="598" t="s">
         <v>320</v>
       </c>
-      <c r="D83" s="595"/>
+      <c r="D83" s="605"/>
       <c r="E83" s="486"/>
       <c r="F83" s="48">
         <f>+F30</f>
@@ -9545,11 +9545,11 @@
     </row>
     <row r="85" spans="1:24" ht="15.9" customHeight="1">
       <c r="A85" s="43"/>
-      <c r="B85" s="616" t="s">
+      <c r="B85" s="606" t="s">
         <v>141</v>
       </c>
-      <c r="C85" s="617"/>
-      <c r="D85" s="618"/>
+      <c r="C85" s="607"/>
+      <c r="D85" s="608"/>
       <c r="E85" s="377"/>
       <c r="F85" s="153" t="s">
         <v>71</v>
@@ -9570,10 +9570,10 @@
       <c r="B86" s="154">
         <v>1</v>
       </c>
-      <c r="C86" s="594" t="s">
+      <c r="C86" s="598" t="s">
         <v>142</v>
       </c>
-      <c r="D86" s="595"/>
+      <c r="D86" s="605"/>
       <c r="E86" s="63"/>
       <c r="F86" s="62">
         <f>+F62</f>
@@ -9602,10 +9602,10 @@
         <f>1+B86</f>
         <v>2</v>
       </c>
-      <c r="C87" s="596" t="s">
+      <c r="C87" s="604" t="s">
         <v>143</v>
       </c>
-      <c r="D87" s="595"/>
+      <c r="D87" s="605"/>
       <c r="E87" s="65"/>
       <c r="F87" s="48">
         <v>0</v>
@@ -9628,10 +9628,10 @@
         <f t="shared" ref="B88:B94" si="7">+B87+1</f>
         <v>3</v>
       </c>
-      <c r="C88" s="596" t="s">
+      <c r="C88" s="604" t="s">
         <v>144</v>
       </c>
-      <c r="D88" s="595"/>
+      <c r="D88" s="605"/>
       <c r="E88" s="65"/>
       <c r="F88" s="62">
         <f>(F66/F23)</f>
@@ -9659,10 +9659,10 @@
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="C89" s="596" t="s">
+      <c r="C89" s="604" t="s">
         <v>145</v>
       </c>
-      <c r="D89" s="595"/>
+      <c r="D89" s="605"/>
       <c r="E89" s="65"/>
       <c r="F89" s="58">
         <f>'Security Deposit'!C17</f>
@@ -9690,10 +9690,10 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="C90" s="596" t="s">
+      <c r="C90" s="604" t="s">
         <v>285</v>
       </c>
-      <c r="D90" s="595"/>
+      <c r="D90" s="605"/>
       <c r="E90" s="65"/>
       <c r="F90" s="190">
         <f>+F64</f>
@@ -9721,10 +9721,10 @@
         <f>+B89+1</f>
         <v>5</v>
       </c>
-      <c r="C91" s="596" t="s">
+      <c r="C91" s="604" t="s">
         <v>146</v>
       </c>
-      <c r="D91" s="595"/>
+      <c r="D91" s="605"/>
       <c r="E91" s="65"/>
       <c r="F91" s="58">
         <f>(+F83/F21/F54)</f>
@@ -9751,10 +9751,10 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="C92" s="596" t="s">
+      <c r="C92" s="604" t="s">
         <v>147</v>
       </c>
-      <c r="D92" s="595"/>
+      <c r="D92" s="605"/>
       <c r="E92" s="65"/>
       <c r="F92" s="58">
         <f>F82/F21/F54</f>
@@ -9782,10 +9782,10 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="C93" s="594" t="s">
+      <c r="C93" s="598" t="s">
         <v>148</v>
       </c>
-      <c r="D93" s="595"/>
+      <c r="D93" s="605"/>
       <c r="E93" s="63"/>
       <c r="F93" s="58">
         <f>+G93/F6</f>
@@ -9813,10 +9813,10 @@
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="C94" s="597" t="s">
+      <c r="C94" s="600" t="s">
         <v>65</v>
       </c>
-      <c r="D94" s="598"/>
+      <c r="D94" s="601"/>
       <c r="E94" s="70"/>
       <c r="F94" s="201">
         <f>SUM(F86:F93)</f>
@@ -9841,8 +9841,8 @@
     <row r="95" spans="1:24" ht="15.9" customHeight="1">
       <c r="A95" s="43"/>
       <c r="B95" s="369"/>
-      <c r="C95" s="636"/>
-      <c r="D95" s="636"/>
+      <c r="C95" s="595"/>
+      <c r="D95" s="595"/>
       <c r="E95" s="76"/>
       <c r="F95" s="77"/>
       <c r="G95" s="77"/>
@@ -9852,11 +9852,11 @@
     </row>
     <row r="96" spans="1:24" ht="15.9" customHeight="1">
       <c r="A96" s="43"/>
-      <c r="B96" s="599" t="s">
+      <c r="B96" s="602" t="s">
         <v>149</v>
       </c>
-      <c r="C96" s="600"/>
-      <c r="D96" s="600"/>
+      <c r="C96" s="603"/>
+      <c r="D96" s="603"/>
       <c r="E96" s="79"/>
       <c r="F96" s="153" t="s">
         <v>71</v>
@@ -9878,11 +9878,11 @@
       <c r="B97" s="154">
         <v>1</v>
       </c>
-      <c r="C97" s="596" t="str">
+      <c r="C97" s="604" t="str">
         <f>+C76</f>
         <v>Siemens Standard Fitout (Existing)</v>
       </c>
-      <c r="D97" s="595"/>
+      <c r="D97" s="605"/>
       <c r="E97" s="80"/>
       <c r="F97" s="58">
         <v>0</v>
@@ -9908,11 +9908,11 @@
         <f t="shared" ref="B98:B103" si="8">+B97+1</f>
         <v>2</v>
       </c>
-      <c r="C98" s="596" t="str">
+      <c r="C98" s="604" t="str">
         <f>+C77</f>
         <v>Siemens Standard Fitout (New)</v>
       </c>
-      <c r="D98" s="595"/>
+      <c r="D98" s="605"/>
       <c r="E98" s="63"/>
       <c r="F98" s="58">
         <f>'CAPEX and PM'!B29</f>
@@ -9940,11 +9940,11 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="C99" s="596" t="str">
+      <c r="C99" s="604" t="str">
         <f>+C78</f>
         <v>Capex over the period of lease period</v>
       </c>
-      <c r="D99" s="595"/>
+      <c r="D99" s="605"/>
       <c r="E99" s="63"/>
       <c r="F99" s="58">
         <f>'CAPEX and PM'!B98</f>
@@ -9972,11 +9972,11 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="C100" s="596" t="str">
+      <c r="C100" s="604" t="str">
         <f>+C79</f>
         <v>PM cost over the period of lease period</v>
       </c>
-      <c r="D100" s="595"/>
+      <c r="D100" s="605"/>
       <c r="E100" s="63"/>
       <c r="F100" s="58">
         <f>+'CAPEX and PM'!B105</f>
@@ -10004,11 +10004,11 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="C101" s="596" t="str">
+      <c r="C101" s="604" t="str">
         <f>+C80</f>
         <v>Asset Retirement Obligation ( Removal &amp; Restoration Obligation)</v>
       </c>
-      <c r="D101" s="595"/>
+      <c r="D101" s="605"/>
       <c r="E101" s="63"/>
       <c r="F101" s="58">
         <f>'Security Deposit'!D25</f>
@@ -10039,10 +10039,10 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="C102" s="594" t="s">
+      <c r="C102" s="598" t="s">
         <v>150</v>
       </c>
-      <c r="D102" s="595"/>
+      <c r="D102" s="605"/>
       <c r="E102" s="65"/>
       <c r="F102" s="58">
         <f>+F81/F21/F27</f>
@@ -10070,10 +10070,10 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="C103" s="597" t="s">
+      <c r="C103" s="600" t="s">
         <v>151</v>
       </c>
-      <c r="D103" s="598"/>
+      <c r="D103" s="601"/>
       <c r="E103" s="70"/>
       <c r="F103" s="46">
         <f>SUM(F97:F102)</f>
@@ -10110,11 +10110,11 @@
     </row>
     <row r="105" spans="1:26" ht="15.9" customHeight="1">
       <c r="A105" s="43"/>
-      <c r="B105" s="690" t="s">
+      <c r="B105" s="609" t="s">
         <v>152</v>
       </c>
-      <c r="C105" s="611"/>
-      <c r="D105" s="611"/>
+      <c r="C105" s="610"/>
+      <c r="D105" s="610"/>
       <c r="E105" s="79"/>
       <c r="F105" s="153" t="s">
         <v>71</v>
@@ -10135,10 +10135,10 @@
       <c r="B106" s="154">
         <v>1</v>
       </c>
-      <c r="C106" s="594" t="s">
+      <c r="C106" s="598" t="s">
         <v>65</v>
       </c>
-      <c r="D106" s="595"/>
+      <c r="D106" s="605"/>
       <c r="E106" s="63"/>
       <c r="F106" s="48">
         <f>+F94</f>
@@ -10166,10 +10166,10 @@
         <f>+B106+1</f>
         <v>2</v>
       </c>
-      <c r="C107" s="594" t="s">
+      <c r="C107" s="598" t="s">
         <v>151</v>
       </c>
-      <c r="D107" s="604"/>
+      <c r="D107" s="599"/>
       <c r="E107" s="63"/>
       <c r="F107" s="48">
         <f>+F103</f>
@@ -10197,10 +10197,10 @@
         <f>+B107+1</f>
         <v>3</v>
       </c>
-      <c r="C108" s="597" t="s">
+      <c r="C108" s="600" t="s">
         <v>153</v>
       </c>
-      <c r="D108" s="598"/>
+      <c r="D108" s="601"/>
       <c r="E108" s="70"/>
       <c r="F108" s="46">
         <f>SUM(F106:F107)</f>
@@ -10229,11 +10229,11 @@
     </row>
     <row r="109" spans="1:26" ht="15.9" customHeight="1">
       <c r="A109" s="43"/>
-      <c r="B109" s="599" t="s">
+      <c r="B109" s="602" t="s">
         <v>154</v>
       </c>
-      <c r="C109" s="600"/>
-      <c r="D109" s="600"/>
+      <c r="C109" s="603"/>
+      <c r="D109" s="603"/>
       <c r="E109" s="81"/>
       <c r="F109" s="153" t="s">
         <v>71</v>
@@ -10255,10 +10255,10 @@
       <c r="B110" s="237">
         <v>1</v>
       </c>
-      <c r="C110" s="594" t="s">
+      <c r="C110" s="598" t="s">
         <v>155</v>
       </c>
-      <c r="D110" s="604"/>
+      <c r="D110" s="599"/>
       <c r="E110" s="75"/>
       <c r="F110" s="364"/>
       <c r="G110" s="364"/>
@@ -10272,10 +10272,10 @@
         <f t="shared" ref="B111:B119" si="9">1+B110</f>
         <v>2</v>
       </c>
-      <c r="C111" s="594" t="s">
+      <c r="C111" s="598" t="s">
         <v>156</v>
       </c>
-      <c r="D111" s="604"/>
+      <c r="D111" s="599"/>
       <c r="E111" s="75"/>
       <c r="F111" s="364"/>
       <c r="G111" s="364"/>
@@ -10291,10 +10291,10 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="C112" s="594" t="s">
+      <c r="C112" s="598" t="s">
         <v>157</v>
       </c>
-      <c r="D112" s="604"/>
+      <c r="D112" s="599"/>
       <c r="E112" s="75"/>
       <c r="F112" s="376">
         <f>+F64*0</f>
@@ -10322,10 +10322,10 @@
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="C113" s="594" t="s">
+      <c r="C113" s="598" t="s">
         <v>158</v>
       </c>
-      <c r="D113" s="604"/>
+      <c r="D113" s="599"/>
       <c r="E113" s="75"/>
       <c r="F113" s="364"/>
       <c r="G113" s="364"/>
@@ -10339,10 +10339,10 @@
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="C114" s="594" t="s">
+      <c r="C114" s="598" t="s">
         <v>159</v>
       </c>
-      <c r="D114" s="604"/>
+      <c r="D114" s="599"/>
       <c r="E114" s="75"/>
       <c r="F114" s="364"/>
       <c r="G114" s="364"/>
@@ -10356,10 +10356,10 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="C115" s="594" t="s">
+      <c r="C115" s="598" t="s">
         <v>160</v>
       </c>
-      <c r="D115" s="604"/>
+      <c r="D115" s="599"/>
       <c r="E115" s="75"/>
       <c r="F115" s="364"/>
       <c r="G115" s="364"/>
@@ -10373,10 +10373,10 @@
         <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="C116" s="594" t="s">
+      <c r="C116" s="598" t="s">
         <v>161</v>
       </c>
-      <c r="D116" s="604"/>
+      <c r="D116" s="599"/>
       <c r="E116" s="75"/>
       <c r="F116" s="364"/>
       <c r="G116" s="364"/>
@@ -10390,10 +10390,10 @@
         <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="C117" s="594" t="s">
+      <c r="C117" s="598" t="s">
         <v>162</v>
       </c>
-      <c r="D117" s="595"/>
+      <c r="D117" s="605"/>
       <c r="E117" s="240"/>
       <c r="F117" s="348">
         <v>654</v>
@@ -10419,10 +10419,10 @@
         <f t="shared" si="9"/>
         <v>9</v>
       </c>
-      <c r="C118" s="594" t="s">
+      <c r="C118" s="598" t="s">
         <v>163</v>
       </c>
-      <c r="D118" s="604"/>
+      <c r="D118" s="599"/>
       <c r="E118" s="240"/>
       <c r="F118" s="82">
         <f>F117*7%</f>
@@ -10448,10 +10448,10 @@
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="C119" s="597" t="s">
+      <c r="C119" s="600" t="s">
         <v>164</v>
       </c>
-      <c r="D119" s="598"/>
+      <c r="D119" s="601"/>
       <c r="E119" s="241"/>
       <c r="F119" s="46">
         <f>SUM(F110:F118)</f>
@@ -10477,8 +10477,8 @@
     <row r="120" spans="1:26" ht="15.9" customHeight="1">
       <c r="A120" s="69"/>
       <c r="B120" s="154"/>
-      <c r="C120" s="602"/>
-      <c r="D120" s="603"/>
+      <c r="C120" s="594"/>
+      <c r="D120" s="611"/>
       <c r="E120" s="70"/>
       <c r="F120" s="46"/>
       <c r="G120" s="373"/>
@@ -10492,11 +10492,11 @@
     </row>
     <row r="121" spans="1:26" ht="15.9" customHeight="1">
       <c r="A121" s="69"/>
-      <c r="B121" s="599" t="s">
+      <c r="B121" s="602" t="s">
         <v>165</v>
       </c>
-      <c r="C121" s="600"/>
-      <c r="D121" s="600"/>
+      <c r="C121" s="603"/>
+      <c r="D121" s="603"/>
       <c r="E121" s="81"/>
       <c r="F121" s="153" t="s">
         <v>71</v>
@@ -10519,10 +10519,10 @@
       <c r="B122" s="239">
         <v>1</v>
       </c>
-      <c r="C122" s="594" t="s">
+      <c r="C122" s="598" t="s">
         <v>166</v>
       </c>
-      <c r="D122" s="604"/>
+      <c r="D122" s="599"/>
       <c r="E122" s="70"/>
       <c r="F122" s="46"/>
       <c r="G122" s="373"/>
@@ -10535,10 +10535,10 @@
       <c r="B123" s="154">
         <v>2</v>
       </c>
-      <c r="C123" s="597" t="s">
+      <c r="C123" s="600" t="s">
         <v>167</v>
       </c>
-      <c r="D123" s="598"/>
+      <c r="D123" s="601"/>
       <c r="E123" s="70"/>
       <c r="F123" s="46">
         <f>SUM(F122)</f>
@@ -10561,8 +10561,8 @@
     <row r="124" spans="1:26" ht="15.9" customHeight="1">
       <c r="A124" s="69"/>
       <c r="B124" s="154"/>
-      <c r="C124" s="602"/>
-      <c r="D124" s="603"/>
+      <c r="C124" s="594"/>
+      <c r="D124" s="611"/>
       <c r="E124" s="55"/>
       <c r="F124" s="46"/>
       <c r="G124" s="373"/>
@@ -10572,11 +10572,11 @@
     </row>
     <row r="125" spans="1:26" ht="15.9" customHeight="1">
       <c r="A125" s="69"/>
-      <c r="B125" s="599" t="s">
+      <c r="B125" s="602" t="s">
         <v>168</v>
       </c>
-      <c r="C125" s="600"/>
-      <c r="D125" s="600"/>
+      <c r="C125" s="603"/>
+      <c r="D125" s="603"/>
       <c r="E125" s="81"/>
       <c r="F125" s="153" t="s">
         <v>71</v>
@@ -10597,10 +10597,10 @@
       <c r="B126" s="237">
         <v>1</v>
       </c>
-      <c r="C126" s="594" t="s">
+      <c r="C126" s="598" t="s">
         <v>169</v>
       </c>
-      <c r="D126" s="604"/>
+      <c r="D126" s="599"/>
       <c r="E126" s="238"/>
       <c r="F126" s="373"/>
       <c r="G126" s="373"/>
@@ -10614,10 +10614,10 @@
         <f>1+B126</f>
         <v>2</v>
       </c>
-      <c r="C127" s="594" t="s">
+      <c r="C127" s="598" t="s">
         <v>170</v>
       </c>
-      <c r="D127" s="604"/>
+      <c r="D127" s="599"/>
       <c r="E127" s="238"/>
       <c r="F127" s="373"/>
       <c r="G127" s="373"/>
@@ -10631,10 +10631,10 @@
         <f>1+B127</f>
         <v>3</v>
       </c>
-      <c r="C128" s="594" t="s">
+      <c r="C128" s="598" t="s">
         <v>171</v>
       </c>
-      <c r="D128" s="604"/>
+      <c r="D128" s="599"/>
       <c r="E128" s="238"/>
       <c r="F128" s="373"/>
       <c r="G128" s="373"/>
@@ -10648,10 +10648,10 @@
         <f>1+B128</f>
         <v>4</v>
       </c>
-      <c r="C129" s="594" t="s">
+      <c r="C129" s="598" t="s">
         <v>172</v>
       </c>
-      <c r="D129" s="604"/>
+      <c r="D129" s="599"/>
       <c r="E129" s="238"/>
       <c r="F129" s="373"/>
       <c r="G129" s="373"/>
@@ -10665,10 +10665,10 @@
         <f>1+B129</f>
         <v>5</v>
       </c>
-      <c r="C130" s="594" t="s">
+      <c r="C130" s="598" t="s">
         <v>173</v>
       </c>
-      <c r="D130" s="604"/>
+      <c r="D130" s="599"/>
       <c r="E130" s="238"/>
       <c r="F130" s="373"/>
       <c r="G130" s="373"/>
@@ -10682,10 +10682,10 @@
         <f>1+B130</f>
         <v>6</v>
       </c>
-      <c r="C131" s="594" t="s">
+      <c r="C131" s="598" t="s">
         <v>174</v>
       </c>
-      <c r="D131" s="604"/>
+      <c r="D131" s="599"/>
       <c r="E131" s="238"/>
       <c r="F131" s="373"/>
       <c r="G131" s="373"/>
@@ -10698,10 +10698,10 @@
       <c r="B132" s="369">
         <v>7</v>
       </c>
-      <c r="C132" s="597" t="s">
+      <c r="C132" s="600" t="s">
         <v>175</v>
       </c>
-      <c r="D132" s="598"/>
+      <c r="D132" s="601"/>
       <c r="E132" s="238"/>
       <c r="F132" s="373">
         <f>SUM(F126:F131)</f>
@@ -10724,8 +10724,8 @@
     <row r="133" spans="1:20" ht="15.9" customHeight="1">
       <c r="A133" s="69"/>
       <c r="B133" s="154"/>
-      <c r="C133" s="636"/>
-      <c r="D133" s="603"/>
+      <c r="C133" s="595"/>
+      <c r="D133" s="611"/>
       <c r="E133" s="238"/>
       <c r="F133" s="373"/>
       <c r="G133" s="373"/>
@@ -10735,11 +10735,11 @@
     </row>
     <row r="134" spans="1:20" ht="15.9" customHeight="1">
       <c r="A134" s="43"/>
-      <c r="B134" s="599" t="s">
+      <c r="B134" s="602" t="s">
         <v>176</v>
       </c>
-      <c r="C134" s="600"/>
-      <c r="D134" s="600"/>
+      <c r="C134" s="603"/>
+      <c r="D134" s="603"/>
       <c r="E134" s="81"/>
       <c r="F134" s="153" t="s">
         <v>71</v>
@@ -10760,10 +10760,10 @@
       <c r="B135" s="154">
         <v>1</v>
       </c>
-      <c r="C135" s="597" t="s">
+      <c r="C135" s="600" t="s">
         <v>177</v>
       </c>
-      <c r="D135" s="598"/>
+      <c r="D135" s="601"/>
       <c r="E135" s="70"/>
       <c r="F135" s="46">
         <f>F119+F108+F123+F132</f>
@@ -10788,8 +10788,8 @@
     <row r="136" spans="1:20" ht="15.9" customHeight="1">
       <c r="A136" s="69"/>
       <c r="B136" s="154"/>
-      <c r="C136" s="602"/>
-      <c r="D136" s="603"/>
+      <c r="C136" s="594"/>
+      <c r="D136" s="611"/>
       <c r="E136" s="70"/>
       <c r="F136" s="46"/>
       <c r="G136" s="373"/>
@@ -10803,23 +10803,23 @@
       <c r="C137" s="368"/>
       <c r="D137" s="365"/>
       <c r="E137" s="159"/>
-      <c r="F137" s="602" t="s">
+      <c r="F137" s="594" t="s">
         <v>69</v>
       </c>
-      <c r="G137" s="636"/>
+      <c r="G137" s="595"/>
       <c r="H137" s="392"/>
-      <c r="I137" s="637" t="s">
+      <c r="I137" s="596" t="s">
         <v>63</v>
       </c>
-      <c r="J137" s="638"/>
+      <c r="J137" s="597"/>
     </row>
     <row r="138" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A138" s="43"/>
-      <c r="B138" s="599" t="s">
+      <c r="B138" s="602" t="s">
         <v>178</v>
       </c>
-      <c r="C138" s="600"/>
-      <c r="D138" s="601"/>
+      <c r="C138" s="603"/>
+      <c r="D138" s="618"/>
       <c r="E138" s="153"/>
       <c r="F138" s="153" t="s">
         <v>71</v>
@@ -10838,8 +10838,8 @@
     <row r="139" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A139" s="43"/>
       <c r="B139" s="83"/>
-      <c r="C139" s="605"/>
-      <c r="D139" s="606"/>
+      <c r="C139" s="619"/>
+      <c r="D139" s="620"/>
       <c r="E139" s="155"/>
       <c r="F139" s="46"/>
       <c r="G139" s="373"/>
@@ -10850,10 +10850,10 @@
     <row r="140" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A140" s="43"/>
       <c r="B140" s="83"/>
-      <c r="C140" s="594" t="s">
+      <c r="C140" s="598" t="s">
         <v>179</v>
       </c>
-      <c r="D140" s="595"/>
+      <c r="D140" s="605"/>
       <c r="E140" s="50"/>
       <c r="F140" s="231">
         <f>F21</f>
@@ -10876,10 +10876,10 @@
     <row r="141" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A141" s="43"/>
       <c r="B141" s="83"/>
-      <c r="C141" s="596" t="s">
+      <c r="C141" s="604" t="s">
         <v>180</v>
       </c>
-      <c r="D141" s="595"/>
+      <c r="D141" s="605"/>
       <c r="E141" s="51"/>
       <c r="F141" s="48">
         <f>F24</f>
@@ -10902,10 +10902,10 @@
     <row r="142" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A142" s="43"/>
       <c r="B142" s="83"/>
-      <c r="C142" s="596" t="s">
+      <c r="C142" s="604" t="s">
         <v>181</v>
       </c>
-      <c r="D142" s="595"/>
+      <c r="D142" s="605"/>
       <c r="E142" s="65"/>
       <c r="F142" s="48" t="e">
         <f>+#REF!</f>
@@ -10928,10 +10928,10 @@
     <row r="143" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A143" s="43"/>
       <c r="B143" s="83"/>
-      <c r="C143" s="594" t="s">
+      <c r="C143" s="598" t="s">
         <v>182</v>
       </c>
-      <c r="D143" s="595"/>
+      <c r="D143" s="605"/>
       <c r="E143" s="65"/>
       <c r="F143" s="48">
         <f>F108</f>
@@ -10954,10 +10954,10 @@
     <row r="144" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A144" s="43"/>
       <c r="B144" s="83"/>
-      <c r="C144" s="624" t="s">
+      <c r="C144" s="689" t="s">
         <v>183</v>
       </c>
-      <c r="D144" s="625"/>
+      <c r="D144" s="690"/>
       <c r="E144" s="84"/>
       <c r="F144" s="85">
         <f>F119</f>
@@ -10980,10 +10980,10 @@
     <row r="145" spans="1:10" ht="15.9" hidden="1" customHeight="1">
       <c r="A145" s="69"/>
       <c r="B145" s="154"/>
-      <c r="C145" s="597" t="s">
+      <c r="C145" s="600" t="s">
         <v>184</v>
       </c>
-      <c r="D145" s="598"/>
+      <c r="D145" s="601"/>
       <c r="E145" s="70"/>
       <c r="F145" s="233" t="e">
         <f>F135*#REF!</f>
@@ -11017,11 +11017,11 @@
     </row>
     <row r="147" spans="1:10" ht="15.9" customHeight="1">
       <c r="A147" s="69"/>
-      <c r="B147" s="599" t="s">
+      <c r="B147" s="602" t="s">
         <v>185</v>
       </c>
-      <c r="C147" s="600"/>
-      <c r="D147" s="601"/>
+      <c r="C147" s="603"/>
+      <c r="D147" s="618"/>
       <c r="E147" s="367"/>
       <c r="F147" s="367" t="s">
         <v>186</v>
@@ -11040,8 +11040,8 @@
     <row r="148" spans="1:10" ht="15.9" customHeight="1">
       <c r="A148" s="43"/>
       <c r="B148" s="91"/>
-      <c r="C148" s="605"/>
-      <c r="D148" s="606"/>
+      <c r="C148" s="619"/>
+      <c r="D148" s="620"/>
       <c r="E148" s="92"/>
       <c r="F148" s="93"/>
       <c r="G148" s="197"/>
@@ -11052,10 +11052,10 @@
     <row r="149" spans="1:10" ht="15.9" customHeight="1">
       <c r="A149" s="43"/>
       <c r="B149" s="91"/>
-      <c r="C149" s="596" t="s">
+      <c r="C149" s="604" t="s">
         <v>187</v>
       </c>
-      <c r="D149" s="595"/>
+      <c r="D149" s="605"/>
       <c r="E149" s="92"/>
       <c r="F149" s="93">
         <f>(+F63)*115%</f>
@@ -11078,10 +11078,10 @@
     <row r="150" spans="1:10" ht="15.9" customHeight="1">
       <c r="A150" s="43"/>
       <c r="B150" s="91"/>
-      <c r="C150" s="596" t="s">
+      <c r="C150" s="604" t="s">
         <v>188</v>
       </c>
-      <c r="D150" s="595"/>
+      <c r="D150" s="605"/>
       <c r="E150" s="92"/>
       <c r="F150" s="93">
         <v>0</v>
@@ -11100,10 +11100,10 @@
     <row r="151" spans="1:10" ht="15.9" customHeight="1">
       <c r="A151" s="43"/>
       <c r="B151" s="91"/>
-      <c r="C151" s="596" t="s">
+      <c r="C151" s="604" t="s">
         <v>189</v>
       </c>
-      <c r="D151" s="595"/>
+      <c r="D151" s="605"/>
       <c r="E151" s="92"/>
       <c r="F151" s="93">
         <f>(+F65)*115%</f>
@@ -11126,10 +11126,10 @@
     <row r="152" spans="1:10" ht="15.9" customHeight="1">
       <c r="A152" s="43"/>
       <c r="B152" s="91"/>
-      <c r="C152" s="596" t="s">
+      <c r="C152" s="604" t="s">
         <v>190</v>
       </c>
-      <c r="D152" s="595"/>
+      <c r="D152" s="605"/>
       <c r="E152" s="92"/>
       <c r="F152" s="93">
         <f>(+F66)*115%</f>
@@ -11152,10 +11152,10 @@
     <row r="153" spans="1:10" ht="15.9" customHeight="1">
       <c r="A153" s="43"/>
       <c r="B153" s="91"/>
-      <c r="C153" s="594" t="s">
+      <c r="C153" s="598" t="s">
         <v>191</v>
       </c>
-      <c r="D153" s="595"/>
+      <c r="D153" s="605"/>
       <c r="E153" s="95"/>
       <c r="F153" s="96">
         <f>SUM(F149:F152)</f>
@@ -11178,10 +11178,10 @@
     <row r="154" spans="1:10" ht="15.9" customHeight="1">
       <c r="A154" s="43"/>
       <c r="B154" s="91"/>
-      <c r="C154" s="594" t="s">
+      <c r="C154" s="598" t="s">
         <v>192</v>
       </c>
-      <c r="D154" s="595"/>
+      <c r="D154" s="605"/>
       <c r="E154" s="97"/>
       <c r="F154" s="93">
         <f>+F153*12</f>
@@ -11204,8 +11204,8 @@
     <row r="155" spans="1:10" ht="15.9" customHeight="1">
       <c r="A155" s="43"/>
       <c r="B155" s="91"/>
-      <c r="C155" s="605"/>
-      <c r="D155" s="606"/>
+      <c r="C155" s="619"/>
+      <c r="D155" s="620"/>
       <c r="E155" s="97"/>
       <c r="F155" s="93"/>
       <c r="G155" s="197"/>
@@ -11215,11 +11215,11 @@
     </row>
     <row r="156" spans="1:10" ht="15.9" customHeight="1">
       <c r="A156" s="43"/>
-      <c r="B156" s="599" t="s">
+      <c r="B156" s="602" t="s">
         <v>193</v>
       </c>
-      <c r="C156" s="600"/>
-      <c r="D156" s="601"/>
+      <c r="C156" s="603"/>
+      <c r="D156" s="618"/>
       <c r="E156" s="363"/>
       <c r="F156" s="367" t="s">
         <v>186</v>
@@ -11238,8 +11238,8 @@
     <row r="157" spans="1:10" ht="15.9" customHeight="1">
       <c r="A157" s="43"/>
       <c r="B157" s="91"/>
-      <c r="C157" s="605"/>
-      <c r="D157" s="606"/>
+      <c r="C157" s="619"/>
+      <c r="D157" s="620"/>
       <c r="E157" s="97"/>
       <c r="F157" s="93"/>
       <c r="G157" s="197"/>
@@ -11250,10 +11250,10 @@
     <row r="158" spans="1:10" ht="15.9" customHeight="1">
       <c r="A158" s="43"/>
       <c r="B158" s="91"/>
-      <c r="C158" s="622" t="s">
+      <c r="C158" s="687" t="s">
         <v>194</v>
       </c>
-      <c r="D158" s="623"/>
+      <c r="D158" s="688"/>
       <c r="E158" s="97"/>
       <c r="F158" s="93">
         <f t="shared" ref="F158:G160" si="10">+F77</f>
@@ -11276,10 +11276,10 @@
     <row r="159" spans="1:10" ht="15.9" customHeight="1">
       <c r="A159" s="43"/>
       <c r="B159" s="91"/>
-      <c r="C159" s="594" t="s">
+      <c r="C159" s="598" t="s">
         <v>195</v>
       </c>
-      <c r="D159" s="604"/>
+      <c r="D159" s="599"/>
       <c r="E159" s="97"/>
       <c r="F159" s="93">
         <f t="shared" si="10"/>
@@ -11302,10 +11302,10 @@
     <row r="160" spans="1:10" ht="15.9" customHeight="1">
       <c r="A160" s="43"/>
       <c r="B160" s="91"/>
-      <c r="C160" s="594" t="s">
+      <c r="C160" s="598" t="s">
         <v>196</v>
       </c>
-      <c r="D160" s="604"/>
+      <c r="D160" s="599"/>
       <c r="E160" s="97"/>
       <c r="F160" s="93">
         <f t="shared" si="10"/>
@@ -11328,10 +11328,10 @@
     <row r="161" spans="1:22" ht="15.9" customHeight="1">
       <c r="A161" s="43"/>
       <c r="B161" s="91"/>
-      <c r="C161" s="597" t="s">
+      <c r="C161" s="600" t="s">
         <v>29</v>
       </c>
-      <c r="D161" s="598"/>
+      <c r="D161" s="601"/>
       <c r="E161" s="97"/>
       <c r="F161" s="225">
         <f>SUM(F158:F160)</f>
@@ -11354,8 +11354,8 @@
     <row r="162" spans="1:22" ht="15.9" customHeight="1">
       <c r="A162" s="43"/>
       <c r="B162" s="91"/>
-      <c r="C162" s="605"/>
-      <c r="D162" s="606"/>
+      <c r="C162" s="619"/>
+      <c r="D162" s="620"/>
       <c r="E162" s="97"/>
       <c r="F162" s="93"/>
       <c r="G162" s="197"/>
@@ -11365,12 +11365,12 @@
     </row>
     <row r="163" spans="1:22" ht="15.9" customHeight="1">
       <c r="A163" s="98"/>
-      <c r="B163" s="616" t="s">
+      <c r="B163" s="606" t="s">
         <v>197</v>
       </c>
-      <c r="C163" s="617"/>
-      <c r="D163" s="618"/>
-      <c r="E163" s="689"/>
+      <c r="C163" s="607"/>
+      <c r="D163" s="608"/>
+      <c r="E163" s="616"/>
       <c r="F163" s="153" t="s">
         <v>71</v>
       </c>
@@ -11387,10 +11387,10 @@
     </row>
     <row r="164" spans="1:22" ht="15.9" customHeight="1">
       <c r="A164" s="98"/>
-      <c r="B164" s="619"/>
-      <c r="C164" s="620"/>
-      <c r="D164" s="621"/>
-      <c r="E164" s="609"/>
+      <c r="B164" s="684"/>
+      <c r="C164" s="685"/>
+      <c r="D164" s="686"/>
+      <c r="E164" s="617"/>
       <c r="F164" s="153" t="s">
         <v>69</v>
       </c>
@@ -11408,8 +11408,8 @@
     <row r="165" spans="1:22" ht="15.9" customHeight="1">
       <c r="A165" s="99"/>
       <c r="B165" s="91"/>
-      <c r="C165" s="605"/>
-      <c r="D165" s="606"/>
+      <c r="C165" s="619"/>
+      <c r="D165" s="620"/>
       <c r="E165" s="51"/>
       <c r="F165" s="48"/>
       <c r="G165" s="376"/>
@@ -11420,11 +11420,11 @@
     <row r="166" spans="1:22" ht="15.9" customHeight="1">
       <c r="A166" s="99"/>
       <c r="B166" s="91"/>
-      <c r="C166" s="607" t="str">
+      <c r="C166" s="682" t="str">
         <f>+C106</f>
         <v>Net Rent I</v>
       </c>
-      <c r="D166" s="608"/>
+      <c r="D166" s="683"/>
       <c r="E166" s="51"/>
       <c r="F166" s="48">
         <f>+F106</f>
@@ -11448,11 +11448,11 @@
     <row r="167" spans="1:22" ht="15.9" customHeight="1">
       <c r="A167" s="99"/>
       <c r="B167" s="91"/>
-      <c r="C167" s="607" t="str">
+      <c r="C167" s="682" t="str">
         <f>+C107</f>
         <v>Net Rent II</v>
       </c>
-      <c r="D167" s="608"/>
+      <c r="D167" s="683"/>
       <c r="E167" s="51"/>
       <c r="F167" s="48">
         <f>+F107</f>
@@ -11476,10 +11476,10 @@
     <row r="168" spans="1:22" ht="15.9" customHeight="1">
       <c r="A168" s="99"/>
       <c r="B168" s="139"/>
-      <c r="C168" s="612" t="s">
+      <c r="C168" s="678" t="s">
         <v>198</v>
       </c>
-      <c r="D168" s="613"/>
+      <c r="D168" s="679"/>
       <c r="E168" s="140"/>
       <c r="F168" s="141">
         <f>SUM(F166:F167)</f>
@@ -11504,8 +11504,8 @@
     <row r="169" spans="1:22" ht="15.9" customHeight="1">
       <c r="A169" s="99"/>
       <c r="B169" s="154"/>
-      <c r="C169" s="614"/>
-      <c r="D169" s="615"/>
+      <c r="C169" s="680"/>
+      <c r="D169" s="681"/>
       <c r="E169" s="67"/>
       <c r="F169" s="46"/>
       <c r="G169" s="373"/>
@@ -11518,11 +11518,11 @@
     <row r="170" spans="1:22" ht="15.9" customHeight="1">
       <c r="A170" s="99"/>
       <c r="B170" s="91"/>
-      <c r="C170" s="607" t="str">
+      <c r="C170" s="682" t="str">
         <f>+C119</f>
         <v xml:space="preserve">OpEx I </v>
       </c>
-      <c r="D170" s="608"/>
+      <c r="D170" s="683"/>
       <c r="E170" s="51"/>
       <c r="F170" s="48">
         <f>+F119</f>
@@ -11546,11 +11546,11 @@
     <row r="171" spans="1:22" ht="15.9" customHeight="1">
       <c r="A171" s="99"/>
       <c r="B171" s="91"/>
-      <c r="C171" s="607" t="str">
+      <c r="C171" s="682" t="str">
         <f>+C123</f>
         <v xml:space="preserve">OpEx II </v>
       </c>
-      <c r="D171" s="608"/>
+      <c r="D171" s="683"/>
       <c r="E171" s="51"/>
       <c r="F171" s="48">
         <f>+F123</f>
@@ -11573,10 +11573,10 @@
     <row r="172" spans="1:22" ht="15.9" customHeight="1">
       <c r="A172" s="99"/>
       <c r="B172" s="142"/>
-      <c r="C172" s="612" t="s">
+      <c r="C172" s="678" t="s">
         <v>199</v>
       </c>
-      <c r="D172" s="613"/>
+      <c r="D172" s="679"/>
       <c r="E172" s="143"/>
       <c r="F172" s="144">
         <f>SUM(F170:F171)</f>
@@ -11611,11 +11611,11 @@
     <row r="174" spans="1:22" ht="15.9" customHeight="1">
       <c r="A174" s="99"/>
       <c r="B174" s="91"/>
-      <c r="C174" s="607" t="str">
+      <c r="C174" s="682" t="str">
         <f>+C132</f>
         <v xml:space="preserve">Services </v>
       </c>
-      <c r="D174" s="608"/>
+      <c r="D174" s="683"/>
       <c r="E174" s="51"/>
       <c r="F174" s="48">
         <f>+F132</f>
@@ -11638,10 +11638,10 @@
     <row r="175" spans="1:22" ht="15.9" customHeight="1">
       <c r="A175" s="99"/>
       <c r="B175" s="142"/>
-      <c r="C175" s="612" t="s">
+      <c r="C175" s="678" t="s">
         <v>200</v>
       </c>
-      <c r="D175" s="613"/>
+      <c r="D175" s="679"/>
       <c r="E175" s="143"/>
       <c r="F175" s="144">
         <f>SUM(F174)</f>
@@ -11664,8 +11664,8 @@
     <row r="176" spans="1:22" ht="15.9" customHeight="1">
       <c r="A176" s="99"/>
       <c r="B176" s="91"/>
-      <c r="C176" s="605"/>
-      <c r="D176" s="606"/>
+      <c r="C176" s="619"/>
+      <c r="D176" s="620"/>
       <c r="E176" s="51"/>
       <c r="F176" s="48"/>
       <c r="G176" s="376"/>
@@ -11676,10 +11676,10 @@
     <row r="177" spans="1:19" ht="15.9" customHeight="1">
       <c r="A177" s="99"/>
       <c r="B177" s="142"/>
-      <c r="C177" s="612" t="s">
+      <c r="C177" s="678" t="s">
         <v>201</v>
       </c>
-      <c r="D177" s="613"/>
+      <c r="D177" s="679"/>
       <c r="E177" s="146"/>
       <c r="F177" s="141">
         <f>+F168+F172+F175</f>
@@ -11714,11 +11714,11 @@
     </row>
     <row r="179" spans="1:19" ht="15.9" customHeight="1">
       <c r="A179" s="99"/>
-      <c r="B179" s="599" t="s">
+      <c r="B179" s="602" t="s">
         <v>202</v>
       </c>
-      <c r="C179" s="600"/>
-      <c r="D179" s="601"/>
+      <c r="C179" s="603"/>
+      <c r="D179" s="618"/>
       <c r="E179" s="367"/>
       <c r="F179" s="367" t="s">
         <v>186</v>
@@ -11737,8 +11737,8 @@
     <row r="180" spans="1:19" ht="15.9" customHeight="1">
       <c r="A180" s="99"/>
       <c r="B180" s="91"/>
-      <c r="C180" s="605"/>
-      <c r="D180" s="606"/>
+      <c r="C180" s="619"/>
+      <c r="D180" s="620"/>
       <c r="E180" s="51"/>
       <c r="F180" s="48"/>
       <c r="G180" s="376"/>
@@ -11749,10 +11749,10 @@
     <row r="181" spans="1:19" ht="15.9" customHeight="1">
       <c r="A181" s="99"/>
       <c r="B181" s="91"/>
-      <c r="C181" s="596" t="s">
+      <c r="C181" s="604" t="s">
         <v>203</v>
       </c>
-      <c r="D181" s="595"/>
+      <c r="D181" s="605"/>
       <c r="E181" s="92"/>
       <c r="F181" s="93"/>
       <c r="G181" s="197">
@@ -11769,10 +11769,10 @@
     <row r="182" spans="1:19" ht="15.9" customHeight="1">
       <c r="A182" s="99"/>
       <c r="B182" s="91"/>
-      <c r="C182" s="594" t="s">
+      <c r="C182" s="598" t="s">
         <v>204</v>
       </c>
-      <c r="D182" s="595"/>
+      <c r="D182" s="605"/>
       <c r="E182" s="92"/>
       <c r="F182" s="93"/>
       <c r="G182" s="197">
@@ -11789,10 +11789,10 @@
     <row r="183" spans="1:19" ht="15.9" customHeight="1">
       <c r="A183" s="99"/>
       <c r="B183" s="91"/>
-      <c r="C183" s="594" t="s">
+      <c r="C183" s="598" t="s">
         <v>205</v>
       </c>
-      <c r="D183" s="604"/>
+      <c r="D183" s="599"/>
       <c r="E183" s="92"/>
       <c r="F183" s="93"/>
       <c r="G183" s="197">
@@ -11806,10 +11806,10 @@
     <row r="184" spans="1:19" ht="15.9" customHeight="1">
       <c r="A184" s="99"/>
       <c r="B184" s="91"/>
-      <c r="C184" s="594" t="s">
+      <c r="C184" s="598" t="s">
         <v>206</v>
       </c>
-      <c r="D184" s="595"/>
+      <c r="D184" s="605"/>
       <c r="E184" s="92"/>
       <c r="F184" s="93"/>
       <c r="G184" s="197">
@@ -11826,10 +11826,10 @@
     <row r="185" spans="1:19" ht="15.9" customHeight="1">
       <c r="A185" s="99"/>
       <c r="B185" s="91"/>
-      <c r="C185" s="594" t="s">
+      <c r="C185" s="598" t="s">
         <v>207</v>
       </c>
-      <c r="D185" s="595"/>
+      <c r="D185" s="605"/>
       <c r="E185" s="92"/>
       <c r="F185" s="93"/>
       <c r="G185" s="197">
@@ -11857,25 +11857,25 @@
     </row>
     <row r="187" spans="1:19" ht="15.9" customHeight="1" thickBot="1">
       <c r="A187" s="99"/>
-      <c r="B187" s="629" t="s">
+      <c r="B187" s="675" t="s">
         <v>208</v>
       </c>
-      <c r="C187" s="630"/>
-      <c r="D187" s="630"/>
-      <c r="E187" s="630"/>
-      <c r="F187" s="630"/>
-      <c r="G187" s="630"/>
-      <c r="H187" s="630"/>
-      <c r="I187" s="630"/>
-      <c r="J187" s="631"/>
+      <c r="C187" s="676"/>
+      <c r="D187" s="676"/>
+      <c r="E187" s="676"/>
+      <c r="F187" s="676"/>
+      <c r="G187" s="676"/>
+      <c r="H187" s="676"/>
+      <c r="I187" s="676"/>
+      <c r="J187" s="677"/>
     </row>
     <row r="188" spans="1:19" ht="15.9" customHeight="1">
       <c r="A188" s="43"/>
       <c r="B188" s="156"/>
-      <c r="C188" s="609" t="s">
+      <c r="C188" s="617" t="s">
         <v>209</v>
       </c>
-      <c r="D188" s="609"/>
+      <c r="D188" s="617"/>
       <c r="E188" s="366"/>
       <c r="F188" s="366" t="s">
         <v>186</v>
@@ -11883,7 +11883,7 @@
       <c r="G188" s="160" t="s">
         <v>186</v>
       </c>
-      <c r="H188" s="626"/>
+      <c r="H188" s="672"/>
       <c r="I188" s="217" t="s">
         <v>63</v>
       </c>
@@ -11894,17 +11894,17 @@
     <row r="189" spans="1:19" ht="15.9" customHeight="1">
       <c r="A189" s="43"/>
       <c r="B189" s="154"/>
-      <c r="C189" s="596" t="s">
+      <c r="C189" s="604" t="s">
         <v>210</v>
       </c>
-      <c r="D189" s="595"/>
+      <c r="D189" s="605"/>
       <c r="E189" s="155"/>
       <c r="F189" s="155"/>
       <c r="G189" s="94">
         <f>+G20</f>
         <v>0</v>
       </c>
-      <c r="H189" s="627"/>
+      <c r="H189" s="673"/>
       <c r="I189" s="154"/>
       <c r="J189" s="94">
         <f>+G189/J5</f>
@@ -11914,17 +11914,17 @@
     <row r="190" spans="1:19" ht="15.9" customHeight="1">
       <c r="A190" s="43"/>
       <c r="B190" s="154"/>
-      <c r="C190" s="596" t="s">
+      <c r="C190" s="604" t="s">
         <v>211</v>
       </c>
-      <c r="D190" s="595"/>
+      <c r="D190" s="605"/>
       <c r="E190" s="155"/>
       <c r="F190" s="155"/>
       <c r="G190" s="94">
         <f>+G189*G23</f>
         <v>0</v>
       </c>
-      <c r="H190" s="627"/>
+      <c r="H190" s="673"/>
       <c r="I190" s="154"/>
       <c r="J190" s="94">
         <f>+J189*J23</f>
@@ -11934,17 +11934,17 @@
     <row r="191" spans="1:19" ht="15.9" customHeight="1">
       <c r="A191" s="43"/>
       <c r="B191" s="154"/>
-      <c r="C191" s="610" t="s">
+      <c r="C191" s="642" t="s">
         <v>212</v>
       </c>
-      <c r="D191" s="610"/>
+      <c r="D191" s="642"/>
       <c r="E191" s="155"/>
       <c r="F191" s="155"/>
       <c r="G191" s="94">
         <f>+G190*25%</f>
         <v>0</v>
       </c>
-      <c r="H191" s="627"/>
+      <c r="H191" s="673"/>
       <c r="I191" s="154"/>
       <c r="J191" s="94">
         <f>+J190*25%</f>
@@ -11954,17 +11954,17 @@
     <row r="192" spans="1:19" ht="15.9" customHeight="1">
       <c r="A192" s="43"/>
       <c r="B192" s="154"/>
-      <c r="C192" s="594" t="s">
+      <c r="C192" s="598" t="s">
         <v>213</v>
       </c>
-      <c r="D192" s="595"/>
+      <c r="D192" s="605"/>
       <c r="E192" s="155"/>
       <c r="F192" s="155"/>
       <c r="G192" s="94">
         <f>+G191*1%</f>
         <v>0</v>
       </c>
-      <c r="H192" s="627"/>
+      <c r="H192" s="673"/>
       <c r="I192" s="154"/>
       <c r="J192" s="94">
         <f>G192/J5</f>
@@ -11974,17 +11974,17 @@
     <row r="193" spans="1:20" ht="15.9" customHeight="1">
       <c r="A193" s="43"/>
       <c r="B193" s="154"/>
-      <c r="C193" s="594" t="s">
+      <c r="C193" s="598" t="s">
         <v>214</v>
       </c>
-      <c r="D193" s="595"/>
+      <c r="D193" s="605"/>
       <c r="E193" s="155"/>
       <c r="F193" s="155"/>
       <c r="G193" s="94">
         <f>G192*0.5</f>
         <v>0</v>
       </c>
-      <c r="H193" s="627"/>
+      <c r="H193" s="673"/>
       <c r="I193" s="154"/>
       <c r="J193" s="94">
         <f>G193/J5</f>
@@ -11994,17 +11994,17 @@
     <row r="194" spans="1:20" ht="15.9" customHeight="1" thickBot="1">
       <c r="A194" s="43"/>
       <c r="B194" s="154"/>
-      <c r="C194" s="610" t="s">
+      <c r="C194" s="642" t="s">
         <v>215</v>
       </c>
-      <c r="D194" s="610"/>
+      <c r="D194" s="642"/>
       <c r="E194" s="155"/>
       <c r="F194" s="155"/>
       <c r="G194" s="102">
         <f>G82</f>
         <v>565315.30184775486</v>
       </c>
-      <c r="H194" s="627"/>
+      <c r="H194" s="673"/>
       <c r="I194" s="154"/>
       <c r="J194" s="102">
         <f>+J192+J193</f>
@@ -12014,8 +12014,8 @@
     <row r="195" spans="1:20" ht="15.9" customHeight="1">
       <c r="A195" s="158"/>
       <c r="B195" s="370"/>
-      <c r="C195" s="611"/>
-      <c r="D195" s="611"/>
+      <c r="C195" s="610"/>
+      <c r="D195" s="610"/>
       <c r="E195" s="367"/>
       <c r="F195" s="367" t="s">
         <v>186</v>
@@ -12023,7 +12023,7 @@
       <c r="G195" s="45" t="s">
         <v>186</v>
       </c>
-      <c r="H195" s="627"/>
+      <c r="H195" s="673"/>
       <c r="I195" s="217" t="s">
         <v>63</v>
       </c>
@@ -12034,17 +12034,17 @@
     <row r="196" spans="1:20" ht="15.9" customHeight="1">
       <c r="A196" s="66"/>
       <c r="B196" s="91"/>
-      <c r="C196" s="596" t="s">
+      <c r="C196" s="604" t="s">
         <v>216</v>
       </c>
-      <c r="D196" s="595"/>
+      <c r="D196" s="605"/>
       <c r="E196" s="50"/>
       <c r="F196" s="42"/>
       <c r="G196" s="94">
         <f>+G54</f>
         <v>72</v>
       </c>
-      <c r="H196" s="627"/>
+      <c r="H196" s="673"/>
       <c r="I196" s="83"/>
       <c r="J196" s="94">
         <f>+J54</f>
@@ -12054,17 +12054,17 @@
     <row r="197" spans="1:20" ht="15.9" customHeight="1">
       <c r="A197" s="66"/>
       <c r="B197" s="91"/>
-      <c r="C197" s="596" t="s">
+      <c r="C197" s="604" t="s">
         <v>217</v>
       </c>
-      <c r="D197" s="595"/>
+      <c r="D197" s="605"/>
       <c r="E197" s="50"/>
       <c r="F197" s="42"/>
       <c r="G197" s="94">
         <f>F140</f>
         <v>9515</v>
       </c>
-      <c r="H197" s="627"/>
+      <c r="H197" s="673"/>
       <c r="I197" s="83"/>
       <c r="J197" s="94">
         <f>I140</f>
@@ -12074,17 +12074,17 @@
     <row r="198" spans="1:20" ht="15.9" customHeight="1">
       <c r="A198" s="112"/>
       <c r="B198" s="91"/>
-      <c r="C198" s="596" t="s">
+      <c r="C198" s="604" t="s">
         <v>218</v>
       </c>
-      <c r="D198" s="595"/>
+      <c r="D198" s="605"/>
       <c r="E198" s="50"/>
       <c r="F198" s="42"/>
       <c r="G198" s="103">
         <f>+F60</f>
         <v>129</v>
       </c>
-      <c r="H198" s="627"/>
+      <c r="H198" s="673"/>
       <c r="I198" s="83"/>
       <c r="J198" s="103">
         <f>+I60</f>
@@ -12094,17 +12094,17 @@
     <row r="199" spans="1:20" ht="15.9" customHeight="1">
       <c r="A199" s="66"/>
       <c r="B199" s="91"/>
-      <c r="C199" s="596" t="s">
+      <c r="C199" s="604" t="s">
         <v>218</v>
       </c>
-      <c r="D199" s="595"/>
+      <c r="D199" s="605"/>
       <c r="E199" s="50"/>
       <c r="F199" s="42"/>
       <c r="G199" s="94">
         <f>(G197*G198*G196)</f>
         <v>88375320</v>
       </c>
-      <c r="H199" s="627"/>
+      <c r="H199" s="673"/>
       <c r="I199" s="83"/>
       <c r="J199" s="94">
         <f>+G199/$J$5</f>
@@ -12114,17 +12114,17 @@
     <row r="200" spans="1:20" ht="15.9" customHeight="1">
       <c r="A200" s="66"/>
       <c r="B200" s="91"/>
-      <c r="C200" s="596" t="s">
+      <c r="C200" s="604" t="s">
         <v>219</v>
       </c>
-      <c r="D200" s="595"/>
+      <c r="D200" s="605"/>
       <c r="E200" s="50"/>
       <c r="F200" s="42"/>
       <c r="G200" s="94">
         <f>G199/G196*12</f>
         <v>14729220</v>
       </c>
-      <c r="H200" s="627"/>
+      <c r="H200" s="673"/>
       <c r="I200" s="83"/>
       <c r="J200" s="94">
         <f>+G200/$J$5</f>
@@ -12134,17 +12134,17 @@
     <row r="201" spans="1:20" ht="15.9" customHeight="1">
       <c r="A201" s="66"/>
       <c r="B201" s="91"/>
-      <c r="C201" s="596" t="s">
+      <c r="C201" s="604" t="s">
         <v>220</v>
       </c>
-      <c r="D201" s="595"/>
+      <c r="D201" s="605"/>
       <c r="E201" s="50"/>
       <c r="F201" s="42"/>
       <c r="G201" s="94">
         <f>(+G220*115%)/5</f>
         <v>3026339.9999999995</v>
       </c>
-      <c r="H201" s="627"/>
+      <c r="H201" s="673"/>
       <c r="I201" s="83"/>
       <c r="J201" s="94">
         <f>+G201/$J$5</f>
@@ -12154,17 +12154,17 @@
     <row r="202" spans="1:20" ht="15.9" customHeight="1">
       <c r="A202" s="66"/>
       <c r="B202" s="91"/>
-      <c r="C202" s="596" t="s">
+      <c r="C202" s="604" t="s">
         <v>221</v>
       </c>
-      <c r="D202" s="595"/>
+      <c r="D202" s="605"/>
       <c r="E202" s="50"/>
       <c r="F202" s="42"/>
       <c r="G202" s="94">
         <f>(+I220*115%)/5</f>
         <v>2765157.6185172233</v>
       </c>
-      <c r="H202" s="627"/>
+      <c r="H202" s="673"/>
       <c r="I202" s="83"/>
       <c r="J202" s="94">
         <f>+G202/$J$5</f>
@@ -12174,17 +12174,17 @@
     <row r="203" spans="1:20" ht="15.9" customHeight="1">
       <c r="A203" s="66"/>
       <c r="B203" s="91"/>
-      <c r="C203" s="596" t="s">
+      <c r="C203" s="604" t="s">
         <v>36</v>
       </c>
-      <c r="D203" s="595"/>
+      <c r="D203" s="605"/>
       <c r="E203" s="50"/>
       <c r="F203" s="42"/>
       <c r="G203" s="94">
         <f>+G67</f>
         <v>11418000</v>
       </c>
-      <c r="H203" s="627"/>
+      <c r="H203" s="673"/>
       <c r="I203" s="83"/>
       <c r="J203" s="94">
         <f>+G203/$J$5</f>
@@ -12194,17 +12194,17 @@
     <row r="204" spans="1:20" ht="15.9" customHeight="1">
       <c r="A204" s="66"/>
       <c r="B204" s="91"/>
-      <c r="C204" s="594" t="s">
+      <c r="C204" s="598" t="s">
         <v>222</v>
       </c>
-      <c r="D204" s="595"/>
+      <c r="D204" s="605"/>
       <c r="E204" s="50"/>
       <c r="F204" s="42"/>
       <c r="G204" s="94">
         <f>(G200+G201+G202+G203)*1.18</f>
         <v>37687686.789850324</v>
       </c>
-      <c r="H204" s="627"/>
+      <c r="H204" s="673"/>
       <c r="I204" s="83"/>
       <c r="J204" s="94">
         <f>+J200+J201+J202+J203</f>
@@ -12214,17 +12214,17 @@
     <row r="205" spans="1:20" ht="15.9" customHeight="1">
       <c r="A205" s="66"/>
       <c r="B205" s="91"/>
-      <c r="C205" s="594" t="s">
+      <c r="C205" s="598" t="s">
         <v>223</v>
       </c>
-      <c r="D205" s="595"/>
+      <c r="D205" s="605"/>
       <c r="E205" s="50"/>
       <c r="F205" s="42"/>
       <c r="G205" s="94">
         <f>G204*1%</f>
         <v>376876.86789850326</v>
       </c>
-      <c r="H205" s="627"/>
+      <c r="H205" s="673"/>
       <c r="I205" s="83"/>
       <c r="J205" s="94">
         <f>J204*1%</f>
@@ -12234,17 +12234,17 @@
     <row r="206" spans="1:20" ht="15.9" customHeight="1">
       <c r="A206" s="66"/>
       <c r="B206" s="91"/>
-      <c r="C206" s="596" t="s">
+      <c r="C206" s="604" t="s">
         <v>224</v>
       </c>
-      <c r="D206" s="595"/>
+      <c r="D206" s="605"/>
       <c r="E206" s="50"/>
       <c r="F206" s="42"/>
       <c r="G206" s="94">
         <f>G204*0.5%</f>
         <v>188438.43394925163</v>
       </c>
-      <c r="H206" s="627"/>
+      <c r="H206" s="673"/>
       <c r="I206" s="83"/>
       <c r="J206" s="94">
         <f>J204*0.5%</f>
@@ -12254,17 +12254,17 @@
     <row r="207" spans="1:20" ht="15.9" customHeight="1">
       <c r="A207" s="66"/>
       <c r="B207" s="91"/>
-      <c r="C207" s="597" t="s">
+      <c r="C207" s="600" t="s">
         <v>215</v>
       </c>
-      <c r="D207" s="598"/>
+      <c r="D207" s="601"/>
       <c r="E207" s="50"/>
       <c r="F207" s="42"/>
       <c r="G207" s="94">
         <f>G205+G206</f>
         <v>565315.30184775486</v>
       </c>
-      <c r="H207" s="627"/>
+      <c r="H207" s="673"/>
       <c r="I207" s="83"/>
       <c r="J207" s="94">
         <v>0</v>
@@ -12279,7 +12279,7 @@
       <c r="E208" s="72"/>
       <c r="F208" s="43"/>
       <c r="G208" s="325"/>
-      <c r="H208" s="627"/>
+      <c r="H208" s="673"/>
       <c r="I208" s="86"/>
       <c r="J208" s="73"/>
     </row>
@@ -12301,7 +12301,7 @@
       <c r="G209" s="153" t="s">
         <v>229</v>
       </c>
-      <c r="H209" s="627"/>
+      <c r="H209" s="673"/>
       <c r="I209" s="367" t="s">
         <v>230</v>
       </c>
@@ -12327,7 +12327,7 @@
         <f>'Lease Rent'!P39</f>
         <v>1360000</v>
       </c>
-      <c r="H210" s="627"/>
+      <c r="H210" s="673"/>
       <c r="I210" s="93">
         <f>'Lease Rent'!O39</f>
         <v>1178337.5999999999</v>
@@ -12357,7 +12357,7 @@
         <f>'Lease Rent'!P51</f>
         <v>2040000</v>
       </c>
-      <c r="H211" s="627"/>
+      <c r="H211" s="673"/>
       <c r="I211" s="93">
         <f>'Lease Rent'!O51</f>
         <v>1826423.2800000005</v>
@@ -12386,7 +12386,7 @@
         <f>'Lease Rent'!P63</f>
         <v>2040000</v>
       </c>
-      <c r="H212" s="627"/>
+      <c r="H212" s="673"/>
       <c r="I212" s="93">
         <f>'Lease Rent'!O63</f>
         <v>1917744.4440000001</v>
@@ -12415,7 +12415,7 @@
         <f>'Lease Rent'!P75</f>
         <v>2244000</v>
       </c>
-      <c r="H213" s="627"/>
+      <c r="H213" s="673"/>
       <c r="I213" s="93">
         <f>'Lease Rent'!O75</f>
         <v>2013631.6662000006</v>
@@ -12444,7 +12444,7 @@
         <f>'Lease Rent'!P87</f>
         <v>2345999.9999999995</v>
       </c>
-      <c r="H214" s="627"/>
+      <c r="H214" s="673"/>
       <c r="I214" s="93">
         <f>'Lease Rent'!O87</f>
         <v>2114313.2495100005</v>
@@ -12473,7 +12473,7 @@
         <f>'Lease Rent'!P99</f>
         <v>2345999.9999999995</v>
       </c>
-      <c r="H215" s="627"/>
+      <c r="H215" s="673"/>
       <c r="I215" s="93">
         <f>'Lease Rent'!O99</f>
         <v>2220028.9119855007</v>
@@ -12501,7 +12501,7 @@
         <f>'Lease Rent'!P103</f>
         <v>781999.99999999988</v>
       </c>
-      <c r="H216" s="627"/>
+      <c r="H216" s="673"/>
       <c r="I216" s="93">
         <f>'Lease Rent'!O103</f>
         <v>751945.27664025011</v>
@@ -12524,7 +12524,7 @@
         <f>'Lease Rent'!R10</f>
         <v>0</v>
       </c>
-      <c r="H217" s="627"/>
+      <c r="H217" s="673"/>
       <c r="I217" s="289"/>
       <c r="J217" s="103"/>
     </row>
@@ -12541,7 +12541,7 @@
         <v>0</v>
       </c>
       <c r="G218" s="110"/>
-      <c r="H218" s="627"/>
+      <c r="H218" s="673"/>
       <c r="I218" s="93"/>
       <c r="J218" s="103"/>
     </row>
@@ -12555,7 +12555,7 @@
       <c r="E219" s="109"/>
       <c r="F219" s="220"/>
       <c r="G219" s="110"/>
-      <c r="H219" s="627"/>
+      <c r="H219" s="673"/>
       <c r="I219" s="93"/>
       <c r="J219" s="103"/>
     </row>
@@ -12578,7 +12578,7 @@
         <f>SUM(G210:G219)</f>
         <v>13158000</v>
       </c>
-      <c r="H220" s="628"/>
+      <c r="H220" s="674"/>
       <c r="I220" s="271">
         <f>SUM(I210:I219)</f>
         <v>12022424.428335754</v>
@@ -12648,35 +12648,190 @@
     </row>
   </sheetData>
   <mergeCells count="237">
-    <mergeCell ref="F137:G137"/>
-    <mergeCell ref="I137:J137"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C131:D131"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="B134:D134"/>
-    <mergeCell ref="C106:D106"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="B105:D105"/>
-    <mergeCell ref="C124:D124"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="C204:D204"/>
+    <mergeCell ref="C203:D203"/>
+    <mergeCell ref="C161:D161"/>
+    <mergeCell ref="B138:D138"/>
+    <mergeCell ref="C141:D141"/>
+    <mergeCell ref="C120:D120"/>
+    <mergeCell ref="C192:D192"/>
+    <mergeCell ref="C193:D193"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="C189:D189"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C160:D160"/>
+    <mergeCell ref="C190:D190"/>
+    <mergeCell ref="B179:D179"/>
+    <mergeCell ref="C162:D162"/>
+    <mergeCell ref="C165:D165"/>
+    <mergeCell ref="C205:D205"/>
+    <mergeCell ref="C206:D206"/>
+    <mergeCell ref="C207:D207"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C174:D174"/>
+    <mergeCell ref="C197:D197"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="C199:D199"/>
+    <mergeCell ref="C200:D200"/>
+    <mergeCell ref="C201:D201"/>
+    <mergeCell ref="C202:D202"/>
+    <mergeCell ref="C188:D188"/>
+    <mergeCell ref="C191:D191"/>
+    <mergeCell ref="C194:D194"/>
+    <mergeCell ref="C195:D195"/>
+    <mergeCell ref="C196:D196"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C181:D181"/>
+    <mergeCell ref="C185:D185"/>
+    <mergeCell ref="C168:D168"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="C169:D169"/>
+    <mergeCell ref="C183:D183"/>
+    <mergeCell ref="C170:D170"/>
+    <mergeCell ref="C140:D140"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="C122:D122"/>
+    <mergeCell ref="C171:D171"/>
+    <mergeCell ref="C167:D167"/>
+    <mergeCell ref="B147:D147"/>
+    <mergeCell ref="B163:D164"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="C144:D144"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="C166:D166"/>
+    <mergeCell ref="C182:D182"/>
+    <mergeCell ref="H188:H220"/>
+    <mergeCell ref="C159:D159"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B187:J187"/>
+    <mergeCell ref="C172:D172"/>
+    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="C177:D177"/>
+    <mergeCell ref="C180:D180"/>
+    <mergeCell ref="C157:D157"/>
+    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="C175:D175"/>
+    <mergeCell ref="C149:D149"/>
+    <mergeCell ref="C150:D150"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="C143:D143"/>
+    <mergeCell ref="C184:D184"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B1:J3"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C48:D48"/>
     <mergeCell ref="F52:G52"/>
     <mergeCell ref="F48:G48"/>
     <mergeCell ref="F49:G49"/>
@@ -12701,190 +12856,35 @@
     <mergeCell ref="C135:D135"/>
     <mergeCell ref="C136:D136"/>
     <mergeCell ref="C133:D133"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B1:J3"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="H188:H220"/>
-    <mergeCell ref="C159:D159"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B187:J187"/>
-    <mergeCell ref="C172:D172"/>
-    <mergeCell ref="C176:D176"/>
-    <mergeCell ref="C177:D177"/>
-    <mergeCell ref="C180:D180"/>
-    <mergeCell ref="C157:D157"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="C175:D175"/>
-    <mergeCell ref="C149:D149"/>
-    <mergeCell ref="C150:D150"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="I58:J58"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="C143:D143"/>
-    <mergeCell ref="C184:D184"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C181:D181"/>
-    <mergeCell ref="C185:D185"/>
-    <mergeCell ref="C168:D168"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="C169:D169"/>
-    <mergeCell ref="C183:D183"/>
-    <mergeCell ref="C170:D170"/>
-    <mergeCell ref="C140:D140"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="C122:D122"/>
-    <mergeCell ref="C171:D171"/>
-    <mergeCell ref="C167:D167"/>
-    <mergeCell ref="B147:D147"/>
-    <mergeCell ref="B163:D164"/>
-    <mergeCell ref="B125:D125"/>
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="C144:D144"/>
-    <mergeCell ref="C139:D139"/>
-    <mergeCell ref="C166:D166"/>
-    <mergeCell ref="C182:D182"/>
-    <mergeCell ref="C205:D205"/>
-    <mergeCell ref="C206:D206"/>
-    <mergeCell ref="C207:D207"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C174:D174"/>
-    <mergeCell ref="C197:D197"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="C199:D199"/>
-    <mergeCell ref="C200:D200"/>
-    <mergeCell ref="C201:D201"/>
-    <mergeCell ref="C202:D202"/>
-    <mergeCell ref="C188:D188"/>
-    <mergeCell ref="C191:D191"/>
-    <mergeCell ref="C194:D194"/>
-    <mergeCell ref="C195:D195"/>
-    <mergeCell ref="C196:D196"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C204:D204"/>
-    <mergeCell ref="C203:D203"/>
-    <mergeCell ref="C161:D161"/>
-    <mergeCell ref="B138:D138"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="C120:D120"/>
-    <mergeCell ref="C192:D192"/>
-    <mergeCell ref="C193:D193"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="C189:D189"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C160:D160"/>
-    <mergeCell ref="C190:D190"/>
-    <mergeCell ref="B179:D179"/>
-    <mergeCell ref="C162:D162"/>
-    <mergeCell ref="C165:D165"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="B134:D134"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="B105:D105"/>
+    <mergeCell ref="C124:D124"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="F137:G137"/>
+    <mergeCell ref="I137:J137"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C107:D107"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.25" top="0.75" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="58" orientation="portrait" r:id="rId1"/>
@@ -12957,32 +12957,32 @@
       <c r="S1" s="1"/>
     </row>
     <row r="2" spans="1:27" ht="11.25" customHeight="1">
-      <c r="A2" s="670"/>
-      <c r="B2" s="671"/>
-      <c r="C2" s="671"/>
-      <c r="D2" s="671"/>
-      <c r="E2" s="671"/>
-      <c r="F2" s="671"/>
-      <c r="G2" s="671"/>
-      <c r="H2" s="671"/>
-      <c r="I2" s="671"/>
-      <c r="J2" s="671"/>
-      <c r="K2" s="671"/>
-      <c r="L2" s="671"/>
-      <c r="M2" s="671"/>
-      <c r="N2" s="671"/>
-      <c r="O2" s="671"/>
-      <c r="P2" s="671"/>
-      <c r="Q2" s="671"/>
-      <c r="R2" s="671"/>
-      <c r="S2" s="671"/>
-      <c r="T2" s="671"/>
-      <c r="U2" s="671"/>
-      <c r="V2" s="671"/>
-      <c r="W2" s="671"/>
-      <c r="X2" s="671"/>
-      <c r="Y2" s="671"/>
-      <c r="Z2" s="671"/>
+      <c r="A2" s="658"/>
+      <c r="B2" s="659"/>
+      <c r="C2" s="659"/>
+      <c r="D2" s="659"/>
+      <c r="E2" s="659"/>
+      <c r="F2" s="659"/>
+      <c r="G2" s="659"/>
+      <c r="H2" s="659"/>
+      <c r="I2" s="659"/>
+      <c r="J2" s="659"/>
+      <c r="K2" s="659"/>
+      <c r="L2" s="659"/>
+      <c r="M2" s="659"/>
+      <c r="N2" s="659"/>
+      <c r="O2" s="659"/>
+      <c r="P2" s="659"/>
+      <c r="Q2" s="659"/>
+      <c r="R2" s="659"/>
+      <c r="S2" s="659"/>
+      <c r="T2" s="659"/>
+      <c r="U2" s="659"/>
+      <c r="V2" s="659"/>
+      <c r="W2" s="659"/>
+      <c r="X2" s="659"/>
+      <c r="Y2" s="659"/>
+      <c r="Z2" s="659"/>
       <c r="AA2" s="695"/>
     </row>
     <row r="3" spans="1:27" ht="11.25" customHeight="1">
@@ -13044,34 +13044,34 @@
       <c r="AA4" s="701"/>
     </row>
     <row r="5" spans="1:27" ht="12.75" customHeight="1">
-      <c r="A5" s="670" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="671"/>
-      <c r="C5" s="671"/>
-      <c r="D5" s="671"/>
-      <c r="E5" s="671"/>
-      <c r="F5" s="671"/>
-      <c r="G5" s="671"/>
-      <c r="H5" s="671"/>
-      <c r="I5" s="671"/>
-      <c r="J5" s="671"/>
-      <c r="K5" s="671"/>
-      <c r="L5" s="671"/>
-      <c r="M5" s="671"/>
-      <c r="N5" s="671"/>
-      <c r="O5" s="671"/>
-      <c r="P5" s="671"/>
-      <c r="Q5" s="671"/>
-      <c r="R5" s="671"/>
-      <c r="S5" s="671"/>
-      <c r="T5" s="671"/>
-      <c r="U5" s="671"/>
-      <c r="V5" s="671"/>
-      <c r="W5" s="671"/>
-      <c r="X5" s="671"/>
-      <c r="Y5" s="671"/>
-      <c r="Z5" s="671"/>
+      <c r="A5" s="658" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="659"/>
+      <c r="C5" s="659"/>
+      <c r="D5" s="659"/>
+      <c r="E5" s="659"/>
+      <c r="F5" s="659"/>
+      <c r="G5" s="659"/>
+      <c r="H5" s="659"/>
+      <c r="I5" s="659"/>
+      <c r="J5" s="659"/>
+      <c r="K5" s="659"/>
+      <c r="L5" s="659"/>
+      <c r="M5" s="659"/>
+      <c r="N5" s="659"/>
+      <c r="O5" s="659"/>
+      <c r="P5" s="659"/>
+      <c r="Q5" s="659"/>
+      <c r="R5" s="659"/>
+      <c r="S5" s="659"/>
+      <c r="T5" s="659"/>
+      <c r="U5" s="659"/>
+      <c r="V5" s="659"/>
+      <c r="W5" s="659"/>
+      <c r="X5" s="659"/>
+      <c r="Y5" s="659"/>
+      <c r="Z5" s="659"/>
       <c r="AA5" s="695"/>
     </row>
     <row r="6" spans="1:27" ht="13.5" customHeight="1">
@@ -24201,27 +24201,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" xsi:nil="true"/>
-    <Status xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100907921E7373C1341A3C877D189CE8922" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2036b66ca2b7955135caa708c7901a86">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xmlns:ns3="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fed2217af4f675ffeab875e34aa73a78" ns2:_="" ns3:_="">
     <xsd:import namespace="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
@@ -24464,26 +24443,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC57694E-BA35-486E-AC74-B7B624F1FDE0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8" xsi:nil="true"/>
+    <Status xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12D5BE44-B07C-4182-BC7A-71E5962390BD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
-    <ds:schemaRef ds:uri="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB719E29-C329-4AB1-8ED0-5CC29C0FF757}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24502,6 +24483,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12D5BE44-B07C-4182-BC7A-71E5962390BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1"/>
+    <ds:schemaRef ds:uri="c08142bf-fe70-4204-ae0f-fc8dda0aa6d8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC57694E-BA35-486E-AC74-B7B624F1FDE0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{a59b6cd5-d141-4a33-8bf1-0ca04484304f}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" removed="0"/>

--- a/artifacts/Rental Specimen.xlsx
+++ b/artifacts/Rental Specimen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z0050s8t\Documents\rental-automation\artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1051DB5E-6430-4095-987A-803B467179E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4FCAA39-B4B3-4DA6-B837-6F282600495B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="764" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="764" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="26" r:id="rId1"/>
@@ -5562,9 +5562,132 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="184" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="184" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="184" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5574,284 +5697,161 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="33" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="29" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="33" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="29" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7489,62 +7489,62 @@
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1">
       <c r="A1" s="43"/>
-      <c r="B1" s="633"/>
-      <c r="C1" s="634"/>
-      <c r="D1" s="634"/>
-      <c r="E1" s="634"/>
-      <c r="F1" s="634"/>
-      <c r="G1" s="634"/>
-      <c r="H1" s="634"/>
-      <c r="I1" s="634"/>
-      <c r="J1" s="635"/>
+      <c r="B1" s="643"/>
+      <c r="C1" s="644"/>
+      <c r="D1" s="644"/>
+      <c r="E1" s="644"/>
+      <c r="F1" s="644"/>
+      <c r="G1" s="644"/>
+      <c r="H1" s="644"/>
+      <c r="I1" s="644"/>
+      <c r="J1" s="645"/>
     </row>
     <row r="2" spans="1:10" ht="14.25" customHeight="1">
       <c r="A2" s="43"/>
-      <c r="B2" s="636"/>
-      <c r="C2" s="637"/>
-      <c r="D2" s="637"/>
-      <c r="E2" s="637"/>
-      <c r="F2" s="637"/>
-      <c r="G2" s="637"/>
-      <c r="H2" s="637"/>
-      <c r="I2" s="637"/>
-      <c r="J2" s="638"/>
+      <c r="B2" s="646"/>
+      <c r="C2" s="647"/>
+      <c r="D2" s="647"/>
+      <c r="E2" s="647"/>
+      <c r="F2" s="647"/>
+      <c r="G2" s="647"/>
+      <c r="H2" s="647"/>
+      <c r="I2" s="647"/>
+      <c r="J2" s="648"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A3" s="43"/>
-      <c r="B3" s="639"/>
-      <c r="C3" s="640"/>
-      <c r="D3" s="640"/>
-      <c r="E3" s="640"/>
-      <c r="F3" s="640"/>
-      <c r="G3" s="640"/>
-      <c r="H3" s="640"/>
-      <c r="I3" s="637"/>
-      <c r="J3" s="638"/>
+      <c r="B3" s="649"/>
+      <c r="C3" s="650"/>
+      <c r="D3" s="650"/>
+      <c r="E3" s="650"/>
+      <c r="F3" s="650"/>
+      <c r="G3" s="650"/>
+      <c r="H3" s="650"/>
+      <c r="I3" s="647"/>
+      <c r="J3" s="648"/>
     </row>
     <row r="4" spans="1:10" ht="13">
       <c r="A4" s="43"/>
-      <c r="B4" s="658"/>
-      <c r="C4" s="659"/>
-      <c r="D4" s="659"/>
-      <c r="E4" s="659"/>
-      <c r="F4" s="659"/>
-      <c r="G4" s="659"/>
+      <c r="B4" s="670"/>
+      <c r="C4" s="671"/>
+      <c r="D4" s="671"/>
+      <c r="E4" s="671"/>
+      <c r="F4" s="671"/>
+      <c r="G4" s="671"/>
       <c r="H4" s="389"/>
       <c r="I4" s="390"/>
       <c r="J4" s="391"/>
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="43"/>
-      <c r="B5" s="660" t="s">
+      <c r="B5" s="672" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="661"/>
-      <c r="D5" s="661"/>
-      <c r="E5" s="661"/>
-      <c r="F5" s="661"/>
-      <c r="G5" s="662"/>
+      <c r="C5" s="673"/>
+      <c r="D5" s="673"/>
+      <c r="E5" s="673"/>
+      <c r="F5" s="673"/>
+      <c r="G5" s="674"/>
       <c r="H5" s="392"/>
       <c r="I5" s="469" t="s">
         <v>16</v>
@@ -7555,29 +7555,29 @@
     </row>
     <row r="6" spans="1:10" ht="13.5" thickBot="1">
       <c r="A6" s="43"/>
-      <c r="B6" s="663"/>
-      <c r="C6" s="664"/>
-      <c r="D6" s="665"/>
+      <c r="B6" s="675"/>
+      <c r="C6" s="676"/>
+      <c r="D6" s="677"/>
       <c r="E6" s="44"/>
-      <c r="F6" s="656">
+      <c r="F6" s="668">
         <v>10.763999999999999</v>
       </c>
-      <c r="G6" s="657"/>
+      <c r="G6" s="669"/>
       <c r="H6" s="393"/>
-      <c r="I6" s="647">
+      <c r="I6" s="656">
         <v>10.763999999999999</v>
       </c>
-      <c r="J6" s="648"/>
+      <c r="J6" s="657"/>
     </row>
     <row r="7" spans="1:10" ht="26">
       <c r="A7" s="43"/>
       <c r="B7" s="470" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="666" t="s">
+      <c r="C7" s="678" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="667"/>
+      <c r="D7" s="679"/>
       <c r="E7" s="471"/>
       <c r="F7" s="471" t="s">
         <v>299</v>
@@ -7605,23 +7605,23 @@
       <c r="C8" s="474"/>
       <c r="D8" s="475"/>
       <c r="E8" s="476"/>
-      <c r="F8" s="594" t="s">
+      <c r="F8" s="602" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="595"/>
+      <c r="G8" s="636"/>
       <c r="H8" s="392"/>
-      <c r="I8" s="596" t="s">
+      <c r="I8" s="637" t="s">
         <v>63</v>
       </c>
-      <c r="J8" s="597"/>
+      <c r="J8" s="638"/>
     </row>
     <row r="9" spans="1:10" ht="13">
       <c r="A9" s="43"/>
-      <c r="B9" s="596" t="s">
+      <c r="B9" s="637" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="595"/>
-      <c r="D9" s="611"/>
+      <c r="C9" s="636"/>
+      <c r="D9" s="603"/>
       <c r="E9" s="477"/>
       <c r="F9" s="364" t="s">
         <v>71</v>
@@ -7642,21 +7642,21 @@
       <c r="B10" s="478">
         <v>1</v>
       </c>
-      <c r="C10" s="641" t="s">
+      <c r="C10" s="651" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="642"/>
+      <c r="D10" s="610"/>
       <c r="E10" s="479"/>
-      <c r="F10" s="653" t="s">
+      <c r="F10" s="662" t="s">
         <v>295</v>
       </c>
-      <c r="G10" s="654"/>
+      <c r="G10" s="663"/>
       <c r="H10" s="392"/>
-      <c r="I10" s="649" t="str">
+      <c r="I10" s="658" t="str">
         <f>+F10</f>
         <v>Chennai</v>
       </c>
-      <c r="J10" s="650"/>
+      <c r="J10" s="659"/>
     </row>
     <row r="11" spans="1:10" ht="28.5" customHeight="1">
       <c r="A11" s="43"/>
@@ -7664,19 +7664,19 @@
         <f>1+B10</f>
         <v>2</v>
       </c>
-      <c r="C11" s="643" t="s">
+      <c r="C11" s="652" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="644"/>
+      <c r="D11" s="653"/>
       <c r="E11" s="42"/>
-      <c r="F11" s="653"/>
-      <c r="G11" s="654"/>
+      <c r="F11" s="662"/>
+      <c r="G11" s="663"/>
       <c r="H11" s="392"/>
-      <c r="I11" s="651">
+      <c r="I11" s="660">
         <f>+F11</f>
         <v>0</v>
       </c>
-      <c r="J11" s="652"/>
+      <c r="J11" s="661"/>
     </row>
     <row r="12" spans="1:10" ht="27.75" customHeight="1">
       <c r="A12" s="43"/>
@@ -7684,19 +7684,19 @@
         <f>1+B11</f>
         <v>3</v>
       </c>
-      <c r="C12" s="604" t="s">
+      <c r="C12" s="596" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="605"/>
+      <c r="D12" s="595"/>
       <c r="E12" s="480"/>
-      <c r="F12" s="632"/>
-      <c r="G12" s="627"/>
+      <c r="F12" s="664"/>
+      <c r="G12" s="665"/>
       <c r="H12" s="392"/>
-      <c r="I12" s="628">
+      <c r="I12" s="680">
         <f>+F12</f>
         <v>0</v>
       </c>
-      <c r="J12" s="629"/>
+      <c r="J12" s="681"/>
     </row>
     <row r="13" spans="1:10" ht="15.9" customHeight="1">
       <c r="A13" s="43"/>
@@ -7704,16 +7704,16 @@
         <f t="shared" ref="B13:B30" si="0">1+B12</f>
         <v>4</v>
       </c>
-      <c r="C13" s="604" t="s">
+      <c r="C13" s="596" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="605"/>
+      <c r="D13" s="595"/>
       <c r="E13" s="42"/>
-      <c r="F13" s="626"/>
-      <c r="G13" s="627"/>
+      <c r="F13" s="667"/>
+      <c r="G13" s="665"/>
       <c r="H13" s="392"/>
-      <c r="I13" s="628"/>
-      <c r="J13" s="629"/>
+      <c r="I13" s="680"/>
+      <c r="J13" s="681"/>
     </row>
     <row r="14" spans="1:10" ht="48" customHeight="1">
       <c r="A14" s="43"/>
@@ -7721,21 +7721,21 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="645" t="s">
+      <c r="C14" s="654" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="646"/>
+      <c r="D14" s="655"/>
       <c r="E14" s="464"/>
-      <c r="F14" s="632" t="s">
+      <c r="F14" s="664" t="s">
         <v>296</v>
       </c>
-      <c r="G14" s="655"/>
+      <c r="G14" s="666"/>
       <c r="H14" s="392"/>
-      <c r="I14" s="628" t="str">
+      <c r="I14" s="680" t="str">
         <f>+F14</f>
         <v>6th floor</v>
       </c>
-      <c r="J14" s="629"/>
+      <c r="J14" s="681"/>
     </row>
     <row r="15" spans="1:10" ht="51.75" customHeight="1">
       <c r="A15" s="43"/>
@@ -7743,19 +7743,19 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="604" t="s">
+      <c r="C15" s="596" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="605"/>
+      <c r="D15" s="595"/>
       <c r="E15" s="50"/>
-      <c r="F15" s="594"/>
-      <c r="G15" s="595"/>
+      <c r="F15" s="602"/>
+      <c r="G15" s="636"/>
       <c r="H15" s="392"/>
-      <c r="I15" s="596">
+      <c r="I15" s="637">
         <f>+F15</f>
         <v>0</v>
       </c>
-      <c r="J15" s="597"/>
+      <c r="J15" s="638"/>
     </row>
     <row r="16" spans="1:10" ht="15.9" customHeight="1">
       <c r="A16" s="43"/>
@@ -7763,16 +7763,16 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="604" t="s">
+      <c r="C16" s="596" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="605"/>
+      <c r="D16" s="595"/>
       <c r="E16" s="50"/>
-      <c r="F16" s="626"/>
-      <c r="G16" s="627"/>
+      <c r="F16" s="667"/>
+      <c r="G16" s="665"/>
       <c r="H16" s="392"/>
-      <c r="I16" s="628"/>
-      <c r="J16" s="629"/>
+      <c r="I16" s="680"/>
+      <c r="J16" s="681"/>
     </row>
     <row r="17" spans="1:10" ht="15.9" customHeight="1">
       <c r="A17" s="43"/>
@@ -7780,21 +7780,21 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="604" t="s">
+      <c r="C17" s="596" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="605"/>
+      <c r="D17" s="595"/>
       <c r="E17" s="50"/>
-      <c r="F17" s="632" t="s">
+      <c r="F17" s="664" t="s">
         <v>81</v>
       </c>
-      <c r="G17" s="627"/>
+      <c r="G17" s="665"/>
       <c r="H17" s="392"/>
-      <c r="I17" s="628" t="str">
+      <c r="I17" s="680" t="str">
         <f>+F17</f>
         <v>Warm Shell</v>
       </c>
-      <c r="J17" s="629"/>
+      <c r="J17" s="681"/>
     </row>
     <row r="18" spans="1:10" ht="48" customHeight="1">
       <c r="A18" s="43"/>
@@ -7802,22 +7802,22 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="604" t="s">
+      <c r="C18" s="596" t="s">
         <v>82</v>
       </c>
-      <c r="D18" s="605"/>
+      <c r="D18" s="595"/>
       <c r="E18" s="155"/>
-      <c r="F18" s="594">
+      <c r="F18" s="602">
         <f>F15</f>
         <v>0</v>
       </c>
-      <c r="G18" s="595"/>
+      <c r="G18" s="636"/>
       <c r="H18" s="392"/>
-      <c r="I18" s="596">
+      <c r="I18" s="637">
         <f>+F18</f>
         <v>0</v>
       </c>
-      <c r="J18" s="597"/>
+      <c r="J18" s="638"/>
     </row>
     <row r="19" spans="1:10" ht="15.9" customHeight="1">
       <c r="A19" s="43"/>
@@ -7825,16 +7825,16 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="604" t="s">
+      <c r="C19" s="596" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="605"/>
+      <c r="D19" s="595"/>
       <c r="E19" s="155"/>
-      <c r="F19" s="626"/>
-      <c r="G19" s="627"/>
+      <c r="F19" s="667"/>
+      <c r="G19" s="665"/>
       <c r="H19" s="392"/>
-      <c r="I19" s="628"/>
-      <c r="J19" s="629"/>
+      <c r="I19" s="680"/>
+      <c r="J19" s="681"/>
     </row>
     <row r="20" spans="1:10" ht="15.9" customHeight="1">
       <c r="A20" s="43"/>
@@ -7842,10 +7842,10 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="598" t="s">
+      <c r="C20" s="594" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="605"/>
+      <c r="D20" s="595"/>
       <c r="E20" s="482"/>
       <c r="F20" s="48"/>
       <c r="G20" s="376"/>
@@ -7865,10 +7865,10 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="604" t="s">
+      <c r="C21" s="596" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="605"/>
+      <c r="D21" s="595"/>
       <c r="E21" s="482"/>
       <c r="F21" s="48">
         <f>Main!B3</f>
@@ -7894,10 +7894,10 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="598" t="s">
+      <c r="C22" s="594" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="605"/>
+      <c r="D22" s="595"/>
       <c r="E22" s="482"/>
       <c r="F22" s="48">
         <v>0</v>
@@ -7921,10 +7921,10 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="604" t="s">
+      <c r="C23" s="596" t="s">
         <v>87</v>
       </c>
-      <c r="D23" s="605"/>
+      <c r="D23" s="595"/>
       <c r="E23" s="482"/>
       <c r="F23" s="48">
         <f>+F21+F22</f>
@@ -7950,10 +7950,10 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="604" t="s">
+      <c r="C24" s="596" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="605"/>
+      <c r="D24" s="595"/>
       <c r="E24" s="51"/>
       <c r="F24" s="48"/>
       <c r="G24" s="376">
@@ -7976,10 +7976,10 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="604" t="s">
+      <c r="C25" s="596" t="s">
         <v>89</v>
       </c>
-      <c r="D25" s="605"/>
+      <c r="D25" s="595"/>
       <c r="E25" s="51"/>
       <c r="F25" s="48">
         <v>0</v>
@@ -8004,10 +8004,10 @@
         <f>1+B25</f>
         <v>17</v>
       </c>
-      <c r="C26" s="604" t="s">
+      <c r="C26" s="596" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="605"/>
+      <c r="D26" s="595"/>
       <c r="E26" s="52"/>
       <c r="F26" s="53">
         <f>F25/F23</f>
@@ -8033,10 +8033,10 @@
         <f>1+B26</f>
         <v>18</v>
       </c>
-      <c r="C27" s="598" t="s">
+      <c r="C27" s="594" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="605"/>
+      <c r="D27" s="595"/>
       <c r="E27" s="50"/>
       <c r="F27" s="281">
         <f>'CAPEX and PM'!E3</f>
@@ -8062,10 +8062,10 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="598" t="s">
+      <c r="C28" s="594" t="s">
         <v>92</v>
       </c>
-      <c r="D28" s="605"/>
+      <c r="D28" s="595"/>
       <c r="E28" s="56"/>
       <c r="F28" s="56">
         <f>Main!B12</f>
@@ -8091,10 +8091,10 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="598" t="s">
+      <c r="C29" s="594" t="s">
         <v>93</v>
       </c>
-      <c r="D29" s="605"/>
+      <c r="D29" s="595"/>
       <c r="E29" s="56"/>
       <c r="F29" s="52">
         <f>Main!B13</f>
@@ -8120,10 +8120,10 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="604" t="s">
+      <c r="C30" s="596" t="s">
         <v>94</v>
       </c>
-      <c r="D30" s="605"/>
+      <c r="D30" s="595"/>
       <c r="E30" s="50"/>
       <c r="F30" s="48">
         <v>0</v>
@@ -8144,11 +8144,11 @@
     </row>
     <row r="31" spans="1:10" ht="15.9" customHeight="1">
       <c r="A31" s="43"/>
-      <c r="B31" s="623" t="s">
+      <c r="B31" s="682" t="s">
         <v>95</v>
       </c>
-      <c r="C31" s="624"/>
-      <c r="D31" s="625"/>
+      <c r="C31" s="683"/>
+      <c r="D31" s="684"/>
       <c r="E31" s="485"/>
       <c r="F31" s="364" t="s">
         <v>71</v>
@@ -8169,10 +8169,10 @@
       <c r="B32" s="154">
         <v>1</v>
       </c>
-      <c r="C32" s="598" t="s">
+      <c r="C32" s="594" t="s">
         <v>96</v>
       </c>
-      <c r="D32" s="605"/>
+      <c r="D32" s="595"/>
       <c r="E32" s="51"/>
       <c r="F32" s="48">
         <f>Main!B9/(Main!B3*Main!B7)</f>
@@ -8198,10 +8198,10 @@
         <f>1+B32</f>
         <v>2</v>
       </c>
-      <c r="C33" s="598" t="s">
+      <c r="C33" s="594" t="s">
         <v>97</v>
       </c>
-      <c r="D33" s="605"/>
+      <c r="D33" s="595"/>
       <c r="E33" s="51"/>
       <c r="F33" s="48">
         <v>0</v>
@@ -8225,10 +8225,10 @@
         <f t="shared" ref="B34:B47" si="1">1+B33</f>
         <v>3</v>
       </c>
-      <c r="C34" s="598" t="s">
+      <c r="C34" s="594" t="s">
         <v>98</v>
       </c>
-      <c r="D34" s="605"/>
+      <c r="D34" s="595"/>
       <c r="E34" s="51"/>
       <c r="F34" s="48">
         <v>0</v>
@@ -8253,10 +8253,10 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="C35" s="604" t="s">
+      <c r="C35" s="596" t="s">
         <v>99</v>
       </c>
-      <c r="D35" s="605"/>
+      <c r="D35" s="595"/>
       <c r="E35" s="486"/>
       <c r="F35" s="60">
         <v>0</v>
@@ -8278,10 +8278,10 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="C36" s="598" t="s">
+      <c r="C36" s="594" t="s">
         <v>100</v>
       </c>
-      <c r="D36" s="605"/>
+      <c r="D36" s="595"/>
       <c r="E36" s="486"/>
       <c r="F36" s="62">
         <f>'Lease Rent'!H37</f>
@@ -8307,10 +8307,10 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="C37" s="598" t="s">
+      <c r="C37" s="594" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="605"/>
+      <c r="D37" s="595"/>
       <c r="E37" s="486"/>
       <c r="F37" s="62"/>
       <c r="G37" s="192">
@@ -8327,10 +8327,10 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="C38" s="598" t="s">
+      <c r="C38" s="594" t="s">
         <v>102</v>
       </c>
-      <c r="D38" s="605"/>
+      <c r="D38" s="595"/>
       <c r="E38" s="63"/>
       <c r="F38" s="62">
         <f>'Lease Rent'!J31</f>
@@ -8356,10 +8356,10 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="C39" s="598" t="s">
+      <c r="C39" s="594" t="s">
         <v>103</v>
       </c>
-      <c r="D39" s="605"/>
+      <c r="D39" s="595"/>
       <c r="E39" s="486"/>
       <c r="F39" s="62">
         <f>F36</f>
@@ -8385,10 +8385,10 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="C40" s="598" t="s">
+      <c r="C40" s="594" t="s">
         <v>104</v>
       </c>
-      <c r="D40" s="605"/>
+      <c r="D40" s="595"/>
       <c r="E40" s="486"/>
       <c r="F40" s="62">
         <v>0</v>
@@ -8413,10 +8413,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="C41" s="598" t="s">
+      <c r="C41" s="594" t="s">
         <v>105</v>
       </c>
-      <c r="D41" s="605"/>
+      <c r="D41" s="595"/>
       <c r="E41" s="50"/>
       <c r="F41" s="106">
         <f>F38</f>
@@ -8442,10 +8442,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="C42" s="604" t="s">
+      <c r="C42" s="596" t="s">
         <v>106</v>
       </c>
-      <c r="D42" s="605"/>
+      <c r="D42" s="595"/>
       <c r="E42" s="51"/>
       <c r="F42" s="101">
         <v>0</v>
@@ -8470,10 +8470,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="C43" s="604" t="s">
+      <c r="C43" s="596" t="s">
         <v>107</v>
       </c>
-      <c r="D43" s="605"/>
+      <c r="D43" s="595"/>
       <c r="E43" s="65"/>
       <c r="F43" s="60">
         <f>'Lease Rent'!D22</f>
@@ -8499,10 +8499,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="C44" s="604" t="s">
+      <c r="C44" s="596" t="s">
         <v>108</v>
       </c>
-      <c r="D44" s="605"/>
+      <c r="D44" s="595"/>
       <c r="E44" s="51"/>
       <c r="F44" s="48">
         <f>'Lease Rent'!C22</f>
@@ -8528,10 +8528,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="C45" s="598" t="s">
+      <c r="C45" s="594" t="s">
         <v>109</v>
       </c>
-      <c r="D45" s="605"/>
+      <c r="D45" s="595"/>
       <c r="E45" s="51"/>
       <c r="F45" s="101">
         <v>0</v>
@@ -8553,10 +8553,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="C46" s="604" t="s">
+      <c r="C46" s="596" t="s">
         <v>331</v>
       </c>
-      <c r="D46" s="605"/>
+      <c r="D46" s="595"/>
       <c r="E46" s="51"/>
       <c r="F46" s="48">
         <f>'Lease Rent'!D23</f>
@@ -8573,10 +8573,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="C47" s="604" t="s">
+      <c r="C47" s="596" t="s">
         <v>332</v>
       </c>
-      <c r="D47" s="605"/>
+      <c r="D47" s="595"/>
       <c r="E47" s="51"/>
       <c r="F47" s="48">
         <f>'Lease Rent'!C23</f>
@@ -8589,46 +8589,46 @@
     </row>
     <row r="48" spans="1:10" ht="28.5" customHeight="1">
       <c r="A48" s="43"/>
-      <c r="B48" s="670">
+      <c r="B48" s="641">
         <f>1+B47</f>
         <v>17</v>
       </c>
-      <c r="C48" s="598" t="s">
+      <c r="C48" s="594" t="s">
         <v>110</v>
       </c>
-      <c r="D48" s="605"/>
+      <c r="D48" s="595"/>
       <c r="E48" s="65"/>
-      <c r="F48" s="614" t="str">
+      <c r="F48" s="687" t="str">
         <f>Main!B14</f>
         <v>15% every 3 years</v>
       </c>
-      <c r="G48" s="615"/>
+      <c r="G48" s="688"/>
       <c r="H48" s="392"/>
-      <c r="I48" s="628" t="str">
+      <c r="I48" s="680" t="str">
         <f>+F48</f>
         <v>15% every 3 years</v>
       </c>
-      <c r="J48" s="629"/>
+      <c r="J48" s="681"/>
     </row>
     <row r="49" spans="1:18" ht="15.9" customHeight="1">
       <c r="A49" s="43"/>
-      <c r="B49" s="671"/>
-      <c r="C49" s="598" t="s">
+      <c r="B49" s="642"/>
+      <c r="C49" s="594" t="s">
         <v>111</v>
       </c>
-      <c r="D49" s="605"/>
+      <c r="D49" s="595"/>
       <c r="E49" s="65"/>
-      <c r="F49" s="614" t="str">
+      <c r="F49" s="687" t="str">
         <f>Main!B15</f>
         <v>5% every years</v>
       </c>
-      <c r="G49" s="615"/>
+      <c r="G49" s="688"/>
       <c r="H49" s="392"/>
-      <c r="I49" s="630" t="str">
+      <c r="I49" s="685" t="str">
         <f t="shared" ref="I49:I56" si="2">F49</f>
         <v>5% every years</v>
       </c>
-      <c r="J49" s="631"/>
+      <c r="J49" s="686"/>
     </row>
     <row r="50" spans="1:18" ht="15.9" customHeight="1">
       <c r="A50" s="43"/>
@@ -8636,22 +8636,22 @@
         <f>1+B48</f>
         <v>18</v>
       </c>
-      <c r="C50" s="604" t="s">
+      <c r="C50" s="596" t="s">
         <v>112</v>
       </c>
-      <c r="D50" s="605"/>
+      <c r="D50" s="595"/>
       <c r="E50" s="65"/>
-      <c r="F50" s="612">
+      <c r="F50" s="632">
         <f>'Lease Rent'!B31</f>
         <v>46023</v>
       </c>
-      <c r="G50" s="613"/>
+      <c r="G50" s="633"/>
       <c r="H50" s="392"/>
-      <c r="I50" s="621">
+      <c r="I50" s="634">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J50" s="622"/>
+      <c r="J50" s="635"/>
     </row>
     <row r="51" spans="1:18" ht="15.9" customHeight="1">
       <c r="A51" s="43"/>
@@ -8659,22 +8659,22 @@
         <f t="shared" ref="B51:B57" si="3">1+B50</f>
         <v>19</v>
       </c>
-      <c r="C51" s="598" t="s">
+      <c r="C51" s="594" t="s">
         <v>113</v>
       </c>
-      <c r="D51" s="605"/>
+      <c r="D51" s="595"/>
       <c r="E51" s="65"/>
-      <c r="F51" s="612">
+      <c r="F51" s="632">
         <f>'Lease Rent'!C102</f>
         <v>48213</v>
       </c>
-      <c r="G51" s="613"/>
+      <c r="G51" s="633"/>
       <c r="H51" s="392"/>
-      <c r="I51" s="621">
+      <c r="I51" s="634">
         <f>F51</f>
         <v>48213</v>
       </c>
-      <c r="J51" s="622"/>
+      <c r="J51" s="635"/>
     </row>
     <row r="52" spans="1:18" ht="15.9" customHeight="1">
       <c r="A52" s="43"/>
@@ -8682,22 +8682,22 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="C52" s="598" t="s">
+      <c r="C52" s="594" t="s">
         <v>114</v>
       </c>
-      <c r="D52" s="599"/>
+      <c r="D52" s="604"/>
       <c r="E52" s="65"/>
-      <c r="F52" s="612">
+      <c r="F52" s="632">
         <f>F50</f>
         <v>46023</v>
       </c>
-      <c r="G52" s="613"/>
+      <c r="G52" s="633"/>
       <c r="H52" s="392"/>
-      <c r="I52" s="621">
+      <c r="I52" s="634">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J52" s="622"/>
+      <c r="J52" s="635"/>
     </row>
     <row r="53" spans="1:18" ht="15.9" customHeight="1">
       <c r="A53" s="43"/>
@@ -8705,21 +8705,21 @@
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="C53" s="598" t="s">
+      <c r="C53" s="594" t="s">
         <v>115</v>
       </c>
-      <c r="D53" s="599"/>
+      <c r="D53" s="604"/>
       <c r="E53" s="65"/>
-      <c r="F53" s="594">
-        <v>0</v>
-      </c>
-      <c r="G53" s="595"/>
+      <c r="F53" s="602">
+        <v>0</v>
+      </c>
+      <c r="G53" s="636"/>
       <c r="H53" s="392"/>
-      <c r="I53" s="596">
+      <c r="I53" s="637">
         <f>+F53</f>
         <v>0</v>
       </c>
-      <c r="J53" s="597"/>
+      <c r="J53" s="638"/>
     </row>
     <row r="54" spans="1:18" ht="15.9" customHeight="1">
       <c r="A54" s="43"/>
@@ -8727,10 +8727,10 @@
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="C54" s="604" t="s">
+      <c r="C54" s="596" t="s">
         <v>116</v>
       </c>
-      <c r="D54" s="605"/>
+      <c r="D54" s="595"/>
       <c r="E54" s="50"/>
       <c r="F54" s="48">
         <f>(F51-F50)/365*12</f>
@@ -8757,10 +8757,10 @@
         <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="C55" s="604" t="s">
+      <c r="C55" s="596" t="s">
         <v>117</v>
       </c>
-      <c r="D55" s="605"/>
+      <c r="D55" s="595"/>
       <c r="E55" s="63"/>
       <c r="F55" s="48">
         <v>0</v>
@@ -8786,10 +8786,10 @@
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="C56" s="604" t="s">
+      <c r="C56" s="596" t="s">
         <v>118</v>
       </c>
-      <c r="D56" s="605"/>
+      <c r="D56" s="595"/>
       <c r="E56" s="63"/>
       <c r="F56" s="290" t="s">
         <v>64</v>
@@ -8815,10 +8815,10 @@
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="C57" s="604" t="s">
+      <c r="C57" s="596" t="s">
         <v>119</v>
       </c>
-      <c r="D57" s="605"/>
+      <c r="D57" s="595"/>
       <c r="E57" s="63"/>
       <c r="F57" s="48"/>
       <c r="G57" s="376"/>
@@ -8833,23 +8833,23 @@
       <c r="C58" s="66"/>
       <c r="D58" s="66"/>
       <c r="E58" s="50"/>
-      <c r="F58" s="594" t="s">
+      <c r="F58" s="602" t="s">
         <v>69</v>
       </c>
-      <c r="G58" s="595"/>
+      <c r="G58" s="636"/>
       <c r="H58" s="392"/>
-      <c r="I58" s="596" t="s">
+      <c r="I58" s="637" t="s">
         <v>63</v>
       </c>
-      <c r="J58" s="597"/>
+      <c r="J58" s="638"/>
     </row>
     <row r="59" spans="1:18" ht="15.9" customHeight="1">
       <c r="A59" s="43"/>
-      <c r="B59" s="668" t="s">
+      <c r="B59" s="639" t="s">
         <v>120</v>
       </c>
-      <c r="C59" s="669"/>
-      <c r="D59" s="669"/>
+      <c r="C59" s="640"/>
+      <c r="D59" s="640"/>
       <c r="E59" s="485"/>
       <c r="F59" s="364" t="s">
         <v>71</v>
@@ -8870,10 +8870,10 @@
       <c r="B60" s="154">
         <v>1</v>
       </c>
-      <c r="C60" s="598" t="s">
+      <c r="C60" s="594" t="s">
         <v>121</v>
       </c>
-      <c r="D60" s="605"/>
+      <c r="D60" s="595"/>
       <c r="E60" s="487"/>
       <c r="F60" s="62">
         <f>C220/F21/F54</f>
@@ -8899,10 +8899,10 @@
         <f>1+B60</f>
         <v>2</v>
       </c>
-      <c r="C61" s="598" t="s">
+      <c r="C61" s="594" t="s">
         <v>122</v>
       </c>
-      <c r="D61" s="605"/>
+      <c r="D61" s="595"/>
       <c r="E61" s="487"/>
       <c r="F61" s="62">
         <v>0</v>
@@ -8926,10 +8926,10 @@
         <f t="shared" ref="B62:B83" si="4">1+B61</f>
         <v>3</v>
       </c>
-      <c r="C62" s="600" t="s">
+      <c r="C62" s="597" t="s">
         <v>123</v>
       </c>
-      <c r="D62" s="601"/>
+      <c r="D62" s="598"/>
       <c r="E62" s="67"/>
       <c r="F62" s="68">
         <f>F60+F61</f>
@@ -8955,10 +8955,10 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="C63" s="598" t="s">
+      <c r="C63" s="594" t="s">
         <v>317</v>
       </c>
-      <c r="D63" s="605"/>
+      <c r="D63" s="595"/>
       <c r="E63" s="48"/>
       <c r="F63" s="46">
         <f>F62*F21</f>
@@ -8984,10 +8984,10 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="C64" s="598" t="s">
+      <c r="C64" s="594" t="s">
         <v>124</v>
       </c>
-      <c r="D64" s="605"/>
+      <c r="D64" s="595"/>
       <c r="E64" s="48"/>
       <c r="F64" s="62">
         <f>I220/F21/F54</f>
@@ -9013,10 +9013,10 @@
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="C65" s="604" t="s">
+      <c r="C65" s="596" t="s">
         <v>318</v>
       </c>
-      <c r="D65" s="605"/>
+      <c r="D65" s="595"/>
       <c r="E65" s="63"/>
       <c r="F65" s="46">
         <f>+F64*F21</f>
@@ -9042,10 +9042,10 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="C66" s="604" t="s">
+      <c r="C66" s="596" t="s">
         <v>319</v>
       </c>
-      <c r="D66" s="605"/>
+      <c r="D66" s="595"/>
       <c r="E66" s="51"/>
       <c r="F66" s="48">
         <f>(+G220/F54)</f>
@@ -9071,10 +9071,10 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="C67" s="604" t="s">
+      <c r="C67" s="596" t="s">
         <v>125</v>
       </c>
-      <c r="D67" s="605"/>
+      <c r="D67" s="595"/>
       <c r="E67" s="48"/>
       <c r="F67" s="48">
         <f>Main!B9</f>
@@ -9100,10 +9100,10 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="C68" s="604" t="s">
+      <c r="C68" s="596" t="s">
         <v>126</v>
       </c>
-      <c r="D68" s="605"/>
+      <c r="D68" s="595"/>
       <c r="E68" s="48"/>
       <c r="F68" s="48">
         <v>0</v>
@@ -9128,10 +9128,10 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="C69" s="598" t="s">
+      <c r="C69" s="594" t="s">
         <v>127</v>
       </c>
-      <c r="D69" s="605"/>
+      <c r="D69" s="595"/>
       <c r="E69" s="48"/>
       <c r="F69" s="48">
         <v>500000</v>
@@ -9156,10 +9156,10 @@
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="C70" s="604" t="s">
+      <c r="C70" s="596" t="s">
         <v>128</v>
       </c>
-      <c r="D70" s="605"/>
+      <c r="D70" s="595"/>
       <c r="E70" s="48"/>
       <c r="F70" s="46">
         <v>0</v>
@@ -9181,10 +9181,10 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="C71" s="604" t="s">
+      <c r="C71" s="596" t="s">
         <v>129</v>
       </c>
-      <c r="D71" s="605"/>
+      <c r="D71" s="595"/>
       <c r="E71" s="48"/>
       <c r="F71" s="46">
         <f>F38*F23*F33</f>
@@ -9210,10 +9210,10 @@
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="C72" s="604" t="s">
+      <c r="C72" s="596" t="s">
         <v>130</v>
       </c>
-      <c r="D72" s="605"/>
+      <c r="D72" s="595"/>
       <c r="E72" s="48"/>
       <c r="F72" s="48">
         <v>0</v>
@@ -9238,10 +9238,10 @@
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="C73" s="598" t="s">
+      <c r="C73" s="594" t="s">
         <v>131</v>
       </c>
-      <c r="D73" s="605"/>
+      <c r="D73" s="595"/>
       <c r="E73" s="486"/>
       <c r="F73" s="60">
         <f>+F35*F63</f>
@@ -9295,10 +9295,10 @@
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="C75" s="598" t="s">
+      <c r="C75" s="594" t="s">
         <v>133</v>
       </c>
-      <c r="D75" s="605"/>
+      <c r="D75" s="595"/>
       <c r="E75" s="51"/>
       <c r="F75" s="48">
         <f>+F77/F23</f>
@@ -9324,10 +9324,10 @@
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="C76" s="598" t="s">
+      <c r="C76" s="594" t="s">
         <v>134</v>
       </c>
-      <c r="D76" s="605"/>
+      <c r="D76" s="595"/>
       <c r="E76" s="63"/>
       <c r="F76" s="43"/>
       <c r="G76" s="481"/>
@@ -9347,10 +9347,10 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="C77" s="598" t="s">
+      <c r="C77" s="594" t="s">
         <v>135</v>
       </c>
-      <c r="D77" s="605"/>
+      <c r="D77" s="595"/>
       <c r="E77" s="63"/>
       <c r="F77" s="48">
         <f>'CAPEX and PM'!B6</f>
@@ -9376,10 +9376,10 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="C78" s="598" t="s">
+      <c r="C78" s="594" t="s">
         <v>136</v>
       </c>
-      <c r="D78" s="605"/>
+      <c r="D78" s="595"/>
       <c r="E78" s="63"/>
       <c r="F78" s="48">
         <f>'CAPEX and PM'!B37</f>
@@ -9405,10 +9405,10 @@
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="C79" s="598" t="s">
+      <c r="C79" s="594" t="s">
         <v>137</v>
       </c>
-      <c r="D79" s="605"/>
+      <c r="D79" s="595"/>
       <c r="E79" s="63"/>
       <c r="F79" s="48">
         <f>+'CAPEX and PM'!B104</f>
@@ -9434,10 +9434,10 @@
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="C80" s="598" t="s">
+      <c r="C80" s="594" t="s">
         <v>138</v>
       </c>
-      <c r="D80" s="605"/>
+      <c r="D80" s="595"/>
       <c r="E80" s="63"/>
       <c r="F80" s="48"/>
       <c r="G80" s="376"/>
@@ -9457,10 +9457,10 @@
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="C81" s="598" t="s">
+      <c r="C81" s="594" t="s">
         <v>139</v>
       </c>
-      <c r="D81" s="599"/>
+      <c r="D81" s="604"/>
       <c r="E81" s="63"/>
       <c r="F81" s="48"/>
       <c r="G81" s="376"/>
@@ -9480,10 +9480,10 @@
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="C82" s="598" t="s">
+      <c r="C82" s="594" t="s">
         <v>140</v>
       </c>
-      <c r="D82" s="605"/>
+      <c r="D82" s="595"/>
       <c r="E82" s="51"/>
       <c r="F82" s="48">
         <f>+G207</f>
@@ -9509,10 +9509,10 @@
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="C83" s="598" t="s">
+      <c r="C83" s="594" t="s">
         <v>320</v>
       </c>
-      <c r="D83" s="605"/>
+      <c r="D83" s="595"/>
       <c r="E83" s="486"/>
       <c r="F83" s="48">
         <f>+F30</f>
@@ -9545,11 +9545,11 @@
     </row>
     <row r="85" spans="1:24" ht="15.9" customHeight="1">
       <c r="A85" s="43"/>
-      <c r="B85" s="606" t="s">
+      <c r="B85" s="616" t="s">
         <v>141</v>
       </c>
-      <c r="C85" s="607"/>
-      <c r="D85" s="608"/>
+      <c r="C85" s="617"/>
+      <c r="D85" s="618"/>
       <c r="E85" s="377"/>
       <c r="F85" s="153" t="s">
         <v>71</v>
@@ -9570,10 +9570,10 @@
       <c r="B86" s="154">
         <v>1</v>
       </c>
-      <c r="C86" s="598" t="s">
+      <c r="C86" s="594" t="s">
         <v>142</v>
       </c>
-      <c r="D86" s="605"/>
+      <c r="D86" s="595"/>
       <c r="E86" s="63"/>
       <c r="F86" s="62">
         <f>+F62</f>
@@ -9602,10 +9602,10 @@
         <f>1+B86</f>
         <v>2</v>
       </c>
-      <c r="C87" s="604" t="s">
+      <c r="C87" s="596" t="s">
         <v>143</v>
       </c>
-      <c r="D87" s="605"/>
+      <c r="D87" s="595"/>
       <c r="E87" s="65"/>
       <c r="F87" s="48">
         <v>0</v>
@@ -9628,10 +9628,10 @@
         <f t="shared" ref="B88:B94" si="7">+B87+1</f>
         <v>3</v>
       </c>
-      <c r="C88" s="604" t="s">
+      <c r="C88" s="596" t="s">
         <v>144</v>
       </c>
-      <c r="D88" s="605"/>
+      <c r="D88" s="595"/>
       <c r="E88" s="65"/>
       <c r="F88" s="62">
         <f>(F66/F23)</f>
@@ -9659,10 +9659,10 @@
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="C89" s="604" t="s">
+      <c r="C89" s="596" t="s">
         <v>145</v>
       </c>
-      <c r="D89" s="605"/>
+      <c r="D89" s="595"/>
       <c r="E89" s="65"/>
       <c r="F89" s="58">
         <f>'Security Deposit'!C17</f>
@@ -9690,10 +9690,10 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="C90" s="604" t="s">
+      <c r="C90" s="596" t="s">
         <v>285</v>
       </c>
-      <c r="D90" s="605"/>
+      <c r="D90" s="595"/>
       <c r="E90" s="65"/>
       <c r="F90" s="190">
         <f>+F64</f>
@@ -9721,10 +9721,10 @@
         <f>+B89+1</f>
         <v>5</v>
       </c>
-      <c r="C91" s="604" t="s">
+      <c r="C91" s="596" t="s">
         <v>146</v>
       </c>
-      <c r="D91" s="605"/>
+      <c r="D91" s="595"/>
       <c r="E91" s="65"/>
       <c r="F91" s="58">
         <f>(+F83/F21/F54)</f>
@@ -9751,10 +9751,10 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="C92" s="604" t="s">
+      <c r="C92" s="596" t="s">
         <v>147</v>
       </c>
-      <c r="D92" s="605"/>
+      <c r="D92" s="595"/>
       <c r="E92" s="65"/>
       <c r="F92" s="58">
         <f>F82/F21/F54</f>
@@ -9782,10 +9782,10 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="C93" s="598" t="s">
+      <c r="C93" s="594" t="s">
         <v>148</v>
       </c>
-      <c r="D93" s="605"/>
+      <c r="D93" s="595"/>
       <c r="E93" s="63"/>
       <c r="F93" s="58">
         <f>+G93/F6</f>
@@ -9813,10 +9813,10 @@
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="C94" s="600" t="s">
+      <c r="C94" s="597" t="s">
         <v>65</v>
       </c>
-      <c r="D94" s="601"/>
+      <c r="D94" s="598"/>
       <c r="E94" s="70"/>
       <c r="F94" s="201">
         <f>SUM(F86:F93)</f>
@@ -9841,8 +9841,8 @@
     <row r="95" spans="1:24" ht="15.9" customHeight="1">
       <c r="A95" s="43"/>
       <c r="B95" s="369"/>
-      <c r="C95" s="595"/>
-      <c r="D95" s="595"/>
+      <c r="C95" s="636"/>
+      <c r="D95" s="636"/>
       <c r="E95" s="76"/>
       <c r="F95" s="77"/>
       <c r="G95" s="77"/>
@@ -9852,11 +9852,11 @@
     </row>
     <row r="96" spans="1:24" ht="15.9" customHeight="1">
       <c r="A96" s="43"/>
-      <c r="B96" s="602" t="s">
+      <c r="B96" s="599" t="s">
         <v>149</v>
       </c>
-      <c r="C96" s="603"/>
-      <c r="D96" s="603"/>
+      <c r="C96" s="600"/>
+      <c r="D96" s="600"/>
       <c r="E96" s="79"/>
       <c r="F96" s="153" t="s">
         <v>71</v>
@@ -9878,11 +9878,11 @@
       <c r="B97" s="154">
         <v>1</v>
       </c>
-      <c r="C97" s="604" t="str">
+      <c r="C97" s="596" t="str">
         <f>+C76</f>
         <v>Siemens Standard Fitout (Existing)</v>
       </c>
-      <c r="D97" s="605"/>
+      <c r="D97" s="595"/>
       <c r="E97" s="80"/>
       <c r="F97" s="58">
         <v>0</v>
@@ -9908,11 +9908,11 @@
         <f t="shared" ref="B98:B103" si="8">+B97+1</f>
         <v>2</v>
       </c>
-      <c r="C98" s="604" t="str">
+      <c r="C98" s="596" t="str">
         <f>+C77</f>
         <v>Siemens Standard Fitout (New)</v>
       </c>
-      <c r="D98" s="605"/>
+      <c r="D98" s="595"/>
       <c r="E98" s="63"/>
       <c r="F98" s="58">
         <f>'CAPEX and PM'!B29</f>
@@ -9940,11 +9940,11 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="C99" s="604" t="str">
+      <c r="C99" s="596" t="str">
         <f>+C78</f>
         <v>Capex over the period of lease period</v>
       </c>
-      <c r="D99" s="605"/>
+      <c r="D99" s="595"/>
       <c r="E99" s="63"/>
       <c r="F99" s="58">
         <f>'CAPEX and PM'!B98</f>
@@ -9972,11 +9972,11 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="C100" s="604" t="str">
+      <c r="C100" s="596" t="str">
         <f>+C79</f>
         <v>PM cost over the period of lease period</v>
       </c>
-      <c r="D100" s="605"/>
+      <c r="D100" s="595"/>
       <c r="E100" s="63"/>
       <c r="F100" s="58">
         <f>+'CAPEX and PM'!B105</f>
@@ -10004,11 +10004,11 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="C101" s="604" t="str">
+      <c r="C101" s="596" t="str">
         <f>+C80</f>
         <v>Asset Retirement Obligation ( Removal &amp; Restoration Obligation)</v>
       </c>
-      <c r="D101" s="605"/>
+      <c r="D101" s="595"/>
       <c r="E101" s="63"/>
       <c r="F101" s="58">
         <f>'Security Deposit'!D25</f>
@@ -10039,10 +10039,10 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="C102" s="598" t="s">
+      <c r="C102" s="594" t="s">
         <v>150</v>
       </c>
-      <c r="D102" s="605"/>
+      <c r="D102" s="595"/>
       <c r="E102" s="65"/>
       <c r="F102" s="58">
         <f>+F81/F21/F27</f>
@@ -10070,10 +10070,10 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="C103" s="600" t="s">
+      <c r="C103" s="597" t="s">
         <v>151</v>
       </c>
-      <c r="D103" s="601"/>
+      <c r="D103" s="598"/>
       <c r="E103" s="70"/>
       <c r="F103" s="46">
         <f>SUM(F97:F102)</f>
@@ -10110,11 +10110,11 @@
     </row>
     <row r="105" spans="1:26" ht="15.9" customHeight="1">
       <c r="A105" s="43"/>
-      <c r="B105" s="609" t="s">
+      <c r="B105" s="690" t="s">
         <v>152</v>
       </c>
-      <c r="C105" s="610"/>
-      <c r="D105" s="610"/>
+      <c r="C105" s="611"/>
+      <c r="D105" s="611"/>
       <c r="E105" s="79"/>
       <c r="F105" s="153" t="s">
         <v>71</v>
@@ -10135,10 +10135,10 @@
       <c r="B106" s="154">
         <v>1</v>
       </c>
-      <c r="C106" s="598" t="s">
+      <c r="C106" s="594" t="s">
         <v>65</v>
       </c>
-      <c r="D106" s="605"/>
+      <c r="D106" s="595"/>
       <c r="E106" s="63"/>
       <c r="F106" s="48">
         <f>+F94</f>
@@ -10166,10 +10166,10 @@
         <f>+B106+1</f>
         <v>2</v>
       </c>
-      <c r="C107" s="598" t="s">
+      <c r="C107" s="594" t="s">
         <v>151</v>
       </c>
-      <c r="D107" s="599"/>
+      <c r="D107" s="604"/>
       <c r="E107" s="63"/>
       <c r="F107" s="48">
         <f>+F103</f>
@@ -10197,10 +10197,10 @@
         <f>+B107+1</f>
         <v>3</v>
       </c>
-      <c r="C108" s="600" t="s">
+      <c r="C108" s="597" t="s">
         <v>153</v>
       </c>
-      <c r="D108" s="601"/>
+      <c r="D108" s="598"/>
       <c r="E108" s="70"/>
       <c r="F108" s="46">
         <f>SUM(F106:F107)</f>
@@ -10229,11 +10229,11 @@
     </row>
     <row r="109" spans="1:26" ht="15.9" customHeight="1">
       <c r="A109" s="43"/>
-      <c r="B109" s="602" t="s">
+      <c r="B109" s="599" t="s">
         <v>154</v>
       </c>
-      <c r="C109" s="603"/>
-      <c r="D109" s="603"/>
+      <c r="C109" s="600"/>
+      <c r="D109" s="600"/>
       <c r="E109" s="81"/>
       <c r="F109" s="153" t="s">
         <v>71</v>
@@ -10255,10 +10255,10 @@
       <c r="B110" s="237">
         <v>1</v>
       </c>
-      <c r="C110" s="598" t="s">
+      <c r="C110" s="594" t="s">
         <v>155</v>
       </c>
-      <c r="D110" s="599"/>
+      <c r="D110" s="604"/>
       <c r="E110" s="75"/>
       <c r="F110" s="364"/>
       <c r="G110" s="364"/>
@@ -10272,10 +10272,10 @@
         <f t="shared" ref="B111:B119" si="9">1+B110</f>
         <v>2</v>
       </c>
-      <c r="C111" s="598" t="s">
+      <c r="C111" s="594" t="s">
         <v>156</v>
       </c>
-      <c r="D111" s="599"/>
+      <c r="D111" s="604"/>
       <c r="E111" s="75"/>
       <c r="F111" s="364"/>
       <c r="G111" s="364"/>
@@ -10291,10 +10291,10 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="C112" s="598" t="s">
+      <c r="C112" s="594" t="s">
         <v>157</v>
       </c>
-      <c r="D112" s="599"/>
+      <c r="D112" s="604"/>
       <c r="E112" s="75"/>
       <c r="F112" s="376">
         <f>+F64*0</f>
@@ -10322,10 +10322,10 @@
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="C113" s="598" t="s">
+      <c r="C113" s="594" t="s">
         <v>158</v>
       </c>
-      <c r="D113" s="599"/>
+      <c r="D113" s="604"/>
       <c r="E113" s="75"/>
       <c r="F113" s="364"/>
       <c r="G113" s="364"/>
@@ -10339,10 +10339,10 @@
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="C114" s="598" t="s">
+      <c r="C114" s="594" t="s">
         <v>159</v>
       </c>
-      <c r="D114" s="599"/>
+      <c r="D114" s="604"/>
       <c r="E114" s="75"/>
       <c r="F114" s="364"/>
       <c r="G114" s="364"/>
@@ -10356,10 +10356,10 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="C115" s="598" t="s">
+      <c r="C115" s="594" t="s">
         <v>160</v>
       </c>
-      <c r="D115" s="599"/>
+      <c r="D115" s="604"/>
       <c r="E115" s="75"/>
       <c r="F115" s="364"/>
       <c r="G115" s="364"/>
@@ -10373,10 +10373,10 @@
         <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="C116" s="598" t="s">
+      <c r="C116" s="594" t="s">
         <v>161</v>
       </c>
-      <c r="D116" s="599"/>
+      <c r="D116" s="604"/>
       <c r="E116" s="75"/>
       <c r="F116" s="364"/>
       <c r="G116" s="364"/>
@@ -10390,10 +10390,10 @@
         <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="C117" s="598" t="s">
+      <c r="C117" s="594" t="s">
         <v>162</v>
       </c>
-      <c r="D117" s="605"/>
+      <c r="D117" s="595"/>
       <c r="E117" s="240"/>
       <c r="F117" s="348">
         <v>654</v>
@@ -10419,10 +10419,10 @@
         <f t="shared" si="9"/>
         <v>9</v>
       </c>
-      <c r="C118" s="598" t="s">
+      <c r="C118" s="594" t="s">
         <v>163</v>
       </c>
-      <c r="D118" s="599"/>
+      <c r="D118" s="604"/>
       <c r="E118" s="240"/>
       <c r="F118" s="82">
         <f>F117*7%</f>
@@ -10448,10 +10448,10 @@
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="C119" s="600" t="s">
+      <c r="C119" s="597" t="s">
         <v>164</v>
       </c>
-      <c r="D119" s="601"/>
+      <c r="D119" s="598"/>
       <c r="E119" s="241"/>
       <c r="F119" s="46">
         <f>SUM(F110:F118)</f>
@@ -10477,8 +10477,8 @@
     <row r="120" spans="1:26" ht="15.9" customHeight="1">
       <c r="A120" s="69"/>
       <c r="B120" s="154"/>
-      <c r="C120" s="594"/>
-      <c r="D120" s="611"/>
+      <c r="C120" s="602"/>
+      <c r="D120" s="603"/>
       <c r="E120" s="70"/>
       <c r="F120" s="46"/>
       <c r="G120" s="373"/>
@@ -10492,11 +10492,11 @@
     </row>
     <row r="121" spans="1:26" ht="15.9" customHeight="1">
       <c r="A121" s="69"/>
-      <c r="B121" s="602" t="s">
+      <c r="B121" s="599" t="s">
         <v>165</v>
       </c>
-      <c r="C121" s="603"/>
-      <c r="D121" s="603"/>
+      <c r="C121" s="600"/>
+      <c r="D121" s="600"/>
       <c r="E121" s="81"/>
       <c r="F121" s="153" t="s">
         <v>71</v>
@@ -10519,10 +10519,10 @@
       <c r="B122" s="239">
         <v>1</v>
       </c>
-      <c r="C122" s="598" t="s">
+      <c r="C122" s="594" t="s">
         <v>166</v>
       </c>
-      <c r="D122" s="599"/>
+      <c r="D122" s="604"/>
       <c r="E122" s="70"/>
       <c r="F122" s="46"/>
       <c r="G122" s="373"/>
@@ -10535,10 +10535,10 @@
       <c r="B123" s="154">
         <v>2</v>
       </c>
-      <c r="C123" s="600" t="s">
+      <c r="C123" s="597" t="s">
         <v>167</v>
       </c>
-      <c r="D123" s="601"/>
+      <c r="D123" s="598"/>
       <c r="E123" s="70"/>
       <c r="F123" s="46">
         <f>SUM(F122)</f>
@@ -10561,8 +10561,8 @@
     <row r="124" spans="1:26" ht="15.9" customHeight="1">
       <c r="A124" s="69"/>
       <c r="B124" s="154"/>
-      <c r="C124" s="594"/>
-      <c r="D124" s="611"/>
+      <c r="C124" s="602"/>
+      <c r="D124" s="603"/>
       <c r="E124" s="55"/>
       <c r="F124" s="46"/>
       <c r="G124" s="373"/>
@@ -10572,11 +10572,11 @@
     </row>
     <row r="125" spans="1:26" ht="15.9" customHeight="1">
       <c r="A125" s="69"/>
-      <c r="B125" s="602" t="s">
+      <c r="B125" s="599" t="s">
         <v>168</v>
       </c>
-      <c r="C125" s="603"/>
-      <c r="D125" s="603"/>
+      <c r="C125" s="600"/>
+      <c r="D125" s="600"/>
       <c r="E125" s="81"/>
       <c r="F125" s="153" t="s">
         <v>71</v>
@@ -10597,10 +10597,10 @@
       <c r="B126" s="237">
         <v>1</v>
       </c>
-      <c r="C126" s="598" t="s">
+      <c r="C126" s="594" t="s">
         <v>169</v>
       </c>
-      <c r="D126" s="599"/>
+      <c r="D126" s="604"/>
       <c r="E126" s="238"/>
       <c r="F126" s="373"/>
       <c r="G126" s="373"/>
@@ -10614,10 +10614,10 @@
         <f>1+B126</f>
         <v>2</v>
       </c>
-      <c r="C127" s="598" t="s">
+      <c r="C127" s="594" t="s">
         <v>170</v>
       </c>
-      <c r="D127" s="599"/>
+      <c r="D127" s="604"/>
       <c r="E127" s="238"/>
       <c r="F127" s="373"/>
       <c r="G127" s="373"/>
@@ -10631,10 +10631,10 @@
         <f>1+B127</f>
         <v>3</v>
       </c>
-      <c r="C128" s="598" t="s">
+      <c r="C128" s="594" t="s">
         <v>171</v>
       </c>
-      <c r="D128" s="599"/>
+      <c r="D128" s="604"/>
       <c r="E128" s="238"/>
       <c r="F128" s="373"/>
       <c r="G128" s="373"/>
@@ -10648,10 +10648,10 @@
         <f>1+B128</f>
         <v>4</v>
       </c>
-      <c r="C129" s="598" t="s">
+      <c r="C129" s="594" t="s">
         <v>172</v>
       </c>
-      <c r="D129" s="599"/>
+      <c r="D129" s="604"/>
       <c r="E129" s="238"/>
       <c r="F129" s="373"/>
       <c r="G129" s="373"/>
@@ -10665,10 +10665,10 @@
         <f>1+B129</f>
         <v>5</v>
       </c>
-      <c r="C130" s="598" t="s">
+      <c r="C130" s="594" t="s">
         <v>173</v>
       </c>
-      <c r="D130" s="599"/>
+      <c r="D130" s="604"/>
       <c r="E130" s="238"/>
       <c r="F130" s="373"/>
       <c r="G130" s="373"/>
@@ -10682,10 +10682,10 @@
         <f>1+B130</f>
         <v>6</v>
       </c>
-      <c r="C131" s="598" t="s">
+      <c r="C131" s="594" t="s">
         <v>174</v>
       </c>
-      <c r="D131" s="599"/>
+      <c r="D131" s="604"/>
       <c r="E131" s="238"/>
       <c r="F131" s="373"/>
       <c r="G131" s="373"/>
@@ -10698,10 +10698,10 @@
       <c r="B132" s="369">
         <v>7</v>
       </c>
-      <c r="C132" s="600" t="s">
+      <c r="C132" s="597" t="s">
         <v>175</v>
       </c>
-      <c r="D132" s="601"/>
+      <c r="D132" s="598"/>
       <c r="E132" s="238"/>
       <c r="F132" s="373">
         <f>SUM(F126:F131)</f>
@@ -10724,8 +10724,8 @@
     <row r="133" spans="1:20" ht="15.9" customHeight="1">
       <c r="A133" s="69"/>
       <c r="B133" s="154"/>
-      <c r="C133" s="595"/>
-      <c r="D133" s="611"/>
+      <c r="C133" s="636"/>
+      <c r="D133" s="603"/>
       <c r="E133" s="238"/>
       <c r="F133" s="373"/>
       <c r="G133" s="373"/>
@@ -10735,11 +10735,11 @@
     </row>
     <row r="134" spans="1:20" ht="15.9" customHeight="1">
       <c r="A134" s="43"/>
-      <c r="B134" s="602" t="s">
+      <c r="B134" s="599" t="s">
         <v>176</v>
       </c>
-      <c r="C134" s="603"/>
-      <c r="D134" s="603"/>
+      <c r="C134" s="600"/>
+      <c r="D134" s="600"/>
       <c r="E134" s="81"/>
       <c r="F134" s="153" t="s">
         <v>71</v>
@@ -10760,10 +10760,10 @@
       <c r="B135" s="154">
         <v>1</v>
       </c>
-      <c r="C135" s="600" t="s">
+      <c r="C135" s="597" t="s">
         <v>177</v>
       </c>
-      <c r="D135" s="601"/>
+      <c r="D135" s="598"/>
       <c r="E135" s="70"/>
       <c r="F135" s="46">
         <f>F119+F108+F123+F132</f>
@@ -10788,8 +10788,8 @@
     <row r="136" spans="1:20" ht="15.9" customHeight="1">
       <c r="A136" s="69"/>
       <c r="B136" s="154"/>
-      <c r="C136" s="594"/>
-      <c r="D136" s="611"/>
+      <c r="C136" s="602"/>
+      <c r="D136" s="603"/>
       <c r="E136" s="70"/>
       <c r="F136" s="46"/>
       <c r="G136" s="373"/>
@@ -10803,23 +10803,23 @@
       <c r="C137" s="368"/>
       <c r="D137" s="365"/>
       <c r="E137" s="159"/>
-      <c r="F137" s="594" t="s">
+      <c r="F137" s="602" t="s">
         <v>69</v>
       </c>
-      <c r="G137" s="595"/>
+      <c r="G137" s="636"/>
       <c r="H137" s="392"/>
-      <c r="I137" s="596" t="s">
+      <c r="I137" s="637" t="s">
         <v>63</v>
       </c>
-      <c r="J137" s="597"/>
+      <c r="J137" s="638"/>
     </row>
     <row r="138" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A138" s="43"/>
-      <c r="B138" s="602" t="s">
+      <c r="B138" s="599" t="s">
         <v>178</v>
       </c>
-      <c r="C138" s="603"/>
-      <c r="D138" s="618"/>
+      <c r="C138" s="600"/>
+      <c r="D138" s="601"/>
       <c r="E138" s="153"/>
       <c r="F138" s="153" t="s">
         <v>71</v>
@@ -10838,8 +10838,8 @@
     <row r="139" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A139" s="43"/>
       <c r="B139" s="83"/>
-      <c r="C139" s="619"/>
-      <c r="D139" s="620"/>
+      <c r="C139" s="605"/>
+      <c r="D139" s="606"/>
       <c r="E139" s="155"/>
       <c r="F139" s="46"/>
       <c r="G139" s="373"/>
@@ -10850,10 +10850,10 @@
     <row r="140" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A140" s="43"/>
       <c r="B140" s="83"/>
-      <c r="C140" s="598" t="s">
+      <c r="C140" s="594" t="s">
         <v>179</v>
       </c>
-      <c r="D140" s="605"/>
+      <c r="D140" s="595"/>
       <c r="E140" s="50"/>
       <c r="F140" s="231">
         <f>F21</f>
@@ -10876,10 +10876,10 @@
     <row r="141" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A141" s="43"/>
       <c r="B141" s="83"/>
-      <c r="C141" s="604" t="s">
+      <c r="C141" s="596" t="s">
         <v>180</v>
       </c>
-      <c r="D141" s="605"/>
+      <c r="D141" s="595"/>
       <c r="E141" s="51"/>
       <c r="F141" s="48">
         <f>F24</f>
@@ -10902,10 +10902,10 @@
     <row r="142" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A142" s="43"/>
       <c r="B142" s="83"/>
-      <c r="C142" s="604" t="s">
+      <c r="C142" s="596" t="s">
         <v>181</v>
       </c>
-      <c r="D142" s="605"/>
+      <c r="D142" s="595"/>
       <c r="E142" s="65"/>
       <c r="F142" s="48" t="e">
         <f>+#REF!</f>
@@ -10928,10 +10928,10 @@
     <row r="143" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A143" s="43"/>
       <c r="B143" s="83"/>
-      <c r="C143" s="598" t="s">
+      <c r="C143" s="594" t="s">
         <v>182</v>
       </c>
-      <c r="D143" s="605"/>
+      <c r="D143" s="595"/>
       <c r="E143" s="65"/>
       <c r="F143" s="48">
         <f>F108</f>
@@ -10954,10 +10954,10 @@
     <row r="144" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A144" s="43"/>
       <c r="B144" s="83"/>
-      <c r="C144" s="689" t="s">
+      <c r="C144" s="624" t="s">
         <v>183</v>
       </c>
-      <c r="D144" s="690"/>
+      <c r="D144" s="625"/>
       <c r="E144" s="84"/>
       <c r="F144" s="85">
         <f>F119</f>
@@ -10980,10 +10980,10 @@
     <row r="145" spans="1:10" ht="15.9" hidden="1" customHeight="1">
       <c r="A145" s="69"/>
       <c r="B145" s="154"/>
-      <c r="C145" s="600" t="s">
+      <c r="C145" s="597" t="s">
         <v>184</v>
       </c>
-      <c r="D145" s="601"/>
+      <c r="D145" s="598"/>
       <c r="E145" s="70"/>
       <c r="F145" s="233" t="e">
         <f>F135*#REF!</f>
@@ -11017,11 +11017,11 @@
     </row>
     <row r="147" spans="1:10" ht="15.9" customHeight="1">
       <c r="A147" s="69"/>
-      <c r="B147" s="602" t="s">
+      <c r="B147" s="599" t="s">
         <v>185</v>
       </c>
-      <c r="C147" s="603"/>
-      <c r="D147" s="618"/>
+      <c r="C147" s="600"/>
+      <c r="D147" s="601"/>
       <c r="E147" s="367"/>
       <c r="F147" s="367" t="s">
         <v>186</v>
@@ -11040,8 +11040,8 @@
     <row r="148" spans="1:10" ht="15.9" customHeight="1">
       <c r="A148" s="43"/>
       <c r="B148" s="91"/>
-      <c r="C148" s="619"/>
-      <c r="D148" s="620"/>
+      <c r="C148" s="605"/>
+      <c r="D148" s="606"/>
       <c r="E148" s="92"/>
       <c r="F148" s="93"/>
       <c r="G148" s="197"/>
@@ -11052,10 +11052,10 @@
     <row r="149" spans="1:10" ht="15.9" customHeight="1">
       <c r="A149" s="43"/>
       <c r="B149" s="91"/>
-      <c r="C149" s="604" t="s">
+      <c r="C149" s="596" t="s">
         <v>187</v>
       </c>
-      <c r="D149" s="605"/>
+      <c r="D149" s="595"/>
       <c r="E149" s="92"/>
       <c r="F149" s="93">
         <f>(+F63)*115%</f>
@@ -11078,10 +11078,10 @@
     <row r="150" spans="1:10" ht="15.9" customHeight="1">
       <c r="A150" s="43"/>
       <c r="B150" s="91"/>
-      <c r="C150" s="604" t="s">
+      <c r="C150" s="596" t="s">
         <v>188</v>
       </c>
-      <c r="D150" s="605"/>
+      <c r="D150" s="595"/>
       <c r="E150" s="92"/>
       <c r="F150" s="93">
         <v>0</v>
@@ -11100,10 +11100,10 @@
     <row r="151" spans="1:10" ht="15.9" customHeight="1">
       <c r="A151" s="43"/>
       <c r="B151" s="91"/>
-      <c r="C151" s="604" t="s">
+      <c r="C151" s="596" t="s">
         <v>189</v>
       </c>
-      <c r="D151" s="605"/>
+      <c r="D151" s="595"/>
       <c r="E151" s="92"/>
       <c r="F151" s="93">
         <f>(+F65)*115%</f>
@@ -11126,10 +11126,10 @@
     <row r="152" spans="1:10" ht="15.9" customHeight="1">
       <c r="A152" s="43"/>
       <c r="B152" s="91"/>
-      <c r="C152" s="604" t="s">
+      <c r="C152" s="596" t="s">
         <v>190</v>
       </c>
-      <c r="D152" s="605"/>
+      <c r="D152" s="595"/>
       <c r="E152" s="92"/>
       <c r="F152" s="93">
         <f>(+F66)*115%</f>
@@ -11152,10 +11152,10 @@
     <row r="153" spans="1:10" ht="15.9" customHeight="1">
       <c r="A153" s="43"/>
       <c r="B153" s="91"/>
-      <c r="C153" s="598" t="s">
+      <c r="C153" s="594" t="s">
         <v>191</v>
       </c>
-      <c r="D153" s="605"/>
+      <c r="D153" s="595"/>
       <c r="E153" s="95"/>
       <c r="F153" s="96">
         <f>SUM(F149:F152)</f>
@@ -11178,10 +11178,10 @@
     <row r="154" spans="1:10" ht="15.9" customHeight="1">
       <c r="A154" s="43"/>
       <c r="B154" s="91"/>
-      <c r="C154" s="598" t="s">
+      <c r="C154" s="594" t="s">
         <v>192</v>
       </c>
-      <c r="D154" s="605"/>
+      <c r="D154" s="595"/>
       <c r="E154" s="97"/>
       <c r="F154" s="93">
         <f>+F153*12</f>
@@ -11204,8 +11204,8 @@
     <row r="155" spans="1:10" ht="15.9" customHeight="1">
       <c r="A155" s="43"/>
       <c r="B155" s="91"/>
-      <c r="C155" s="619"/>
-      <c r="D155" s="620"/>
+      <c r="C155" s="605"/>
+      <c r="D155" s="606"/>
       <c r="E155" s="97"/>
       <c r="F155" s="93"/>
       <c r="G155" s="197"/>
@@ -11215,11 +11215,11 @@
     </row>
     <row r="156" spans="1:10" ht="15.9" customHeight="1">
       <c r="A156" s="43"/>
-      <c r="B156" s="602" t="s">
+      <c r="B156" s="599" t="s">
         <v>193</v>
       </c>
-      <c r="C156" s="603"/>
-      <c r="D156" s="618"/>
+      <c r="C156" s="600"/>
+      <c r="D156" s="601"/>
       <c r="E156" s="363"/>
       <c r="F156" s="367" t="s">
         <v>186</v>
@@ -11238,8 +11238,8 @@
     <row r="157" spans="1:10" ht="15.9" customHeight="1">
       <c r="A157" s="43"/>
       <c r="B157" s="91"/>
-      <c r="C157" s="619"/>
-      <c r="D157" s="620"/>
+      <c r="C157" s="605"/>
+      <c r="D157" s="606"/>
       <c r="E157" s="97"/>
       <c r="F157" s="93"/>
       <c r="G157" s="197"/>
@@ -11250,10 +11250,10 @@
     <row r="158" spans="1:10" ht="15.9" customHeight="1">
       <c r="A158" s="43"/>
       <c r="B158" s="91"/>
-      <c r="C158" s="687" t="s">
+      <c r="C158" s="622" t="s">
         <v>194</v>
       </c>
-      <c r="D158" s="688"/>
+      <c r="D158" s="623"/>
       <c r="E158" s="97"/>
       <c r="F158" s="93">
         <f t="shared" ref="F158:G160" si="10">+F77</f>
@@ -11276,10 +11276,10 @@
     <row r="159" spans="1:10" ht="15.9" customHeight="1">
       <c r="A159" s="43"/>
       <c r="B159" s="91"/>
-      <c r="C159" s="598" t="s">
+      <c r="C159" s="594" t="s">
         <v>195</v>
       </c>
-      <c r="D159" s="599"/>
+      <c r="D159" s="604"/>
       <c r="E159" s="97"/>
       <c r="F159" s="93">
         <f t="shared" si="10"/>
@@ -11302,10 +11302,10 @@
     <row r="160" spans="1:10" ht="15.9" customHeight="1">
       <c r="A160" s="43"/>
       <c r="B160" s="91"/>
-      <c r="C160" s="598" t="s">
+      <c r="C160" s="594" t="s">
         <v>196</v>
       </c>
-      <c r="D160" s="599"/>
+      <c r="D160" s="604"/>
       <c r="E160" s="97"/>
       <c r="F160" s="93">
         <f t="shared" si="10"/>
@@ -11328,10 +11328,10 @@
     <row r="161" spans="1:22" ht="15.9" customHeight="1">
       <c r="A161" s="43"/>
       <c r="B161" s="91"/>
-      <c r="C161" s="600" t="s">
+      <c r="C161" s="597" t="s">
         <v>29</v>
       </c>
-      <c r="D161" s="601"/>
+      <c r="D161" s="598"/>
       <c r="E161" s="97"/>
       <c r="F161" s="225">
         <f>SUM(F158:F160)</f>
@@ -11354,8 +11354,8 @@
     <row r="162" spans="1:22" ht="15.9" customHeight="1">
       <c r="A162" s="43"/>
       <c r="B162" s="91"/>
-      <c r="C162" s="619"/>
-      <c r="D162" s="620"/>
+      <c r="C162" s="605"/>
+      <c r="D162" s="606"/>
       <c r="E162" s="97"/>
       <c r="F162" s="93"/>
       <c r="G162" s="197"/>
@@ -11365,12 +11365,12 @@
     </row>
     <row r="163" spans="1:22" ht="15.9" customHeight="1">
       <c r="A163" s="98"/>
-      <c r="B163" s="606" t="s">
+      <c r="B163" s="616" t="s">
         <v>197</v>
       </c>
-      <c r="C163" s="607"/>
-      <c r="D163" s="608"/>
-      <c r="E163" s="616"/>
+      <c r="C163" s="617"/>
+      <c r="D163" s="618"/>
+      <c r="E163" s="689"/>
       <c r="F163" s="153" t="s">
         <v>71</v>
       </c>
@@ -11387,10 +11387,10 @@
     </row>
     <row r="164" spans="1:22" ht="15.9" customHeight="1">
       <c r="A164" s="98"/>
-      <c r="B164" s="684"/>
-      <c r="C164" s="685"/>
-      <c r="D164" s="686"/>
-      <c r="E164" s="617"/>
+      <c r="B164" s="619"/>
+      <c r="C164" s="620"/>
+      <c r="D164" s="621"/>
+      <c r="E164" s="609"/>
       <c r="F164" s="153" t="s">
         <v>69</v>
       </c>
@@ -11408,8 +11408,8 @@
     <row r="165" spans="1:22" ht="15.9" customHeight="1">
       <c r="A165" s="99"/>
       <c r="B165" s="91"/>
-      <c r="C165" s="619"/>
-      <c r="D165" s="620"/>
+      <c r="C165" s="605"/>
+      <c r="D165" s="606"/>
       <c r="E165" s="51"/>
       <c r="F165" s="48"/>
       <c r="G165" s="376"/>
@@ -11420,11 +11420,11 @@
     <row r="166" spans="1:22" ht="15.9" customHeight="1">
       <c r="A166" s="99"/>
       <c r="B166" s="91"/>
-      <c r="C166" s="682" t="str">
+      <c r="C166" s="607" t="str">
         <f>+C106</f>
         <v>Net Rent I</v>
       </c>
-      <c r="D166" s="683"/>
+      <c r="D166" s="608"/>
       <c r="E166" s="51"/>
       <c r="F166" s="48">
         <f>+F106</f>
@@ -11448,11 +11448,11 @@
     <row r="167" spans="1:22" ht="15.9" customHeight="1">
       <c r="A167" s="99"/>
       <c r="B167" s="91"/>
-      <c r="C167" s="682" t="str">
+      <c r="C167" s="607" t="str">
         <f>+C107</f>
         <v>Net Rent II</v>
       </c>
-      <c r="D167" s="683"/>
+      <c r="D167" s="608"/>
       <c r="E167" s="51"/>
       <c r="F167" s="48">
         <f>+F107</f>
@@ -11476,10 +11476,10 @@
     <row r="168" spans="1:22" ht="15.9" customHeight="1">
       <c r="A168" s="99"/>
       <c r="B168" s="139"/>
-      <c r="C168" s="678" t="s">
+      <c r="C168" s="612" t="s">
         <v>198</v>
       </c>
-      <c r="D168" s="679"/>
+      <c r="D168" s="613"/>
       <c r="E168" s="140"/>
       <c r="F168" s="141">
         <f>SUM(F166:F167)</f>
@@ -11504,8 +11504,8 @@
     <row r="169" spans="1:22" ht="15.9" customHeight="1">
       <c r="A169" s="99"/>
       <c r="B169" s="154"/>
-      <c r="C169" s="680"/>
-      <c r="D169" s="681"/>
+      <c r="C169" s="614"/>
+      <c r="D169" s="615"/>
       <c r="E169" s="67"/>
       <c r="F169" s="46"/>
       <c r="G169" s="373"/>
@@ -11518,11 +11518,11 @@
     <row r="170" spans="1:22" ht="15.9" customHeight="1">
       <c r="A170" s="99"/>
       <c r="B170" s="91"/>
-      <c r="C170" s="682" t="str">
+      <c r="C170" s="607" t="str">
         <f>+C119</f>
         <v xml:space="preserve">OpEx I </v>
       </c>
-      <c r="D170" s="683"/>
+      <c r="D170" s="608"/>
       <c r="E170" s="51"/>
       <c r="F170" s="48">
         <f>+F119</f>
@@ -11546,11 +11546,11 @@
     <row r="171" spans="1:22" ht="15.9" customHeight="1">
       <c r="A171" s="99"/>
       <c r="B171" s="91"/>
-      <c r="C171" s="682" t="str">
+      <c r="C171" s="607" t="str">
         <f>+C123</f>
         <v xml:space="preserve">OpEx II </v>
       </c>
-      <c r="D171" s="683"/>
+      <c r="D171" s="608"/>
       <c r="E171" s="51"/>
       <c r="F171" s="48">
         <f>+F123</f>
@@ -11573,10 +11573,10 @@
     <row r="172" spans="1:22" ht="15.9" customHeight="1">
       <c r="A172" s="99"/>
       <c r="B172" s="142"/>
-      <c r="C172" s="678" t="s">
+      <c r="C172" s="612" t="s">
         <v>199</v>
       </c>
-      <c r="D172" s="679"/>
+      <c r="D172" s="613"/>
       <c r="E172" s="143"/>
       <c r="F172" s="144">
         <f>SUM(F170:F171)</f>
@@ -11611,11 +11611,11 @@
     <row r="174" spans="1:22" ht="15.9" customHeight="1">
       <c r="A174" s="99"/>
       <c r="B174" s="91"/>
-      <c r="C174" s="682" t="str">
+      <c r="C174" s="607" t="str">
         <f>+C132</f>
         <v xml:space="preserve">Services </v>
       </c>
-      <c r="D174" s="683"/>
+      <c r="D174" s="608"/>
       <c r="E174" s="51"/>
       <c r="F174" s="48">
         <f>+F132</f>
@@ -11638,10 +11638,10 @@
     <row r="175" spans="1:22" ht="15.9" customHeight="1">
       <c r="A175" s="99"/>
       <c r="B175" s="142"/>
-      <c r="C175" s="678" t="s">
+      <c r="C175" s="612" t="s">
         <v>200</v>
       </c>
-      <c r="D175" s="679"/>
+      <c r="D175" s="613"/>
       <c r="E175" s="143"/>
       <c r="F175" s="144">
         <f>SUM(F174)</f>
@@ -11664,8 +11664,8 @@
     <row r="176" spans="1:22" ht="15.9" customHeight="1">
       <c r="A176" s="99"/>
       <c r="B176" s="91"/>
-      <c r="C176" s="619"/>
-      <c r="D176" s="620"/>
+      <c r="C176" s="605"/>
+      <c r="D176" s="606"/>
       <c r="E176" s="51"/>
       <c r="F176" s="48"/>
       <c r="G176" s="376"/>
@@ -11676,10 +11676,10 @@
     <row r="177" spans="1:19" ht="15.9" customHeight="1">
       <c r="A177" s="99"/>
       <c r="B177" s="142"/>
-      <c r="C177" s="678" t="s">
+      <c r="C177" s="612" t="s">
         <v>201</v>
       </c>
-      <c r="D177" s="679"/>
+      <c r="D177" s="613"/>
       <c r="E177" s="146"/>
       <c r="F177" s="141">
         <f>+F168+F172+F175</f>
@@ -11714,11 +11714,11 @@
     </row>
     <row r="179" spans="1:19" ht="15.9" customHeight="1">
       <c r="A179" s="99"/>
-      <c r="B179" s="602" t="s">
+      <c r="B179" s="599" t="s">
         <v>202</v>
       </c>
-      <c r="C179" s="603"/>
-      <c r="D179" s="618"/>
+      <c r="C179" s="600"/>
+      <c r="D179" s="601"/>
       <c r="E179" s="367"/>
       <c r="F179" s="367" t="s">
         <v>186</v>
@@ -11737,8 +11737,8 @@
     <row r="180" spans="1:19" ht="15.9" customHeight="1">
       <c r="A180" s="99"/>
       <c r="B180" s="91"/>
-      <c r="C180" s="619"/>
-      <c r="D180" s="620"/>
+      <c r="C180" s="605"/>
+      <c r="D180" s="606"/>
       <c r="E180" s="51"/>
       <c r="F180" s="48"/>
       <c r="G180" s="376"/>
@@ -11749,10 +11749,10 @@
     <row r="181" spans="1:19" ht="15.9" customHeight="1">
       <c r="A181" s="99"/>
       <c r="B181" s="91"/>
-      <c r="C181" s="604" t="s">
+      <c r="C181" s="596" t="s">
         <v>203</v>
       </c>
-      <c r="D181" s="605"/>
+      <c r="D181" s="595"/>
       <c r="E181" s="92"/>
       <c r="F181" s="93"/>
       <c r="G181" s="197">
@@ -11769,10 +11769,10 @@
     <row r="182" spans="1:19" ht="15.9" customHeight="1">
       <c r="A182" s="99"/>
       <c r="B182" s="91"/>
-      <c r="C182" s="598" t="s">
+      <c r="C182" s="594" t="s">
         <v>204</v>
       </c>
-      <c r="D182" s="605"/>
+      <c r="D182" s="595"/>
       <c r="E182" s="92"/>
       <c r="F182" s="93"/>
       <c r="G182" s="197">
@@ -11789,10 +11789,10 @@
     <row r="183" spans="1:19" ht="15.9" customHeight="1">
       <c r="A183" s="99"/>
       <c r="B183" s="91"/>
-      <c r="C183" s="598" t="s">
+      <c r="C183" s="594" t="s">
         <v>205</v>
       </c>
-      <c r="D183" s="599"/>
+      <c r="D183" s="604"/>
       <c r="E183" s="92"/>
       <c r="F183" s="93"/>
       <c r="G183" s="197">
@@ -11806,10 +11806,10 @@
     <row r="184" spans="1:19" ht="15.9" customHeight="1">
       <c r="A184" s="99"/>
       <c r="B184" s="91"/>
-      <c r="C184" s="598" t="s">
+      <c r="C184" s="594" t="s">
         <v>206</v>
       </c>
-      <c r="D184" s="605"/>
+      <c r="D184" s="595"/>
       <c r="E184" s="92"/>
       <c r="F184" s="93"/>
       <c r="G184" s="197">
@@ -11826,10 +11826,10 @@
     <row r="185" spans="1:19" ht="15.9" customHeight="1">
       <c r="A185" s="99"/>
       <c r="B185" s="91"/>
-      <c r="C185" s="598" t="s">
+      <c r="C185" s="594" t="s">
         <v>207</v>
       </c>
-      <c r="D185" s="605"/>
+      <c r="D185" s="595"/>
       <c r="E185" s="92"/>
       <c r="F185" s="93"/>
       <c r="G185" s="197">
@@ -11857,25 +11857,25 @@
     </row>
     <row r="187" spans="1:19" ht="15.9" customHeight="1" thickBot="1">
       <c r="A187" s="99"/>
-      <c r="B187" s="675" t="s">
+      <c r="B187" s="629" t="s">
         <v>208</v>
       </c>
-      <c r="C187" s="676"/>
-      <c r="D187" s="676"/>
-      <c r="E187" s="676"/>
-      <c r="F187" s="676"/>
-      <c r="G187" s="676"/>
-      <c r="H187" s="676"/>
-      <c r="I187" s="676"/>
-      <c r="J187" s="677"/>
+      <c r="C187" s="630"/>
+      <c r="D187" s="630"/>
+      <c r="E187" s="630"/>
+      <c r="F187" s="630"/>
+      <c r="G187" s="630"/>
+      <c r="H187" s="630"/>
+      <c r="I187" s="630"/>
+      <c r="J187" s="631"/>
     </row>
     <row r="188" spans="1:19" ht="15.9" customHeight="1">
       <c r="A188" s="43"/>
       <c r="B188" s="156"/>
-      <c r="C188" s="617" t="s">
+      <c r="C188" s="609" t="s">
         <v>209</v>
       </c>
-      <c r="D188" s="617"/>
+      <c r="D188" s="609"/>
       <c r="E188" s="366"/>
       <c r="F188" s="366" t="s">
         <v>186</v>
@@ -11883,7 +11883,7 @@
       <c r="G188" s="160" t="s">
         <v>186</v>
       </c>
-      <c r="H188" s="672"/>
+      <c r="H188" s="626"/>
       <c r="I188" s="217" t="s">
         <v>63</v>
       </c>
@@ -11894,17 +11894,17 @@
     <row r="189" spans="1:19" ht="15.9" customHeight="1">
       <c r="A189" s="43"/>
       <c r="B189" s="154"/>
-      <c r="C189" s="604" t="s">
+      <c r="C189" s="596" t="s">
         <v>210</v>
       </c>
-      <c r="D189" s="605"/>
+      <c r="D189" s="595"/>
       <c r="E189" s="155"/>
       <c r="F189" s="155"/>
       <c r="G189" s="94">
         <f>+G20</f>
         <v>0</v>
       </c>
-      <c r="H189" s="673"/>
+      <c r="H189" s="627"/>
       <c r="I189" s="154"/>
       <c r="J189" s="94">
         <f>+G189/J5</f>
@@ -11914,17 +11914,17 @@
     <row r="190" spans="1:19" ht="15.9" customHeight="1">
       <c r="A190" s="43"/>
       <c r="B190" s="154"/>
-      <c r="C190" s="604" t="s">
+      <c r="C190" s="596" t="s">
         <v>211</v>
       </c>
-      <c r="D190" s="605"/>
+      <c r="D190" s="595"/>
       <c r="E190" s="155"/>
       <c r="F190" s="155"/>
       <c r="G190" s="94">
         <f>+G189*G23</f>
         <v>0</v>
       </c>
-      <c r="H190" s="673"/>
+      <c r="H190" s="627"/>
       <c r="I190" s="154"/>
       <c r="J190" s="94">
         <f>+J189*J23</f>
@@ -11934,17 +11934,17 @@
     <row r="191" spans="1:19" ht="15.9" customHeight="1">
       <c r="A191" s="43"/>
       <c r="B191" s="154"/>
-      <c r="C191" s="642" t="s">
+      <c r="C191" s="610" t="s">
         <v>212</v>
       </c>
-      <c r="D191" s="642"/>
+      <c r="D191" s="610"/>
       <c r="E191" s="155"/>
       <c r="F191" s="155"/>
       <c r="G191" s="94">
         <f>+G190*25%</f>
         <v>0</v>
       </c>
-      <c r="H191" s="673"/>
+      <c r="H191" s="627"/>
       <c r="I191" s="154"/>
       <c r="J191" s="94">
         <f>+J190*25%</f>
@@ -11954,17 +11954,17 @@
     <row r="192" spans="1:19" ht="15.9" customHeight="1">
       <c r="A192" s="43"/>
       <c r="B192" s="154"/>
-      <c r="C192" s="598" t="s">
+      <c r="C192" s="594" t="s">
         <v>213</v>
       </c>
-      <c r="D192" s="605"/>
+      <c r="D192" s="595"/>
       <c r="E192" s="155"/>
       <c r="F192" s="155"/>
       <c r="G192" s="94">
         <f>+G191*1%</f>
         <v>0</v>
       </c>
-      <c r="H192" s="673"/>
+      <c r="H192" s="627"/>
       <c r="I192" s="154"/>
       <c r="J192" s="94">
         <f>G192/J5</f>
@@ -11974,17 +11974,17 @@
     <row r="193" spans="1:20" ht="15.9" customHeight="1">
       <c r="A193" s="43"/>
       <c r="B193" s="154"/>
-      <c r="C193" s="598" t="s">
+      <c r="C193" s="594" t="s">
         <v>214</v>
       </c>
-      <c r="D193" s="605"/>
+      <c r="D193" s="595"/>
       <c r="E193" s="155"/>
       <c r="F193" s="155"/>
       <c r="G193" s="94">
         <f>G192*0.5</f>
         <v>0</v>
       </c>
-      <c r="H193" s="673"/>
+      <c r="H193" s="627"/>
       <c r="I193" s="154"/>
       <c r="J193" s="94">
         <f>G193/J5</f>
@@ -11994,17 +11994,17 @@
     <row r="194" spans="1:20" ht="15.9" customHeight="1" thickBot="1">
       <c r="A194" s="43"/>
       <c r="B194" s="154"/>
-      <c r="C194" s="642" t="s">
+      <c r="C194" s="610" t="s">
         <v>215</v>
       </c>
-      <c r="D194" s="642"/>
+      <c r="D194" s="610"/>
       <c r="E194" s="155"/>
       <c r="F194" s="155"/>
       <c r="G194" s="102">
         <f>G82</f>
         <v>565315.30184775486</v>
       </c>
-      <c r="H194" s="673"/>
+      <c r="H194" s="627"/>
       <c r="I194" s="154"/>
       <c r="J194" s="102">
         <f>+J192+J193</f>
@@ -12014,8 +12014,8 @@
     <row r="195" spans="1:20" ht="15.9" customHeight="1">
       <c r="A195" s="158"/>
       <c r="B195" s="370"/>
-      <c r="C195" s="610"/>
-      <c r="D195" s="610"/>
+      <c r="C195" s="611"/>
+      <c r="D195" s="611"/>
       <c r="E195" s="367"/>
       <c r="F195" s="367" t="s">
         <v>186</v>
@@ -12023,7 +12023,7 @@
       <c r="G195" s="45" t="s">
         <v>186</v>
       </c>
-      <c r="H195" s="673"/>
+      <c r="H195" s="627"/>
       <c r="I195" s="217" t="s">
         <v>63</v>
       </c>
@@ -12034,17 +12034,17 @@
     <row r="196" spans="1:20" ht="15.9" customHeight="1">
       <c r="A196" s="66"/>
       <c r="B196" s="91"/>
-      <c r="C196" s="604" t="s">
+      <c r="C196" s="596" t="s">
         <v>216</v>
       </c>
-      <c r="D196" s="605"/>
+      <c r="D196" s="595"/>
       <c r="E196" s="50"/>
       <c r="F196" s="42"/>
       <c r="G196" s="94">
         <f>+G54</f>
         <v>72</v>
       </c>
-      <c r="H196" s="673"/>
+      <c r="H196" s="627"/>
       <c r="I196" s="83"/>
       <c r="J196" s="94">
         <f>+J54</f>
@@ -12054,17 +12054,17 @@
     <row r="197" spans="1:20" ht="15.9" customHeight="1">
       <c r="A197" s="66"/>
       <c r="B197" s="91"/>
-      <c r="C197" s="604" t="s">
+      <c r="C197" s="596" t="s">
         <v>217</v>
       </c>
-      <c r="D197" s="605"/>
+      <c r="D197" s="595"/>
       <c r="E197" s="50"/>
       <c r="F197" s="42"/>
       <c r="G197" s="94">
         <f>F140</f>
         <v>9515</v>
       </c>
-      <c r="H197" s="673"/>
+      <c r="H197" s="627"/>
       <c r="I197" s="83"/>
       <c r="J197" s="94">
         <f>I140</f>
@@ -12074,17 +12074,17 @@
     <row r="198" spans="1:20" ht="15.9" customHeight="1">
       <c r="A198" s="112"/>
       <c r="B198" s="91"/>
-      <c r="C198" s="604" t="s">
+      <c r="C198" s="596" t="s">
         <v>218</v>
       </c>
-      <c r="D198" s="605"/>
+      <c r="D198" s="595"/>
       <c r="E198" s="50"/>
       <c r="F198" s="42"/>
       <c r="G198" s="103">
         <f>+F60</f>
         <v>129</v>
       </c>
-      <c r="H198" s="673"/>
+      <c r="H198" s="627"/>
       <c r="I198" s="83"/>
       <c r="J198" s="103">
         <f>+I60</f>
@@ -12094,17 +12094,17 @@
     <row r="199" spans="1:20" ht="15.9" customHeight="1">
       <c r="A199" s="66"/>
       <c r="B199" s="91"/>
-      <c r="C199" s="604" t="s">
+      <c r="C199" s="596" t="s">
         <v>218</v>
       </c>
-      <c r="D199" s="605"/>
+      <c r="D199" s="595"/>
       <c r="E199" s="50"/>
       <c r="F199" s="42"/>
       <c r="G199" s="94">
         <f>(G197*G198*G196)</f>
         <v>88375320</v>
       </c>
-      <c r="H199" s="673"/>
+      <c r="H199" s="627"/>
       <c r="I199" s="83"/>
       <c r="J199" s="94">
         <f>+G199/$J$5</f>
@@ -12114,17 +12114,17 @@
     <row r="200" spans="1:20" ht="15.9" customHeight="1">
       <c r="A200" s="66"/>
       <c r="B200" s="91"/>
-      <c r="C200" s="604" t="s">
+      <c r="C200" s="596" t="s">
         <v>219</v>
       </c>
-      <c r="D200" s="605"/>
+      <c r="D200" s="595"/>
       <c r="E200" s="50"/>
       <c r="F200" s="42"/>
       <c r="G200" s="94">
         <f>G199/G196*12</f>
         <v>14729220</v>
       </c>
-      <c r="H200" s="673"/>
+      <c r="H200" s="627"/>
       <c r="I200" s="83"/>
       <c r="J200" s="94">
         <f>+G200/$J$5</f>
@@ -12134,17 +12134,17 @@
     <row r="201" spans="1:20" ht="15.9" customHeight="1">
       <c r="A201" s="66"/>
       <c r="B201" s="91"/>
-      <c r="C201" s="604" t="s">
+      <c r="C201" s="596" t="s">
         <v>220</v>
       </c>
-      <c r="D201" s="605"/>
+      <c r="D201" s="595"/>
       <c r="E201" s="50"/>
       <c r="F201" s="42"/>
       <c r="G201" s="94">
         <f>(+G220*115%)/5</f>
         <v>3026339.9999999995</v>
       </c>
-      <c r="H201" s="673"/>
+      <c r="H201" s="627"/>
       <c r="I201" s="83"/>
       <c r="J201" s="94">
         <f>+G201/$J$5</f>
@@ -12154,17 +12154,17 @@
     <row r="202" spans="1:20" ht="15.9" customHeight="1">
       <c r="A202" s="66"/>
       <c r="B202" s="91"/>
-      <c r="C202" s="604" t="s">
+      <c r="C202" s="596" t="s">
         <v>221</v>
       </c>
-      <c r="D202" s="605"/>
+      <c r="D202" s="595"/>
       <c r="E202" s="50"/>
       <c r="F202" s="42"/>
       <c r="G202" s="94">
         <f>(+I220*115%)/5</f>
         <v>2765157.6185172233</v>
       </c>
-      <c r="H202" s="673"/>
+      <c r="H202" s="627"/>
       <c r="I202" s="83"/>
       <c r="J202" s="94">
         <f>+G202/$J$5</f>
@@ -12174,17 +12174,17 @@
     <row r="203" spans="1:20" ht="15.9" customHeight="1">
       <c r="A203" s="66"/>
       <c r="B203" s="91"/>
-      <c r="C203" s="604" t="s">
+      <c r="C203" s="596" t="s">
         <v>36</v>
       </c>
-      <c r="D203" s="605"/>
+      <c r="D203" s="595"/>
       <c r="E203" s="50"/>
       <c r="F203" s="42"/>
       <c r="G203" s="94">
         <f>+G67</f>
         <v>11418000</v>
       </c>
-      <c r="H203" s="673"/>
+      <c r="H203" s="627"/>
       <c r="I203" s="83"/>
       <c r="J203" s="94">
         <f>+G203/$J$5</f>
@@ -12194,17 +12194,17 @@
     <row r="204" spans="1:20" ht="15.9" customHeight="1">
       <c r="A204" s="66"/>
       <c r="B204" s="91"/>
-      <c r="C204" s="598" t="s">
+      <c r="C204" s="594" t="s">
         <v>222</v>
       </c>
-      <c r="D204" s="605"/>
+      <c r="D204" s="595"/>
       <c r="E204" s="50"/>
       <c r="F204" s="42"/>
       <c r="G204" s="94">
         <f>(G200+G201+G202+G203)*1.18</f>
         <v>37687686.789850324</v>
       </c>
-      <c r="H204" s="673"/>
+      <c r="H204" s="627"/>
       <c r="I204" s="83"/>
       <c r="J204" s="94">
         <f>+J200+J201+J202+J203</f>
@@ -12214,17 +12214,17 @@
     <row r="205" spans="1:20" ht="15.9" customHeight="1">
       <c r="A205" s="66"/>
       <c r="B205" s="91"/>
-      <c r="C205" s="598" t="s">
+      <c r="C205" s="594" t="s">
         <v>223</v>
       </c>
-      <c r="D205" s="605"/>
+      <c r="D205" s="595"/>
       <c r="E205" s="50"/>
       <c r="F205" s="42"/>
       <c r="G205" s="94">
         <f>G204*1%</f>
         <v>376876.86789850326</v>
       </c>
-      <c r="H205" s="673"/>
+      <c r="H205" s="627"/>
       <c r="I205" s="83"/>
       <c r="J205" s="94">
         <f>J204*1%</f>
@@ -12234,17 +12234,17 @@
     <row r="206" spans="1:20" ht="15.9" customHeight="1">
       <c r="A206" s="66"/>
       <c r="B206" s="91"/>
-      <c r="C206" s="604" t="s">
+      <c r="C206" s="596" t="s">
         <v>224</v>
       </c>
-      <c r="D206" s="605"/>
+      <c r="D206" s="595"/>
       <c r="E206" s="50"/>
       <c r="F206" s="42"/>
       <c r="G206" s="94">
         <f>G204*0.5%</f>
         <v>188438.43394925163</v>
       </c>
-      <c r="H206" s="673"/>
+      <c r="H206" s="627"/>
       <c r="I206" s="83"/>
       <c r="J206" s="94">
         <f>J204*0.5%</f>
@@ -12254,17 +12254,17 @@
     <row r="207" spans="1:20" ht="15.9" customHeight="1">
       <c r="A207" s="66"/>
       <c r="B207" s="91"/>
-      <c r="C207" s="600" t="s">
+      <c r="C207" s="597" t="s">
         <v>215</v>
       </c>
-      <c r="D207" s="601"/>
+      <c r="D207" s="598"/>
       <c r="E207" s="50"/>
       <c r="F207" s="42"/>
       <c r="G207" s="94">
         <f>G205+G206</f>
         <v>565315.30184775486</v>
       </c>
-      <c r="H207" s="673"/>
+      <c r="H207" s="627"/>
       <c r="I207" s="83"/>
       <c r="J207" s="94">
         <v>0</v>
@@ -12279,7 +12279,7 @@
       <c r="E208" s="72"/>
       <c r="F208" s="43"/>
       <c r="G208" s="325"/>
-      <c r="H208" s="673"/>
+      <c r="H208" s="627"/>
       <c r="I208" s="86"/>
       <c r="J208" s="73"/>
     </row>
@@ -12301,7 +12301,7 @@
       <c r="G209" s="153" t="s">
         <v>229</v>
       </c>
-      <c r="H209" s="673"/>
+      <c r="H209" s="627"/>
       <c r="I209" s="367" t="s">
         <v>230</v>
       </c>
@@ -12327,7 +12327,7 @@
         <f>'Lease Rent'!P39</f>
         <v>1360000</v>
       </c>
-      <c r="H210" s="673"/>
+      <c r="H210" s="627"/>
       <c r="I210" s="93">
         <f>'Lease Rent'!O39</f>
         <v>1178337.5999999999</v>
@@ -12357,7 +12357,7 @@
         <f>'Lease Rent'!P51</f>
         <v>2040000</v>
       </c>
-      <c r="H211" s="673"/>
+      <c r="H211" s="627"/>
       <c r="I211" s="93">
         <f>'Lease Rent'!O51</f>
         <v>1826423.2800000005</v>
@@ -12386,7 +12386,7 @@
         <f>'Lease Rent'!P63</f>
         <v>2040000</v>
       </c>
-      <c r="H212" s="673"/>
+      <c r="H212" s="627"/>
       <c r="I212" s="93">
         <f>'Lease Rent'!O63</f>
         <v>1917744.4440000001</v>
@@ -12415,7 +12415,7 @@
         <f>'Lease Rent'!P75</f>
         <v>2244000</v>
       </c>
-      <c r="H213" s="673"/>
+      <c r="H213" s="627"/>
       <c r="I213" s="93">
         <f>'Lease Rent'!O75</f>
         <v>2013631.6662000006</v>
@@ -12444,7 +12444,7 @@
         <f>'Lease Rent'!P87</f>
         <v>2345999.9999999995</v>
       </c>
-      <c r="H214" s="673"/>
+      <c r="H214" s="627"/>
       <c r="I214" s="93">
         <f>'Lease Rent'!O87</f>
         <v>2114313.2495100005</v>
@@ -12473,7 +12473,7 @@
         <f>'Lease Rent'!P99</f>
         <v>2345999.9999999995</v>
       </c>
-      <c r="H215" s="673"/>
+      <c r="H215" s="627"/>
       <c r="I215" s="93">
         <f>'Lease Rent'!O99</f>
         <v>2220028.9119855007</v>
@@ -12501,7 +12501,7 @@
         <f>'Lease Rent'!P103</f>
         <v>781999.99999999988</v>
       </c>
-      <c r="H216" s="673"/>
+      <c r="H216" s="627"/>
       <c r="I216" s="93">
         <f>'Lease Rent'!O103</f>
         <v>751945.27664025011</v>
@@ -12524,7 +12524,7 @@
         <f>'Lease Rent'!R10</f>
         <v>0</v>
       </c>
-      <c r="H217" s="673"/>
+      <c r="H217" s="627"/>
       <c r="I217" s="289"/>
       <c r="J217" s="103"/>
     </row>
@@ -12541,7 +12541,7 @@
         <v>0</v>
       </c>
       <c r="G218" s="110"/>
-      <c r="H218" s="673"/>
+      <c r="H218" s="627"/>
       <c r="I218" s="93"/>
       <c r="J218" s="103"/>
     </row>
@@ -12555,7 +12555,7 @@
       <c r="E219" s="109"/>
       <c r="F219" s="220"/>
       <c r="G219" s="110"/>
-      <c r="H219" s="673"/>
+      <c r="H219" s="627"/>
       <c r="I219" s="93"/>
       <c r="J219" s="103"/>
     </row>
@@ -12578,7 +12578,7 @@
         <f>SUM(G210:G219)</f>
         <v>13158000</v>
       </c>
-      <c r="H220" s="674"/>
+      <c r="H220" s="628"/>
       <c r="I220" s="271">
         <f>SUM(I210:I219)</f>
         <v>12022424.428335754</v>
@@ -12648,6 +12648,219 @@
     </row>
   </sheetData>
   <mergeCells count="237">
+    <mergeCell ref="F137:G137"/>
+    <mergeCell ref="I137:J137"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="B134:D134"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="B105:D105"/>
+    <mergeCell ref="C124:D124"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="E163:E164"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="C123:D123"/>
+    <mergeCell ref="C118:D118"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="B156:D156"/>
+    <mergeCell ref="C151:D151"/>
+    <mergeCell ref="C152:D152"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="C145:D145"/>
+    <mergeCell ref="C148:D148"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B1:J3"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="H188:H220"/>
+    <mergeCell ref="C159:D159"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B187:J187"/>
+    <mergeCell ref="C172:D172"/>
+    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="C177:D177"/>
+    <mergeCell ref="C180:D180"/>
+    <mergeCell ref="C157:D157"/>
+    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="C175:D175"/>
+    <mergeCell ref="C149:D149"/>
+    <mergeCell ref="C150:D150"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="I58:J58"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="C143:D143"/>
+    <mergeCell ref="C184:D184"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C181:D181"/>
+    <mergeCell ref="C185:D185"/>
+    <mergeCell ref="C168:D168"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="C169:D169"/>
+    <mergeCell ref="C183:D183"/>
+    <mergeCell ref="C170:D170"/>
+    <mergeCell ref="C140:D140"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="C122:D122"/>
+    <mergeCell ref="C171:D171"/>
+    <mergeCell ref="C167:D167"/>
+    <mergeCell ref="B147:D147"/>
+    <mergeCell ref="B163:D164"/>
+    <mergeCell ref="B125:D125"/>
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="C144:D144"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="C166:D166"/>
+    <mergeCell ref="C182:D182"/>
+    <mergeCell ref="C205:D205"/>
+    <mergeCell ref="C206:D206"/>
+    <mergeCell ref="C207:D207"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C174:D174"/>
+    <mergeCell ref="C197:D197"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="C199:D199"/>
+    <mergeCell ref="C200:D200"/>
+    <mergeCell ref="C201:D201"/>
+    <mergeCell ref="C202:D202"/>
+    <mergeCell ref="C188:D188"/>
+    <mergeCell ref="C191:D191"/>
+    <mergeCell ref="C194:D194"/>
+    <mergeCell ref="C195:D195"/>
+    <mergeCell ref="C196:D196"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
     <mergeCell ref="C204:D204"/>
     <mergeCell ref="C203:D203"/>
     <mergeCell ref="C161:D161"/>
@@ -12672,219 +12885,6 @@
     <mergeCell ref="B179:D179"/>
     <mergeCell ref="C162:D162"/>
     <mergeCell ref="C165:D165"/>
-    <mergeCell ref="C205:D205"/>
-    <mergeCell ref="C206:D206"/>
-    <mergeCell ref="C207:D207"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C174:D174"/>
-    <mergeCell ref="C197:D197"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="C199:D199"/>
-    <mergeCell ref="C200:D200"/>
-    <mergeCell ref="C201:D201"/>
-    <mergeCell ref="C202:D202"/>
-    <mergeCell ref="C188:D188"/>
-    <mergeCell ref="C191:D191"/>
-    <mergeCell ref="C194:D194"/>
-    <mergeCell ref="C195:D195"/>
-    <mergeCell ref="C196:D196"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C181:D181"/>
-    <mergeCell ref="C185:D185"/>
-    <mergeCell ref="C168:D168"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="C169:D169"/>
-    <mergeCell ref="C183:D183"/>
-    <mergeCell ref="C170:D170"/>
-    <mergeCell ref="C140:D140"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="C122:D122"/>
-    <mergeCell ref="C171:D171"/>
-    <mergeCell ref="C167:D167"/>
-    <mergeCell ref="B147:D147"/>
-    <mergeCell ref="B163:D164"/>
-    <mergeCell ref="B125:D125"/>
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="C144:D144"/>
-    <mergeCell ref="C139:D139"/>
-    <mergeCell ref="C166:D166"/>
-    <mergeCell ref="C182:D182"/>
-    <mergeCell ref="H188:H220"/>
-    <mergeCell ref="C159:D159"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B187:J187"/>
-    <mergeCell ref="C172:D172"/>
-    <mergeCell ref="C176:D176"/>
-    <mergeCell ref="C177:D177"/>
-    <mergeCell ref="C180:D180"/>
-    <mergeCell ref="C157:D157"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="C175:D175"/>
-    <mergeCell ref="C149:D149"/>
-    <mergeCell ref="C150:D150"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="I58:J58"/>
-    <mergeCell ref="B121:D121"/>
-    <mergeCell ref="C143:D143"/>
-    <mergeCell ref="C184:D184"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B1:J3"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="E163:E164"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="C123:D123"/>
-    <mergeCell ref="C118:D118"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="B156:D156"/>
-    <mergeCell ref="C151:D151"/>
-    <mergeCell ref="C152:D152"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="C145:D145"/>
-    <mergeCell ref="C148:D148"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="C136:D136"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="B134:D134"/>
-    <mergeCell ref="C106:D106"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="B105:D105"/>
-    <mergeCell ref="C124:D124"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="F137:G137"/>
-    <mergeCell ref="I137:J137"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="B109:D109"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C131:D131"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="C107:D107"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.25" top="0.75" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="58" orientation="portrait" r:id="rId1"/>
@@ -12957,32 +12957,32 @@
       <c r="S1" s="1"/>
     </row>
     <row r="2" spans="1:27" ht="11.25" customHeight="1">
-      <c r="A2" s="658"/>
-      <c r="B2" s="659"/>
-      <c r="C2" s="659"/>
-      <c r="D2" s="659"/>
-      <c r="E2" s="659"/>
-      <c r="F2" s="659"/>
-      <c r="G2" s="659"/>
-      <c r="H2" s="659"/>
-      <c r="I2" s="659"/>
-      <c r="J2" s="659"/>
-      <c r="K2" s="659"/>
-      <c r="L2" s="659"/>
-      <c r="M2" s="659"/>
-      <c r="N2" s="659"/>
-      <c r="O2" s="659"/>
-      <c r="P2" s="659"/>
-      <c r="Q2" s="659"/>
-      <c r="R2" s="659"/>
-      <c r="S2" s="659"/>
-      <c r="T2" s="659"/>
-      <c r="U2" s="659"/>
-      <c r="V2" s="659"/>
-      <c r="W2" s="659"/>
-      <c r="X2" s="659"/>
-      <c r="Y2" s="659"/>
-      <c r="Z2" s="659"/>
+      <c r="A2" s="670"/>
+      <c r="B2" s="671"/>
+      <c r="C2" s="671"/>
+      <c r="D2" s="671"/>
+      <c r="E2" s="671"/>
+      <c r="F2" s="671"/>
+      <c r="G2" s="671"/>
+      <c r="H2" s="671"/>
+      <c r="I2" s="671"/>
+      <c r="J2" s="671"/>
+      <c r="K2" s="671"/>
+      <c r="L2" s="671"/>
+      <c r="M2" s="671"/>
+      <c r="N2" s="671"/>
+      <c r="O2" s="671"/>
+      <c r="P2" s="671"/>
+      <c r="Q2" s="671"/>
+      <c r="R2" s="671"/>
+      <c r="S2" s="671"/>
+      <c r="T2" s="671"/>
+      <c r="U2" s="671"/>
+      <c r="V2" s="671"/>
+      <c r="W2" s="671"/>
+      <c r="X2" s="671"/>
+      <c r="Y2" s="671"/>
+      <c r="Z2" s="671"/>
       <c r="AA2" s="695"/>
     </row>
     <row r="3" spans="1:27" ht="11.25" customHeight="1">
@@ -13044,34 +13044,34 @@
       <c r="AA4" s="701"/>
     </row>
     <row r="5" spans="1:27" ht="12.75" customHeight="1">
-      <c r="A5" s="658" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="659"/>
-      <c r="C5" s="659"/>
-      <c r="D5" s="659"/>
-      <c r="E5" s="659"/>
-      <c r="F5" s="659"/>
-      <c r="G5" s="659"/>
-      <c r="H5" s="659"/>
-      <c r="I5" s="659"/>
-      <c r="J5" s="659"/>
-      <c r="K5" s="659"/>
-      <c r="L5" s="659"/>
-      <c r="M5" s="659"/>
-      <c r="N5" s="659"/>
-      <c r="O5" s="659"/>
-      <c r="P5" s="659"/>
-      <c r="Q5" s="659"/>
-      <c r="R5" s="659"/>
-      <c r="S5" s="659"/>
-      <c r="T5" s="659"/>
-      <c r="U5" s="659"/>
-      <c r="V5" s="659"/>
-      <c r="W5" s="659"/>
-      <c r="X5" s="659"/>
-      <c r="Y5" s="659"/>
-      <c r="Z5" s="659"/>
+      <c r="A5" s="670" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="671"/>
+      <c r="C5" s="671"/>
+      <c r="D5" s="671"/>
+      <c r="E5" s="671"/>
+      <c r="F5" s="671"/>
+      <c r="G5" s="671"/>
+      <c r="H5" s="671"/>
+      <c r="I5" s="671"/>
+      <c r="J5" s="671"/>
+      <c r="K5" s="671"/>
+      <c r="L5" s="671"/>
+      <c r="M5" s="671"/>
+      <c r="N5" s="671"/>
+      <c r="O5" s="671"/>
+      <c r="P5" s="671"/>
+      <c r="Q5" s="671"/>
+      <c r="R5" s="671"/>
+      <c r="S5" s="671"/>
+      <c r="T5" s="671"/>
+      <c r="U5" s="671"/>
+      <c r="V5" s="671"/>
+      <c r="W5" s="671"/>
+      <c r="X5" s="671"/>
+      <c r="Y5" s="671"/>
+      <c r="Z5" s="671"/>
       <c r="AA5" s="695"/>
     </row>
     <row r="6" spans="1:27" ht="13.5" customHeight="1">
@@ -24444,6 +24444,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1">
@@ -24453,15 +24462,6 @@
     <Status xmlns="d83aeb52-d2fa-41b9-9c50-14da36e1ffc1" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24484,6 +24484,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC57694E-BA35-486E-AC74-B7B624F1FDE0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12D5BE44-B07C-4182-BC7A-71E5962390BD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -24494,14 +24502,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC57694E-BA35-486E-AC74-B7B624F1FDE0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{a59b6cd5-d141-4a33-8bf1-0ca04484304f}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" removed="0"/>

--- a/artifacts/Rental Specimen.xlsx
+++ b/artifacts/Rental Specimen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z0050s8t\Documents\rental-automation\artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4FCAA39-B4B3-4DA6-B837-6F282600495B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B24D4D-F512-4F86-A60F-D4BDC5EBBBE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="764" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5562,81 +5562,276 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="184" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="184" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="184" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="33" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="29" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="15" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5657,201 +5852,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="7" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="33" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="29" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="33" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="29" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="9" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="207" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7489,62 +7489,62 @@
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1">
       <c r="A1" s="43"/>
-      <c r="B1" s="643"/>
-      <c r="C1" s="644"/>
-      <c r="D1" s="644"/>
-      <c r="E1" s="644"/>
-      <c r="F1" s="644"/>
-      <c r="G1" s="644"/>
-      <c r="H1" s="644"/>
-      <c r="I1" s="644"/>
-      <c r="J1" s="645"/>
+      <c r="B1" s="633"/>
+      <c r="C1" s="634"/>
+      <c r="D1" s="634"/>
+      <c r="E1" s="634"/>
+      <c r="F1" s="634"/>
+      <c r="G1" s="634"/>
+      <c r="H1" s="634"/>
+      <c r="I1" s="634"/>
+      <c r="J1" s="635"/>
     </row>
     <row r="2" spans="1:10" ht="14.25" customHeight="1">
       <c r="A2" s="43"/>
-      <c r="B2" s="646"/>
-      <c r="C2" s="647"/>
-      <c r="D2" s="647"/>
-      <c r="E2" s="647"/>
-      <c r="F2" s="647"/>
-      <c r="G2" s="647"/>
-      <c r="H2" s="647"/>
-      <c r="I2" s="647"/>
-      <c r="J2" s="648"/>
+      <c r="B2" s="636"/>
+      <c r="C2" s="637"/>
+      <c r="D2" s="637"/>
+      <c r="E2" s="637"/>
+      <c r="F2" s="637"/>
+      <c r="G2" s="637"/>
+      <c r="H2" s="637"/>
+      <c r="I2" s="637"/>
+      <c r="J2" s="638"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A3" s="43"/>
-      <c r="B3" s="649"/>
-      <c r="C3" s="650"/>
-      <c r="D3" s="650"/>
-      <c r="E3" s="650"/>
-      <c r="F3" s="650"/>
-      <c r="G3" s="650"/>
-      <c r="H3" s="650"/>
-      <c r="I3" s="647"/>
-      <c r="J3" s="648"/>
+      <c r="B3" s="639"/>
+      <c r="C3" s="640"/>
+      <c r="D3" s="640"/>
+      <c r="E3" s="640"/>
+      <c r="F3" s="640"/>
+      <c r="G3" s="640"/>
+      <c r="H3" s="640"/>
+      <c r="I3" s="637"/>
+      <c r="J3" s="638"/>
     </row>
     <row r="4" spans="1:10" ht="13">
       <c r="A4" s="43"/>
-      <c r="B4" s="670"/>
-      <c r="C4" s="671"/>
-      <c r="D4" s="671"/>
-      <c r="E4" s="671"/>
-      <c r="F4" s="671"/>
-      <c r="G4" s="671"/>
+      <c r="B4" s="658"/>
+      <c r="C4" s="659"/>
+      <c r="D4" s="659"/>
+      <c r="E4" s="659"/>
+      <c r="F4" s="659"/>
+      <c r="G4" s="659"/>
       <c r="H4" s="389"/>
       <c r="I4" s="390"/>
       <c r="J4" s="391"/>
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="43"/>
-      <c r="B5" s="672" t="s">
+      <c r="B5" s="660" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="673"/>
-      <c r="D5" s="673"/>
-      <c r="E5" s="673"/>
-      <c r="F5" s="673"/>
-      <c r="G5" s="674"/>
+      <c r="C5" s="661"/>
+      <c r="D5" s="661"/>
+      <c r="E5" s="661"/>
+      <c r="F5" s="661"/>
+      <c r="G5" s="662"/>
       <c r="H5" s="392"/>
       <c r="I5" s="469" t="s">
         <v>16</v>
@@ -7555,29 +7555,29 @@
     </row>
     <row r="6" spans="1:10" ht="13.5" thickBot="1">
       <c r="A6" s="43"/>
-      <c r="B6" s="675"/>
-      <c r="C6" s="676"/>
-      <c r="D6" s="677"/>
+      <c r="B6" s="663"/>
+      <c r="C6" s="664"/>
+      <c r="D6" s="665"/>
       <c r="E6" s="44"/>
-      <c r="F6" s="668">
+      <c r="F6" s="656">
         <v>10.763999999999999</v>
       </c>
-      <c r="G6" s="669"/>
+      <c r="G6" s="657"/>
       <c r="H6" s="393"/>
-      <c r="I6" s="656">
+      <c r="I6" s="647">
         <v>10.763999999999999</v>
       </c>
-      <c r="J6" s="657"/>
+      <c r="J6" s="648"/>
     </row>
     <row r="7" spans="1:10" ht="26">
       <c r="A7" s="43"/>
       <c r="B7" s="470" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="678" t="s">
+      <c r="C7" s="666" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="679"/>
+      <c r="D7" s="667"/>
       <c r="E7" s="471"/>
       <c r="F7" s="471" t="s">
         <v>299</v>
@@ -7605,23 +7605,23 @@
       <c r="C8" s="474"/>
       <c r="D8" s="475"/>
       <c r="E8" s="476"/>
-      <c r="F8" s="602" t="s">
+      <c r="F8" s="594" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="636"/>
+      <c r="G8" s="595"/>
       <c r="H8" s="392"/>
-      <c r="I8" s="637" t="s">
+      <c r="I8" s="596" t="s">
         <v>63</v>
       </c>
-      <c r="J8" s="638"/>
+      <c r="J8" s="597"/>
     </row>
     <row r="9" spans="1:10" ht="13">
       <c r="A9" s="43"/>
-      <c r="B9" s="637" t="s">
+      <c r="B9" s="596" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="636"/>
-      <c r="D9" s="603"/>
+      <c r="C9" s="595"/>
+      <c r="D9" s="611"/>
       <c r="E9" s="477"/>
       <c r="F9" s="364" t="s">
         <v>71</v>
@@ -7642,21 +7642,21 @@
       <c r="B10" s="478">
         <v>1</v>
       </c>
-      <c r="C10" s="651" t="s">
+      <c r="C10" s="641" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="610"/>
+      <c r="D10" s="642"/>
       <c r="E10" s="479"/>
-      <c r="F10" s="662" t="s">
+      <c r="F10" s="653" t="s">
         <v>295</v>
       </c>
-      <c r="G10" s="663"/>
+      <c r="G10" s="654"/>
       <c r="H10" s="392"/>
-      <c r="I10" s="658" t="str">
+      <c r="I10" s="649" t="str">
         <f>+F10</f>
         <v>Chennai</v>
       </c>
-      <c r="J10" s="659"/>
+      <c r="J10" s="650"/>
     </row>
     <row r="11" spans="1:10" ht="28.5" customHeight="1">
       <c r="A11" s="43"/>
@@ -7664,19 +7664,19 @@
         <f>1+B10</f>
         <v>2</v>
       </c>
-      <c r="C11" s="652" t="s">
+      <c r="C11" s="643" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="653"/>
+      <c r="D11" s="644"/>
       <c r="E11" s="42"/>
-      <c r="F11" s="662"/>
-      <c r="G11" s="663"/>
+      <c r="F11" s="653"/>
+      <c r="G11" s="654"/>
       <c r="H11" s="392"/>
-      <c r="I11" s="660">
+      <c r="I11" s="651">
         <f>+F11</f>
         <v>0</v>
       </c>
-      <c r="J11" s="661"/>
+      <c r="J11" s="652"/>
     </row>
     <row r="12" spans="1:10" ht="27.75" customHeight="1">
       <c r="A12" s="43"/>
@@ -7684,19 +7684,19 @@
         <f>1+B11</f>
         <v>3</v>
       </c>
-      <c r="C12" s="596" t="s">
+      <c r="C12" s="604" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="595"/>
+      <c r="D12" s="605"/>
       <c r="E12" s="480"/>
-      <c r="F12" s="664"/>
-      <c r="G12" s="665"/>
+      <c r="F12" s="632"/>
+      <c r="G12" s="627"/>
       <c r="H12" s="392"/>
-      <c r="I12" s="680">
+      <c r="I12" s="628">
         <f>+F12</f>
         <v>0</v>
       </c>
-      <c r="J12" s="681"/>
+      <c r="J12" s="629"/>
     </row>
     <row r="13" spans="1:10" ht="15.9" customHeight="1">
       <c r="A13" s="43"/>
@@ -7704,16 +7704,16 @@
         <f t="shared" ref="B13:B30" si="0">1+B12</f>
         <v>4</v>
       </c>
-      <c r="C13" s="596" t="s">
+      <c r="C13" s="604" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="595"/>
+      <c r="D13" s="605"/>
       <c r="E13" s="42"/>
-      <c r="F13" s="667"/>
-      <c r="G13" s="665"/>
+      <c r="F13" s="626"/>
+      <c r="G13" s="627"/>
       <c r="H13" s="392"/>
-      <c r="I13" s="680"/>
-      <c r="J13" s="681"/>
+      <c r="I13" s="628"/>
+      <c r="J13" s="629"/>
     </row>
     <row r="14" spans="1:10" ht="48" customHeight="1">
       <c r="A14" s="43"/>
@@ -7721,21 +7721,21 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="654" t="s">
+      <c r="C14" s="645" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="655"/>
+      <c r="D14" s="646"/>
       <c r="E14" s="464"/>
-      <c r="F14" s="664" t="s">
+      <c r="F14" s="632" t="s">
         <v>296</v>
       </c>
-      <c r="G14" s="666"/>
+      <c r="G14" s="655"/>
       <c r="H14" s="392"/>
-      <c r="I14" s="680" t="str">
+      <c r="I14" s="628" t="str">
         <f>+F14</f>
         <v>6th floor</v>
       </c>
-      <c r="J14" s="681"/>
+      <c r="J14" s="629"/>
     </row>
     <row r="15" spans="1:10" ht="51.75" customHeight="1">
       <c r="A15" s="43"/>
@@ -7743,19 +7743,19 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="596" t="s">
+      <c r="C15" s="604" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="595"/>
+      <c r="D15" s="605"/>
       <c r="E15" s="50"/>
-      <c r="F15" s="602"/>
-      <c r="G15" s="636"/>
+      <c r="F15" s="594"/>
+      <c r="G15" s="595"/>
       <c r="H15" s="392"/>
-      <c r="I15" s="637">
+      <c r="I15" s="596">
         <f>+F15</f>
         <v>0</v>
       </c>
-      <c r="J15" s="638"/>
+      <c r="J15" s="597"/>
     </row>
     <row r="16" spans="1:10" ht="15.9" customHeight="1">
       <c r="A16" s="43"/>
@@ -7763,16 +7763,16 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="596" t="s">
+      <c r="C16" s="604" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="595"/>
+      <c r="D16" s="605"/>
       <c r="E16" s="50"/>
-      <c r="F16" s="667"/>
-      <c r="G16" s="665"/>
+      <c r="F16" s="626"/>
+      <c r="G16" s="627"/>
       <c r="H16" s="392"/>
-      <c r="I16" s="680"/>
-      <c r="J16" s="681"/>
+      <c r="I16" s="628"/>
+      <c r="J16" s="629"/>
     </row>
     <row r="17" spans="1:10" ht="15.9" customHeight="1">
       <c r="A17" s="43"/>
@@ -7780,21 +7780,21 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="596" t="s">
+      <c r="C17" s="604" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="595"/>
+      <c r="D17" s="605"/>
       <c r="E17" s="50"/>
-      <c r="F17" s="664" t="s">
+      <c r="F17" s="632" t="s">
         <v>81</v>
       </c>
-      <c r="G17" s="665"/>
+      <c r="G17" s="627"/>
       <c r="H17" s="392"/>
-      <c r="I17" s="680" t="str">
+      <c r="I17" s="628" t="str">
         <f>+F17</f>
         <v>Warm Shell</v>
       </c>
-      <c r="J17" s="681"/>
+      <c r="J17" s="629"/>
     </row>
     <row r="18" spans="1:10" ht="48" customHeight="1">
       <c r="A18" s="43"/>
@@ -7802,22 +7802,22 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="596" t="s">
+      <c r="C18" s="604" t="s">
         <v>82</v>
       </c>
-      <c r="D18" s="595"/>
+      <c r="D18" s="605"/>
       <c r="E18" s="155"/>
-      <c r="F18" s="602">
+      <c r="F18" s="594">
         <f>F15</f>
         <v>0</v>
       </c>
-      <c r="G18" s="636"/>
+      <c r="G18" s="595"/>
       <c r="H18" s="392"/>
-      <c r="I18" s="637">
+      <c r="I18" s="596">
         <f>+F18</f>
         <v>0</v>
       </c>
-      <c r="J18" s="638"/>
+      <c r="J18" s="597"/>
     </row>
     <row r="19" spans="1:10" ht="15.9" customHeight="1">
       <c r="A19" s="43"/>
@@ -7825,16 +7825,16 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="596" t="s">
+      <c r="C19" s="604" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="595"/>
+      <c r="D19" s="605"/>
       <c r="E19" s="155"/>
-      <c r="F19" s="667"/>
-      <c r="G19" s="665"/>
+      <c r="F19" s="626"/>
+      <c r="G19" s="627"/>
       <c r="H19" s="392"/>
-      <c r="I19" s="680"/>
-      <c r="J19" s="681"/>
+      <c r="I19" s="628"/>
+      <c r="J19" s="629"/>
     </row>
     <row r="20" spans="1:10" ht="15.9" customHeight="1">
       <c r="A20" s="43"/>
@@ -7842,10 +7842,10 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="594" t="s">
+      <c r="C20" s="598" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="595"/>
+      <c r="D20" s="605"/>
       <c r="E20" s="482"/>
       <c r="F20" s="48"/>
       <c r="G20" s="376"/>
@@ -7865,10 +7865,10 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="596" t="s">
+      <c r="C21" s="604" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="595"/>
+      <c r="D21" s="605"/>
       <c r="E21" s="482"/>
       <c r="F21" s="48">
         <f>Main!B3</f>
@@ -7894,10 +7894,10 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="594" t="s">
+      <c r="C22" s="598" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="595"/>
+      <c r="D22" s="605"/>
       <c r="E22" s="482"/>
       <c r="F22" s="48">
         <v>0</v>
@@ -7921,10 +7921,10 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="596" t="s">
+      <c r="C23" s="604" t="s">
         <v>87</v>
       </c>
-      <c r="D23" s="595"/>
+      <c r="D23" s="605"/>
       <c r="E23" s="482"/>
       <c r="F23" s="48">
         <f>+F21+F22</f>
@@ -7950,10 +7950,10 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="596" t="s">
+      <c r="C24" s="604" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="595"/>
+      <c r="D24" s="605"/>
       <c r="E24" s="51"/>
       <c r="F24" s="48"/>
       <c r="G24" s="376">
@@ -7976,10 +7976,10 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="596" t="s">
+      <c r="C25" s="604" t="s">
         <v>89</v>
       </c>
-      <c r="D25" s="595"/>
+      <c r="D25" s="605"/>
       <c r="E25" s="51"/>
       <c r="F25" s="48">
         <v>0</v>
@@ -8004,10 +8004,10 @@
         <f>1+B25</f>
         <v>17</v>
       </c>
-      <c r="C26" s="596" t="s">
+      <c r="C26" s="604" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="595"/>
+      <c r="D26" s="605"/>
       <c r="E26" s="52"/>
       <c r="F26" s="53">
         <f>F25/F23</f>
@@ -8033,10 +8033,10 @@
         <f>1+B26</f>
         <v>18</v>
       </c>
-      <c r="C27" s="594" t="s">
+      <c r="C27" s="598" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="595"/>
+      <c r="D27" s="605"/>
       <c r="E27" s="50"/>
       <c r="F27" s="281">
         <f>'CAPEX and PM'!E3</f>
@@ -8062,10 +8062,10 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="594" t="s">
+      <c r="C28" s="598" t="s">
         <v>92</v>
       </c>
-      <c r="D28" s="595"/>
+      <c r="D28" s="605"/>
       <c r="E28" s="56"/>
       <c r="F28" s="56">
         <f>Main!B12</f>
@@ -8091,10 +8091,10 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="594" t="s">
+      <c r="C29" s="598" t="s">
         <v>93</v>
       </c>
-      <c r="D29" s="595"/>
+      <c r="D29" s="605"/>
       <c r="E29" s="56"/>
       <c r="F29" s="52">
         <f>Main!B13</f>
@@ -8120,10 +8120,10 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="596" t="s">
+      <c r="C30" s="604" t="s">
         <v>94</v>
       </c>
-      <c r="D30" s="595"/>
+      <c r="D30" s="605"/>
       <c r="E30" s="50"/>
       <c r="F30" s="48">
         <v>0</v>
@@ -8144,11 +8144,11 @@
     </row>
     <row r="31" spans="1:10" ht="15.9" customHeight="1">
       <c r="A31" s="43"/>
-      <c r="B31" s="682" t="s">
+      <c r="B31" s="623" t="s">
         <v>95</v>
       </c>
-      <c r="C31" s="683"/>
-      <c r="D31" s="684"/>
+      <c r="C31" s="624"/>
+      <c r="D31" s="625"/>
       <c r="E31" s="485"/>
       <c r="F31" s="364" t="s">
         <v>71</v>
@@ -8169,10 +8169,10 @@
       <c r="B32" s="154">
         <v>1</v>
       </c>
-      <c r="C32" s="594" t="s">
+      <c r="C32" s="598" t="s">
         <v>96</v>
       </c>
-      <c r="D32" s="595"/>
+      <c r="D32" s="605"/>
       <c r="E32" s="51"/>
       <c r="F32" s="48">
         <f>Main!B9/(Main!B3*Main!B7)</f>
@@ -8198,10 +8198,10 @@
         <f>1+B32</f>
         <v>2</v>
       </c>
-      <c r="C33" s="594" t="s">
+      <c r="C33" s="598" t="s">
         <v>97</v>
       </c>
-      <c r="D33" s="595"/>
+      <c r="D33" s="605"/>
       <c r="E33" s="51"/>
       <c r="F33" s="48">
         <v>0</v>
@@ -8225,10 +8225,10 @@
         <f t="shared" ref="B34:B47" si="1">1+B33</f>
         <v>3</v>
       </c>
-      <c r="C34" s="594" t="s">
+      <c r="C34" s="598" t="s">
         <v>98</v>
       </c>
-      <c r="D34" s="595"/>
+      <c r="D34" s="605"/>
       <c r="E34" s="51"/>
       <c r="F34" s="48">
         <v>0</v>
@@ -8253,10 +8253,10 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="C35" s="596" t="s">
+      <c r="C35" s="604" t="s">
         <v>99</v>
       </c>
-      <c r="D35" s="595"/>
+      <c r="D35" s="605"/>
       <c r="E35" s="486"/>
       <c r="F35" s="60">
         <v>0</v>
@@ -8278,10 +8278,10 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="C36" s="594" t="s">
+      <c r="C36" s="598" t="s">
         <v>100</v>
       </c>
-      <c r="D36" s="595"/>
+      <c r="D36" s="605"/>
       <c r="E36" s="486"/>
       <c r="F36" s="62">
         <f>'Lease Rent'!H37</f>
@@ -8307,10 +8307,10 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="C37" s="594" t="s">
+      <c r="C37" s="598" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="595"/>
+      <c r="D37" s="605"/>
       <c r="E37" s="486"/>
       <c r="F37" s="62"/>
       <c r="G37" s="192">
@@ -8327,10 +8327,10 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="C38" s="594" t="s">
+      <c r="C38" s="598" t="s">
         <v>102</v>
       </c>
-      <c r="D38" s="595"/>
+      <c r="D38" s="605"/>
       <c r="E38" s="63"/>
       <c r="F38" s="62">
         <f>'Lease Rent'!J31</f>
@@ -8356,10 +8356,10 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="C39" s="594" t="s">
+      <c r="C39" s="598" t="s">
         <v>103</v>
       </c>
-      <c r="D39" s="595"/>
+      <c r="D39" s="605"/>
       <c r="E39" s="486"/>
       <c r="F39" s="62">
         <f>F36</f>
@@ -8385,10 +8385,10 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="C40" s="594" t="s">
+      <c r="C40" s="598" t="s">
         <v>104</v>
       </c>
-      <c r="D40" s="595"/>
+      <c r="D40" s="605"/>
       <c r="E40" s="486"/>
       <c r="F40" s="62">
         <v>0</v>
@@ -8413,10 +8413,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="C41" s="594" t="s">
+      <c r="C41" s="598" t="s">
         <v>105</v>
       </c>
-      <c r="D41" s="595"/>
+      <c r="D41" s="605"/>
       <c r="E41" s="50"/>
       <c r="F41" s="106">
         <f>F38</f>
@@ -8442,10 +8442,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="C42" s="596" t="s">
+      <c r="C42" s="604" t="s">
         <v>106</v>
       </c>
-      <c r="D42" s="595"/>
+      <c r="D42" s="605"/>
       <c r="E42" s="51"/>
       <c r="F42" s="101">
         <v>0</v>
@@ -8470,10 +8470,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="C43" s="596" t="s">
+      <c r="C43" s="604" t="s">
         <v>107</v>
       </c>
-      <c r="D43" s="595"/>
+      <c r="D43" s="605"/>
       <c r="E43" s="65"/>
       <c r="F43" s="60">
         <f>'Lease Rent'!D22</f>
@@ -8499,10 +8499,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="C44" s="596" t="s">
+      <c r="C44" s="604" t="s">
         <v>108</v>
       </c>
-      <c r="D44" s="595"/>
+      <c r="D44" s="605"/>
       <c r="E44" s="51"/>
       <c r="F44" s="48">
         <f>'Lease Rent'!C22</f>
@@ -8528,10 +8528,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="C45" s="594" t="s">
+      <c r="C45" s="598" t="s">
         <v>109</v>
       </c>
-      <c r="D45" s="595"/>
+      <c r="D45" s="605"/>
       <c r="E45" s="51"/>
       <c r="F45" s="101">
         <v>0</v>
@@ -8553,10 +8553,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="C46" s="596" t="s">
+      <c r="C46" s="604" t="s">
         <v>331</v>
       </c>
-      <c r="D46" s="595"/>
+      <c r="D46" s="605"/>
       <c r="E46" s="51"/>
       <c r="F46" s="48">
         <f>'Lease Rent'!D23</f>
@@ -8573,10 +8573,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="C47" s="596" t="s">
+      <c r="C47" s="604" t="s">
         <v>332</v>
       </c>
-      <c r="D47" s="595"/>
+      <c r="D47" s="605"/>
       <c r="E47" s="51"/>
       <c r="F47" s="48">
         <f>'Lease Rent'!C23</f>
@@ -8589,46 +8589,46 @@
     </row>
     <row r="48" spans="1:10" ht="28.5" customHeight="1">
       <c r="A48" s="43"/>
-      <c r="B48" s="641">
+      <c r="B48" s="670">
         <f>1+B47</f>
         <v>17</v>
       </c>
-      <c r="C48" s="594" t="s">
+      <c r="C48" s="598" t="s">
         <v>110</v>
       </c>
-      <c r="D48" s="595"/>
+      <c r="D48" s="605"/>
       <c r="E48" s="65"/>
-      <c r="F48" s="687" t="str">
+      <c r="F48" s="614" t="str">
         <f>Main!B14</f>
         <v>15% every 3 years</v>
       </c>
-      <c r="G48" s="688"/>
+      <c r="G48" s="615"/>
       <c r="H48" s="392"/>
-      <c r="I48" s="680" t="str">
+      <c r="I48" s="628" t="str">
         <f>+F48</f>
         <v>15% every 3 years</v>
       </c>
-      <c r="J48" s="681"/>
+      <c r="J48" s="629"/>
     </row>
     <row r="49" spans="1:18" ht="15.9" customHeight="1">
       <c r="A49" s="43"/>
-      <c r="B49" s="642"/>
-      <c r="C49" s="594" t="s">
+      <c r="B49" s="671"/>
+      <c r="C49" s="598" t="s">
         <v>111</v>
       </c>
-      <c r="D49" s="595"/>
+      <c r="D49" s="605"/>
       <c r="E49" s="65"/>
-      <c r="F49" s="687" t="str">
+      <c r="F49" s="614" t="str">
         <f>Main!B15</f>
         <v>5% every years</v>
       </c>
-      <c r="G49" s="688"/>
+      <c r="G49" s="615"/>
       <c r="H49" s="392"/>
-      <c r="I49" s="685" t="str">
+      <c r="I49" s="630" t="str">
         <f t="shared" ref="I49:I56" si="2">F49</f>
         <v>5% every years</v>
       </c>
-      <c r="J49" s="686"/>
+      <c r="J49" s="631"/>
     </row>
     <row r="50" spans="1:18" ht="15.9" customHeight="1">
       <c r="A50" s="43"/>
@@ -8636,22 +8636,22 @@
         <f>1+B48</f>
         <v>18</v>
       </c>
-      <c r="C50" s="596" t="s">
+      <c r="C50" s="604" t="s">
         <v>112</v>
       </c>
-      <c r="D50" s="595"/>
+      <c r="D50" s="605"/>
       <c r="E50" s="65"/>
-      <c r="F50" s="632">
+      <c r="F50" s="612">
         <f>'Lease Rent'!B31</f>
         <v>46023</v>
       </c>
-      <c r="G50" s="633"/>
+      <c r="G50" s="613"/>
       <c r="H50" s="392"/>
-      <c r="I50" s="634">
+      <c r="I50" s="621">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J50" s="635"/>
+      <c r="J50" s="622"/>
     </row>
     <row r="51" spans="1:18" ht="15.9" customHeight="1">
       <c r="A51" s="43"/>
@@ -8659,22 +8659,22 @@
         <f t="shared" ref="B51:B57" si="3">1+B50</f>
         <v>19</v>
       </c>
-      <c r="C51" s="594" t="s">
+      <c r="C51" s="598" t="s">
         <v>113</v>
       </c>
-      <c r="D51" s="595"/>
+      <c r="D51" s="605"/>
       <c r="E51" s="65"/>
-      <c r="F51" s="632">
+      <c r="F51" s="612">
         <f>'Lease Rent'!C102</f>
         <v>48213</v>
       </c>
-      <c r="G51" s="633"/>
+      <c r="G51" s="613"/>
       <c r="H51" s="392"/>
-      <c r="I51" s="634">
+      <c r="I51" s="621">
         <f>F51</f>
         <v>48213</v>
       </c>
-      <c r="J51" s="635"/>
+      <c r="J51" s="622"/>
     </row>
     <row r="52" spans="1:18" ht="15.9" customHeight="1">
       <c r="A52" s="43"/>
@@ -8682,22 +8682,22 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="C52" s="594" t="s">
+      <c r="C52" s="598" t="s">
         <v>114</v>
       </c>
-      <c r="D52" s="604"/>
+      <c r="D52" s="599"/>
       <c r="E52" s="65"/>
-      <c r="F52" s="632">
+      <c r="F52" s="612">
         <f>F50</f>
         <v>46023</v>
       </c>
-      <c r="G52" s="633"/>
+      <c r="G52" s="613"/>
       <c r="H52" s="392"/>
-      <c r="I52" s="634">
+      <c r="I52" s="621">
         <f t="shared" si="2"/>
         <v>46023</v>
       </c>
-      <c r="J52" s="635"/>
+      <c r="J52" s="622"/>
     </row>
     <row r="53" spans="1:18" ht="15.9" customHeight="1">
       <c r="A53" s="43"/>
@@ -8705,21 +8705,21 @@
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="C53" s="594" t="s">
+      <c r="C53" s="598" t="s">
         <v>115</v>
       </c>
-      <c r="D53" s="604"/>
+      <c r="D53" s="599"/>
       <c r="E53" s="65"/>
-      <c r="F53" s="602">
-        <v>0</v>
-      </c>
-      <c r="G53" s="636"/>
+      <c r="F53" s="594">
+        <v>0</v>
+      </c>
+      <c r="G53" s="595"/>
       <c r="H53" s="392"/>
-      <c r="I53" s="637">
+      <c r="I53" s="596">
         <f>+F53</f>
         <v>0</v>
       </c>
-      <c r="J53" s="638"/>
+      <c r="J53" s="597"/>
     </row>
     <row r="54" spans="1:18" ht="15.9" customHeight="1">
       <c r="A54" s="43"/>
@@ -8727,10 +8727,10 @@
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="C54" s="596" t="s">
+      <c r="C54" s="604" t="s">
         <v>116</v>
       </c>
-      <c r="D54" s="595"/>
+      <c r="D54" s="605"/>
       <c r="E54" s="50"/>
       <c r="F54" s="48">
         <f>(F51-F50)/365*12</f>
@@ -8757,10 +8757,10 @@
         <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="C55" s="596" t="s">
+      <c r="C55" s="604" t="s">
         <v>117</v>
       </c>
-      <c r="D55" s="595"/>
+      <c r="D55" s="605"/>
       <c r="E55" s="63"/>
       <c r="F55" s="48">
         <v>0</v>
@@ -8786,10 +8786,10 @@
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="C56" s="596" t="s">
+      <c r="C56" s="604" t="s">
         <v>118</v>
       </c>
-      <c r="D56" s="595"/>
+      <c r="D56" s="605"/>
       <c r="E56" s="63"/>
       <c r="F56" s="290" t="s">
         <v>64</v>
@@ -8815,10 +8815,10 @@
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="C57" s="596" t="s">
+      <c r="C57" s="604" t="s">
         <v>119</v>
       </c>
-      <c r="D57" s="595"/>
+      <c r="D57" s="605"/>
       <c r="E57" s="63"/>
       <c r="F57" s="48"/>
       <c r="G57" s="376"/>
@@ -8833,23 +8833,23 @@
       <c r="C58" s="66"/>
       <c r="D58" s="66"/>
       <c r="E58" s="50"/>
-      <c r="F58" s="602" t="s">
+      <c r="F58" s="594" t="s">
         <v>69</v>
       </c>
-      <c r="G58" s="636"/>
+      <c r="G58" s="595"/>
       <c r="H58" s="392"/>
-      <c r="I58" s="637" t="s">
+      <c r="I58" s="596" t="s">
         <v>63</v>
       </c>
-      <c r="J58" s="638"/>
+      <c r="J58" s="597"/>
     </row>
     <row r="59" spans="1:18" ht="15.9" customHeight="1">
       <c r="A59" s="43"/>
-      <c r="B59" s="639" t="s">
+      <c r="B59" s="668" t="s">
         <v>120</v>
       </c>
-      <c r="C59" s="640"/>
-      <c r="D59" s="640"/>
+      <c r="C59" s="669"/>
+      <c r="D59" s="669"/>
       <c r="E59" s="485"/>
       <c r="F59" s="364" t="s">
         <v>71</v>
@@ -8870,10 +8870,10 @@
       <c r="B60" s="154">
         <v>1</v>
       </c>
-      <c r="C60" s="594" t="s">
+      <c r="C60" s="598" t="s">
         <v>121</v>
       </c>
-      <c r="D60" s="595"/>
+      <c r="D60" s="605"/>
       <c r="E60" s="487"/>
       <c r="F60" s="62">
         <f>C220/F21/F54</f>
@@ -8899,10 +8899,10 @@
         <f>1+B60</f>
         <v>2</v>
       </c>
-      <c r="C61" s="594" t="s">
+      <c r="C61" s="598" t="s">
         <v>122</v>
       </c>
-      <c r="D61" s="595"/>
+      <c r="D61" s="605"/>
       <c r="E61" s="487"/>
       <c r="F61" s="62">
         <v>0</v>
@@ -8926,10 +8926,10 @@
         <f t="shared" ref="B62:B83" si="4">1+B61</f>
         <v>3</v>
       </c>
-      <c r="C62" s="597" t="s">
+      <c r="C62" s="600" t="s">
         <v>123</v>
       </c>
-      <c r="D62" s="598"/>
+      <c r="D62" s="601"/>
       <c r="E62" s="67"/>
       <c r="F62" s="68">
         <f>F60+F61</f>
@@ -8955,10 +8955,10 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="C63" s="594" t="s">
+      <c r="C63" s="598" t="s">
         <v>317</v>
       </c>
-      <c r="D63" s="595"/>
+      <c r="D63" s="605"/>
       <c r="E63" s="48"/>
       <c r="F63" s="46">
         <f>F62*F21</f>
@@ -8984,10 +8984,10 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="C64" s="594" t="s">
+      <c r="C64" s="598" t="s">
         <v>124</v>
       </c>
-      <c r="D64" s="595"/>
+      <c r="D64" s="605"/>
       <c r="E64" s="48"/>
       <c r="F64" s="62">
         <f>I220/F21/F54</f>
@@ -9013,10 +9013,10 @@
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="C65" s="596" t="s">
+      <c r="C65" s="604" t="s">
         <v>318</v>
       </c>
-      <c r="D65" s="595"/>
+      <c r="D65" s="605"/>
       <c r="E65" s="63"/>
       <c r="F65" s="46">
         <f>+F64*F21</f>
@@ -9042,10 +9042,10 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="C66" s="596" t="s">
+      <c r="C66" s="604" t="s">
         <v>319</v>
       </c>
-      <c r="D66" s="595"/>
+      <c r="D66" s="605"/>
       <c r="E66" s="51"/>
       <c r="F66" s="48">
         <f>(+G220/F54)</f>
@@ -9071,10 +9071,10 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="C67" s="596" t="s">
+      <c r="C67" s="604" t="s">
         <v>125</v>
       </c>
-      <c r="D67" s="595"/>
+      <c r="D67" s="605"/>
       <c r="E67" s="48"/>
       <c r="F67" s="48">
         <f>Main!B9</f>
@@ -9100,10 +9100,10 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="C68" s="596" t="s">
+      <c r="C68" s="604" t="s">
         <v>126</v>
       </c>
-      <c r="D68" s="595"/>
+      <c r="D68" s="605"/>
       <c r="E68" s="48"/>
       <c r="F68" s="48">
         <v>0</v>
@@ -9128,10 +9128,10 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="C69" s="594" t="s">
+      <c r="C69" s="598" t="s">
         <v>127</v>
       </c>
-      <c r="D69" s="595"/>
+      <c r="D69" s="605"/>
       <c r="E69" s="48"/>
       <c r="F69" s="48">
         <v>500000</v>
@@ -9156,10 +9156,10 @@
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="C70" s="596" t="s">
+      <c r="C70" s="604" t="s">
         <v>128</v>
       </c>
-      <c r="D70" s="595"/>
+      <c r="D70" s="605"/>
       <c r="E70" s="48"/>
       <c r="F70" s="46">
         <v>0</v>
@@ -9181,10 +9181,10 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="C71" s="596" t="s">
+      <c r="C71" s="604" t="s">
         <v>129</v>
       </c>
-      <c r="D71" s="595"/>
+      <c r="D71" s="605"/>
       <c r="E71" s="48"/>
       <c r="F71" s="46">
         <f>F38*F23*F33</f>
@@ -9210,10 +9210,10 @@
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="C72" s="596" t="s">
+      <c r="C72" s="604" t="s">
         <v>130</v>
       </c>
-      <c r="D72" s="595"/>
+      <c r="D72" s="605"/>
       <c r="E72" s="48"/>
       <c r="F72" s="48">
         <v>0</v>
@@ -9238,10 +9238,10 @@
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="C73" s="594" t="s">
+      <c r="C73" s="598" t="s">
         <v>131</v>
       </c>
-      <c r="D73" s="595"/>
+      <c r="D73" s="605"/>
       <c r="E73" s="486"/>
       <c r="F73" s="60">
         <f>+F35*F63</f>
@@ -9295,10 +9295,10 @@
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="C75" s="594" t="s">
+      <c r="C75" s="598" t="s">
         <v>133</v>
       </c>
-      <c r="D75" s="595"/>
+      <c r="D75" s="605"/>
       <c r="E75" s="51"/>
       <c r="F75" s="48">
         <f>+F77/F23</f>
@@ -9324,10 +9324,10 @@
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="C76" s="594" t="s">
+      <c r="C76" s="598" t="s">
         <v>134</v>
       </c>
-      <c r="D76" s="595"/>
+      <c r="D76" s="605"/>
       <c r="E76" s="63"/>
       <c r="F76" s="43"/>
       <c r="G76" s="481"/>
@@ -9347,10 +9347,10 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="C77" s="594" t="s">
+      <c r="C77" s="598" t="s">
         <v>135</v>
       </c>
-      <c r="D77" s="595"/>
+      <c r="D77" s="605"/>
       <c r="E77" s="63"/>
       <c r="F77" s="48">
         <f>'CAPEX and PM'!B6</f>
@@ -9376,10 +9376,10 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="C78" s="594" t="s">
+      <c r="C78" s="598" t="s">
         <v>136</v>
       </c>
-      <c r="D78" s="595"/>
+      <c r="D78" s="605"/>
       <c r="E78" s="63"/>
       <c r="F78" s="48">
         <f>'CAPEX and PM'!B37</f>
@@ -9405,10 +9405,10 @@
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="C79" s="594" t="s">
+      <c r="C79" s="598" t="s">
         <v>137</v>
       </c>
-      <c r="D79" s="595"/>
+      <c r="D79" s="605"/>
       <c r="E79" s="63"/>
       <c r="F79" s="48">
         <f>+'CAPEX and PM'!B104</f>
@@ -9434,10 +9434,10 @@
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="C80" s="594" t="s">
+      <c r="C80" s="598" t="s">
         <v>138</v>
       </c>
-      <c r="D80" s="595"/>
+      <c r="D80" s="605"/>
       <c r="E80" s="63"/>
       <c r="F80" s="48"/>
       <c r="G80" s="376"/>
@@ -9457,10 +9457,10 @@
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="C81" s="594" t="s">
+      <c r="C81" s="598" t="s">
         <v>139</v>
       </c>
-      <c r="D81" s="604"/>
+      <c r="D81" s="599"/>
       <c r="E81" s="63"/>
       <c r="F81" s="48"/>
       <c r="G81" s="376"/>
@@ -9480,10 +9480,10 @@
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="C82" s="594" t="s">
+      <c r="C82" s="598" t="s">
         <v>140</v>
       </c>
-      <c r="D82" s="595"/>
+      <c r="D82" s="605"/>
       <c r="E82" s="51"/>
       <c r="F82" s="48">
         <f>+G207</f>
@@ -9509,10 +9509,10 @@
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="C83" s="594" t="s">
+      <c r="C83" s="598" t="s">
         <v>320</v>
       </c>
-      <c r="D83" s="595"/>
+      <c r="D83" s="605"/>
       <c r="E83" s="486"/>
       <c r="F83" s="48">
         <f>+F30</f>
@@ -9545,11 +9545,11 @@
     </row>
     <row r="85" spans="1:24" ht="15.9" customHeight="1">
       <c r="A85" s="43"/>
-      <c r="B85" s="616" t="s">
+      <c r="B85" s="606" t="s">
         <v>141</v>
       </c>
-      <c r="C85" s="617"/>
-      <c r="D85" s="618"/>
+      <c r="C85" s="607"/>
+      <c r="D85" s="608"/>
       <c r="E85" s="377"/>
       <c r="F85" s="153" t="s">
         <v>71</v>
@@ -9570,10 +9570,10 @@
       <c r="B86" s="154">
         <v>1</v>
       </c>
-      <c r="C86" s="594" t="s">
+      <c r="C86" s="598" t="s">
         <v>142</v>
       </c>
-      <c r="D86" s="595"/>
+      <c r="D86" s="605"/>
       <c r="E86" s="63"/>
       <c r="F86" s="62">
         <f>+F62</f>
@@ -9602,10 +9602,10 @@
         <f>1+B86</f>
         <v>2</v>
       </c>
-      <c r="C87" s="596" t="s">
+      <c r="C87" s="604" t="s">
         <v>143</v>
       </c>
-      <c r="D87" s="595"/>
+      <c r="D87" s="605"/>
       <c r="E87" s="65"/>
       <c r="F87" s="48">
         <v>0</v>
@@ -9628,10 +9628,10 @@
         <f t="shared" ref="B88:B94" si="7">+B87+1</f>
         <v>3</v>
       </c>
-      <c r="C88" s="596" t="s">
+      <c r="C88" s="604" t="s">
         <v>144</v>
       </c>
-      <c r="D88" s="595"/>
+      <c r="D88" s="605"/>
       <c r="E88" s="65"/>
       <c r="F88" s="62">
         <f>(F66/F23)</f>
@@ -9659,10 +9659,10 @@
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="C89" s="596" t="s">
+      <c r="C89" s="604" t="s">
         <v>145</v>
       </c>
-      <c r="D89" s="595"/>
+      <c r="D89" s="605"/>
       <c r="E89" s="65"/>
       <c r="F89" s="58">
         <f>'Security Deposit'!C17</f>
@@ -9690,10 +9690,10 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="C90" s="596" t="s">
+      <c r="C90" s="604" t="s">
         <v>285</v>
       </c>
-      <c r="D90" s="595"/>
+      <c r="D90" s="605"/>
       <c r="E90" s="65"/>
       <c r="F90" s="190">
         <f>+F64</f>
@@ -9721,10 +9721,10 @@
         <f>+B89+1</f>
         <v>5</v>
       </c>
-      <c r="C91" s="596" t="s">
+      <c r="C91" s="604" t="s">
         <v>146</v>
       </c>
-      <c r="D91" s="595"/>
+      <c r="D91" s="605"/>
       <c r="E91" s="65"/>
       <c r="F91" s="58">
         <f>(+F83/F21/F54)</f>
@@ -9751,10 +9751,10 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="C92" s="596" t="s">
+      <c r="C92" s="604" t="s">
         <v>147</v>
       </c>
-      <c r="D92" s="595"/>
+      <c r="D92" s="605"/>
       <c r="E92" s="65"/>
       <c r="F92" s="58">
         <f>F82/F21/F54</f>
@@ -9782,10 +9782,10 @@
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="C93" s="594" t="s">
+      <c r="C93" s="598" t="s">
         <v>148</v>
       </c>
-      <c r="D93" s="595"/>
+      <c r="D93" s="605"/>
       <c r="E93" s="63"/>
       <c r="F93" s="58">
         <f>+G93/F6</f>
@@ -9813,10 +9813,10 @@
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="C94" s="597" t="s">
+      <c r="C94" s="600" t="s">
         <v>65</v>
       </c>
-      <c r="D94" s="598"/>
+      <c r="D94" s="601"/>
       <c r="E94" s="70"/>
       <c r="F94" s="201">
         <f>SUM(F86:F93)</f>
@@ -9841,8 +9841,8 @@
     <row r="95" spans="1:24" ht="15.9" customHeight="1">
       <c r="A95" s="43"/>
       <c r="B95" s="369"/>
-      <c r="C95" s="636"/>
-      <c r="D95" s="636"/>
+      <c r="C95" s="595"/>
+      <c r="D95" s="595"/>
       <c r="E95" s="76"/>
       <c r="F95" s="77"/>
       <c r="G95" s="77"/>
@@ -9852,11 +9852,11 @@
     </row>
     <row r="96" spans="1:24" ht="15.9" customHeight="1">
       <c r="A96" s="43"/>
-      <c r="B96" s="599" t="s">
+      <c r="B96" s="602" t="s">
         <v>149</v>
       </c>
-      <c r="C96" s="600"/>
-      <c r="D96" s="600"/>
+      <c r="C96" s="603"/>
+      <c r="D96" s="603"/>
       <c r="E96" s="79"/>
       <c r="F96" s="153" t="s">
         <v>71</v>
@@ -9878,11 +9878,11 @@
       <c r="B97" s="154">
         <v>1</v>
       </c>
-      <c r="C97" s="596" t="str">
+      <c r="C97" s="604" t="str">
         <f>+C76</f>
         <v>Siemens Standard Fitout (Existing)</v>
       </c>
-      <c r="D97" s="595"/>
+      <c r="D97" s="605"/>
       <c r="E97" s="80"/>
       <c r="F97" s="58">
         <v>0</v>
@@ -9908,11 +9908,11 @@
         <f t="shared" ref="B98:B103" si="8">+B97+1</f>
         <v>2</v>
       </c>
-      <c r="C98" s="596" t="str">
+      <c r="C98" s="604" t="str">
         <f>+C77</f>
         <v>Siemens Standard Fitout (New)</v>
       </c>
-      <c r="D98" s="595"/>
+      <c r="D98" s="605"/>
       <c r="E98" s="63"/>
       <c r="F98" s="58">
         <f>'CAPEX and PM'!B29</f>
@@ -9940,11 +9940,11 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="C99" s="596" t="str">
+      <c r="C99" s="604" t="str">
         <f>+C78</f>
         <v>Capex over the period of lease period</v>
       </c>
-      <c r="D99" s="595"/>
+      <c r="D99" s="605"/>
       <c r="E99" s="63"/>
       <c r="F99" s="58">
         <f>'CAPEX and PM'!B98</f>
@@ -9972,11 +9972,11 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="C100" s="596" t="str">
+      <c r="C100" s="604" t="str">
         <f>+C79</f>
         <v>PM cost over the period of lease period</v>
       </c>
-      <c r="D100" s="595"/>
+      <c r="D100" s="605"/>
       <c r="E100" s="63"/>
       <c r="F100" s="58">
         <f>+'CAPEX and PM'!B105</f>
@@ -10004,11 +10004,11 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="C101" s="596" t="str">
+      <c r="C101" s="604" t="str">
         <f>+C80</f>
         <v>Asset Retirement Obligation ( Removal &amp; Restoration Obligation)</v>
       </c>
-      <c r="D101" s="595"/>
+      <c r="D101" s="605"/>
       <c r="E101" s="63"/>
       <c r="F101" s="58">
         <f>'Security Deposit'!D25</f>
@@ -10039,10 +10039,10 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="C102" s="594" t="s">
+      <c r="C102" s="598" t="s">
         <v>150</v>
       </c>
-      <c r="D102" s="595"/>
+      <c r="D102" s="605"/>
       <c r="E102" s="65"/>
       <c r="F102" s="58">
         <f>+F81/F21/F27</f>
@@ -10070,10 +10070,10 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="C103" s="597" t="s">
+      <c r="C103" s="600" t="s">
         <v>151</v>
       </c>
-      <c r="D103" s="598"/>
+      <c r="D103" s="601"/>
       <c r="E103" s="70"/>
       <c r="F103" s="46">
         <f>SUM(F97:F102)</f>
@@ -10110,11 +10110,11 @@
     </row>
     <row r="105" spans="1:26" ht="15.9" customHeight="1">
       <c r="A105" s="43"/>
-      <c r="B105" s="690" t="s">
+      <c r="B105" s="609" t="s">
         <v>152</v>
       </c>
-      <c r="C105" s="611"/>
-      <c r="D105" s="611"/>
+      <c r="C105" s="610"/>
+      <c r="D105" s="610"/>
       <c r="E105" s="79"/>
       <c r="F105" s="153" t="s">
         <v>71</v>
@@ -10135,10 +10135,10 @@
       <c r="B106" s="154">
         <v>1</v>
       </c>
-      <c r="C106" s="594" t="s">
+      <c r="C106" s="598" t="s">
         <v>65</v>
       </c>
-      <c r="D106" s="595"/>
+      <c r="D106" s="605"/>
       <c r="E106" s="63"/>
       <c r="F106" s="48">
         <f>+F94</f>
@@ -10166,10 +10166,10 @@
         <f>+B106+1</f>
         <v>2</v>
       </c>
-      <c r="C107" s="594" t="s">
+      <c r="C107" s="598" t="s">
         <v>151</v>
       </c>
-      <c r="D107" s="604"/>
+      <c r="D107" s="599"/>
       <c r="E107" s="63"/>
       <c r="F107" s="48">
         <f>+F103</f>
@@ -10197,10 +10197,10 @@
         <f>+B107+1</f>
         <v>3</v>
       </c>
-      <c r="C108" s="597" t="s">
+      <c r="C108" s="600" t="s">
         <v>153</v>
       </c>
-      <c r="D108" s="598"/>
+      <c r="D108" s="601"/>
       <c r="E108" s="70"/>
       <c r="F108" s="46">
         <f>SUM(F106:F107)</f>
@@ -10229,11 +10229,11 @@
     </row>
     <row r="109" spans="1:26" ht="15.9" customHeight="1">
       <c r="A109" s="43"/>
-      <c r="B109" s="599" t="s">
+      <c r="B109" s="602" t="s">
         <v>154</v>
       </c>
-      <c r="C109" s="600"/>
-      <c r="D109" s="600"/>
+      <c r="C109" s="603"/>
+      <c r="D109" s="603"/>
       <c r="E109" s="81"/>
       <c r="F109" s="153" t="s">
         <v>71</v>
@@ -10255,10 +10255,10 @@
       <c r="B110" s="237">
         <v>1</v>
       </c>
-      <c r="C110" s="594" t="s">
+      <c r="C110" s="598" t="s">
         <v>155</v>
       </c>
-      <c r="D110" s="604"/>
+      <c r="D110" s="599"/>
       <c r="E110" s="75"/>
       <c r="F110" s="364"/>
       <c r="G110" s="364"/>
@@ -10272,10 +10272,10 @@
         <f t="shared" ref="B111:B119" si="9">1+B110</f>
         <v>2</v>
       </c>
-      <c r="C111" s="594" t="s">
+      <c r="C111" s="598" t="s">
         <v>156</v>
       </c>
-      <c r="D111" s="604"/>
+      <c r="D111" s="599"/>
       <c r="E111" s="75"/>
       <c r="F111" s="364"/>
       <c r="G111" s="364"/>
@@ -10291,10 +10291,10 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="C112" s="594" t="s">
+      <c r="C112" s="598" t="s">
         <v>157</v>
       </c>
-      <c r="D112" s="604"/>
+      <c r="D112" s="599"/>
       <c r="E112" s="75"/>
       <c r="F112" s="376">
         <f>+F64*0</f>
@@ -10322,10 +10322,10 @@
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="C113" s="594" t="s">
+      <c r="C113" s="598" t="s">
         <v>158</v>
       </c>
-      <c r="D113" s="604"/>
+      <c r="D113" s="599"/>
       <c r="E113" s="75"/>
       <c r="F113" s="364"/>
       <c r="G113" s="364"/>
@@ -10339,10 +10339,10 @@
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="C114" s="594" t="s">
+      <c r="C114" s="598" t="s">
         <v>159</v>
       </c>
-      <c r="D114" s="604"/>
+      <c r="D114" s="599"/>
       <c r="E114" s="75"/>
       <c r="F114" s="364"/>
       <c r="G114" s="364"/>
@@ -10356,10 +10356,10 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="C115" s="594" t="s">
+      <c r="C115" s="598" t="s">
         <v>160</v>
       </c>
-      <c r="D115" s="604"/>
+      <c r="D115" s="599"/>
       <c r="E115" s="75"/>
       <c r="F115" s="364"/>
       <c r="G115" s="364"/>
@@ -10373,10 +10373,10 @@
         <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="C116" s="594" t="s">
+      <c r="C116" s="598" t="s">
         <v>161</v>
       </c>
-      <c r="D116" s="604"/>
+      <c r="D116" s="599"/>
       <c r="E116" s="75"/>
       <c r="F116" s="364"/>
       <c r="G116" s="364"/>
@@ -10390,10 +10390,10 @@
         <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="C117" s="594" t="s">
+      <c r="C117" s="598" t="s">
         <v>162</v>
       </c>
-      <c r="D117" s="595"/>
+      <c r="D117" s="605"/>
       <c r="E117" s="240"/>
       <c r="F117" s="348">
         <v>654</v>
@@ -10419,10 +10419,10 @@
         <f t="shared" si="9"/>
         <v>9</v>
       </c>
-      <c r="C118" s="594" t="s">
+      <c r="C118" s="598" t="s">
         <v>163</v>
       </c>
-      <c r="D118" s="604"/>
+      <c r="D118" s="599"/>
       <c r="E118" s="240"/>
       <c r="F118" s="82">
         <f>F117*7%</f>
@@ -10448,10 +10448,10 @@
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="C119" s="597" t="s">
+      <c r="C119" s="600" t="s">
         <v>164</v>
       </c>
-      <c r="D119" s="598"/>
+      <c r="D119" s="601"/>
       <c r="E119" s="241"/>
       <c r="F119" s="46">
         <f>SUM(F110:F118)</f>
@@ -10477,8 +10477,8 @@
     <row r="120" spans="1:26" ht="15.9" customHeight="1">
       <c r="A120" s="69"/>
       <c r="B120" s="154"/>
-      <c r="C120" s="602"/>
-      <c r="D120" s="603"/>
+      <c r="C120" s="594"/>
+      <c r="D120" s="611"/>
       <c r="E120" s="70"/>
       <c r="F120" s="46"/>
       <c r="G120" s="373"/>
@@ -10492,11 +10492,11 @@
     </row>
     <row r="121" spans="1:26" ht="15.9" customHeight="1">
       <c r="A121" s="69"/>
-      <c r="B121" s="599" t="s">
+      <c r="B121" s="602" t="s">
         <v>165</v>
       </c>
-      <c r="C121" s="600"/>
-      <c r="D121" s="600"/>
+      <c r="C121" s="603"/>
+      <c r="D121" s="603"/>
       <c r="E121" s="81"/>
       <c r="F121" s="153" t="s">
         <v>71</v>
@@ -10519,13 +10519,16 @@
       <c r="B122" s="239">
         <v>1</v>
       </c>
-      <c r="C122" s="594" t="s">
+      <c r="C122" s="598" t="s">
         <v>166</v>
       </c>
-      <c r="D122" s="604"/>
+      <c r="D122" s="599"/>
       <c r="E122" s="70"/>
       <c r="F122" s="46"/>
-      <c r="G122" s="373"/>
+      <c r="G122" s="373">
+        <f>F122*F6</f>
+        <v>0</v>
+      </c>
       <c r="H122" s="392"/>
       <c r="I122" s="180"/>
       <c r="J122" s="74"/>
@@ -10535,10 +10538,10 @@
       <c r="B123" s="154">
         <v>2</v>
       </c>
-      <c r="C123" s="597" t="s">
+      <c r="C123" s="600" t="s">
         <v>167</v>
       </c>
-      <c r="D123" s="598"/>
+      <c r="D123" s="601"/>
       <c r="E123" s="70"/>
       <c r="F123" s="46">
         <f>SUM(F122)</f>
@@ -10561,8 +10564,8 @@
     <row r="124" spans="1:26" ht="15.9" customHeight="1">
       <c r="A124" s="69"/>
       <c r="B124" s="154"/>
-      <c r="C124" s="602"/>
-      <c r="D124" s="603"/>
+      <c r="C124" s="594"/>
+      <c r="D124" s="611"/>
       <c r="E124" s="55"/>
       <c r="F124" s="46"/>
       <c r="G124" s="373"/>
@@ -10572,11 +10575,11 @@
     </row>
     <row r="125" spans="1:26" ht="15.9" customHeight="1">
       <c r="A125" s="69"/>
-      <c r="B125" s="599" t="s">
+      <c r="B125" s="602" t="s">
         <v>168</v>
       </c>
-      <c r="C125" s="600"/>
-      <c r="D125" s="600"/>
+      <c r="C125" s="603"/>
+      <c r="D125" s="603"/>
       <c r="E125" s="81"/>
       <c r="F125" s="153" t="s">
         <v>71</v>
@@ -10597,10 +10600,10 @@
       <c r="B126" s="237">
         <v>1</v>
       </c>
-      <c r="C126" s="594" t="s">
+      <c r="C126" s="598" t="s">
         <v>169</v>
       </c>
-      <c r="D126" s="604"/>
+      <c r="D126" s="599"/>
       <c r="E126" s="238"/>
       <c r="F126" s="373"/>
       <c r="G126" s="373"/>
@@ -10614,10 +10617,10 @@
         <f>1+B126</f>
         <v>2</v>
       </c>
-      <c r="C127" s="594" t="s">
+      <c r="C127" s="598" t="s">
         <v>170</v>
       </c>
-      <c r="D127" s="604"/>
+      <c r="D127" s="599"/>
       <c r="E127" s="238"/>
       <c r="F127" s="373"/>
       <c r="G127" s="373"/>
@@ -10631,10 +10634,10 @@
         <f>1+B127</f>
         <v>3</v>
       </c>
-      <c r="C128" s="594" t="s">
+      <c r="C128" s="598" t="s">
         <v>171</v>
       </c>
-      <c r="D128" s="604"/>
+      <c r="D128" s="599"/>
       <c r="E128" s="238"/>
       <c r="F128" s="373"/>
       <c r="G128" s="373"/>
@@ -10648,10 +10651,10 @@
         <f>1+B128</f>
         <v>4</v>
       </c>
-      <c r="C129" s="594" t="s">
+      <c r="C129" s="598" t="s">
         <v>172</v>
       </c>
-      <c r="D129" s="604"/>
+      <c r="D129" s="599"/>
       <c r="E129" s="238"/>
       <c r="F129" s="373"/>
       <c r="G129" s="373"/>
@@ -10665,10 +10668,10 @@
         <f>1+B129</f>
         <v>5</v>
       </c>
-      <c r="C130" s="594" t="s">
+      <c r="C130" s="598" t="s">
         <v>173</v>
       </c>
-      <c r="D130" s="604"/>
+      <c r="D130" s="599"/>
       <c r="E130" s="238"/>
       <c r="F130" s="373"/>
       <c r="G130" s="373"/>
@@ -10682,10 +10685,10 @@
         <f>1+B130</f>
         <v>6</v>
       </c>
-      <c r="C131" s="594" t="s">
+      <c r="C131" s="598" t="s">
         <v>174</v>
       </c>
-      <c r="D131" s="604"/>
+      <c r="D131" s="599"/>
       <c r="E131" s="238"/>
       <c r="F131" s="373"/>
       <c r="G131" s="373"/>
@@ -10698,10 +10701,10 @@
       <c r="B132" s="369">
         <v>7</v>
       </c>
-      <c r="C132" s="597" t="s">
+      <c r="C132" s="600" t="s">
         <v>175</v>
       </c>
-      <c r="D132" s="598"/>
+      <c r="D132" s="601"/>
       <c r="E132" s="238"/>
       <c r="F132" s="373">
         <f>SUM(F126:F131)</f>
@@ -10724,8 +10727,8 @@
     <row r="133" spans="1:20" ht="15.9" customHeight="1">
       <c r="A133" s="69"/>
       <c r="B133" s="154"/>
-      <c r="C133" s="636"/>
-      <c r="D133" s="603"/>
+      <c r="C133" s="595"/>
+      <c r="D133" s="611"/>
       <c r="E133" s="238"/>
       <c r="F133" s="373"/>
       <c r="G133" s="373"/>
@@ -10735,11 +10738,11 @@
     </row>
     <row r="134" spans="1:20" ht="15.9" customHeight="1">
       <c r="A134" s="43"/>
-      <c r="B134" s="599" t="s">
+      <c r="B134" s="602" t="s">
         <v>176</v>
       </c>
-      <c r="C134" s="600"/>
-      <c r="D134" s="600"/>
+      <c r="C134" s="603"/>
+      <c r="D134" s="603"/>
       <c r="E134" s="81"/>
       <c r="F134" s="153" t="s">
         <v>71</v>
@@ -10760,10 +10763,10 @@
       <c r="B135" s="154">
         <v>1</v>
       </c>
-      <c r="C135" s="597" t="s">
+      <c r="C135" s="600" t="s">
         <v>177</v>
       </c>
-      <c r="D135" s="598"/>
+      <c r="D135" s="601"/>
       <c r="E135" s="70"/>
       <c r="F135" s="46">
         <f>F119+F108+F123+F132</f>
@@ -10788,8 +10791,8 @@
     <row r="136" spans="1:20" ht="15.9" customHeight="1">
       <c r="A136" s="69"/>
       <c r="B136" s="154"/>
-      <c r="C136" s="602"/>
-      <c r="D136" s="603"/>
+      <c r="C136" s="594"/>
+      <c r="D136" s="611"/>
       <c r="E136" s="70"/>
       <c r="F136" s="46"/>
       <c r="G136" s="373"/>
@@ -10803,23 +10806,23 @@
       <c r="C137" s="368"/>
       <c r="D137" s="365"/>
       <c r="E137" s="159"/>
-      <c r="F137" s="602" t="s">
+      <c r="F137" s="594" t="s">
         <v>69</v>
       </c>
-      <c r="G137" s="636"/>
+      <c r="G137" s="595"/>
       <c r="H137" s="392"/>
-      <c r="I137" s="637" t="s">
+      <c r="I137" s="596" t="s">
         <v>63</v>
       </c>
-      <c r="J137" s="638"/>
+      <c r="J137" s="597"/>
     </row>
     <row r="138" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A138" s="43"/>
-      <c r="B138" s="599" t="s">
+      <c r="B138" s="602" t="s">
         <v>178</v>
       </c>
-      <c r="C138" s="600"/>
-      <c r="D138" s="601"/>
+      <c r="C138" s="603"/>
+      <c r="D138" s="618"/>
       <c r="E138" s="153"/>
       <c r="F138" s="153" t="s">
         <v>71</v>
@@ -10838,8 +10841,8 @@
     <row r="139" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A139" s="43"/>
       <c r="B139" s="83"/>
-      <c r="C139" s="605"/>
-      <c r="D139" s="606"/>
+      <c r="C139" s="619"/>
+      <c r="D139" s="620"/>
       <c r="E139" s="155"/>
       <c r="F139" s="46"/>
       <c r="G139" s="373"/>
@@ -10850,10 +10853,10 @@
     <row r="140" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A140" s="43"/>
       <c r="B140" s="83"/>
-      <c r="C140" s="594" t="s">
+      <c r="C140" s="598" t="s">
         <v>179</v>
       </c>
-      <c r="D140" s="595"/>
+      <c r="D140" s="605"/>
       <c r="E140" s="50"/>
       <c r="F140" s="231">
         <f>F21</f>
@@ -10876,10 +10879,10 @@
     <row r="141" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A141" s="43"/>
       <c r="B141" s="83"/>
-      <c r="C141" s="596" t="s">
+      <c r="C141" s="604" t="s">
         <v>180</v>
       </c>
-      <c r="D141" s="595"/>
+      <c r="D141" s="605"/>
       <c r="E141" s="51"/>
       <c r="F141" s="48">
         <f>F24</f>
@@ -10902,10 +10905,10 @@
     <row r="142" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A142" s="43"/>
       <c r="B142" s="83"/>
-      <c r="C142" s="596" t="s">
+      <c r="C142" s="604" t="s">
         <v>181</v>
       </c>
-      <c r="D142" s="595"/>
+      <c r="D142" s="605"/>
       <c r="E142" s="65"/>
       <c r="F142" s="48" t="e">
         <f>+#REF!</f>
@@ -10928,10 +10931,10 @@
     <row r="143" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A143" s="43"/>
       <c r="B143" s="83"/>
-      <c r="C143" s="594" t="s">
+      <c r="C143" s="598" t="s">
         <v>182</v>
       </c>
-      <c r="D143" s="595"/>
+      <c r="D143" s="605"/>
       <c r="E143" s="65"/>
       <c r="F143" s="48">
         <f>F108</f>
@@ -10954,10 +10957,10 @@
     <row r="144" spans="1:20" ht="15.9" hidden="1" customHeight="1">
       <c r="A144" s="43"/>
       <c r="B144" s="83"/>
-      <c r="C144" s="624" t="s">
+      <c r="C144" s="689" t="s">
         <v>183</v>
       </c>
-      <c r="D144" s="625"/>
+      <c r="D144" s="690"/>
       <c r="E144" s="84"/>
       <c r="F144" s="85">
         <f>F119</f>
@@ -10980,10 +10983,10 @@
     <row r="145" spans="1:10" ht="15.9" hidden="1" customHeight="1">
       <c r="A145" s="69"/>
       <c r="B145" s="154"/>
-      <c r="C145" s="597" t="s">
+      <c r="C145" s="600" t="s">
         <v>184</v>
       </c>
-      <c r="D145" s="598"/>
+      <c r="D145" s="601"/>
       <c r="E145" s="70"/>
       <c r="F145" s="233" t="e">
         <f>F135*#REF!</f>
@@ -11017,11 +11020,11 @@
     </row>
     <row r="147" spans="1:10" ht="15.9" customHeight="1">
       <c r="A147" s="69"/>
-      <c r="B147" s="599" t="s">
+      <c r="B147" s="602" t="s">
         <v>185</v>
       </c>
-      <c r="C147" s="600"/>
-      <c r="D147" s="601"/>
+      <c r="C147" s="603"/>
+      <c r="D147" s="618"/>
       <c r="E147" s="367"/>
       <c r="F147" s="367" t="s">
         <v>186</v>
@@ -11040,8 +11043,8 @@
     <row r="148" spans="1:10" ht="15.9" customHeight="1">
       <c r="A148" s="43"/>
       <c r="B148" s="91"/>
-      <c r="C148" s="605"/>
-      <c r="D148" s="606"/>
+      <c r="C148" s="619"/>
+      <c r="D148" s="620"/>
       <c r="E148" s="92"/>
       <c r="F148" s="93"/>
       <c r="G148" s="197"/>
@@ -11052,10 +11055,10 @@
     <row r="149" spans="1:10" ht="15.9" customHeight="1">
       <c r="A149" s="43"/>
       <c r="B149" s="91"/>
-      <c r="C149" s="596" t="s">
+      <c r="C149" s="604" t="s">
         <v>187</v>
       </c>
-      <c r="D149" s="595"/>
+      <c r="D149" s="605"/>
       <c r="E149" s="92"/>
       <c r="F149" s="93">
         <f>(+F63)*115%</f>
@@ -11078,10 +11081,10 @@
     <row r="150" spans="1:10" ht="15.9" customHeight="1">
       <c r="A150" s="43"/>
       <c r="B150" s="91"/>
-      <c r="C150" s="596" t="s">
+      <c r="C150" s="604" t="s">
         <v>188</v>
       </c>
-      <c r="D150" s="595"/>
+      <c r="D150" s="605"/>
       <c r="E150" s="92"/>
       <c r="F150" s="93">
         <v>0</v>
@@ -11100,10 +11103,10 @@
     <row r="151" spans="1:10" ht="15.9" customHeight="1">
       <c r="A151" s="43"/>
       <c r="B151" s="91"/>
-      <c r="C151" s="596" t="s">
+      <c r="C151" s="604" t="s">
         <v>189</v>
       </c>
-      <c r="D151" s="595"/>
+      <c r="D151" s="605"/>
       <c r="E151" s="92"/>
       <c r="F151" s="93">
         <f>(+F65)*115%</f>
@@ -11126,10 +11129,10 @@
     <row r="152" spans="1:10" ht="15.9" customHeight="1">
       <c r="A152" s="43"/>
       <c r="B152" s="91"/>
-      <c r="C152" s="596" t="s">
+      <c r="C152" s="604" t="s">
         <v>190</v>
       </c>
-      <c r="D152" s="595"/>
+      <c r="D152" s="605"/>
       <c r="E152" s="92"/>
       <c r="F152" s="93">
         <f>(+F66)*115%</f>
@@ -11152,10 +11155,10 @@
     <row r="153" spans="1:10" ht="15.9" customHeight="1">
       <c r="A153" s="43"/>
       <c r="B153" s="91"/>
-      <c r="C153" s="594" t="s">
+      <c r="C153" s="598" t="s">
         <v>191</v>
       </c>
-      <c r="D153" s="595"/>
+      <c r="D153" s="605"/>
       <c r="E153" s="95"/>
       <c r="F153" s="96">
         <f>SUM(F149:F152)</f>
@@ -11178,10 +11181,10 @@
     <row r="154" spans="1:10" ht="15.9" customHeight="1">
       <c r="A154" s="43"/>
       <c r="B154" s="91"/>
-      <c r="C154" s="594" t="s">
+      <c r="C154" s="598" t="s">
         <v>192</v>
       </c>
-      <c r="D154" s="595"/>
+      <c r="D154" s="605"/>
       <c r="E154" s="97"/>
       <c r="F154" s="93">
         <f>+F153*12</f>
@@ -11204,8 +11207,8 @@
     <row r="155" spans="1:10" ht="15.9" customHeight="1">
       <c r="A155" s="43"/>
       <c r="B155" s="91"/>
-      <c r="C155" s="605"/>
-      <c r="D155" s="606"/>
+      <c r="C155" s="619"/>
+      <c r="D155" s="620"/>
       <c r="E155" s="97"/>
       <c r="F155" s="93"/>
       <c r="G155" s="197"/>
@@ -11215,11 +11218,11 @@
     </row>
     <row r="156" spans="1:10" ht="15.9" customHeight="1">
       <c r="A156" s="43"/>
-      <c r="B156" s="599" t="s">
+      <c r="B156" s="602" t="s">
         <v>193</v>
       </c>
-      <c r="C156" s="600"/>
-      <c r="D156" s="601"/>
+      <c r="C156" s="603"/>
+      <c r="D156" s="618"/>
       <c r="E156" s="363"/>
       <c r="F156" s="367" t="s">
         <v>186</v>
@@ -11238,8 +11241,8 @@
     <row r="157" spans="1:10" ht="15.9" customHeight="1">
       <c r="A157" s="43"/>
       <c r="B157" s="91"/>
-      <c r="C157" s="605"/>
-      <c r="D157" s="606"/>
+      <c r="C157" s="619"/>
+      <c r="D157" s="620"/>
       <c r="E157" s="97"/>
       <c r="F157" s="93"/>
       <c r="G157" s="197"/>
@@ -11250,10 +11253,10 @@
     <row r="158" spans="1:10" ht="15.9" customHeight="1">
       <c r="A158" s="43"/>
       <c r="B158" s="91"/>
-      <c r="C158" s="622" t="s">
+      <c r="C158" s="687" t="s">
         <v>194</v>
       </c>
-      <c r="D158" s="623"/>
+      <c r="D158" s="688"/>
       <c r="E158" s="97"/>
       <c r="F158" s="93">
         <f t="shared" ref="F158:G160" si="10">+F77</f>
@@ -11276,10 +11279,10 @@
     <row r="159" spans="1:10" ht="15.9" customHeight="1">
       <c r="A159" s="43"/>
       <c r="B159" s="91"/>
-      <c r="C159" s="594" t="s">
+      <c r="C159" s="598" t="s">
         <v>195</v>
       </c>
-      <c r="D159" s="604"/>
+      <c r="D159" s="599"/>
       <c r="E159" s="97"/>
       <c r="F159" s="93">
         <f t="shared" si="10"/>
@@ -11302,10 +11305,10 @@
     <row r="160" spans="1:10" ht="15.9" customHeight="1">
       <c r="A160" s="43"/>
       <c r="B160" s="91"/>
-      <c r="C160" s="594" t="s">
+      <c r="C160" s="598" t="s">
         <v>196</v>
       </c>
-      <c r="D160" s="604"/>
+      <c r="D160" s="599"/>
       <c r="E160" s="97"/>
       <c r="F160" s="93">
         <f t="shared" si="10"/>
@@ -11328,10 +11331,10 @@
     <row r="161" spans="1:22" ht="15.9" customHeight="1">
       <c r="A161" s="43"/>
       <c r="B161" s="91"/>
-      <c r="C161" s="597" t="s">
+      <c r="C161" s="600" t="s">
         <v>29</v>
       </c>
-      <c r="D161" s="598"/>
+      <c r="D161" s="601"/>
       <c r="E161" s="97"/>
       <c r="F161" s="225">
         <f>SUM(F158:F160)</f>
@@ -11354,8 +11357,8 @@
     <row r="162" spans="1:22" ht="15.9" customHeight="1">
       <c r="A162" s="43"/>
       <c r="B162" s="91"/>
-      <c r="C162" s="605"/>
-      <c r="D162" s="606"/>
+      <c r="C162" s="619"/>
+      <c r="D162" s="620"/>
       <c r="E162" s="97"/>
       <c r="F162" s="93"/>
       <c r="G162" s="197"/>
@@ -11365,12 +11368,12 @@
     </row>
     <row r="163" spans="1:22" ht="15.9" customHeight="1">
       <c r="A163" s="98"/>
-      <c r="B163" s="616" t="s">
+      <c r="B163" s="606" t="s">
         <v>197</v>
       </c>
-      <c r="C163" s="617"/>
-      <c r="D163" s="618"/>
-      <c r="E163" s="689"/>
+      <c r="C163" s="607"/>
+      <c r="D163" s="608"/>
+      <c r="E163" s="616"/>
       <c r="F163" s="153" t="s">
         <v>71</v>
       </c>
@@ -11387,10 +11390,10 @@
     </row>
     <row r="164" spans="1:22" ht="15.9" customHeight="1">
       <c r="A164" s="98"/>
-      <c r="B164" s="619"/>
-      <c r="C164" s="620"/>
-      <c r="D164" s="621"/>
-      <c r="E164" s="609"/>
+      <c r="B164" s="684"/>
+      <c r="C164" s="685"/>
+      <c r="D164" s="686"/>
+      <c r="E164" s="617"/>
       <c r="F164" s="153" t="s">
         <v>69</v>
       </c>
@@ -11408,8 +11411,8 @@
     <row r="165" spans="1:22" ht="15.9" customHeight="1">
       <c r="A165" s="99"/>
       <c r="B165" s="91"/>
-      <c r="C165" s="605"/>
-      <c r="D165" s="606"/>
+      <c r="C165" s="619"/>
+      <c r="D165" s="620"/>
       <c r="E165" s="51"/>
       <c r="F165" s="48"/>
       <c r="G165" s="376"/>
@@ -11420,11 +11423,11 @@
     <row r="166" spans="1:22" ht="15.9" customHeight="1">
       <c r="A166" s="99"/>
       <c r="B166" s="91"/>
-      <c r="C166" s="607" t="str">
+      <c r="C166" s="682" t="str">
         <f>+C106</f>
         <v>Net Rent I</v>
       </c>
-      <c r="D166" s="608"/>
+      <c r="D166" s="683"/>
       <c r="E166" s="51"/>
       <c r="F166" s="48">
         <f>+F106</f>
@@ -11448,11 +11451,11 @@
     <row r="167" spans="1:22" ht="15.9" customHeight="1">
       <c r="A167" s="99"/>
       <c r="B167" s="91"/>
-      <c r="C167" s="607" t="str">
+      <c r="C167" s="682" t="str">
         <f>+C107</f>
         <v>Net Rent II</v>
       </c>
-      <c r="D167" s="608"/>
+      <c r="D167" s="683"/>
       <c r="E167" s="51"/>
       <c r="F167" s="48">
         <f>+F107</f>
@@ -11476,10 +11479,10 @@
     <row r="168" spans="1:22" ht="15.9" customHeight="1">
       <c r="A168" s="99"/>
       <c r="B168" s="139"/>
-      <c r="C168" s="612" t="s">
+      <c r="C168" s="678" t="s">
         <v>198</v>
       </c>
-      <c r="D168" s="613"/>
+      <c r="D168" s="679"/>
       <c r="E168" s="140"/>
       <c r="F168" s="141">
         <f>SUM(F166:F167)</f>
@@ -11504,8 +11507,8 @@
     <row r="169" spans="1:22" ht="15.9" customHeight="1">
       <c r="A169" s="99"/>
       <c r="B169" s="154"/>
-      <c r="C169" s="614"/>
-      <c r="D169" s="615"/>
+      <c r="C169" s="680"/>
+      <c r="D169" s="681"/>
       <c r="E169" s="67"/>
       <c r="F169" s="46"/>
       <c r="G169" s="373"/>
@@ -11518,11 +11521,11 @@
     <row r="170" spans="1:22" ht="15.9" customHeight="1">
       <c r="A170" s="99"/>
       <c r="B170" s="91"/>
-      <c r="C170" s="607" t="str">
+      <c r="C170" s="682" t="str">
         <f>+C119</f>
         <v xml:space="preserve">OpEx I </v>
       </c>
-      <c r="D170" s="608"/>
+      <c r="D170" s="683"/>
       <c r="E170" s="51"/>
       <c r="F170" s="48">
         <f>+F119</f>
@@ -11546,11 +11549,11 @@
     <row r="171" spans="1:22" ht="15.9" customHeight="1">
       <c r="A171" s="99"/>
       <c r="B171" s="91"/>
-      <c r="C171" s="607" t="str">
+      <c r="C171" s="682" t="str">
         <f>+C123</f>
         <v xml:space="preserve">OpEx II </v>
       </c>
-      <c r="D171" s="608"/>
+      <c r="D171" s="683"/>
       <c r="E171" s="51"/>
       <c r="F171" s="48">
         <f>+F123</f>
@@ -11573,10 +11576,10 @@
     <row r="172" spans="1:22" ht="15.9" customHeight="1">
       <c r="A172" s="99"/>
       <c r="B172" s="142"/>
-      <c r="C172" s="612" t="s">
+      <c r="C172" s="678" t="s">
         <v>199</v>
       </c>
-      <c r="D172" s="613"/>
+      <c r="D172" s="679"/>
       <c r="E172" s="143"/>
       <c r="F172" s="144">
         <f>SUM(F170:F171)</f>
@@ -11611,11 +11614,11 @@
     <row r="174" spans="1:22" ht="15.9" customHeight="1">
       <c r="A174" s="99"/>
       <c r="B174" s="91"/>
-      <c r="C174" s="607" t="str">
+      <c r="C174" s="682" t="str">
         <f>+C132</f>
         <v xml:space="preserve">Services </v>
       </c>
-      <c r="D174" s="608"/>
+      <c r="D174" s="683"/>
       <c r="E174" s="51"/>
       <c r="F174" s="48">
         <f>+F132</f>
@@ -11638,10 +11641,10 @@
     <row r="175" spans="1:22" ht="15.9" customHeight="1">
       <c r="A175" s="99"/>
       <c r="B175" s="142"/>
-      <c r="C175" s="612" t="s">
+      <c r="C175" s="678" t="s">
         <v>200</v>
       </c>
-      <c r="D175" s="613"/>
+      <c r="D175" s="679"/>
       <c r="E175" s="143"/>
       <c r="F175" s="144">
         <f>SUM(F174)</f>
@@ -11664,8 +11667,8 @@
     <row r="176" spans="1:22" ht="15.9" customHeight="1">
       <c r="A176" s="99"/>
       <c r="B176" s="91"/>
-      <c r="C176" s="605"/>
-      <c r="D176" s="606"/>
+      <c r="C176" s="619"/>
+      <c r="D176" s="620"/>
       <c r="E176" s="51"/>
       <c r="F176" s="48"/>
       <c r="G176" s="376"/>
@@ -11676,10 +11679,10 @@
     <row r="177" spans="1:19" ht="15.9" customHeight="1">
       <c r="A177" s="99"/>
       <c r="B177" s="142"/>
-      <c r="C177" s="612" t="s">
+      <c r="C177" s="678" t="s">
         <v>201</v>
       </c>
-      <c r="D177" s="613"/>
+      <c r="D177" s="679"/>
       <c r="E177" s="146"/>
       <c r="F177" s="141">
         <f>+F168+F172+F175</f>
@@ -11714,11 +11717,11 @@
     </row>
     <row r="179" spans="1:19" ht="15.9" customHeight="1">
       <c r="A179" s="99"/>
-      <c r="B179" s="599" t="s">
+      <c r="B179" s="602" t="s">
         <v>202</v>
       </c>
-      <c r="C179" s="600"/>
-      <c r="D179" s="601"/>
+      <c r="C179" s="603"/>
+      <c r="D179" s="618"/>
       <c r="E179" s="367"/>
       <c r="F179" s="367" t="s">
         <v>186</v>
@@ -11737,8 +11740,8 @@
     <row r="180" spans="1:19" ht="15.9" customHeight="1">
       <c r="A180" s="99"/>
       <c r="B180" s="91"/>
-      <c r="C180" s="605"/>
-      <c r="D180" s="606"/>
+      <c r="C180" s="619"/>
+      <c r="D180" s="620"/>
       <c r="E180" s="51"/>
       <c r="F180" s="48"/>
       <c r="G180" s="376"/>
@@ -11749,10 +11752,10 @@
     <row r="181" spans="1:19" ht="15.9" customHeight="1">
       <c r="A181" s="99"/>
       <c r="B181" s="91"/>
-      <c r="C181" s="596" t="s">
+      <c r="C181" s="604" t="s">
         <v>203</v>
       </c>
-      <c r="D181" s="595"/>
+      <c r="D181" s="605"/>
       <c r="E181" s="92"/>
       <c r="F181" s="93"/>
       <c r="G181" s="197">
@@ -11769,10 +11772,10 @@
     <row r="182" spans="1:19" ht="15.9" customHeight="1">
       <c r="A182" s="99"/>
       <c r="B182" s="91"/>
-      <c r="C182" s="594" t="s">
+      <c r="C182" s="598" t="s">
         <v>204</v>
       </c>
-      <c r="D182" s="595"/>
+      <c r="D182" s="605"/>
       <c r="E182" s="92"/>
       <c r="F182" s="93"/>
       <c r="G182" s="197">
@@ -11789,10 +11792,10 @@
     <row r="183" spans="1:19" ht="15.9" customHeight="1">
       <c r="A183" s="99"/>
       <c r="B183" s="91"/>
-      <c r="C183" s="594" t="s">
+      <c r="C183" s="598" t="s">
         <v>205</v>
       </c>
-      <c r="D183" s="604"/>
+      <c r="D183" s="599"/>
       <c r="E183" s="92"/>
       <c r="F183" s="93"/>
       <c r="G183" s="197">
@@ -11806,10 +11809,10 @@
     <row r="184" spans="1:19" ht="15.9" customHeight="1">
       <c r="A184" s="99"/>
       <c r="B184" s="91"/>
-      <c r="C184" s="594" t="s">
+      <c r="C184" s="598" t="s">
         <v>206</v>
       </c>
-      <c r="D184" s="595"/>
+      <c r="D184" s="605"/>
       <c r="E184" s="92"/>
       <c r="F184" s="93"/>
       <c r="G184" s="197">
@@ -11826,10 +11829,10 @@
     <row r="185" spans="1:19" ht="15.9" customHeight="1">
       <c r="A185" s="99"/>
       <c r="B185" s="91"/>
-      <c r="C185" s="594" t="s">
+      <c r="C185" s="598" t="s">
         <v>207</v>
       </c>
-      <c r="D185" s="595"/>
+      <c r="D185" s="605"/>
       <c r="E185" s="92"/>
       <c r="F185" s="93"/>
       <c r="G185" s="197">
@@ -11857,25 +11860,25 @@
     </row>
     <row r="187" spans="1:19" ht="15.9" customHeight="1" thickBot="1">
       <c r="A187" s="99"/>
-      <c r="B187" s="629" t="s">
+      <c r="B187" s="675" t="s">
         <v>208</v>
       </c>
-      <c r="C187" s="630"/>
-      <c r="D187" s="630"/>
-      <c r="E187" s="630"/>
-      <c r="F187" s="630"/>
-      <c r="G187" s="630"/>
-      <c r="H187" s="630"/>
-      <c r="I187" s="630"/>
-      <c r="J187" s="631"/>
+      <c r="C187" s="676"/>
+      <c r="D187" s="676"/>
+      <c r="E187" s="676"/>
+      <c r="F187" s="676"/>
+      <c r="G187" s="676"/>
+      <c r="H187" s="676"/>
+      <c r="I187" s="676"/>
+      <c r="J187" s="677"/>
     </row>
     <row r="188" spans="1:19" ht="15.9" customHeight="1">
       <c r="A188" s="43"/>
       <c r="B188" s="156"/>
-      <c r="C188" s="609" t="s">
+      <c r="C188" s="617" t="s">
         <v>209</v>
       </c>
-      <c r="D188" s="609"/>
+      <c r="D188" s="617"/>
       <c r="E188" s="366"/>
       <c r="F188" s="366" t="s">
         <v>186</v>
@@ -11883,7 +11886,7 @@
       <c r="G188" s="160" t="s">
         <v>186</v>
       </c>
-      <c r="H188" s="626"/>
+      <c r="H188" s="672"/>
       <c r="I188" s="217" t="s">
         <v>63</v>
       </c>
@@ -11894,17 +11897,17 @@
     <row r="189" spans="1:19" ht="15.9" customHeight="1">
       <c r="A189" s="43"/>
       <c r="B189" s="154"/>
-      <c r="C189" s="596" t="s">
+      <c r="C189" s="604" t="s">
         <v>210</v>
       </c>
-      <c r="D189" s="595"/>
+      <c r="D189" s="605"/>
       <c r="E189" s="155"/>
       <c r="F189" s="155"/>
       <c r="G189" s="94">
         <f>+G20</f>
         <v>0</v>
       </c>
-      <c r="H189" s="627"/>
+      <c r="H189" s="673"/>
       <c r="I189" s="154"/>
       <c r="J189" s="94">
         <f>+G189/J5</f>
@@ -11914,17 +11917,17 @@
     <row r="190" spans="1:19" ht="15.9" customHeight="1">
       <c r="A190" s="43"/>
       <c r="B190" s="154"/>
-      <c r="C190" s="596" t="s">
+      <c r="C190" s="604" t="s">
         <v>211</v>
       </c>
-      <c r="D190" s="595"/>
+      <c r="D190" s="605"/>
       <c r="E190" s="155"/>
       <c r="F190" s="155"/>
       <c r="G190" s="94">
         <f>+G189*G23</f>
         <v>0</v>
       </c>
-      <c r="H190" s="627"/>
+      <c r="H190" s="673"/>
       <c r="I190" s="154"/>
       <c r="J190" s="94">
         <f>+J189*J23</f>
@@ -11934,17 +11937,17 @@
     <row r="191" spans="1:19" ht="15.9" customHeight="1">
       <c r="A191" s="43"/>
       <c r="B191" s="154"/>
-      <c r="C191" s="610" t="s">
+      <c r="C191" s="642" t="s">
         <v>212</v>
       </c>
-      <c r="D191" s="610"/>
+      <c r="D191" s="642"/>
       <c r="E191" s="155"/>
       <c r="F191" s="155"/>
       <c r="G191" s="94">
         <f>+G190*25%</f>
         <v>0</v>
       </c>
-      <c r="H191" s="627"/>
+      <c r="H191" s="673"/>
       <c r="I191" s="154"/>
       <c r="J191" s="94">
         <f>+J190*25%</f>
@@ -11954,17 +11957,17 @@
     <row r="192" spans="1:19" ht="15.9" customHeight="1">
       <c r="A192" s="43"/>
       <c r="B192" s="154"/>
-      <c r="C192" s="594" t="s">
+      <c r="C192" s="598" t="s">
         <v>213</v>
       </c>
-      <c r="D192" s="595"/>
+      <c r="D192" s="605"/>
       <c r="E192" s="155"/>
       <c r="F192" s="155"/>
       <c r="G192" s="94">
         <f>+G191*1%</f>
         <v>0</v>
       </c>
-      <c r="H192" s="627"/>
+      <c r="H192" s="673"/>
       <c r="I192" s="154"/>
       <c r="J192" s="94">
         <f>G192/J5</f>
@@ -11974,17 +11977,17 @@
     <row r="193" spans="1:20" ht="15.9" customHeight="1">
       <c r="A193" s="43"/>
       <c r="B193" s="154"/>
-      <c r="C193" s="594" t="s">
+      <c r="C193" s="598" t="s">
         <v>214</v>
       </c>
-      <c r="D193" s="595"/>
+      <c r="D193" s="605"/>
       <c r="E193" s="155"/>
       <c r="F193" s="155"/>
       <c r="G193" s="94">
         <f>G192*0.5</f>
         <v>0</v>
       </c>
-      <c r="H193" s="627"/>
+      <c r="H193" s="673"/>
       <c r="I193" s="154"/>
       <c r="J193" s="94">
         <f>G193/J5</f>
@@ -11994,17 +11997,17 @@
     <row r="194" spans="1:20" ht="15.9" customHeight="1" thickBot="1">
       <c r="A194" s="43"/>
       <c r="B194" s="154"/>
-      <c r="C194" s="610" t="s">
+      <c r="C194" s="642" t="s">
         <v>215</v>
       </c>
-      <c r="D194" s="610"/>
+      <c r="D194" s="642"/>
       <c r="E194" s="155"/>
       <c r="F194" s="155"/>
       <c r="G194" s="102">
         <f>G82</f>
         <v>565315.30184775486</v>
       </c>
-      <c r="H194" s="627"/>
+      <c r="H194" s="673"/>
       <c r="I194" s="154"/>
       <c r="J194" s="102">
         <f>+J192+J193</f>
@@ -12014,8 +12017,8 @@
     <row r="195" spans="1:20" ht="15.9" customHeight="1">
       <c r="A195" s="158"/>
       <c r="B195" s="370"/>
-      <c r="C195" s="611"/>
-      <c r="D195" s="611"/>
+      <c r="C195" s="610"/>
+      <c r="D195" s="610"/>
       <c r="E195" s="367"/>
       <c r="F195" s="367" t="s">
         <v>186</v>
@@ -12023,7 +12026,7 @@
       <c r="G195" s="45" t="s">
         <v>186</v>
       </c>
-      <c r="H195" s="627"/>
+      <c r="H195" s="673"/>
       <c r="I195" s="217" t="s">
         <v>63</v>
       </c>
@@ -12034,17 +12037,17 @@
     <row r="196" spans="1:20" ht="15.9" customHeight="1">
       <c r="A196" s="66"/>
       <c r="B196" s="91"/>
-      <c r="C196" s="596" t="s">
+      <c r="C196" s="604" t="s">
         <v>216</v>
       </c>
-      <c r="D196" s="595"/>
+      <c r="D196" s="605"/>
       <c r="E196" s="50"/>
       <c r="F196" s="42"/>
       <c r="G196" s="94">
         <f>+G54</f>
         <v>72</v>
       </c>
-      <c r="H196" s="627"/>
+      <c r="H196" s="673"/>
       <c r="I196" s="83"/>
       <c r="J196" s="94">
         <f>+J54</f>
@@ -12054,17 +12057,17 @@
     <row r="197" spans="1:20" ht="15.9" customHeight="1">
       <c r="A197" s="66"/>
       <c r="B197" s="91"/>
-      <c r="C197" s="596" t="s">
+      <c r="C197" s="604" t="s">
         <v>217</v>
       </c>
-      <c r="D197" s="595"/>
+      <c r="D197" s="605"/>
       <c r="E197" s="50"/>
       <c r="F197" s="42"/>
       <c r="G197" s="94">
         <f>F140</f>
         <v>9515</v>
       </c>
-      <c r="H197" s="627"/>
+      <c r="H197" s="673"/>
       <c r="I197" s="83"/>
       <c r="J197" s="94">
         <f>I140</f>
@@ -12074,17 +12077,17 @@
     <row r="198" spans="1:20" ht="15.9" customHeight="1">
       <c r="A198" s="112"/>
       <c r="B198" s="91"/>
-      <c r="C198" s="596" t="s">
+      <c r="C198" s="604" t="s">
         <v>218</v>
       </c>
-      <c r="D198" s="595"/>
+      <c r="D198" s="605"/>
       <c r="E198" s="50"/>
       <c r="F198" s="42"/>
       <c r="G198" s="103">
         <f>+F60</f>
         <v>129</v>
       </c>
-      <c r="H198" s="627"/>
+      <c r="H198" s="673"/>
       <c r="I198" s="83"/>
       <c r="J198" s="103">
         <f>+I60</f>
@@ -12094,17 +12097,17 @@
     <row r="199" spans="1:20" ht="15.9" customHeight="1">
       <c r="A199" s="66"/>
       <c r="B199" s="91"/>
-      <c r="C199" s="596" t="s">
+      <c r="C199" s="604" t="s">
         <v>218</v>
       </c>
-      <c r="D199" s="595"/>
+      <c r="D199" s="605"/>
       <c r="E199" s="50"/>
       <c r="F199" s="42"/>
       <c r="G199" s="94">
         <f>(G197*G198*G196)</f>
         <v>88375320</v>
       </c>
-      <c r="H199" s="627"/>
+      <c r="H199" s="673"/>
       <c r="I199" s="83"/>
       <c r="J199" s="94">
         <f>+G199/$J$5</f>
@@ -12114,17 +12117,17 @@
     <row r="200" spans="1:20" ht="15.9" customHeight="1">
       <c r="A200" s="66"/>
       <c r="B200" s="91"/>
-      <c r="C200" s="596" t="s">
+      <c r="C200" s="604" t="s">
         <v>219</v>
       </c>
-      <c r="D200" s="595"/>
+      <c r="D200" s="605"/>
       <c r="E200" s="50"/>
       <c r="F200" s="42"/>
       <c r="G200" s="94">
         <f>G199/G196*12</f>
         <v>14729220</v>
       </c>
-      <c r="H200" s="627"/>
+      <c r="H200" s="673"/>
       <c r="I200" s="83"/>
       <c r="J200" s="94">
         <f>+G200/$J$5</f>
@@ -12134,17 +12137,17 @@
     <row r="201" spans="1:20" ht="15.9" customHeight="1">
       <c r="A201" s="66"/>
       <c r="B201" s="91"/>
-      <c r="C201" s="596" t="s">
+      <c r="C201" s="604" t="s">
         <v>220</v>
       </c>
-      <c r="D201" s="595"/>
+      <c r="D201" s="605"/>
       <c r="E201" s="50"/>
       <c r="F201" s="42"/>
       <c r="G201" s="94">
         <f>(+G220*115%)/5</f>
         <v>3026339.9999999995</v>
       </c>
-      <c r="H201" s="627"/>
+      <c r="H201" s="673"/>
       <c r="I201" s="83"/>
       <c r="J201" s="94">
         <f>+G201/$J$5</f>
@@ -12154,17 +12157,17 @@
     <row r="202" spans="1:20" ht="15.9" customHeight="1">
       <c r="A202" s="66"/>
       <c r="B202" s="91"/>
-      <c r="C202" s="596" t="s">
+      <c r="C202" s="604" t="s">
         <v>221</v>
       </c>
-      <c r="D202" s="595"/>
+      <c r="D202" s="605"/>
       <c r="E202" s="50"/>
       <c r="F202" s="42"/>
       <c r="G202" s="94">
         <f>(+I220*115%)/5</f>
         <v>2765157.6185172233</v>
       </c>
-      <c r="H202" s="627"/>
+      <c r="H202" s="673"/>
       <c r="I202" s="83"/>
       <c r="J202" s="94">
         <f>+G202/$J$5</f>
@@ -12174,17 +12177,17 @@
     <row r="203" spans="1:20" ht="15.9" customHeight="1">
       <c r="A203" s="66"/>
       <c r="B203" s="91"/>
-      <c r="C203" s="596" t="s">
+      <c r="C203" s="604" t="s">
         <v>36</v>
       </c>
-      <c r="D203" s="595"/>
+      <c r="D203" s="605"/>
       <c r="E203" s="50"/>
       <c r="F203" s="42"/>
       <c r="G203" s="94">
         <f>+G67</f>
         <v>11418000</v>
       </c>
-      <c r="H203" s="627"/>
+      <c r="H203" s="673"/>
       <c r="I203" s="83"/>
       <c r="J203" s="94">
         <f>+G203/$J$5</f>
@@ -12194,17 +12197,17 @@
     <row r="204" spans="1:20" ht="15.9" customHeight="1">
       <c r="A204" s="66"/>
       <c r="B204" s="91"/>
-      <c r="C204" s="594" t="s">
+      <c r="C204" s="598" t="s">
         <v>222</v>
       </c>
-      <c r="D204" s="595"/>
+      <c r="D204" s="605"/>
       <c r="E204" s="50"/>
       <c r="F204" s="42"/>
       <c r="G204" s="94">
         <f>(G200+G201+G202+G203)*1.18</f>
         <v>37687686.789850324</v>
       </c>
-      <c r="H204" s="627"/>
+      <c r="H204" s="673"/>
       <c r="I204" s="83"/>
       <c r="J204" s="94">
         <f>+J200+J201+J202+J203</f>
@@ -12214,17 +12217,17 @@
     <row r="205" spans="1:20" ht="15.9" customHeight="1">
       <c r="A205" s="66"/>
       <c r="B205" s="91"/>
-      <c r="C205" s="594" t="s">
+      <c r="C205" s="598" t="s">
         <v>223</v>
       </c>
-      <c r="D205" s="595"/>
+      <c r="D205" s="605"/>
       <c r="E205" s="50"/>
       <c r="F205" s="42"/>
       <c r="G205" s="94">
         <f>G204*1%</f>
         <v>376876.86789850326</v>
       </c>
-      <c r="H205" s="627"/>
+      <c r="H205" s="673"/>
       <c r="I205" s="83"/>
       <c r="J205" s="94">
         <f>J204*1%</f>
@@ -12234,17 +12237,17 @@
     <row r="206" spans="1:20" ht="15.9" customHeight="1">
       <c r="A206" s="66"/>
       <c r="B206" s="91"/>
-      <c r="C206" s="596" t="s">
+      <c r="C206" s="604" t="s">
         <v>224</v>
       </c>
-      <c r="D206" s="595"/>
+      <c r="D206" s="605"/>
       <c r="E206" s="50"/>
       <c r="F206" s="42"/>
       <c r="G206" s="94">
         <f>G204*0.5%</f>
         <v>188438.43394925163</v>
       </c>
-      <c r="H206" s="627"/>
+      <c r="H206" s="673"/>
       <c r="I206" s="83"/>
       <c r="J206" s="94">
         <f>J204*0.5%</f>
@@ -12254,17 +12257,17 @@
     <row r="207" spans="1:20" ht="15.9" customHeight="1">
       <c r="A207" s="66"/>
       <c r="B207" s="91"/>
-      <c r="C207" s="597" t="s">
+      <c r="C207" s="600" t="s">
         <v>215</v>
       </c>
-      <c r="D207" s="598"/>
+      <c r="D207" s="601"/>
       <c r="E207" s="50"/>
       <c r="F207" s="42"/>
       <c r="G207" s="94">
         <f>G205+G206</f>
         <v>565315.30184775486</v>
       </c>
-      <c r="H207" s="627"/>
+      <c r="H207" s="673"/>
       <c r="I207" s="83"/>
       <c r="J207" s="94">
         <v>0</v>
@@ -12279,7 +12282,7 @@
       <c r="E208" s="72"/>
       <c r="F208" s="43"/>
       <c r="G208" s="325"/>
-      <c r="H208" s="627"/>
+      <c r="H208" s="673"/>
       <c r="I208" s="86"/>
       <c r="J208" s="73"/>
     </row>
@@ -12301,7 +12304,7 @@
       <c r="G209" s="153" t="s">
         <v>229</v>
       </c>
-      <c r="H209" s="627"/>
+      <c r="H209" s="673"/>
       <c r="I209" s="367" t="s">
         <v>230</v>
       </c>
@@ -12327,7 +12330,7 @@
         <f>'Lease Rent'!P39</f>
         <v>1360000</v>
       </c>
-      <c r="H210" s="627"/>
+      <c r="H210" s="673"/>
       <c r="I210" s="93">
         <f>'Lease Rent'!O39</f>
         <v>1178337.5999999999</v>
@@ -12357,7 +12360,7 @@
         <f>'Lease Rent'!P51</f>
         <v>2040000</v>
       </c>
-      <c r="H211" s="627"/>
+      <c r="H211" s="673"/>
       <c r="I211" s="93">
         <f>'Lease Rent'!O51</f>
         <v>1826423.2800000005</v>
@@ -12386,7 +12389,7 @@
         <f>'Lease Rent'!P63</f>
         <v>2040000</v>
       </c>
-      <c r="H212" s="627"/>
+      <c r="H212" s="673"/>
       <c r="I212" s="93">
         <f>'Lease Rent'!O63</f>
         <v>1917744.4440000001</v>
@@ -12415,7 +12418,7 @@
         <f>'Lease Rent'!P75</f>
         <v>2244000</v>
       </c>
-      <c r="H213" s="627"/>
+      <c r="H213" s="673"/>
       <c r="I213" s="93">
         <f>'Lease Rent'!O75</f>
         <v>2013631.6662000006</v>
@@ -12444,7 +12447,7 @@
         <f>'Lease Rent'!P87</f>
         <v>2345999.9999999995</v>
       </c>
-      <c r="H214" s="627"/>
+      <c r="H214" s="673"/>
       <c r="I214" s="93">
         <f>'Lease Rent'!O87</f>
         <v>2114313.2495100005</v>
@@ -12473,7 +12476,7 @@
         <f>'Lease Rent'!P99</f>
         <v>2345999.9999999995</v>
       </c>
-      <c r="H215" s="627"/>
+      <c r="H215" s="673"/>
       <c r="I215" s="93">
         <f>'Lease Rent'!O99</f>
         <v>2220028.9119855007</v>
@@ -12501,7 +12504,7 @@
         <f>'Lease Rent'!P103</f>
         <v>781999.99999999988</v>
       </c>
-      <c r="H216" s="627"/>
+      <c r="H216" s="673"/>
       <c r="I216" s="93">
         <f>'Lease Rent'!O103</f>
         <v>751945.27664025011</v>
@@ -12524,7 +12527,7 @@
         <f>'Lease Rent'!R10</f>
         <v>0</v>
       </c>
-      <c r="H217" s="627"/>
+      <c r="H217" s="673"/>
       <c r="I217" s="289"/>
       <c r="J217" s="103"/>
     </row>
@@ -12541,7 +12544,7 @@
         <v>0</v>
       </c>
       <c r="G218" s="110"/>
-      <c r="H218" s="627"/>
+      <c r="H218" s="673"/>
       <c r="I218" s="93"/>
       <c r="J218" s="103"/>
     </row>
@@ -12555,7 +12558,7 @@
       <c r="E219" s="109"/>
       <c r="F219" s="220"/>
       <c r="G219" s="110"/>
-      <c r="H219" s="627"/>
+      <c r="H219" s="673"/>
       <c r="I219" s="93"/>
       <c r="J219" s="103"/>
     </row>
@@ -12578,7 +12581,7 @@
         <f>SUM(G210:G219)</f>
         <v>13158000</v>
       </c>
-      <c r="H220" s=